--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -5,29 +5,30 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E1566A-D666-476A-8D67-45ABB84859F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB1D7AD-EEFF-4C1B-AB17-7EFE78F4EA5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
-    <sheet name="オブジェクト" sheetId="1" r:id="rId1"/>
-    <sheet name="バトルフロー" sheetId="2" r:id="rId2"/>
-    <sheet name="コード" sheetId="5" r:id="rId3"/>
-    <sheet name="スキル" sheetId="3" r:id="rId4"/>
-    <sheet name="モンスター" sheetId="4" r:id="rId5"/>
-    <sheet name="モンスタースキル" sheetId="6" r:id="rId6"/>
-    <sheet name="戦績レポート" sheetId="7" r:id="rId7"/>
-    <sheet name="各種設定" sheetId="8" r:id="rId8"/>
-    <sheet name="guitarCrawler" sheetId="9" r:id="rId9"/>
-    <sheet name="public API" sheetId="10" r:id="rId10"/>
-    <sheet name="guiatr gallery" sheetId="11" r:id="rId11"/>
+    <sheet name="architecture" sheetId="12" r:id="rId1"/>
+    <sheet name="オブジェクト" sheetId="1" r:id="rId2"/>
+    <sheet name="バトルフロー" sheetId="2" r:id="rId3"/>
+    <sheet name="コード" sheetId="5" r:id="rId4"/>
+    <sheet name="スキル" sheetId="3" r:id="rId5"/>
+    <sheet name="モンスター" sheetId="4" r:id="rId6"/>
+    <sheet name="モンスタースキル" sheetId="6" r:id="rId7"/>
+    <sheet name="戦績レポート" sheetId="7" r:id="rId8"/>
+    <sheet name="各種設定" sheetId="8" r:id="rId9"/>
+    <sheet name="guitarCrawler" sheetId="9" r:id="rId10"/>
+    <sheet name="public API" sheetId="10" r:id="rId11"/>
+    <sheet name="guiatr gallery" sheetId="11" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">スキル!$C$3:$O$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">モンスタースキル!$C$4:$C$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">スキル!$C$3:$O$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">モンスタースキル!$C$4:$C$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3853" uniqueCount="1718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3854" uniqueCount="1719">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -7495,6 +7496,10 @@
     <rPh sb="0" eb="2">
       <t>ケンサク</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -7887,7 +7892,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -8041,6 +8046,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -8061,6 +8070,2902 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>457199</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>87086</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>97970</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>206828</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8C55531-860A-5319-7BBF-E2A078523B42}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1132113" y="1001486"/>
+          <a:ext cx="3015343" cy="359228"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Virtual</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Private Server (Ubuntu)</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>359229</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>54427</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>500743</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>185058</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E483A0DB-56BA-4DD4-9E26-9FF6A029F090}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1709058" y="1436913"/>
+          <a:ext cx="1491342" cy="370116"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Docker</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t> compose</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>87086</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>97972</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>478972</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>185057</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78782136-3A96-4BC9-9D11-49F8F8A229ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4811486" y="1012372"/>
+          <a:ext cx="391886" cy="326571"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>80</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>97972</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>478972</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>195943</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28C46FA2-471D-45BF-AC3E-A569A1153DB7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5399314" y="1012372"/>
+          <a:ext cx="478972" cy="337457"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>443</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>620486</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>76198</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>87085</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>43544</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="正方形/長方形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE5C78AC-1793-40BF-BCF9-ED9EA6812982}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4669972" y="1687284"/>
+          <a:ext cx="1491342" cy="1349831"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Reverse Proxy</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>HTTPS</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>終端</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Let's Encrypt</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>nginx</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>185055</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>555170</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>141516</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="正方形/長方形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4D6139D-A3AE-4C1B-BD6E-08B469F01FF5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2209798" y="3614057"/>
+          <a:ext cx="1719943" cy="1578430"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>WebUI(Frontend)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>React</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Type Script</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Vite</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>styled-component</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>620490</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>141514</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>435433</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>108857</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="正方形/長方形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D386B14-A92D-452E-BC14-60096F0F165A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4669976" y="3363685"/>
+          <a:ext cx="1839686" cy="1567543"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Public REST API</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>ギターデータ取得</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>GET method only</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>/public/v1/guitars</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>C# ASP.NET Core</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>598712</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>65312</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>10884</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>65313</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="正方形/長方形 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F284BE6B-1180-44A1-A823-BE8038DAE00E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4648198" y="5116283"/>
+          <a:ext cx="2111829" cy="1828801"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Private API(Backend)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>各種サーバー処理</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>React</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>と連携</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>C# ASP.NET Core</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>NpgSQL</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Dapper(ORM)</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>163285</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>97973</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>435429</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>10889</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="正方形/長方形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30C18E0F-A8AC-419F-9670-66E8E51FEAD7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4887685" y="97973"/>
+          <a:ext cx="947058" cy="370116"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Internet</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>674913</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>511628</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>32659</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="正方形/長方形 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D68C3F2B-67BF-4CEF-AEB9-68168C9139EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8098970" y="6041571"/>
+          <a:ext cx="1186544" cy="870859"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>DB</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>PostgreSQL</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>598714</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>43541</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>217715</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>174173</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="正方形/長方形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29A9CE31-1714-4C01-BEBC-A3089B772AAF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10722428" y="2579912"/>
+          <a:ext cx="1643744" cy="2645232"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Batch</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Web Crawler</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>スクレイピング</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>ギターデータ収集</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>データ正規化</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Go</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>言語</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>colly</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>chromedp</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>goquery</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>cron</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>370113</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>195941</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>468085</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="正方形/長方形 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A2E2966-54D2-49B4-8BDE-79D6EE8CA187}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12518570" y="3646712"/>
+          <a:ext cx="2122715" cy="1567545"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Batch</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Monster auto</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t> battle</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>戦績、試合結果を記録</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>C# </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>コンソールアプリ</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>cron</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>326570</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>217714</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>163286</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>21771</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="正方形/長方形 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E28A91DE-A273-4540-BBB2-CEA5D1EFF116}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15849599" y="217714"/>
+          <a:ext cx="1861458" cy="1883228"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>各種メーカーサイト</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Fender</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Gibson</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>ESP</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>...</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>...</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>511628</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>217717</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>517071</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>97972</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="直線矢印コネクタ 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{181C96B4-2968-14BC-4907-2AE886BE4474}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="22" idx="2"/>
+          <a:endCxn id="20" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7260771" y="446317"/>
+          <a:ext cx="5443" cy="566055"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>54428</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>97972</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>174171</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="正方形/長方形 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B79BA4B-3DB3-4CC9-A9DC-13BA876CE735}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6803571" y="1012372"/>
+          <a:ext cx="925286" cy="315685"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>SSH</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t> Port</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>631370</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>76201</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>391885</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>217717</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="正方形/長方形 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D0FA7EB-AC6B-4E22-A356-0F69223F2504}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6705599" y="76201"/>
+          <a:ext cx="1110343" cy="370116"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>SSH Client</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>283029</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>10889</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>636814</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>97972</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="26" name="直線矢印コネクタ 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B4C05B5-3140-4912-9C75-127F73BF9D4C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="13" idx="2"/>
+          <a:endCxn id="5" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="5007429" y="468089"/>
+          <a:ext cx="353785" cy="544283"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>636814</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>10889</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>239486</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>97972</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="27" name="直線矢印コネクタ 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE9867E9-3029-43FB-8B39-1D6D05DEF7C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="13" idx="2"/>
+          <a:endCxn id="6" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5361214" y="468089"/>
+          <a:ext cx="277586" cy="544283"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>261257</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>174172</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>261257</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>76201</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="28" name="直線矢印コネクタ 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62B32069-DC27-45AC-97CB-F3FC9B9860E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4985657" y="1328058"/>
+          <a:ext cx="0" cy="359229"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>239486</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>239486</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>65315</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="29" name="直線矢印コネクタ 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF45F80C-A40C-4E99-BD42-10D6D8C8FE7A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5638800" y="1317172"/>
+          <a:ext cx="0" cy="359229"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>337457</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>195943</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>43543</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="30" name="直線矢印コネクタ 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63B458E1-3C27-41C5-8E76-4F2EC40B17B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="5061857" y="1349829"/>
+          <a:ext cx="381000" cy="315685"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>370113</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>54429</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>620486</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="39" name="直線矢印コネクタ 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5930D49-108D-4699-9131-A021A1411000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="8" idx="1"/>
+          <a:endCxn id="10" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3069770" y="2362200"/>
+          <a:ext cx="1600202" cy="1251857"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>370113</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>141516</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>598712</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>65313</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="41" name="直線矢印コネクタ 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B8324AD-6A96-4404-9CDB-D3D773980F52}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="10" idx="2"/>
+          <a:endCxn id="12" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3069770" y="5192487"/>
+          <a:ext cx="1578428" cy="838197"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>16329</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>43544</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>190505</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>141514</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="44" name="直線矢印コネクタ 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E4DD22E-DEC8-4D35-A66E-813814A69F12}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="8" idx="2"/>
+          <a:endCxn id="11" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5415643" y="3037115"/>
+          <a:ext cx="174176" cy="326570"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>555170</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>10886</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>620490</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="48" name="直線矢印コネクタ 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{281C2595-C16A-4D7B-9B80-BB64ECEA9DAD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="10" idx="3"/>
+          <a:endCxn id="11" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="3929741" y="4147457"/>
+          <a:ext cx="740235" cy="255815"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>435433</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>10886</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>589461</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="51" name="直線矢印コネクタ 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88548ED9-1736-42F2-B38A-708120F90580}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="11" idx="3"/>
+          <a:endCxn id="14" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6509662" y="4147457"/>
+          <a:ext cx="2178770" cy="1894114"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>10884</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>65313</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>667293</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>54430</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="54" name="直線矢印コネクタ 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A906D93D-423F-491C-9CF1-049A51D5A558}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="12" idx="3"/>
+          <a:endCxn id="14" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6760027" y="6030684"/>
+          <a:ext cx="1331323" cy="446317"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>511628</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>174173</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>70757</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>54430</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="59" name="直線矢印コネクタ 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18D19B57-AEFC-4A7E-85A2-72FAC21A9EB8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="14" idx="3"/>
+          <a:endCxn id="15" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="9285514" y="5225144"/>
+          <a:ext cx="2258786" cy="1251857"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>511628</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>81642</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>54430</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="61" name="直線矢印コネクタ 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A155F7F0-BBD8-431F-BDA8-909A0A4DC0DE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="14" idx="3"/>
+          <a:endCxn id="16" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="9285514" y="5214257"/>
+          <a:ext cx="4294414" cy="1262744"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>70757</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>5442</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>326570</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>43541</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="85" name="直線矢印コネクタ 84">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B92EBDC-5337-4878-B5E1-5067C05B447D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="15" idx="0"/>
+          <a:endCxn id="17" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="11544300" y="1159328"/>
+          <a:ext cx="4305299" cy="1420584"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -11180,7 +14085,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -11569,13 +14474,750 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6672014-33B5-48C4-9202-55E4E667EEEF}">
+  <dimension ref="C5:AA32"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="16384" width="9" style="5"/>
+    <col min="2" max="3" width="8.796875" customWidth="1"/>
+    <col min="27" max="27" width="4.3984375" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="5" spans="3:27" ht="18.600000000000001" thickBot="1">
+      <c r="V5" s="67"/>
+      <c r="W5" s="67"/>
+    </row>
+    <row r="6" spans="3:27">
+      <c r="C6" s="95"/>
+      <c r="D6" s="96"/>
+      <c r="E6" s="96"/>
+      <c r="F6" s="96"/>
+      <c r="G6" s="96"/>
+      <c r="H6" s="96"/>
+      <c r="I6" s="96"/>
+      <c r="J6" s="96"/>
+      <c r="K6" s="96"/>
+      <c r="L6" s="96"/>
+      <c r="M6" s="96"/>
+      <c r="N6" s="96"/>
+      <c r="O6" s="96"/>
+      <c r="P6" s="96"/>
+      <c r="Q6" s="96"/>
+      <c r="R6" s="96"/>
+      <c r="S6" s="96"/>
+      <c r="T6" s="96"/>
+      <c r="U6" s="96"/>
+      <c r="V6" s="98"/>
+      <c r="W6" s="97"/>
+      <c r="X6" s="98"/>
+      <c r="Y6" s="98"/>
+      <c r="Z6" s="98"/>
+      <c r="AA6" s="98"/>
+    </row>
+    <row r="7" spans="3:27">
+      <c r="C7" s="64"/>
+      <c r="D7" s="98"/>
+      <c r="E7" s="98"/>
+      <c r="F7" s="98"/>
+      <c r="G7" s="98"/>
+      <c r="H7" s="98"/>
+      <c r="I7" s="98"/>
+      <c r="J7" s="98"/>
+      <c r="K7" s="98"/>
+      <c r="L7" s="98"/>
+      <c r="M7" s="98"/>
+      <c r="N7" s="98"/>
+      <c r="O7" s="98"/>
+      <c r="P7" s="98"/>
+      <c r="Q7" s="98"/>
+      <c r="R7" s="98"/>
+      <c r="S7" s="98"/>
+      <c r="T7" s="98"/>
+      <c r="U7" s="98"/>
+      <c r="V7" s="98"/>
+      <c r="W7" s="65"/>
+      <c r="X7" s="98"/>
+      <c r="Y7" s="98"/>
+      <c r="Z7" s="98"/>
+      <c r="AA7" s="98"/>
+    </row>
+    <row r="8" spans="3:27">
+      <c r="C8" s="64"/>
+      <c r="D8" s="98"/>
+      <c r="E8" s="98"/>
+      <c r="F8" s="98"/>
+      <c r="G8" s="98"/>
+      <c r="H8" s="98"/>
+      <c r="I8" s="98"/>
+      <c r="J8" s="98"/>
+      <c r="K8" s="98"/>
+      <c r="L8" s="98"/>
+      <c r="M8" s="98"/>
+      <c r="N8" s="98"/>
+      <c r="O8" s="98"/>
+      <c r="P8" s="98"/>
+      <c r="Q8" s="98"/>
+      <c r="R8" s="98"/>
+      <c r="S8" s="98"/>
+      <c r="T8" s="98"/>
+      <c r="U8" s="98"/>
+      <c r="V8" s="98"/>
+      <c r="W8" s="65"/>
+      <c r="X8" s="98"/>
+      <c r="Y8" s="98"/>
+      <c r="Z8" s="98"/>
+      <c r="AA8" s="98"/>
+    </row>
+    <row r="9" spans="3:27" ht="18.600000000000001" thickBot="1">
+      <c r="C9" s="64"/>
+      <c r="D9" s="98"/>
+      <c r="E9" s="98"/>
+      <c r="F9" s="98"/>
+      <c r="G9" s="98"/>
+      <c r="H9" s="98"/>
+      <c r="I9" s="98"/>
+      <c r="J9" s="98"/>
+      <c r="K9" s="98"/>
+      <c r="L9" s="98" t="s">
+        <v>1718</v>
+      </c>
+      <c r="M9" s="98"/>
+      <c r="N9" s="98"/>
+      <c r="O9" s="98"/>
+      <c r="P9" s="98"/>
+      <c r="Q9" s="98"/>
+      <c r="R9" s="98"/>
+      <c r="S9" s="98"/>
+      <c r="T9" s="98"/>
+      <c r="U9" s="98"/>
+      <c r="V9" s="98"/>
+      <c r="W9" s="65"/>
+      <c r="X9" s="98"/>
+      <c r="Y9" s="98"/>
+      <c r="Z9" s="98"/>
+      <c r="AA9" s="98"/>
+    </row>
+    <row r="10" spans="3:27">
+      <c r="C10" s="64"/>
+      <c r="D10" s="95"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="96"/>
+      <c r="H10" s="96"/>
+      <c r="I10" s="96"/>
+      <c r="J10" s="96"/>
+      <c r="K10" s="96"/>
+      <c r="L10" s="96"/>
+      <c r="M10" s="96"/>
+      <c r="N10" s="96"/>
+      <c r="O10" s="96"/>
+      <c r="P10" s="96"/>
+      <c r="Q10" s="96"/>
+      <c r="R10" s="96"/>
+      <c r="S10" s="96"/>
+      <c r="T10" s="96"/>
+      <c r="U10" s="96"/>
+      <c r="V10" s="97"/>
+      <c r="W10" s="65"/>
+      <c r="X10" s="98"/>
+      <c r="Y10" s="98"/>
+      <c r="Z10" s="98"/>
+      <c r="AA10" s="98"/>
+    </row>
+    <row r="11" spans="3:27">
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98"/>
+      <c r="H11" s="98"/>
+      <c r="I11" s="98"/>
+      <c r="J11" s="98"/>
+      <c r="K11" s="98"/>
+      <c r="L11" s="98"/>
+      <c r="M11" s="98"/>
+      <c r="N11" s="98"/>
+      <c r="O11" s="98"/>
+      <c r="P11" s="98"/>
+      <c r="Q11" s="98"/>
+      <c r="R11" s="98"/>
+      <c r="S11" s="98"/>
+      <c r="T11" s="98"/>
+      <c r="U11" s="98"/>
+      <c r="V11" s="65"/>
+      <c r="W11" s="65"/>
+      <c r="X11" s="98"/>
+      <c r="Y11" s="98"/>
+      <c r="Z11" s="98"/>
+      <c r="AA11" s="98"/>
+    </row>
+    <row r="12" spans="3:27">
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="98"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="98"/>
+      <c r="I12" s="98"/>
+      <c r="J12" s="98"/>
+      <c r="K12" s="98"/>
+      <c r="L12" s="98"/>
+      <c r="M12" s="98"/>
+      <c r="N12" s="98"/>
+      <c r="O12" s="98"/>
+      <c r="P12" s="98"/>
+      <c r="Q12" s="98"/>
+      <c r="R12" s="98"/>
+      <c r="S12" s="98"/>
+      <c r="T12" s="98"/>
+      <c r="U12" s="98"/>
+      <c r="V12" s="65"/>
+      <c r="W12" s="65"/>
+      <c r="X12" s="98"/>
+      <c r="Y12" s="98"/>
+      <c r="Z12" s="98"/>
+      <c r="AA12" s="98"/>
+    </row>
+    <row r="13" spans="3:27">
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="98"/>
+      <c r="F13" s="98"/>
+      <c r="G13" s="98"/>
+      <c r="H13" s="98"/>
+      <c r="I13" s="98"/>
+      <c r="J13" s="98"/>
+      <c r="K13" s="98"/>
+      <c r="L13" s="98"/>
+      <c r="M13" s="98"/>
+      <c r="N13" s="98"/>
+      <c r="O13" s="98"/>
+      <c r="P13" s="98"/>
+      <c r="Q13" s="98"/>
+      <c r="R13" s="98"/>
+      <c r="S13" s="98"/>
+      <c r="T13" s="98"/>
+      <c r="U13" s="98"/>
+      <c r="V13" s="65"/>
+      <c r="W13" s="65"/>
+      <c r="X13" s="98"/>
+      <c r="Y13" s="98"/>
+      <c r="Z13" s="98"/>
+      <c r="AA13" s="98"/>
+    </row>
+    <row r="14" spans="3:27">
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="98"/>
+      <c r="H14" s="98"/>
+      <c r="I14" s="98"/>
+      <c r="J14" s="98"/>
+      <c r="K14" s="98"/>
+      <c r="L14" s="98"/>
+      <c r="M14" s="98"/>
+      <c r="N14" s="98"/>
+      <c r="O14" s="98"/>
+      <c r="P14" s="98"/>
+      <c r="Q14" s="98"/>
+      <c r="R14" s="98"/>
+      <c r="S14" s="98"/>
+      <c r="T14" s="98"/>
+      <c r="U14" s="98"/>
+      <c r="V14" s="65"/>
+      <c r="W14" s="65"/>
+      <c r="X14" s="98"/>
+      <c r="Y14" s="98"/>
+      <c r="Z14" s="98"/>
+      <c r="AA14" s="98"/>
+    </row>
+    <row r="15" spans="3:27">
+      <c r="C15" s="64"/>
+      <c r="D15" s="64"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
+      <c r="G15" s="98"/>
+      <c r="H15" s="98"/>
+      <c r="I15" s="98"/>
+      <c r="J15" s="98"/>
+      <c r="K15" s="98"/>
+      <c r="L15" s="98"/>
+      <c r="M15" s="98"/>
+      <c r="N15" s="98"/>
+      <c r="O15" s="98"/>
+      <c r="P15" s="98"/>
+      <c r="Q15" s="98"/>
+      <c r="R15" s="98"/>
+      <c r="S15" s="98"/>
+      <c r="T15" s="98"/>
+      <c r="U15" s="98"/>
+      <c r="V15" s="65"/>
+      <c r="W15" s="65"/>
+      <c r="X15" s="98"/>
+      <c r="Y15" s="98"/>
+      <c r="Z15" s="98"/>
+      <c r="AA15" s="98"/>
+    </row>
+    <row r="16" spans="3:27">
+      <c r="C16" s="64"/>
+      <c r="D16" s="64"/>
+      <c r="E16" s="98"/>
+      <c r="F16" s="98"/>
+      <c r="G16" s="98"/>
+      <c r="H16" s="98"/>
+      <c r="I16" s="98"/>
+      <c r="J16" s="98"/>
+      <c r="K16" s="98"/>
+      <c r="L16" s="98"/>
+      <c r="M16" s="98"/>
+      <c r="N16" s="98"/>
+      <c r="O16" s="98"/>
+      <c r="P16" s="98"/>
+      <c r="Q16" s="98"/>
+      <c r="R16" s="98"/>
+      <c r="S16" s="98"/>
+      <c r="T16" s="98"/>
+      <c r="U16" s="98"/>
+      <c r="V16" s="65"/>
+      <c r="W16" s="65"/>
+      <c r="X16" s="98"/>
+      <c r="Y16" s="98"/>
+      <c r="Z16" s="98"/>
+      <c r="AA16" s="98"/>
+    </row>
+    <row r="17" spans="3:27">
+      <c r="C17" s="64"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="98"/>
+      <c r="F17" s="98"/>
+      <c r="G17" s="98"/>
+      <c r="H17" s="98"/>
+      <c r="I17" s="98"/>
+      <c r="J17" s="98"/>
+      <c r="K17" s="98"/>
+      <c r="L17" s="98"/>
+      <c r="M17" s="98"/>
+      <c r="N17" s="98"/>
+      <c r="O17" s="98"/>
+      <c r="P17" s="98"/>
+      <c r="Q17" s="98"/>
+      <c r="R17" s="98"/>
+      <c r="S17" s="98"/>
+      <c r="T17" s="98"/>
+      <c r="U17" s="98"/>
+      <c r="V17" s="65"/>
+      <c r="W17" s="65"/>
+      <c r="X17" s="98"/>
+      <c r="Y17" s="98"/>
+      <c r="Z17" s="98"/>
+      <c r="AA17" s="98"/>
+    </row>
+    <row r="18" spans="3:27">
+      <c r="C18" s="64"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="98"/>
+      <c r="G18" s="98"/>
+      <c r="H18" s="98"/>
+      <c r="I18" s="98"/>
+      <c r="J18" s="98"/>
+      <c r="K18" s="98"/>
+      <c r="L18" s="98"/>
+      <c r="M18" s="98"/>
+      <c r="N18" s="98"/>
+      <c r="O18" s="98"/>
+      <c r="P18" s="98"/>
+      <c r="Q18" s="98"/>
+      <c r="R18" s="98"/>
+      <c r="S18" s="98"/>
+      <c r="T18" s="98"/>
+      <c r="U18" s="98"/>
+      <c r="V18" s="65"/>
+      <c r="W18" s="65"/>
+      <c r="X18" s="98"/>
+      <c r="Y18" s="98"/>
+      <c r="Z18" s="98"/>
+      <c r="AA18" s="98"/>
+    </row>
+    <row r="19" spans="3:27">
+      <c r="C19" s="64"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="98"/>
+      <c r="F19" s="98"/>
+      <c r="G19" s="98"/>
+      <c r="H19" s="98"/>
+      <c r="I19" s="98"/>
+      <c r="J19" s="98"/>
+      <c r="K19" s="98"/>
+      <c r="L19" s="98"/>
+      <c r="M19" s="98"/>
+      <c r="N19" s="98"/>
+      <c r="O19" s="98"/>
+      <c r="P19" s="98"/>
+      <c r="Q19" s="98"/>
+      <c r="R19" s="98"/>
+      <c r="S19" s="98"/>
+      <c r="T19" s="98"/>
+      <c r="U19" s="98"/>
+      <c r="V19" s="65"/>
+      <c r="W19" s="65"/>
+      <c r="X19" s="98"/>
+      <c r="Y19" s="98"/>
+      <c r="Z19" s="98"/>
+      <c r="AA19" s="98"/>
+    </row>
+    <row r="20" spans="3:27">
+      <c r="C20" s="64"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="98"/>
+      <c r="F20" s="98"/>
+      <c r="G20" s="98"/>
+      <c r="H20" s="98"/>
+      <c r="I20" s="98"/>
+      <c r="J20" s="98"/>
+      <c r="K20" s="98"/>
+      <c r="L20" s="98"/>
+      <c r="M20" s="98"/>
+      <c r="N20" s="98"/>
+      <c r="O20" s="98"/>
+      <c r="P20" s="98"/>
+      <c r="Q20" s="98"/>
+      <c r="R20" s="98"/>
+      <c r="S20" s="98"/>
+      <c r="T20" s="98"/>
+      <c r="U20" s="98"/>
+      <c r="V20" s="65"/>
+      <c r="W20" s="65"/>
+      <c r="X20" s="98"/>
+      <c r="Y20" s="98"/>
+      <c r="Z20" s="98"/>
+      <c r="AA20" s="98"/>
+    </row>
+    <row r="21" spans="3:27">
+      <c r="C21" s="64"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="98"/>
+      <c r="F21" s="98"/>
+      <c r="G21" s="98"/>
+      <c r="H21" s="98"/>
+      <c r="I21" s="98"/>
+      <c r="J21" s="98"/>
+      <c r="K21" s="98"/>
+      <c r="L21" s="98"/>
+      <c r="M21" s="98"/>
+      <c r="N21" s="98"/>
+      <c r="O21" s="98"/>
+      <c r="P21" s="98"/>
+      <c r="Q21" s="98"/>
+      <c r="R21" s="98"/>
+      <c r="S21" s="98"/>
+      <c r="T21" s="98"/>
+      <c r="U21" s="98"/>
+      <c r="V21" s="65"/>
+      <c r="W21" s="65"/>
+      <c r="X21" s="98"/>
+      <c r="Y21" s="98"/>
+      <c r="Z21" s="98"/>
+      <c r="AA21" s="98"/>
+    </row>
+    <row r="22" spans="3:27">
+      <c r="C22" s="64"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="98"/>
+      <c r="F22" s="98"/>
+      <c r="G22" s="98"/>
+      <c r="H22" s="98"/>
+      <c r="I22" s="98"/>
+      <c r="J22" s="98"/>
+      <c r="K22" s="98"/>
+      <c r="L22" s="98"/>
+      <c r="M22" s="98"/>
+      <c r="N22" s="98"/>
+      <c r="O22" s="98"/>
+      <c r="P22" s="98"/>
+      <c r="Q22" s="98"/>
+      <c r="R22" s="98"/>
+      <c r="S22" s="98"/>
+      <c r="T22" s="98"/>
+      <c r="U22" s="98"/>
+      <c r="V22" s="65"/>
+      <c r="W22" s="65"/>
+      <c r="X22" s="98"/>
+      <c r="Y22" s="98"/>
+      <c r="Z22" s="98"/>
+      <c r="AA22" s="98"/>
+    </row>
+    <row r="23" spans="3:27">
+      <c r="C23" s="64"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="98"/>
+      <c r="F23" s="98"/>
+      <c r="G23" s="98"/>
+      <c r="H23" s="98"/>
+      <c r="I23" s="98"/>
+      <c r="J23" s="98"/>
+      <c r="K23" s="98"/>
+      <c r="L23" s="98"/>
+      <c r="M23" s="98"/>
+      <c r="N23" s="98"/>
+      <c r="O23" s="98"/>
+      <c r="P23" s="98"/>
+      <c r="Q23" s="98"/>
+      <c r="R23" s="98"/>
+      <c r="S23" s="98"/>
+      <c r="T23" s="98"/>
+      <c r="U23" s="98"/>
+      <c r="V23" s="65"/>
+      <c r="W23" s="65"/>
+      <c r="X23" s="98"/>
+      <c r="Y23" s="98"/>
+      <c r="Z23" s="98"/>
+      <c r="AA23" s="98"/>
+    </row>
+    <row r="24" spans="3:27">
+      <c r="C24" s="64"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="98"/>
+      <c r="F24" s="98"/>
+      <c r="G24" s="98"/>
+      <c r="H24" s="98"/>
+      <c r="I24" s="98"/>
+      <c r="J24" s="98"/>
+      <c r="K24" s="98"/>
+      <c r="L24" s="98"/>
+      <c r="M24" s="98"/>
+      <c r="N24" s="98"/>
+      <c r="O24" s="98"/>
+      <c r="P24" s="98"/>
+      <c r="Q24" s="98"/>
+      <c r="R24" s="98"/>
+      <c r="S24" s="98"/>
+      <c r="T24" s="98"/>
+      <c r="U24" s="98"/>
+      <c r="V24" s="65"/>
+      <c r="W24" s="65"/>
+      <c r="X24" s="98"/>
+      <c r="Y24" s="98"/>
+      <c r="Z24" s="98"/>
+      <c r="AA24" s="98"/>
+    </row>
+    <row r="25" spans="3:27">
+      <c r="C25" s="64"/>
+      <c r="D25" s="64"/>
+      <c r="E25" s="98"/>
+      <c r="F25" s="98"/>
+      <c r="G25" s="98"/>
+      <c r="H25" s="98"/>
+      <c r="I25" s="98"/>
+      <c r="J25" s="98"/>
+      <c r="K25" s="98"/>
+      <c r="L25" s="98"/>
+      <c r="M25" s="98"/>
+      <c r="N25" s="98"/>
+      <c r="O25" s="98"/>
+      <c r="P25" s="98"/>
+      <c r="Q25" s="98"/>
+      <c r="R25" s="98"/>
+      <c r="S25" s="98"/>
+      <c r="T25" s="98"/>
+      <c r="U25" s="98"/>
+      <c r="V25" s="65"/>
+      <c r="W25" s="65"/>
+      <c r="X25" s="98"/>
+      <c r="Y25" s="98"/>
+      <c r="Z25" s="98"/>
+      <c r="AA25" s="98"/>
+    </row>
+    <row r="26" spans="3:27">
+      <c r="C26" s="64"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="98"/>
+      <c r="F26" s="98"/>
+      <c r="G26" s="98"/>
+      <c r="H26" s="98"/>
+      <c r="I26" s="98"/>
+      <c r="J26" s="98"/>
+      <c r="K26" s="98"/>
+      <c r="L26" s="98"/>
+      <c r="M26" s="98"/>
+      <c r="N26" s="98"/>
+      <c r="O26" s="98"/>
+      <c r="P26" s="98"/>
+      <c r="Q26" s="98"/>
+      <c r="R26" s="98"/>
+      <c r="S26" s="98"/>
+      <c r="T26" s="98"/>
+      <c r="U26" s="98"/>
+      <c r="V26" s="65"/>
+      <c r="W26" s="65"/>
+      <c r="X26" s="98"/>
+      <c r="Y26" s="98"/>
+      <c r="Z26" s="98"/>
+      <c r="AA26" s="98"/>
+    </row>
+    <row r="27" spans="3:27">
+      <c r="C27" s="64"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="98"/>
+      <c r="F27" s="98"/>
+      <c r="G27" s="98"/>
+      <c r="H27" s="98"/>
+      <c r="I27" s="98"/>
+      <c r="J27" s="98"/>
+      <c r="K27" s="98"/>
+      <c r="L27" s="98"/>
+      <c r="M27" s="98"/>
+      <c r="N27" s="98"/>
+      <c r="O27" s="98"/>
+      <c r="P27" s="98"/>
+      <c r="Q27" s="98"/>
+      <c r="R27" s="98"/>
+      <c r="S27" s="98"/>
+      <c r="T27" s="98"/>
+      <c r="U27" s="98"/>
+      <c r="V27" s="65"/>
+      <c r="W27" s="65"/>
+      <c r="X27" s="98"/>
+      <c r="Y27" s="98"/>
+      <c r="Z27" s="98"/>
+      <c r="AA27" s="98"/>
+    </row>
+    <row r="28" spans="3:27">
+      <c r="C28" s="64"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="98"/>
+      <c r="F28" s="98"/>
+      <c r="G28" s="98"/>
+      <c r="H28" s="98"/>
+      <c r="I28" s="98"/>
+      <c r="J28" s="98"/>
+      <c r="K28" s="98"/>
+      <c r="L28" s="98"/>
+      <c r="M28" s="98"/>
+      <c r="N28" s="98"/>
+      <c r="O28" s="98"/>
+      <c r="P28" s="98"/>
+      <c r="Q28" s="98"/>
+      <c r="R28" s="98"/>
+      <c r="S28" s="98"/>
+      <c r="T28" s="98"/>
+      <c r="U28" s="98"/>
+      <c r="V28" s="65"/>
+      <c r="W28" s="65"/>
+      <c r="X28" s="98"/>
+      <c r="Y28" s="98"/>
+      <c r="Z28" s="98"/>
+      <c r="AA28" s="98"/>
+    </row>
+    <row r="29" spans="3:27">
+      <c r="C29" s="64"/>
+      <c r="D29" s="64"/>
+      <c r="E29" s="98"/>
+      <c r="F29" s="98"/>
+      <c r="G29" s="98"/>
+      <c r="H29" s="98"/>
+      <c r="I29" s="98"/>
+      <c r="J29" s="98"/>
+      <c r="K29" s="98"/>
+      <c r="L29" s="98"/>
+      <c r="M29" s="98"/>
+      <c r="N29" s="98"/>
+      <c r="O29" s="98"/>
+      <c r="P29" s="98"/>
+      <c r="Q29" s="98"/>
+      <c r="R29" s="98"/>
+      <c r="S29" s="98"/>
+      <c r="T29" s="98"/>
+      <c r="U29" s="98"/>
+      <c r="V29" s="65"/>
+      <c r="W29" s="65"/>
+      <c r="X29" s="98"/>
+      <c r="Y29" s="98"/>
+      <c r="Z29" s="98"/>
+      <c r="AA29" s="98"/>
+    </row>
+    <row r="30" spans="3:27">
+      <c r="C30" s="64"/>
+      <c r="D30" s="64"/>
+      <c r="E30" s="98"/>
+      <c r="F30" s="98"/>
+      <c r="G30" s="98"/>
+      <c r="H30" s="98"/>
+      <c r="I30" s="98"/>
+      <c r="J30" s="98"/>
+      <c r="K30" s="98"/>
+      <c r="L30" s="98"/>
+      <c r="M30" s="98"/>
+      <c r="N30" s="98"/>
+      <c r="O30" s="98"/>
+      <c r="P30" s="98"/>
+      <c r="Q30" s="98"/>
+      <c r="R30" s="98"/>
+      <c r="S30" s="98"/>
+      <c r="T30" s="98"/>
+      <c r="U30" s="98"/>
+      <c r="V30" s="65"/>
+      <c r="W30" s="65"/>
+      <c r="X30" s="98"/>
+      <c r="Y30" s="98"/>
+      <c r="Z30" s="98"/>
+      <c r="AA30" s="98"/>
+    </row>
+    <row r="31" spans="3:27" ht="18.600000000000001" thickBot="1">
+      <c r="C31" s="64"/>
+      <c r="D31" s="66"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="67"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="67"/>
+      <c r="J31" s="67"/>
+      <c r="K31" s="67"/>
+      <c r="L31" s="67"/>
+      <c r="M31" s="67"/>
+      <c r="N31" s="67"/>
+      <c r="O31" s="67"/>
+      <c r="P31" s="67"/>
+      <c r="Q31" s="67"/>
+      <c r="R31" s="67"/>
+      <c r="S31" s="67"/>
+      <c r="T31" s="67"/>
+      <c r="U31" s="67"/>
+      <c r="V31" s="68"/>
+      <c r="W31" s="65"/>
+      <c r="X31" s="98"/>
+      <c r="Y31" s="98"/>
+      <c r="Z31" s="98"/>
+      <c r="AA31" s="98"/>
+    </row>
+    <row r="32" spans="3:27" ht="13.2" customHeight="1" thickBot="1">
+      <c r="C32" s="66"/>
+      <c r="D32" s="67"/>
+      <c r="E32" s="67"/>
+      <c r="F32" s="67"/>
+      <c r="G32" s="67"/>
+      <c r="H32" s="67"/>
+      <c r="I32" s="67"/>
+      <c r="J32" s="67"/>
+      <c r="K32" s="67"/>
+      <c r="L32" s="67"/>
+      <c r="M32" s="67"/>
+      <c r="N32" s="67"/>
+      <c r="O32" s="67"/>
+      <c r="P32" s="67"/>
+      <c r="Q32" s="67"/>
+      <c r="R32" s="67"/>
+      <c r="S32" s="67"/>
+      <c r="T32" s="67"/>
+      <c r="U32" s="67"/>
+      <c r="V32" s="67"/>
+      <c r="W32" s="68"/>
+      <c r="X32" s="98"/>
+      <c r="Y32" s="98"/>
+      <c r="Z32" s="98"/>
+      <c r="AA32" s="98"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -11583,6 +15225,966 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F0B575-2DDF-49B9-8DE2-F372EEC2F3B3}">
+  <dimension ref="A2:O79"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <cols>
+    <col min="1" max="1" width="11.8984375" style="1" customWidth="1"/>
+    <col min="2" max="6" width="10.8984375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:15">
+      <c r="B2" s="1" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="B3" s="59" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C3" s="59" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>1236</v>
+      </c>
+      <c r="E3" s="59" t="s">
+        <v>1290</v>
+      </c>
+      <c r="F3" s="59" t="s">
+        <v>1397</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="18">
+      <c r="A4" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B4" s="60" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C4" s="61" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D4" s="60" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E4" s="60" t="s">
+        <v>1429</v>
+      </c>
+      <c r="F4" s="60" t="s">
+        <v>1300</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="O4" s="62" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="13.2">
+      <c r="B5" s="58" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>1239</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="13.2">
+      <c r="B6" s="58" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>1240</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>1184</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="13.2">
+      <c r="B7" s="58" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="13.2">
+      <c r="B8" s="58" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="13.2">
+      <c r="B9" s="58" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>1243</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="13.2">
+      <c r="B10" s="58" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="13.2">
+      <c r="B11" s="58" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>1310</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="13.2">
+      <c r="B12" s="58" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>1253</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="13.2">
+      <c r="B13" s="58" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>1263</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>1312</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="13.2">
+      <c r="B14" s="58" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="13.2">
+      <c r="B15" s="58" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>1248</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>1314</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="13.2">
+      <c r="B16" s="58" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>1249</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" ht="13.2">
+      <c r="B17" s="58" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" ht="13.2">
+      <c r="B18" s="58" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" ht="13.2">
+      <c r="B19" s="58" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>1318</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" ht="13.2">
+      <c r="B20" s="58" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10">
+      <c r="C21" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>1320</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10">
+      <c r="C22" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10">
+      <c r="C23" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>1220</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>1322</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10">
+      <c r="C24" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>1323</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10">
+      <c r="C25" s="1" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>1324</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10">
+      <c r="C26" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10">
+      <c r="C27" s="1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10">
+      <c r="C28" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10">
+      <c r="C29" s="1" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>1226</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10">
+      <c r="C30" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10">
+      <c r="C31" s="1" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10">
+      <c r="C32" s="1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>1260</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="33" spans="3:8">
+      <c r="C33" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="34" spans="3:8">
+      <c r="C34" s="1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="35" spans="3:8">
+      <c r="C35" s="1" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>1263</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="36" spans="3:8">
+      <c r="C36" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="37" spans="3:8">
+      <c r="C37" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>1265</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="38" spans="3:8">
+      <c r="C38" s="1" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="39" spans="3:8">
+      <c r="C39" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="40" spans="3:8">
+      <c r="C40" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="41" spans="3:8">
+      <c r="C41" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="42" spans="3:8">
+      <c r="D42" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="43" spans="3:8">
+      <c r="D43" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="44" spans="3:8">
+      <c r="D44" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="45" spans="3:8">
+      <c r="D45" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="46" spans="3:8">
+      <c r="D46" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="47" spans="3:8">
+      <c r="D47" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="48" spans="3:8">
+      <c r="D48" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="49" spans="4:8">
+      <c r="D49" s="1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="50" spans="4:8">
+      <c r="D50" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="51" spans="4:8">
+      <c r="D51" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="52" spans="4:8">
+      <c r="D52" s="1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="53" spans="4:8">
+      <c r="D53" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="54" spans="4:8">
+      <c r="D54" s="1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="55" spans="4:8">
+      <c r="D55" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="56" spans="4:8">
+      <c r="D56" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="57" spans="4:8">
+      <c r="D57" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="58" spans="4:8">
+      <c r="D58" s="1" t="s">
+        <v>1283</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="59" spans="4:8">
+      <c r="D59" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="60" spans="4:8">
+      <c r="D60" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="61" spans="4:8">
+      <c r="D61" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="62" spans="4:8">
+      <c r="D62" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="63" spans="4:8">
+      <c r="H63" s="1" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="64" spans="4:8">
+      <c r="H64" s="1" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="65" spans="8:8">
+      <c r="H65" s="1" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="66" spans="8:8">
+      <c r="H66" s="1" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="67" spans="8:8">
+      <c r="H67" s="1" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="68" spans="8:8">
+      <c r="H68" s="1" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="69" spans="8:8">
+      <c r="H69" s="1" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="70" spans="8:8">
+      <c r="H70" s="1" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="71" spans="8:8">
+      <c r="H71" s="1" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="72" spans="8:8">
+      <c r="H72" s="1" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="73" spans="8:8">
+      <c r="H73" s="1" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="74" spans="8:8">
+      <c r="H74" s="1" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="75" spans="8:8">
+      <c r="H75" s="1" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="76" spans="8:8">
+      <c r="H76" s="1" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="77" spans="8:8">
+      <c r="H77" s="1" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="78" spans="8:8">
+      <c r="H78" s="1" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="79" spans="8:8">
+      <c r="H79" s="1" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J9:J23">
+    <sortCondition ref="J23"/>
+  </sortState>
+  <phoneticPr fontId="2"/>
+  <hyperlinks>
+    <hyperlink ref="E4" r:id="rId1" xr:uid="{36F1793A-29C9-405A-842F-63D38582F0C1}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{47C463A0-4E7E-44B9-A3BC-085128374E6F}"/>
+    <hyperlink ref="O4" r:id="rId3" xr:uid="{AD83982B-8566-420D-9973-0173E41E1161}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FCFD5C-696C-43AD-A2BD-D69C05CB2D44}">
   <dimension ref="B2:P57"/>
   <sheetFormatPr defaultRowHeight="12.6"/>
@@ -12060,7 +16662,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E898285-845A-4583-B20D-F3A331C07E8E}">
   <dimension ref="B2:R45"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -12654,6 +17256,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="5"/>
+  </cols>
+  <sheetData/>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBD988A-503C-4F44-AC4A-B26683FC9B4C}">
   <dimension ref="B4:O34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
@@ -12804,7 +17420,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
   <dimension ref="B3:L159"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
@@ -16988,7 +21604,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EB7090A-0065-41E7-85DA-75EEB9504A67}">
   <dimension ref="C3:Q81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
@@ -20419,7 +25035,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F51B408-D4E3-46FE-97DE-15AB67B6AAB6}">
   <dimension ref="B1:Q100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
@@ -23238,7 +27854,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E63A27D9-C8B6-491D-9205-8D7433312F14}">
   <dimension ref="A4:U522"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
@@ -40154,7 +44770,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A843E7EA-D614-495E-86B7-D31F628C6221}">
   <dimension ref="A1:I30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
@@ -40523,7 +45139,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE71EC6-0DD3-461C-A8FC-74E22154B7A5}">
   <dimension ref="A4:H13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
@@ -40628,964 +45244,4 @@
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F0B575-2DDF-49B9-8DE2-F372EEC2F3B3}">
-  <dimension ref="A2:O79"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
-  <cols>
-    <col min="1" max="1" width="11.8984375" style="1" customWidth="1"/>
-    <col min="2" max="6" width="10.8984375" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:15">
-      <c r="B2" s="1" t="s">
-        <v>1237</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="B3" s="59" t="s">
-        <v>1183</v>
-      </c>
-      <c r="C3" s="59" t="s">
-        <v>1197</v>
-      </c>
-      <c r="D3" s="59" t="s">
-        <v>1236</v>
-      </c>
-      <c r="E3" s="59" t="s">
-        <v>1290</v>
-      </c>
-      <c r="F3" s="59" t="s">
-        <v>1397</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>1304</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>1549</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="18">
-      <c r="A4" s="1" t="s">
-        <v>1289</v>
-      </c>
-      <c r="B4" s="60" t="s">
-        <v>1288</v>
-      </c>
-      <c r="C4" s="61" t="s">
-        <v>1548</v>
-      </c>
-      <c r="D4" s="60" t="s">
-        <v>1238</v>
-      </c>
-      <c r="E4" s="60" t="s">
-        <v>1429</v>
-      </c>
-      <c r="F4" s="60" t="s">
-        <v>1300</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>1305</v>
-      </c>
-      <c r="O4" s="62" t="s">
-        <v>1551</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="13.2">
-      <c r="B5" s="58" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>1201</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>1239</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>1291</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="13.2">
-      <c r="B6" s="58" t="s">
-        <v>1185</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>1240</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>1292</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>1184</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>1431</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>1379</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="13.2">
-      <c r="B7" s="58" t="s">
-        <v>1198</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>1203</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>1241</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>1293</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>1185</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>1306</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>1387</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>1389</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>1567</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="13.2">
-      <c r="B8" s="58" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>1204</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>1242</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>1208</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>1302</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>1307</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>1388</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>1390</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>1568</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="13.2">
-      <c r="B9" s="58" t="s">
-        <v>1187</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>1205</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>1243</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>1209</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>1212</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>1308</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>1206</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>1569</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="13.2">
-      <c r="B10" s="58" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>1206</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>1244</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>1210</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>1188</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>1309</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>1203</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>1391</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="13.2">
-      <c r="B11" s="58" t="s">
-        <v>1189</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>1207</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>1195</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>1294</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>1217</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>1310</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>1194</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>1392</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="13.2">
-      <c r="B12" s="58" t="s">
-        <v>1190</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>1208</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>1245</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>1253</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>1195</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>1311</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>1385</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="13.2">
-      <c r="B13" s="58" t="s">
-        <v>1191</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>1209</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>1246</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>1263</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>1194</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>1312</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>1196</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="13.2">
-      <c r="B14" s="58" t="s">
-        <v>1192</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>1210</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>1247</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>1213</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>1303</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>1313</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>1394</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="13.2">
-      <c r="B15" s="58" t="s">
-        <v>1193</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>1211</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>1248</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>1214</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>1291</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>1314</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>1380</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="13.2">
-      <c r="B16" s="58" t="s">
-        <v>1194</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>1212</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>1249</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>1295</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>1315</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>1381</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" ht="13.2">
-      <c r="B17" s="58" t="s">
-        <v>1195</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>1213</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>1202</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>1296</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>1316</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" ht="13.2">
-      <c r="B18" s="58" t="s">
-        <v>1199</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>1214</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>1203</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>1297</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>1317</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>1383</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" ht="13.2">
-      <c r="B19" s="58" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>1215</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>1250</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>1194</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>1318</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>1253</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" ht="13.2">
-      <c r="B20" s="58" t="s">
-        <v>1200</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>1216</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>1251</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>1224</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>1319</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>1382</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10">
-      <c r="C21" s="1" t="s">
-        <v>1217</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>1252</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>1273</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>1320</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>1386</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10">
-      <c r="C22" s="1" t="s">
-        <v>1218</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>1253</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>1298</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>1321</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>1208</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10">
-      <c r="C23" s="1" t="s">
-        <v>1194</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>1254</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>1220</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>1322</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>1432</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10">
-      <c r="C24" s="1" t="s">
-        <v>1219</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>1255</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>1323</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>1433</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10">
-      <c r="C25" s="1" t="s">
-        <v>1220</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>1208</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>1324</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>1384</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10">
-      <c r="C26" s="1" t="s">
-        <v>1221</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>1256</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10">
-      <c r="C27" s="1" t="s">
-        <v>1222</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>1257</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>1326</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10">
-      <c r="C28" s="1" t="s">
-        <v>1223</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>1258</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>1327</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10">
-      <c r="C29" s="1" t="s">
-        <v>1224</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>1226</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10">
-      <c r="C30" s="1" t="s">
-        <v>1225</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>1259</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>1329</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10">
-      <c r="C31" s="1" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>1225</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10">
-      <c r="C32" s="1" t="s">
-        <v>1196</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>1260</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>1331</v>
-      </c>
-    </row>
-    <row r="33" spans="3:8">
-      <c r="C33" s="1" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>1261</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="34" spans="3:8">
-      <c r="C34" s="1" t="s">
-        <v>1228</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>1262</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="35" spans="3:8">
-      <c r="C35" s="1" t="s">
-        <v>1229</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>1263</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="36" spans="3:8">
-      <c r="C36" s="1" t="s">
-        <v>1230</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>1264</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="37" spans="3:8">
-      <c r="C37" s="1" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>1265</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="38" spans="3:8">
-      <c r="C38" s="1" t="s">
-        <v>1232</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>1266</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="39" spans="3:8">
-      <c r="C39" s="1" t="s">
-        <v>1233</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>1267</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="40" spans="3:8">
-      <c r="C40" s="1" t="s">
-        <v>1234</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>1268</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>1339</v>
-      </c>
-    </row>
-    <row r="41" spans="3:8">
-      <c r="C41" s="1" t="s">
-        <v>1235</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>1269</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="42" spans="3:8">
-      <c r="D42" s="1" t="s">
-        <v>1270</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="43" spans="3:8">
-      <c r="D43" s="1" t="s">
-        <v>1271</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="44" spans="3:8">
-      <c r="D44" s="1" t="s">
-        <v>1272</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>1343</v>
-      </c>
-    </row>
-    <row r="45" spans="3:8">
-      <c r="D45" s="1" t="s">
-        <v>1189</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="46" spans="3:8">
-      <c r="D46" s="1" t="s">
-        <v>1273</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>1345</v>
-      </c>
-    </row>
-    <row r="47" spans="3:8">
-      <c r="D47" s="1" t="s">
-        <v>1194</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="48" spans="3:8">
-      <c r="D48" s="1" t="s">
-        <v>1274</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>1347</v>
-      </c>
-    </row>
-    <row r="49" spans="4:8">
-      <c r="D49" s="1" t="s">
-        <v>1275</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="50" spans="4:8">
-      <c r="D50" s="1" t="s">
-        <v>1221</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>1349</v>
-      </c>
-    </row>
-    <row r="51" spans="4:8">
-      <c r="D51" s="1" t="s">
-        <v>1276</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="52" spans="4:8">
-      <c r="D52" s="1" t="s">
-        <v>1277</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>1351</v>
-      </c>
-    </row>
-    <row r="53" spans="4:8">
-      <c r="D53" s="1" t="s">
-        <v>1278</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="54" spans="4:8">
-      <c r="D54" s="1" t="s">
-        <v>1279</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>1353</v>
-      </c>
-    </row>
-    <row r="55" spans="4:8">
-      <c r="D55" s="1" t="s">
-        <v>1280</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>1354</v>
-      </c>
-    </row>
-    <row r="56" spans="4:8">
-      <c r="D56" s="1" t="s">
-        <v>1281</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>1355</v>
-      </c>
-    </row>
-    <row r="57" spans="4:8">
-      <c r="D57" s="1" t="s">
-        <v>1282</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>1356</v>
-      </c>
-    </row>
-    <row r="58" spans="4:8">
-      <c r="D58" s="1" t="s">
-        <v>1283</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>1357</v>
-      </c>
-    </row>
-    <row r="59" spans="4:8">
-      <c r="D59" s="1" t="s">
-        <v>1284</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>1358</v>
-      </c>
-    </row>
-    <row r="60" spans="4:8">
-      <c r="D60" s="1" t="s">
-        <v>1285</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>1359</v>
-      </c>
-    </row>
-    <row r="61" spans="4:8">
-      <c r="D61" s="1" t="s">
-        <v>1286</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>1360</v>
-      </c>
-    </row>
-    <row r="62" spans="4:8">
-      <c r="D62" s="1" t="s">
-        <v>1287</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>1361</v>
-      </c>
-    </row>
-    <row r="63" spans="4:8">
-      <c r="H63" s="1" t="s">
-        <v>1362</v>
-      </c>
-    </row>
-    <row r="64" spans="4:8">
-      <c r="H64" s="1" t="s">
-        <v>1363</v>
-      </c>
-    </row>
-    <row r="65" spans="8:8">
-      <c r="H65" s="1" t="s">
-        <v>1364</v>
-      </c>
-    </row>
-    <row r="66" spans="8:8">
-      <c r="H66" s="1" t="s">
-        <v>1365</v>
-      </c>
-    </row>
-    <row r="67" spans="8:8">
-      <c r="H67" s="1" t="s">
-        <v>1366</v>
-      </c>
-    </row>
-    <row r="68" spans="8:8">
-      <c r="H68" s="1" t="s">
-        <v>1367</v>
-      </c>
-    </row>
-    <row r="69" spans="8:8">
-      <c r="H69" s="1" t="s">
-        <v>1368</v>
-      </c>
-    </row>
-    <row r="70" spans="8:8">
-      <c r="H70" s="1" t="s">
-        <v>1369</v>
-      </c>
-    </row>
-    <row r="71" spans="8:8">
-      <c r="H71" s="1" t="s">
-        <v>1370</v>
-      </c>
-    </row>
-    <row r="72" spans="8:8">
-      <c r="H72" s="1" t="s">
-        <v>1371</v>
-      </c>
-    </row>
-    <row r="73" spans="8:8">
-      <c r="H73" s="1" t="s">
-        <v>1372</v>
-      </c>
-    </row>
-    <row r="74" spans="8:8">
-      <c r="H74" s="1" t="s">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="75" spans="8:8">
-      <c r="H75" s="1" t="s">
-        <v>1374</v>
-      </c>
-    </row>
-    <row r="76" spans="8:8">
-      <c r="H76" s="1" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="77" spans="8:8">
-      <c r="H77" s="1" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="78" spans="8:8">
-      <c r="H78" s="1" t="s">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="79" spans="8:8">
-      <c r="H79" s="1" t="s">
-        <v>1378</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J9:J23">
-    <sortCondition ref="J23"/>
-  </sortState>
-  <phoneticPr fontId="2"/>
-  <hyperlinks>
-    <hyperlink ref="E4" r:id="rId1" xr:uid="{36F1793A-29C9-405A-842F-63D38582F0C1}"/>
-    <hyperlink ref="C4" r:id="rId2" xr:uid="{47C463A0-4E7E-44B9-A3BC-085128374E6F}"/>
-    <hyperlink ref="O4" r:id="rId3" xr:uid="{AD83982B-8566-420D-9973-0173E41E1161}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB1D7AD-EEFF-4C1B-AB17-7EFE78F4EA5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1214E9E5-C31C-494B-8A73-864EB96A510C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -8459,8 +8459,8 @@
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>87085</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>43544</xdr:rowOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -8476,7 +8476,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4669972" y="1687284"/>
-          <a:ext cx="1491342" cy="1349831"/>
+          <a:ext cx="1491342" cy="1240973"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8598,15 +8598,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>185055</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>163286</xdr:rowOff>
+      <xdr:colOff>402770</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>195943</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>555170</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>141516</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>97970</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>174173</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -8621,7 +8621,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2209798" y="3614057"/>
+          <a:off x="2427513" y="2732314"/>
           <a:ext cx="1719943" cy="1578430"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -8746,16 +8746,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>620490</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>141514</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>468089</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>435433</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>108857</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>283033</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>65314</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -8770,8 +8770,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4669976" y="3363685"/>
-          <a:ext cx="1839686" cy="1567543"/>
+          <a:off x="6542318" y="2688771"/>
+          <a:ext cx="1839686" cy="1970314"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8810,7 +8810,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -8823,7 +8823,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -8832,7 +8832,7 @@
             </a:rPr>
             <a:t>ギターデータ取得</a:t>
           </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -8842,7 +8842,7 @@
         </a:p>
         <a:p>
           <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -8853,7 +8853,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -8866,7 +8866,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -8877,9 +8877,109 @@
           </a:r>
         </a:p>
         <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>/public/v1/colors</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>/public/v1/series</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>...</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -8888,7 +8988,7 @@
             </a:rPr>
             <a:t>C# ASP.NET Core</a:t>
           </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -9923,8 +10023,8 @@
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
           </a:solidFill>
-          <a:headEnd type="triangle"/>
-          <a:tailEnd type="triangle"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -10170,8 +10270,8 @@
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
           </a:solidFill>
-          <a:headEnd type="triangle"/>
-          <a:tailEnd type="triangle"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -10230,8 +10330,8 @@
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
           </a:solidFill>
-          <a:headEnd type="triangle"/>
-          <a:tailEnd type="triangle"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -10256,11 +10356,11 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>261257</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>174172</xdr:rowOff>
+      <xdr:rowOff>185057</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>261257</xdr:colOff>
+      <xdr:colOff>283029</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>76201</xdr:rowOff>
     </xdr:to>
@@ -10273,12 +10373,14 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="5" idx="2"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4985657" y="1328058"/>
-          <a:ext cx="0" cy="359229"/>
+        <a:xfrm flipH="1">
+          <a:off x="4985657" y="1338943"/>
+          <a:ext cx="21772" cy="348344"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -10287,8 +10389,8 @@
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
           </a:solidFill>
-          <a:headEnd type="triangle"/>
-          <a:tailEnd type="triangle"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -10313,7 +10415,7 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>239486</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>163286</xdr:rowOff>
+      <xdr:rowOff>195943</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
@@ -10330,12 +10432,14 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="6" idx="2"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5638800" y="1317172"/>
-          <a:ext cx="0" cy="359229"/>
+          <a:off x="5638800" y="1349829"/>
+          <a:ext cx="0" cy="326572"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -10344,8 +10448,8 @@
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
           </a:solidFill>
-          <a:headEnd type="triangle"/>
-          <a:tailEnd type="triangle"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -10425,15 +10529,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>370113</xdr:colOff>
+      <xdr:colOff>587828</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>54429</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>620486</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>163286</xdr:rowOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>195943</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -10451,8 +10555,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="3069770" y="2362200"/>
-          <a:ext cx="1600202" cy="1251857"/>
+          <a:off x="3287485" y="2307771"/>
+          <a:ext cx="1382487" cy="424543"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -10461,8 +10565,8 @@
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
           </a:solidFill>
-          <a:headEnd type="triangle"/>
-          <a:tailEnd type="triangle"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -10485,9 +10589,9 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>370113</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>141516</xdr:rowOff>
+      <xdr:colOff>587828</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>174173</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
@@ -10511,8 +10615,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3069770" y="5192487"/>
-          <a:ext cx="1578428" cy="838197"/>
+          <a:off x="3287485" y="4310744"/>
+          <a:ext cx="1360713" cy="1719940"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -10521,128 +10625,8 @@
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
           </a:solidFill>
-          <a:headEnd type="triangle"/>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>16329</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>43544</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>190505</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>141514</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="44" name="直線矢印コネクタ 43">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E4DD22E-DEC8-4D35-A66E-813814A69F12}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="8" idx="2"/>
-          <a:endCxn id="11" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5415643" y="3037115"/>
-          <a:ext cx="174176" cy="326570"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="28575">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:headEnd type="triangle"/>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>555170</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>10886</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>620490</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="48" name="直線矢印コネクタ 47">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{281C2595-C16A-4D7B-9B80-BB64ECEA9DAD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="10" idx="3"/>
-          <a:endCxn id="11" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="3929741" y="4147457"/>
-          <a:ext cx="740235" cy="255815"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="28575">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:headEnd type="triangle"/>
-          <a:tailEnd type="triangle"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -10665,9 +10649,129 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>435433</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>10886</xdr:rowOff>
+      <xdr:colOff>87085</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>38104</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="44" name="直線矢印コネクタ 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E4DD22E-DEC8-4D35-A66E-813814A69F12}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="8" idx="3"/>
+          <a:endCxn id="11" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6161314" y="2307771"/>
+          <a:ext cx="1300847" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>97970</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>70758</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>468089</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>223157</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="48" name="直線矢印コネクタ 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{281C2595-C16A-4D7B-9B80-BB64ECEA9DAD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="10" idx="3"/>
+          <a:endCxn id="11" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4147456" y="3521529"/>
+          <a:ext cx="2394862" cy="152399"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>38104</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>65314</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
@@ -10685,14 +10789,14 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="11" idx="3"/>
+          <a:stCxn id="11" idx="2"/>
           <a:endCxn id="14" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6509662" y="4147457"/>
-          <a:ext cx="2178770" cy="1894114"/>
+          <a:off x="7462161" y="4659085"/>
+          <a:ext cx="1226271" cy="1382486"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -10701,8 +10805,8 @@
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
           </a:solidFill>
-          <a:headEnd type="triangle"/>
-          <a:tailEnd type="triangle"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -10761,8 +10865,8 @@
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
           </a:solidFill>
-          <a:headEnd type="triangle"/>
-          <a:tailEnd type="triangle"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -10821,8 +10925,8 @@
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
           </a:solidFill>
-          <a:headEnd type="triangle"/>
-          <a:tailEnd type="triangle"/>
+          <a:headEnd type="triangle" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -10881,8 +10985,8 @@
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
           </a:solidFill>
-          <a:headEnd type="triangle"/>
-          <a:tailEnd type="triangle"/>
+          <a:headEnd type="triangle" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -10941,8 +11045,8 @@
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
           </a:solidFill>
-          <a:headEnd type="triangle"/>
-          <a:tailEnd type="triangle"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1214E9E5-C31C-494B-8A73-864EB96A510C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52FF0D88-6C02-47B0-B281-42D6BA9907AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="architecture" sheetId="12" r:id="rId1"/>
-    <sheet name="オブジェクト" sheetId="1" r:id="rId2"/>
+    <sheet name="ゲームオブジェクト" sheetId="1" r:id="rId2"/>
     <sheet name="バトルフロー" sheetId="2" r:id="rId3"/>
     <sheet name="コード" sheetId="5" r:id="rId4"/>
     <sheet name="スキル" sheetId="3" r:id="rId5"/>
@@ -22,9 +22,10 @@
     <sheet name="モンスタースキル" sheetId="6" r:id="rId7"/>
     <sheet name="戦績レポート" sheetId="7" r:id="rId8"/>
     <sheet name="各種設定" sheetId="8" r:id="rId9"/>
-    <sheet name="guitarCrawler" sheetId="9" r:id="rId10"/>
-    <sheet name="public API" sheetId="10" r:id="rId11"/>
-    <sheet name="guiatr gallery" sheetId="11" r:id="rId12"/>
+    <sheet name="jobCrawler" sheetId="13" r:id="rId10"/>
+    <sheet name="guitarCrawler" sheetId="9" r:id="rId11"/>
+    <sheet name="public API" sheetId="10" r:id="rId12"/>
+    <sheet name="guiatr gallery" sheetId="11" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">スキル!$C$3:$O$3</definedName>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3854" uniqueCount="1719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3933" uniqueCount="1797">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -7502,6 +7503,340 @@
     <t xml:space="preserve">  </t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>案件情報収集基盤＋検索・分析UI</t>
+    <rPh sb="0" eb="2">
+      <t>アンケン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シュウシュウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キバン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ブンセキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>Findy</t>
+  </si>
+  <si>
+    <t>paiza</t>
+  </si>
+  <si>
+    <t>Wantedly</t>
+  </si>
+  <si>
+    <t>あたりから</t>
+  </si>
+  <si>
+    <t>言語</t>
+  </si>
+  <si>
+    <t>単価</t>
+  </si>
+  <si>
+    <t>リモート率</t>
+  </si>
+  <si>
+    <t>必須スキル</t>
+  </si>
+  <si>
+    <t>を集めて分析。</t>
+  </si>
+  <si>
+    <t>Forkwell</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>今日の○○案件数</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ASP.NET案件</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Go案件</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>平均単価</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>フルリモート率</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>勤務地ランキング</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>データから価値を作る</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>データから生み出す価値</t>
+    <rPh sb="5" eb="6">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Java 312件 (+15)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Go 41件 (+7)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>React 267件 (+22)</t>
+  </si>
+  <si>
+    <t>Java 67万</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>C# 70万</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>先週比</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>福岡案件 xx件</t>
+    <rPh sb="7" eb="8">
+      <t>ケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>例えば、</t>
+  </si>
+  <si>
+    <t>「Go案件はこの半年で増えているのか？」</t>
+  </si>
+  <si>
+    <t>「ReactとVueはどちらが多い？」</t>
+  </si>
+  <si>
+    <t>「ASP.NET Coreの単価推移」</t>
+  </si>
+  <si>
+    <t>「福岡のフルリモート案件の割合」</t>
+  </si>
+  <si>
+    <t>業界の動きが見える</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SES営業って毎朝こんなことをしてる。</t>
+  </si>
+  <si>
+    <t>案件サイトを巡回</t>
+  </si>
+  <si>
+    <t>新着案件を見る</t>
+  </si>
+  <si>
+    <t>単価を見る</t>
+  </si>
+  <si>
+    <t>エンジニアを探す</t>
+  </si>
+  <si>
+    <t>顧客へ提案</t>
+  </si>
+  <si>
+    <t>ターゲット</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自分</t>
+    <rPh sb="0" eb="2">
+      <t>ジブン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SES</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>フリーランス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>企業？</t>
+    <rPh sb="0" eb="2">
+      <t>キギョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Ver1</t>
+  </si>
+  <si>
+    <t>完全無料。</t>
+  </si>
+  <si>
+    <t>広告もなし。</t>
+  </si>
+  <si>
+    <t>とにかく</t>
+  </si>
+  <si>
+    <t>自分が毎日使う。</t>
+  </si>
+  <si>
+    <t>Ver2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Xとかで</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Go +8件</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>React +21件</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>平均単価72万</t>
+  </si>
+  <si>
+    <t>Ver3</t>
+  </si>
+  <si>
+    <t>例えば</t>
+  </si>
+  <si>
+    <t>有料（月980円）</t>
+  </si>
+  <si>
+    <t>推移</t>
+  </si>
+  <si>
+    <t>AI分析</t>
+  </si>
+  <si>
+    <t>通知</t>
+  </si>
+  <si>
+    <t>保存検索</t>
+  </si>
+  <si>
+    <t>人が増えたら有料</t>
+    <rPh sb="6" eb="8">
+      <t>ユウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>無料 &gt;　案件検索</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>案件サイトによっては</t>
+  </si>
+  <si>
+    <t>スクレイピング禁止</t>
+  </si>
+  <si>
+    <t>再配布禁止</t>
+  </si>
+  <si>
+    <t>商用利用禁止</t>
+  </si>
+  <si>
+    <t>というケースもある。</t>
+  </si>
+  <si>
+    <t>価値を感じたら↓</t>
+    <rPh sb="0" eb="2">
+      <t>カチ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「自分が欲しい」を絶対に曲げないこと。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「案件を検索するサービスではなく、案件市場を分析するサービスを目指す。」</t>
+  </si>
+  <si>
+    <t>利用規約はちゃんと見る。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これ、結構手作業らしい。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>こういう時系列データは、毎日収集するからこそ作れる価値。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>AIと統合もあり？</t>
+    <rPh sb="3" eb="5">
+      <t>トウゴウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>OPEN API等にpublic apiがある。</t>
+    <rPh sb="8" eb="9">
+      <t>トウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>**「市場分析」**までいける？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>多分、商用利用は無理。</t>
+    <rPh sb="0" eb="2">
+      <t>タブン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショウヨウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ムリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -7510,7 +7845,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7572,6 +7907,20 @@
       <color theme="1"/>
       <name val="Segoe UI Symbol"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="BIZ UDゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="BIZ UDゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="8">
@@ -7892,7 +8241,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -8049,7 +8398,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -14316,6 +14675,275 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>670687</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>145053</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A5E7C75-B86C-C5A1-1374-78AF838F6E89}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2598420" y="1158240"/>
+          <a:ext cx="1470787" cy="3147333"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>510643</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>68706</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BA2967B-EAD4-50E4-073D-654B56836F01}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4998720" y="2453640"/>
+          <a:ext cx="1188823" cy="1455546"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>777240</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>251605</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>15369</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96AC2E16-7B5A-A524-7A68-958C91C8DAC5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4937760" y="3962400"/>
+          <a:ext cx="1676545" cy="1493649"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>411480</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>53428</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>170</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34E50281-D423-9E58-635B-F7EEBD3B91E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6774180" y="3802380"/>
+          <a:ext cx="1013548" cy="1958510"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>640080</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>617337</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>30588</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6343320D-982A-755C-DB0F-B931ED79CA66}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6316980" y="2468880"/>
+          <a:ext cx="1348857" cy="1242168"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>388620</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>586902</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>129868</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69875439-DC51-0D94-9BA4-5F4F1073EA8C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="388620" y="502920"/>
+          <a:ext cx="1867062" cy="3787468"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -14579,18 +15207,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6672014-33B5-48C4-9202-55E4E667EEEF}">
-  <dimension ref="C5:AA32"/>
+  <dimension ref="C5:W32"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="3" width="8.796875" customWidth="1"/>
     <col min="27" max="27" width="4.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:27" ht="18.600000000000001" thickBot="1">
+    <row r="5" spans="3:23" ht="18.600000000000001" thickBot="1">
       <c r="V5" s="67"/>
       <c r="W5" s="67"/>
     </row>
-    <row r="6" spans="3:27">
+    <row r="6" spans="3:23">
       <c r="C6" s="95"/>
       <c r="D6" s="96"/>
       <c r="E6" s="96"/>
@@ -14610,97 +15238,24 @@
       <c r="S6" s="96"/>
       <c r="T6" s="96"/>
       <c r="U6" s="96"/>
-      <c r="V6" s="98"/>
       <c r="W6" s="97"/>
-      <c r="X6" s="98"/>
-      <c r="Y6" s="98"/>
-      <c r="Z6" s="98"/>
-      <c r="AA6" s="98"/>
-    </row>
-    <row r="7" spans="3:27">
+    </row>
+    <row r="7" spans="3:23">
       <c r="C7" s="64"/>
-      <c r="D7" s="98"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="98"/>
-      <c r="J7" s="98"/>
-      <c r="K7" s="98"/>
-      <c r="L7" s="98"/>
-      <c r="M7" s="98"/>
-      <c r="N7" s="98"/>
-      <c r="O7" s="98"/>
-      <c r="P7" s="98"/>
-      <c r="Q7" s="98"/>
-      <c r="R7" s="98"/>
-      <c r="S7" s="98"/>
-      <c r="T7" s="98"/>
-      <c r="U7" s="98"/>
-      <c r="V7" s="98"/>
       <c r="W7" s="65"/>
-      <c r="X7" s="98"/>
-      <c r="Y7" s="98"/>
-      <c r="Z7" s="98"/>
-      <c r="AA7" s="98"/>
-    </row>
-    <row r="8" spans="3:27">
+    </row>
+    <row r="8" spans="3:23">
       <c r="C8" s="64"/>
-      <c r="D8" s="98"/>
-      <c r="E8" s="98"/>
-      <c r="F8" s="98"/>
-      <c r="G8" s="98"/>
-      <c r="H8" s="98"/>
-      <c r="I8" s="98"/>
-      <c r="J8" s="98"/>
-      <c r="K8" s="98"/>
-      <c r="L8" s="98"/>
-      <c r="M8" s="98"/>
-      <c r="N8" s="98"/>
-      <c r="O8" s="98"/>
-      <c r="P8" s="98"/>
-      <c r="Q8" s="98"/>
-      <c r="R8" s="98"/>
-      <c r="S8" s="98"/>
-      <c r="T8" s="98"/>
-      <c r="U8" s="98"/>
-      <c r="V8" s="98"/>
       <c r="W8" s="65"/>
-      <c r="X8" s="98"/>
-      <c r="Y8" s="98"/>
-      <c r="Z8" s="98"/>
-      <c r="AA8" s="98"/>
-    </row>
-    <row r="9" spans="3:27" ht="18.600000000000001" thickBot="1">
+    </row>
+    <row r="9" spans="3:23" ht="18.600000000000001" thickBot="1">
       <c r="C9" s="64"/>
-      <c r="D9" s="98"/>
-      <c r="E9" s="98"/>
-      <c r="F9" s="98"/>
-      <c r="G9" s="98"/>
-      <c r="H9" s="98"/>
-      <c r="I9" s="98"/>
-      <c r="J9" s="98"/>
-      <c r="K9" s="98"/>
-      <c r="L9" s="98" t="s">
+      <c r="L9" t="s">
         <v>1718</v>
       </c>
-      <c r="M9" s="98"/>
-      <c r="N9" s="98"/>
-      <c r="O9" s="98"/>
-      <c r="P9" s="98"/>
-      <c r="Q9" s="98"/>
-      <c r="R9" s="98"/>
-      <c r="S9" s="98"/>
-      <c r="T9" s="98"/>
-      <c r="U9" s="98"/>
-      <c r="V9" s="98"/>
       <c r="W9" s="65"/>
-      <c r="X9" s="98"/>
-      <c r="Y9" s="98"/>
-      <c r="Z9" s="98"/>
-      <c r="AA9" s="98"/>
-    </row>
-    <row r="10" spans="3:27">
+    </row>
+    <row r="10" spans="3:23">
       <c r="C10" s="64"/>
       <c r="D10" s="95"/>
       <c r="E10" s="96"/>
@@ -14722,552 +15277,128 @@
       <c r="U10" s="96"/>
       <c r="V10" s="97"/>
       <c r="W10" s="65"/>
-      <c r="X10" s="98"/>
-      <c r="Y10" s="98"/>
-      <c r="Z10" s="98"/>
-      <c r="AA10" s="98"/>
-    </row>
-    <row r="11" spans="3:27">
+    </row>
+    <row r="11" spans="3:23">
       <c r="C11" s="64"/>
       <c r="D11" s="64"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="98"/>
-      <c r="I11" s="98"/>
-      <c r="J11" s="98"/>
-      <c r="K11" s="98"/>
-      <c r="L11" s="98"/>
-      <c r="M11" s="98"/>
-      <c r="N11" s="98"/>
-      <c r="O11" s="98"/>
-      <c r="P11" s="98"/>
-      <c r="Q11" s="98"/>
-      <c r="R11" s="98"/>
-      <c r="S11" s="98"/>
-      <c r="T11" s="98"/>
-      <c r="U11" s="98"/>
       <c r="V11" s="65"/>
       <c r="W11" s="65"/>
-      <c r="X11" s="98"/>
-      <c r="Y11" s="98"/>
-      <c r="Z11" s="98"/>
-      <c r="AA11" s="98"/>
-    </row>
-    <row r="12" spans="3:27">
+    </row>
+    <row r="12" spans="3:23">
       <c r="C12" s="64"/>
       <c r="D12" s="64"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="98"/>
-      <c r="H12" s="98"/>
-      <c r="I12" s="98"/>
-      <c r="J12" s="98"/>
-      <c r="K12" s="98"/>
-      <c r="L12" s="98"/>
-      <c r="M12" s="98"/>
-      <c r="N12" s="98"/>
-      <c r="O12" s="98"/>
-      <c r="P12" s="98"/>
-      <c r="Q12" s="98"/>
-      <c r="R12" s="98"/>
-      <c r="S12" s="98"/>
-      <c r="T12" s="98"/>
-      <c r="U12" s="98"/>
       <c r="V12" s="65"/>
       <c r="W12" s="65"/>
-      <c r="X12" s="98"/>
-      <c r="Y12" s="98"/>
-      <c r="Z12" s="98"/>
-      <c r="AA12" s="98"/>
-    </row>
-    <row r="13" spans="3:27">
+    </row>
+    <row r="13" spans="3:23">
       <c r="C13" s="64"/>
       <c r="D13" s="64"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="98"/>
-      <c r="G13" s="98"/>
-      <c r="H13" s="98"/>
-      <c r="I13" s="98"/>
-      <c r="J13" s="98"/>
-      <c r="K13" s="98"/>
-      <c r="L13" s="98"/>
-      <c r="M13" s="98"/>
-      <c r="N13" s="98"/>
-      <c r="O13" s="98"/>
-      <c r="P13" s="98"/>
-      <c r="Q13" s="98"/>
-      <c r="R13" s="98"/>
-      <c r="S13" s="98"/>
-      <c r="T13" s="98"/>
-      <c r="U13" s="98"/>
       <c r="V13" s="65"/>
       <c r="W13" s="65"/>
-      <c r="X13" s="98"/>
-      <c r="Y13" s="98"/>
-      <c r="Z13" s="98"/>
-      <c r="AA13" s="98"/>
-    </row>
-    <row r="14" spans="3:27">
+    </row>
+    <row r="14" spans="3:23">
       <c r="C14" s="64"/>
       <c r="D14" s="64"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="98"/>
-      <c r="G14" s="98"/>
-      <c r="H14" s="98"/>
-      <c r="I14" s="98"/>
-      <c r="J14" s="98"/>
-      <c r="K14" s="98"/>
-      <c r="L14" s="98"/>
-      <c r="M14" s="98"/>
-      <c r="N14" s="98"/>
-      <c r="O14" s="98"/>
-      <c r="P14" s="98"/>
-      <c r="Q14" s="98"/>
-      <c r="R14" s="98"/>
-      <c r="S14" s="98"/>
-      <c r="T14" s="98"/>
-      <c r="U14" s="98"/>
       <c r="V14" s="65"/>
       <c r="W14" s="65"/>
-      <c r="X14" s="98"/>
-      <c r="Y14" s="98"/>
-      <c r="Z14" s="98"/>
-      <c r="AA14" s="98"/>
-    </row>
-    <row r="15" spans="3:27">
+    </row>
+    <row r="15" spans="3:23">
       <c r="C15" s="64"/>
       <c r="D15" s="64"/>
-      <c r="E15" s="98"/>
-      <c r="F15" s="98"/>
-      <c r="G15" s="98"/>
-      <c r="H15" s="98"/>
-      <c r="I15" s="98"/>
-      <c r="J15" s="98"/>
-      <c r="K15" s="98"/>
-      <c r="L15" s="98"/>
-      <c r="M15" s="98"/>
-      <c r="N15" s="98"/>
-      <c r="O15" s="98"/>
-      <c r="P15" s="98"/>
-      <c r="Q15" s="98"/>
-      <c r="R15" s="98"/>
-      <c r="S15" s="98"/>
-      <c r="T15" s="98"/>
-      <c r="U15" s="98"/>
       <c r="V15" s="65"/>
       <c r="W15" s="65"/>
-      <c r="X15" s="98"/>
-      <c r="Y15" s="98"/>
-      <c r="Z15" s="98"/>
-      <c r="AA15" s="98"/>
-    </row>
-    <row r="16" spans="3:27">
+    </row>
+    <row r="16" spans="3:23">
       <c r="C16" s="64"/>
       <c r="D16" s="64"/>
-      <c r="E16" s="98"/>
-      <c r="F16" s="98"/>
-      <c r="G16" s="98"/>
-      <c r="H16" s="98"/>
-      <c r="I16" s="98"/>
-      <c r="J16" s="98"/>
-      <c r="K16" s="98"/>
-      <c r="L16" s="98"/>
-      <c r="M16" s="98"/>
-      <c r="N16" s="98"/>
-      <c r="O16" s="98"/>
-      <c r="P16" s="98"/>
-      <c r="Q16" s="98"/>
-      <c r="R16" s="98"/>
-      <c r="S16" s="98"/>
-      <c r="T16" s="98"/>
-      <c r="U16" s="98"/>
       <c r="V16" s="65"/>
       <c r="W16" s="65"/>
-      <c r="X16" s="98"/>
-      <c r="Y16" s="98"/>
-      <c r="Z16" s="98"/>
-      <c r="AA16" s="98"/>
-    </row>
-    <row r="17" spans="3:27">
+    </row>
+    <row r="17" spans="3:23">
       <c r="C17" s="64"/>
       <c r="D17" s="64"/>
-      <c r="E17" s="98"/>
-      <c r="F17" s="98"/>
-      <c r="G17" s="98"/>
-      <c r="H17" s="98"/>
-      <c r="I17" s="98"/>
-      <c r="J17" s="98"/>
-      <c r="K17" s="98"/>
-      <c r="L17" s="98"/>
-      <c r="M17" s="98"/>
-      <c r="N17" s="98"/>
-      <c r="O17" s="98"/>
-      <c r="P17" s="98"/>
-      <c r="Q17" s="98"/>
-      <c r="R17" s="98"/>
-      <c r="S17" s="98"/>
-      <c r="T17" s="98"/>
-      <c r="U17" s="98"/>
       <c r="V17" s="65"/>
       <c r="W17" s="65"/>
-      <c r="X17" s="98"/>
-      <c r="Y17" s="98"/>
-      <c r="Z17" s="98"/>
-      <c r="AA17" s="98"/>
-    </row>
-    <row r="18" spans="3:27">
+    </row>
+    <row r="18" spans="3:23">
       <c r="C18" s="64"/>
       <c r="D18" s="64"/>
-      <c r="E18" s="98"/>
-      <c r="F18" s="98"/>
-      <c r="G18" s="98"/>
-      <c r="H18" s="98"/>
-      <c r="I18" s="98"/>
-      <c r="J18" s="98"/>
-      <c r="K18" s="98"/>
-      <c r="L18" s="98"/>
-      <c r="M18" s="98"/>
-      <c r="N18" s="98"/>
-      <c r="O18" s="98"/>
-      <c r="P18" s="98"/>
-      <c r="Q18" s="98"/>
-      <c r="R18" s="98"/>
-      <c r="S18" s="98"/>
-      <c r="T18" s="98"/>
-      <c r="U18" s="98"/>
       <c r="V18" s="65"/>
       <c r="W18" s="65"/>
-      <c r="X18" s="98"/>
-      <c r="Y18" s="98"/>
-      <c r="Z18" s="98"/>
-      <c r="AA18" s="98"/>
-    </row>
-    <row r="19" spans="3:27">
+    </row>
+    <row r="19" spans="3:23">
       <c r="C19" s="64"/>
       <c r="D19" s="64"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
-      <c r="H19" s="98"/>
-      <c r="I19" s="98"/>
-      <c r="J19" s="98"/>
-      <c r="K19" s="98"/>
-      <c r="L19" s="98"/>
-      <c r="M19" s="98"/>
-      <c r="N19" s="98"/>
-      <c r="O19" s="98"/>
-      <c r="P19" s="98"/>
-      <c r="Q19" s="98"/>
-      <c r="R19" s="98"/>
-      <c r="S19" s="98"/>
-      <c r="T19" s="98"/>
-      <c r="U19" s="98"/>
       <c r="V19" s="65"/>
       <c r="W19" s="65"/>
-      <c r="X19" s="98"/>
-      <c r="Y19" s="98"/>
-      <c r="Z19" s="98"/>
-      <c r="AA19" s="98"/>
-    </row>
-    <row r="20" spans="3:27">
+    </row>
+    <row r="20" spans="3:23">
       <c r="C20" s="64"/>
       <c r="D20" s="64"/>
-      <c r="E20" s="98"/>
-      <c r="F20" s="98"/>
-      <c r="G20" s="98"/>
-      <c r="H20" s="98"/>
-      <c r="I20" s="98"/>
-      <c r="J20" s="98"/>
-      <c r="K20" s="98"/>
-      <c r="L20" s="98"/>
-      <c r="M20" s="98"/>
-      <c r="N20" s="98"/>
-      <c r="O20" s="98"/>
-      <c r="P20" s="98"/>
-      <c r="Q20" s="98"/>
-      <c r="R20" s="98"/>
-      <c r="S20" s="98"/>
-      <c r="T20" s="98"/>
-      <c r="U20" s="98"/>
       <c r="V20" s="65"/>
       <c r="W20" s="65"/>
-      <c r="X20" s="98"/>
-      <c r="Y20" s="98"/>
-      <c r="Z20" s="98"/>
-      <c r="AA20" s="98"/>
-    </row>
-    <row r="21" spans="3:27">
+    </row>
+    <row r="21" spans="3:23">
       <c r="C21" s="64"/>
       <c r="D21" s="64"/>
-      <c r="E21" s="98"/>
-      <c r="F21" s="98"/>
-      <c r="G21" s="98"/>
-      <c r="H21" s="98"/>
-      <c r="I21" s="98"/>
-      <c r="J21" s="98"/>
-      <c r="K21" s="98"/>
-      <c r="L21" s="98"/>
-      <c r="M21" s="98"/>
-      <c r="N21" s="98"/>
-      <c r="O21" s="98"/>
-      <c r="P21" s="98"/>
-      <c r="Q21" s="98"/>
-      <c r="R21" s="98"/>
-      <c r="S21" s="98"/>
-      <c r="T21" s="98"/>
-      <c r="U21" s="98"/>
       <c r="V21" s="65"/>
       <c r="W21" s="65"/>
-      <c r="X21" s="98"/>
-      <c r="Y21" s="98"/>
-      <c r="Z21" s="98"/>
-      <c r="AA21" s="98"/>
-    </row>
-    <row r="22" spans="3:27">
+    </row>
+    <row r="22" spans="3:23">
       <c r="C22" s="64"/>
       <c r="D22" s="64"/>
-      <c r="E22" s="98"/>
-      <c r="F22" s="98"/>
-      <c r="G22" s="98"/>
-      <c r="H22" s="98"/>
-      <c r="I22" s="98"/>
-      <c r="J22" s="98"/>
-      <c r="K22" s="98"/>
-      <c r="L22" s="98"/>
-      <c r="M22" s="98"/>
-      <c r="N22" s="98"/>
-      <c r="O22" s="98"/>
-      <c r="P22" s="98"/>
-      <c r="Q22" s="98"/>
-      <c r="R22" s="98"/>
-      <c r="S22" s="98"/>
-      <c r="T22" s="98"/>
-      <c r="U22" s="98"/>
       <c r="V22" s="65"/>
       <c r="W22" s="65"/>
-      <c r="X22" s="98"/>
-      <c r="Y22" s="98"/>
-      <c r="Z22" s="98"/>
-      <c r="AA22" s="98"/>
-    </row>
-    <row r="23" spans="3:27">
+    </row>
+    <row r="23" spans="3:23">
       <c r="C23" s="64"/>
       <c r="D23" s="64"/>
-      <c r="E23" s="98"/>
-      <c r="F23" s="98"/>
-      <c r="G23" s="98"/>
-      <c r="H23" s="98"/>
-      <c r="I23" s="98"/>
-      <c r="J23" s="98"/>
-      <c r="K23" s="98"/>
-      <c r="L23" s="98"/>
-      <c r="M23" s="98"/>
-      <c r="N23" s="98"/>
-      <c r="O23" s="98"/>
-      <c r="P23" s="98"/>
-      <c r="Q23" s="98"/>
-      <c r="R23" s="98"/>
-      <c r="S23" s="98"/>
-      <c r="T23" s="98"/>
-      <c r="U23" s="98"/>
       <c r="V23" s="65"/>
       <c r="W23" s="65"/>
-      <c r="X23" s="98"/>
-      <c r="Y23" s="98"/>
-      <c r="Z23" s="98"/>
-      <c r="AA23" s="98"/>
-    </row>
-    <row r="24" spans="3:27">
+    </row>
+    <row r="24" spans="3:23">
       <c r="C24" s="64"/>
       <c r="D24" s="64"/>
-      <c r="E24" s="98"/>
-      <c r="F24" s="98"/>
-      <c r="G24" s="98"/>
-      <c r="H24" s="98"/>
-      <c r="I24" s="98"/>
-      <c r="J24" s="98"/>
-      <c r="K24" s="98"/>
-      <c r="L24" s="98"/>
-      <c r="M24" s="98"/>
-      <c r="N24" s="98"/>
-      <c r="O24" s="98"/>
-      <c r="P24" s="98"/>
-      <c r="Q24" s="98"/>
-      <c r="R24" s="98"/>
-      <c r="S24" s="98"/>
-      <c r="T24" s="98"/>
-      <c r="U24" s="98"/>
       <c r="V24" s="65"/>
       <c r="W24" s="65"/>
-      <c r="X24" s="98"/>
-      <c r="Y24" s="98"/>
-      <c r="Z24" s="98"/>
-      <c r="AA24" s="98"/>
-    </row>
-    <row r="25" spans="3:27">
+    </row>
+    <row r="25" spans="3:23">
       <c r="C25" s="64"/>
       <c r="D25" s="64"/>
-      <c r="E25" s="98"/>
-      <c r="F25" s="98"/>
-      <c r="G25" s="98"/>
-      <c r="H25" s="98"/>
-      <c r="I25" s="98"/>
-      <c r="J25" s="98"/>
-      <c r="K25" s="98"/>
-      <c r="L25" s="98"/>
-      <c r="M25" s="98"/>
-      <c r="N25" s="98"/>
-      <c r="O25" s="98"/>
-      <c r="P25" s="98"/>
-      <c r="Q25" s="98"/>
-      <c r="R25" s="98"/>
-      <c r="S25" s="98"/>
-      <c r="T25" s="98"/>
-      <c r="U25" s="98"/>
       <c r="V25" s="65"/>
       <c r="W25" s="65"/>
-      <c r="X25" s="98"/>
-      <c r="Y25" s="98"/>
-      <c r="Z25" s="98"/>
-      <c r="AA25" s="98"/>
-    </row>
-    <row r="26" spans="3:27">
+    </row>
+    <row r="26" spans="3:23">
       <c r="C26" s="64"/>
       <c r="D26" s="64"/>
-      <c r="E26" s="98"/>
-      <c r="F26" s="98"/>
-      <c r="G26" s="98"/>
-      <c r="H26" s="98"/>
-      <c r="I26" s="98"/>
-      <c r="J26" s="98"/>
-      <c r="K26" s="98"/>
-      <c r="L26" s="98"/>
-      <c r="M26" s="98"/>
-      <c r="N26" s="98"/>
-      <c r="O26" s="98"/>
-      <c r="P26" s="98"/>
-      <c r="Q26" s="98"/>
-      <c r="R26" s="98"/>
-      <c r="S26" s="98"/>
-      <c r="T26" s="98"/>
-      <c r="U26" s="98"/>
       <c r="V26" s="65"/>
       <c r="W26" s="65"/>
-      <c r="X26" s="98"/>
-      <c r="Y26" s="98"/>
-      <c r="Z26" s="98"/>
-      <c r="AA26" s="98"/>
-    </row>
-    <row r="27" spans="3:27">
+    </row>
+    <row r="27" spans="3:23">
       <c r="C27" s="64"/>
       <c r="D27" s="64"/>
-      <c r="E27" s="98"/>
-      <c r="F27" s="98"/>
-      <c r="G27" s="98"/>
-      <c r="H27" s="98"/>
-      <c r="I27" s="98"/>
-      <c r="J27" s="98"/>
-      <c r="K27" s="98"/>
-      <c r="L27" s="98"/>
-      <c r="M27" s="98"/>
-      <c r="N27" s="98"/>
-      <c r="O27" s="98"/>
-      <c r="P27" s="98"/>
-      <c r="Q27" s="98"/>
-      <c r="R27" s="98"/>
-      <c r="S27" s="98"/>
-      <c r="T27" s="98"/>
-      <c r="U27" s="98"/>
       <c r="V27" s="65"/>
       <c r="W27" s="65"/>
-      <c r="X27" s="98"/>
-      <c r="Y27" s="98"/>
-      <c r="Z27" s="98"/>
-      <c r="AA27" s="98"/>
-    </row>
-    <row r="28" spans="3:27">
+    </row>
+    <row r="28" spans="3:23">
       <c r="C28" s="64"/>
       <c r="D28" s="64"/>
-      <c r="E28" s="98"/>
-      <c r="F28" s="98"/>
-      <c r="G28" s="98"/>
-      <c r="H28" s="98"/>
-      <c r="I28" s="98"/>
-      <c r="J28" s="98"/>
-      <c r="K28" s="98"/>
-      <c r="L28" s="98"/>
-      <c r="M28" s="98"/>
-      <c r="N28" s="98"/>
-      <c r="O28" s="98"/>
-      <c r="P28" s="98"/>
-      <c r="Q28" s="98"/>
-      <c r="R28" s="98"/>
-      <c r="S28" s="98"/>
-      <c r="T28" s="98"/>
-      <c r="U28" s="98"/>
       <c r="V28" s="65"/>
       <c r="W28" s="65"/>
-      <c r="X28" s="98"/>
-      <c r="Y28" s="98"/>
-      <c r="Z28" s="98"/>
-      <c r="AA28" s="98"/>
-    </row>
-    <row r="29" spans="3:27">
+    </row>
+    <row r="29" spans="3:23">
       <c r="C29" s="64"/>
       <c r="D29" s="64"/>
-      <c r="E29" s="98"/>
-      <c r="F29" s="98"/>
-      <c r="G29" s="98"/>
-      <c r="H29" s="98"/>
-      <c r="I29" s="98"/>
-      <c r="J29" s="98"/>
-      <c r="K29" s="98"/>
-      <c r="L29" s="98"/>
-      <c r="M29" s="98"/>
-      <c r="N29" s="98"/>
-      <c r="O29" s="98"/>
-      <c r="P29" s="98"/>
-      <c r="Q29" s="98"/>
-      <c r="R29" s="98"/>
-      <c r="S29" s="98"/>
-      <c r="T29" s="98"/>
-      <c r="U29" s="98"/>
       <c r="V29" s="65"/>
       <c r="W29" s="65"/>
-      <c r="X29" s="98"/>
-      <c r="Y29" s="98"/>
-      <c r="Z29" s="98"/>
-      <c r="AA29" s="98"/>
-    </row>
-    <row r="30" spans="3:27">
+    </row>
+    <row r="30" spans="3:23">
       <c r="C30" s="64"/>
       <c r="D30" s="64"/>
-      <c r="E30" s="98"/>
-      <c r="F30" s="98"/>
-      <c r="G30" s="98"/>
-      <c r="H30" s="98"/>
-      <c r="I30" s="98"/>
-      <c r="J30" s="98"/>
-      <c r="K30" s="98"/>
-      <c r="L30" s="98"/>
-      <c r="M30" s="98"/>
-      <c r="N30" s="98"/>
-      <c r="O30" s="98"/>
-      <c r="P30" s="98"/>
-      <c r="Q30" s="98"/>
-      <c r="R30" s="98"/>
-      <c r="S30" s="98"/>
-      <c r="T30" s="98"/>
-      <c r="U30" s="98"/>
       <c r="V30" s="65"/>
       <c r="W30" s="65"/>
-      <c r="X30" s="98"/>
-      <c r="Y30" s="98"/>
-      <c r="Z30" s="98"/>
-      <c r="AA30" s="98"/>
-    </row>
-    <row r="31" spans="3:27" ht="18.600000000000001" thickBot="1">
+    </row>
+    <row r="31" spans="3:23" ht="18.600000000000001" thickBot="1">
       <c r="C31" s="64"/>
       <c r="D31" s="66"/>
       <c r="E31" s="67"/>
@@ -15289,12 +15420,8 @@
       <c r="U31" s="67"/>
       <c r="V31" s="68"/>
       <c r="W31" s="65"/>
-      <c r="X31" s="98"/>
-      <c r="Y31" s="98"/>
-      <c r="Z31" s="98"/>
-      <c r="AA31" s="98"/>
-    </row>
-    <row r="32" spans="3:27" ht="13.2" customHeight="1" thickBot="1">
+    </row>
+    <row r="32" spans="3:23" ht="13.2" customHeight="1" thickBot="1">
       <c r="C32" s="66"/>
       <c r="D32" s="67"/>
       <c r="E32" s="67"/>
@@ -15316,10 +15443,6 @@
       <c r="U32" s="67"/>
       <c r="V32" s="67"/>
       <c r="W32" s="68"/>
-      <c r="X32" s="98"/>
-      <c r="Y32" s="98"/>
-      <c r="Z32" s="98"/>
-      <c r="AA32" s="98"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -15329,6 +15452,373 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC349EE6-5475-4F9C-BD43-5DC02797CE07}">
+  <dimension ref="A2:Q56"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <cols>
+    <col min="1" max="1" width="11" style="98" customWidth="1"/>
+    <col min="2" max="6" width="10.8984375" style="98" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="98"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:15">
+      <c r="A2" s="98" t="s">
+        <v>1719</v>
+      </c>
+      <c r="D2" s="98" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="B3" s="100"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="D6" s="98" t="s">
+        <v>1793</v>
+      </c>
+      <c r="G6" s="98" t="s">
+        <v>1795</v>
+      </c>
+      <c r="M6" s="100" t="s">
+        <v>1720</v>
+      </c>
+      <c r="O6" s="100" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="D7" s="98" t="s">
+        <v>1794</v>
+      </c>
+      <c r="M7" s="100" t="s">
+        <v>1721</v>
+      </c>
+      <c r="O7" s="100"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="G8" s="98" t="s">
+        <v>1746</v>
+      </c>
+      <c r="M8" s="100" t="s">
+        <v>1730</v>
+      </c>
+      <c r="O8" s="98" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="G9" s="99"/>
+      <c r="M9" s="100" t="s">
+        <v>1722</v>
+      </c>
+      <c r="O9" s="98" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="G10" s="99" t="s">
+        <v>1747</v>
+      </c>
+      <c r="M10" s="100" t="s">
+        <v>1723</v>
+      </c>
+      <c r="O10" s="98" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="G11" s="99" t="s">
+        <v>1748</v>
+      </c>
+      <c r="M11" s="100"/>
+      <c r="O11" s="98" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="G12" s="99" t="s">
+        <v>1749</v>
+      </c>
+      <c r="M12" s="100" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="G13" s="99" t="s">
+        <v>1750</v>
+      </c>
+      <c r="M13" s="100"/>
+      <c r="O13" s="98" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="M14" s="100" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="G15" s="98" t="s">
+        <v>1792</v>
+      </c>
+      <c r="M15" s="100" t="s">
+        <v>1726</v>
+      </c>
+      <c r="O15" s="98" t="s">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="M16" s="100" t="s">
+        <v>1727</v>
+      </c>
+      <c r="O16" s="98" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17">
+      <c r="M17" s="100" t="s">
+        <v>1728</v>
+      </c>
+      <c r="O17" s="98" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17">
+      <c r="M18" s="100"/>
+      <c r="O18" s="98" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17">
+      <c r="M19" s="100" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17">
+      <c r="O20" s="100" t="s">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17">
+      <c r="O22" s="98" t="s">
+        <v>1780</v>
+      </c>
+      <c r="Q22" s="98" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17">
+      <c r="Q23" s="98" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17">
+      <c r="O24" s="98" t="s">
+        <v>1774</v>
+      </c>
+      <c r="Q24" s="99"/>
+    </row>
+    <row r="25" spans="2:17">
+      <c r="O25" s="98" t="s">
+        <v>1781</v>
+      </c>
+      <c r="Q25" s="102" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17">
+      <c r="O26" s="98" t="s">
+        <v>1775</v>
+      </c>
+      <c r="Q26" s="99" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17">
+      <c r="O27" s="99" t="s">
+        <v>1776</v>
+      </c>
+      <c r="Q27" s="99" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17">
+      <c r="O28" s="99" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17">
+      <c r="B29" s="98" t="s">
+        <v>1758</v>
+      </c>
+      <c r="O29" s="99" t="s">
+        <v>1778</v>
+      </c>
+      <c r="Q29" s="98" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17">
+      <c r="O30" s="99" t="s">
+        <v>1779</v>
+      </c>
+      <c r="Q30" s="101" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17">
+      <c r="B31" s="98" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17">
+      <c r="B32" s="98" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9">
+      <c r="B33" s="98" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9">
+      <c r="B34" s="98" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9">
+      <c r="B35" s="98" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9">
+      <c r="B37" s="98" t="s">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9">
+      <c r="B38" s="98" t="s">
+        <v>1789</v>
+      </c>
+      <c r="I38" s="98" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9">
+      <c r="B40" s="98" t="s">
+        <v>1752</v>
+      </c>
+      <c r="I40" s="98" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9">
+      <c r="B41" s="99"/>
+      <c r="I41" s="98" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9">
+      <c r="B42" s="99" t="s">
+        <v>1753</v>
+      </c>
+      <c r="I42" s="98" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9">
+      <c r="B43" s="99" t="s">
+        <v>1754</v>
+      </c>
+      <c r="I43" s="98" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9">
+      <c r="B44" s="99" t="s">
+        <v>1755</v>
+      </c>
+      <c r="I44" s="98" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9">
+      <c r="B45" s="99" t="s">
+        <v>1756</v>
+      </c>
+      <c r="I45" s="98" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9">
+      <c r="B46" s="99" t="s">
+        <v>1757</v>
+      </c>
+      <c r="I46" s="98" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9">
+      <c r="B47" s="98" t="s">
+        <v>1791</v>
+      </c>
+      <c r="I47" s="98" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9">
+      <c r="I48" s="98" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9">
+      <c r="I49" s="98" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9">
+      <c r="I50" s="98" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9">
+      <c r="I51" s="98" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9">
+      <c r="B52" s="99"/>
+      <c r="I52" s="98" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9">
+      <c r="B53" s="99"/>
+      <c r="I53" s="98" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9">
+      <c r="B54" s="99"/>
+      <c r="I54" s="98" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9">
+      <c r="B55" s="99"/>
+    </row>
+    <row r="56" spans="2:9">
+      <c r="B56" s="99"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F0B575-2DDF-49B9-8DE2-F372EEC2F3B3}">
   <dimension ref="A2:O79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
@@ -16288,7 +16778,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FCFD5C-696C-43AD-A2BD-D69C05CB2D44}">
   <dimension ref="B2:P57"/>
   <sheetFormatPr defaultRowHeight="12.6"/>
@@ -16766,7 +17256,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E898285-845A-4583-B20D-F3A331C07E8E}">
   <dimension ref="B2:R45"/>
   <sheetFormatPr defaultRowHeight="18"/>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A8627AB-B9FC-4EDE-814F-30912DF0A167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF9249D-F5EB-4F8F-9E95-B64C4222A4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="3" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="6" activeTab="13" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="architecture" sheetId="12" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="guitarCrawler" sheetId="9" r:id="rId11"/>
     <sheet name="public API" sheetId="10" r:id="rId12"/>
     <sheet name="guiatr gallery" sheetId="11" r:id="rId13"/>
+    <sheet name="batch監視システム" sheetId="14" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">スキル!$C$3:$O$3</definedName>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3932" uniqueCount="1796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4050" uniqueCount="1886">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -7833,6 +7834,310 @@
     <t>guitar_colors</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>batch_execution --------------- execution_id、batch_name、started_at、finished_at status、message hostname</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>開始時</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>NSERT status = RUNNING</t>
+  </si>
+  <si>
+    <t>終了時</t>
+  </si>
+  <si>
+    <t>UPDATE status = SUCCESS finished_at = now()</t>
+  </si>
+  <si>
+    <t>例外</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>UPDATE status = ERROR message = ex.Message finished_at = now()</t>
+  </si>
+  <si>
+    <t>Goなら</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>try</t>
+  </si>
+  <si>
+    <t>catch(Exception ex)</t>
+  </si>
+  <si>
+    <t>finally</t>
+  </si>
+  <si>
+    <t>defer func() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if r := recover(); r != nil {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // ERROR更新</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    }</t>
+  </si>
+  <si>
+    <t>}()</t>
+  </si>
+  <si>
+    <t>NETなら</t>
+  </si>
+  <si>
+    <t>// ERROR 更新</t>
+    <rPh sb="9" eb="11">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>実行ログだけで</t>
+  </si>
+  <si>
+    <t>batch_name</t>
+  </si>
+  <si>
+    <t>started_at</t>
+  </si>
+  <si>
+    <t>finished_at</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>があれば</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>毎日1回実行されるはずなのに</t>
+  </si>
+  <si>
+    <t>24時間以上SUCCESSがない</t>
+  </si>
+  <si>
+    <t>異常</t>
+  </si>
+  <si>
+    <t>INSERTよりUPDATEの方が楽</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HeartBeat専用テーブルはいらないかも</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Discord通知</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>【異常】</t>
+  </si>
+  <si>
+    <t>CrawlerBatch</t>
+  </si>
+  <si>
+    <t>最後の成功</t>
+  </si>
+  <si>
+    <t>現在</t>
+  </si>
+  <si>
+    <t>31時間実行されていません</t>
+  </si>
+  <si>
+    <t>AutoBattle</t>
+  </si>
+  <si>
+    <t>終了ステータス</t>
+  </si>
+  <si>
+    <t>ERROR</t>
+  </si>
+  <si>
+    <t>System.TimeoutException</t>
+  </si>
+  <si>
+    <t>timeout監視</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>RUNNING</t>
+  </si>
+  <si>
+    <t>7時間前</t>
+  </si>
+  <si>
+    <t>終了レコードがない。</t>
+  </si>
+  <si>
+    <t>つまり</t>
+  </si>
+  <si>
+    <t>途中で死んだ。</t>
+  </si>
+  <si>
+    <t>これも通知対象。</t>
+  </si>
+  <si>
+    <t>RUNNINGが3時間以上継続</t>
+  </si>
+  <si>
+    <t>Docker死んだ問題も検知できる</t>
+  </si>
+  <si>
+    <t>cron死んだ</t>
+  </si>
+  <si>
+    <t>Docker停止</t>
+  </si>
+  <si>
+    <t>コンテナ落ちた</t>
+  </si>
+  <si>
+    <t>OS再起動</t>
+  </si>
+  <si>
+    <t>DB停止</t>
+  </si>
+  <si>
+    <t>全部</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンブ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SUCCESSが更新されない</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ので検知できる。</t>
+  </si>
+  <si>
+    <t>バッチごとに期待実行間隔を持つ</t>
+  </si>
+  <si>
+    <t>batch_master</t>
+  </si>
+  <si>
+    <t>expected_interval_minutes</t>
+  </si>
+  <si>
+    <t>timeout_minutes</t>
+  </si>
+  <si>
+    <t>enabled</t>
+  </si>
+  <si>
+    <t>Batch</t>
+  </si>
+  <si>
+    <t>Interval</t>
+  </si>
+  <si>
+    <t>Timeout</t>
+  </si>
+  <si>
+    <t>Crawler</t>
+  </si>
+  <si>
+    <t>MailSender</t>
+  </si>
+  <si>
+    <t>監視Batchは</t>
+  </si>
+  <si>
+    <t>expected_interval</t>
+  </si>
+  <si>
+    <t>を見るだけ。</t>
+  </si>
+  <si>
+    <t>監視システム自体の監視</t>
+  </si>
+  <si>
+    <t>MonitorBatch</t>
+  </si>
+  <si>
+    <t>MonitorBatch自身もbatch_executionへ記録</t>
+    <rPh sb="31" eb="33">
+      <t>キロク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    ↓</t>
+  </si>
+  <si>
+    <t>各Batch開始</t>
+  </si>
+  <si>
+    <t>INSERT(RUNNING)</t>
+  </si>
+  <si>
+    <t>処理</t>
+  </si>
+  <si>
+    <t>UPDATE(SUCCESS/ERROR)</t>
+  </si>
+  <si>
+    <t>cron</t>
+  </si>
+  <si>
+    <t>↓↓↓</t>
+  </si>
+  <si>
+    <t>batch_execution確認</t>
+  </si>
+  <si>
+    <t>異常ならDiscord通知</t>
+  </si>
+  <si>
+    <t>この構成が一番バランスがいい????</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(コンテナ常駐もあり。長時間sleep併用)</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウチュウ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>チョウジカン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヘイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>テーブルイメージ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>batch_master      ← 設定</t>
+  </si>
+  <si>
+    <t>-------------------------</t>
+  </si>
+  <si>
+    <t>interval_minutes</t>
+  </si>
+  <si>
+    <t>batch_execution   ← 実行ログ</t>
+  </si>
+  <si>
+    <t>execution_id</t>
+  </si>
+  <si>
+    <t>message</t>
+  </si>
 </sst>
 </file>
 
@@ -7841,7 +8146,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7917,6 +8222,15 @@
       <name val="BIZ UDゴシック"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -8237,7 +8551,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -8405,6 +8719,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -17845,6 +18169,567 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD79B98E-03E4-44E6-9FBF-39CA1C89C95A}">
+  <dimension ref="B3:L113"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="2" max="2" width="8.796875" style="73"/>
+    <col min="3" max="3" width="10.59765625" customWidth="1"/>
+    <col min="6" max="6" width="10.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:11">
+      <c r="B3" s="106" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11">
+      <c r="C5" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11">
+      <c r="C7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11">
+      <c r="C8" t="s">
+        <v>1799</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11">
+      <c r="C9" t="s">
+        <v>1801</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11">
+      <c r="C11" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1807</v>
+      </c>
+      <c r="I11" t="s">
+        <v>1812</v>
+      </c>
+      <c r="K11" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11">
+      <c r="E12" t="s">
+        <v>1808</v>
+      </c>
+      <c r="K12" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11">
+      <c r="E13" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11">
+      <c r="E14" t="s">
+        <v>1810</v>
+      </c>
+      <c r="K14" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11">
+      <c r="E15" t="s">
+        <v>1811</v>
+      </c>
+      <c r="K15" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11">
+      <c r="K16" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12">
+      <c r="L17" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12">
+      <c r="K18" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12">
+      <c r="K19" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12">
+      <c r="K20" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12">
+      <c r="K22" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12">
+      <c r="B24" s="106" t="s">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12">
+      <c r="C26" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12">
+      <c r="D27" t="s">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12">
+      <c r="D28" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12">
+      <c r="D29" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12">
+      <c r="D30" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12">
+      <c r="C31" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12">
+      <c r="D32" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="D33" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="D35" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6">
+      <c r="D37" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6">
+      <c r="B39" s="106" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6">
+      <c r="C41" t="s">
+        <v>1826</v>
+      </c>
+      <c r="F41" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6">
+      <c r="C43" t="s">
+        <v>1827</v>
+      </c>
+      <c r="F43" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6">
+      <c r="C45" t="s">
+        <v>1828</v>
+      </c>
+      <c r="F45" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6">
+      <c r="C47" s="103">
+        <v>46220.041666666664</v>
+      </c>
+      <c r="F47" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7">
+      <c r="C49" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7">
+      <c r="C51" s="103">
+        <v>46221.333333333336</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7">
+      <c r="C53" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7">
+      <c r="B56" s="106" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7">
+      <c r="C57" t="s">
+        <v>1836</v>
+      </c>
+      <c r="D57" t="s">
+        <v>1838</v>
+      </c>
+      <c r="G57" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7">
+      <c r="D58" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7">
+      <c r="C59" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D59" t="s">
+        <v>1840</v>
+      </c>
+      <c r="G59" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7">
+      <c r="D60" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7">
+      <c r="C61" t="s">
+        <v>1837</v>
+      </c>
+      <c r="G61" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7">
+      <c r="B64" s="106" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10">
+      <c r="C66" t="s">
+        <v>1844</v>
+      </c>
+      <c r="E66" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10">
+      <c r="C67" t="s">
+        <v>1845</v>
+      </c>
+      <c r="E67" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10">
+      <c r="C68" t="s">
+        <v>1846</v>
+      </c>
+      <c r="E68" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10">
+      <c r="C69" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10">
+      <c r="C70" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10">
+      <c r="B72" s="106" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10">
+      <c r="C74" t="s">
+        <v>1853</v>
+      </c>
+      <c r="F74" s="104" t="s">
+        <v>1857</v>
+      </c>
+      <c r="G74" s="104" t="s">
+        <v>1858</v>
+      </c>
+      <c r="H74" s="104" t="s">
+        <v>1859</v>
+      </c>
+      <c r="J74" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10">
+      <c r="C75" t="s">
+        <v>1815</v>
+      </c>
+      <c r="F75" s="105" t="s">
+        <v>1860</v>
+      </c>
+      <c r="G75" s="105">
+        <v>1440</v>
+      </c>
+      <c r="H75" s="105">
+        <v>180</v>
+      </c>
+      <c r="J75" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10">
+      <c r="C76" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F76" s="105" t="s">
+        <v>1831</v>
+      </c>
+      <c r="G76" s="105">
+        <v>30</v>
+      </c>
+      <c r="H76" s="105">
+        <v>10</v>
+      </c>
+      <c r="J76" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10">
+      <c r="C77" t="s">
+        <v>1855</v>
+      </c>
+      <c r="F77" s="105" t="s">
+        <v>1861</v>
+      </c>
+      <c r="G77" s="105">
+        <v>5</v>
+      </c>
+      <c r="H77" s="105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10">
+      <c r="C78" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10">
+      <c r="B80" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5">
+      <c r="C82" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5">
+      <c r="B84" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5">
+      <c r="D86" t="s">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5">
+      <c r="D87" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5">
+      <c r="D88" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5">
+      <c r="D89" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5">
+      <c r="D90" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="91" spans="2:5">
+      <c r="D91" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="92" spans="2:5">
+      <c r="D92" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="93" spans="2:5">
+      <c r="D93" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5">
+      <c r="D94" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="95" spans="2:5">
+      <c r="D95" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5">
+      <c r="D96" t="s">
+        <v>1873</v>
+      </c>
+      <c r="E96" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7">
+      <c r="D97" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7">
+      <c r="D98" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7">
+      <c r="D99" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="100" spans="2:7">
+      <c r="D100" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7">
+      <c r="D101" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7">
+      <c r="D102" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7">
+      <c r="B104" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7">
+      <c r="B105"/>
+    </row>
+    <row r="106" spans="2:7">
+      <c r="C106" t="s">
+        <v>7</v>
+      </c>
+      <c r="D106" t="s">
+        <v>1880</v>
+      </c>
+      <c r="G106" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7">
+      <c r="D107" t="s">
+        <v>1881</v>
+      </c>
+      <c r="G107" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7">
+      <c r="D108" t="s">
+        <v>1815</v>
+      </c>
+      <c r="G108" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7">
+      <c r="D109" t="s">
+        <v>1882</v>
+      </c>
+      <c r="G109" t="s">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="110" spans="2:7">
+      <c r="D110" t="s">
+        <v>1855</v>
+      </c>
+      <c r="G110" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7">
+      <c r="D111" t="s">
+        <v>1856</v>
+      </c>
+      <c r="G111" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="112" spans="2:7">
+      <c r="G112" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="113" spans="7:7">
+      <c r="G113" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF9249D-F5EB-4F8F-9E95-B64C4222A4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE80C35B-67D7-4B63-8240-D56A02478AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="6" activeTab="13" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="778" firstSheet="6" activeTab="13" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="architecture" sheetId="12" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4050" uniqueCount="1886">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4093" uniqueCount="1926">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -7919,14 +7919,7 @@
     <t>毎日1回実行されるはずなのに</t>
   </si>
   <si>
-    <t>24時間以上SUCCESSがない</t>
-  </si>
-  <si>
     <t>異常</t>
-  </si>
-  <si>
-    <t>INSERTよりUPDATEの方が楽</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>HeartBeat専用テーブルはいらないかも</t>
@@ -8127,16 +8120,253 @@
     <t>-------------------------</t>
   </si>
   <si>
-    <t>interval_minutes</t>
-  </si>
-  <si>
     <t>batch_execution   ← 実行ログ</t>
   </si>
   <si>
-    <t>execution_id</t>
-  </si>
-  <si>
     <t>message</t>
+  </si>
+  <si>
+    <t>INSERTよりUPDATEの方が楽？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>24時間以上SUCCESSがない</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>通知のトリガー</t>
+    <rPh sb="0" eb="2">
+      <t>ツウチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>exception、panicのメッセージ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>監視対象とするか否か</t>
+    <rPh sb="0" eb="4">
+      <t>カンシタイショウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>イナ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>完了するであろう時間</t>
+    <rPh sb="0" eb="2">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>start_at</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>end_at</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>開始してから監視を待つ時間</t>
+    <rPh sb="0" eb="2">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンシ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>expected_duration_minutes</t>
+  </si>
+  <si>
+    <t>処理の流れ</t>
+    <rPh sb="0" eb="2">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナガ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>① バッチ開始</t>
+  </si>
+  <si>
+    <t>INSERT</t>
+  </si>
+  <si>
+    <t>----------------</t>
+  </si>
+  <si>
+    <t>id        = 100</t>
+  </si>
+  <si>
+    <t>batch_id  = 1</t>
+  </si>
+  <si>
+    <t>start_at  = 06:00</t>
+  </si>
+  <si>
+    <t>end_at    = NULL</t>
+  </si>
+  <si>
+    <t>status    = STARTED</t>
+  </si>
+  <si>
+    <t>message   = NULL</t>
+  </si>
+  <si>
+    <t>② 正常終了</t>
+  </si>
+  <si>
+    <t>UPDATE id = 100</t>
+  </si>
+  <si>
+    <t>end_at    = 06:03</t>
+  </si>
+  <si>
+    <t>status    = SUCCESS</t>
+  </si>
+  <si>
+    <t>③ 例外終了</t>
+  </si>
+  <si>
+    <t>end_at    = 06:02</t>
+  </si>
+  <si>
+    <t>status    = ERROR</t>
+  </si>
+  <si>
+    <t>message   = "..."</t>
+  </si>
+  <si>
+    <t>status  = TIMEOUT</t>
+  </si>
+  <si>
+    <t>message = "Execution timeout"</t>
+  </si>
+  <si>
+    <t>scheduled_time</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>log_id</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>STARTED or SUCCESS or ERROR or TIMEOUT or NOT_STARTED or SLOW</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ステータスがERROR or TIMEOUT or NOT_STARTED or SLOW</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ERROR</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TIMEOUT</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>NOT_STARTED</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SLOW</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>例外、パニック発生</t>
+    <rPh sb="0" eb="2">
+      <t>レイガイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハッセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>時間内に終えてない（timeout_minutes &lt; end_at - start_at）</t>
+    <rPh sb="0" eb="2">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>start_delay_time</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>予定時刻からバッチ開始までの猶予</t>
+    <rPh sb="0" eb="2">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジコク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ユウヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>予定時刻～猶予時間中に開始していない</t>
+    <rPh sb="0" eb="2">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジコク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ユウヨ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カイシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>想定より完了が遅い（expected_duration_minutes &lt; end_at - start_at</t>
+    <rPh sb="0" eb="2">
+      <t>ソウテイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オソ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -12259,8 +12489,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7985930" y="1467837"/>
-          <a:ext cx="1820498" cy="1167653"/>
+          <a:off x="7911971" y="1528349"/>
+          <a:ext cx="1800328" cy="1214718"/>
           <a:chOff x="8992083" y="208776"/>
           <a:chExt cx="1814762" cy="1244600"/>
         </a:xfrm>
@@ -12569,8 +12799,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="11283097" y="2938582"/>
-          <a:ext cx="1842700" cy="1889768"/>
+          <a:off x="11175520" y="3059605"/>
+          <a:ext cx="1822530" cy="1963728"/>
           <a:chOff x="8549484" y="3956874"/>
           <a:chExt cx="1810288" cy="1437363"/>
         </a:xfrm>
@@ -13121,8 +13351,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4721439" y="1597449"/>
-          <a:ext cx="1890124" cy="3208246"/>
+          <a:off x="4681098" y="1657961"/>
+          <a:ext cx="1869953" cy="3342717"/>
           <a:chOff x="5970441" y="628674"/>
           <a:chExt cx="1893913" cy="3428095"/>
         </a:xfrm>
@@ -13590,8 +13820,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10941124" y="6969538"/>
-          <a:ext cx="2220201" cy="2422569"/>
+          <a:off x="10840271" y="7258650"/>
+          <a:ext cx="2193307" cy="2523422"/>
           <a:chOff x="12007370" y="5957071"/>
           <a:chExt cx="2223130" cy="2581251"/>
         </a:xfrm>
@@ -13797,8 +14027,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14468704" y="4627977"/>
-          <a:ext cx="2246929" cy="1653108"/>
+          <a:off x="14334233" y="4816236"/>
+          <a:ext cx="2220036" cy="1720343"/>
           <a:chOff x="15050343" y="4729843"/>
           <a:chExt cx="2243515" cy="1763032"/>
         </a:xfrm>
@@ -14227,8 +14457,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6914030" y="5002306"/>
-          <a:ext cx="1795181" cy="1264024"/>
+          <a:off x="6846794" y="5210735"/>
+          <a:ext cx="1781735" cy="1311089"/>
           <a:chOff x="6846794" y="5210735"/>
           <a:chExt cx="2341399" cy="1311089"/>
         </a:xfrm>
@@ -14604,8 +14834,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3760297" y="7340331"/>
-          <a:ext cx="2355242" cy="1808149"/>
+          <a:off x="3726679" y="7642890"/>
+          <a:ext cx="2335072" cy="1882107"/>
           <a:chOff x="3726679" y="7642891"/>
           <a:chExt cx="2335072" cy="1468663"/>
         </a:xfrm>
@@ -15528,13 +15758,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6672014-33B5-48C4-9202-55E4E667EEEF}">
   <dimension ref="C5:W32"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="3" width="8.796875" customWidth="1"/>
-    <col min="27" max="27" width="4.3984375" customWidth="1"/>
+    <col min="2" max="3" width="8.75" customWidth="1"/>
+    <col min="27" max="27" width="4.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:23" ht="18.600000000000001" thickBot="1">
+    <row r="5" spans="3:23" ht="19.5" thickBot="1">
       <c r="V5" s="67"/>
       <c r="W5" s="67"/>
     </row>
@@ -15568,7 +15798,7 @@
       <c r="C8" s="64"/>
       <c r="W8" s="65"/>
     </row>
-    <row r="9" spans="3:23" ht="18.600000000000001" thickBot="1">
+    <row r="9" spans="3:23" ht="19.5" thickBot="1">
       <c r="C9" s="64"/>
       <c r="L9" t="s">
         <v>1706</v>
@@ -15718,7 +15948,7 @@
       <c r="V30" s="65"/>
       <c r="W30" s="65"/>
     </row>
-    <row r="31" spans="3:23" ht="18.600000000000001" thickBot="1">
+    <row r="31" spans="3:23" ht="19.5" thickBot="1">
       <c r="C31" s="64"/>
       <c r="D31" s="66"/>
       <c r="E31" s="67"/>
@@ -15741,7 +15971,7 @@
       <c r="V31" s="68"/>
       <c r="W31" s="65"/>
     </row>
-    <row r="32" spans="3:23" ht="13.2" customHeight="1" thickBot="1">
+    <row r="32" spans="3:23" ht="13.15" customHeight="1" thickBot="1">
       <c r="C32" s="66"/>
       <c r="D32" s="67"/>
       <c r="E32" s="67"/>
@@ -15774,10 +16004,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC349EE6-5475-4F9C-BD43-5DC02797CE07}">
   <dimension ref="A2:Q56"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11" style="98" customWidth="1"/>
-    <col min="2" max="6" width="10.8984375" style="98" customWidth="1"/>
+    <col min="2" max="6" width="10.875" style="98" customWidth="1"/>
     <col min="7" max="16384" width="9" style="98"/>
   </cols>
   <sheetData>
@@ -16141,10 +16371,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F0B575-2DDF-49B9-8DE2-F372EEC2F3B3}">
   <dimension ref="A2:O79"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.8984375" style="1" customWidth="1"/>
-    <col min="2" max="6" width="10.8984375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.875" style="1" customWidth="1"/>
+    <col min="2" max="6" width="10.875" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -16176,7 +16406,7 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="18">
+    <row r="4" spans="1:15" ht="18.75">
       <c r="A4" s="1" t="s">
         <v>1280</v>
       </c>
@@ -16205,7 +16435,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="13.2">
+    <row r="5" spans="1:15">
       <c r="B5" s="58" t="s">
         <v>1175</v>
       </c>
@@ -16222,7 +16452,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="13.2">
+    <row r="6" spans="1:15">
       <c r="B6" s="58" t="s">
         <v>1176</v>
       </c>
@@ -16245,7 +16475,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="13.2">
+    <row r="7" spans="1:15">
       <c r="B7" s="58" t="s">
         <v>1189</v>
       </c>
@@ -16274,7 +16504,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="13.2">
+    <row r="8" spans="1:15">
       <c r="B8" s="58" t="s">
         <v>1177</v>
       </c>
@@ -16303,7 +16533,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="13.2">
+    <row r="9" spans="1:15">
       <c r="B9" s="58" t="s">
         <v>1178</v>
       </c>
@@ -16329,7 +16559,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="13.2">
+    <row r="10" spans="1:15">
       <c r="B10" s="58" t="s">
         <v>1179</v>
       </c>
@@ -16355,7 +16585,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="13.2">
+    <row r="11" spans="1:15">
       <c r="B11" s="58" t="s">
         <v>1180</v>
       </c>
@@ -16381,7 +16611,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="13.2">
+    <row r="12" spans="1:15">
       <c r="B12" s="58" t="s">
         <v>1181</v>
       </c>
@@ -16407,7 +16637,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="13.2">
+    <row r="13" spans="1:15">
       <c r="B13" s="58" t="s">
         <v>1182</v>
       </c>
@@ -16430,7 +16660,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="13.2">
+    <row r="14" spans="1:15">
       <c r="B14" s="58" t="s">
         <v>1183</v>
       </c>
@@ -16453,7 +16683,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="13.2">
+    <row r="15" spans="1:15">
       <c r="B15" s="58" t="s">
         <v>1184</v>
       </c>
@@ -16476,7 +16706,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="13.2">
+    <row r="16" spans="1:15">
       <c r="B16" s="58" t="s">
         <v>1185</v>
       </c>
@@ -16496,7 +16726,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="17" spans="2:10" ht="13.2">
+    <row r="17" spans="2:10">
       <c r="B17" s="58" t="s">
         <v>1186</v>
       </c>
@@ -16516,7 +16746,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="18" spans="2:10" ht="13.2">
+    <row r="18" spans="2:10">
       <c r="B18" s="58" t="s">
         <v>1190</v>
       </c>
@@ -16536,7 +16766,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="19" spans="2:10" ht="13.2">
+    <row r="19" spans="2:10">
       <c r="B19" s="58" t="s">
         <v>1187</v>
       </c>
@@ -16556,7 +16786,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="20" spans="2:10" ht="13.2">
+    <row r="20" spans="2:10">
       <c r="B20" s="58" t="s">
         <v>1191</v>
       </c>
@@ -17101,9 +17331,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FCFD5C-696C-43AD-A2BD-D69C05CB2D44}">
   <dimension ref="B2:P57"/>
-  <sheetFormatPr defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
@@ -17579,9 +17809,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E898285-845A-4583-B20D-F3A331C07E8E}">
   <dimension ref="B2:R45"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="13" max="13" width="8.59765625" customWidth="1"/>
+    <col min="13" max="13" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18">
@@ -17596,7 +17826,7 @@
       <c r="O2" s="86"/>
       <c r="P2" s="86"/>
     </row>
-    <row r="3" spans="2:18" ht="18.600000000000001" thickBot="1">
+    <row r="3" spans="2:18" ht="19.5" thickBot="1">
       <c r="F3" s="89" t="s">
         <v>1582</v>
       </c>
@@ -17718,7 +17948,7 @@
       <c r="P10" s="65"/>
       <c r="R10" s="84"/>
     </row>
-    <row r="11" spans="2:18" ht="18.600000000000001" thickBot="1">
+    <row r="11" spans="2:18" ht="19.5" thickBot="1">
       <c r="F11" s="91"/>
       <c r="I11" s="75"/>
       <c r="J11" s="66"/>
@@ -17807,7 +18037,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="22" spans="4:18" ht="18.600000000000001" thickBot="1">
+    <row r="22" spans="4:18" ht="19.5" thickBot="1">
       <c r="D22" s="80"/>
       <c r="E22" s="81"/>
       <c r="F22" s="81"/>
@@ -17936,7 +18166,7 @@
       </c>
       <c r="N29" s="84"/>
     </row>
-    <row r="30" spans="4:18" ht="18.600000000000001" thickBot="1">
+    <row r="30" spans="4:18" ht="19.5" thickBot="1">
       <c r="D30" s="83"/>
       <c r="E30" s="77"/>
       <c r="F30" s="78"/>
@@ -18171,25 +18401,25 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD79B98E-03E4-44E6-9FBF-39CA1C89C95A}">
-  <dimension ref="B3:L113"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="B3:L155"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="8.796875" style="73"/>
-    <col min="3" max="3" width="10.59765625" customWidth="1"/>
-    <col min="6" max="6" width="10.8984375" customWidth="1"/>
+    <col min="2" max="2" width="8.75" style="73"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="6" max="6" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:11">
-      <c r="B3" s="106" t="s">
-        <v>1823</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11">
+    <row r="3" spans="2:10">
+      <c r="B3" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10">
       <c r="C5" t="s">
         <v>1796</v>
       </c>
     </row>
-    <row r="7" spans="2:11">
+    <row r="7" spans="2:10">
       <c r="C7" t="s">
         <v>1797</v>
       </c>
@@ -18197,7 +18427,7 @@
         <v>1798</v>
       </c>
     </row>
-    <row r="8" spans="2:11">
+    <row r="8" spans="2:10">
       <c r="C8" t="s">
         <v>1799</v>
       </c>
@@ -18205,7 +18435,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="9" spans="2:11">
+    <row r="9" spans="2:10">
       <c r="C9" t="s">
         <v>1801</v>
       </c>
@@ -18213,51 +18443,51 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="11" spans="2:11">
+    <row r="11" spans="2:10">
       <c r="C11" t="s">
         <v>1803</v>
       </c>
       <c r="E11" t="s">
         <v>1807</v>
       </c>
-      <c r="I11" t="s">
+      <c r="H11" t="s">
         <v>1812</v>
       </c>
-      <c r="K11" t="s">
+      <c r="J11" t="s">
         <v>1804</v>
       </c>
     </row>
-    <row r="12" spans="2:11">
+    <row r="12" spans="2:10">
       <c r="E12" t="s">
         <v>1808</v>
       </c>
-      <c r="K12" t="s">
+      <c r="J12" t="s">
         <v>1590</v>
       </c>
     </row>
-    <row r="13" spans="2:11">
+    <row r="13" spans="2:10">
       <c r="E13" t="s">
         <v>1809</v>
       </c>
     </row>
-    <row r="14" spans="2:11">
+    <row r="14" spans="2:10">
       <c r="E14" t="s">
         <v>1810</v>
       </c>
-      <c r="K14" t="s">
+      <c r="J14" t="s">
         <v>1596</v>
       </c>
     </row>
-    <row r="15" spans="2:11">
+    <row r="15" spans="2:10">
       <c r="E15" t="s">
         <v>1811</v>
       </c>
-      <c r="K15" t="s">
+      <c r="J15" t="s">
         <v>1805</v>
       </c>
     </row>
-    <row r="16" spans="2:11">
-      <c r="K16" t="s">
+    <row r="16" spans="2:10">
+      <c r="J16" t="s">
         <v>1590</v>
       </c>
     </row>
@@ -18267,28 +18497,28 @@
       </c>
     </row>
     <row r="18" spans="2:12">
-      <c r="K18" t="s">
+      <c r="J18" t="s">
         <v>1596</v>
       </c>
     </row>
     <row r="19" spans="2:12">
-      <c r="K19" t="s">
+      <c r="J19" t="s">
         <v>1806</v>
       </c>
     </row>
     <row r="20" spans="2:12">
-      <c r="K20" t="s">
+      <c r="J20" t="s">
         <v>1590</v>
       </c>
     </row>
     <row r="22" spans="2:12">
-      <c r="K22" t="s">
+      <c r="J22" t="s">
         <v>1596</v>
       </c>
     </row>
     <row r="24" spans="2:12">
-      <c r="B24" s="106" t="s">
-        <v>1824</v>
+      <c r="B24" t="s">
+        <v>1822</v>
       </c>
     </row>
     <row r="26" spans="2:12">
@@ -18328,7 +18558,7 @@
     </row>
     <row r="33" spans="2:6">
       <c r="D33" t="s">
-        <v>1821</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="35" spans="2:6">
@@ -18338,36 +18568,36 @@
     </row>
     <row r="37" spans="2:6">
       <c r="D37" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="106" t="s">
-        <v>1825</v>
+      <c r="B39" t="s">
+        <v>1823</v>
       </c>
     </row>
     <row r="41" spans="2:6">
       <c r="C41" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="F41" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="43" spans="2:6">
       <c r="C43" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="F43" t="s">
-        <v>1832</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="45" spans="2:6">
       <c r="C45" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="F45" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="47" spans="2:6">
@@ -18375,12 +18605,12 @@
         <v>46220.041666666664</v>
       </c>
       <c r="F47" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="49" spans="2:7">
       <c r="C49" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="51" spans="2:7">
@@ -18390,28 +18620,28 @@
     </row>
     <row r="53" spans="2:7">
       <c r="C53" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="56" spans="2:7">
-      <c r="B56" s="106" t="s">
-        <v>1835</v>
+      <c r="B56" t="s">
+        <v>1833</v>
       </c>
     </row>
     <row r="57" spans="2:7">
       <c r="C57" t="s">
+        <v>1834</v>
+      </c>
+      <c r="D57" t="s">
         <v>1836</v>
       </c>
-      <c r="D57" t="s">
-        <v>1838</v>
-      </c>
       <c r="G57" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="58" spans="2:7">
       <c r="D58" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="59" spans="2:7">
@@ -18419,7 +18649,7 @@
         <v>1816</v>
       </c>
       <c r="D59" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
       <c r="G59" t="s">
         <v>1617</v>
@@ -18427,76 +18657,76 @@
     </row>
     <row r="60" spans="2:7">
       <c r="D60" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="61" spans="2:7">
       <c r="C61" t="s">
-        <v>1837</v>
+        <v>1835</v>
       </c>
       <c r="G61" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="64" spans="2:7">
-      <c r="B64" s="106" t="s">
-        <v>1843</v>
+      <c r="B64" t="s">
+        <v>1841</v>
       </c>
     </row>
     <row r="66" spans="2:10">
       <c r="C66" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="E66" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="67" spans="2:10">
       <c r="C67" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="E67" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="68" spans="2:10">
       <c r="C68" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="E68" t="s">
-        <v>1851</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="69" spans="2:10">
       <c r="C69" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="70" spans="2:10">
       <c r="C70" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="72" spans="2:10">
-      <c r="B72" s="106" t="s">
-        <v>1852</v>
+      <c r="B72" t="s">
+        <v>1850</v>
       </c>
     </row>
     <row r="74" spans="2:10">
       <c r="C74" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="F74" s="104" t="s">
+        <v>1855</v>
+      </c>
+      <c r="G74" s="104" t="s">
+        <v>1856</v>
+      </c>
+      <c r="H74" s="104" t="s">
         <v>1857</v>
       </c>
-      <c r="G74" s="104" t="s">
-        <v>1858</v>
-      </c>
-      <c r="H74" s="104" t="s">
-        <v>1859</v>
-      </c>
       <c r="J74" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="75" spans="2:10">
@@ -18504,7 +18734,7 @@
         <v>1815</v>
       </c>
       <c r="F75" s="105" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
       <c r="G75" s="105">
         <v>1440</v>
@@ -18513,15 +18743,15 @@
         <v>180</v>
       </c>
       <c r="J75" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="76" spans="2:10">
       <c r="C76" t="s">
-        <v>1854</v>
+        <v>1852</v>
       </c>
       <c r="F76" s="105" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
       <c r="G76" s="105">
         <v>30</v>
@@ -18530,15 +18760,15 @@
         <v>10</v>
       </c>
       <c r="J76" t="s">
-        <v>1864</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="77" spans="2:10">
       <c r="C77" t="s">
-        <v>1855</v>
+        <v>1853</v>
       </c>
       <c r="F77" s="105" t="s">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="G77" s="105">
         <v>5</v>
@@ -18549,115 +18779,115 @@
     </row>
     <row r="78" spans="2:10">
       <c r="C78" t="s">
-        <v>1856</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="80" spans="2:10">
       <c r="B80" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="82" spans="2:5">
       <c r="C82" t="s">
-        <v>1867</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="84" spans="2:5">
       <c r="B84" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="86" spans="2:5">
       <c r="D86" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="87" spans="2:5">
       <c r="D87" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="88" spans="2:5">
       <c r="D88" t="s">
-        <v>1869</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="89" spans="2:5">
       <c r="D89" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="90" spans="2:5">
       <c r="D90" t="s">
-        <v>1870</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="91" spans="2:5">
       <c r="D91" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="92" spans="2:5">
       <c r="D92" t="s">
-        <v>1871</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="93" spans="2:5">
       <c r="D93" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="94" spans="2:5">
       <c r="D94" t="s">
-        <v>1872</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="95" spans="2:5">
       <c r="D95" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="96" spans="2:5">
       <c r="D96" t="s">
-        <v>1873</v>
+        <v>1871</v>
       </c>
       <c r="E96" t="s">
-        <v>1878</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="97" spans="2:7">
       <c r="D97" t="s">
-        <v>1874</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="98" spans="2:7">
       <c r="D98" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="99" spans="2:7">
       <c r="D99" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="100" spans="2:7">
       <c r="D100" t="s">
-        <v>1875</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="101" spans="2:7">
       <c r="D101" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="102" spans="2:7">
       <c r="D102" t="s">
-        <v>1876</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="104" spans="2:7">
       <c r="B104" t="s">
-        <v>1879</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="105" spans="2:7">
@@ -18668,60 +18898,262 @@
         <v>7</v>
       </c>
       <c r="D106" t="s">
-        <v>1880</v>
-      </c>
-      <c r="G106" t="s">
-        <v>1883</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="107" spans="2:7">
       <c r="D107" t="s">
-        <v>1881</v>
-      </c>
-      <c r="G107" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="108" spans="2:7">
-      <c r="D108" t="s">
+      <c r="D108" s="73" t="s">
         <v>1815</v>
-      </c>
-      <c r="G108" t="s">
-        <v>1884</v>
       </c>
     </row>
     <row r="109" spans="2:7">
       <c r="D109" t="s">
-        <v>1882</v>
+        <v>1854</v>
       </c>
       <c r="G109" t="s">
-        <v>1815</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="110" spans="2:7">
       <c r="D110" t="s">
-        <v>1855</v>
-      </c>
-      <c r="G110" t="s">
-        <v>1816</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="111" spans="2:7">
       <c r="D111" t="s">
-        <v>1856</v>
+        <v>1922</v>
       </c>
       <c r="G111" t="s">
-        <v>1817</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="112" spans="2:7">
+      <c r="D112" t="s">
+        <v>1891</v>
+      </c>
       <c r="G112" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="113" spans="2:7">
+      <c r="D113" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G113" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="116" spans="2:7">
+      <c r="D116" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="117" spans="2:7">
+      <c r="D117" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="118" spans="2:7">
+      <c r="D118" s="73" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="119" spans="2:7">
+      <c r="D119" s="106" t="s">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="120" spans="2:7">
+      <c r="D120" s="106" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="121" spans="2:7">
+      <c r="D121" s="106" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="122" spans="2:7">
+      <c r="D122" t="s">
         <v>1818</v>
       </c>
-    </row>
-    <row r="113" spans="7:7">
-      <c r="G113" t="s">
+      <c r="F122" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="123" spans="2:7">
+      <c r="D123" t="s">
+        <v>1881</v>
+      </c>
+      <c r="F123" t="s">
         <v>1885</v>
+      </c>
+    </row>
+    <row r="124" spans="2:7">
+      <c r="D124" s="106"/>
+    </row>
+    <row r="126" spans="2:7">
+      <c r="B126" s="106" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="127" spans="2:7">
+      <c r="D127" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="128" spans="2:7">
+      <c r="D128" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F128" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="129" spans="2:6">
+      <c r="D129" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F129" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="130" spans="2:6">
+      <c r="D130" t="s">
+        <v>1918</v>
+      </c>
+      <c r="F130" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="131" spans="2:6">
+      <c r="D131" t="s">
+        <v>1919</v>
+      </c>
+      <c r="F131" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="133" spans="2:6">
+      <c r="B133" s="106" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="134" spans="2:6">
+      <c r="D134" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="135" spans="2:6">
+      <c r="D135" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="136" spans="2:6">
+      <c r="D136" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="137" spans="2:6">
+      <c r="D137" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="138" spans="2:6">
+      <c r="D138" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="139" spans="2:6">
+      <c r="D139" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="140" spans="2:6">
+      <c r="D140" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="141" spans="2:6">
+      <c r="D141" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="142" spans="2:6">
+      <c r="D142" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="144" spans="2:6">
+      <c r="D144" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="145" spans="4:6">
+      <c r="D145" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="146" spans="4:6">
+      <c r="D146" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="147" spans="4:6">
+      <c r="D147" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="148" spans="4:6">
+      <c r="D148" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="150" spans="4:6">
+      <c r="D150" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="151" spans="4:6">
+      <c r="D151" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F151" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="152" spans="4:6">
+      <c r="D152" t="s">
+        <v>1895</v>
+      </c>
+      <c r="F152" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="153" spans="4:6">
+      <c r="D153" t="s">
+        <v>1907</v>
+      </c>
+      <c r="F153" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="154" spans="4:6">
+      <c r="D154" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F154" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="155" spans="4:6">
+      <c r="D155" t="s">
+        <v>1909</v>
       </c>
     </row>
   </sheetData>
@@ -18733,7 +19165,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="5"/>
   </cols>
@@ -18747,7 +19179,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBD988A-503C-4F44-AC4A-B26683FC9B4C}">
   <dimension ref="B4:O34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="5"/>
   </cols>
@@ -18898,14 +19330,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
   <dimension ref="B4:K159"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="2" width="20.19921875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="24.09765625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.25" style="5" customWidth="1"/>
+    <col min="3" max="3" width="24.125" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" style="5" customWidth="1"/>
     <col min="5" max="8" width="9" style="5"/>
-    <col min="9" max="9" width="45.59765625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="45.625" style="5" customWidth="1"/>
     <col min="10" max="22" width="9" style="5"/>
     <col min="23" max="23" width="8" style="5" customWidth="1"/>
     <col min="24" max="16384" width="9" style="5"/>
@@ -23077,22 +23509,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EB7090A-0065-41E7-85DA-75EEB9504A67}">
   <dimension ref="C3:Q81"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="7.5" style="5" customWidth="1"/>
-    <col min="3" max="3" width="13.69921875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="13.75" style="5" customWidth="1"/>
     <col min="4" max="4" width="20" style="5" customWidth="1"/>
-    <col min="5" max="5" width="30.59765625" style="5" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="13.3984375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="30.625" style="5" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="13.375" style="5" customWidth="1"/>
     <col min="7" max="7" width="11" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.19921875" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.69921875" style="5" customWidth="1"/>
-    <col min="10" max="12" width="9.8984375" style="18" customWidth="1"/>
-    <col min="13" max="13" width="9.19921875" style="18" customWidth="1"/>
-    <col min="14" max="14" width="12.59765625" style="18" customWidth="1"/>
-    <col min="15" max="15" width="27.09765625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="15.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.75" style="5" customWidth="1"/>
+    <col min="10" max="12" width="9.875" style="18" customWidth="1"/>
+    <col min="13" max="13" width="9.25" style="18" customWidth="1"/>
+    <col min="14" max="14" width="12.625" style="18" customWidth="1"/>
+    <col min="15" max="15" width="27.125" style="5" customWidth="1"/>
     <col min="16" max="16" width="7.5" style="5" customWidth="1"/>
-    <col min="17" max="17" width="15.09765625" style="5" customWidth="1"/>
+    <col min="17" max="17" width="15.125" style="5" customWidth="1"/>
     <col min="18" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -24756,7 +25188,7 @@
         <v>INSERT INTO m_skill VALUES ('skill037','グラビジャ',4,0,0,1,75,50,0.0,1,1200,'現HPの７５％ダメージ');</v>
       </c>
     </row>
-    <row r="41" spans="3:17" ht="37.799999999999997">
+    <row r="41" spans="3:17" ht="40.5">
       <c r="C41" s="47" t="s">
         <v>1048</v>
       </c>
@@ -26508,10 +26940,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F51B408-D4E3-46FE-97DE-15AB67B6AAB6}">
   <dimension ref="B1:Q100"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="2" width="12.69921875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="5" customWidth="1"/>
     <col min="3" max="3" width="17.5" style="5" customWidth="1"/>
     <col min="4" max="16384" width="9" style="5"/>
   </cols>
@@ -29327,22 +29759,22 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E63A27D9-C8B6-491D-9205-8D7433312F14}">
   <dimension ref="A4:U522"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="12.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.8984375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.59765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.625" style="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="12.69921875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="5.3984375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14.09765625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.75" style="3" customWidth="1"/>
+    <col min="8" max="8" width="5.375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="14.125" style="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="1"/>
-    <col min="12" max="12" width="17.69921875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.75" style="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1"/>
-    <col min="14" max="14" width="5.19921875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="5.25" style="1" customWidth="1"/>
     <col min="15" max="20" width="9" style="1"/>
-    <col min="21" max="21" width="8.8984375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="8.875" style="1" customWidth="1"/>
     <col min="22" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -45935,7 +46367,7 @@
         <v>INSERT INTO m_monster_skills VALUES ('myskill0505','monster084','skill051',FALSE);</v>
       </c>
     </row>
-    <row r="510" spans="1:21" ht="18">
+    <row r="510" spans="1:21" ht="18.75">
       <c r="A510"/>
       <c r="B510"/>
       <c r="C510"/>
@@ -45958,7 +46390,7 @@
       <c r="T510"/>
       <c r="U510"/>
     </row>
-    <row r="511" spans="1:21" ht="18">
+    <row r="511" spans="1:21" ht="18.75">
       <c r="A511"/>
       <c r="B511"/>
       <c r="C511"/>
@@ -45981,7 +46413,7 @@
       <c r="T511"/>
       <c r="U511"/>
     </row>
-    <row r="512" spans="1:21" ht="18">
+    <row r="512" spans="1:21" ht="18.75">
       <c r="A512"/>
       <c r="B512"/>
       <c r="C512"/>
@@ -46004,7 +46436,7 @@
       <c r="T512"/>
       <c r="U512"/>
     </row>
-    <row r="513" spans="1:21" ht="18">
+    <row r="513" spans="1:21" ht="18.75">
       <c r="A513"/>
       <c r="B513"/>
       <c r="C513"/>
@@ -46027,7 +46459,7 @@
       <c r="T513"/>
       <c r="U513"/>
     </row>
-    <row r="514" spans="1:21" ht="18">
+    <row r="514" spans="1:21" ht="18.75">
       <c r="A514"/>
       <c r="B514"/>
       <c r="C514"/>
@@ -46050,7 +46482,7 @@
       <c r="T514"/>
       <c r="U514"/>
     </row>
-    <row r="515" spans="1:21" ht="18">
+    <row r="515" spans="1:21" ht="18.75">
       <c r="A515"/>
       <c r="B515"/>
       <c r="C515"/>
@@ -46073,7 +46505,7 @@
       <c r="T515"/>
       <c r="U515"/>
     </row>
-    <row r="516" spans="1:21" ht="18">
+    <row r="516" spans="1:21" ht="18.75">
       <c r="A516"/>
       <c r="B516"/>
       <c r="C516"/>
@@ -46096,7 +46528,7 @@
       <c r="T516"/>
       <c r="U516"/>
     </row>
-    <row r="517" spans="1:21" ht="18">
+    <row r="517" spans="1:21" ht="18.75">
       <c r="A517"/>
       <c r="B517"/>
       <c r="C517"/>
@@ -46119,7 +46551,7 @@
       <c r="T517"/>
       <c r="U517"/>
     </row>
-    <row r="518" spans="1:21" ht="18">
+    <row r="518" spans="1:21" ht="18.75">
       <c r="A518"/>
       <c r="B518"/>
       <c r="C518"/>
@@ -46142,7 +46574,7 @@
       <c r="T518"/>
       <c r="U518"/>
     </row>
-    <row r="519" spans="1:21" ht="18">
+    <row r="519" spans="1:21" ht="18.75">
       <c r="A519"/>
       <c r="B519"/>
       <c r="C519"/>
@@ -46165,7 +46597,7 @@
       <c r="T519"/>
       <c r="U519"/>
     </row>
-    <row r="520" spans="1:21" ht="18">
+    <row r="520" spans="1:21" ht="18.75">
       <c r="A520"/>
       <c r="B520"/>
       <c r="C520"/>
@@ -46188,7 +46620,7 @@
       <c r="T520"/>
       <c r="U520"/>
     </row>
-    <row r="521" spans="1:21" ht="18">
+    <row r="521" spans="1:21" ht="18.75">
       <c r="A521"/>
       <c r="B521"/>
       <c r="C521"/>
@@ -46211,7 +46643,7 @@
       <c r="T521"/>
       <c r="U521"/>
     </row>
-    <row r="522" spans="1:21" ht="18">
+    <row r="522" spans="1:21" ht="18.75">
       <c r="A522"/>
       <c r="B522"/>
       <c r="C522"/>
@@ -46243,15 +46675,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A843E7EA-D614-495E-86B7-D31F628C6221}">
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="3" width="17.19921875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="17.25" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.59765625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.69921875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="11.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.75" style="5" customWidth="1"/>
     <col min="7" max="7" width="13.5" style="5" customWidth="1"/>
-    <col min="8" max="8" width="11.8984375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="11.875" style="5" customWidth="1"/>
     <col min="9" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -46612,13 +47044,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE71EC6-0DD3-461C-A8FC-74E22154B7A5}">
   <dimension ref="A4:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="3.8984375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="3.875" style="1" customWidth="1"/>
     <col min="2" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="4.19921875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="95.19921875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.8984375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="4.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="95.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.875" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE80C35B-67D7-4B63-8240-D56A02478AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{567AC50F-ED9F-4773-9D01-93E6BDEBE1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="778" firstSheet="6" activeTab="13" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="3" activeTab="13" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="architecture" sheetId="12" r:id="rId1"/>
@@ -33,6 +33,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">モンスタースキル!$C$4:$C$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4093" uniqueCount="1926">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4117" uniqueCount="1930">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -7926,35 +7927,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Discord通知</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>【異常】</t>
-  </si>
-  <si>
-    <t>CrawlerBatch</t>
-  </si>
-  <si>
-    <t>最後の成功</t>
-  </si>
-  <si>
-    <t>現在</t>
-  </si>
-  <si>
-    <t>31時間実行されていません</t>
-  </si>
-  <si>
     <t>AutoBattle</t>
-  </si>
-  <si>
-    <t>終了ステータス</t>
-  </si>
-  <si>
-    <t>ERROR</t>
-  </si>
-  <si>
-    <t>System.TimeoutException</t>
   </si>
   <si>
     <t>timeout監視</t>
@@ -8271,10 +8244,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ステータスがERROR or TIMEOUT or NOT_STARTED or SLOW</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ERROR</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -8365,6 +8334,127 @@
     </rPh>
     <rPh sb="7" eb="8">
       <t>オソ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>CREATE INDEX idx_batch_execution_batch_name_start_at ON batch_execution (batch_name, start_at DESC);</t>
+  </si>
+  <si>
+    <t>バッチステータスCD</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>コード名</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SUCCESS</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>STARTED</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>batch_status</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>処理成功</t>
+    <rPh sb="0" eb="2">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セイコウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>処理開始。いずかのステータスに遷移する。</t>
+    <rPh sb="0" eb="4">
+      <t>ショリカイシ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>予定時刻に開始されていない。</t>
+    <rPh sb="0" eb="2">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジコク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カイシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>例外、パニック等が発生した。</t>
+    <rPh sb="0" eb="2">
+      <t>レイガイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハッセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>時間内に処理が終了しなかった。</t>
+    <rPh sb="0" eb="2">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>想定時間内に処理が終了しなかった。</t>
+    <rPh sb="0" eb="2">
+      <t>ソウテイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">STARTED </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>状態が更新されていない</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウシン</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -8781,7 +8871,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -8949,16 +9039,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -12489,8 +12575,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7911971" y="1528349"/>
-          <a:ext cx="1800328" cy="1214718"/>
+          <a:off x="7984025" y="1633012"/>
+          <a:ext cx="1824308" cy="1293159"/>
           <a:chOff x="8992083" y="208776"/>
           <a:chExt cx="1814762" cy="1244600"/>
         </a:xfrm>
@@ -12799,8 +12885,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="11175520" y="3059605"/>
-          <a:ext cx="1822530" cy="1963728"/>
+          <a:off x="11281192" y="3261311"/>
+          <a:ext cx="1842700" cy="2086992"/>
           <a:chOff x="8549484" y="3956874"/>
           <a:chExt cx="1810288" cy="1437363"/>
         </a:xfrm>
@@ -13351,8 +13437,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4681098" y="1657961"/>
-          <a:ext cx="1869953" cy="3342717"/>
+          <a:off x="4719534" y="1760719"/>
+          <a:ext cx="1895839" cy="3563024"/>
           <a:chOff x="5970441" y="628674"/>
           <a:chExt cx="1893913" cy="3428095"/>
         </a:xfrm>
@@ -13820,8 +13906,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10840271" y="7258650"/>
-          <a:ext cx="2193307" cy="2523422"/>
+          <a:off x="10944934" y="7742408"/>
+          <a:ext cx="2214486" cy="2691510"/>
           <a:chOff x="12007370" y="5957071"/>
           <a:chExt cx="2223130" cy="2581251"/>
         </a:xfrm>
@@ -14027,8 +14113,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14334233" y="4816236"/>
-          <a:ext cx="2220036" cy="1720343"/>
+          <a:off x="14472514" y="5130000"/>
+          <a:ext cx="2243119" cy="1832402"/>
           <a:chOff x="15050343" y="4729843"/>
           <a:chExt cx="2243515" cy="1763032"/>
         </a:xfrm>
@@ -14457,8 +14543,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6846794" y="5210735"/>
-          <a:ext cx="1781735" cy="1311089"/>
+          <a:off x="6912125" y="5558118"/>
+          <a:ext cx="1795181" cy="1393339"/>
           <a:chOff x="6846794" y="5210735"/>
           <a:chExt cx="2341399" cy="1311089"/>
         </a:xfrm>
@@ -14834,8 +14920,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3726679" y="7642890"/>
-          <a:ext cx="2335072" cy="1882107"/>
+          <a:off x="3760297" y="8147154"/>
+          <a:ext cx="2359052" cy="2005373"/>
           <a:chOff x="3726679" y="7642891"/>
           <a:chExt cx="2335072" cy="1468663"/>
         </a:xfrm>
@@ -18401,7 +18487,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD79B98E-03E4-44E6-9FBF-39CA1C89C95A}">
-  <dimension ref="B3:L155"/>
+  <dimension ref="B3:L139"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="8.75" style="73"/>
@@ -18411,7 +18497,7 @@
   <sheetData>
     <row r="3" spans="2:10">
       <c r="B3" t="s">
-        <v>1882</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="5" spans="2:10">
@@ -18556,604 +18642,555 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:7">
       <c r="D33" t="s">
-        <v>1883</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
       <c r="D35" t="s">
         <v>1617</v>
       </c>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:7">
       <c r="D37" t="s">
         <v>1821</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:7">
       <c r="B39" t="s">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7">
+      <c r="C40" t="s">
+        <v>1825</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1827</v>
+      </c>
+      <c r="G40" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7">
+      <c r="D41" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7">
+      <c r="C42" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1829</v>
+      </c>
+      <c r="G42" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7">
+      <c r="D43" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7">
+      <c r="C44" t="s">
+        <v>1826</v>
+      </c>
+      <c r="G44" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7">
+      <c r="B47" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5">
+      <c r="C49" t="s">
+        <v>1833</v>
+      </c>
+      <c r="E49" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5">
+      <c r="C50" t="s">
+        <v>1834</v>
+      </c>
+      <c r="E50" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5">
+      <c r="C51" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E51" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5">
+      <c r="C52" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5">
+      <c r="C53" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5">
+      <c r="B56" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5">
+      <c r="C58" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5">
+      <c r="B60" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5">
+      <c r="D62" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5">
+      <c r="D63" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5">
+      <c r="D64" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5">
+      <c r="D65" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5">
+      <c r="D66" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5">
+      <c r="D67" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5">
+      <c r="D68" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5">
+      <c r="D69" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="70" spans="2:5">
+      <c r="D70" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5">
+      <c r="D71" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5">
+      <c r="D72" t="s">
+        <v>1862</v>
+      </c>
+      <c r="E72" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5">
+      <c r="D73" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5">
+      <c r="D74" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5">
+      <c r="D75" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5">
+      <c r="D76" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5">
+      <c r="D77" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5">
+      <c r="D78" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="80" spans="2:5">
+      <c r="B80" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10">
+      <c r="C82" t="s">
+        <v>1842</v>
+      </c>
+      <c r="F82" s="103" t="s">
+        <v>1846</v>
+      </c>
+      <c r="G82" s="103" t="s">
+        <v>1847</v>
+      </c>
+      <c r="H82" s="103" t="s">
+        <v>1848</v>
+      </c>
+      <c r="J82" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10">
+      <c r="C83" t="s">
+        <v>1815</v>
+      </c>
+      <c r="F83" s="104" t="s">
+        <v>1849</v>
+      </c>
+      <c r="G83" s="104">
+        <v>1440</v>
+      </c>
+      <c r="H83" s="104">
+        <v>180</v>
+      </c>
+      <c r="J83" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10">
+      <c r="C84" t="s">
+        <v>1843</v>
+      </c>
+      <c r="F84" s="104" t="s">
         <v>1823</v>
       </c>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="C41" t="s">
-        <v>1824</v>
-      </c>
-      <c r="F41" t="s">
-        <v>1829</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6">
-      <c r="C43" t="s">
-        <v>1825</v>
-      </c>
-      <c r="F43" t="s">
-        <v>1830</v>
-      </c>
-    </row>
-    <row r="45" spans="2:6">
-      <c r="C45" t="s">
-        <v>1826</v>
-      </c>
-      <c r="F45" t="s">
-        <v>1831</v>
-      </c>
-    </row>
-    <row r="47" spans="2:6">
-      <c r="C47" s="103">
-        <v>46220.041666666664</v>
-      </c>
-      <c r="F47" t="s">
-        <v>1832</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7">
-      <c r="C49" t="s">
-        <v>1827</v>
-      </c>
-    </row>
-    <row r="51" spans="2:7">
-      <c r="C51" s="103">
-        <v>46221.333333333336</v>
-      </c>
-    </row>
-    <row r="53" spans="2:7">
-      <c r="C53" t="s">
-        <v>1828</v>
-      </c>
-    </row>
-    <row r="56" spans="2:7">
-      <c r="B56" t="s">
-        <v>1833</v>
-      </c>
-    </row>
-    <row r="57" spans="2:7">
-      <c r="C57" t="s">
-        <v>1834</v>
-      </c>
-      <c r="D57" t="s">
-        <v>1836</v>
-      </c>
-      <c r="G57" t="s">
-        <v>1840</v>
-      </c>
-    </row>
-    <row r="58" spans="2:7">
-      <c r="D58" t="s">
-        <v>1837</v>
-      </c>
-    </row>
-    <row r="59" spans="2:7">
-      <c r="C59" t="s">
-        <v>1816</v>
-      </c>
-      <c r="D59" t="s">
-        <v>1838</v>
-      </c>
-      <c r="G59" t="s">
-        <v>1617</v>
-      </c>
-    </row>
-    <row r="60" spans="2:7">
-      <c r="D60" t="s">
-        <v>1839</v>
-      </c>
-    </row>
-    <row r="61" spans="2:7">
-      <c r="C61" t="s">
-        <v>1835</v>
-      </c>
-      <c r="G61" t="s">
-        <v>1821</v>
-      </c>
-    </row>
-    <row r="64" spans="2:7">
-      <c r="B64" t="s">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10">
-      <c r="C66" t="s">
-        <v>1842</v>
-      </c>
-      <c r="E66" t="s">
-        <v>1847</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10">
-      <c r="C67" t="s">
-        <v>1843</v>
-      </c>
-      <c r="E67" t="s">
-        <v>1848</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10">
-      <c r="C68" t="s">
+      <c r="G84" s="104">
+        <v>30</v>
+      </c>
+      <c r="H84" s="104">
+        <v>10</v>
+      </c>
+      <c r="J84" t="s">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10">
+      <c r="C85" t="s">
         <v>1844</v>
       </c>
-      <c r="E68" t="s">
-        <v>1849</v>
-      </c>
-    </row>
-    <row r="69" spans="2:10">
-      <c r="C69" t="s">
+      <c r="F85" s="104" t="s">
+        <v>1850</v>
+      </c>
+      <c r="G85" s="104">
+        <v>5</v>
+      </c>
+      <c r="H85" s="104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10">
+      <c r="C86" t="s">
         <v>1845</v>
       </c>
     </row>
-    <row r="70" spans="2:10">
-      <c r="C70" t="s">
-        <v>1846</v>
-      </c>
-    </row>
-    <row r="72" spans="2:10">
-      <c r="B72" t="s">
-        <v>1850</v>
-      </c>
-    </row>
-    <row r="74" spans="2:10">
-      <c r="C74" t="s">
-        <v>1851</v>
-      </c>
-      <c r="F74" s="104" t="s">
-        <v>1855</v>
-      </c>
-      <c r="G74" s="104" t="s">
-        <v>1856</v>
-      </c>
-      <c r="H74" s="104" t="s">
-        <v>1857</v>
-      </c>
-      <c r="J74" t="s">
-        <v>1860</v>
-      </c>
-    </row>
-    <row r="75" spans="2:10">
-      <c r="C75" t="s">
+    <row r="88" spans="2:10">
+      <c r="B88" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10">
+      <c r="B89"/>
+    </row>
+    <row r="90" spans="2:10">
+      <c r="C90" t="s">
+        <v>7</v>
+      </c>
+      <c r="D90" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10">
+      <c r="D91" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10">
+      <c r="D92" s="73" t="s">
         <v>1815</v>
       </c>
-      <c r="F75" s="105" t="s">
-        <v>1858</v>
-      </c>
-      <c r="G75" s="105">
-        <v>1440</v>
-      </c>
-      <c r="H75" s="105">
-        <v>180</v>
-      </c>
-      <c r="J75" t="s">
-        <v>1861</v>
-      </c>
-    </row>
-    <row r="76" spans="2:10">
-      <c r="C76" t="s">
-        <v>1852</v>
-      </c>
-      <c r="F76" s="105" t="s">
-        <v>1829</v>
-      </c>
-      <c r="G76" s="105">
-        <v>30</v>
-      </c>
-      <c r="H76" s="105">
-        <v>10</v>
-      </c>
-      <c r="J76" t="s">
-        <v>1862</v>
-      </c>
-    </row>
-    <row r="77" spans="2:10">
-      <c r="C77" t="s">
-        <v>1853</v>
-      </c>
-      <c r="F77" s="105" t="s">
-        <v>1859</v>
-      </c>
-      <c r="G77" s="105">
-        <v>5</v>
-      </c>
-      <c r="H77" s="105">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78" spans="2:10">
-      <c r="C78" t="s">
-        <v>1854</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10">
-      <c r="B80" t="s">
-        <v>1863</v>
-      </c>
-    </row>
-    <row r="82" spans="2:5">
-      <c r="C82" t="s">
-        <v>1865</v>
-      </c>
-    </row>
-    <row r="84" spans="2:5">
-      <c r="B84" t="s">
-        <v>1875</v>
-      </c>
-    </row>
-    <row r="86" spans="2:5">
-      <c r="D86" t="s">
-        <v>1851</v>
-      </c>
-    </row>
-    <row r="87" spans="2:5">
-      <c r="D87" t="s">
-        <v>1866</v>
-      </c>
-    </row>
-    <row r="88" spans="2:5">
-      <c r="D88" t="s">
-        <v>1867</v>
-      </c>
-    </row>
-    <row r="89" spans="2:5">
-      <c r="D89" t="s">
-        <v>1866</v>
-      </c>
-    </row>
-    <row r="90" spans="2:5">
-      <c r="D90" t="s">
-        <v>1868</v>
-      </c>
-    </row>
-    <row r="91" spans="2:5">
-      <c r="D91" t="s">
-        <v>1866</v>
-      </c>
-    </row>
-    <row r="92" spans="2:5">
-      <c r="D92" t="s">
-        <v>1869</v>
-      </c>
-    </row>
-    <row r="93" spans="2:5">
+    </row>
+    <row r="93" spans="2:10">
       <c r="D93" t="s">
-        <v>1866</v>
-      </c>
-    </row>
-    <row r="94" spans="2:5">
+        <v>1845</v>
+      </c>
+      <c r="G93" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="94" spans="2:10">
       <c r="D94" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="95" spans="2:5">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="95" spans="2:10">
       <c r="D95" t="s">
-        <v>1866</v>
-      </c>
-    </row>
-    <row r="96" spans="2:5">
+        <v>1912</v>
+      </c>
+      <c r="G95" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="96" spans="2:10">
       <c r="D96" t="s">
-        <v>1871</v>
-      </c>
-      <c r="E96" t="s">
-        <v>1876</v>
+        <v>1882</v>
+      </c>
+      <c r="G96" t="s">
+        <v>1878</v>
       </c>
     </row>
     <row r="97" spans="2:7">
       <c r="D97" t="s">
-        <v>1872</v>
-      </c>
-    </row>
-    <row r="98" spans="2:7">
-      <c r="D98" t="s">
-        <v>1864</v>
-      </c>
-    </row>
-    <row r="99" spans="2:7">
-      <c r="D99" t="s">
-        <v>1866</v>
+        <v>1844</v>
+      </c>
+      <c r="G97" t="s">
+        <v>1881</v>
       </c>
     </row>
     <row r="100" spans="2:7">
       <c r="D100" t="s">
-        <v>1873</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="101" spans="2:7">
       <c r="D101" t="s">
-        <v>1866</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="102" spans="2:7">
-      <c r="D102" t="s">
-        <v>1874</v>
+      <c r="D102" s="73" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F102" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7">
+      <c r="D103" t="s">
+        <v>1815</v>
       </c>
     </row>
     <row r="104" spans="2:7">
-      <c r="B104" t="s">
-        <v>1877</v>
+      <c r="D104" t="s">
+        <v>1879</v>
       </c>
     </row>
     <row r="105" spans="2:7">
-      <c r="B105"/>
+      <c r="D105" t="s">
+        <v>1880</v>
+      </c>
     </row>
     <row r="106" spans="2:7">
-      <c r="C106" t="s">
-        <v>7</v>
-      </c>
       <c r="D106" t="s">
-        <v>1878</v>
+        <v>1818</v>
+      </c>
+      <c r="F106" t="s">
+        <v>1905</v>
       </c>
     </row>
     <row r="107" spans="2:7">
       <c r="D107" t="s">
-        <v>1879</v>
-      </c>
-    </row>
-    <row r="108" spans="2:7">
-      <c r="D108" s="73" t="s">
-        <v>1815</v>
-      </c>
-    </row>
-    <row r="109" spans="2:7">
-      <c r="D109" t="s">
-        <v>1854</v>
-      </c>
-      <c r="G109" t="s">
-        <v>1886</v>
+        <v>1872</v>
+      </c>
+      <c r="F107" t="s">
+        <v>1876</v>
       </c>
     </row>
     <row r="110" spans="2:7">
-      <c r="D110" t="s">
-        <v>1912</v>
+      <c r="B110" t="s">
+        <v>1875</v>
       </c>
     </row>
     <row r="111" spans="2:7">
       <c r="D111" t="s">
-        <v>1922</v>
-      </c>
-      <c r="G111" t="s">
-        <v>1923</v>
+        <v>1928</v>
+      </c>
+      <c r="F111" t="s">
+        <v>1929</v>
       </c>
     </row>
     <row r="112" spans="2:7">
       <c r="D112" t="s">
+        <v>1906</v>
+      </c>
+      <c r="F112" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="113" spans="2:6">
+      <c r="D113" t="s">
+        <v>1907</v>
+      </c>
+      <c r="F113" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="114" spans="2:6">
+      <c r="D114" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F114" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="115" spans="2:6">
+      <c r="D115" t="s">
+        <v>1909</v>
+      </c>
+      <c r="F115" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="117" spans="2:6">
+      <c r="B117" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="118" spans="2:6">
+      <c r="D118" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="119" spans="2:6">
+      <c r="D119" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="120" spans="2:6">
+      <c r="D120" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="121" spans="2:6">
+      <c r="D121" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="122" spans="2:6">
+      <c r="D122" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="123" spans="2:6">
+      <c r="D123" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="124" spans="2:6">
+      <c r="D124" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="125" spans="2:6">
+      <c r="D125" t="s">
         <v>1891</v>
       </c>
-      <c r="G112" t="s">
-        <v>1887</v>
-      </c>
-    </row>
-    <row r="113" spans="2:7">
-      <c r="D113" t="s">
-        <v>1853</v>
-      </c>
-      <c r="G113" t="s">
-        <v>1890</v>
-      </c>
-    </row>
-    <row r="116" spans="2:7">
-      <c r="D116" t="s">
-        <v>1880</v>
-      </c>
-    </row>
-    <row r="117" spans="2:7">
-      <c r="D117" t="s">
-        <v>1879</v>
-      </c>
-    </row>
-    <row r="118" spans="2:7">
-      <c r="D118" s="73" t="s">
-        <v>1913</v>
-      </c>
-    </row>
-    <row r="119" spans="2:7">
-      <c r="D119" s="106" t="s">
-        <v>1815</v>
-      </c>
-    </row>
-    <row r="120" spans="2:7">
-      <c r="D120" s="106" t="s">
-        <v>1888</v>
-      </c>
-    </row>
-    <row r="121" spans="2:7">
-      <c r="D121" s="106" t="s">
-        <v>1889</v>
-      </c>
-    </row>
-    <row r="122" spans="2:7">
-      <c r="D122" t="s">
-        <v>1818</v>
-      </c>
-      <c r="F122" t="s">
-        <v>1914</v>
-      </c>
-    </row>
-    <row r="123" spans="2:7">
-      <c r="D123" t="s">
-        <v>1881</v>
-      </c>
-      <c r="F123" t="s">
-        <v>1885</v>
-      </c>
-    </row>
-    <row r="124" spans="2:7">
-      <c r="D124" s="106"/>
-    </row>
-    <row r="126" spans="2:7">
-      <c r="B126" s="106" t="s">
-        <v>1884</v>
-      </c>
-    </row>
-    <row r="127" spans="2:7">
-      <c r="D127" t="s">
-        <v>1915</v>
-      </c>
-    </row>
-    <row r="128" spans="2:7">
+    </row>
+    <row r="126" spans="2:6">
+      <c r="D126" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="128" spans="2:6">
       <c r="D128" t="s">
-        <v>1916</v>
-      </c>
-      <c r="F128" t="s">
-        <v>1920</v>
-      </c>
-    </row>
-    <row r="129" spans="2:6">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="129" spans="4:6">
       <c r="D129" t="s">
-        <v>1917</v>
-      </c>
-      <c r="F129" t="s">
-        <v>1921</v>
-      </c>
-    </row>
-    <row r="130" spans="2:6">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="130" spans="4:6">
       <c r="D130" t="s">
-        <v>1918</v>
-      </c>
-      <c r="F130" t="s">
-        <v>1924</v>
-      </c>
-    </row>
-    <row r="131" spans="2:6">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="131" spans="4:6">
       <c r="D131" t="s">
-        <v>1919</v>
-      </c>
-      <c r="F131" t="s">
-        <v>1925</v>
-      </c>
-    </row>
-    <row r="133" spans="2:6">
-      <c r="B133" s="106" t="s">
-        <v>1892</v>
-      </c>
-    </row>
-    <row r="134" spans="2:6">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="132" spans="4:6">
+      <c r="D132" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="134" spans="4:6">
       <c r="D134" t="s">
-        <v>1893</v>
-      </c>
-    </row>
-    <row r="135" spans="2:6">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="135" spans="4:6">
       <c r="D135" t="s">
         <v>1894</v>
       </c>
-    </row>
-    <row r="136" spans="2:6">
+      <c r="F135" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="136" spans="4:6">
       <c r="D136" t="s">
-        <v>1895</v>
-      </c>
-    </row>
-    <row r="137" spans="2:6">
+        <v>1886</v>
+      </c>
+      <c r="F136" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="137" spans="4:6">
       <c r="D137" t="s">
-        <v>1896</v>
-      </c>
-    </row>
-    <row r="138" spans="2:6">
+        <v>1898</v>
+      </c>
+      <c r="F137" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="138" spans="4:6">
       <c r="D138" t="s">
-        <v>1897</v>
-      </c>
-    </row>
-    <row r="139" spans="2:6">
+        <v>1899</v>
+      </c>
+      <c r="F138" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="139" spans="4:6">
       <c r="D139" t="s">
-        <v>1898</v>
-      </c>
-    </row>
-    <row r="140" spans="2:6">
-      <c r="D140" t="s">
-        <v>1899</v>
-      </c>
-    </row>
-    <row r="141" spans="2:6">
-      <c r="D141" t="s">
         <v>1900</v>
-      </c>
-    </row>
-    <row r="142" spans="2:6">
-      <c r="D142" t="s">
-        <v>1901</v>
-      </c>
-    </row>
-    <row r="144" spans="2:6">
-      <c r="D144" t="s">
-        <v>1902</v>
-      </c>
-    </row>
-    <row r="145" spans="4:6">
-      <c r="D145" t="s">
-        <v>1903</v>
-      </c>
-    </row>
-    <row r="146" spans="4:6">
-      <c r="D146" t="s">
-        <v>1895</v>
-      </c>
-    </row>
-    <row r="147" spans="4:6">
-      <c r="D147" t="s">
-        <v>1904</v>
-      </c>
-    </row>
-    <row r="148" spans="4:6">
-      <c r="D148" t="s">
-        <v>1905</v>
-      </c>
-    </row>
-    <row r="150" spans="4:6">
-      <c r="D150" t="s">
-        <v>1906</v>
-      </c>
-    </row>
-    <row r="151" spans="4:6">
-      <c r="D151" t="s">
-        <v>1903</v>
-      </c>
-      <c r="F151" t="s">
-        <v>1903</v>
-      </c>
-    </row>
-    <row r="152" spans="4:6">
-      <c r="D152" t="s">
-        <v>1895</v>
-      </c>
-      <c r="F152" t="s">
-        <v>1895</v>
-      </c>
-    </row>
-    <row r="153" spans="4:6">
-      <c r="D153" t="s">
-        <v>1907</v>
-      </c>
-      <c r="F153" t="s">
-        <v>1910</v>
-      </c>
-    </row>
-    <row r="154" spans="4:6">
-      <c r="D154" t="s">
-        <v>1908</v>
-      </c>
-      <c r="F154" t="s">
-        <v>1911</v>
-      </c>
-    </row>
-    <row r="155" spans="4:6">
-      <c r="D155" t="s">
-        <v>1909</v>
       </c>
     </row>
   </sheetData>
@@ -19329,7 +19366,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
-  <dimension ref="B4:K159"/>
+  <dimension ref="B4:K166"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -23106,7 +23143,7 @@
       </c>
       <c r="I144" s="8"/>
       <c r="K144" s="5" t="str">
-        <f t="shared" ref="K144:K159" si="18">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B144&amp;"'"&amp;","&amp;E144&amp;","&amp;"'"&amp;C144&amp;"'"&amp;","&amp;"'"&amp;D144&amp;"'"&amp;","&amp;"'"&amp;F144&amp;"'"&amp;","&amp;G144&amp;","&amp;H144&amp;","&amp;"'"&amp;I144&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K144:K166" si="18">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B144&amp;"'"&amp;","&amp;E144&amp;","&amp;"'"&amp;C144&amp;"'"&amp;","&amp;"'"&amp;D144&amp;"'"&amp;","&amp;"'"&amp;F144&amp;"'"&amp;","&amp;G144&amp;","&amp;H144&amp;","&amp;"'"&amp;I144&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('guitar_colors',1,'Red','','レッド',0,0.0,'');</v>
       </c>
     </row>
@@ -23498,6 +23535,188 @@
       <c r="K159" s="5" t="str">
         <f t="shared" si="18"/>
         <v>INSERT INTO m_code VALUES ('guitar_colors',99,'Others','','その他',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="160" spans="2:11">
+      <c r="B160" s="6" t="s">
+        <v>1917</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>1918</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E160" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F160" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G160" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H160" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I160" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="161" spans="2:11">
+      <c r="B161" s="8" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C161" s="8" t="s">
+        <v>1919</v>
+      </c>
+      <c r="D161" s="8"/>
+      <c r="E161" s="8">
+        <v>1</v>
+      </c>
+      <c r="F161" s="8"/>
+      <c r="G161" s="9">
+        <v>0</v>
+      </c>
+      <c r="H161" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I161" s="8" t="s">
+        <v>1922</v>
+      </c>
+      <c r="K161" s="5" t="str">
+        <f t="shared" si="18"/>
+        <v>INSERT INTO m_code VALUES ('batch_status',1,'SUCCESS','','',0,0.0,'処理成功');</v>
+      </c>
+    </row>
+    <row r="162" spans="2:11">
+      <c r="B162" s="8" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C162" s="8" t="s">
+        <v>1920</v>
+      </c>
+      <c r="D162" s="8"/>
+      <c r="E162" s="8">
+        <v>2</v>
+      </c>
+      <c r="F162" s="8"/>
+      <c r="G162" s="9">
+        <v>0</v>
+      </c>
+      <c r="H162" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I162" s="8" t="s">
+        <v>1923</v>
+      </c>
+      <c r="K162" s="5" t="str">
+        <f t="shared" si="18"/>
+        <v>INSERT INTO m_code VALUES ('batch_status',2,'STARTED','','',0,0.0,'処理開始。いずかのステータスに遷移する。');</v>
+      </c>
+    </row>
+    <row r="163" spans="2:11">
+      <c r="B163" s="8" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C163" s="8" t="s">
+        <v>1908</v>
+      </c>
+      <c r="D163" s="8"/>
+      <c r="E163" s="8">
+        <v>3</v>
+      </c>
+      <c r="F163" s="8"/>
+      <c r="G163" s="9">
+        <v>0</v>
+      </c>
+      <c r="H163" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I163" s="8" t="s">
+        <v>1924</v>
+      </c>
+      <c r="K163" s="5" t="str">
+        <f t="shared" si="18"/>
+        <v>INSERT INTO m_code VALUES ('batch_status',3,'NOT_STARTED','','',0,0.0,'予定時刻に開始されていない。');</v>
+      </c>
+    </row>
+    <row r="164" spans="2:11">
+      <c r="B164" s="8" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C164" s="8" t="s">
+        <v>1906</v>
+      </c>
+      <c r="D164" s="8"/>
+      <c r="E164" s="8">
+        <v>4</v>
+      </c>
+      <c r="F164" s="8"/>
+      <c r="G164" s="9">
+        <v>0</v>
+      </c>
+      <c r="H164" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I164" s="8" t="s">
+        <v>1925</v>
+      </c>
+      <c r="K164" s="5" t="str">
+        <f t="shared" si="18"/>
+        <v>INSERT INTO m_code VALUES ('batch_status',4,'ERROR','','',0,0.0,'例外、パニック等が発生した。');</v>
+      </c>
+    </row>
+    <row r="165" spans="2:11">
+      <c r="B165" s="8" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C165" s="8" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D165" s="8"/>
+      <c r="E165" s="8">
+        <v>5</v>
+      </c>
+      <c r="F165" s="8"/>
+      <c r="G165" s="9">
+        <v>0</v>
+      </c>
+      <c r="H165" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I165" s="8" t="s">
+        <v>1927</v>
+      </c>
+      <c r="K165" s="5" t="str">
+        <f t="shared" si="18"/>
+        <v>INSERT INTO m_code VALUES ('batch_status',5,'SLOW','','',0,0.0,'想定時間内に処理が終了しなかった。');</v>
+      </c>
+    </row>
+    <row r="166" spans="2:11">
+      <c r="B166" s="8" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C166" s="8" t="s">
+        <v>1907</v>
+      </c>
+      <c r="D166" s="8"/>
+      <c r="E166" s="8">
+        <v>6</v>
+      </c>
+      <c r="F166" s="8"/>
+      <c r="G166" s="9">
+        <v>0</v>
+      </c>
+      <c r="H166" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I166" s="8" t="s">
+        <v>1926</v>
+      </c>
+      <c r="K166" s="5" t="str">
+        <f t="shared" si="18"/>
+        <v>INSERT INTO m_code VALUES ('batch_status',6,'TIMEOUT','','',0,0.0,'時間内に処理が終了しなかった。');</v>
       </c>
     </row>
   </sheetData>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{567AC50F-ED9F-4773-9D01-93E6BDEBE1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183BBFB3-FA9C-4D3F-9431-D0830D458C4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="3" activeTab="13" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4117" uniqueCount="1930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4134" uniqueCount="1947">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -8087,18 +8087,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>batch_master      ← 設定</t>
-  </si>
-  <si>
-    <t>-------------------------</t>
-  </si>
-  <si>
-    <t>batch_execution   ← 実行ログ</t>
-  </si>
-  <si>
-    <t>message</t>
-  </si>
-  <si>
     <t>INSERTよりUPDATEの方が楽？</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -8138,14 +8126,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>start_at</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>end_at</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>開始してから監視を待つ時間</t>
     <rPh sb="0" eb="2">
       <t>カイシ</t>
@@ -8162,9 +8142,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>expected_duration_minutes</t>
-  </si>
-  <si>
     <t>処理の流れ</t>
     <rPh sb="0" eb="2">
       <t>ショリ</t>
@@ -8226,20 +8203,6 @@
     <t>message   = "..."</t>
   </si>
   <si>
-    <t>status  = TIMEOUT</t>
-  </si>
-  <si>
-    <t>message = "Execution timeout"</t>
-  </si>
-  <si>
-    <t>scheduled_time</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>log_id</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>STARTED or SUCCESS or ERROR or TIMEOUT or NOT_STARTED or SLOW</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -8283,10 +8246,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>start_delay_time</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>予定時刻からバッチ開始までの猶予</t>
     <rPh sb="0" eb="2">
       <t>ヨテイ</t>
@@ -8338,9 +8297,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>CREATE INDEX idx_batch_execution_batch_name_start_at ON batch_execution (batch_name, start_at DESC);</t>
-  </si>
-  <si>
     <t>バッチステータスCD</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -8455,6 +8411,111 @@
     </rPh>
     <rPh sb="3" eb="5">
       <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>CREATE TABLE batch_master (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    batch_name                  VARCHAR(100) PRIMARY KEY,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    enabled                     BOOLEAN NOT NULL,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    scheduled_time              TIME NOT NULL,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    start_delay_minutes         INTEGER NOT NULL,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    expected_duration_minutes   INTEGER NOT NULL,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    timeout_minutes             INTEGER NOT NULL</t>
+  </si>
+  <si>
+    <t>);</t>
+  </si>
+  <si>
+    <t>CREATE TABLE batch_execution (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    log_id      BIGSERIAL PRIMARY KEY,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    batch_name  VARCHAR(100) NOT NULL,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    exec_date   DATE NOT NULL,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    start_at    TIMESTAMPTZ NOT NULL,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    end_at      TIMESTAMPTZ,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    status      VARCHAR(20) NOT NULL,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    message     TEXT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    CONSTRAINT chk_batch_execution_status</t>
+  </si>
+  <si>
+    <t>CREATE INDEX idx_batch_execution_batch_name_exec_date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ON batch_execution (batch_name, exec_date);</t>
+  </si>
+  <si>
+    <t>CREATE INDEX idx_batch_execution_latest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ON batch_execution (batch_name, start_at DESC);</t>
+  </si>
+  <si>
+    <t>保留</t>
+    <rPh sb="0" eb="2">
+      <t>ホリュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">        CHECK (status IN ('STARTED', 'NOT_STARTED', 'SUCCESS', 'ERROR', 'SLOW', 'TIMEOUT'))</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>status    = TIMEOUT</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>end_at    = ????</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>message   = "..."</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>message   = "e.message"</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>status    = SLOW</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>message   = ""</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>いずれかのレコードが存在しない</t>
+    <rPh sb="10" eb="12">
+      <t>ソンザイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -8466,7 +8527,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8545,6 +8606,23 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Yu Gothic"/>
@@ -8871,7 +8949,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -9045,6 +9123,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -18487,7 +18568,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD79B98E-03E4-44E6-9FBF-39CA1C89C95A}">
-  <dimension ref="B3:L139"/>
+  <dimension ref="B3:L149"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="8.75" style="73"/>
@@ -18497,7 +18578,7 @@
   <sheetData>
     <row r="3" spans="2:10">
       <c r="B3" t="s">
-        <v>1873</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="5" spans="2:10">
@@ -18644,7 +18725,7 @@
     </row>
     <row r="33" spans="2:7">
       <c r="D33" t="s">
-        <v>1874</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -18849,7 +18930,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="82" spans="2:10">
+    <row r="82" spans="2:11">
       <c r="C82" t="s">
         <v>1842</v>
       </c>
@@ -18866,7 +18947,7 @@
         <v>1851</v>
       </c>
     </row>
-    <row r="83" spans="2:10">
+    <row r="83" spans="2:11">
       <c r="C83" t="s">
         <v>1815</v>
       </c>
@@ -18883,7 +18964,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="84" spans="2:10">
+    <row r="84" spans="2:11">
       <c r="C84" t="s">
         <v>1843</v>
       </c>
@@ -18900,7 +18981,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="85" spans="2:10">
+    <row r="85" spans="2:11">
       <c r="C85" t="s">
         <v>1844</v>
       </c>
@@ -18914,283 +18995,353 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="2:10">
+    <row r="86" spans="2:11">
       <c r="C86" t="s">
         <v>1845</v>
       </c>
     </row>
-    <row r="88" spans="2:10">
+    <row r="88" spans="2:11">
       <c r="B88" t="s">
         <v>1868</v>
       </c>
     </row>
-    <row r="89" spans="2:10">
+    <row r="89" spans="2:11">
       <c r="B89"/>
     </row>
-    <row r="90" spans="2:10">
+    <row r="90" spans="2:11">
       <c r="C90" t="s">
         <v>7</v>
       </c>
       <c r="D90" t="s">
-        <v>1869</v>
-      </c>
-    </row>
-    <row r="91" spans="2:10">
-      <c r="D91" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="92" spans="2:10">
-      <c r="D92" s="73" t="s">
-        <v>1815</v>
-      </c>
-    </row>
-    <row r="93" spans="2:10">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11">
+      <c r="D91" s="105" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11">
+      <c r="D92" s="105" t="s">
+        <v>1919</v>
+      </c>
+      <c r="K92" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11">
       <c r="D93" t="s">
-        <v>1845</v>
-      </c>
-      <c r="G93" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11">
+      <c r="D94" t="s">
+        <v>1921</v>
+      </c>
+      <c r="K94" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11">
+      <c r="D95" t="s">
+        <v>1922</v>
+      </c>
+      <c r="K95" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11">
+      <c r="D96" t="s">
+        <v>1923</v>
+      </c>
+      <c r="K96" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="97" spans="3:10">
+      <c r="D97" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="99" spans="3:10">
+      <c r="D99" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="100" spans="3:10">
+      <c r="D100" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="101" spans="3:10">
+      <c r="D101" s="105" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="102" spans="3:10">
+      <c r="D102" s="105" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="103" spans="3:10">
+      <c r="D103" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="104" spans="3:10">
+      <c r="D104" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="105" spans="3:10">
+      <c r="D105" t="s">
+        <v>1931</v>
+      </c>
+      <c r="J105" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="106" spans="3:10">
+      <c r="D106" t="s">
+        <v>1932</v>
+      </c>
+      <c r="J106" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="108" spans="3:10">
+      <c r="D108" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="109" spans="3:10">
+      <c r="D109" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="110" spans="3:10">
+      <c r="D110" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="112" spans="3:10">
+      <c r="C112" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D112" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="113" spans="2:10">
+      <c r="D113" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="115" spans="2:10">
+      <c r="C115" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D115" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="116" spans="2:10">
+      <c r="D116" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="118" spans="2:10">
+      <c r="E118" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119" spans="2:10">
+      <c r="B119" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="120" spans="2:10">
+      <c r="D120" t="s">
+        <v>1915</v>
+      </c>
+      <c r="F120" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="121" spans="2:10">
+      <c r="D121" t="s">
+        <v>1895</v>
+      </c>
+      <c r="F121" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="122" spans="2:10">
+      <c r="D122" t="s">
+        <v>1896</v>
+      </c>
+      <c r="F122" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="123" spans="2:10">
+      <c r="D123" s="106" t="s">
+        <v>1897</v>
+      </c>
+      <c r="E123" s="107"/>
+      <c r="F123" s="107" t="s">
+        <v>1902</v>
+      </c>
+      <c r="J123" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="124" spans="2:10">
+      <c r="D124" t="s">
+        <v>1898</v>
+      </c>
+      <c r="F124" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="126" spans="2:10">
+      <c r="B126" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="127" spans="2:10">
+      <c r="D127" t="s">
         <v>1877</v>
       </c>
     </row>
-    <row r="94" spans="2:10">
-      <c r="D94" t="s">
-        <v>1903</v>
-      </c>
-    </row>
-    <row r="95" spans="2:10">
-      <c r="D95" t="s">
-        <v>1912</v>
-      </c>
-      <c r="G95" t="s">
-        <v>1913</v>
-      </c>
-    </row>
-    <row r="96" spans="2:10">
-      <c r="D96" t="s">
+    <row r="128" spans="2:10">
+      <c r="D128" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="129" spans="4:4">
+      <c r="D129" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="130" spans="4:4">
+      <c r="D130" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="131" spans="4:4">
+      <c r="D131" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="132" spans="4:4">
+      <c r="D132" t="s">
         <v>1882</v>
       </c>
-      <c r="G96" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="97" spans="2:7">
-      <c r="D97" t="s">
-        <v>1844</v>
-      </c>
-      <c r="G97" t="s">
-        <v>1881</v>
-      </c>
-    </row>
-    <row r="100" spans="2:7">
-      <c r="D100" t="s">
-        <v>1871</v>
-      </c>
-    </row>
-    <row r="101" spans="2:7">
-      <c r="D101" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="102" spans="2:7">
-      <c r="D102" s="73" t="s">
-        <v>1904</v>
-      </c>
-      <c r="F102" t="s">
-        <v>1916</v>
-      </c>
-    </row>
-    <row r="103" spans="2:7">
-      <c r="D103" t="s">
-        <v>1815</v>
-      </c>
-    </row>
-    <row r="104" spans="2:7">
-      <c r="D104" t="s">
+    </row>
+    <row r="133" spans="4:4">
+      <c r="D133" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="134" spans="4:4">
+      <c r="D134" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="135" spans="4:4">
+      <c r="D135" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="137" spans="4:4">
+      <c r="D137" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="138" spans="4:4">
+      <c r="D138" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="139" spans="4:4">
+      <c r="D139" t="s">
         <v>1879</v>
       </c>
     </row>
-    <row r="105" spans="2:7">
-      <c r="D105" t="s">
-        <v>1880</v>
-      </c>
-    </row>
-    <row r="106" spans="2:7">
-      <c r="D106" t="s">
-        <v>1818</v>
-      </c>
-      <c r="F106" t="s">
-        <v>1905</v>
-      </c>
-    </row>
-    <row r="107" spans="2:7">
-      <c r="D107" t="s">
-        <v>1872</v>
-      </c>
-      <c r="F107" t="s">
-        <v>1876</v>
-      </c>
-    </row>
-    <row r="110" spans="2:7">
-      <c r="B110" t="s">
-        <v>1875</v>
-      </c>
-    </row>
-    <row r="111" spans="2:7">
-      <c r="D111" t="s">
-        <v>1928</v>
-      </c>
-      <c r="F111" t="s">
-        <v>1929</v>
-      </c>
-    </row>
-    <row r="112" spans="2:7">
-      <c r="D112" t="s">
-        <v>1906</v>
-      </c>
-      <c r="F112" t="s">
-        <v>1910</v>
-      </c>
-    </row>
-    <row r="113" spans="2:6">
-      <c r="D113" t="s">
-        <v>1907</v>
-      </c>
-      <c r="F113" t="s">
-        <v>1911</v>
-      </c>
-    </row>
-    <row r="114" spans="2:6">
-      <c r="D114" t="s">
-        <v>1908</v>
-      </c>
-      <c r="F114" t="s">
-        <v>1914</v>
-      </c>
-    </row>
-    <row r="115" spans="2:6">
-      <c r="D115" t="s">
-        <v>1909</v>
-      </c>
-      <c r="F115" t="s">
-        <v>1915</v>
-      </c>
-    </row>
-    <row r="117" spans="2:6">
-      <c r="B117" t="s">
-        <v>1883</v>
-      </c>
-    </row>
-    <row r="118" spans="2:6">
-      <c r="D118" t="s">
-        <v>1884</v>
-      </c>
-    </row>
-    <row r="119" spans="2:6">
-      <c r="D119" t="s">
-        <v>1885</v>
-      </c>
-    </row>
-    <row r="120" spans="2:6">
-      <c r="D120" t="s">
-        <v>1886</v>
-      </c>
-    </row>
-    <row r="121" spans="2:6">
-      <c r="D121" t="s">
+    <row r="140" spans="4:4">
+      <c r="D140" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="141" spans="4:4">
+      <c r="D141" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="142" spans="4:4">
+      <c r="D142" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="144" spans="4:4">
+      <c r="D144" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="145" spans="4:10">
+      <c r="D145" t="s">
         <v>1887</v>
       </c>
-    </row>
-    <row r="122" spans="2:6">
-      <c r="D122" t="s">
-        <v>1888</v>
-      </c>
-    </row>
-    <row r="123" spans="2:6">
-      <c r="D123" t="s">
-        <v>1889</v>
-      </c>
-    </row>
-    <row r="124" spans="2:6">
-      <c r="D124" t="s">
-        <v>1890</v>
-      </c>
-    </row>
-    <row r="125" spans="2:6">
-      <c r="D125" t="s">
+      <c r="G145" t="s">
+        <v>1887</v>
+      </c>
+      <c r="J145" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="146" spans="4:10">
+      <c r="D146" t="s">
+        <v>1879</v>
+      </c>
+      <c r="G146" t="s">
+        <v>1879</v>
+      </c>
+      <c r="J146" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="147" spans="4:10">
+      <c r="D147" t="s">
         <v>1891</v>
       </c>
-    </row>
-    <row r="126" spans="2:6">
-      <c r="D126" t="s">
+      <c r="G147" t="s">
+        <v>1941</v>
+      </c>
+      <c r="J147" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="148" spans="4:10">
+      <c r="D148" t="s">
         <v>1892</v>
       </c>
-    </row>
-    <row r="128" spans="2:6">
-      <c r="D128" t="s">
+      <c r="G148" t="s">
+        <v>1944</v>
+      </c>
+      <c r="J148" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="149" spans="4:10">
+      <c r="D149" t="s">
+        <v>1943</v>
+      </c>
+      <c r="G149" t="s">
         <v>1893</v>
       </c>
-    </row>
-    <row r="129" spans="4:6">
-      <c r="D129" t="s">
-        <v>1894</v>
-      </c>
-    </row>
-    <row r="130" spans="4:6">
-      <c r="D130" t="s">
-        <v>1886</v>
-      </c>
-    </row>
-    <row r="131" spans="4:6">
-      <c r="D131" t="s">
-        <v>1895</v>
-      </c>
-    </row>
-    <row r="132" spans="4:6">
-      <c r="D132" t="s">
-        <v>1896</v>
-      </c>
-    </row>
-    <row r="134" spans="4:6">
-      <c r="D134" t="s">
-        <v>1897</v>
-      </c>
-    </row>
-    <row r="135" spans="4:6">
-      <c r="D135" t="s">
-        <v>1894</v>
-      </c>
-      <c r="F135" t="s">
-        <v>1894</v>
-      </c>
-    </row>
-    <row r="136" spans="4:6">
-      <c r="D136" t="s">
-        <v>1886</v>
-      </c>
-      <c r="F136" t="s">
-        <v>1886</v>
-      </c>
-    </row>
-    <row r="137" spans="4:6">
-      <c r="D137" t="s">
-        <v>1898</v>
-      </c>
-      <c r="F137" t="s">
-        <v>1901</v>
-      </c>
-    </row>
-    <row r="138" spans="4:6">
-      <c r="D138" t="s">
-        <v>1899</v>
-      </c>
-      <c r="F138" t="s">
-        <v>1902</v>
-      </c>
-    </row>
-    <row r="139" spans="4:6">
-      <c r="D139" t="s">
-        <v>1900</v>
+      <c r="J149" t="s">
+        <v>1942</v>
       </c>
     </row>
   </sheetData>
@@ -23539,10 +23690,10 @@
     </row>
     <row r="160" spans="2:11">
       <c r="B160" s="6" t="s">
-        <v>1917</v>
+        <v>1904</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>1918</v>
+        <v>1905</v>
       </c>
       <c r="D160" s="6" t="s">
         <v>1117</v>
@@ -23565,10 +23716,10 @@
     </row>
     <row r="161" spans="2:11">
       <c r="B161" s="8" t="s">
-        <v>1921</v>
+        <v>1908</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>1919</v>
+        <v>1906</v>
       </c>
       <c r="D161" s="8"/>
       <c r="E161" s="8">
@@ -23582,7 +23733,7 @@
         <v>125</v>
       </c>
       <c r="I161" s="8" t="s">
-        <v>1922</v>
+        <v>1909</v>
       </c>
       <c r="K161" s="5" t="str">
         <f t="shared" si="18"/>
@@ -23591,10 +23742,10 @@
     </row>
     <row r="162" spans="2:11">
       <c r="B162" s="8" t="s">
-        <v>1921</v>
+        <v>1908</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>1920</v>
+        <v>1907</v>
       </c>
       <c r="D162" s="8"/>
       <c r="E162" s="8">
@@ -23608,7 +23759,7 @@
         <v>125</v>
       </c>
       <c r="I162" s="8" t="s">
-        <v>1923</v>
+        <v>1910</v>
       </c>
       <c r="K162" s="5" t="str">
         <f t="shared" si="18"/>
@@ -23617,10 +23768,10 @@
     </row>
     <row r="163" spans="2:11">
       <c r="B163" s="8" t="s">
-        <v>1921</v>
+        <v>1908</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>1908</v>
+        <v>1897</v>
       </c>
       <c r="D163" s="8"/>
       <c r="E163" s="8">
@@ -23634,7 +23785,7 @@
         <v>125</v>
       </c>
       <c r="I163" s="8" t="s">
-        <v>1924</v>
+        <v>1911</v>
       </c>
       <c r="K163" s="5" t="str">
         <f t="shared" si="18"/>
@@ -23643,10 +23794,10 @@
     </row>
     <row r="164" spans="2:11">
       <c r="B164" s="8" t="s">
-        <v>1921</v>
+        <v>1908</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>1906</v>
+        <v>1895</v>
       </c>
       <c r="D164" s="8"/>
       <c r="E164" s="8">
@@ -23660,7 +23811,7 @@
         <v>125</v>
       </c>
       <c r="I164" s="8" t="s">
-        <v>1925</v>
+        <v>1912</v>
       </c>
       <c r="K164" s="5" t="str">
         <f t="shared" si="18"/>
@@ -23669,10 +23820,10 @@
     </row>
     <row r="165" spans="2:11">
       <c r="B165" s="8" t="s">
-        <v>1921</v>
+        <v>1908</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>1909</v>
+        <v>1898</v>
       </c>
       <c r="D165" s="8"/>
       <c r="E165" s="8">
@@ -23686,7 +23837,7 @@
         <v>125</v>
       </c>
       <c r="I165" s="8" t="s">
-        <v>1927</v>
+        <v>1914</v>
       </c>
       <c r="K165" s="5" t="str">
         <f t="shared" si="18"/>
@@ -23695,10 +23846,10 @@
     </row>
     <row r="166" spans="2:11">
       <c r="B166" s="8" t="s">
-        <v>1921</v>
+        <v>1908</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>1907</v>
+        <v>1896</v>
       </c>
       <c r="D166" s="8"/>
       <c r="E166" s="8">
@@ -23712,7 +23863,7 @@
         <v>125</v>
       </c>
       <c r="I166" s="8" t="s">
-        <v>1926</v>
+        <v>1913</v>
       </c>
       <c r="K166" s="5" t="str">
         <f t="shared" si="18"/>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183BBFB3-FA9C-4D3F-9431-D0830D458C4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B9B185-3B53-455A-BB29-989EC80AD349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="3" activeTab="13" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -33,7 +33,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">モンスタースキル!$C$4:$C$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -8513,8 +8512,8 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>いずれかのレコードが存在しない</t>
-    <rPh sb="10" eb="12">
+    <t>レコードが存在しない</t>
+    <rPh sb="5" eb="7">
       <t>ソンザイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
@@ -8949,7 +8948,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -9123,7 +9122,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -12656,8 +12654,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7984025" y="1633012"/>
-          <a:ext cx="1824308" cy="1293159"/>
+          <a:off x="7985930" y="1467837"/>
+          <a:ext cx="1820498" cy="1167653"/>
           <a:chOff x="8992083" y="208776"/>
           <a:chExt cx="1814762" cy="1244600"/>
         </a:xfrm>
@@ -12966,8 +12964,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="11281192" y="3261311"/>
-          <a:ext cx="1842700" cy="2086992"/>
+          <a:off x="11283097" y="2938582"/>
+          <a:ext cx="1842700" cy="1889768"/>
           <a:chOff x="8549484" y="3956874"/>
           <a:chExt cx="1810288" cy="1437363"/>
         </a:xfrm>
@@ -13518,8 +13516,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4719534" y="1760719"/>
-          <a:ext cx="1895839" cy="3563024"/>
+          <a:off x="4721439" y="1597449"/>
+          <a:ext cx="1890124" cy="3208246"/>
           <a:chOff x="5970441" y="628674"/>
           <a:chExt cx="1893913" cy="3428095"/>
         </a:xfrm>
@@ -13987,8 +13985,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10944934" y="7742408"/>
-          <a:ext cx="2214486" cy="2691510"/>
+          <a:off x="10941124" y="6969538"/>
+          <a:ext cx="2220201" cy="2422569"/>
           <a:chOff x="12007370" y="5957071"/>
           <a:chExt cx="2223130" cy="2581251"/>
         </a:xfrm>
@@ -14194,8 +14192,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14472514" y="5130000"/>
-          <a:ext cx="2243119" cy="1832402"/>
+          <a:off x="14468704" y="4627977"/>
+          <a:ext cx="2246929" cy="1653108"/>
           <a:chOff x="15050343" y="4729843"/>
           <a:chExt cx="2243515" cy="1763032"/>
         </a:xfrm>
@@ -14624,8 +14622,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6912125" y="5558118"/>
-          <a:ext cx="1795181" cy="1393339"/>
+          <a:off x="6914030" y="5002306"/>
+          <a:ext cx="1795181" cy="1264024"/>
           <a:chOff x="6846794" y="5210735"/>
           <a:chExt cx="2341399" cy="1311089"/>
         </a:xfrm>
@@ -15001,8 +14999,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3760297" y="8147154"/>
-          <a:ext cx="2359052" cy="2005373"/>
+          <a:off x="3760297" y="7340331"/>
+          <a:ext cx="2355242" cy="1808149"/>
           <a:chOff x="3726679" y="7642891"/>
           <a:chExt cx="2335072" cy="1468663"/>
         </a:xfrm>
@@ -15925,13 +15923,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6672014-33B5-48C4-9202-55E4E667EEEF}">
   <dimension ref="C5:W32"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="3" width="8.75" customWidth="1"/>
-    <col min="27" max="27" width="4.375" customWidth="1"/>
+    <col min="2" max="3" width="8.69921875" customWidth="1"/>
+    <col min="27" max="27" width="4.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:23" ht="19.5" thickBot="1">
+    <row r="5" spans="3:23" ht="18.600000000000001" thickBot="1">
       <c r="V5" s="67"/>
       <c r="W5" s="67"/>
     </row>
@@ -15965,7 +15963,7 @@
       <c r="C8" s="64"/>
       <c r="W8" s="65"/>
     </row>
-    <row r="9" spans="3:23" ht="19.5" thickBot="1">
+    <row r="9" spans="3:23" ht="18.600000000000001" thickBot="1">
       <c r="C9" s="64"/>
       <c r="L9" t="s">
         <v>1706</v>
@@ -16115,7 +16113,7 @@
       <c r="V30" s="65"/>
       <c r="W30" s="65"/>
     </row>
-    <row r="31" spans="3:23" ht="19.5" thickBot="1">
+    <row r="31" spans="3:23" ht="18.600000000000001" thickBot="1">
       <c r="C31" s="64"/>
       <c r="D31" s="66"/>
       <c r="E31" s="67"/>
@@ -16138,7 +16136,7 @@
       <c r="V31" s="68"/>
       <c r="W31" s="65"/>
     </row>
-    <row r="32" spans="3:23" ht="13.15" customHeight="1" thickBot="1">
+    <row r="32" spans="3:23" ht="13.2" customHeight="1" thickBot="1">
       <c r="C32" s="66"/>
       <c r="D32" s="67"/>
       <c r="E32" s="67"/>
@@ -16171,10 +16169,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC349EE6-5475-4F9C-BD43-5DC02797CE07}">
   <dimension ref="A2:Q56"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="11" style="98" customWidth="1"/>
-    <col min="2" max="6" width="10.875" style="98" customWidth="1"/>
+    <col min="2" max="6" width="10.8984375" style="98" customWidth="1"/>
     <col min="7" max="16384" width="9" style="98"/>
   </cols>
   <sheetData>
@@ -16538,10 +16536,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F0B575-2DDF-49B9-8DE2-F372EEC2F3B3}">
   <dimension ref="A2:O79"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="11.875" style="1" customWidth="1"/>
-    <col min="2" max="6" width="10.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.8984375" style="1" customWidth="1"/>
+    <col min="2" max="6" width="10.8984375" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -16573,7 +16571,7 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="18.75">
+    <row r="4" spans="1:15" ht="18">
       <c r="A4" s="1" t="s">
         <v>1280</v>
       </c>
@@ -16602,7 +16600,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" ht="13.2">
       <c r="B5" s="58" t="s">
         <v>1175</v>
       </c>
@@ -16619,7 +16617,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" ht="13.2">
       <c r="B6" s="58" t="s">
         <v>1176</v>
       </c>
@@ -16642,7 +16640,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" ht="13.2">
       <c r="B7" s="58" t="s">
         <v>1189</v>
       </c>
@@ -16671,7 +16669,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" ht="13.2">
       <c r="B8" s="58" t="s">
         <v>1177</v>
       </c>
@@ -16700,7 +16698,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" ht="13.2">
       <c r="B9" s="58" t="s">
         <v>1178</v>
       </c>
@@ -16726,7 +16724,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" ht="13.2">
       <c r="B10" s="58" t="s">
         <v>1179</v>
       </c>
@@ -16752,7 +16750,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" ht="13.2">
       <c r="B11" s="58" t="s">
         <v>1180</v>
       </c>
@@ -16778,7 +16776,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" ht="13.2">
       <c r="B12" s="58" t="s">
         <v>1181</v>
       </c>
@@ -16804,7 +16802,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" ht="13.2">
       <c r="B13" s="58" t="s">
         <v>1182</v>
       </c>
@@ -16827,7 +16825,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" ht="13.2">
       <c r="B14" s="58" t="s">
         <v>1183</v>
       </c>
@@ -16850,7 +16848,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" ht="13.2">
       <c r="B15" s="58" t="s">
         <v>1184</v>
       </c>
@@ -16873,7 +16871,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" ht="13.2">
       <c r="B16" s="58" t="s">
         <v>1185</v>
       </c>
@@ -16893,7 +16891,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" ht="13.2">
       <c r="B17" s="58" t="s">
         <v>1186</v>
       </c>
@@ -16913,7 +16911,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:10" ht="13.2">
       <c r="B18" s="58" t="s">
         <v>1190</v>
       </c>
@@ -16933,7 +16931,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:10" ht="13.2">
       <c r="B19" s="58" t="s">
         <v>1187</v>
       </c>
@@ -16953,7 +16951,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:10" ht="13.2">
       <c r="B20" s="58" t="s">
         <v>1191</v>
       </c>
@@ -17498,9 +17496,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FCFD5C-696C-43AD-A2BD-D69C05CB2D44}">
   <dimension ref="B2:P57"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="16384" width="8.75" style="1"/>
+    <col min="1" max="16384" width="8.69921875" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
@@ -17976,9 +17974,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E898285-845A-4583-B20D-F3A331C07E8E}">
   <dimension ref="B2:R45"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="13" max="13" width="8.625" customWidth="1"/>
+    <col min="13" max="13" width="8.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18">
@@ -17993,7 +17991,7 @@
       <c r="O2" s="86"/>
       <c r="P2" s="86"/>
     </row>
-    <row r="3" spans="2:18" ht="19.5" thickBot="1">
+    <row r="3" spans="2:18" ht="18.600000000000001" thickBot="1">
       <c r="F3" s="89" t="s">
         <v>1582</v>
       </c>
@@ -18115,7 +18113,7 @@
       <c r="P10" s="65"/>
       <c r="R10" s="84"/>
     </row>
-    <row r="11" spans="2:18" ht="19.5" thickBot="1">
+    <row r="11" spans="2:18" ht="18.600000000000001" thickBot="1">
       <c r="F11" s="91"/>
       <c r="I11" s="75"/>
       <c r="J11" s="66"/>
@@ -18204,7 +18202,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="22" spans="4:18" ht="19.5" thickBot="1">
+    <row r="22" spans="4:18" ht="18.600000000000001" thickBot="1">
       <c r="D22" s="80"/>
       <c r="E22" s="81"/>
       <c r="F22" s="81"/>
@@ -18333,7 +18331,7 @@
       </c>
       <c r="N29" s="84"/>
     </row>
-    <row r="30" spans="4:18" ht="19.5" thickBot="1">
+    <row r="30" spans="4:18" ht="18.600000000000001" thickBot="1">
       <c r="D30" s="83"/>
       <c r="E30" s="77"/>
       <c r="F30" s="78"/>
@@ -18569,11 +18567,11 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD79B98E-03E4-44E6-9FBF-39CA1C89C95A}">
   <dimension ref="B3:L149"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="8.75" style="73"/>
-    <col min="3" max="3" width="10.625" customWidth="1"/>
-    <col min="6" max="6" width="10.875" customWidth="1"/>
+    <col min="2" max="2" width="8.69921875" style="73"/>
+    <col min="3" max="3" width="10.59765625" customWidth="1"/>
+    <col min="6" max="6" width="10.8984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:10">
@@ -19017,12 +19015,12 @@
       </c>
     </row>
     <row r="91" spans="2:11">
-      <c r="D91" s="105" t="s">
+      <c r="D91" t="s">
         <v>1918</v>
       </c>
     </row>
     <row r="92" spans="2:11">
-      <c r="D92" s="105" t="s">
+      <c r="D92" t="s">
         <v>1919</v>
       </c>
       <c r="K92" t="s">
@@ -19074,12 +19072,12 @@
       </c>
     </row>
     <row r="101" spans="3:10">
-      <c r="D101" s="105" t="s">
+      <c r="D101" t="s">
         <v>1927</v>
       </c>
     </row>
     <row r="102" spans="3:10">
-      <c r="D102" s="105" t="s">
+      <c r="D102" t="s">
         <v>1928</v>
       </c>
     </row>
@@ -19185,11 +19183,11 @@
       </c>
     </row>
     <row r="123" spans="2:10">
-      <c r="D123" s="106" t="s">
+      <c r="D123" s="105" t="s">
         <v>1897</v>
       </c>
-      <c r="E123" s="107"/>
-      <c r="F123" s="107" t="s">
+      <c r="E123" s="106"/>
+      <c r="F123" s="106" t="s">
         <v>1902</v>
       </c>
       <c r="J123" t="s">
@@ -19353,7 +19351,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="16384" width="9" style="5"/>
   </cols>
@@ -19367,7 +19365,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBD988A-503C-4F44-AC4A-B26683FC9B4C}">
   <dimension ref="B4:O34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="16384" width="9" style="5"/>
   </cols>
@@ -19518,14 +19516,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
   <dimension ref="B4:K166"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="2" width="20.25" style="5" customWidth="1"/>
-    <col min="3" max="3" width="24.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.19921875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="24.09765625" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" style="5" customWidth="1"/>
     <col min="5" max="8" width="9" style="5"/>
-    <col min="9" max="9" width="45.625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="45.59765625" style="5" customWidth="1"/>
     <col min="10" max="22" width="9" style="5"/>
     <col min="23" max="23" width="8" style="5" customWidth="1"/>
     <col min="24" max="16384" width="9" style="5"/>
@@ -23879,22 +23877,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EB7090A-0065-41E7-85DA-75EEB9504A67}">
   <dimension ref="C3:Q81"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="2" width="7.5" style="5" customWidth="1"/>
-    <col min="3" max="3" width="13.75" style="5" customWidth="1"/>
+    <col min="3" max="3" width="13.69921875" style="5" customWidth="1"/>
     <col min="4" max="4" width="20" style="5" customWidth="1"/>
-    <col min="5" max="5" width="30.625" style="5" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="13.375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="30.59765625" style="5" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="13.3984375" style="5" customWidth="1"/>
     <col min="7" max="7" width="11" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.75" style="5" customWidth="1"/>
-    <col min="10" max="12" width="9.875" style="18" customWidth="1"/>
-    <col min="13" max="13" width="9.25" style="18" customWidth="1"/>
-    <col min="14" max="14" width="12.625" style="18" customWidth="1"/>
-    <col min="15" max="15" width="27.125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="15.19921875" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.69921875" style="5" customWidth="1"/>
+    <col min="10" max="12" width="9.8984375" style="18" customWidth="1"/>
+    <col min="13" max="13" width="9.19921875" style="18" customWidth="1"/>
+    <col min="14" max="14" width="12.59765625" style="18" customWidth="1"/>
+    <col min="15" max="15" width="27.09765625" style="5" customWidth="1"/>
     <col min="16" max="16" width="7.5" style="5" customWidth="1"/>
-    <col min="17" max="17" width="15.125" style="5" customWidth="1"/>
+    <col min="17" max="17" width="15.09765625" style="5" customWidth="1"/>
     <col min="18" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -25558,7 +25556,7 @@
         <v>INSERT INTO m_skill VALUES ('skill037','グラビジャ',4,0,0,1,75,50,0.0,1,1200,'現HPの７５％ダメージ');</v>
       </c>
     </row>
-    <row r="41" spans="3:17" ht="40.5">
+    <row r="41" spans="3:17" ht="37.799999999999997">
       <c r="C41" s="47" t="s">
         <v>1048</v>
       </c>
@@ -27310,10 +27308,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F51B408-D4E3-46FE-97DE-15AB67B6AAB6}">
   <dimension ref="B1:Q100"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="2" width="12.75" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.69921875" style="5" customWidth="1"/>
     <col min="3" max="3" width="17.5" style="5" customWidth="1"/>
     <col min="4" max="16384" width="9" style="5"/>
   </cols>
@@ -30129,22 +30127,22 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E63A27D9-C8B6-491D-9205-8D7433312F14}">
   <dimension ref="A4:U522"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="12.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.8984375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="12.75" style="3" customWidth="1"/>
-    <col min="8" max="8" width="5.375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="5.3984375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="14.09765625" style="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="1"/>
-    <col min="12" max="12" width="17.75" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.69921875" style="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1"/>
-    <col min="14" max="14" width="5.25" style="1" customWidth="1"/>
+    <col min="14" max="14" width="5.19921875" style="1" customWidth="1"/>
     <col min="15" max="20" width="9" style="1"/>
-    <col min="21" max="21" width="8.875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="8.8984375" style="1" customWidth="1"/>
     <col min="22" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -46737,7 +46735,7 @@
         <v>INSERT INTO m_monster_skills VALUES ('myskill0505','monster084','skill051',FALSE);</v>
       </c>
     </row>
-    <row r="510" spans="1:21" ht="18.75">
+    <row r="510" spans="1:21" ht="18">
       <c r="A510"/>
       <c r="B510"/>
       <c r="C510"/>
@@ -46760,7 +46758,7 @@
       <c r="T510"/>
       <c r="U510"/>
     </row>
-    <row r="511" spans="1:21" ht="18.75">
+    <row r="511" spans="1:21" ht="18">
       <c r="A511"/>
       <c r="B511"/>
       <c r="C511"/>
@@ -46783,7 +46781,7 @@
       <c r="T511"/>
       <c r="U511"/>
     </row>
-    <row r="512" spans="1:21" ht="18.75">
+    <row r="512" spans="1:21" ht="18">
       <c r="A512"/>
       <c r="B512"/>
       <c r="C512"/>
@@ -46806,7 +46804,7 @@
       <c r="T512"/>
       <c r="U512"/>
     </row>
-    <row r="513" spans="1:21" ht="18.75">
+    <row r="513" spans="1:21" ht="18">
       <c r="A513"/>
       <c r="B513"/>
       <c r="C513"/>
@@ -46829,7 +46827,7 @@
       <c r="T513"/>
       <c r="U513"/>
     </row>
-    <row r="514" spans="1:21" ht="18.75">
+    <row r="514" spans="1:21" ht="18">
       <c r="A514"/>
       <c r="B514"/>
       <c r="C514"/>
@@ -46852,7 +46850,7 @@
       <c r="T514"/>
       <c r="U514"/>
     </row>
-    <row r="515" spans="1:21" ht="18.75">
+    <row r="515" spans="1:21" ht="18">
       <c r="A515"/>
       <c r="B515"/>
       <c r="C515"/>
@@ -46875,7 +46873,7 @@
       <c r="T515"/>
       <c r="U515"/>
     </row>
-    <row r="516" spans="1:21" ht="18.75">
+    <row r="516" spans="1:21" ht="18">
       <c r="A516"/>
       <c r="B516"/>
       <c r="C516"/>
@@ -46898,7 +46896,7 @@
       <c r="T516"/>
       <c r="U516"/>
     </row>
-    <row r="517" spans="1:21" ht="18.75">
+    <row r="517" spans="1:21" ht="18">
       <c r="A517"/>
       <c r="B517"/>
       <c r="C517"/>
@@ -46921,7 +46919,7 @@
       <c r="T517"/>
       <c r="U517"/>
     </row>
-    <row r="518" spans="1:21" ht="18.75">
+    <row r="518" spans="1:21" ht="18">
       <c r="A518"/>
       <c r="B518"/>
       <c r="C518"/>
@@ -46944,7 +46942,7 @@
       <c r="T518"/>
       <c r="U518"/>
     </row>
-    <row r="519" spans="1:21" ht="18.75">
+    <row r="519" spans="1:21" ht="18">
       <c r="A519"/>
       <c r="B519"/>
       <c r="C519"/>
@@ -46967,7 +46965,7 @@
       <c r="T519"/>
       <c r="U519"/>
     </row>
-    <row r="520" spans="1:21" ht="18.75">
+    <row r="520" spans="1:21" ht="18">
       <c r="A520"/>
       <c r="B520"/>
       <c r="C520"/>
@@ -46990,7 +46988,7 @@
       <c r="T520"/>
       <c r="U520"/>
     </row>
-    <row r="521" spans="1:21" ht="18.75">
+    <row r="521" spans="1:21" ht="18">
       <c r="A521"/>
       <c r="B521"/>
       <c r="C521"/>
@@ -47013,7 +47011,7 @@
       <c r="T521"/>
       <c r="U521"/>
     </row>
-    <row r="522" spans="1:21" ht="18.75">
+    <row r="522" spans="1:21" ht="18">
       <c r="A522"/>
       <c r="B522"/>
       <c r="C522"/>
@@ -47045,15 +47043,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A843E7EA-D614-495E-86B7-D31F628C6221}">
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="3" width="17.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="17.19921875" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.75" style="5" customWidth="1"/>
+    <col min="5" max="5" width="11.59765625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.69921875" style="5" customWidth="1"/>
     <col min="7" max="7" width="13.5" style="5" customWidth="1"/>
-    <col min="8" max="8" width="11.875" style="5" customWidth="1"/>
+    <col min="8" max="8" width="11.8984375" style="5" customWidth="1"/>
     <col min="9" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -47414,13 +47412,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE71EC6-0DD3-461C-A8FC-74E22154B7A5}">
   <dimension ref="A4:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="3.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="3.8984375" style="1" customWidth="1"/>
     <col min="2" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="4.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="95.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="4.19921875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="95.19921875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.8984375" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B9B185-3B53-455A-BB29-989EC80AD349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B485CA79-858E-44C7-BA17-B9F94FB3517F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="3" activeTab="13" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="architecture" sheetId="12" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4134" uniqueCount="1947">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4138" uniqueCount="1950">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -8518,6 +8518,18 @@
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t xml:space="preserve">データ・処理フロー </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>監視・通知フロー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>インフラ・接続関係</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -8526,7 +8538,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8628,6 +8640,20 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="BIZ UDゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="BIZ UDゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="8">
@@ -8948,7 +8974,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -9124,6 +9150,8 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -9672,15 +9700,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>402770</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>195943</xdr:rowOff>
+      <xdr:colOff>348341</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>108858</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>97970</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>174173</xdr:rowOff>
+      <xdr:colOff>43541</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>87088</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9695,7 +9723,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2427513" y="2732314"/>
+          <a:off x="2351312" y="3331029"/>
           <a:ext cx="1719943" cy="1578430"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -9820,16 +9848,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>468089</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>609604</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>21772</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>283033</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>65314</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>424548</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>174172</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9844,8 +9872,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6542318" y="2688771"/>
-          <a:ext cx="1839686" cy="1970314"/>
+          <a:off x="4637318" y="3243943"/>
+          <a:ext cx="1839687" cy="1752600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9979,37 +10007,6 @@
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
             <a:t>/public/v1/colors</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
-              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>/public/v1/series</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -10347,15 +10344,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>674913</xdr:colOff>
+      <xdr:colOff>667293</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>108857</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>511628</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>32659</xdr:rowOff>
+      <xdr:rowOff>65316</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10370,8 +10367,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8098970" y="6041571"/>
-          <a:ext cx="1186544" cy="870859"/>
+          <a:off x="8069579" y="6074228"/>
+          <a:ext cx="1194163" cy="870859"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10456,16 +10453,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>598714</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>43541</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>163283</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>217715</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>174173</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>293916</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>65315</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10480,7 +10477,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10722428" y="2579912"/>
+          <a:off x="9046029" y="2275112"/>
           <a:ext cx="1643744" cy="2645232"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -10708,16 +10705,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>370113</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>195941</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>457199</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>174170</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>468085</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>163286</xdr:rowOff>
+      <xdr:colOff>119742</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>141515</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10732,7 +10729,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12518570" y="3646712"/>
+          <a:off x="10853056" y="2285999"/>
           <a:ext cx="2122715" cy="1567545"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -10897,8 +10894,8 @@
       <xdr:rowOff>217714</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>163286</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>130629</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>21771</xdr:rowOff>
     </xdr:to>
@@ -10915,8 +10912,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15849599" y="217714"/>
-          <a:ext cx="1861458" cy="1883228"/>
+          <a:off x="14194970" y="217714"/>
+          <a:ext cx="1861459" cy="1883228"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11061,13 +11058,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>511628</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>217717</xdr:rowOff>
+      <xdr:colOff>517072</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>10886</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>517071</xdr:colOff>
+      <xdr:colOff>522513</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>97972</xdr:rowOff>
     </xdr:to>
@@ -11086,16 +11083,16 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7260771" y="446317"/>
-          <a:ext cx="5443" cy="566055"/>
+        <a:xfrm flipH="1">
+          <a:off x="7244443" y="468086"/>
+          <a:ext cx="5441" cy="544286"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
         </a:prstGeom>
         <a:ln w="28575">
           <a:solidFill>
-            <a:srgbClr val="FF0000"/>
+            <a:sysClr val="windowText" lastClr="000000"/>
           </a:solidFill>
           <a:headEnd type="none" w="med" len="med"/>
           <a:tailEnd type="triangle" w="med" len="med"/>
@@ -11218,15 +11215,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>631370</xdr:colOff>
+      <xdr:colOff>642255</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>76201</xdr:rowOff>
+      <xdr:rowOff>119744</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>391885</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>217717</xdr:rowOff>
+      <xdr:colOff>402770</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>10886</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -11241,8 +11238,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6705599" y="76201"/>
-          <a:ext cx="1110343" cy="370116"/>
+          <a:off x="6694712" y="119744"/>
+          <a:ext cx="1110344" cy="348342"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11603,15 +11600,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>587828</xdr:colOff>
+      <xdr:colOff>533398</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>620486</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>195943</xdr:rowOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>108858</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -11629,8 +11626,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="3287485" y="2307771"/>
-          <a:ext cx="1382487" cy="424543"/>
+          <a:off x="3211284" y="2307771"/>
+          <a:ext cx="1436916" cy="1023258"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -11663,9 +11660,9 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>587828</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>174173</xdr:rowOff>
+      <xdr:colOff>533398</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>87088</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
@@ -11689,8 +11686,128 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3287485" y="4310744"/>
-          <a:ext cx="1360713" cy="1719940"/>
+          <a:off x="3211284" y="4909459"/>
+          <a:ext cx="1415142" cy="1121225"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>16328</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>179619</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>21772</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="44" name="直線矢印コネクタ 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E4DD22E-DEC8-4D35-A66E-813814A69F12}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="8" idx="2"/>
+          <a:endCxn id="11" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5393871" y="2928257"/>
+          <a:ext cx="163291" cy="315686"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>43541</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>212272</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>609604</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>212273</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="48" name="直線矢印コネクタ 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{281C2595-C16A-4D7B-9B80-BB64ECEA9DAD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="10" idx="3"/>
+          <a:endCxn id="11" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="4071255" y="4120243"/>
+          <a:ext cx="566063" cy="1"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -11723,135 +11840,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>87085</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>38104</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="44" name="直線矢印コネクタ 43">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E4DD22E-DEC8-4D35-A66E-813814A69F12}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="8" idx="3"/>
-          <a:endCxn id="11" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6161314" y="2307771"/>
-          <a:ext cx="1300847" cy="381000"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="28575">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="triangle" w="med" len="med"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>97970</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>70758</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>468089</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>223157</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="48" name="直線矢印コネクタ 47">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{281C2595-C16A-4D7B-9B80-BB64ECEA9DAD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="10" idx="3"/>
-          <a:endCxn id="11" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4147456" y="3521529"/>
-          <a:ext cx="2394862" cy="152399"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="28575">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="triangle" w="med" len="med"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>38104</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>65314</xdr:rowOff>
+      <xdr:colOff>424548</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>212272</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>589461</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>108857</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -11863,14 +11860,14 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="11" idx="2"/>
+          <a:stCxn id="11" idx="3"/>
           <a:endCxn id="14" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7462161" y="4659085"/>
-          <a:ext cx="1226271" cy="1382486"/>
+          <a:off x="6477005" y="4120243"/>
+          <a:ext cx="2189656" cy="1953985"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -11911,7 +11908,7 @@
       <xdr:col>11</xdr:col>
       <xdr:colOff>667293</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>54430</xdr:rowOff>
+      <xdr:rowOff>87087</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -11929,8 +11926,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6760027" y="6030684"/>
-          <a:ext cx="1331323" cy="446317"/>
+          <a:off x="6738255" y="6030684"/>
+          <a:ext cx="1331324" cy="478974"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -11964,14 +11961,14 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>511628</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>174173</xdr:rowOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>65315</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>70757</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>146958</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>54430</xdr:rowOff>
+      <xdr:rowOff>87087</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -11989,8 +11986,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="9285514" y="5225144"/>
-          <a:ext cx="2258786" cy="1251857"/>
+          <a:off x="8882742" y="4920344"/>
+          <a:ext cx="985159" cy="1621972"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -12024,14 +12021,14 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>511628</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>163286</xdr:rowOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>141515</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>81642</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>168728</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>54430</xdr:rowOff>
+      <xdr:rowOff>87087</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -12049,8 +12046,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="9285514" y="5214257"/>
-          <a:ext cx="4294414" cy="1262744"/>
+          <a:off x="8882742" y="3853544"/>
+          <a:ext cx="3031672" cy="2688772"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -12082,16 +12079,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>70757</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>5442</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>146958</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>326570</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>43541</xdr:rowOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>163283</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -12109,8 +12106,797 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="11544300" y="1159328"/>
-          <a:ext cx="4305299" cy="1420584"/>
+          <a:off x="9867901" y="1175657"/>
+          <a:ext cx="3946069" cy="1099455"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>517072</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>174171</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>589461</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>108857</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="45" name="直線矢印コネクタ 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DB86A05-3710-4F88-A260-C42412CBD964}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="20" idx="2"/>
+          <a:endCxn id="14" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7244443" y="1328057"/>
+          <a:ext cx="1422218" cy="4746171"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>500744</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>163285</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>108858</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>65316</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="正方形/長方形 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{362A5F42-DF1A-40EA-8F56-61CEEF5551B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10221687" y="5475514"/>
+          <a:ext cx="2743200" cy="1502231"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>BatchMonitor</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>各バッチの実行ログを監視</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>異常終了・未実行を検知・通知</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>プッシュ通知</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>522516</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>141515</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>168728</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>163285</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="60" name="直線矢印コネクタ 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4B98AB5-C406-4950-9AB8-5E74D8E8AAA0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="16" idx="2"/>
+          <a:endCxn id="50" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="11593287" y="3853544"/>
+          <a:ext cx="321127" cy="1621970"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="7030A0"/>
+          </a:solidFill>
+          <a:headEnd type="triangle" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>146958</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>65315</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>522516</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>163285</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="66" name="直線矢印コネクタ 65">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A222D5D-1E02-459C-9290-2386E499B8A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="15" idx="2"/>
+          <a:endCxn id="50" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9867901" y="4920344"/>
+          <a:ext cx="1725386" cy="555170"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="7030A0"/>
+          </a:solidFill>
+          <a:headEnd type="triangle" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>511628</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>500744</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>87087</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="69" name="直線矢印コネクタ 68">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{186E3BD5-8E8D-4096-91E1-BEC9C1EF0378}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="14" idx="3"/>
+          <a:endCxn id="50" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="8882742" y="6226630"/>
+          <a:ext cx="1338945" cy="315686"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="7030A0"/>
+          </a:solidFill>
+          <a:headEnd type="triangle" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>365759</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>32657</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>217715</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>195942</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="72" name="正方形/長方形 71">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC4D229A-3806-4000-80CD-2035D2E86167}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13918473" y="5802086"/>
+          <a:ext cx="1571899" cy="849085"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>管理者（製作者）の</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>スマートフォン</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>108858</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>365759</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="76" name="直線矢印コネクタ 75">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AA6D569-0BE2-482A-A035-D17281065804}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="72" idx="1"/>
+          <a:endCxn id="50" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="12964887" y="6226629"/>
+          <a:ext cx="888272" cy="1"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:srgbClr val="7030A0"/>
+          </a:solidFill>
+          <a:headEnd type="triangle" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>365759</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>130629</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>217715</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>65314</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="91" name="正方形/長方形 90">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99B7B97F-E0D6-43A3-975F-0B602D86AB23}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13918473" y="4071258"/>
+          <a:ext cx="1571899" cy="849085"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Github</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t> Action</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>CI/CD</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>継続的デプロイ</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="BIZ UDゴシック" panose="020B0400000000000000" pitchFamily="49" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>97972</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>365759</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>97972</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="92" name="直線矢印コネクタ 91">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E652EB8F-62D2-4D9F-9CBE-FECA94A30D91}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="91" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="13237029" y="4495801"/>
+          <a:ext cx="681444" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>370116</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>108857</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>21772</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>108857</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="96" name="直線矢印コネクタ 95">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5968607C-CE53-48CB-9011-E089F6A08488}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1992087" y="337457"/>
+          <a:ext cx="326571" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -12118,6 +12904,120 @@
         <a:ln w="28575">
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>381002</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>97971</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>32658</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>97971</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="98" name="直線矢印コネクタ 97">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBCA1BCE-7242-4966-B074-6C0357D7CBBF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2002973" y="566057"/>
+          <a:ext cx="326571" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="7030A0"/>
+          </a:solidFill>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>391886</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>97971</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>43542</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>97971</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="100" name="直線矢印コネクタ 99">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF8A53E2-5FAB-461B-9B72-CEE5F688A367}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2013857" y="805542"/>
+          <a:ext cx="326571" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
           </a:solidFill>
           <a:headEnd type="none" w="med" len="med"/>
           <a:tailEnd type="triangle" w="med" len="med"/>
@@ -15922,18 +16822,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6672014-33B5-48C4-9202-55E4E667EEEF}">
-  <dimension ref="C5:W32"/>
+  <dimension ref="A1:W32"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
+    <col min="1" max="1" width="3.796875" customWidth="1"/>
     <col min="2" max="3" width="8.69921875" customWidth="1"/>
+    <col min="20" max="21" width="2.796875" customWidth="1"/>
+    <col min="22" max="23" width="4.09765625" customWidth="1"/>
+    <col min="24" max="24" width="4.796875" customWidth="1"/>
+    <col min="25" max="25" width="8.796875" customWidth="1"/>
     <col min="27" max="27" width="4.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:23" ht="18.600000000000001" thickBot="1">
+    <row r="1" spans="1:23">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="19.2">
+      <c r="A2" s="108"/>
+      <c r="B2" s="107" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="19.2">
+      <c r="A3" s="107"/>
+      <c r="B3" s="107" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="19.2">
+      <c r="A4" s="107"/>
+      <c r="B4" s="107" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="18.600000000000001" thickBot="1">
       <c r="V5" s="67"/>
       <c r="W5" s="67"/>
     </row>
-    <row r="6" spans="3:23">
+    <row r="6" spans="1:23">
       <c r="C6" s="95"/>
       <c r="D6" s="96"/>
       <c r="E6" s="96"/>
@@ -15955,22 +16883,22 @@
       <c r="U6" s="96"/>
       <c r="W6" s="97"/>
     </row>
-    <row r="7" spans="3:23">
+    <row r="7" spans="1:23">
       <c r="C7" s="64"/>
       <c r="W7" s="65"/>
     </row>
-    <row r="8" spans="3:23">
+    <row r="8" spans="1:23">
       <c r="C8" s="64"/>
       <c r="W8" s="65"/>
     </row>
-    <row r="9" spans="3:23" ht="18.600000000000001" thickBot="1">
+    <row r="9" spans="1:23" ht="18.600000000000001" thickBot="1">
       <c r="C9" s="64"/>
       <c r="L9" t="s">
         <v>1706</v>
       </c>
       <c r="W9" s="65"/>
     </row>
-    <row r="10" spans="3:23">
+    <row r="10" spans="1:23">
       <c r="C10" s="64"/>
       <c r="D10" s="95"/>
       <c r="E10" s="96"/>
@@ -15993,37 +16921,37 @@
       <c r="V10" s="97"/>
       <c r="W10" s="65"/>
     </row>
-    <row r="11" spans="3:23">
+    <row r="11" spans="1:23">
       <c r="C11" s="64"/>
       <c r="D11" s="64"/>
       <c r="V11" s="65"/>
       <c r="W11" s="65"/>
     </row>
-    <row r="12" spans="3:23">
+    <row r="12" spans="1:23">
       <c r="C12" s="64"/>
       <c r="D12" s="64"/>
       <c r="V12" s="65"/>
       <c r="W12" s="65"/>
     </row>
-    <row r="13" spans="3:23">
+    <row r="13" spans="1:23">
       <c r="C13" s="64"/>
       <c r="D13" s="64"/>
       <c r="V13" s="65"/>
       <c r="W13" s="65"/>
     </row>
-    <row r="14" spans="3:23">
+    <row r="14" spans="1:23">
       <c r="C14" s="64"/>
       <c r="D14" s="64"/>
       <c r="V14" s="65"/>
       <c r="W14" s="65"/>
     </row>
-    <row r="15" spans="3:23">
+    <row r="15" spans="1:23">
       <c r="C15" s="64"/>
       <c r="D15" s="64"/>
       <c r="V15" s="65"/>
       <c r="W15" s="65"/>
     </row>
-    <row r="16" spans="3:23">
+    <row r="16" spans="1:23">
       <c r="C16" s="64"/>
       <c r="D16" s="64"/>
       <c r="V16" s="65"/>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B485CA79-858E-44C7-BA17-B9F94FB3517F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8956C0-FFE4-4DBF-B0C5-582B479E961F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="3" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="architecture" sheetId="12" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4138" uniqueCount="1950">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4172" uniqueCount="1983">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -7479,40 +7479,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Green</t>
-  </si>
-  <si>
-    <t>Findy</t>
-  </si>
-  <si>
-    <t>paiza</t>
-  </si>
-  <si>
-    <t>Wantedly</t>
-  </si>
-  <si>
-    <t>あたりから</t>
-  </si>
-  <si>
-    <t>言語</t>
-  </si>
-  <si>
-    <t>単価</t>
-  </si>
-  <si>
-    <t>リモート率</t>
-  </si>
-  <si>
-    <t>必須スキル</t>
-  </si>
-  <si>
-    <t>を集めて分析。</t>
-  </si>
-  <si>
-    <t>Forkwell</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>今日の○○案件数</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -7647,9 +7613,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Ver1</t>
-  </si>
-  <si>
     <t>完全無料。</t>
   </si>
   <si>
@@ -7662,14 +7625,6 @@
     <t>自分が毎日使う。</t>
   </si>
   <si>
-    <t>Ver2</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Xとかで</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>Go +8件</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -7679,9 +7634,6 @@
   </si>
   <si>
     <t>平均単価72万</t>
-  </si>
-  <si>
-    <t>Ver3</t>
   </si>
   <si>
     <t>例えば</t>
@@ -8528,6 +8480,180 @@
   </si>
   <si>
     <t>インフラ・接続関係</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>まず最優先。案件数が多い</t>
+  </si>
+  <si>
+    <t>フリジョブ — 複数の案件サイト・エージェントの公開案件を横断検索</t>
+  </si>
+  <si>
+    <t>フリーランスフリー — 1,000件以上のIT案件</t>
+  </si>
+  <si>
+    <t>さらに候補</t>
+  </si>
+  <si>
+    <t>レバテックフリーランス</t>
+  </si>
+  <si>
+    <t>Midworks</t>
+  </si>
+  <si>
+    <t>TechStock</t>
+  </si>
+  <si>
+    <t>PE-BANK</t>
+  </si>
+  <si>
+    <t>ギークスジョブ</t>
+  </si>
+  <si>
+    <t>テックリーチ</t>
+  </si>
+  <si>
+    <t>Findy Freelance</t>
+  </si>
+  <si>
+    <t>エンジニアファクトリー</t>
+  </si>
+  <si>
+    <t>フォスターフリーランス</t>
+  </si>
+  <si>
+    <t>フリーランススタート</t>
+  </si>
+  <si>
+    <t>テクフリ</t>
+  </si>
+  <si>
+    <t>doocyJob</t>
+  </si>
+  <si>
+    <t>案件ナビ</t>
+  </si>
+  <si>
+    <t>エンジニアスタイル東京</t>
+  </si>
+  <si>
+    <t>テックビズフリーランス</t>
+  </si>
+  <si>
+    <t>ポテパンフリーランス</t>
+  </si>
+  <si>
+    <t>PE-BANK案件検索</t>
+  </si>
+  <si>
+    <t>TechSpace — 会員登録なしで案件閲覧可能。エンド直・元請直案件も検索対象</t>
+  </si>
+  <si>
+    <t>ENGER — 公開案件は多数。ただし案件詳細の閲覧には登録が必要なものあり</t>
+  </si>
+  <si>
+    <t>フリーランスHub — 37万件超。Java、C#/.NET、Go、TypeScriptなどで大量検索可能</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クローラー対象</t>
+    <rPh sb="5" eb="7">
+      <t>タイショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Xとかで発信</t>
+    <rPh sb="4" eb="6">
+      <t>ハッシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>DB</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>step1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>step2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>step3</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>job_id</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>jobs</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>job_skills</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>テーブル名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>job_title</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SES JOB LINK — 4.4万件超。SES/業務委託案件を大量に見られる</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>エイジレスフリーランス — 6,800件前後。年齢不問を掲げるIT案件サイト</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>案件テーブル</t>
+  </si>
+  <si>
+    <t>案件スキルテーブル</t>
+  </si>
+  <si>
+    <t>スキルマスタ</t>
+  </si>
+  <si>
+    <t>スキルコード体系</t>
+  </si>
+  <si>
+    <t>文言からのスキル抽出</t>
+  </si>
+  <si>
+    <t>同義語・表記揺れ</t>
+  </si>
+  <si>
+    <t>案件の重複排除</t>
+  </si>
+  <si>
+    <t>掲載元ごとの差異</t>
+  </si>
+  <si>
+    <t>差分クロール</t>
+  </si>
+  <si>
+    <t>文言から抜き取るワード集</t>
+  </si>
+  <si>
+    <t>何の準備がいる？</t>
+    <rPh sb="0" eb="1">
+      <t>ナン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジュンビ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -8656,7 +8782,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8696,6 +8822,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -8974,7 +9106,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -9152,6 +9284,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -16842,19 +16975,19 @@
     <row r="2" spans="1:23" ht="19.2">
       <c r="A2" s="108"/>
       <c r="B2" s="107" t="s">
-        <v>1947</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="19.2">
       <c r="A3" s="107"/>
       <c r="B3" s="107" t="s">
-        <v>1948</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="19.2">
       <c r="A4" s="107"/>
       <c r="B4" s="107" t="s">
-        <v>1949</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="18.600000000000001" thickBot="1">
@@ -17096,7 +17229,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC349EE6-5475-4F9C-BD43-5DC02797CE07}">
-  <dimension ref="A2:Q56"/>
+  <dimension ref="A2:Q92"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="11" style="98" customWidth="1"/>
@@ -17109,350 +17242,525 @@
         <v>1707</v>
       </c>
       <c r="D2" s="98" t="s">
-        <v>1725</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="B3" s="100"/>
     </row>
     <row r="6" spans="1:15">
-      <c r="D6" s="98" t="s">
-        <v>1781</v>
-      </c>
-      <c r="G6" s="98" t="s">
-        <v>1783</v>
-      </c>
-      <c r="M6" s="100" t="s">
-        <v>1708</v>
-      </c>
+      <c r="D6" s="109" t="s">
+        <v>1766</v>
+      </c>
+      <c r="G6" s="109" t="s">
+        <v>1768</v>
+      </c>
+      <c r="M6" s="100"/>
       <c r="O6" s="100" t="s">
-        <v>1751</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="D7" s="98" t="s">
-        <v>1782</v>
-      </c>
-      <c r="M7" s="100" t="s">
-        <v>1709</v>
-      </c>
+        <v>1767</v>
+      </c>
+      <c r="M7" s="100"/>
       <c r="O7" s="100"/>
     </row>
     <row r="8" spans="1:15">
       <c r="G8" s="98" t="s">
-        <v>1734</v>
-      </c>
-      <c r="M8" s="100" t="s">
-        <v>1718</v>
-      </c>
+        <v>1723</v>
+      </c>
+      <c r="M8" s="100"/>
       <c r="O8" s="98" t="s">
-        <v>1752</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="G9" s="99"/>
-      <c r="M9" s="100" t="s">
-        <v>1710</v>
-      </c>
+      <c r="M9" s="100"/>
       <c r="O9" s="98" t="s">
-        <v>1753</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="G10" s="99" t="s">
-        <v>1735</v>
-      </c>
-      <c r="M10" s="100" t="s">
-        <v>1711</v>
-      </c>
+        <v>1724</v>
+      </c>
+      <c r="M10" s="100"/>
       <c r="O10" s="98" t="s">
-        <v>1754</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="G11" s="99" t="s">
-        <v>1736</v>
+        <v>1725</v>
       </c>
       <c r="M11" s="100"/>
       <c r="O11" s="98" t="s">
-        <v>1755</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="G12" s="99" t="s">
-        <v>1737</v>
-      </c>
-      <c r="M12" s="100" t="s">
-        <v>1712</v>
-      </c>
+        <v>1726</v>
+      </c>
+      <c r="M12" s="100"/>
     </row>
     <row r="13" spans="1:15">
       <c r="G13" s="99" t="s">
-        <v>1738</v>
+        <v>1727</v>
       </c>
       <c r="M13" s="100"/>
       <c r="O13" s="98" t="s">
-        <v>1756</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="14" spans="1:15">
-      <c r="M14" s="100" t="s">
-        <v>1713</v>
-      </c>
+      <c r="M14" s="100"/>
     </row>
     <row r="15" spans="1:15">
       <c r="G15" s="98" t="s">
-        <v>1780</v>
-      </c>
-      <c r="M15" s="100" t="s">
-        <v>1714</v>
-      </c>
+        <v>1765</v>
+      </c>
+      <c r="M15" s="100"/>
       <c r="O15" s="98" t="s">
-        <v>1757</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="16" spans="1:15">
-      <c r="M16" s="100" t="s">
-        <v>1715</v>
-      </c>
+      <c r="M16" s="100"/>
       <c r="O16" s="98" t="s">
-        <v>1758</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="17" spans="2:17">
-      <c r="M17" s="100" t="s">
-        <v>1716</v>
-      </c>
+      <c r="M17" s="100"/>
       <c r="O17" s="98" t="s">
-        <v>1759</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="18" spans="2:17">
       <c r="M18" s="100"/>
       <c r="O18" s="98" t="s">
-        <v>1760</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="19" spans="2:17">
-      <c r="M19" s="100" t="s">
-        <v>1717</v>
-      </c>
+      <c r="M19" s="100"/>
     </row>
     <row r="20" spans="2:17">
       <c r="O20" s="100" t="s">
-        <v>1761</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="22" spans="2:17">
       <c r="O22" s="98" t="s">
-        <v>1768</v>
+        <v>1753</v>
       </c>
       <c r="Q22" s="98" t="s">
-        <v>1778</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="23" spans="2:17">
       <c r="Q23" s="98" t="s">
-        <v>1770</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="24" spans="2:17">
       <c r="O24" s="98" t="s">
-        <v>1762</v>
+        <v>1747</v>
       </c>
       <c r="Q24" s="99"/>
     </row>
     <row r="25" spans="2:17">
       <c r="O25" s="98" t="s">
-        <v>1769</v>
+        <v>1754</v>
       </c>
       <c r="Q25" s="102" t="s">
-        <v>1771</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="26" spans="2:17">
       <c r="O26" s="98" t="s">
-        <v>1763</v>
+        <v>1748</v>
       </c>
       <c r="Q26" s="99" t="s">
-        <v>1772</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="27" spans="2:17">
       <c r="O27" s="99" t="s">
-        <v>1764</v>
+        <v>1749</v>
       </c>
       <c r="Q27" s="99" t="s">
-        <v>1773</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="28" spans="2:17">
       <c r="O28" s="99" t="s">
-        <v>1765</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="29" spans="2:17">
       <c r="B29" s="98" t="s">
-        <v>1746</v>
+        <v>1735</v>
       </c>
       <c r="O29" s="99" t="s">
-        <v>1766</v>
+        <v>1751</v>
       </c>
       <c r="Q29" s="98" t="s">
-        <v>1774</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="30" spans="2:17">
       <c r="O30" s="99" t="s">
-        <v>1767</v>
+        <v>1752</v>
       </c>
       <c r="Q30" s="101" t="s">
-        <v>1784</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="31" spans="2:17">
       <c r="B31" s="98" t="s">
-        <v>1747</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="32" spans="2:17">
       <c r="B32" s="98" t="s">
-        <v>1775</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10">
       <c r="B33" s="98" t="s">
-        <v>1748</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10">
       <c r="B34" s="98" t="s">
-        <v>1749</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10">
       <c r="B35" s="98" t="s">
-        <v>1750</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10">
       <c r="B37" s="98" t="s">
-        <v>1776</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10">
       <c r="B38" s="98" t="s">
-        <v>1777</v>
-      </c>
-      <c r="I38" s="98" t="s">
-        <v>1726</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9">
-      <c r="B40" s="98" t="s">
-        <v>1740</v>
-      </c>
-      <c r="I40" s="98" t="s">
+        <v>1762</v>
+      </c>
+      <c r="J38" s="109" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10">
+      <c r="B40" s="109" t="s">
+        <v>1729</v>
+      </c>
+      <c r="J40" s="98" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10">
+      <c r="B41" s="99"/>
+      <c r="J41" s="98" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10">
+      <c r="B42" s="99" t="s">
+        <v>1730</v>
+      </c>
+      <c r="J42" s="98" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10">
+      <c r="B43" s="99" t="s">
+        <v>1731</v>
+      </c>
+      <c r="J43" s="98" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10">
+      <c r="B44" s="99" t="s">
+        <v>1732</v>
+      </c>
+      <c r="J44" s="98" t="s">
         <v>1719</v>
       </c>
     </row>
-    <row r="41" spans="2:9">
-      <c r="B41" s="99"/>
-      <c r="I41" s="98" t="s">
+    <row r="45" spans="2:10">
+      <c r="B45" s="99" t="s">
+        <v>1733</v>
+      </c>
+      <c r="J45" s="98" t="s">
         <v>1720</v>
       </c>
     </row>
-    <row r="42" spans="2:9">
-      <c r="B42" s="99" t="s">
-        <v>1741</v>
-      </c>
-      <c r="I42" s="98" t="s">
+    <row r="46" spans="2:10">
+      <c r="B46" s="99" t="s">
+        <v>1734</v>
+      </c>
+      <c r="J46" s="98" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10">
+      <c r="B47" s="98" t="s">
+        <v>1764</v>
+      </c>
+      <c r="J47" s="98" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10">
+      <c r="J48" s="98" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10">
+      <c r="J49" s="98" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10">
+      <c r="B50" s="109" t="s">
+        <v>1959</v>
+      </c>
+      <c r="J50" s="98" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10">
+      <c r="B51" s="98" t="s">
+        <v>1935</v>
+      </c>
+      <c r="J51" s="98" t="s">
         <v>1721</v>
       </c>
     </row>
-    <row r="43" spans="2:9">
-      <c r="B43" s="99" t="s">
-        <v>1742</v>
-      </c>
-      <c r="I43" s="98" t="s">
+    <row r="52" spans="2:10">
+      <c r="B52" s="99"/>
+      <c r="J52" s="98" t="s">
         <v>1722</v>
       </c>
     </row>
-    <row r="44" spans="2:9">
-      <c r="B44" s="99" t="s">
-        <v>1743</v>
-      </c>
-      <c r="I44" s="98" t="s">
-        <v>1730</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9">
-      <c r="B45" s="99" t="s">
-        <v>1744</v>
-      </c>
-      <c r="I45" s="98" t="s">
-        <v>1731</v>
-      </c>
-    </row>
-    <row r="46" spans="2:9">
-      <c r="B46" s="99" t="s">
-        <v>1745</v>
-      </c>
-      <c r="I46" s="98" t="s">
-        <v>1723</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9">
-      <c r="B47" s="98" t="s">
-        <v>1779</v>
-      </c>
-      <c r="I47" s="98" t="s">
-        <v>1724</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9">
-      <c r="I48" s="98" t="s">
-        <v>1727</v>
-      </c>
-    </row>
-    <row r="49" spans="2:9">
-      <c r="I49" s="98" t="s">
+    <row r="53" spans="2:10">
+      <c r="B53" s="99" t="s">
+        <v>1958</v>
+      </c>
+      <c r="J53" s="98" t="s">
         <v>1728</v>
       </c>
     </row>
-    <row r="50" spans="2:9">
-      <c r="I50" s="98" t="s">
-        <v>1729</v>
-      </c>
-    </row>
-    <row r="51" spans="2:9">
-      <c r="I51" s="98" t="s">
-        <v>1732</v>
-      </c>
-    </row>
-    <row r="52" spans="2:9">
-      <c r="B52" s="99"/>
-      <c r="I52" s="98" t="s">
-        <v>1733</v>
-      </c>
-    </row>
-    <row r="53" spans="2:9">
-      <c r="B53" s="99"/>
-      <c r="I53" s="98" t="s">
-        <v>1739</v>
-      </c>
-    </row>
-    <row r="54" spans="2:9">
-      <c r="B54" s="99"/>
-      <c r="I54" s="98" t="s">
+    <row r="54" spans="2:10">
+      <c r="B54" s="99" t="s">
+        <v>1970</v>
+      </c>
+      <c r="J54" s="98" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="55" spans="2:9">
-      <c r="B55" s="99"/>
-    </row>
-    <row r="56" spans="2:9">
-      <c r="B56" s="99"/>
+    <row r="55" spans="2:10">
+      <c r="B55" s="99" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10">
+      <c r="B56" s="99" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10">
+      <c r="B57" s="98" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10">
+      <c r="B58" s="98" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10">
+      <c r="B59" s="98" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10">
+      <c r="B61" s="98" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10">
+      <c r="B63" s="98" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10">
+      <c r="B64" s="98" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="98" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="98" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" s="98" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" s="98" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" s="98" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="98" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="98" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" s="98" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" s="98" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="98" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" s="98" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" s="98" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" s="98" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78" s="98" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79" s="98" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="J81" s="109" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="B82" s="109" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" s="98" t="s">
+        <v>1968</v>
+      </c>
+      <c r="B83" s="98" t="s">
+        <v>1966</v>
+      </c>
+      <c r="E83" s="98" t="s">
+        <v>1967</v>
+      </c>
+      <c r="J83" s="98" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="J84" s="98" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="B85" s="98" t="s">
+        <v>1965</v>
+      </c>
+      <c r="E85" s="98" t="s">
+        <v>1965</v>
+      </c>
+      <c r="J85" s="98" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="B86" s="98" t="s">
+        <v>1969</v>
+      </c>
+      <c r="J86" s="98" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="J87" s="98" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="J88" s="98" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="J89" s="98" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="J90" s="98" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
+      <c r="J91" s="98" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="J92" s="98" t="s">
+        <v>1981</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -19504,55 +19812,55 @@
   <sheetData>
     <row r="3" spans="2:10">
       <c r="B3" t="s">
-        <v>1869</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="5" spans="2:10">
       <c r="C5" t="s">
-        <v>1796</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="7" spans="2:10">
       <c r="C7" t="s">
-        <v>1797</v>
+        <v>1782</v>
       </c>
       <c r="E7" t="s">
-        <v>1798</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="8" spans="2:10">
       <c r="C8" t="s">
-        <v>1799</v>
+        <v>1784</v>
       </c>
       <c r="E8" t="s">
-        <v>1800</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="9" spans="2:10">
       <c r="C9" t="s">
-        <v>1801</v>
+        <v>1786</v>
       </c>
       <c r="E9" t="s">
-        <v>1802</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="11" spans="2:10">
       <c r="C11" t="s">
-        <v>1803</v>
+        <v>1788</v>
       </c>
       <c r="E11" t="s">
-        <v>1807</v>
+        <v>1792</v>
       </c>
       <c r="H11" t="s">
-        <v>1812</v>
+        <v>1797</v>
       </c>
       <c r="J11" t="s">
-        <v>1804</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="12" spans="2:10">
       <c r="E12" t="s">
-        <v>1808</v>
+        <v>1793</v>
       </c>
       <c r="J12" t="s">
         <v>1590</v>
@@ -19560,12 +19868,12 @@
     </row>
     <row r="13" spans="2:10">
       <c r="E13" t="s">
-        <v>1809</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="14" spans="2:10">
       <c r="E14" t="s">
-        <v>1810</v>
+        <v>1795</v>
       </c>
       <c r="J14" t="s">
         <v>1596</v>
@@ -19573,10 +19881,10 @@
     </row>
     <row r="15" spans="2:10">
       <c r="E15" t="s">
-        <v>1811</v>
+        <v>1796</v>
       </c>
       <c r="J15" t="s">
-        <v>1805</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="16" spans="2:10">
@@ -19586,7 +19894,7 @@
     </row>
     <row r="17" spans="2:12">
       <c r="L17" t="s">
-        <v>1813</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="18" spans="2:12">
@@ -19596,7 +19904,7 @@
     </row>
     <row r="19" spans="2:12">
       <c r="J19" t="s">
-        <v>1806</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="20" spans="2:12">
@@ -19611,47 +19919,47 @@
     </row>
     <row r="24" spans="2:12">
       <c r="B24" t="s">
-        <v>1822</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="26" spans="2:12">
       <c r="C26" t="s">
-        <v>1814</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="27" spans="2:12">
       <c r="D27" t="s">
-        <v>1815</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="28" spans="2:12">
       <c r="D28" t="s">
-        <v>1816</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="29" spans="2:12">
       <c r="D29" t="s">
-        <v>1817</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="30" spans="2:12">
       <c r="D30" t="s">
-        <v>1818</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="31" spans="2:12">
       <c r="C31" t="s">
-        <v>1819</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="32" spans="2:12">
       <c r="D32" t="s">
-        <v>1820</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="D33" t="s">
-        <v>1870</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19661,36 +19969,36 @@
     </row>
     <row r="37" spans="2:7">
       <c r="D37" t="s">
-        <v>1821</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="39" spans="2:7">
       <c r="B39" t="s">
-        <v>1824</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="40" spans="2:7">
       <c r="C40" t="s">
-        <v>1825</v>
+        <v>1810</v>
       </c>
       <c r="D40" t="s">
-        <v>1827</v>
+        <v>1812</v>
       </c>
       <c r="G40" t="s">
-        <v>1831</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="41" spans="2:7">
       <c r="D41" t="s">
-        <v>1828</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="42" spans="2:7">
       <c r="C42" t="s">
-        <v>1816</v>
+        <v>1801</v>
       </c>
       <c r="D42" t="s">
-        <v>1829</v>
+        <v>1814</v>
       </c>
       <c r="G42" t="s">
         <v>1617</v>
@@ -19698,187 +20006,187 @@
     </row>
     <row r="43" spans="2:7">
       <c r="D43" t="s">
-        <v>1830</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="44" spans="2:7">
       <c r="C44" t="s">
-        <v>1826</v>
+        <v>1811</v>
       </c>
       <c r="G44" t="s">
-        <v>1821</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="47" spans="2:7">
       <c r="B47" t="s">
-        <v>1832</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="49" spans="2:5">
       <c r="C49" t="s">
-        <v>1833</v>
+        <v>1818</v>
       </c>
       <c r="E49" t="s">
-        <v>1838</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="50" spans="2:5">
       <c r="C50" t="s">
-        <v>1834</v>
+        <v>1819</v>
       </c>
       <c r="E50" t="s">
-        <v>1839</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="51" spans="2:5">
       <c r="C51" t="s">
-        <v>1835</v>
+        <v>1820</v>
       </c>
       <c r="E51" t="s">
-        <v>1840</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="52" spans="2:5">
       <c r="C52" t="s">
-        <v>1836</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="53" spans="2:5">
       <c r="C53" t="s">
-        <v>1837</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="56" spans="2:5">
       <c r="B56" t="s">
-        <v>1854</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="58" spans="2:5">
       <c r="C58" t="s">
-        <v>1856</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="60" spans="2:5">
       <c r="B60" t="s">
-        <v>1866</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="62" spans="2:5">
       <c r="D62" t="s">
-        <v>1842</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="63" spans="2:5">
       <c r="D63" t="s">
-        <v>1857</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="64" spans="2:5">
       <c r="D64" t="s">
-        <v>1858</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="65" spans="2:5">
       <c r="D65" t="s">
-        <v>1857</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="66" spans="2:5">
       <c r="D66" t="s">
-        <v>1859</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="67" spans="2:5">
       <c r="D67" t="s">
-        <v>1857</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="68" spans="2:5">
       <c r="D68" t="s">
-        <v>1860</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="69" spans="2:5">
       <c r="D69" t="s">
-        <v>1857</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="70" spans="2:5">
       <c r="D70" t="s">
-        <v>1861</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="71" spans="2:5">
       <c r="D71" t="s">
-        <v>1857</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="72" spans="2:5">
       <c r="D72" t="s">
-        <v>1862</v>
+        <v>1847</v>
       </c>
       <c r="E72" t="s">
-        <v>1867</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="73" spans="2:5">
       <c r="D73" t="s">
-        <v>1863</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="74" spans="2:5">
       <c r="D74" t="s">
-        <v>1855</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="75" spans="2:5">
       <c r="D75" t="s">
-        <v>1857</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="76" spans="2:5">
       <c r="D76" t="s">
-        <v>1864</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="77" spans="2:5">
       <c r="D77" t="s">
-        <v>1857</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="78" spans="2:5">
       <c r="D78" t="s">
-        <v>1865</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="80" spans="2:5">
       <c r="B80" t="s">
-        <v>1841</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="82" spans="2:11">
       <c r="C82" t="s">
-        <v>1842</v>
+        <v>1827</v>
       </c>
       <c r="F82" s="103" t="s">
-        <v>1846</v>
+        <v>1831</v>
       </c>
       <c r="G82" s="103" t="s">
-        <v>1847</v>
+        <v>1832</v>
       </c>
       <c r="H82" s="103" t="s">
-        <v>1848</v>
+        <v>1833</v>
       </c>
       <c r="J82" t="s">
-        <v>1851</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="83" spans="2:11">
       <c r="C83" t="s">
-        <v>1815</v>
+        <v>1800</v>
       </c>
       <c r="F83" s="104" t="s">
-        <v>1849</v>
+        <v>1834</v>
       </c>
       <c r="G83" s="104">
         <v>1440</v>
@@ -19887,15 +20195,15 @@
         <v>180</v>
       </c>
       <c r="J83" t="s">
-        <v>1852</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="84" spans="2:11">
       <c r="C84" t="s">
-        <v>1843</v>
+        <v>1828</v>
       </c>
       <c r="F84" s="104" t="s">
-        <v>1823</v>
+        <v>1808</v>
       </c>
       <c r="G84" s="104">
         <v>30</v>
@@ -19904,15 +20212,15 @@
         <v>10</v>
       </c>
       <c r="J84" t="s">
-        <v>1853</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="85" spans="2:11">
       <c r="C85" t="s">
-        <v>1844</v>
+        <v>1829</v>
       </c>
       <c r="F85" s="104" t="s">
-        <v>1850</v>
+        <v>1835</v>
       </c>
       <c r="G85" s="104">
         <v>5</v>
@@ -19923,12 +20231,12 @@
     </row>
     <row r="86" spans="2:11">
       <c r="C86" t="s">
-        <v>1845</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="88" spans="2:11">
       <c r="B88" t="s">
-        <v>1868</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="89" spans="2:11">
@@ -19939,141 +20247,141 @@
         <v>7</v>
       </c>
       <c r="D90" t="s">
-        <v>1917</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="91" spans="2:11">
       <c r="D91" t="s">
-        <v>1918</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="92" spans="2:11">
       <c r="D92" t="s">
-        <v>1919</v>
+        <v>1904</v>
       </c>
       <c r="K92" t="s">
-        <v>1873</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="93" spans="2:11">
       <c r="D93" t="s">
-        <v>1920</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="94" spans="2:11">
       <c r="D94" t="s">
-        <v>1921</v>
+        <v>1906</v>
       </c>
       <c r="K94" t="s">
-        <v>1901</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="95" spans="2:11">
       <c r="D95" t="s">
-        <v>1922</v>
+        <v>1907</v>
       </c>
       <c r="K95" t="s">
-        <v>1874</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="96" spans="2:11">
       <c r="D96" t="s">
-        <v>1923</v>
+        <v>1908</v>
       </c>
       <c r="K96" t="s">
-        <v>1875</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="97" spans="3:10">
       <c r="D97" t="s">
-        <v>1924</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="99" spans="3:10">
       <c r="D99" t="s">
-        <v>1925</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="100" spans="3:10">
       <c r="D100" t="s">
-        <v>1926</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="101" spans="3:10">
       <c r="D101" t="s">
-        <v>1927</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="102" spans="3:10">
       <c r="D102" t="s">
-        <v>1928</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="103" spans="3:10">
       <c r="D103" t="s">
-        <v>1929</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="104" spans="3:10">
       <c r="D104" t="s">
-        <v>1930</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="105" spans="3:10">
       <c r="D105" t="s">
-        <v>1931</v>
+        <v>1916</v>
       </c>
       <c r="J105" t="s">
-        <v>1894</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="106" spans="3:10">
       <c r="D106" t="s">
-        <v>1932</v>
+        <v>1917</v>
       </c>
       <c r="J106" t="s">
-        <v>1872</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="108" spans="3:10">
       <c r="D108" t="s">
-        <v>1933</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="109" spans="3:10">
       <c r="D109" t="s">
-        <v>1939</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="110" spans="3:10">
       <c r="D110" t="s">
-        <v>1924</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="112" spans="3:10">
       <c r="C112" t="s">
-        <v>1938</v>
+        <v>1923</v>
       </c>
       <c r="D112" t="s">
-        <v>1934</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="113" spans="2:10">
       <c r="D113" t="s">
-        <v>1935</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="115" spans="2:10">
       <c r="C115" t="s">
-        <v>1938</v>
+        <v>1923</v>
       </c>
       <c r="D115" t="s">
-        <v>1936</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="116" spans="2:10">
       <c r="D116" t="s">
-        <v>1937</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="118" spans="2:10">
@@ -20083,191 +20391,191 @@
     </row>
     <row r="119" spans="2:10">
       <c r="B119" t="s">
-        <v>1871</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="120" spans="2:10">
       <c r="D120" t="s">
-        <v>1915</v>
+        <v>1900</v>
       </c>
       <c r="F120" t="s">
-        <v>1916</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="121" spans="2:10">
       <c r="D121" t="s">
-        <v>1895</v>
+        <v>1880</v>
       </c>
       <c r="F121" t="s">
-        <v>1899</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="122" spans="2:10">
       <c r="D122" t="s">
-        <v>1896</v>
+        <v>1881</v>
       </c>
       <c r="F122" t="s">
-        <v>1900</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="123" spans="2:10">
       <c r="D123" s="105" t="s">
-        <v>1897</v>
+        <v>1882</v>
       </c>
       <c r="E123" s="106"/>
       <c r="F123" s="106" t="s">
-        <v>1902</v>
+        <v>1887</v>
       </c>
       <c r="J123" t="s">
-        <v>1946</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="124" spans="2:10">
       <c r="D124" t="s">
-        <v>1898</v>
+        <v>1883</v>
       </c>
       <c r="F124" t="s">
-        <v>1903</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="126" spans="2:10">
       <c r="B126" t="s">
-        <v>1876</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="127" spans="2:10">
       <c r="D127" t="s">
-        <v>1877</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="128" spans="2:10">
       <c r="D128" t="s">
-        <v>1878</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="129" spans="4:4">
       <c r="D129" t="s">
-        <v>1879</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="130" spans="4:4">
       <c r="D130" t="s">
-        <v>1880</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="131" spans="4:4">
       <c r="D131" t="s">
-        <v>1881</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="132" spans="4:4">
       <c r="D132" t="s">
-        <v>1882</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="133" spans="4:4">
       <c r="D133" t="s">
-        <v>1883</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="134" spans="4:4">
       <c r="D134" t="s">
-        <v>1884</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="135" spans="4:4">
       <c r="D135" t="s">
-        <v>1885</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="137" spans="4:4">
       <c r="D137" t="s">
-        <v>1886</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="138" spans="4:4">
       <c r="D138" t="s">
-        <v>1887</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="139" spans="4:4">
       <c r="D139" t="s">
-        <v>1879</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="140" spans="4:4">
       <c r="D140" t="s">
-        <v>1888</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="141" spans="4:4">
       <c r="D141" t="s">
-        <v>1889</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="142" spans="4:4">
       <c r="D142" t="s">
-        <v>1945</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="144" spans="4:4">
       <c r="D144" t="s">
-        <v>1890</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="145" spans="4:10">
       <c r="D145" t="s">
-        <v>1887</v>
+        <v>1872</v>
       </c>
       <c r="G145" t="s">
-        <v>1887</v>
+        <v>1872</v>
       </c>
       <c r="J145" t="s">
-        <v>1887</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="146" spans="4:10">
       <c r="D146" t="s">
-        <v>1879</v>
+        <v>1864</v>
       </c>
       <c r="G146" t="s">
-        <v>1879</v>
+        <v>1864</v>
       </c>
       <c r="J146" t="s">
-        <v>1879</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="147" spans="4:10">
       <c r="D147" t="s">
-        <v>1891</v>
+        <v>1876</v>
       </c>
       <c r="G147" t="s">
-        <v>1941</v>
+        <v>1926</v>
       </c>
       <c r="J147" t="s">
-        <v>1941</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="148" spans="4:10">
       <c r="D148" t="s">
-        <v>1892</v>
+        <v>1877</v>
       </c>
       <c r="G148" t="s">
-        <v>1944</v>
+        <v>1929</v>
       </c>
       <c r="J148" t="s">
-        <v>1940</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="149" spans="4:10">
       <c r="D149" t="s">
-        <v>1943</v>
+        <v>1928</v>
       </c>
       <c r="G149" t="s">
-        <v>1893</v>
+        <v>1878</v>
       </c>
       <c r="J149" t="s">
-        <v>1942</v>
+        <v>1927</v>
       </c>
     </row>
   </sheetData>
@@ -20486,7 +20794,7 @@
     </row>
     <row r="5" spans="2:11">
       <c r="B5" s="43" t="s">
-        <v>1785</v>
+        <v>1770</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>128</v>
@@ -20511,7 +20819,7 @@
     </row>
     <row r="6" spans="2:11">
       <c r="B6" s="43" t="s">
-        <v>1785</v>
+        <v>1770</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>150</v>
@@ -20537,7 +20845,7 @@
     </row>
     <row r="7" spans="2:11">
       <c r="B7" s="43" t="s">
-        <v>1785</v>
+        <v>1770</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>34</v>
@@ -20563,7 +20871,7 @@
     </row>
     <row r="8" spans="2:11">
       <c r="B8" s="43" t="s">
-        <v>1785</v>
+        <v>1770</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>151</v>
@@ -20589,7 +20897,7 @@
     </row>
     <row r="9" spans="2:11">
       <c r="B9" s="43" t="s">
-        <v>1785</v>
+        <v>1770</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>35</v>
@@ -20615,7 +20923,7 @@
     </row>
     <row r="10" spans="2:11">
       <c r="B10" s="43" t="s">
-        <v>1785</v>
+        <v>1770</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>36</v>
@@ -20641,7 +20949,7 @@
     </row>
     <row r="11" spans="2:11">
       <c r="B11" s="43" t="s">
-        <v>1785</v>
+        <v>1770</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>37</v>
@@ -20694,7 +21002,7 @@
     </row>
     <row r="13" spans="2:11">
       <c r="B13" s="43" t="s">
-        <v>1786</v>
+        <v>1771</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>128</v>
@@ -20722,7 +21030,7 @@
     </row>
     <row r="14" spans="2:11">
       <c r="B14" s="43" t="s">
-        <v>1786</v>
+        <v>1771</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>58</v>
@@ -20751,7 +21059,7 @@
     </row>
     <row r="15" spans="2:11">
       <c r="B15" s="43" t="s">
-        <v>1786</v>
+        <v>1771</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>77</v>
@@ -20780,7 +21088,7 @@
     </row>
     <row r="16" spans="2:11">
       <c r="B16" s="43" t="s">
-        <v>1786</v>
+        <v>1771</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>59</v>
@@ -20809,7 +21117,7 @@
     </row>
     <row r="17" spans="2:11">
       <c r="B17" s="43" t="s">
-        <v>1786</v>
+        <v>1771</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>63</v>
@@ -20838,7 +21146,7 @@
     </row>
     <row r="18" spans="2:11">
       <c r="B18" s="43" t="s">
-        <v>1786</v>
+        <v>1771</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>147</v>
@@ -20867,7 +21175,7 @@
     </row>
     <row r="19" spans="2:11">
       <c r="B19" s="43" t="s">
-        <v>1786</v>
+        <v>1771</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>148</v>
@@ -20896,7 +21204,7 @@
     </row>
     <row r="20" spans="2:11">
       <c r="B20" s="43" t="s">
-        <v>1786</v>
+        <v>1771</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>1116</v>
@@ -20925,7 +21233,7 @@
     </row>
     <row r="21" spans="2:11">
       <c r="B21" s="43" t="s">
-        <v>1786</v>
+        <v>1771</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>1115</v>
@@ -20954,7 +21262,7 @@
     </row>
     <row r="22" spans="2:11">
       <c r="B22" s="43" t="s">
-        <v>1786</v>
+        <v>1771</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>1114</v>
@@ -21010,7 +21318,7 @@
     </row>
     <row r="24" spans="2:11">
       <c r="B24" s="43" t="s">
-        <v>1788</v>
+        <v>1773</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>127</v>
@@ -21035,7 +21343,7 @@
     </row>
     <row r="25" spans="2:11">
       <c r="B25" s="43" t="s">
-        <v>1788</v>
+        <v>1773</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>27</v>
@@ -21061,7 +21369,7 @@
     </row>
     <row r="26" spans="2:11">
       <c r="B26" s="43" t="s">
-        <v>1788</v>
+        <v>1773</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>32</v>
@@ -21087,7 +21395,7 @@
     </row>
     <row r="27" spans="2:11">
       <c r="B27" s="43" t="s">
-        <v>1788</v>
+        <v>1773</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>112</v>
@@ -21113,7 +21421,7 @@
     </row>
     <row r="28" spans="2:11">
       <c r="B28" s="43" t="s">
-        <v>1788</v>
+        <v>1773</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>111</v>
@@ -21139,7 +21447,7 @@
     </row>
     <row r="29" spans="2:11">
       <c r="B29" s="43" t="s">
-        <v>1788</v>
+        <v>1773</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>110</v>
@@ -21165,7 +21473,7 @@
     </row>
     <row r="30" spans="2:11">
       <c r="B30" s="43" t="s">
-        <v>1788</v>
+        <v>1773</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>73</v>
@@ -21191,7 +21499,7 @@
     </row>
     <row r="31" spans="2:11">
       <c r="B31" s="43" t="s">
-        <v>1788</v>
+        <v>1773</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>71</v>
@@ -21217,7 +21525,7 @@
     </row>
     <row r="32" spans="2:11">
       <c r="B32" s="43" t="s">
-        <v>1788</v>
+        <v>1773</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>113</v>
@@ -21270,7 +21578,7 @@
     </row>
     <row r="34" spans="2:11">
       <c r="B34" s="43" t="s">
-        <v>1787</v>
+        <v>1772</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>127</v>
@@ -21297,7 +21605,7 @@
     </row>
     <row r="35" spans="2:11">
       <c r="B35" s="43" t="s">
-        <v>1787</v>
+        <v>1772</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>90</v>
@@ -21325,7 +21633,7 @@
     </row>
     <row r="36" spans="2:11">
       <c r="B36" s="43" t="s">
-        <v>1787</v>
+        <v>1772</v>
       </c>
       <c r="C36" s="13" t="s">
         <v>91</v>
@@ -21353,7 +21661,7 @@
     </row>
     <row r="37" spans="2:11">
       <c r="B37" s="43" t="s">
-        <v>1787</v>
+        <v>1772</v>
       </c>
       <c r="C37" s="13" t="s">
         <v>89</v>
@@ -21381,7 +21689,7 @@
     </row>
     <row r="38" spans="2:11">
       <c r="B38" s="43" t="s">
-        <v>1787</v>
+        <v>1772</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>140</v>
@@ -21409,7 +21717,7 @@
     </row>
     <row r="39" spans="2:11">
       <c r="B39" s="43" t="s">
-        <v>1787</v>
+        <v>1772</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>145</v>
@@ -21437,7 +21745,7 @@
     </row>
     <row r="40" spans="2:11">
       <c r="B40" s="43" t="s">
-        <v>1787</v>
+        <v>1772</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>69</v>
@@ -21465,7 +21773,7 @@
     </row>
     <row r="41" spans="2:11">
       <c r="B41" s="43" t="s">
-        <v>1787</v>
+        <v>1772</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>57</v>
@@ -21493,7 +21801,7 @@
     </row>
     <row r="42" spans="2:11">
       <c r="B42" s="43" t="s">
-        <v>1787</v>
+        <v>1772</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>86</v>
@@ -21548,7 +21856,7 @@
     </row>
     <row r="44" spans="2:11">
       <c r="B44" s="43" t="s">
-        <v>1789</v>
+        <v>1774</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>117</v>
@@ -21573,7 +21881,7 @@
     </row>
     <row r="45" spans="2:11">
       <c r="B45" s="43" t="s">
-        <v>1789</v>
+        <v>1774</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>118</v>
@@ -21599,7 +21907,7 @@
     </row>
     <row r="46" spans="2:11">
       <c r="B46" s="43" t="s">
-        <v>1789</v>
+        <v>1774</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>119</v>
@@ -21652,7 +21960,7 @@
     </row>
     <row r="48" spans="2:11">
       <c r="B48" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>195</v>
@@ -21677,7 +21985,7 @@
     </row>
     <row r="49" spans="2:11">
       <c r="B49" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C49" s="9" t="s">
         <v>163</v>
@@ -21703,7 +22011,7 @@
     </row>
     <row r="50" spans="2:11">
       <c r="B50" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C50" s="9" t="s">
         <v>164</v>
@@ -21729,7 +22037,7 @@
     </row>
     <row r="51" spans="2:11">
       <c r="B51" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C51" s="9" t="s">
         <v>99</v>
@@ -21755,7 +22063,7 @@
     </row>
     <row r="52" spans="2:11">
       <c r="B52" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C52" s="9" t="s">
         <v>191</v>
@@ -21781,7 +22089,7 @@
     </row>
     <row r="53" spans="2:11">
       <c r="B53" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C53" s="9" t="s">
         <v>165</v>
@@ -21807,7 +22115,7 @@
     </row>
     <row r="54" spans="2:11">
       <c r="B54" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C54" s="9" t="s">
         <v>194</v>
@@ -21833,7 +22141,7 @@
     </row>
     <row r="55" spans="2:11">
       <c r="B55" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C55" s="9" t="s">
         <v>100</v>
@@ -21859,7 +22167,7 @@
     </row>
     <row r="56" spans="2:11">
       <c r="B56" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C56" s="9" t="s">
         <v>192</v>
@@ -21885,7 +22193,7 @@
     </row>
     <row r="57" spans="2:11">
       <c r="B57" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C57" s="9" t="s">
         <v>166</v>
@@ -21911,7 +22219,7 @@
     </row>
     <row r="58" spans="2:11">
       <c r="B58" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C58" s="9" t="s">
         <v>167</v>
@@ -21937,7 +22245,7 @@
     </row>
     <row r="59" spans="2:11">
       <c r="B59" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C59" s="9" t="s">
         <v>168</v>
@@ -21963,7 +22271,7 @@
     </row>
     <row r="60" spans="2:11">
       <c r="B60" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C60" s="9" t="s">
         <v>169</v>
@@ -21989,7 +22297,7 @@
     </row>
     <row r="61" spans="2:11">
       <c r="B61" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C61" s="9" t="s">
         <v>171</v>
@@ -22015,7 +22323,7 @@
     </row>
     <row r="62" spans="2:11">
       <c r="B62" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C62" s="9" t="s">
         <v>193</v>
@@ -22041,7 +22349,7 @@
     </row>
     <row r="63" spans="2:11">
       <c r="B63" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C63" s="9" t="s">
         <v>185</v>
@@ -22067,7 +22375,7 @@
     </row>
     <row r="64" spans="2:11">
       <c r="B64" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>267</v>
@@ -22092,7 +22400,7 @@
     </row>
     <row r="65" spans="2:11">
       <c r="B65" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>271</v>
@@ -22117,7 +22425,7 @@
     </row>
     <row r="66" spans="2:11">
       <c r="B66" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>235</v>
@@ -22142,7 +22450,7 @@
     </row>
     <row r="67" spans="2:11">
       <c r="B67" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>196</v>
@@ -22167,7 +22475,7 @@
     </row>
     <row r="68" spans="2:11">
       <c r="B68" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>239</v>
@@ -22192,7 +22500,7 @@
     </row>
     <row r="69" spans="2:11">
       <c r="B69" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>197</v>
@@ -22217,7 +22525,7 @@
     </row>
     <row r="70" spans="2:11">
       <c r="B70" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>280</v>
@@ -22242,7 +22550,7 @@
     </row>
     <row r="71" spans="2:11">
       <c r="B71" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>242</v>
@@ -22267,7 +22575,7 @@
     </row>
     <row r="72" spans="2:11">
       <c r="B72" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C72" s="8" t="s">
         <v>244</v>
@@ -22292,7 +22600,7 @@
     </row>
     <row r="73" spans="2:11">
       <c r="B73" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>246</v>
@@ -22317,7 +22625,7 @@
     </row>
     <row r="74" spans="2:11">
       <c r="B74" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C74" s="8" t="s">
         <v>248</v>
@@ -22342,7 +22650,7 @@
     </row>
     <row r="75" spans="2:11">
       <c r="B75" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>250</v>
@@ -22367,7 +22675,7 @@
     </row>
     <row r="76" spans="2:11">
       <c r="B76" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C76" s="8" t="s">
         <v>253</v>
@@ -22392,7 +22700,7 @@
     </row>
     <row r="77" spans="2:11">
       <c r="B77" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>199</v>
@@ -22417,7 +22725,7 @@
     </row>
     <row r="78" spans="2:11">
       <c r="B78" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>201</v>
@@ -22442,7 +22750,7 @@
     </row>
     <row r="79" spans="2:11">
       <c r="B79" s="43" t="s">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>285</v>
@@ -22493,7 +22801,7 @@
     </row>
     <row r="81" spans="2:11">
       <c r="B81" s="43" t="s">
-        <v>1791</v>
+        <v>1776</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>336</v>
@@ -22519,7 +22827,7 @@
     </row>
     <row r="82" spans="2:11">
       <c r="B82" s="43" t="s">
-        <v>1791</v>
+        <v>1776</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>338</v>
@@ -22545,7 +22853,7 @@
     </row>
     <row r="83" spans="2:11">
       <c r="B83" s="43" t="s">
-        <v>1791</v>
+        <v>1776</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>339</v>
@@ -22571,7 +22879,7 @@
     </row>
     <row r="84" spans="2:11">
       <c r="B84" s="43" t="s">
-        <v>1791</v>
+        <v>1776</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>337</v>
@@ -22597,7 +22905,7 @@
     </row>
     <row r="85" spans="2:11">
       <c r="B85" s="43" t="s">
-        <v>1791</v>
+        <v>1776</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>340</v>
@@ -22623,7 +22931,7 @@
     </row>
     <row r="86" spans="2:11">
       <c r="B86" s="43" t="s">
-        <v>1791</v>
+        <v>1776</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>341</v>
@@ -22649,7 +22957,7 @@
     </row>
     <row r="87" spans="2:11">
       <c r="B87" s="43" t="s">
-        <v>1791</v>
+        <v>1776</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>342</v>
@@ -22701,7 +23009,7 @@
     </row>
     <row r="89" spans="2:11">
       <c r="B89" s="43" t="s">
-        <v>1792</v>
+        <v>1777</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>1110</v>
@@ -22725,7 +23033,7 @@
     </row>
     <row r="90" spans="2:11">
       <c r="B90" s="43" t="s">
-        <v>1792</v>
+        <v>1777</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>1100</v>
@@ -22749,7 +23057,7 @@
     </row>
     <row r="91" spans="2:11">
       <c r="B91" s="43" t="s">
-        <v>1792</v>
+        <v>1777</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>1111</v>
@@ -22799,7 +23107,7 @@
     </row>
     <row r="93" spans="2:11">
       <c r="B93" s="8" t="s">
-        <v>1793</v>
+        <v>1778</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>1174</v>
@@ -22825,7 +23133,7 @@
     </row>
     <row r="94" spans="2:11">
       <c r="B94" s="8" t="s">
-        <v>1793</v>
+        <v>1778</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>1281</v>
@@ -22851,7 +23159,7 @@
     </row>
     <row r="95" spans="2:11">
       <c r="B95" s="8" t="s">
-        <v>1793</v>
+        <v>1778</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>1188</v>
@@ -22877,7 +23185,7 @@
     </row>
     <row r="96" spans="2:11">
       <c r="B96" s="8" t="s">
-        <v>1793</v>
+        <v>1778</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>1540</v>
@@ -22906,7 +23214,7 @@
     </row>
     <row r="97" spans="2:11">
       <c r="B97" s="8" t="s">
-        <v>1793</v>
+        <v>1778</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>1290</v>
@@ -22932,7 +23240,7 @@
     </row>
     <row r="98" spans="2:11">
       <c r="B98" s="8" t="s">
-        <v>1793</v>
+        <v>1778</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>1538</v>
@@ -22958,7 +23266,7 @@
     </row>
     <row r="99" spans="2:11">
       <c r="B99" s="8" t="s">
-        <v>1793</v>
+        <v>1778</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>1543</v>
@@ -22984,7 +23292,7 @@
     </row>
     <row r="100" spans="2:11">
       <c r="B100" s="8" t="s">
-        <v>1793</v>
+        <v>1778</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>1544</v>
@@ -23010,7 +23318,7 @@
     </row>
     <row r="101" spans="2:11">
       <c r="B101" s="8" t="s">
-        <v>1793</v>
+        <v>1778</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>1545</v>
@@ -23036,7 +23344,7 @@
     </row>
     <row r="102" spans="2:11">
       <c r="B102" s="8" t="s">
-        <v>1793</v>
+        <v>1778</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>1546</v>
@@ -23062,7 +23370,7 @@
     </row>
     <row r="103" spans="2:11">
       <c r="B103" s="8" t="s">
-        <v>1793</v>
+        <v>1778</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>1570</v>
@@ -23088,7 +23396,7 @@
     </row>
     <row r="104" spans="2:11">
       <c r="B104" s="8" t="s">
-        <v>1793</v>
+        <v>1778</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>1547</v>
@@ -23140,7 +23448,7 @@
     </row>
     <row r="106" spans="2:11">
       <c r="B106" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>1425</v>
@@ -23168,7 +23476,7 @@
     </row>
     <row r="107" spans="2:11">
       <c r="B107" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C107" s="8" t="s">
         <v>1426</v>
@@ -23196,7 +23504,7 @@
     </row>
     <row r="108" spans="2:11">
       <c r="B108" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>1427</v>
@@ -23224,7 +23532,7 @@
     </row>
     <row r="109" spans="2:11">
       <c r="B109" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>1428</v>
@@ -23252,7 +23560,7 @@
     </row>
     <row r="110" spans="2:11">
       <c r="B110" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C110" s="8" t="s">
         <v>1429</v>
@@ -23280,7 +23588,7 @@
     </row>
     <row r="111" spans="2:11">
       <c r="B111" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C111" s="8" t="s">
         <v>1389</v>
@@ -23308,7 +23616,7 @@
     </row>
     <row r="112" spans="2:11">
       <c r="B112" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>1430</v>
@@ -23336,7 +23644,7 @@
     </row>
     <row r="113" spans="2:11">
       <c r="B113" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C113" s="8" t="s">
         <v>1390</v>
@@ -23364,7 +23672,7 @@
     </row>
     <row r="114" spans="2:11">
       <c r="B114" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C114" s="8" t="s">
         <v>1431</v>
@@ -23392,7 +23700,7 @@
     </row>
     <row r="115" spans="2:11">
       <c r="B115" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C115" s="8" t="s">
         <v>1397</v>
@@ -23420,7 +23728,7 @@
     </row>
     <row r="116" spans="2:11">
       <c r="B116" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C116" s="8" t="s">
         <v>1432</v>
@@ -23448,7 +23756,7 @@
     </row>
     <row r="117" spans="2:11">
       <c r="B117" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>1391</v>
@@ -23476,7 +23784,7 @@
     </row>
     <row r="118" spans="2:11">
       <c r="B118" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C118" s="8" t="s">
         <v>1392</v>
@@ -23504,7 +23812,7 @@
     </row>
     <row r="119" spans="2:11">
       <c r="B119" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>1393</v>
@@ -23532,7 +23840,7 @@
     </row>
     <row r="120" spans="2:11">
       <c r="B120" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C120" s="8" t="s">
         <v>1402</v>
@@ -23560,7 +23868,7 @@
     </row>
     <row r="121" spans="2:11">
       <c r="B121" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C121" s="8" t="s">
         <v>1398</v>
@@ -23588,7 +23896,7 @@
     </row>
     <row r="122" spans="2:11">
       <c r="B122" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C122" s="8" t="s">
         <v>1399</v>
@@ -23616,7 +23924,7 @@
     </row>
     <row r="123" spans="2:11">
       <c r="B123" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C123" s="8" t="s">
         <v>1433</v>
@@ -23644,7 +23952,7 @@
     </row>
     <row r="124" spans="2:11">
       <c r="B124" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C124" s="8" t="s">
         <v>1434</v>
@@ -23672,7 +23980,7 @@
     </row>
     <row r="125" spans="2:11">
       <c r="B125" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C125" s="8" t="s">
         <v>1394</v>
@@ -23700,7 +24008,7 @@
     </row>
     <row r="126" spans="2:11">
       <c r="B126" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C126" s="8" t="s">
         <v>1435</v>
@@ -23728,7 +24036,7 @@
     </row>
     <row r="127" spans="2:11">
       <c r="B127" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C127" s="8" t="s">
         <v>1400</v>
@@ -23756,7 +24064,7 @@
     </row>
     <row r="128" spans="2:11">
       <c r="B128" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C128" s="8" t="s">
         <v>1395</v>
@@ -23784,7 +24092,7 @@
     </row>
     <row r="129" spans="2:11">
       <c r="B129" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C129" s="8" t="s">
         <v>1396</v>
@@ -23812,7 +24120,7 @@
     </row>
     <row r="130" spans="2:11">
       <c r="B130" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C130" s="8" t="s">
         <v>1436</v>
@@ -23840,7 +24148,7 @@
     </row>
     <row r="131" spans="2:11">
       <c r="B131" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C131" s="8" t="s">
         <v>1401</v>
@@ -23868,7 +24176,7 @@
     </row>
     <row r="132" spans="2:11">
       <c r="B132" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C132" s="8" t="s">
         <v>1403</v>
@@ -23896,7 +24204,7 @@
     </row>
     <row r="133" spans="2:11">
       <c r="B133" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C133" s="8" t="s">
         <v>1404</v>
@@ -23924,7 +24232,7 @@
     </row>
     <row r="134" spans="2:11">
       <c r="B134" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C134" s="8" t="s">
         <v>1405</v>
@@ -23952,7 +24260,7 @@
     </row>
     <row r="135" spans="2:11">
       <c r="B135" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C135" s="8" t="s">
         <v>1406</v>
@@ -23980,7 +24288,7 @@
     </row>
     <row r="136" spans="2:11">
       <c r="B136" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C136" s="8" t="s">
         <v>1407</v>
@@ -24008,7 +24316,7 @@
     </row>
     <row r="137" spans="2:11">
       <c r="B137" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C137" s="8" t="s">
         <v>1437</v>
@@ -24036,7 +24344,7 @@
     </row>
     <row r="138" spans="2:11">
       <c r="B138" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C138" s="8" t="s">
         <v>1558</v>
@@ -24064,7 +24372,7 @@
     </row>
     <row r="139" spans="2:11">
       <c r="B139" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>1562</v>
@@ -24092,7 +24400,7 @@
     </row>
     <row r="140" spans="2:11">
       <c r="B140" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C140" s="8" t="s">
         <v>1564</v>
@@ -24120,7 +24428,7 @@
     </row>
     <row r="141" spans="2:11">
       <c r="B141" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>1566</v>
@@ -24148,7 +24456,7 @@
     </row>
     <row r="142" spans="2:11">
       <c r="B142" s="8" t="s">
-        <v>1794</v>
+        <v>1779</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>1424</v>
@@ -24200,7 +24508,7 @@
     </row>
     <row r="144" spans="2:11">
       <c r="B144" s="8" t="s">
-        <v>1795</v>
+        <v>1780</v>
       </c>
       <c r="C144" s="8" t="s">
         <v>1504</v>
@@ -24226,7 +24534,7 @@
     </row>
     <row r="145" spans="2:11">
       <c r="B145" s="8" t="s">
-        <v>1795</v>
+        <v>1780</v>
       </c>
       <c r="C145" s="8" t="s">
         <v>1518</v>
@@ -24252,7 +24560,7 @@
     </row>
     <row r="146" spans="2:11">
       <c r="B146" s="8" t="s">
-        <v>1795</v>
+        <v>1780</v>
       </c>
       <c r="C146" s="8" t="s">
         <v>1505</v>
@@ -24278,7 +24586,7 @@
     </row>
     <row r="147" spans="2:11">
       <c r="B147" s="8" t="s">
-        <v>1795</v>
+        <v>1780</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>1506</v>
@@ -24304,7 +24612,7 @@
     </row>
     <row r="148" spans="2:11">
       <c r="B148" s="8" t="s">
-        <v>1795</v>
+        <v>1780</v>
       </c>
       <c r="C148" s="8" t="s">
         <v>1507</v>
@@ -24330,7 +24638,7 @@
     </row>
     <row r="149" spans="2:11">
       <c r="B149" s="8" t="s">
-        <v>1795</v>
+        <v>1780</v>
       </c>
       <c r="C149" s="8" t="s">
         <v>1508</v>
@@ -24356,7 +24664,7 @@
     </row>
     <row r="150" spans="2:11">
       <c r="B150" s="8" t="s">
-        <v>1795</v>
+        <v>1780</v>
       </c>
       <c r="C150" s="8" t="s">
         <v>1509</v>
@@ -24382,7 +24690,7 @@
     </row>
     <row r="151" spans="2:11">
       <c r="B151" s="8" t="s">
-        <v>1795</v>
+        <v>1780</v>
       </c>
       <c r="C151" s="8" t="s">
         <v>1510</v>
@@ -24408,7 +24716,7 @@
     </row>
     <row r="152" spans="2:11">
       <c r="B152" s="8" t="s">
-        <v>1795</v>
+        <v>1780</v>
       </c>
       <c r="C152" s="8" t="s">
         <v>1511</v>
@@ -24434,7 +24742,7 @@
     </row>
     <row r="153" spans="2:11">
       <c r="B153" s="8" t="s">
-        <v>1795</v>
+        <v>1780</v>
       </c>
       <c r="C153" s="8" t="s">
         <v>1512</v>
@@ -24460,7 +24768,7 @@
     </row>
     <row r="154" spans="2:11">
       <c r="B154" s="8" t="s">
-        <v>1795</v>
+        <v>1780</v>
       </c>
       <c r="C154" s="8" t="s">
         <v>1513</v>
@@ -24486,7 +24794,7 @@
     </row>
     <row r="155" spans="2:11">
       <c r="B155" s="8" t="s">
-        <v>1795</v>
+        <v>1780</v>
       </c>
       <c r="C155" s="8" t="s">
         <v>1514</v>
@@ -24512,7 +24820,7 @@
     </row>
     <row r="156" spans="2:11">
       <c r="B156" s="8" t="s">
-        <v>1795</v>
+        <v>1780</v>
       </c>
       <c r="C156" s="8" t="s">
         <v>1519</v>
@@ -24538,7 +24846,7 @@
     </row>
     <row r="157" spans="2:11">
       <c r="B157" s="8" t="s">
-        <v>1795</v>
+        <v>1780</v>
       </c>
       <c r="C157" s="8" t="s">
         <v>1515</v>
@@ -24564,7 +24872,7 @@
     </row>
     <row r="158" spans="2:11">
       <c r="B158" s="8" t="s">
-        <v>1795</v>
+        <v>1780</v>
       </c>
       <c r="C158" s="8" t="s">
         <v>1516</v>
@@ -24590,7 +24898,7 @@
     </row>
     <row r="159" spans="2:11">
       <c r="B159" s="8" t="s">
-        <v>1795</v>
+        <v>1780</v>
       </c>
       <c r="C159" s="8" t="s">
         <v>1517</v>
@@ -24616,10 +24924,10 @@
     </row>
     <row r="160" spans="2:11">
       <c r="B160" s="6" t="s">
-        <v>1904</v>
+        <v>1889</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>1905</v>
+        <v>1890</v>
       </c>
       <c r="D160" s="6" t="s">
         <v>1117</v>
@@ -24642,10 +24950,10 @@
     </row>
     <row r="161" spans="2:11">
       <c r="B161" s="8" t="s">
-        <v>1908</v>
+        <v>1893</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>1906</v>
+        <v>1891</v>
       </c>
       <c r="D161" s="8"/>
       <c r="E161" s="8">
@@ -24659,7 +24967,7 @@
         <v>125</v>
       </c>
       <c r="I161" s="8" t="s">
-        <v>1909</v>
+        <v>1894</v>
       </c>
       <c r="K161" s="5" t="str">
         <f t="shared" si="18"/>
@@ -24668,10 +24976,10 @@
     </row>
     <row r="162" spans="2:11">
       <c r="B162" s="8" t="s">
-        <v>1908</v>
+        <v>1893</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>1907</v>
+        <v>1892</v>
       </c>
       <c r="D162" s="8"/>
       <c r="E162" s="8">
@@ -24685,7 +24993,7 @@
         <v>125</v>
       </c>
       <c r="I162" s="8" t="s">
-        <v>1910</v>
+        <v>1895</v>
       </c>
       <c r="K162" s="5" t="str">
         <f t="shared" si="18"/>
@@ -24694,10 +25002,10 @@
     </row>
     <row r="163" spans="2:11">
       <c r="B163" s="8" t="s">
-        <v>1908</v>
+        <v>1893</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>1897</v>
+        <v>1882</v>
       </c>
       <c r="D163" s="8"/>
       <c r="E163" s="8">
@@ -24711,7 +25019,7 @@
         <v>125</v>
       </c>
       <c r="I163" s="8" t="s">
-        <v>1911</v>
+        <v>1896</v>
       </c>
       <c r="K163" s="5" t="str">
         <f t="shared" si="18"/>
@@ -24720,10 +25028,10 @@
     </row>
     <row r="164" spans="2:11">
       <c r="B164" s="8" t="s">
-        <v>1908</v>
+        <v>1893</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>1895</v>
+        <v>1880</v>
       </c>
       <c r="D164" s="8"/>
       <c r="E164" s="8">
@@ -24737,7 +25045,7 @@
         <v>125</v>
       </c>
       <c r="I164" s="8" t="s">
-        <v>1912</v>
+        <v>1897</v>
       </c>
       <c r="K164" s="5" t="str">
         <f t="shared" si="18"/>
@@ -24746,10 +25054,10 @@
     </row>
     <row r="165" spans="2:11">
       <c r="B165" s="8" t="s">
-        <v>1908</v>
+        <v>1893</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>1898</v>
+        <v>1883</v>
       </c>
       <c r="D165" s="8"/>
       <c r="E165" s="8">
@@ -24763,7 +25071,7 @@
         <v>125</v>
       </c>
       <c r="I165" s="8" t="s">
-        <v>1914</v>
+        <v>1899</v>
       </c>
       <c r="K165" s="5" t="str">
         <f t="shared" si="18"/>
@@ -24772,10 +25080,10 @@
     </row>
     <row r="166" spans="2:11">
       <c r="B166" s="8" t="s">
-        <v>1908</v>
+        <v>1893</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>1896</v>
+        <v>1881</v>
       </c>
       <c r="D166" s="8"/>
       <c r="E166" s="8">
@@ -24789,7 +25097,7 @@
         <v>125</v>
       </c>
       <c r="I166" s="8" t="s">
-        <v>1913</v>
+        <v>1898</v>
       </c>
       <c r="K166" s="5" t="str">
         <f t="shared" si="18"/>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8956C0-FFE4-4DBF-B0C5-582B479E961F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC50E2E-20D0-41EE-86C8-92FB0540E3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="3" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="1536" yWindow="1104" windowWidth="21600" windowHeight="11232" tabRatio="778" firstSheet="3" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="architecture" sheetId="12" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4172" uniqueCount="1983">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4208" uniqueCount="2017">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -8605,10 +8605,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>job_title</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>SES JOB LINK — 4.4万件超。SES/業務委託案件を大量に見られる</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -8654,6 +8650,139 @@
     <rPh sb="2" eb="4">
       <t>ジュンビ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>id BIGSERIAL PRIMARY KEY,</t>
+  </si>
+  <si>
+    <t>-- 元案件ページ</t>
+  </si>
+  <si>
+    <t>url TEXT NOT NULL UNIQUE,</t>
+  </si>
+  <si>
+    <t>-- 基本情報</t>
+  </si>
+  <si>
+    <t>title VARCHAR(500) NOT NULL,</t>
+  </si>
+  <si>
+    <t>company_name VARCHAR(255),</t>
+  </si>
+  <si>
+    <t>price_text VARCHAR(255),</t>
+  </si>
+  <si>
+    <t>location VARCHAR(255),</t>
+  </si>
+  <si>
+    <t>-- スキル</t>
+  </si>
+  <si>
+    <t>required_skills_text TEXT,</t>
+  </si>
+  <si>
+    <t>preferred_skills_text TEXT,</t>
+  </si>
+  <si>
+    <t>-- 案件詳細</t>
+  </si>
+  <si>
+    <t>description TEXT,</t>
+  </si>
+  <si>
+    <t>source_site VARCHAR(100), -- Green、Findy、レバテックなど</t>
+  </si>
+  <si>
+    <t>employment_type VARCHAR(100), -- 業務委託、正社員...</t>
+  </si>
+  <si>
+    <t>remote_type VARCHAR(100), -- フルリモート、一部リモート、常駐</t>
+  </si>
+  <si>
+    <t>is_active BOOLEAN -- まだ募集しているか</t>
+  </si>
+  <si>
+    <t>similarity_score DOUBLE -- 案件類似度</t>
+  </si>
+  <si>
+    <t>-- 管理</t>
+  </si>
+  <si>
+    <t>created_at TIMESTAMP NOT NULL DEFAULT CURRENT_TIMESTAMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">updated_at TIMESTAMP </t>
+  </si>
+  <si>
+    <t>同一・類似案件判定</t>
+    <rPh sb="0" eb="2">
+      <t>ドウイツ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ルイジ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>アンケン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>将来案：</t>
+  </si>
+  <si>
+    <t>job_similarity</t>
+  </si>
+  <si>
+    <t>目的：</t>
+  </si>
+  <si>
+    <t>別サイトに掲載された同一求人候補を検出</t>
+  </si>
+  <si>
+    <t>方式案：</t>
+  </si>
+  <si>
+    <t>例：</t>
+  </si>
+  <si>
+    <t>0.70 → 要確認</t>
+  </si>
+  <si>
+    <t>会社名正規化</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>求人タイトル正規化</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>similarity_score保存</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>0.92 → 同一候補</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>文字一致率 / n-gram比較（会社名、求人タイトルを仕様）</t>
+    <rPh sb="17" eb="20">
+      <t>カイシャメイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>キュウジン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>m_skills</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -13687,8 +13816,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7985930" y="1467837"/>
-          <a:ext cx="1820498" cy="1167653"/>
+          <a:off x="7911971" y="1528349"/>
+          <a:ext cx="1800328" cy="1214718"/>
           <a:chOff x="8992083" y="208776"/>
           <a:chExt cx="1814762" cy="1244600"/>
         </a:xfrm>
@@ -13997,8 +14126,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="11283097" y="2938582"/>
-          <a:ext cx="1842700" cy="1889768"/>
+          <a:off x="11175520" y="3059605"/>
+          <a:ext cx="1822530" cy="1963728"/>
           <a:chOff x="8549484" y="3956874"/>
           <a:chExt cx="1810288" cy="1437363"/>
         </a:xfrm>
@@ -14549,8 +14678,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4721439" y="1597449"/>
-          <a:ext cx="1890124" cy="3208246"/>
+          <a:off x="4681098" y="1657961"/>
+          <a:ext cx="1869953" cy="3342717"/>
           <a:chOff x="5970441" y="628674"/>
           <a:chExt cx="1893913" cy="3428095"/>
         </a:xfrm>
@@ -15018,8 +15147,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10941124" y="6969538"/>
-          <a:ext cx="2220201" cy="2422569"/>
+          <a:off x="10840271" y="7258650"/>
+          <a:ext cx="2193307" cy="2523422"/>
           <a:chOff x="12007370" y="5957071"/>
           <a:chExt cx="2223130" cy="2581251"/>
         </a:xfrm>
@@ -15225,8 +15354,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14468704" y="4627977"/>
-          <a:ext cx="2246929" cy="1653108"/>
+          <a:off x="14334233" y="4816236"/>
+          <a:ext cx="2220036" cy="1720343"/>
           <a:chOff x="15050343" y="4729843"/>
           <a:chExt cx="2243515" cy="1763032"/>
         </a:xfrm>
@@ -15655,8 +15784,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6914030" y="5002306"/>
-          <a:ext cx="1795181" cy="1264024"/>
+          <a:off x="6846794" y="5210735"/>
+          <a:ext cx="1781735" cy="1311089"/>
           <a:chOff x="6846794" y="5210735"/>
           <a:chExt cx="2341399" cy="1311089"/>
         </a:xfrm>
@@ -16032,8 +16161,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3760297" y="7340331"/>
-          <a:ext cx="2355242" cy="1808149"/>
+          <a:off x="3726679" y="7642890"/>
+          <a:ext cx="2335072" cy="1882107"/>
           <a:chOff x="3726679" y="7642891"/>
           <a:chExt cx="2335072" cy="1468663"/>
         </a:xfrm>
@@ -16434,9 +16563,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>670687</xdr:colOff>
+      <xdr:colOff>674497</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>145053</xdr:rowOff>
+      <xdr:rowOff>146958</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -16478,9 +16607,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>510643</xdr:colOff>
+      <xdr:colOff>514453</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>68706</xdr:rowOff>
+      <xdr:rowOff>70611</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -16522,9 +16651,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>251605</xdr:colOff>
+      <xdr:colOff>255415</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>15369</xdr:rowOff>
+      <xdr:rowOff>19179</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -16566,7 +16695,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>53428</xdr:colOff>
+      <xdr:colOff>57238</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>170</xdr:rowOff>
     </xdr:to>
@@ -16610,9 +16739,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>617337</xdr:colOff>
+      <xdr:colOff>615432</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>30588</xdr:rowOff>
+      <xdr:rowOff>32493</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -16654,9 +16783,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>586902</xdr:colOff>
+      <xdr:colOff>590712</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>129868</xdr:rowOff>
+      <xdr:rowOff>133678</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -16956,15 +17085,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6672014-33B5-48C4-9202-55E4E667EEEF}">
   <dimension ref="A1:W32"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="3.796875" customWidth="1"/>
-    <col min="2" max="3" width="8.69921875" customWidth="1"/>
-    <col min="20" max="21" width="2.796875" customWidth="1"/>
-    <col min="22" max="23" width="4.09765625" customWidth="1"/>
-    <col min="24" max="24" width="4.796875" customWidth="1"/>
-    <col min="25" max="25" width="8.796875" customWidth="1"/>
-    <col min="27" max="27" width="4.3984375" customWidth="1"/>
+    <col min="1" max="1" width="3.75" customWidth="1"/>
+    <col min="2" max="3" width="8.75" customWidth="1"/>
+    <col min="20" max="21" width="2.75" customWidth="1"/>
+    <col min="22" max="23" width="4.125" customWidth="1"/>
+    <col min="24" max="24" width="4.75" customWidth="1"/>
+    <col min="25" max="25" width="8.75" customWidth="1"/>
+    <col min="27" max="27" width="4.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -16972,25 +17101,25 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="19.2">
+    <row r="2" spans="1:23" ht="20.25">
       <c r="A2" s="108"/>
       <c r="B2" s="107" t="s">
         <v>1932</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="19.2">
+    <row r="3" spans="1:23" ht="20.25">
       <c r="A3" s="107"/>
       <c r="B3" s="107" t="s">
         <v>1933</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="19.2">
+    <row r="4" spans="1:23" ht="20.25">
       <c r="A4" s="107"/>
       <c r="B4" s="107" t="s">
         <v>1934</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="18.600000000000001" thickBot="1">
+    <row r="5" spans="1:23" ht="19.5" thickBot="1">
       <c r="V5" s="67"/>
       <c r="W5" s="67"/>
     </row>
@@ -17024,7 +17153,7 @@
       <c r="C8" s="64"/>
       <c r="W8" s="65"/>
     </row>
-    <row r="9" spans="1:23" ht="18.600000000000001" thickBot="1">
+    <row r="9" spans="1:23" ht="19.5" thickBot="1">
       <c r="C9" s="64"/>
       <c r="L9" t="s">
         <v>1706</v>
@@ -17174,7 +17303,7 @@
       <c r="V30" s="65"/>
       <c r="W30" s="65"/>
     </row>
-    <row r="31" spans="3:23" ht="18.600000000000001" thickBot="1">
+    <row r="31" spans="3:23" ht="19.5" thickBot="1">
       <c r="C31" s="64"/>
       <c r="D31" s="66"/>
       <c r="E31" s="67"/>
@@ -17197,7 +17326,7 @@
       <c r="V31" s="68"/>
       <c r="W31" s="65"/>
     </row>
-    <row r="32" spans="3:23" ht="13.2" customHeight="1" thickBot="1">
+    <row r="32" spans="3:23" ht="13.15" customHeight="1" thickBot="1">
       <c r="C32" s="66"/>
       <c r="D32" s="67"/>
       <c r="E32" s="67"/>
@@ -17229,11 +17358,11 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC349EE6-5475-4F9C-BD43-5DC02797CE07}">
-  <dimension ref="A2:Q92"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="A2:Q131"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11" style="98" customWidth="1"/>
-    <col min="2" max="6" width="10.8984375" style="98" customWidth="1"/>
+    <col min="2" max="6" width="10.875" style="98" customWidth="1"/>
     <col min="7" max="16384" width="9" style="98"/>
   </cols>
   <sheetData>
@@ -17563,7 +17692,7 @@
     </row>
     <row r="54" spans="2:10">
       <c r="B54" s="99" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="J54" s="98" t="s">
         <v>307</v>
@@ -17571,7 +17700,7 @@
     </row>
     <row r="55" spans="2:10">
       <c r="B55" s="99" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="56" spans="2:10">
@@ -17686,7 +17815,7 @@
     </row>
     <row r="81" spans="1:10">
       <c r="J81" s="109" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -17704,62 +17833,226 @@
       <c r="E83" s="98" t="s">
         <v>1967</v>
       </c>
+      <c r="G83" s="98" t="s">
+        <v>2016</v>
+      </c>
       <c r="J83" s="98" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="J84" s="98" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="B85" s="98" t="s">
-        <v>1965</v>
+        <v>1982</v>
       </c>
       <c r="E85" s="98" t="s">
         <v>1965</v>
       </c>
+      <c r="G85" s="98" t="s">
+        <v>155</v>
+      </c>
       <c r="J85" s="98" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="E86" s="98" t="s">
+        <v>155</v>
+      </c>
+      <c r="G86" s="98" t="s">
+        <v>231</v>
+      </c>
+      <c r="J86" s="98" t="s">
         <v>1974</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
-      <c r="B86" s="98" t="s">
-        <v>1969</v>
-      </c>
-      <c r="J86" s="98" t="s">
+    <row r="87" spans="1:10">
+      <c r="B87" s="98" t="s">
+        <v>1983</v>
+      </c>
+      <c r="J87" s="98" t="s">
         <v>1975</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
-      <c r="J87" s="98" t="s">
+    <row r="88" spans="1:10">
+      <c r="B88" s="98" t="s">
+        <v>1984</v>
+      </c>
+      <c r="J88" s="98" t="s">
         <v>1976</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10">
-      <c r="J88" s="98" t="s">
-        <v>1977</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="J89" s="98" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="B90" s="98" t="s">
+        <v>1985</v>
+      </c>
+      <c r="J90" s="98" t="s">
         <v>1978</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
-      <c r="J90" s="98" t="s">
+    <row r="91" spans="1:10">
+      <c r="B91" s="98" t="s">
+        <v>1986</v>
+      </c>
+      <c r="J91" s="98" t="s">
         <v>1979</v>
       </c>
     </row>
-    <row r="91" spans="1:10">
-      <c r="J91" s="98" t="s">
+    <row r="92" spans="1:10">
+      <c r="B92" s="98" t="s">
+        <v>1987</v>
+      </c>
+      <c r="J92" s="98" t="s">
         <v>1980</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
-      <c r="J92" s="98" t="s">
-        <v>1981</v>
+    <row r="93" spans="1:10">
+      <c r="B93" s="98" t="s">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
+      <c r="B94" s="98" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="B96" s="98" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97" s="98" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2">
+      <c r="B98" s="98" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2">
+      <c r="B100" s="98" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2">
+      <c r="B101" s="98" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2">
+      <c r="B103" s="98" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2">
+      <c r="B104" s="98" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2">
+      <c r="B105" s="98" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2">
+      <c r="B107" s="98" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2">
+      <c r="B108" s="98" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2">
+      <c r="B109" s="98" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2">
+      <c r="B110" s="98" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2">
+      <c r="B111" s="98" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="98" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="B117" s="98" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="B118" s="98" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="B120" s="98" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="B121" s="98" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="B123" s="98" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="B124" s="98" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="B125" s="98" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="B126" s="98" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="B127" s="98" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2">
+      <c r="B129" s="98" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2">
+      <c r="B130" s="98" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2">
+      <c r="B131" s="98" t="s">
+        <v>2010</v>
       </c>
     </row>
   </sheetData>
@@ -17772,10 +18065,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F0B575-2DDF-49B9-8DE2-F372EEC2F3B3}">
   <dimension ref="A2:O79"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.8984375" style="1" customWidth="1"/>
-    <col min="2" max="6" width="10.8984375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.875" style="1" customWidth="1"/>
+    <col min="2" max="6" width="10.875" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -17807,7 +18100,7 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="18">
+    <row r="4" spans="1:15" ht="18.75">
       <c r="A4" s="1" t="s">
         <v>1280</v>
       </c>
@@ -17836,7 +18129,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="13.2">
+    <row r="5" spans="1:15">
       <c r="B5" s="58" t="s">
         <v>1175</v>
       </c>
@@ -17853,7 +18146,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="13.2">
+    <row r="6" spans="1:15">
       <c r="B6" s="58" t="s">
         <v>1176</v>
       </c>
@@ -17876,7 +18169,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="13.2">
+    <row r="7" spans="1:15">
       <c r="B7" s="58" t="s">
         <v>1189</v>
       </c>
@@ -17905,7 +18198,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="13.2">
+    <row r="8" spans="1:15">
       <c r="B8" s="58" t="s">
         <v>1177</v>
       </c>
@@ -17934,7 +18227,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="13.2">
+    <row r="9" spans="1:15">
       <c r="B9" s="58" t="s">
         <v>1178</v>
       </c>
@@ -17960,7 +18253,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="13.2">
+    <row r="10" spans="1:15">
       <c r="B10" s="58" t="s">
         <v>1179</v>
       </c>
@@ -17986,7 +18279,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="13.2">
+    <row r="11" spans="1:15">
       <c r="B11" s="58" t="s">
         <v>1180</v>
       </c>
@@ -18012,7 +18305,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="13.2">
+    <row r="12" spans="1:15">
       <c r="B12" s="58" t="s">
         <v>1181</v>
       </c>
@@ -18038,7 +18331,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="13.2">
+    <row r="13" spans="1:15">
       <c r="B13" s="58" t="s">
         <v>1182</v>
       </c>
@@ -18061,7 +18354,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="13.2">
+    <row r="14" spans="1:15">
       <c r="B14" s="58" t="s">
         <v>1183</v>
       </c>
@@ -18084,7 +18377,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="13.2">
+    <row r="15" spans="1:15">
       <c r="B15" s="58" t="s">
         <v>1184</v>
       </c>
@@ -18107,7 +18400,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="13.2">
+    <row r="16" spans="1:15">
       <c r="B16" s="58" t="s">
         <v>1185</v>
       </c>
@@ -18127,7 +18420,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="17" spans="2:10" ht="13.2">
+    <row r="17" spans="2:10">
       <c r="B17" s="58" t="s">
         <v>1186</v>
       </c>
@@ -18147,7 +18440,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="18" spans="2:10" ht="13.2">
+    <row r="18" spans="2:10">
       <c r="B18" s="58" t="s">
         <v>1190</v>
       </c>
@@ -18167,7 +18460,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="19" spans="2:10" ht="13.2">
+    <row r="19" spans="2:10">
       <c r="B19" s="58" t="s">
         <v>1187</v>
       </c>
@@ -18187,7 +18480,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="20" spans="2:10" ht="13.2">
+    <row r="20" spans="2:10">
       <c r="B20" s="58" t="s">
         <v>1191</v>
       </c>
@@ -18732,9 +19025,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FCFD5C-696C-43AD-A2BD-D69C05CB2D44}">
   <dimension ref="B2:P57"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="16384" width="8.69921875" style="1"/>
+    <col min="1" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
@@ -19210,9 +19503,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E898285-845A-4583-B20D-F3A331C07E8E}">
   <dimension ref="B2:R45"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="13" max="13" width="8.59765625" customWidth="1"/>
+    <col min="13" max="13" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18">
@@ -19227,7 +19520,7 @@
       <c r="O2" s="86"/>
       <c r="P2" s="86"/>
     </row>
-    <row r="3" spans="2:18" ht="18.600000000000001" thickBot="1">
+    <row r="3" spans="2:18" ht="19.5" thickBot="1">
       <c r="F3" s="89" t="s">
         <v>1582</v>
       </c>
@@ -19349,7 +19642,7 @@
       <c r="P10" s="65"/>
       <c r="R10" s="84"/>
     </row>
-    <row r="11" spans="2:18" ht="18.600000000000001" thickBot="1">
+    <row r="11" spans="2:18" ht="19.5" thickBot="1">
       <c r="F11" s="91"/>
       <c r="I11" s="75"/>
       <c r="J11" s="66"/>
@@ -19438,7 +19731,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="22" spans="4:18" ht="18.600000000000001" thickBot="1">
+    <row r="22" spans="4:18" ht="19.5" thickBot="1">
       <c r="D22" s="80"/>
       <c r="E22" s="81"/>
       <c r="F22" s="81"/>
@@ -19567,7 +19860,7 @@
       </c>
       <c r="N29" s="84"/>
     </row>
-    <row r="30" spans="4:18" ht="18.600000000000001" thickBot="1">
+    <row r="30" spans="4:18" ht="19.5" thickBot="1">
       <c r="D30" s="83"/>
       <c r="E30" s="77"/>
       <c r="F30" s="78"/>
@@ -19803,11 +20096,11 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD79B98E-03E4-44E6-9FBF-39CA1C89C95A}">
   <dimension ref="B3:L149"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="8.69921875" style="73"/>
-    <col min="3" max="3" width="10.59765625" customWidth="1"/>
-    <col min="6" max="6" width="10.8984375" customWidth="1"/>
+    <col min="2" max="2" width="8.75" style="73"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="6" max="6" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:10">
@@ -20587,7 +20880,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="5"/>
   </cols>
@@ -20601,7 +20894,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBD988A-503C-4F44-AC4A-B26683FC9B4C}">
   <dimension ref="B4:O34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="5"/>
   </cols>
@@ -20752,14 +21045,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
   <dimension ref="B4:K166"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="2" width="20.19921875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="24.09765625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.25" style="5" customWidth="1"/>
+    <col min="3" max="3" width="24.125" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" style="5" customWidth="1"/>
     <col min="5" max="8" width="9" style="5"/>
-    <col min="9" max="9" width="45.59765625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="45.625" style="5" customWidth="1"/>
     <col min="10" max="22" width="9" style="5"/>
     <col min="23" max="23" width="8" style="5" customWidth="1"/>
     <col min="24" max="16384" width="9" style="5"/>
@@ -25113,22 +25406,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EB7090A-0065-41E7-85DA-75EEB9504A67}">
   <dimension ref="C3:Q81"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="7.5" style="5" customWidth="1"/>
-    <col min="3" max="3" width="13.69921875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="13.75" style="5" customWidth="1"/>
     <col min="4" max="4" width="20" style="5" customWidth="1"/>
-    <col min="5" max="5" width="30.59765625" style="5" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="13.3984375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="30.625" style="5" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="13.375" style="5" customWidth="1"/>
     <col min="7" max="7" width="11" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.19921875" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.69921875" style="5" customWidth="1"/>
-    <col min="10" max="12" width="9.8984375" style="18" customWidth="1"/>
-    <col min="13" max="13" width="9.19921875" style="18" customWidth="1"/>
-    <col min="14" max="14" width="12.59765625" style="18" customWidth="1"/>
-    <col min="15" max="15" width="27.09765625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="15.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.75" style="5" customWidth="1"/>
+    <col min="10" max="12" width="9.875" style="18" customWidth="1"/>
+    <col min="13" max="13" width="9.25" style="18" customWidth="1"/>
+    <col min="14" max="14" width="12.625" style="18" customWidth="1"/>
+    <col min="15" max="15" width="27.125" style="5" customWidth="1"/>
     <col min="16" max="16" width="7.5" style="5" customWidth="1"/>
-    <col min="17" max="17" width="15.09765625" style="5" customWidth="1"/>
+    <col min="17" max="17" width="15.125" style="5" customWidth="1"/>
     <col min="18" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -26792,7 +27085,7 @@
         <v>INSERT INTO m_skill VALUES ('skill037','グラビジャ',4,0,0,1,75,50,0.0,1,1200,'現HPの７５％ダメージ');</v>
       </c>
     </row>
-    <row r="41" spans="3:17" ht="37.799999999999997">
+    <row r="41" spans="3:17" ht="40.5">
       <c r="C41" s="47" t="s">
         <v>1048</v>
       </c>
@@ -28544,10 +28837,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F51B408-D4E3-46FE-97DE-15AB67B6AAB6}">
   <dimension ref="B1:Q100"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="2" width="12.69921875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="5" customWidth="1"/>
     <col min="3" max="3" width="17.5" style="5" customWidth="1"/>
     <col min="4" max="16384" width="9" style="5"/>
   </cols>
@@ -31363,22 +31656,22 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E63A27D9-C8B6-491D-9205-8D7433312F14}">
   <dimension ref="A4:U522"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="12.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.8984375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.59765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.625" style="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="12.69921875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="5.3984375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14.09765625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.75" style="3" customWidth="1"/>
+    <col min="8" max="8" width="5.375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="14.125" style="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="1"/>
-    <col min="12" max="12" width="17.69921875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.75" style="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1"/>
-    <col min="14" max="14" width="5.19921875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="5.25" style="1" customWidth="1"/>
     <col min="15" max="20" width="9" style="1"/>
-    <col min="21" max="21" width="8.8984375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="8.875" style="1" customWidth="1"/>
     <col min="22" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -47971,7 +48264,7 @@
         <v>INSERT INTO m_monster_skills VALUES ('myskill0505','monster084','skill051',FALSE);</v>
       </c>
     </row>
-    <row r="510" spans="1:21" ht="18">
+    <row r="510" spans="1:21" ht="18.75">
       <c r="A510"/>
       <c r="B510"/>
       <c r="C510"/>
@@ -47994,7 +48287,7 @@
       <c r="T510"/>
       <c r="U510"/>
     </row>
-    <row r="511" spans="1:21" ht="18">
+    <row r="511" spans="1:21" ht="18.75">
       <c r="A511"/>
       <c r="B511"/>
       <c r="C511"/>
@@ -48017,7 +48310,7 @@
       <c r="T511"/>
       <c r="U511"/>
     </row>
-    <row r="512" spans="1:21" ht="18">
+    <row r="512" spans="1:21" ht="18.75">
       <c r="A512"/>
       <c r="B512"/>
       <c r="C512"/>
@@ -48040,7 +48333,7 @@
       <c r="T512"/>
       <c r="U512"/>
     </row>
-    <row r="513" spans="1:21" ht="18">
+    <row r="513" spans="1:21" ht="18.75">
       <c r="A513"/>
       <c r="B513"/>
       <c r="C513"/>
@@ -48063,7 +48356,7 @@
       <c r="T513"/>
       <c r="U513"/>
     </row>
-    <row r="514" spans="1:21" ht="18">
+    <row r="514" spans="1:21" ht="18.75">
       <c r="A514"/>
       <c r="B514"/>
       <c r="C514"/>
@@ -48086,7 +48379,7 @@
       <c r="T514"/>
       <c r="U514"/>
     </row>
-    <row r="515" spans="1:21" ht="18">
+    <row r="515" spans="1:21" ht="18.75">
       <c r="A515"/>
       <c r="B515"/>
       <c r="C515"/>
@@ -48109,7 +48402,7 @@
       <c r="T515"/>
       <c r="U515"/>
     </row>
-    <row r="516" spans="1:21" ht="18">
+    <row r="516" spans="1:21" ht="18.75">
       <c r="A516"/>
       <c r="B516"/>
       <c r="C516"/>
@@ -48132,7 +48425,7 @@
       <c r="T516"/>
       <c r="U516"/>
     </row>
-    <row r="517" spans="1:21" ht="18">
+    <row r="517" spans="1:21" ht="18.75">
       <c r="A517"/>
       <c r="B517"/>
       <c r="C517"/>
@@ -48155,7 +48448,7 @@
       <c r="T517"/>
       <c r="U517"/>
     </row>
-    <row r="518" spans="1:21" ht="18">
+    <row r="518" spans="1:21" ht="18.75">
       <c r="A518"/>
       <c r="B518"/>
       <c r="C518"/>
@@ -48178,7 +48471,7 @@
       <c r="T518"/>
       <c r="U518"/>
     </row>
-    <row r="519" spans="1:21" ht="18">
+    <row r="519" spans="1:21" ht="18.75">
       <c r="A519"/>
       <c r="B519"/>
       <c r="C519"/>
@@ -48201,7 +48494,7 @@
       <c r="T519"/>
       <c r="U519"/>
     </row>
-    <row r="520" spans="1:21" ht="18">
+    <row r="520" spans="1:21" ht="18.75">
       <c r="A520"/>
       <c r="B520"/>
       <c r="C520"/>
@@ -48224,7 +48517,7 @@
       <c r="T520"/>
       <c r="U520"/>
     </row>
-    <row r="521" spans="1:21" ht="18">
+    <row r="521" spans="1:21" ht="18.75">
       <c r="A521"/>
       <c r="B521"/>
       <c r="C521"/>
@@ -48247,7 +48540,7 @@
       <c r="T521"/>
       <c r="U521"/>
     </row>
-    <row r="522" spans="1:21" ht="18">
+    <row r="522" spans="1:21" ht="18.75">
       <c r="A522"/>
       <c r="B522"/>
       <c r="C522"/>
@@ -48279,15 +48572,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A843E7EA-D614-495E-86B7-D31F628C6221}">
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="3" width="17.19921875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="17.25" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.59765625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.69921875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="11.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.75" style="5" customWidth="1"/>
     <col min="7" max="7" width="13.5" style="5" customWidth="1"/>
-    <col min="8" max="8" width="11.8984375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="11.875" style="5" customWidth="1"/>
     <col min="9" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -48648,13 +48941,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE71EC6-0DD3-461C-A8FC-74E22154B7A5}">
   <dimension ref="A4:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="3.8984375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="3.875" style="1" customWidth="1"/>
     <col min="2" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="4.19921875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="95.19921875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.8984375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="4.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="95.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.875" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC50E2E-20D0-41EE-86C8-92FB0540E3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60248C0B-5090-4E08-AF45-C6785DE7BAC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1104" windowWidth="21600" windowHeight="11232" tabRatio="778" firstSheet="3" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="1440" yWindow="1008" windowWidth="21600" windowHeight="11232" tabRatio="778" firstSheet="3" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="architecture" sheetId="12" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4208" uniqueCount="2017">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4212" uniqueCount="2020">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -8590,14 +8590,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>jobs</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>job_skills</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>テーブル名</t>
     <rPh sb="4" eb="5">
       <t>メイ</t>
@@ -8783,6 +8775,34 @@
   </si>
   <si>
     <t>m_skills</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>t_jobs</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>t_job_skills</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>feature</t>
+  </si>
+  <si>
+    <t>服装自由、フレックス等</t>
+    <rPh sb="0" eb="2">
+      <t>フクソウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジユウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>トウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>t_job_option(_feature)</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -13816,8 +13836,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7911971" y="1528349"/>
-          <a:ext cx="1800328" cy="1214718"/>
+          <a:off x="7985930" y="1467837"/>
+          <a:ext cx="1820498" cy="1167653"/>
           <a:chOff x="8992083" y="208776"/>
           <a:chExt cx="1814762" cy="1244600"/>
         </a:xfrm>
@@ -14126,8 +14146,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="11175520" y="3059605"/>
-          <a:ext cx="1822530" cy="1963728"/>
+          <a:off x="11283097" y="2938582"/>
+          <a:ext cx="1842700" cy="1889768"/>
           <a:chOff x="8549484" y="3956874"/>
           <a:chExt cx="1810288" cy="1437363"/>
         </a:xfrm>
@@ -14678,8 +14698,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4681098" y="1657961"/>
-          <a:ext cx="1869953" cy="3342717"/>
+          <a:off x="4721439" y="1597449"/>
+          <a:ext cx="1890124" cy="3208246"/>
           <a:chOff x="5970441" y="628674"/>
           <a:chExt cx="1893913" cy="3428095"/>
         </a:xfrm>
@@ -15147,8 +15167,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10840271" y="7258650"/>
-          <a:ext cx="2193307" cy="2523422"/>
+          <a:off x="10941124" y="6969538"/>
+          <a:ext cx="2220201" cy="2422569"/>
           <a:chOff x="12007370" y="5957071"/>
           <a:chExt cx="2223130" cy="2581251"/>
         </a:xfrm>
@@ -15354,8 +15374,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14334233" y="4816236"/>
-          <a:ext cx="2220036" cy="1720343"/>
+          <a:off x="14468704" y="4627977"/>
+          <a:ext cx="2246929" cy="1653108"/>
           <a:chOff x="15050343" y="4729843"/>
           <a:chExt cx="2243515" cy="1763032"/>
         </a:xfrm>
@@ -15784,8 +15804,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6846794" y="5210735"/>
-          <a:ext cx="1781735" cy="1311089"/>
+          <a:off x="6914030" y="5002306"/>
+          <a:ext cx="1795181" cy="1264024"/>
           <a:chOff x="6846794" y="5210735"/>
           <a:chExt cx="2341399" cy="1311089"/>
         </a:xfrm>
@@ -16161,8 +16181,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3726679" y="7642890"/>
-          <a:ext cx="2335072" cy="1882107"/>
+          <a:off x="3760297" y="7340331"/>
+          <a:ext cx="2355242" cy="1808149"/>
           <a:chOff x="3726679" y="7642891"/>
           <a:chExt cx="2335072" cy="1468663"/>
         </a:xfrm>
@@ -17085,15 +17105,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6672014-33B5-48C4-9202-55E4E667EEEF}">
   <dimension ref="A1:W32"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="3.75" customWidth="1"/>
-    <col min="2" max="3" width="8.75" customWidth="1"/>
-    <col min="20" max="21" width="2.75" customWidth="1"/>
-    <col min="22" max="23" width="4.125" customWidth="1"/>
-    <col min="24" max="24" width="4.75" customWidth="1"/>
-    <col min="25" max="25" width="8.75" customWidth="1"/>
-    <col min="27" max="27" width="4.375" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="3" width="8.69921875" customWidth="1"/>
+    <col min="20" max="21" width="2.69921875" customWidth="1"/>
+    <col min="22" max="23" width="4.09765625" customWidth="1"/>
+    <col min="24" max="24" width="4.69921875" customWidth="1"/>
+    <col min="25" max="25" width="8.69921875" customWidth="1"/>
+    <col min="27" max="27" width="4.3984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -17101,25 +17121,25 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="20.25">
+    <row r="2" spans="1:23" ht="19.2">
       <c r="A2" s="108"/>
       <c r="B2" s="107" t="s">
         <v>1932</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="20.25">
+    <row r="3" spans="1:23" ht="19.2">
       <c r="A3" s="107"/>
       <c r="B3" s="107" t="s">
         <v>1933</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="20.25">
+    <row r="4" spans="1:23" ht="19.2">
       <c r="A4" s="107"/>
       <c r="B4" s="107" t="s">
         <v>1934</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="19.5" thickBot="1">
+    <row r="5" spans="1:23" ht="18.600000000000001" thickBot="1">
       <c r="V5" s="67"/>
       <c r="W5" s="67"/>
     </row>
@@ -17153,7 +17173,7 @@
       <c r="C8" s="64"/>
       <c r="W8" s="65"/>
     </row>
-    <row r="9" spans="1:23" ht="19.5" thickBot="1">
+    <row r="9" spans="1:23" ht="18.600000000000001" thickBot="1">
       <c r="C9" s="64"/>
       <c r="L9" t="s">
         <v>1706</v>
@@ -17303,7 +17323,7 @@
       <c r="V30" s="65"/>
       <c r="W30" s="65"/>
     </row>
-    <row r="31" spans="3:23" ht="19.5" thickBot="1">
+    <row r="31" spans="3:23" ht="18.600000000000001" thickBot="1">
       <c r="C31" s="64"/>
       <c r="D31" s="66"/>
       <c r="E31" s="67"/>
@@ -17326,7 +17346,7 @@
       <c r="V31" s="68"/>
       <c r="W31" s="65"/>
     </row>
-    <row r="32" spans="3:23" ht="13.15" customHeight="1" thickBot="1">
+    <row r="32" spans="3:23" ht="13.2" customHeight="1" thickBot="1">
       <c r="C32" s="66"/>
       <c r="D32" s="67"/>
       <c r="E32" s="67"/>
@@ -17359,10 +17379,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC349EE6-5475-4F9C-BD43-5DC02797CE07}">
   <dimension ref="A2:Q131"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="11" style="98" customWidth="1"/>
-    <col min="2" max="6" width="10.875" style="98" customWidth="1"/>
+    <col min="2" max="6" width="10.8984375" style="98" customWidth="1"/>
     <col min="7" max="16384" width="9" style="98"/>
   </cols>
   <sheetData>
@@ -17692,7 +17712,7 @@
     </row>
     <row r="54" spans="2:10">
       <c r="B54" s="99" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="J54" s="98" t="s">
         <v>307</v>
@@ -17700,7 +17720,7 @@
     </row>
     <row r="55" spans="2:10">
       <c r="B55" s="99" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="56" spans="2:10">
@@ -17813,41 +17833,44 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
-      <c r="J81" s="109" t="s">
-        <v>1981</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10">
+    <row r="81" spans="1:13">
+      <c r="M81" s="109" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13">
       <c r="B82" s="109" t="s">
         <v>1961</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:13">
       <c r="A83" s="98" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="B83" s="98" t="s">
-        <v>1966</v>
+        <v>2015</v>
       </c>
       <c r="E83" s="98" t="s">
-        <v>1967</v>
+        <v>2016</v>
       </c>
       <c r="G83" s="98" t="s">
-        <v>2016</v>
-      </c>
-      <c r="J83" s="98" t="s">
-        <v>1971</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10">
-      <c r="J84" s="98" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10">
+        <v>2014</v>
+      </c>
+      <c r="I83" s="98" t="s">
+        <v>2019</v>
+      </c>
+      <c r="M83" s="98" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13">
+      <c r="M84" s="98" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13">
       <c r="B85" s="98" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="E85" s="98" t="s">
         <v>1965</v>
@@ -17855,204 +17878,213 @@
       <c r="G85" s="98" t="s">
         <v>155</v>
       </c>
-      <c r="J85" s="98" t="s">
-        <v>1973</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10">
+      <c r="I85" s="98" t="s">
+        <v>1965</v>
+      </c>
+      <c r="M85" s="98" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13">
       <c r="E86" s="98" t="s">
         <v>155</v>
       </c>
       <c r="G86" s="98" t="s">
         <v>231</v>
       </c>
+      <c r="I86" s="98" t="s">
+        <v>2017</v>
+      </c>
       <c r="J86" s="98" t="s">
+        <v>2018</v>
+      </c>
+      <c r="M86" s="98" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13">
+      <c r="B87" s="98" t="s">
+        <v>1981</v>
+      </c>
+      <c r="M87" s="98" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13">
+      <c r="B88" s="98" t="s">
+        <v>1982</v>
+      </c>
+      <c r="M88" s="98" t="s">
         <v>1974</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
-      <c r="B87" s="98" t="s">
+    <row r="89" spans="1:13">
+      <c r="M89" s="98" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13">
+      <c r="B90" s="98" t="s">
         <v>1983</v>
       </c>
-      <c r="J87" s="98" t="s">
-        <v>1975</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10">
-      <c r="B88" s="98" t="s">
+      <c r="M90" s="98" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13">
+      <c r="B91" s="98" t="s">
         <v>1984</v>
       </c>
-      <c r="J88" s="98" t="s">
-        <v>1976</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10">
-      <c r="J89" s="98" t="s">
+      <c r="M91" s="98" t="s">
         <v>1977</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
-      <c r="B90" s="98" t="s">
+    <row r="92" spans="1:13">
+      <c r="B92" s="98" t="s">
         <v>1985</v>
       </c>
-      <c r="J90" s="98" t="s">
+      <c r="M92" s="98" t="s">
         <v>1978</v>
       </c>
     </row>
-    <row r="91" spans="1:10">
-      <c r="B91" s="98" t="s">
+    <row r="93" spans="1:13">
+      <c r="B93" s="98" t="s">
         <v>1986</v>
       </c>
-      <c r="J91" s="98" t="s">
-        <v>1979</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10">
-      <c r="B92" s="98" t="s">
+    </row>
+    <row r="94" spans="1:13">
+      <c r="B94" s="98" t="s">
         <v>1987</v>
       </c>
-      <c r="J92" s="98" t="s">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10">
-      <c r="B93" s="98" t="s">
+    </row>
+    <row r="96" spans="1:13">
+      <c r="B96" s="98" t="s">
         <v>1988</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10">
-      <c r="B94" s="98" t="s">
-        <v>1989</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10">
-      <c r="B96" s="98" t="s">
-        <v>1990</v>
       </c>
     </row>
     <row r="97" spans="2:2">
       <c r="B97" s="98" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="98" spans="2:2">
       <c r="B98" s="98" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="100" spans="2:2">
       <c r="B100" s="98" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="101" spans="2:2">
       <c r="B101" s="98" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="103" spans="2:2">
       <c r="B103" s="98" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="104" spans="2:2">
       <c r="B104" s="98" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="105" spans="2:2">
       <c r="B105" s="98" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="107" spans="2:2">
       <c r="B107" s="98" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="108" spans="2:2">
       <c r="B108" s="98" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="109" spans="2:2">
       <c r="B109" s="98" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="110" spans="2:2">
       <c r="B110" s="98" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="111" spans="2:2">
       <c r="B111" s="98" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="98" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="B117" s="98" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="B118" s="98" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="B120" s="98" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="B121" s="98" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="B123" s="98" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="B124" s="98" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="B125" s="98" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="B126" s="98" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="B127" s="98" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="129" spans="2:2">
       <c r="B129" s="98" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="130" spans="2:2">
       <c r="B130" s="98" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="131" spans="2:2">
       <c r="B131" s="98" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
     </row>
   </sheetData>
@@ -18065,10 +18097,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F0B575-2DDF-49B9-8DE2-F372EEC2F3B3}">
   <dimension ref="A2:O79"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="11.875" style="1" customWidth="1"/>
-    <col min="2" max="6" width="10.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.8984375" style="1" customWidth="1"/>
+    <col min="2" max="6" width="10.8984375" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -18100,7 +18132,7 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="18.75">
+    <row r="4" spans="1:15" ht="18">
       <c r="A4" s="1" t="s">
         <v>1280</v>
       </c>
@@ -18129,7 +18161,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" ht="13.2">
       <c r="B5" s="58" t="s">
         <v>1175</v>
       </c>
@@ -18146,7 +18178,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" ht="13.2">
       <c r="B6" s="58" t="s">
         <v>1176</v>
       </c>
@@ -18169,7 +18201,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" ht="13.2">
       <c r="B7" s="58" t="s">
         <v>1189</v>
       </c>
@@ -18198,7 +18230,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" ht="13.2">
       <c r="B8" s="58" t="s">
         <v>1177</v>
       </c>
@@ -18227,7 +18259,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" ht="13.2">
       <c r="B9" s="58" t="s">
         <v>1178</v>
       </c>
@@ -18253,7 +18285,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" ht="13.2">
       <c r="B10" s="58" t="s">
         <v>1179</v>
       </c>
@@ -18279,7 +18311,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" ht="13.2">
       <c r="B11" s="58" t="s">
         <v>1180</v>
       </c>
@@ -18305,7 +18337,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" ht="13.2">
       <c r="B12" s="58" t="s">
         <v>1181</v>
       </c>
@@ -18331,7 +18363,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" ht="13.2">
       <c r="B13" s="58" t="s">
         <v>1182</v>
       </c>
@@ -18354,7 +18386,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" ht="13.2">
       <c r="B14" s="58" t="s">
         <v>1183</v>
       </c>
@@ -18377,7 +18409,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" ht="13.2">
       <c r="B15" s="58" t="s">
         <v>1184</v>
       </c>
@@ -18400,7 +18432,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" ht="13.2">
       <c r="B16" s="58" t="s">
         <v>1185</v>
       </c>
@@ -18420,7 +18452,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" ht="13.2">
       <c r="B17" s="58" t="s">
         <v>1186</v>
       </c>
@@ -18440,7 +18472,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:10" ht="13.2">
       <c r="B18" s="58" t="s">
         <v>1190</v>
       </c>
@@ -18460,7 +18492,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:10" ht="13.2">
       <c r="B19" s="58" t="s">
         <v>1187</v>
       </c>
@@ -18480,7 +18512,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:10" ht="13.2">
       <c r="B20" s="58" t="s">
         <v>1191</v>
       </c>
@@ -19025,9 +19057,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FCFD5C-696C-43AD-A2BD-D69C05CB2D44}">
   <dimension ref="B2:P57"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="16384" width="8.75" style="1"/>
+    <col min="1" max="16384" width="8.69921875" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
@@ -19503,9 +19535,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E898285-845A-4583-B20D-F3A331C07E8E}">
   <dimension ref="B2:R45"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="13" max="13" width="8.625" customWidth="1"/>
+    <col min="13" max="13" width="8.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18">
@@ -19520,7 +19552,7 @@
       <c r="O2" s="86"/>
       <c r="P2" s="86"/>
     </row>
-    <row r="3" spans="2:18" ht="19.5" thickBot="1">
+    <row r="3" spans="2:18" ht="18.600000000000001" thickBot="1">
       <c r="F3" s="89" t="s">
         <v>1582</v>
       </c>
@@ -19642,7 +19674,7 @@
       <c r="P10" s="65"/>
       <c r="R10" s="84"/>
     </row>
-    <row r="11" spans="2:18" ht="19.5" thickBot="1">
+    <row r="11" spans="2:18" ht="18.600000000000001" thickBot="1">
       <c r="F11" s="91"/>
       <c r="I11" s="75"/>
       <c r="J11" s="66"/>
@@ -19731,7 +19763,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="22" spans="4:18" ht="19.5" thickBot="1">
+    <row r="22" spans="4:18" ht="18.600000000000001" thickBot="1">
       <c r="D22" s="80"/>
       <c r="E22" s="81"/>
       <c r="F22" s="81"/>
@@ -19860,7 +19892,7 @@
       </c>
       <c r="N29" s="84"/>
     </row>
-    <row r="30" spans="4:18" ht="19.5" thickBot="1">
+    <row r="30" spans="4:18" ht="18.600000000000001" thickBot="1">
       <c r="D30" s="83"/>
       <c r="E30" s="77"/>
       <c r="F30" s="78"/>
@@ -20096,11 +20128,11 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD79B98E-03E4-44E6-9FBF-39CA1C89C95A}">
   <dimension ref="B3:L149"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="8.75" style="73"/>
-    <col min="3" max="3" width="10.625" customWidth="1"/>
-    <col min="6" max="6" width="10.875" customWidth="1"/>
+    <col min="2" max="2" width="8.69921875" style="73"/>
+    <col min="3" max="3" width="10.59765625" customWidth="1"/>
+    <col min="6" max="6" width="10.8984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:10">
@@ -20880,7 +20912,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="16384" width="9" style="5"/>
   </cols>
@@ -20894,7 +20926,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBD988A-503C-4F44-AC4A-B26683FC9B4C}">
   <dimension ref="B4:O34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="16384" width="9" style="5"/>
   </cols>
@@ -21045,14 +21077,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
   <dimension ref="B4:K166"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="2" width="20.25" style="5" customWidth="1"/>
-    <col min="3" max="3" width="24.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.19921875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="24.09765625" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" style="5" customWidth="1"/>
     <col min="5" max="8" width="9" style="5"/>
-    <col min="9" max="9" width="45.625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="45.59765625" style="5" customWidth="1"/>
     <col min="10" max="22" width="9" style="5"/>
     <col min="23" max="23" width="8" style="5" customWidth="1"/>
     <col min="24" max="16384" width="9" style="5"/>
@@ -25406,22 +25438,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EB7090A-0065-41E7-85DA-75EEB9504A67}">
   <dimension ref="C3:Q81"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="2" width="7.5" style="5" customWidth="1"/>
-    <col min="3" max="3" width="13.75" style="5" customWidth="1"/>
+    <col min="3" max="3" width="13.69921875" style="5" customWidth="1"/>
     <col min="4" max="4" width="20" style="5" customWidth="1"/>
-    <col min="5" max="5" width="30.625" style="5" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="13.375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="30.59765625" style="5" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="13.3984375" style="5" customWidth="1"/>
     <col min="7" max="7" width="11" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.75" style="5" customWidth="1"/>
-    <col min="10" max="12" width="9.875" style="18" customWidth="1"/>
-    <col min="13" max="13" width="9.25" style="18" customWidth="1"/>
-    <col min="14" max="14" width="12.625" style="18" customWidth="1"/>
-    <col min="15" max="15" width="27.125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="15.19921875" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.69921875" style="5" customWidth="1"/>
+    <col min="10" max="12" width="9.8984375" style="18" customWidth="1"/>
+    <col min="13" max="13" width="9.19921875" style="18" customWidth="1"/>
+    <col min="14" max="14" width="12.59765625" style="18" customWidth="1"/>
+    <col min="15" max="15" width="27.09765625" style="5" customWidth="1"/>
     <col min="16" max="16" width="7.5" style="5" customWidth="1"/>
-    <col min="17" max="17" width="15.125" style="5" customWidth="1"/>
+    <col min="17" max="17" width="15.09765625" style="5" customWidth="1"/>
     <col min="18" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -27085,7 +27117,7 @@
         <v>INSERT INTO m_skill VALUES ('skill037','グラビジャ',4,0,0,1,75,50,0.0,1,1200,'現HPの７５％ダメージ');</v>
       </c>
     </row>
-    <row r="41" spans="3:17" ht="40.5">
+    <row r="41" spans="3:17" ht="37.799999999999997">
       <c r="C41" s="47" t="s">
         <v>1048</v>
       </c>
@@ -28837,10 +28869,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F51B408-D4E3-46FE-97DE-15AB67B6AAB6}">
   <dimension ref="B1:Q100"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="2" width="12.75" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.69921875" style="5" customWidth="1"/>
     <col min="3" max="3" width="17.5" style="5" customWidth="1"/>
     <col min="4" max="16384" width="9" style="5"/>
   </cols>
@@ -31656,22 +31688,22 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E63A27D9-C8B6-491D-9205-8D7433312F14}">
   <dimension ref="A4:U522"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="12.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.8984375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="12.75" style="3" customWidth="1"/>
-    <col min="8" max="8" width="5.375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="5.3984375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="14.09765625" style="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="1"/>
-    <col min="12" max="12" width="17.75" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.69921875" style="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1"/>
-    <col min="14" max="14" width="5.25" style="1" customWidth="1"/>
+    <col min="14" max="14" width="5.19921875" style="1" customWidth="1"/>
     <col min="15" max="20" width="9" style="1"/>
-    <col min="21" max="21" width="8.875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="8.8984375" style="1" customWidth="1"/>
     <col min="22" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -48264,7 +48296,7 @@
         <v>INSERT INTO m_monster_skills VALUES ('myskill0505','monster084','skill051',FALSE);</v>
       </c>
     </row>
-    <row r="510" spans="1:21" ht="18.75">
+    <row r="510" spans="1:21" ht="18">
       <c r="A510"/>
       <c r="B510"/>
       <c r="C510"/>
@@ -48287,7 +48319,7 @@
       <c r="T510"/>
       <c r="U510"/>
     </row>
-    <row r="511" spans="1:21" ht="18.75">
+    <row r="511" spans="1:21" ht="18">
       <c r="A511"/>
       <c r="B511"/>
       <c r="C511"/>
@@ -48310,7 +48342,7 @@
       <c r="T511"/>
       <c r="U511"/>
     </row>
-    <row r="512" spans="1:21" ht="18.75">
+    <row r="512" spans="1:21" ht="18">
       <c r="A512"/>
       <c r="B512"/>
       <c r="C512"/>
@@ -48333,7 +48365,7 @@
       <c r="T512"/>
       <c r="U512"/>
     </row>
-    <row r="513" spans="1:21" ht="18.75">
+    <row r="513" spans="1:21" ht="18">
       <c r="A513"/>
       <c r="B513"/>
       <c r="C513"/>
@@ -48356,7 +48388,7 @@
       <c r="T513"/>
       <c r="U513"/>
     </row>
-    <row r="514" spans="1:21" ht="18.75">
+    <row r="514" spans="1:21" ht="18">
       <c r="A514"/>
       <c r="B514"/>
       <c r="C514"/>
@@ -48379,7 +48411,7 @@
       <c r="T514"/>
       <c r="U514"/>
     </row>
-    <row r="515" spans="1:21" ht="18.75">
+    <row r="515" spans="1:21" ht="18">
       <c r="A515"/>
       <c r="B515"/>
       <c r="C515"/>
@@ -48402,7 +48434,7 @@
       <c r="T515"/>
       <c r="U515"/>
     </row>
-    <row r="516" spans="1:21" ht="18.75">
+    <row r="516" spans="1:21" ht="18">
       <c r="A516"/>
       <c r="B516"/>
       <c r="C516"/>
@@ -48425,7 +48457,7 @@
       <c r="T516"/>
       <c r="U516"/>
     </row>
-    <row r="517" spans="1:21" ht="18.75">
+    <row r="517" spans="1:21" ht="18">
       <c r="A517"/>
       <c r="B517"/>
       <c r="C517"/>
@@ -48448,7 +48480,7 @@
       <c r="T517"/>
       <c r="U517"/>
     </row>
-    <row r="518" spans="1:21" ht="18.75">
+    <row r="518" spans="1:21" ht="18">
       <c r="A518"/>
       <c r="B518"/>
       <c r="C518"/>
@@ -48471,7 +48503,7 @@
       <c r="T518"/>
       <c r="U518"/>
     </row>
-    <row r="519" spans="1:21" ht="18.75">
+    <row r="519" spans="1:21" ht="18">
       <c r="A519"/>
       <c r="B519"/>
       <c r="C519"/>
@@ -48494,7 +48526,7 @@
       <c r="T519"/>
       <c r="U519"/>
     </row>
-    <row r="520" spans="1:21" ht="18.75">
+    <row r="520" spans="1:21" ht="18">
       <c r="A520"/>
       <c r="B520"/>
       <c r="C520"/>
@@ -48517,7 +48549,7 @@
       <c r="T520"/>
       <c r="U520"/>
     </row>
-    <row r="521" spans="1:21" ht="18.75">
+    <row r="521" spans="1:21" ht="18">
       <c r="A521"/>
       <c r="B521"/>
       <c r="C521"/>
@@ -48540,7 +48572,7 @@
       <c r="T521"/>
       <c r="U521"/>
     </row>
-    <row r="522" spans="1:21" ht="18.75">
+    <row r="522" spans="1:21" ht="18">
       <c r="A522"/>
       <c r="B522"/>
       <c r="C522"/>
@@ -48572,15 +48604,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A843E7EA-D614-495E-86B7-D31F628C6221}">
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="3" width="17.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="17.19921875" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.75" style="5" customWidth="1"/>
+    <col min="5" max="5" width="11.59765625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.69921875" style="5" customWidth="1"/>
     <col min="7" max="7" width="13.5" style="5" customWidth="1"/>
-    <col min="8" max="8" width="11.875" style="5" customWidth="1"/>
+    <col min="8" max="8" width="11.8984375" style="5" customWidth="1"/>
     <col min="9" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -48941,13 +48973,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE71EC6-0DD3-461C-A8FC-74E22154B7A5}">
   <dimension ref="A4:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="3.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="3.8984375" style="1" customWidth="1"/>
     <col min="2" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="4.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="95.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="4.19921875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="95.19921875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.8984375" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60248C0B-5090-4E08-AF45-C6785DE7BAC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12AAB05F-DE98-4CCF-BA8F-05C6CFC7EC97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="1008" windowWidth="21600" windowHeight="11232" tabRatio="778" firstSheet="3" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4212" uniqueCount="2020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4215" uniqueCount="2024">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -8782,13 +8782,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>t_job_skills</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>feature</t>
-  </si>
-  <si>
     <t>服装自由、フレックス等</t>
     <rPh sb="0" eb="2">
       <t>フクソウ</t>
@@ -8803,6 +8796,31 @@
   </si>
   <si>
     <t>t_job_option(_feature)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>required_type</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>＜コード化？</t>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>t_job_features</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>feature_name</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>option</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -17851,13 +17869,13 @@
         <v>2015</v>
       </c>
       <c r="E83" s="98" t="s">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="G83" s="98" t="s">
         <v>2014</v>
       </c>
       <c r="I83" s="98" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="M83" s="98" t="s">
         <v>1969</v>
@@ -17887,16 +17905,19 @@
     </row>
     <row r="86" spans="1:13">
       <c r="E86" s="98" t="s">
-        <v>155</v>
+        <v>2018</v>
+      </c>
+      <c r="F86" s="98" t="s">
+        <v>2020</v>
       </c>
       <c r="G86" s="98" t="s">
         <v>231</v>
       </c>
       <c r="I86" s="98" t="s">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="J86" s="98" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="M86" s="98" t="s">
         <v>1972</v>
@@ -17906,6 +17927,9 @@
       <c r="B87" s="98" t="s">
         <v>1981</v>
       </c>
+      <c r="E87" s="98" t="s">
+        <v>2019</v>
+      </c>
       <c r="M87" s="98" t="s">
         <v>1973</v>
       </c>
@@ -17913,6 +17937,9 @@
     <row r="88" spans="1:13">
       <c r="B88" s="98" t="s">
         <v>1982</v>
+      </c>
+      <c r="E88" s="98" t="s">
+        <v>2022</v>
       </c>
       <c r="M88" s="98" t="s">
         <v>1974</v>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12AAB05F-DE98-4CCF-BA8F-05C6CFC7EC97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4309F97B-5DDF-4EB4-846E-A17A57E3E84A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="1008" windowWidth="21600" windowHeight="11232" tabRatio="778" firstSheet="3" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4215" uniqueCount="2024">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4236" uniqueCount="2038">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -8822,6 +8822,49 @@
   <si>
     <t>option</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>バルクインサート</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>バッチ開始</t>
+  </si>
+  <si>
+    <t>SELECT job_id</t>
+  </si>
+  <si>
+    <t>FROM t_job_features_created</t>
+  </si>
+  <si>
+    <t>map[int64]struct{} に変換</t>
+  </si>
+  <si>
+    <t>案件をループ</t>
+  </si>
+  <si>
+    <t>mapにjob_idあり？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ├─ あり → continue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    └─ なし → Feature抽出</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">              トランザクション</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        t_job_features バルクINSERT</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> t_job_features_created INSERT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                 COMMIT</t>
   </si>
 </sst>
 </file>
@@ -17396,7 +17439,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC349EE6-5475-4F9C-BD43-5DC02797CE07}">
-  <dimension ref="A2:Q131"/>
+  <dimension ref="A2:Q154"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="11" style="98" customWidth="1"/>
@@ -18099,19 +18142,124 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="129" spans="2:2">
+    <row r="129" spans="1:2">
       <c r="B129" s="98" t="s">
         <v>2007</v>
       </c>
     </row>
-    <row r="130" spans="2:2">
+    <row r="130" spans="1:2">
       <c r="B130" s="98" t="s">
         <v>2012</v>
       </c>
     </row>
-    <row r="131" spans="2:2">
+    <row r="131" spans="1:2">
       <c r="B131" s="98" t="s">
         <v>2008</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="98" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="B135" s="98" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="B136" s="98" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="B137" s="98" t="s">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="B138" s="98" t="s">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="B139" s="98" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="B140" s="98" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="B141" s="98" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="B142" s="98" t="s">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="B143" s="98" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="B144" s="98" t="s">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2">
+      <c r="B145" s="98" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2">
+      <c r="B146" s="98" t="s">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2">
+      <c r="B147" s="98" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2">
+      <c r="B148" s="98" t="s">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2">
+      <c r="B149" s="98" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2">
+      <c r="B150" s="98" t="s">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2">
+      <c r="B151" s="98" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2">
+      <c r="B152" s="98" t="s">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2">
+      <c r="B153" s="98" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="154" spans="2:2">
+      <c r="B154" s="98" t="s">
+        <v>2037</v>
       </c>
     </row>
   </sheetData>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4309F97B-5DDF-4EB4-846E-A17A57E3E84A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D03988-952F-4CD7-A827-29D15097EA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1008" windowWidth="21600" windowHeight="11232" tabRatio="778" firstSheet="3" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="778" firstSheet="3" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="architecture" sheetId="12" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4236" uniqueCount="2038">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4428" uniqueCount="2226">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -8865,6 +8865,577 @@
   </si>
   <si>
     <t xml:space="preserve">                 COMMIT</t>
+  </si>
+  <si>
+    <t>分析可能なもの</t>
+    <rPh sb="0" eb="2">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>求人総数の推移</t>
+  </si>
+  <si>
+    <t>日別・週別・月別</t>
+  </si>
+  <si>
+    <t>新規求人が増えてるか減ってるか</t>
+  </si>
+  <si>
+    <t>サイト別の掲載件数</t>
+  </si>
+  <si>
+    <t>新規求人件数</t>
+  </si>
+  <si>
+    <t>今日初めて観測した求人</t>
+  </si>
+  <si>
+    <t>先週比・先月比</t>
+  </si>
+  <si>
+    <t>「求人市場が活発か」の指標</t>
+  </si>
+  <si>
+    <t>アクティブ求人件数</t>
+  </si>
+  <si>
+    <t>last_seen_at を基準に現在も掲載されていると判断した件数</t>
+  </si>
+  <si>
+    <t>期間内に消えた求人数</t>
+  </si>
+  <si>
+    <t>求人の増減</t>
+  </si>
+  <si>
+    <t>求人の平均掲載期間</t>
+  </si>
+  <si>
+    <t>初回検出日 → 最終検出日</t>
+  </si>
+  <si>
+    <t>何日くらい募集され続けるか</t>
+  </si>
+  <si>
+    <t>長期間残る求人の割合</t>
+  </si>
+  <si>
+    <t>求人の消化速度</t>
+  </si>
+  <si>
+    <t>新規掲載から消えるまでの日数</t>
+  </si>
+  <si>
+    <t>すぐ消える求人＝応募が集まりやすい／採用が決まりやすい可能性</t>
+  </si>
+  <si>
+    <t>長く残る求人＝条件が厳しい可能性</t>
+  </si>
+  <si>
+    <t>プログラミング言語ランキング</t>
+  </si>
+  <si>
+    <t>Go</t>
+  </si>
+  <si>
+    <t>Java</t>
+  </si>
+  <si>
+    <t>C#</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>TypeScript</t>
+  </si>
+  <si>
+    <t>PHP</t>
+  </si>
+  <si>
+    <t>求人数順</t>
+  </si>
+  <si>
+    <t>技術の人気推移</t>
+  </si>
+  <si>
+    <t>Go求人は3か月前より増えたか</t>
+  </si>
+  <si>
+    <t>Reactは横ばいか</t>
+  </si>
+  <si>
+    <t>AI関連技術は増えているか</t>
+  </si>
+  <si>
+    <t>技術ごとの時系列グラフ</t>
+  </si>
+  <si>
+    <t>言語 × フレームワーク</t>
+  </si>
+  <si>
+    <t>Java × Spring</t>
+  </si>
+  <si>
+    <t>C# × ASP.NET Core</t>
+  </si>
+  <si>
+    <t>TypeScript × React</t>
+  </si>
+  <si>
+    <t>Python × Django</t>
+  </si>
+  <si>
+    <t>Go × Gin</t>
+  </si>
+  <si>
+    <t>よくセットで要求される技術</t>
+  </si>
+  <si>
+    <t>スキルの共起分析</t>
+  </si>
+  <si>
+    <t>Go案件に一緒に出やすい技術</t>
+  </si>
+  <si>
+    <t>React案件で要求されやすい技術</t>
+  </si>
+  <si>
+    <t>PostgreSQLと一緒に出やすい技術</t>
+  </si>
+  <si>
+    <t>「次に何を覚えると求人の幅が広がるか」</t>
+  </si>
+  <si>
+    <t>必須スキルと歓迎スキルの比較</t>
+  </si>
+  <si>
+    <t>Goは必須が多いか、歓迎が多いか</t>
+  </si>
+  <si>
+    <t>AWSは必須か、あると有利程度か</t>
+  </si>
+  <si>
+    <t>Reactは必須なのか経験者歓迎なのか</t>
+  </si>
+  <si>
+    <t>カテゴリ別の需要</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>Framework / Library</t>
+  </si>
+  <si>
+    <t>Database</t>
+  </si>
+  <si>
+    <t>Cloud</t>
+  </si>
+  <si>
+    <t>Infrastructure</t>
+  </si>
+  <si>
+    <t>Tool</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Architecture</t>
+  </si>
+  <si>
+    <t>Methodology</t>
+  </si>
+  <si>
+    <t>給与ランキング</t>
+  </si>
+  <si>
+    <t>言語別の平均単価</t>
+  </si>
+  <si>
+    <t>フレームワーク別の平均単価</t>
+  </si>
+  <si>
+    <t>スキル別の平均単価</t>
+  </si>
+  <si>
+    <t>求人件数と単価を合わせた分析</t>
+  </si>
+  <si>
+    <t>給与レンジの分布</t>
+  </si>
+  <si>
+    <t>月40万未満</t>
+  </si>
+  <si>
+    <t>40〜60万</t>
+  </si>
+  <si>
+    <t>60〜80万</t>
+  </si>
+  <si>
+    <t>80万以上</t>
+  </si>
+  <si>
+    <t>単価の中央値</t>
+  </si>
+  <si>
+    <t>技術別の単価</t>
+  </si>
+  <si>
+    <t>Go案件の平均・中央値</t>
+  </si>
+  <si>
+    <t>Java案件の平均・中央値</t>
+  </si>
+  <si>
+    <t>C#案件の平均・中央値</t>
+  </si>
+  <si>
+    <t>React案件の平均・中央値</t>
+  </si>
+  <si>
+    <t>経験年数 × 単価</t>
+  </si>
+  <si>
+    <t>1〜2年</t>
+  </si>
+  <si>
+    <t>3〜5年</t>
+  </si>
+  <si>
+    <t>5年以上</t>
+  </si>
+  <si>
+    <t>経験年数による単価差</t>
+  </si>
+  <si>
+    <t>リモート率</t>
+  </si>
+  <si>
+    <t>フルリモート</t>
+  </si>
+  <si>
+    <t>一部リモート</t>
+  </si>
+  <si>
+    <t>常駐</t>
+  </si>
+  <si>
+    <t>技術別のリモート率</t>
+  </si>
+  <si>
+    <t>地域別求人</t>
+  </si>
+  <si>
+    <t>東京</t>
+  </si>
+  <si>
+    <t>大阪</t>
+  </si>
+  <si>
+    <t>名古屋</t>
+  </si>
+  <si>
+    <t>福岡</t>
+  </si>
+  <si>
+    <t>地方</t>
+  </si>
+  <si>
+    <t>都道府県ごとの求人密度</t>
+  </si>
+  <si>
+    <t>地域 × 単価</t>
+  </si>
+  <si>
+    <t>東京は高単価だが常駐が多い</t>
+  </si>
+  <si>
+    <t>地方は求人が少ないがフルリモート率が高い</t>
+  </si>
+  <si>
+    <t>地域ごとの比較</t>
+  </si>
+  <si>
+    <t>雇用形態の割合</t>
+  </si>
+  <si>
+    <t>正社員</t>
+  </si>
+  <si>
+    <t>業務委託</t>
+  </si>
+  <si>
+    <t>派遣</t>
+  </si>
+  <si>
+    <t>副業</t>
+  </si>
+  <si>
+    <t>アルバイト</t>
+  </si>
+  <si>
+    <t>勤務条件</t>
+  </si>
+  <si>
+    <t>週5</t>
+  </si>
+  <si>
+    <t>週4</t>
+  </si>
+  <si>
+    <t>週3</t>
+  </si>
+  <si>
+    <t>時短</t>
+  </si>
+  <si>
+    <t>副業可</t>
+  </si>
+  <si>
+    <t>案件の競争度っぽい指標</t>
+  </si>
+  <si>
+    <t>掲載期間</t>
+  </si>
+  <si>
+    <t>単価</t>
+  </si>
+  <si>
+    <t>必須スキル数</t>
+  </si>
+  <si>
+    <t>条件の良さ</t>
+  </si>
+  <si>
+    <t>※応募数が取れないなら推定になる</t>
+  </si>
+  <si>
+    <t>求人の難易度</t>
+  </si>
+  <si>
+    <t>必須経験年数</t>
+  </si>
+  <si>
+    <t>求められる技術カテゴリ数</t>
+  </si>
+  <si>
+    <t>「要求が盛られている求人」を可視化</t>
+  </si>
+  <si>
+    <t>スキル要求数ランキング</t>
+  </si>
+  <si>
+    <t>必須スキルが多い求人</t>
+  </si>
+  <si>
+    <t>「全部入り案件」</t>
+  </si>
+  <si>
+    <t>技術スタックが広すぎる求人</t>
+  </si>
+  <si>
+    <t>技術スタックの複雑度</t>
+  </si>
+  <si>
+    <t>言語1個＋FW1個</t>
+  </si>
+  <si>
+    <t>言語3個＋Cloud＋Docker＋Kubernetes＋CI/CD</t>
+  </si>
+  <si>
+    <t>求人ごとの要求範囲</t>
+  </si>
+  <si>
+    <t>求人文の長さ</t>
+  </si>
+  <si>
+    <t>説明文が長い求人</t>
+  </si>
+  <si>
+    <t>短すぎる求人</t>
+  </si>
+  <si>
+    <t>情報量と単価の関係</t>
+  </si>
+  <si>
+    <t>企業別の求人傾向</t>
+  </si>
+  <si>
+    <t>同じ企業が何件出しているか</t>
+  </si>
+  <si>
+    <t>よく募集している技術</t>
+  </si>
+  <si>
+    <t>長期間募集している案件</t>
+  </si>
+  <si>
+    <t>求人サイト比較</t>
+  </si>
+  <si>
+    <t>サイトごとの求人件数</t>
+  </si>
+  <si>
+    <t>平均単価</t>
+  </si>
+  <si>
+    <t>フルリモート率</t>
+  </si>
+  <si>
+    <t>技術の偏り</t>
+  </si>
+  <si>
+    <t>同じ求人の重複率</t>
+  </si>
+  <si>
+    <t>重複求人分析</t>
+  </si>
+  <si>
+    <t>複数サイトに載っている案件</t>
+  </si>
+  <si>
+    <t>どのサイトが一番早く掲載したか</t>
+  </si>
+  <si>
+    <t>サイトごとの掲載遅延</t>
+  </si>
+  <si>
+    <t>新技術の急上昇</t>
+  </si>
+  <si>
+    <t>前月比で急増したスキル</t>
+  </si>
+  <si>
+    <t>3か月移動平均</t>
+  </si>
+  <si>
+    <t>急上昇ランキング</t>
+  </si>
+  <si>
+    <t>技術の衰退傾向</t>
+  </si>
+  <si>
+    <t>求人数が減っている技術</t>
+  </si>
+  <si>
+    <t>長期的な推移</t>
+  </si>
+  <si>
+    <t>ただし収集サイトや収集範囲の変化には注意</t>
+  </si>
+  <si>
+    <t>AI関連求人の推移</t>
+  </si>
+  <si>
+    <t>LLM</t>
+  </si>
+  <si>
+    <t>生成AI</t>
+  </si>
+  <si>
+    <t>RAG</t>
+  </si>
+  <si>
+    <t>AIエージェント</t>
+  </si>
+  <si>
+    <t>MLOps</t>
+  </si>
+  <si>
+    <t>「自分に合う求人」分析</t>
+  </si>
+  <si>
+    <t>登録スキルとの一致率</t>
+  </si>
+  <si>
+    <t>必須スキルの充足率</t>
+  </si>
+  <si>
+    <t>希望単価</t>
+  </si>
+  <si>
+    <t>リモート条件</t>
+  </si>
+  <si>
+    <t>新着順</t>
+  </si>
+  <si>
+    <t>不足スキル分析</t>
+  </si>
+  <si>
+    <t>自分が持っていないが、求人で頻出する技術</t>
+  </si>
+  <si>
+    <t>1つ覚えたら何件応募可能になるか</t>
+  </si>
+  <si>
+    <t>学習コスパランキング</t>
+  </si>
+  <si>
+    <t>学習ロードマップ</t>
+  </si>
+  <si>
+    <t>今のスキルセット</t>
+  </si>
+  <si>
+    <t>次に追加する技術</t>
+  </si>
+  <si>
+    <t>到達可能な求人の増加数</t>
+  </si>
+  <si>
+    <t>「Go + PostgreSQLの次はDockerかAWSか」みたいな分析</t>
+  </si>
+  <si>
+    <t>求人のおすすめ順位</t>
+  </si>
+  <si>
+    <t>スキル一致度</t>
+  </si>
+  <si>
+    <t>リモート</t>
+  </si>
+  <si>
+    <t>新着度</t>
+  </si>
+  <si>
+    <t>必須条件</t>
+  </si>
+  <si>
+    <t>総合スコア</t>
+  </si>
+  <si>
+    <t>「Goの需要を見たい」</t>
+  </si>
+  <si>
+    <t>だけでも、実は定義がいくつもある。</t>
+  </si>
+  <si>
+    <t>A. 現在掲載中のGo案件数</t>
+  </si>
+  <si>
+    <t>B. 今月新しく出たGo案件数</t>
+  </si>
+  <si>
+    <t>C. Go案件の増減率</t>
+  </si>
+  <si>
+    <t>D. Go案件の平均単価</t>
+  </si>
+  <si>
+    <t>E. Go案件で一緒に要求される技術</t>
+  </si>
+  <si>
+    <t>F. Go経験者が応募可能な案件割合</t>
   </si>
 </sst>
 </file>
@@ -13897,8 +14468,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7985930" y="1467837"/>
-          <a:ext cx="1820498" cy="1167653"/>
+          <a:off x="7911971" y="1528349"/>
+          <a:ext cx="1800328" cy="1214718"/>
           <a:chOff x="8992083" y="208776"/>
           <a:chExt cx="1814762" cy="1244600"/>
         </a:xfrm>
@@ -14207,8 +14778,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="11283097" y="2938582"/>
-          <a:ext cx="1842700" cy="1889768"/>
+          <a:off x="11175520" y="3059605"/>
+          <a:ext cx="1822530" cy="1963728"/>
           <a:chOff x="8549484" y="3956874"/>
           <a:chExt cx="1810288" cy="1437363"/>
         </a:xfrm>
@@ -14759,8 +15330,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4721439" y="1597449"/>
-          <a:ext cx="1890124" cy="3208246"/>
+          <a:off x="4681098" y="1657961"/>
+          <a:ext cx="1869953" cy="3342717"/>
           <a:chOff x="5970441" y="628674"/>
           <a:chExt cx="1893913" cy="3428095"/>
         </a:xfrm>
@@ -15228,8 +15799,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10941124" y="6969538"/>
-          <a:ext cx="2220201" cy="2422569"/>
+          <a:off x="10840271" y="7258650"/>
+          <a:ext cx="2193307" cy="2523422"/>
           <a:chOff x="12007370" y="5957071"/>
           <a:chExt cx="2223130" cy="2581251"/>
         </a:xfrm>
@@ -15435,8 +16006,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14468704" y="4627977"/>
-          <a:ext cx="2246929" cy="1653108"/>
+          <a:off x="14334233" y="4816236"/>
+          <a:ext cx="2220036" cy="1720343"/>
           <a:chOff x="15050343" y="4729843"/>
           <a:chExt cx="2243515" cy="1763032"/>
         </a:xfrm>
@@ -15865,8 +16436,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6914030" y="5002306"/>
-          <a:ext cx="1795181" cy="1264024"/>
+          <a:off x="6846794" y="5210735"/>
+          <a:ext cx="1781735" cy="1311089"/>
           <a:chOff x="6846794" y="5210735"/>
           <a:chExt cx="2341399" cy="1311089"/>
         </a:xfrm>
@@ -16242,8 +16813,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3760297" y="7340331"/>
-          <a:ext cx="2355242" cy="1808149"/>
+          <a:off x="3726679" y="7642890"/>
+          <a:ext cx="2335072" cy="1882107"/>
           <a:chOff x="3726679" y="7642891"/>
           <a:chExt cx="2335072" cy="1468663"/>
         </a:xfrm>
@@ -17166,15 +17737,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6672014-33B5-48C4-9202-55E4E667EEEF}">
   <dimension ref="A1:W32"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="3.69921875" customWidth="1"/>
-    <col min="2" max="3" width="8.69921875" customWidth="1"/>
-    <col min="20" max="21" width="2.69921875" customWidth="1"/>
-    <col min="22" max="23" width="4.09765625" customWidth="1"/>
-    <col min="24" max="24" width="4.69921875" customWidth="1"/>
-    <col min="25" max="25" width="8.69921875" customWidth="1"/>
-    <col min="27" max="27" width="4.3984375" customWidth="1"/>
+    <col min="1" max="1" width="3.75" customWidth="1"/>
+    <col min="2" max="3" width="8.75" customWidth="1"/>
+    <col min="20" max="21" width="2.75" customWidth="1"/>
+    <col min="22" max="23" width="4.125" customWidth="1"/>
+    <col min="24" max="24" width="4.75" customWidth="1"/>
+    <col min="25" max="25" width="8.75" customWidth="1"/>
+    <col min="27" max="27" width="4.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -17182,25 +17753,25 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="19.2">
+    <row r="2" spans="1:23" ht="20.25">
       <c r="A2" s="108"/>
       <c r="B2" s="107" t="s">
         <v>1932</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="19.2">
+    <row r="3" spans="1:23" ht="20.25">
       <c r="A3" s="107"/>
       <c r="B3" s="107" t="s">
         <v>1933</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="19.2">
+    <row r="4" spans="1:23" ht="20.25">
       <c r="A4" s="107"/>
       <c r="B4" s="107" t="s">
         <v>1934</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="18.600000000000001" thickBot="1">
+    <row r="5" spans="1:23" ht="19.5" thickBot="1">
       <c r="V5" s="67"/>
       <c r="W5" s="67"/>
     </row>
@@ -17234,7 +17805,7 @@
       <c r="C8" s="64"/>
       <c r="W8" s="65"/>
     </row>
-    <row r="9" spans="1:23" ht="18.600000000000001" thickBot="1">
+    <row r="9" spans="1:23" ht="19.5" thickBot="1">
       <c r="C9" s="64"/>
       <c r="L9" t="s">
         <v>1706</v>
@@ -17384,7 +17955,7 @@
       <c r="V30" s="65"/>
       <c r="W30" s="65"/>
     </row>
-    <row r="31" spans="3:23" ht="18.600000000000001" thickBot="1">
+    <row r="31" spans="3:23" ht="19.5" thickBot="1">
       <c r="C31" s="64"/>
       <c r="D31" s="66"/>
       <c r="E31" s="67"/>
@@ -17407,7 +17978,7 @@
       <c r="V31" s="68"/>
       <c r="W31" s="65"/>
     </row>
-    <row r="32" spans="3:23" ht="13.2" customHeight="1" thickBot="1">
+    <row r="32" spans="3:23" ht="13.15" customHeight="1" thickBot="1">
       <c r="C32" s="66"/>
       <c r="D32" s="67"/>
       <c r="E32" s="67"/>
@@ -17439,11 +18010,11 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC349EE6-5475-4F9C-BD43-5DC02797CE07}">
-  <dimension ref="A2:Q154"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="A2:R290"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11" style="98" customWidth="1"/>
-    <col min="2" max="6" width="10.8984375" style="98" customWidth="1"/>
+    <col min="2" max="6" width="10.875" style="98" customWidth="1"/>
     <col min="7" max="16384" width="9" style="98"/>
   </cols>
   <sheetData>
@@ -17641,35 +18212,43 @@
         <v>1760</v>
       </c>
     </row>
-    <row r="33" spans="2:10">
+    <row r="33" spans="2:15">
       <c r="B33" s="98" t="s">
         <v>1737</v>
       </c>
     </row>
-    <row r="34" spans="2:10">
+    <row r="34" spans="2:15">
       <c r="B34" s="98" t="s">
         <v>1738</v>
       </c>
     </row>
-    <row r="35" spans="2:10">
+    <row r="35" spans="2:15">
       <c r="B35" s="98" t="s">
         <v>1739</v>
       </c>
     </row>
-    <row r="37" spans="2:10">
+    <row r="37" spans="2:15">
       <c r="B37" s="98" t="s">
         <v>1761</v>
       </c>
     </row>
-    <row r="38" spans="2:10">
+    <row r="38" spans="2:15">
       <c r="B38" s="98" t="s">
         <v>1762</v>
       </c>
       <c r="J38" s="109" t="s">
         <v>1715</v>
       </c>
-    </row>
-    <row r="40" spans="2:10">
+      <c r="N38" s="109" t="s">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15">
+      <c r="O39" s="98" t="s">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15">
       <c r="B40" s="109" t="s">
         <v>1729</v>
       </c>
@@ -17677,29 +18256,38 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="41" spans="2:10">
+    <row r="41" spans="2:15">
       <c r="B41" s="99"/>
       <c r="J41" s="98" t="s">
         <v>1709</v>
       </c>
-    </row>
-    <row r="42" spans="2:10">
+      <c r="O41" s="98" t="s">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15">
       <c r="B42" s="99" t="s">
         <v>1730</v>
       </c>
       <c r="J42" s="98" t="s">
         <v>1710</v>
       </c>
-    </row>
-    <row r="43" spans="2:10">
+      <c r="O42" s="98" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15">
       <c r="B43" s="99" t="s">
         <v>1731</v>
       </c>
       <c r="J43" s="98" t="s">
         <v>1711</v>
       </c>
-    </row>
-    <row r="44" spans="2:10">
+      <c r="O43" s="98" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15">
       <c r="B44" s="99" t="s">
         <v>1732</v>
       </c>
@@ -17707,15 +18295,18 @@
         <v>1719</v>
       </c>
     </row>
-    <row r="45" spans="2:10">
+    <row r="45" spans="2:15">
       <c r="B45" s="99" t="s">
         <v>1733</v>
       </c>
       <c r="J45" s="98" t="s">
         <v>1720</v>
       </c>
-    </row>
-    <row r="46" spans="2:10">
+      <c r="O45" s="98" t="s">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15">
       <c r="B46" s="99" t="s">
         <v>1734</v>
       </c>
@@ -17723,25 +18314,34 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="47" spans="2:10">
+    <row r="47" spans="2:15">
       <c r="B47" s="98" t="s">
         <v>1764</v>
       </c>
       <c r="J47" s="98" t="s">
         <v>1713</v>
       </c>
-    </row>
-    <row r="48" spans="2:10">
+      <c r="O47" s="98" t="s">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15">
       <c r="J48" s="98" t="s">
         <v>1716</v>
       </c>
-    </row>
-    <row r="49" spans="2:10">
+      <c r="O48" s="98" t="s">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15">
       <c r="J49" s="98" t="s">
         <v>1717</v>
       </c>
-    </row>
-    <row r="50" spans="2:10">
+      <c r="O49" s="98" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="50" spans="2:15">
       <c r="B50" s="109" t="s">
         <v>1959</v>
       </c>
@@ -17749,162 +18349,287 @@
         <v>1718</v>
       </c>
     </row>
-    <row r="51" spans="2:10">
+    <row r="51" spans="2:15">
       <c r="B51" s="98" t="s">
         <v>1935</v>
       </c>
       <c r="J51" s="98" t="s">
         <v>1721</v>
       </c>
-    </row>
-    <row r="52" spans="2:10">
+      <c r="O51" s="98" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="52" spans="2:15">
       <c r="B52" s="99"/>
       <c r="J52" s="98" t="s">
         <v>1722</v>
       </c>
     </row>
-    <row r="53" spans="2:10">
+    <row r="53" spans="2:15">
       <c r="B53" s="99" t="s">
         <v>1958</v>
       </c>
       <c r="J53" s="98" t="s">
         <v>1728</v>
       </c>
-    </row>
-    <row r="54" spans="2:10">
+      <c r="O53" s="98" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="54" spans="2:15">
       <c r="B54" s="99" t="s">
         <v>1967</v>
       </c>
       <c r="J54" s="98" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="55" spans="2:10">
+      <c r="O54" s="98" t="s">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="55" spans="2:15">
       <c r="B55" s="99" t="s">
         <v>1968</v>
       </c>
-    </row>
-    <row r="56" spans="2:10">
+      <c r="O55" s="98" t="s">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="56" spans="2:15">
       <c r="B56" s="99" t="s">
         <v>1936</v>
       </c>
     </row>
-    <row r="57" spans="2:10">
+    <row r="57" spans="2:15">
       <c r="B57" s="98" t="s">
         <v>1937</v>
       </c>
-    </row>
-    <row r="58" spans="2:10">
+      <c r="O57" s="98" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="58" spans="2:15">
       <c r="B58" s="98" t="s">
         <v>1956</v>
       </c>
     </row>
-    <row r="59" spans="2:10">
+    <row r="59" spans="2:15">
       <c r="B59" s="98" t="s">
         <v>1957</v>
       </c>
-    </row>
-    <row r="61" spans="2:10">
+      <c r="O59" s="98" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="60" spans="2:15">
+      <c r="O60" s="98" t="s">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="61" spans="2:15">
       <c r="B61" s="98" t="s">
         <v>1938</v>
       </c>
-    </row>
-    <row r="63" spans="2:10">
+      <c r="O61" s="98" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="63" spans="2:15">
       <c r="B63" s="98" t="s">
         <v>1939</v>
       </c>
-    </row>
-    <row r="64" spans="2:10">
+      <c r="F63" s="109" t="s">
+        <v>1979</v>
+      </c>
+      <c r="O63" s="98" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="64" spans="2:15">
       <c r="B64" s="98" t="s">
         <v>1940</v>
       </c>
     </row>
-    <row r="65" spans="2:2">
+    <row r="65" spans="2:18">
       <c r="B65" s="98" t="s">
         <v>1941</v>
       </c>
-    </row>
-    <row r="66" spans="2:2">
+      <c r="F65" s="98" t="s">
+        <v>1969</v>
+      </c>
+      <c r="O65" s="98" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18">
       <c r="B66" s="98" t="s">
         <v>1942</v>
       </c>
-    </row>
-    <row r="67" spans="2:2">
+      <c r="F66" s="98" t="s">
+        <v>1970</v>
+      </c>
+      <c r="O66" s="98" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18">
       <c r="B67" s="98" t="s">
         <v>1943</v>
       </c>
-    </row>
-    <row r="68" spans="2:2">
+      <c r="F67" s="98" t="s">
+        <v>1971</v>
+      </c>
+      <c r="O67" s="98" t="s">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="68" spans="2:18">
       <c r="B68" s="98" t="s">
         <v>1944</v>
       </c>
-    </row>
-    <row r="69" spans="2:2">
+      <c r="F68" s="98" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18">
       <c r="B69" s="98" t="s">
         <v>1945</v>
       </c>
-    </row>
-    <row r="70" spans="2:2">
+      <c r="F69" s="98" t="s">
+        <v>1973</v>
+      </c>
+      <c r="O69" s="98" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18">
       <c r="B70" s="98" t="s">
         <v>1946</v>
       </c>
-    </row>
-    <row r="71" spans="2:2">
+      <c r="F70" s="98" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18">
       <c r="B71" s="98" t="s">
         <v>1947</v>
       </c>
-    </row>
-    <row r="72" spans="2:2">
+      <c r="F71" s="98" t="s">
+        <v>1975</v>
+      </c>
+      <c r="O71" s="98" t="s">
+        <v>2060</v>
+      </c>
+      <c r="R71" s="98" t="s">
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18">
       <c r="B72" s="98" t="s">
         <v>1948</v>
       </c>
-    </row>
-    <row r="73" spans="2:2">
+      <c r="F72" s="98" t="s">
+        <v>1976</v>
+      </c>
+      <c r="O72" s="98" t="s">
+        <v>2061</v>
+      </c>
+      <c r="R72" s="98" t="s">
+        <v>2219</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18">
       <c r="B73" s="98" t="s">
         <v>1949</v>
       </c>
-    </row>
-    <row r="74" spans="2:2">
+      <c r="F73" s="98" t="s">
+        <v>1977</v>
+      </c>
+      <c r="O73" s="98" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18">
       <c r="B74" s="98" t="s">
         <v>1950</v>
       </c>
-    </row>
-    <row r="75" spans="2:2">
+      <c r="F74" s="98" t="s">
+        <v>1978</v>
+      </c>
+      <c r="O74" s="98" t="s">
+        <v>2063</v>
+      </c>
+      <c r="R74" s="98" t="s">
+        <v>2220</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18">
       <c r="B75" s="98" t="s">
         <v>1951</v>
       </c>
-    </row>
-    <row r="76" spans="2:2">
+      <c r="O75" s="98" t="s">
+        <v>2064</v>
+      </c>
+      <c r="R75" s="98" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18">
       <c r="B76" s="98" t="s">
         <v>1952</v>
       </c>
-    </row>
-    <row r="77" spans="2:2">
+      <c r="O76" s="98" t="s">
+        <v>2065</v>
+      </c>
+      <c r="R76" s="98" t="s">
+        <v>2222</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18">
       <c r="B77" s="98" t="s">
         <v>1953</v>
       </c>
-    </row>
-    <row r="78" spans="2:2">
+      <c r="O77" s="98" t="s">
+        <v>2066</v>
+      </c>
+      <c r="R77" s="98" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="78" spans="2:18">
       <c r="B78" s="98" t="s">
         <v>1954</v>
       </c>
-    </row>
-    <row r="79" spans="2:2">
+      <c r="R78" s="98" t="s">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18">
       <c r="B79" s="98" t="s">
         <v>1955</v>
       </c>
-    </row>
-    <row r="81" spans="1:13">
-      <c r="M81" s="109" t="s">
-        <v>1979</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13">
+      <c r="O79" s="98" t="s">
+        <v>2067</v>
+      </c>
+      <c r="R79" s="98" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15">
+      <c r="O81" s="98" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15">
       <c r="B82" s="109" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="83" spans="1:13">
+      <c r="O82" s="98" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15">
       <c r="A83" s="98" t="s">
         <v>1966</v>
       </c>
@@ -17920,16 +18645,16 @@
       <c r="I83" s="98" t="s">
         <v>2017</v>
       </c>
-      <c r="M83" s="98" t="s">
-        <v>1969</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13">
-      <c r="M84" s="98" t="s">
-        <v>1970</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13">
+      <c r="O83" s="98" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15">
+      <c r="O84" s="98" t="s">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15">
       <c r="B85" s="98" t="s">
         <v>1980</v>
       </c>
@@ -17942,11 +18667,8 @@
       <c r="I85" s="98" t="s">
         <v>1965</v>
       </c>
-      <c r="M85" s="98" t="s">
-        <v>1971</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13">
+    </row>
+    <row r="86" spans="1:15">
       <c r="E86" s="98" t="s">
         <v>2018</v>
       </c>
@@ -17962,304 +18684,951 @@
       <c r="J86" s="98" t="s">
         <v>2016</v>
       </c>
-      <c r="M86" s="98" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13">
+      <c r="O86" s="98" t="s">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15">
       <c r="B87" s="98" t="s">
         <v>1981</v>
       </c>
       <c r="E87" s="98" t="s">
         <v>2019</v>
       </c>
-      <c r="M87" s="98" t="s">
-        <v>1973</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13">
+    </row>
+    <row r="88" spans="1:15">
       <c r="B88" s="98" t="s">
         <v>1982</v>
       </c>
       <c r="E88" s="98" t="s">
         <v>2022</v>
       </c>
-      <c r="M88" s="98" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13">
-      <c r="M89" s="98" t="s">
-        <v>1975</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13">
+      <c r="O88" s="98" t="s">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15">
+      <c r="O89" s="98" t="s">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15">
       <c r="B90" s="98" t="s">
         <v>1983</v>
       </c>
-      <c r="M90" s="98" t="s">
-        <v>1976</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13">
+      <c r="O90" s="98" t="s">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15">
       <c r="B91" s="98" t="s">
         <v>1984</v>
       </c>
-      <c r="M91" s="98" t="s">
-        <v>1977</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13">
+      <c r="O91" s="98" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15">
       <c r="B92" s="98" t="s">
         <v>1985</v>
       </c>
-      <c r="M92" s="98" t="s">
-        <v>1978</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13">
+      <c r="O92" s="98" t="s">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15">
       <c r="B93" s="98" t="s">
         <v>1986</v>
       </c>
-    </row>
-    <row r="94" spans="1:13">
+      <c r="O93" s="98" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15">
       <c r="B94" s="98" t="s">
         <v>1987</v>
       </c>
     </row>
-    <row r="96" spans="1:13">
+    <row r="95" spans="1:15">
+      <c r="O95" s="98" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15">
       <c r="B96" s="98" t="s">
         <v>1988</v>
       </c>
     </row>
-    <row r="97" spans="2:2">
+    <row r="97" spans="2:15">
       <c r="B97" s="98" t="s">
         <v>1989</v>
       </c>
-    </row>
-    <row r="98" spans="2:2">
+      <c r="O97" s="98" t="s">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="98" spans="2:15">
       <c r="B98" s="98" t="s">
         <v>1990</v>
       </c>
-    </row>
-    <row r="100" spans="2:2">
+      <c r="O98" s="98" t="s">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="99" spans="2:15">
+      <c r="O99" s="98" t="s">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="100" spans="2:15">
       <c r="B100" s="98" t="s">
         <v>1991</v>
       </c>
-    </row>
-    <row r="101" spans="2:2">
+      <c r="O100" s="98" t="s">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="101" spans="2:15">
       <c r="B101" s="98" t="s">
         <v>1992</v>
       </c>
     </row>
-    <row r="103" spans="2:2">
+    <row r="102" spans="2:15">
+      <c r="O102" s="98" t="s">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="103" spans="2:15">
       <c r="B103" s="98" t="s">
         <v>1993</v>
       </c>
     </row>
-    <row r="104" spans="2:2">
+    <row r="104" spans="2:15">
       <c r="B104" s="98" t="s">
         <v>1994</v>
       </c>
-    </row>
-    <row r="105" spans="2:2">
+      <c r="O104" s="98" t="s">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="105" spans="2:15">
       <c r="B105" s="98" t="s">
         <v>1995</v>
       </c>
-    </row>
-    <row r="107" spans="2:2">
+      <c r="O105" s="98" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="106" spans="2:15">
+      <c r="O106" s="98" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="107" spans="2:15">
       <c r="B107" s="98" t="s">
         <v>1996</v>
       </c>
     </row>
-    <row r="108" spans="2:2">
+    <row r="108" spans="2:15">
       <c r="B108" s="98" t="s">
         <v>1997</v>
       </c>
-    </row>
-    <row r="109" spans="2:2">
+      <c r="O108" s="98" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="109" spans="2:15">
       <c r="B109" s="98" t="s">
         <v>1998</v>
       </c>
     </row>
-    <row r="110" spans="2:2">
+    <row r="110" spans="2:15">
       <c r="B110" s="98" t="s">
         <v>1999</v>
       </c>
-    </row>
-    <row r="111" spans="2:2">
+      <c r="O110" s="98" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="111" spans="2:15">
       <c r="B111" s="98" t="s">
         <v>2000</v>
       </c>
-    </row>
-    <row r="116" spans="1:2">
+      <c r="O111" s="98" t="s">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="112" spans="2:15">
+      <c r="O112" s="98" t="s">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15">
+      <c r="O113" s="98" t="s">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15">
+      <c r="O114" s="98" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15">
+      <c r="O115" s="98" t="s">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15">
       <c r="A116" s="98" t="s">
         <v>2001</v>
       </c>
-    </row>
-    <row r="117" spans="1:2">
+      <c r="O116" s="98" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15">
       <c r="B117" s="98" t="s">
         <v>2002</v>
       </c>
-    </row>
-    <row r="118" spans="1:2">
+      <c r="O117" s="98" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15">
       <c r="B118" s="98" t="s">
         <v>2003</v>
       </c>
-    </row>
-    <row r="120" spans="1:2">
+      <c r="O118" s="98" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15">
       <c r="B120" s="98" t="s">
         <v>2004</v>
       </c>
-    </row>
-    <row r="121" spans="1:2">
+      <c r="O120" s="98" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15">
       <c r="B121" s="98" t="s">
         <v>2005</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
+    <row r="122" spans="1:15">
+      <c r="O122" s="98" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15">
       <c r="B123" s="98" t="s">
         <v>2006</v>
       </c>
-    </row>
-    <row r="124" spans="1:2">
+      <c r="O123" s="98" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15">
       <c r="B124" s="98" t="s">
         <v>2009</v>
       </c>
-    </row>
-    <row r="125" spans="1:2">
+      <c r="O124" s="98" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15">
       <c r="B125" s="98" t="s">
         <v>2010</v>
       </c>
-    </row>
-    <row r="126" spans="1:2">
+      <c r="O125" s="98" t="s">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15">
       <c r="B126" s="98" t="s">
         <v>2013</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
+    <row r="127" spans="1:15">
       <c r="B127" s="98" t="s">
         <v>2011</v>
       </c>
-    </row>
-    <row r="129" spans="1:2">
+      <c r="O127" s="98" t="s">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15">
       <c r="B129" s="98" t="s">
         <v>2007</v>
       </c>
-    </row>
-    <row r="130" spans="1:2">
+      <c r="O129" s="98" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15">
       <c r="B130" s="98" t="s">
         <v>2012</v>
       </c>
-    </row>
-    <row r="131" spans="1:2">
+      <c r="O130" s="98" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15">
       <c r="B131" s="98" t="s">
         <v>2008</v>
       </c>
-    </row>
-    <row r="134" spans="1:2">
+      <c r="O131" s="98" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15">
+      <c r="O132" s="98" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15">
+      <c r="O133" s="98" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15">
       <c r="A134" s="98" t="s">
         <v>2024</v>
       </c>
     </row>
-    <row r="135" spans="1:2">
+    <row r="135" spans="1:15">
       <c r="B135" s="98" t="s">
         <v>2025</v>
       </c>
-    </row>
-    <row r="136" spans="1:2">
+      <c r="O135" s="98" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15">
       <c r="B136" s="98" t="s">
         <v>1842</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
+    <row r="137" spans="1:15">
       <c r="B137" s="98" t="s">
         <v>2026</v>
       </c>
-    </row>
-    <row r="138" spans="1:2">
+      <c r="O137" s="98" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15">
       <c r="B138" s="98" t="s">
         <v>2027</v>
       </c>
-    </row>
-    <row r="139" spans="1:2">
+      <c r="O138" s="98" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15">
       <c r="B139" s="98" t="s">
         <v>1842</v>
       </c>
-    </row>
-    <row r="140" spans="1:2">
+      <c r="O139" s="98" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15">
       <c r="B140" s="98" t="s">
         <v>2028</v>
       </c>
-    </row>
-    <row r="141" spans="1:2">
+      <c r="O140" s="98" t="s">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15">
       <c r="B141" s="98" t="s">
         <v>1842</v>
       </c>
     </row>
-    <row r="142" spans="1:2">
+    <row r="142" spans="1:15">
       <c r="B142" s="98" t="s">
         <v>2029</v>
       </c>
-    </row>
-    <row r="143" spans="1:2">
+      <c r="O142" s="98" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15">
       <c r="B143" s="98" t="s">
         <v>1842</v>
       </c>
     </row>
-    <row r="144" spans="1:2">
+    <row r="144" spans="1:15">
       <c r="B144" s="98" t="s">
         <v>2030</v>
       </c>
-    </row>
-    <row r="145" spans="2:2">
+      <c r="O144" s="98" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="145" spans="2:15">
       <c r="B145" s="98" t="s">
         <v>2031</v>
       </c>
-    </row>
-    <row r="146" spans="2:2">
+      <c r="O145" s="98" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="146" spans="2:15">
       <c r="B146" s="98" t="s">
         <v>2032</v>
       </c>
-    </row>
-    <row r="147" spans="2:2">
+      <c r="O146" s="98" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="147" spans="2:15">
       <c r="B147" s="98" t="s">
         <v>2033</v>
       </c>
-    </row>
-    <row r="148" spans="2:2">
+      <c r="O147" s="98" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="148" spans="2:15">
       <c r="B148" s="98" t="s">
         <v>2034</v>
       </c>
     </row>
-    <row r="149" spans="2:2">
+    <row r="149" spans="2:15">
       <c r="B149" s="98" t="s">
         <v>2033</v>
       </c>
-    </row>
-    <row r="150" spans="2:2">
+      <c r="O149" s="98" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="150" spans="2:15">
       <c r="B150" s="98" t="s">
         <v>2035</v>
       </c>
     </row>
-    <row r="151" spans="2:2">
+    <row r="151" spans="2:15">
       <c r="B151" s="98" t="s">
         <v>2033</v>
       </c>
-    </row>
-    <row r="152" spans="2:2">
+      <c r="O151" s="98" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="152" spans="2:15">
       <c r="B152" s="98" t="s">
         <v>2036</v>
       </c>
-    </row>
-    <row r="153" spans="2:2">
+      <c r="O152" s="98" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="153" spans="2:15">
       <c r="B153" s="98" t="s">
         <v>2033</v>
       </c>
-    </row>
-    <row r="154" spans="2:2">
+      <c r="O153" s="98" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="154" spans="2:15">
       <c r="B154" s="98" t="s">
         <v>2037</v>
+      </c>
+      <c r="O154" s="98" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="156" spans="2:15">
+      <c r="O156" s="98" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="158" spans="2:15">
+      <c r="O158" s="98" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="159" spans="2:15">
+      <c r="O159" s="98" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="160" spans="2:15">
+      <c r="O160" s="98" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="161" spans="15:15">
+      <c r="O161" s="98" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="162" spans="15:15">
+      <c r="O162" s="98" t="s">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="163" spans="15:15">
+      <c r="O163" s="98" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="165" spans="15:15">
+      <c r="O165" s="98" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="167" spans="15:15">
+      <c r="O167" s="98" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="168" spans="15:15">
+      <c r="O168" s="98" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="169" spans="15:15">
+      <c r="O169" s="98" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="171" spans="15:15">
+      <c r="O171" s="98" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="173" spans="15:15">
+      <c r="O173" s="98" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="174" spans="15:15">
+      <c r="O174" s="98" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="175" spans="15:15">
+      <c r="O175" s="98" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="176" spans="15:15">
+      <c r="O176" s="98" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="177" spans="15:15">
+      <c r="O177" s="98" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="179" spans="15:15">
+      <c r="O179" s="98" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="181" spans="15:15">
+      <c r="O181" s="98" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="182" spans="15:15">
+      <c r="O182" s="98" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="183" spans="15:15">
+      <c r="O183" s="98" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="184" spans="15:15">
+      <c r="O184" s="98" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="185" spans="15:15">
+      <c r="O185" s="98" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="187" spans="15:15">
+      <c r="O187" s="98" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="189" spans="15:15">
+      <c r="O189" s="98" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="190" spans="15:15">
+      <c r="O190" s="98" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="191" spans="15:15">
+      <c r="O191" s="98" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="192" spans="15:15">
+      <c r="O192" s="98" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="193" spans="15:15">
+      <c r="O193" s="98" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="194" spans="15:15">
+      <c r="O194" s="98" t="s">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="196" spans="15:15">
+      <c r="O196" s="98" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="198" spans="15:15">
+      <c r="O198" s="98" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="199" spans="15:15">
+      <c r="O199" s="98" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="200" spans="15:15">
+      <c r="O200" s="98" t="s">
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="201" spans="15:15">
+      <c r="O201" s="98" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="203" spans="15:15">
+      <c r="O203" s="98" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="205" spans="15:15">
+      <c r="O205" s="98" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="206" spans="15:15">
+      <c r="O206" s="98" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="207" spans="15:15">
+      <c r="O207" s="98" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="209" spans="15:15">
+      <c r="O209" s="98" t="s">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="211" spans="15:15">
+      <c r="O211" s="98" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="212" spans="15:15">
+      <c r="O212" s="98" t="s">
+        <v>2163</v>
+      </c>
+    </row>
+    <row r="213" spans="15:15">
+      <c r="O213" s="98" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="215" spans="15:15">
+      <c r="O215" s="98" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="217" spans="15:15">
+      <c r="O217" s="98" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="218" spans="15:15">
+      <c r="O218" s="98" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="219" spans="15:15">
+      <c r="O219" s="98" t="s">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="221" spans="15:15">
+      <c r="O221" s="98" t="s">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="223" spans="15:15">
+      <c r="O223" s="98" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="224" spans="15:15">
+      <c r="O224" s="98" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="225" spans="15:15">
+      <c r="O225" s="98" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="227" spans="15:15">
+      <c r="O227" s="98" t="s">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="229" spans="15:15">
+      <c r="O229" s="98" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="230" spans="15:15">
+      <c r="O230" s="98" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="231" spans="15:15">
+      <c r="O231" s="98" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="232" spans="15:15">
+      <c r="O232" s="98" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="233" spans="15:15">
+      <c r="O233" s="98" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="235" spans="15:15">
+      <c r="O235" s="98" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="237" spans="15:15">
+      <c r="O237" s="98" t="s">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="238" spans="15:15">
+      <c r="O238" s="98" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="239" spans="15:15">
+      <c r="O239" s="98" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="241" spans="15:15">
+      <c r="O241" s="98" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="243" spans="15:15">
+      <c r="O243" s="98" t="s">
+        <v>2184</v>
+      </c>
+    </row>
+    <row r="244" spans="15:15">
+      <c r="O244" s="98" t="s">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="245" spans="15:15">
+      <c r="O245" s="98" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="247" spans="15:15">
+      <c r="O247" s="98" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="249" spans="15:15">
+      <c r="O249" s="98" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="250" spans="15:15">
+      <c r="O250" s="98" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="251" spans="15:15">
+      <c r="O251" s="98" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="253" spans="15:15">
+      <c r="O253" s="98" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="255" spans="15:15">
+      <c r="O255" s="98" t="s">
+        <v>2192</v>
+      </c>
+    </row>
+    <row r="256" spans="15:15">
+      <c r="O256" s="98" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="257" spans="15:15">
+      <c r="O257" s="98" t="s">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="258" spans="15:15">
+      <c r="O258" s="98" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="259" spans="15:15">
+      <c r="O259" s="98" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="260" spans="15:15">
+      <c r="O260" s="98" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="262" spans="15:15">
+      <c r="O262" s="98" t="s">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="264" spans="15:15">
+      <c r="O264" s="98" t="s">
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="265" spans="15:15">
+      <c r="O265" s="98" t="s">
+        <v>2199</v>
+      </c>
+    </row>
+    <row r="266" spans="15:15">
+      <c r="O266" s="98" t="s">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="267" spans="15:15">
+      <c r="O267" s="98" t="s">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="268" spans="15:15">
+      <c r="O268" s="98" t="s">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="270" spans="15:15">
+      <c r="O270" s="98" t="s">
+        <v>2203</v>
+      </c>
+    </row>
+    <row r="272" spans="15:15">
+      <c r="O272" s="98" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="273" spans="15:15">
+      <c r="O273" s="98" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="274" spans="15:15">
+      <c r="O274" s="98" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="276" spans="15:15">
+      <c r="O276" s="98" t="s">
+        <v>2207</v>
+      </c>
+    </row>
+    <row r="278" spans="15:15">
+      <c r="O278" s="98" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="279" spans="15:15">
+      <c r="O279" s="98" t="s">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="280" spans="15:15">
+      <c r="O280" s="98" t="s">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="281" spans="15:15">
+      <c r="O281" s="98" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="283" spans="15:15">
+      <c r="O283" s="98" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="285" spans="15:15">
+      <c r="O285" s="98" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="286" spans="15:15">
+      <c r="O286" s="98" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="287" spans="15:15">
+      <c r="O287" s="98" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="288" spans="15:15">
+      <c r="O288" s="98" t="s">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="289" spans="15:15">
+      <c r="O289" s="98" t="s">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="290" spans="15:15">
+      <c r="O290" s="98" t="s">
+        <v>2217</v>
       </c>
     </row>
   </sheetData>
@@ -18272,10 +19641,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F0B575-2DDF-49B9-8DE2-F372EEC2F3B3}">
   <dimension ref="A2:O79"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.8984375" style="1" customWidth="1"/>
-    <col min="2" max="6" width="10.8984375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.875" style="1" customWidth="1"/>
+    <col min="2" max="6" width="10.875" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -18307,7 +19676,7 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="18">
+    <row r="4" spans="1:15" ht="18.75">
       <c r="A4" s="1" t="s">
         <v>1280</v>
       </c>
@@ -18336,7 +19705,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="13.2">
+    <row r="5" spans="1:15">
       <c r="B5" s="58" t="s">
         <v>1175</v>
       </c>
@@ -18353,7 +19722,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="13.2">
+    <row r="6" spans="1:15">
       <c r="B6" s="58" t="s">
         <v>1176</v>
       </c>
@@ -18376,7 +19745,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="13.2">
+    <row r="7" spans="1:15">
       <c r="B7" s="58" t="s">
         <v>1189</v>
       </c>
@@ -18405,7 +19774,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="13.2">
+    <row r="8" spans="1:15">
       <c r="B8" s="58" t="s">
         <v>1177</v>
       </c>
@@ -18434,7 +19803,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="13.2">
+    <row r="9" spans="1:15">
       <c r="B9" s="58" t="s">
         <v>1178</v>
       </c>
@@ -18460,7 +19829,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="13.2">
+    <row r="10" spans="1:15">
       <c r="B10" s="58" t="s">
         <v>1179</v>
       </c>
@@ -18486,7 +19855,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="13.2">
+    <row r="11" spans="1:15">
       <c r="B11" s="58" t="s">
         <v>1180</v>
       </c>
@@ -18512,7 +19881,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="13.2">
+    <row r="12" spans="1:15">
       <c r="B12" s="58" t="s">
         <v>1181</v>
       </c>
@@ -18538,7 +19907,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="13.2">
+    <row r="13" spans="1:15">
       <c r="B13" s="58" t="s">
         <v>1182</v>
       </c>
@@ -18561,7 +19930,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="13.2">
+    <row r="14" spans="1:15">
       <c r="B14" s="58" t="s">
         <v>1183</v>
       </c>
@@ -18584,7 +19953,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="13.2">
+    <row r="15" spans="1:15">
       <c r="B15" s="58" t="s">
         <v>1184</v>
       </c>
@@ -18607,7 +19976,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="13.2">
+    <row r="16" spans="1:15">
       <c r="B16" s="58" t="s">
         <v>1185</v>
       </c>
@@ -18627,7 +19996,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="17" spans="2:10" ht="13.2">
+    <row r="17" spans="2:10">
       <c r="B17" s="58" t="s">
         <v>1186</v>
       </c>
@@ -18647,7 +20016,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="18" spans="2:10" ht="13.2">
+    <row r="18" spans="2:10">
       <c r="B18" s="58" t="s">
         <v>1190</v>
       </c>
@@ -18667,7 +20036,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="19" spans="2:10" ht="13.2">
+    <row r="19" spans="2:10">
       <c r="B19" s="58" t="s">
         <v>1187</v>
       </c>
@@ -18687,7 +20056,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="20" spans="2:10" ht="13.2">
+    <row r="20" spans="2:10">
       <c r="B20" s="58" t="s">
         <v>1191</v>
       </c>
@@ -19232,9 +20601,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FCFD5C-696C-43AD-A2BD-D69C05CB2D44}">
   <dimension ref="B2:P57"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="16384" width="8.69921875" style="1"/>
+    <col min="1" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
@@ -19710,9 +21079,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E898285-845A-4583-B20D-F3A331C07E8E}">
   <dimension ref="B2:R45"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="13" max="13" width="8.59765625" customWidth="1"/>
+    <col min="13" max="13" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18">
@@ -19727,7 +21096,7 @@
       <c r="O2" s="86"/>
       <c r="P2" s="86"/>
     </row>
-    <row r="3" spans="2:18" ht="18.600000000000001" thickBot="1">
+    <row r="3" spans="2:18" ht="19.5" thickBot="1">
       <c r="F3" s="89" t="s">
         <v>1582</v>
       </c>
@@ -19849,7 +21218,7 @@
       <c r="P10" s="65"/>
       <c r="R10" s="84"/>
     </row>
-    <row r="11" spans="2:18" ht="18.600000000000001" thickBot="1">
+    <row r="11" spans="2:18" ht="19.5" thickBot="1">
       <c r="F11" s="91"/>
       <c r="I11" s="75"/>
       <c r="J11" s="66"/>
@@ -19938,7 +21307,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="22" spans="4:18" ht="18.600000000000001" thickBot="1">
+    <row r="22" spans="4:18" ht="19.5" thickBot="1">
       <c r="D22" s="80"/>
       <c r="E22" s="81"/>
       <c r="F22" s="81"/>
@@ -20067,7 +21436,7 @@
       </c>
       <c r="N29" s="84"/>
     </row>
-    <row r="30" spans="4:18" ht="18.600000000000001" thickBot="1">
+    <row r="30" spans="4:18" ht="19.5" thickBot="1">
       <c r="D30" s="83"/>
       <c r="E30" s="77"/>
       <c r="F30" s="78"/>
@@ -20303,11 +21672,11 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD79B98E-03E4-44E6-9FBF-39CA1C89C95A}">
   <dimension ref="B3:L149"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="8.69921875" style="73"/>
-    <col min="3" max="3" width="10.59765625" customWidth="1"/>
-    <col min="6" max="6" width="10.8984375" customWidth="1"/>
+    <col min="2" max="2" width="8.75" style="73"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="6" max="6" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:10">
@@ -21087,7 +22456,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="5"/>
   </cols>
@@ -21101,7 +22470,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBD988A-503C-4F44-AC4A-B26683FC9B4C}">
   <dimension ref="B4:O34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="5"/>
   </cols>
@@ -21252,14 +22621,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
   <dimension ref="B4:K166"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="2" width="20.19921875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="24.09765625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.25" style="5" customWidth="1"/>
+    <col min="3" max="3" width="24.125" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" style="5" customWidth="1"/>
     <col min="5" max="8" width="9" style="5"/>
-    <col min="9" max="9" width="45.59765625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="45.625" style="5" customWidth="1"/>
     <col min="10" max="22" width="9" style="5"/>
     <col min="23" max="23" width="8" style="5" customWidth="1"/>
     <col min="24" max="16384" width="9" style="5"/>
@@ -25613,22 +26982,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EB7090A-0065-41E7-85DA-75EEB9504A67}">
   <dimension ref="C3:Q81"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="7.5" style="5" customWidth="1"/>
-    <col min="3" max="3" width="13.69921875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="13.75" style="5" customWidth="1"/>
     <col min="4" max="4" width="20" style="5" customWidth="1"/>
-    <col min="5" max="5" width="30.59765625" style="5" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="13.3984375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="30.625" style="5" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="13.375" style="5" customWidth="1"/>
     <col min="7" max="7" width="11" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.19921875" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.69921875" style="5" customWidth="1"/>
-    <col min="10" max="12" width="9.8984375" style="18" customWidth="1"/>
-    <col min="13" max="13" width="9.19921875" style="18" customWidth="1"/>
-    <col min="14" max="14" width="12.59765625" style="18" customWidth="1"/>
-    <col min="15" max="15" width="27.09765625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="15.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.75" style="5" customWidth="1"/>
+    <col min="10" max="12" width="9.875" style="18" customWidth="1"/>
+    <col min="13" max="13" width="9.25" style="18" customWidth="1"/>
+    <col min="14" max="14" width="12.625" style="18" customWidth="1"/>
+    <col min="15" max="15" width="27.125" style="5" customWidth="1"/>
     <col min="16" max="16" width="7.5" style="5" customWidth="1"/>
-    <col min="17" max="17" width="15.09765625" style="5" customWidth="1"/>
+    <col min="17" max="17" width="15.125" style="5" customWidth="1"/>
     <col min="18" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -27292,7 +28661,7 @@
         <v>INSERT INTO m_skill VALUES ('skill037','グラビジャ',4,0,0,1,75,50,0.0,1,1200,'現HPの７５％ダメージ');</v>
       </c>
     </row>
-    <row r="41" spans="3:17" ht="37.799999999999997">
+    <row r="41" spans="3:17" ht="40.5">
       <c r="C41" s="47" t="s">
         <v>1048</v>
       </c>
@@ -29044,10 +30413,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F51B408-D4E3-46FE-97DE-15AB67B6AAB6}">
   <dimension ref="B1:Q100"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="2" width="12.69921875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="5" customWidth="1"/>
     <col min="3" max="3" width="17.5" style="5" customWidth="1"/>
     <col min="4" max="16384" width="9" style="5"/>
   </cols>
@@ -31863,22 +33232,22 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E63A27D9-C8B6-491D-9205-8D7433312F14}">
   <dimension ref="A4:U522"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="12.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.8984375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.59765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.625" style="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="12.69921875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="5.3984375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14.09765625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.75" style="3" customWidth="1"/>
+    <col min="8" max="8" width="5.375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="14.125" style="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="1"/>
-    <col min="12" max="12" width="17.69921875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.75" style="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1"/>
-    <col min="14" max="14" width="5.19921875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="5.25" style="1" customWidth="1"/>
     <col min="15" max="20" width="9" style="1"/>
-    <col min="21" max="21" width="8.8984375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="8.875" style="1" customWidth="1"/>
     <col min="22" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -48471,7 +49840,7 @@
         <v>INSERT INTO m_monster_skills VALUES ('myskill0505','monster084','skill051',FALSE);</v>
       </c>
     </row>
-    <row r="510" spans="1:21" ht="18">
+    <row r="510" spans="1:21" ht="18.75">
       <c r="A510"/>
       <c r="B510"/>
       <c r="C510"/>
@@ -48494,7 +49863,7 @@
       <c r="T510"/>
       <c r="U510"/>
     </row>
-    <row r="511" spans="1:21" ht="18">
+    <row r="511" spans="1:21" ht="18.75">
       <c r="A511"/>
       <c r="B511"/>
       <c r="C511"/>
@@ -48517,7 +49886,7 @@
       <c r="T511"/>
       <c r="U511"/>
     </row>
-    <row r="512" spans="1:21" ht="18">
+    <row r="512" spans="1:21" ht="18.75">
       <c r="A512"/>
       <c r="B512"/>
       <c r="C512"/>
@@ -48540,7 +49909,7 @@
       <c r="T512"/>
       <c r="U512"/>
     </row>
-    <row r="513" spans="1:21" ht="18">
+    <row r="513" spans="1:21" ht="18.75">
       <c r="A513"/>
       <c r="B513"/>
       <c r="C513"/>
@@ -48563,7 +49932,7 @@
       <c r="T513"/>
       <c r="U513"/>
     </row>
-    <row r="514" spans="1:21" ht="18">
+    <row r="514" spans="1:21" ht="18.75">
       <c r="A514"/>
       <c r="B514"/>
       <c r="C514"/>
@@ -48586,7 +49955,7 @@
       <c r="T514"/>
       <c r="U514"/>
     </row>
-    <row r="515" spans="1:21" ht="18">
+    <row r="515" spans="1:21" ht="18.75">
       <c r="A515"/>
       <c r="B515"/>
       <c r="C515"/>
@@ -48609,7 +49978,7 @@
       <c r="T515"/>
       <c r="U515"/>
     </row>
-    <row r="516" spans="1:21" ht="18">
+    <row r="516" spans="1:21" ht="18.75">
       <c r="A516"/>
       <c r="B516"/>
       <c r="C516"/>
@@ -48632,7 +50001,7 @@
       <c r="T516"/>
       <c r="U516"/>
     </row>
-    <row r="517" spans="1:21" ht="18">
+    <row r="517" spans="1:21" ht="18.75">
       <c r="A517"/>
       <c r="B517"/>
       <c r="C517"/>
@@ -48655,7 +50024,7 @@
       <c r="T517"/>
       <c r="U517"/>
     </row>
-    <row r="518" spans="1:21" ht="18">
+    <row r="518" spans="1:21" ht="18.75">
       <c r="A518"/>
       <c r="B518"/>
       <c r="C518"/>
@@ -48678,7 +50047,7 @@
       <c r="T518"/>
       <c r="U518"/>
     </row>
-    <row r="519" spans="1:21" ht="18">
+    <row r="519" spans="1:21" ht="18.75">
       <c r="A519"/>
       <c r="B519"/>
       <c r="C519"/>
@@ -48701,7 +50070,7 @@
       <c r="T519"/>
       <c r="U519"/>
     </row>
-    <row r="520" spans="1:21" ht="18">
+    <row r="520" spans="1:21" ht="18.75">
       <c r="A520"/>
       <c r="B520"/>
       <c r="C520"/>
@@ -48724,7 +50093,7 @@
       <c r="T520"/>
       <c r="U520"/>
     </row>
-    <row r="521" spans="1:21" ht="18">
+    <row r="521" spans="1:21" ht="18.75">
       <c r="A521"/>
       <c r="B521"/>
       <c r="C521"/>
@@ -48747,7 +50116,7 @@
       <c r="T521"/>
       <c r="U521"/>
     </row>
-    <row r="522" spans="1:21" ht="18">
+    <row r="522" spans="1:21" ht="18.75">
       <c r="A522"/>
       <c r="B522"/>
       <c r="C522"/>
@@ -48779,15 +50148,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A843E7EA-D614-495E-86B7-D31F628C6221}">
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="3" width="17.19921875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="17.25" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.59765625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.69921875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="11.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.75" style="5" customWidth="1"/>
     <col min="7" max="7" width="13.5" style="5" customWidth="1"/>
-    <col min="8" max="8" width="11.8984375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="11.875" style="5" customWidth="1"/>
     <col min="9" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -49148,13 +50517,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE71EC6-0DD3-461C-A8FC-74E22154B7A5}">
   <dimension ref="A4:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="3.8984375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="3.875" style="1" customWidth="1"/>
     <col min="2" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="4.19921875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="95.19921875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.8984375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="4.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="95.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.875" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D03988-952F-4CD7-A827-29D15097EA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D50EB4-36DF-4A89-9A37-9DA17336751B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="778" firstSheet="3" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="3" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="architecture" sheetId="12" r:id="rId1"/>
@@ -8486,74 +8486,7 @@
     <t>まず最優先。案件数が多い</t>
   </si>
   <si>
-    <t>フリジョブ — 複数の案件サイト・エージェントの公開案件を横断検索</t>
-  </si>
-  <si>
-    <t>フリーランスフリー — 1,000件以上のIT案件</t>
-  </si>
-  <si>
     <t>さらに候補</t>
-  </si>
-  <si>
-    <t>レバテックフリーランス</t>
-  </si>
-  <si>
-    <t>Midworks</t>
-  </si>
-  <si>
-    <t>TechStock</t>
-  </si>
-  <si>
-    <t>PE-BANK</t>
-  </si>
-  <si>
-    <t>ギークスジョブ</t>
-  </si>
-  <si>
-    <t>テックリーチ</t>
-  </si>
-  <si>
-    <t>Findy Freelance</t>
-  </si>
-  <si>
-    <t>エンジニアファクトリー</t>
-  </si>
-  <si>
-    <t>フォスターフリーランス</t>
-  </si>
-  <si>
-    <t>フリーランススタート</t>
-  </si>
-  <si>
-    <t>テクフリ</t>
-  </si>
-  <si>
-    <t>doocyJob</t>
-  </si>
-  <si>
-    <t>案件ナビ</t>
-  </si>
-  <si>
-    <t>エンジニアスタイル東京</t>
-  </si>
-  <si>
-    <t>テックビズフリーランス</t>
-  </si>
-  <si>
-    <t>ポテパンフリーランス</t>
-  </si>
-  <si>
-    <t>PE-BANK案件検索</t>
-  </si>
-  <si>
-    <t>TechSpace — 会員登録なしで案件閲覧可能。エンド直・元請直案件も検索対象</t>
-  </si>
-  <si>
-    <t>ENGER — 公開案件は多数。ただし案件詳細の閲覧には登録が必要なものあり</t>
-  </si>
-  <si>
-    <t>フリーランスHub — 37万件超。Java、C#/.NET、Go、TypeScriptなどで大量検索可能</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>クローラー対象</t>
@@ -8597,14 +8530,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>SES JOB LINK — 4.4万件超。SES/業務委託案件を大量に見られる</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>エイジレスフリーランス — 6,800件前後。年齢不問を掲げるIT案件サイト</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>案件テーブル</t>
   </si>
   <si>
@@ -9436,6 +9361,84 @@
   </si>
   <si>
     <t>F. Go経験者が応募可能な案件割合</t>
+  </si>
+  <si>
+    <t>- フリーランスHub（370,000件前後） — Java、C#/.NET、Go、TypeScriptなどで大量検索可能</t>
+  </si>
+  <si>
+    <t>- SES JOB LINK（44,000件前後） — SES/業務委託案件を大量に見られる</t>
+  </si>
+  <si>
+    <t>- エイジレスフリーランス（6,000〜7,000件前後） — 年齢不問を掲げるIT案件サイト</t>
+  </si>
+  <si>
+    <t>- フリジョブ（20,000件前後） — 複数の案件サイト・エージェントの公開案件を横断検索</t>
+  </si>
+  <si>
+    <t>- フリーランスフリー（1,000〜2,000件前後） — IT案件を掲載</t>
+  </si>
+  <si>
+    <t>- レバテックフリーランス（50,000件前後）</t>
+  </si>
+  <si>
+    <t>- Midworks（10,000件前後）</t>
+  </si>
+  <si>
+    <t>- TechStock（8,000件前後）</t>
+  </si>
+  <si>
+    <t>- PE-BANK（5,000件前後）</t>
+  </si>
+  <si>
+    <t>- ギークスジョブ（5,000件前後）</t>
+  </si>
+  <si>
+    <t>- テックリーチ（10,000件前後）</t>
+  </si>
+  <si>
+    <t>- エンジニアファクトリー（10,000件前後）</t>
+  </si>
+  <si>
+    <t>- フォスターフリーランス（5,000件前後）</t>
+  </si>
+  <si>
+    <t>- フリーランススタート（100,000件前後）</t>
+  </si>
+  <si>
+    <t>- テクフリ（10,000件前後）</t>
+  </si>
+  <si>
+    <t>- エンジニアスタイル東京（300,000件前後）</t>
+  </si>
+  <si>
+    <t>- ポテパンフリーランス（2,000〜3,000件前後）</t>
+  </si>
+  <si>
+    <t>- PE-BANK案件検索（5,000件前後）</t>
+  </si>
+  <si>
+    <t>TechSpace(数千件前後) — 会員登録なしで案件閲覧可能。エンド直・元請直案件も検索対象</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ENGER(数千件前後) — 公開案件多数。ただし案件詳細の閲覧には登録が必要なものあり</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Findy Freelance(数千件前後)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>doocyJob(数千件前後)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>案件ナビ(数千件前後)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>テックビズフリーランス(数千件前後)</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -14468,8 +14471,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7911971" y="1528349"/>
-          <a:ext cx="1800328" cy="1214718"/>
+          <a:off x="7985930" y="1467837"/>
+          <a:ext cx="1820498" cy="1167653"/>
           <a:chOff x="8992083" y="208776"/>
           <a:chExt cx="1814762" cy="1244600"/>
         </a:xfrm>
@@ -14778,8 +14781,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="11175520" y="3059605"/>
-          <a:ext cx="1822530" cy="1963728"/>
+          <a:off x="11283097" y="2938582"/>
+          <a:ext cx="1842700" cy="1889768"/>
           <a:chOff x="8549484" y="3956874"/>
           <a:chExt cx="1810288" cy="1437363"/>
         </a:xfrm>
@@ -15330,8 +15333,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4681098" y="1657961"/>
-          <a:ext cx="1869953" cy="3342717"/>
+          <a:off x="4721439" y="1597449"/>
+          <a:ext cx="1890124" cy="3208246"/>
           <a:chOff x="5970441" y="628674"/>
           <a:chExt cx="1893913" cy="3428095"/>
         </a:xfrm>
@@ -15799,8 +15802,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10840271" y="7258650"/>
-          <a:ext cx="2193307" cy="2523422"/>
+          <a:off x="10941124" y="6969538"/>
+          <a:ext cx="2220201" cy="2422569"/>
           <a:chOff x="12007370" y="5957071"/>
           <a:chExt cx="2223130" cy="2581251"/>
         </a:xfrm>
@@ -16006,8 +16009,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14334233" y="4816236"/>
-          <a:ext cx="2220036" cy="1720343"/>
+          <a:off x="14468704" y="4627977"/>
+          <a:ext cx="2246929" cy="1653108"/>
           <a:chOff x="15050343" y="4729843"/>
           <a:chExt cx="2243515" cy="1763032"/>
         </a:xfrm>
@@ -16436,8 +16439,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6846794" y="5210735"/>
-          <a:ext cx="1781735" cy="1311089"/>
+          <a:off x="6914030" y="5002306"/>
+          <a:ext cx="1795181" cy="1264024"/>
           <a:chOff x="6846794" y="5210735"/>
           <a:chExt cx="2341399" cy="1311089"/>
         </a:xfrm>
@@ -16813,8 +16816,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3726679" y="7642890"/>
-          <a:ext cx="2335072" cy="1882107"/>
+          <a:off x="3760297" y="7340331"/>
+          <a:ext cx="2355242" cy="1808149"/>
           <a:chOff x="3726679" y="7642891"/>
           <a:chExt cx="2335072" cy="1468663"/>
         </a:xfrm>
@@ -17737,15 +17740,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6672014-33B5-48C4-9202-55E4E667EEEF}">
   <dimension ref="A1:W32"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="3.75" customWidth="1"/>
-    <col min="2" max="3" width="8.75" customWidth="1"/>
-    <col min="20" max="21" width="2.75" customWidth="1"/>
-    <col min="22" max="23" width="4.125" customWidth="1"/>
-    <col min="24" max="24" width="4.75" customWidth="1"/>
-    <col min="25" max="25" width="8.75" customWidth="1"/>
-    <col min="27" max="27" width="4.375" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="3" width="8.69921875" customWidth="1"/>
+    <col min="20" max="21" width="2.69921875" customWidth="1"/>
+    <col min="22" max="23" width="4.09765625" customWidth="1"/>
+    <col min="24" max="24" width="4.69921875" customWidth="1"/>
+    <col min="25" max="25" width="8.69921875" customWidth="1"/>
+    <col min="27" max="27" width="4.3984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -17753,25 +17756,25 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="20.25">
+    <row r="2" spans="1:23" ht="19.2">
       <c r="A2" s="108"/>
       <c r="B2" s="107" t="s">
         <v>1932</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="20.25">
+    <row r="3" spans="1:23" ht="19.2">
       <c r="A3" s="107"/>
       <c r="B3" s="107" t="s">
         <v>1933</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="20.25">
+    <row r="4" spans="1:23" ht="19.2">
       <c r="A4" s="107"/>
       <c r="B4" s="107" t="s">
         <v>1934</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="19.5" thickBot="1">
+    <row r="5" spans="1:23" ht="18.600000000000001" thickBot="1">
       <c r="V5" s="67"/>
       <c r="W5" s="67"/>
     </row>
@@ -17805,7 +17808,7 @@
       <c r="C8" s="64"/>
       <c r="W8" s="65"/>
     </row>
-    <row r="9" spans="1:23" ht="19.5" thickBot="1">
+    <row r="9" spans="1:23" ht="18.600000000000001" thickBot="1">
       <c r="C9" s="64"/>
       <c r="L9" t="s">
         <v>1706</v>
@@ -17955,7 +17958,7 @@
       <c r="V30" s="65"/>
       <c r="W30" s="65"/>
     </row>
-    <row r="31" spans="3:23" ht="19.5" thickBot="1">
+    <row r="31" spans="3:23" ht="18.600000000000001" thickBot="1">
       <c r="C31" s="64"/>
       <c r="D31" s="66"/>
       <c r="E31" s="67"/>
@@ -17978,7 +17981,7 @@
       <c r="V31" s="68"/>
       <c r="W31" s="65"/>
     </row>
-    <row r="32" spans="3:23" ht="13.15" customHeight="1" thickBot="1">
+    <row r="32" spans="3:23" ht="13.2" customHeight="1" thickBot="1">
       <c r="C32" s="66"/>
       <c r="D32" s="67"/>
       <c r="E32" s="67"/>
@@ -18011,10 +18014,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC349EE6-5475-4F9C-BD43-5DC02797CE07}">
   <dimension ref="A2:R290"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="11" style="98" customWidth="1"/>
-    <col min="2" max="6" width="10.875" style="98" customWidth="1"/>
+    <col min="2" max="6" width="10.8984375" style="98" customWidth="1"/>
     <col min="7" max="16384" width="9" style="98"/>
   </cols>
   <sheetData>
@@ -18038,7 +18041,7 @@
       </c>
       <c r="M6" s="100"/>
       <c r="O6" s="100" t="s">
-        <v>1962</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -18094,7 +18097,7 @@
       </c>
       <c r="M13" s="100"/>
       <c r="O13" s="98" t="s">
-        <v>1963</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -18106,7 +18109,7 @@
       </c>
       <c r="M15" s="100"/>
       <c r="O15" s="98" t="s">
-        <v>1960</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -18132,7 +18135,7 @@
     </row>
     <row r="20" spans="2:17">
       <c r="O20" s="100" t="s">
-        <v>1964</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="22" spans="2:17">
@@ -18240,12 +18243,12 @@
         <v>1715</v>
       </c>
       <c r="N38" s="109" t="s">
-        <v>2038</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="39" spans="2:15">
       <c r="O39" s="98" t="s">
-        <v>2039</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="40" spans="2:15">
@@ -18262,7 +18265,7 @@
         <v>1709</v>
       </c>
       <c r="O41" s="98" t="s">
-        <v>2040</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="42" spans="2:15">
@@ -18273,7 +18276,7 @@
         <v>1710</v>
       </c>
       <c r="O42" s="98" t="s">
-        <v>2041</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="43" spans="2:15">
@@ -18284,7 +18287,7 @@
         <v>1711</v>
       </c>
       <c r="O43" s="98" t="s">
-        <v>2042</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="44" spans="2:15">
@@ -18303,7 +18306,7 @@
         <v>1720</v>
       </c>
       <c r="O45" s="98" t="s">
-        <v>2043</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="46" spans="2:15">
@@ -18322,7 +18325,7 @@
         <v>1713</v>
       </c>
       <c r="O47" s="98" t="s">
-        <v>2044</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="48" spans="2:15">
@@ -18330,7 +18333,7 @@
         <v>1716</v>
       </c>
       <c r="O48" s="98" t="s">
-        <v>2045</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="49" spans="2:15">
@@ -18338,12 +18341,12 @@
         <v>1717</v>
       </c>
       <c r="O49" s="98" t="s">
-        <v>2046</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="50" spans="2:15">
       <c r="B50" s="109" t="s">
-        <v>1959</v>
+        <v>1937</v>
       </c>
       <c r="J50" s="98" t="s">
         <v>1718</v>
@@ -18357,7 +18360,7 @@
         <v>1721</v>
       </c>
       <c r="O51" s="98" t="s">
-        <v>2047</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="52" spans="2:15">
@@ -18368,640 +18371,640 @@
     </row>
     <row r="53" spans="2:15">
       <c r="B53" s="99" t="s">
-        <v>1958</v>
+        <v>2202</v>
       </c>
       <c r="J53" s="98" t="s">
         <v>1728</v>
       </c>
       <c r="O53" s="98" t="s">
-        <v>2048</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="54" spans="2:15">
       <c r="B54" s="99" t="s">
-        <v>1967</v>
+        <v>2203</v>
       </c>
       <c r="J54" s="98" t="s">
         <v>307</v>
       </c>
       <c r="O54" s="98" t="s">
-        <v>2049</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="55" spans="2:15">
       <c r="B55" s="99" t="s">
-        <v>1968</v>
+        <v>2204</v>
       </c>
       <c r="O55" s="98" t="s">
-        <v>2050</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="56" spans="2:15">
       <c r="B56" s="99" t="s">
-        <v>1936</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="57" spans="2:15">
       <c r="B57" s="98" t="s">
-        <v>1937</v>
+        <v>2206</v>
       </c>
       <c r="O57" s="98" t="s">
-        <v>2051</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="58" spans="2:15">
       <c r="B58" s="98" t="s">
-        <v>1956</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="59" spans="2:15">
       <c r="B59" s="98" t="s">
-        <v>1957</v>
+        <v>2221</v>
       </c>
       <c r="O59" s="98" t="s">
-        <v>2052</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="60" spans="2:15">
       <c r="O60" s="98" t="s">
-        <v>2053</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="61" spans="2:15">
       <c r="B61" s="98" t="s">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="O61" s="98" t="s">
-        <v>2054</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="63" spans="2:15">
       <c r="B63" s="98" t="s">
-        <v>1939</v>
+        <v>2207</v>
       </c>
       <c r="F63" s="109" t="s">
-        <v>1979</v>
+        <v>1955</v>
       </c>
       <c r="O63" s="98" t="s">
-        <v>2055</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="64" spans="2:15">
       <c r="B64" s="98" t="s">
-        <v>1940</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="65" spans="2:18">
       <c r="B65" s="98" t="s">
-        <v>1941</v>
+        <v>2209</v>
       </c>
       <c r="F65" s="98" t="s">
-        <v>1969</v>
+        <v>1945</v>
       </c>
       <c r="O65" s="98" t="s">
-        <v>2056</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="66" spans="2:18">
       <c r="B66" s="98" t="s">
-        <v>1942</v>
+        <v>2210</v>
       </c>
       <c r="F66" s="98" t="s">
-        <v>1970</v>
+        <v>1946</v>
       </c>
       <c r="O66" s="98" t="s">
-        <v>2057</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="67" spans="2:18">
       <c r="B67" s="98" t="s">
-        <v>1943</v>
+        <v>2211</v>
       </c>
       <c r="F67" s="98" t="s">
-        <v>1971</v>
+        <v>1947</v>
       </c>
       <c r="O67" s="98" t="s">
-        <v>2058</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="68" spans="2:18">
       <c r="B68" s="98" t="s">
-        <v>1944</v>
+        <v>2212</v>
       </c>
       <c r="F68" s="98" t="s">
-        <v>1972</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="69" spans="2:18">
       <c r="B69" s="98" t="s">
-        <v>1945</v>
+        <v>2222</v>
       </c>
       <c r="F69" s="98" t="s">
-        <v>1973</v>
+        <v>1949</v>
       </c>
       <c r="O69" s="98" t="s">
-        <v>2059</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="70" spans="2:18">
       <c r="B70" s="98" t="s">
-        <v>1946</v>
+        <v>2213</v>
       </c>
       <c r="F70" s="98" t="s">
-        <v>1974</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="71" spans="2:18">
       <c r="B71" s="98" t="s">
-        <v>1947</v>
+        <v>2214</v>
       </c>
       <c r="F71" s="98" t="s">
-        <v>1975</v>
+        <v>1951</v>
       </c>
       <c r="O71" s="98" t="s">
-        <v>2060</v>
+        <v>2036</v>
       </c>
       <c r="R71" s="98" t="s">
-        <v>2218</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="72" spans="2:18">
       <c r="B72" s="98" t="s">
-        <v>1948</v>
+        <v>2215</v>
       </c>
       <c r="F72" s="98" t="s">
-        <v>1976</v>
+        <v>1952</v>
       </c>
       <c r="O72" s="98" t="s">
-        <v>2061</v>
+        <v>2037</v>
       </c>
       <c r="R72" s="98" t="s">
-        <v>2219</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="73" spans="2:18">
       <c r="B73" s="98" t="s">
-        <v>1949</v>
+        <v>2216</v>
       </c>
       <c r="F73" s="98" t="s">
-        <v>1977</v>
+        <v>1953</v>
       </c>
       <c r="O73" s="98" t="s">
-        <v>2062</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="74" spans="2:18">
       <c r="B74" s="98" t="s">
-        <v>1950</v>
+        <v>2223</v>
       </c>
       <c r="F74" s="98" t="s">
-        <v>1978</v>
+        <v>1954</v>
       </c>
       <c r="O74" s="98" t="s">
-        <v>2063</v>
+        <v>2039</v>
       </c>
       <c r="R74" s="98" t="s">
-        <v>2220</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="75" spans="2:18">
       <c r="B75" s="98" t="s">
-        <v>1951</v>
+        <v>2224</v>
       </c>
       <c r="O75" s="98" t="s">
-        <v>2064</v>
+        <v>2040</v>
       </c>
       <c r="R75" s="98" t="s">
-        <v>2221</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="76" spans="2:18">
       <c r="B76" s="98" t="s">
-        <v>1952</v>
+        <v>2217</v>
       </c>
       <c r="O76" s="98" t="s">
-        <v>2065</v>
+        <v>2041</v>
       </c>
       <c r="R76" s="98" t="s">
-        <v>2222</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="77" spans="2:18">
       <c r="B77" s="98" t="s">
-        <v>1953</v>
+        <v>2225</v>
       </c>
       <c r="O77" s="98" t="s">
-        <v>2066</v>
+        <v>2042</v>
       </c>
       <c r="R77" s="98" t="s">
-        <v>2223</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="78" spans="2:18">
       <c r="B78" s="98" t="s">
-        <v>1954</v>
+        <v>2218</v>
       </c>
       <c r="R78" s="98" t="s">
-        <v>2224</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="79" spans="2:18">
       <c r="B79" s="98" t="s">
-        <v>1955</v>
+        <v>2219</v>
       </c>
       <c r="O79" s="98" t="s">
-        <v>2067</v>
+        <v>2043</v>
       </c>
       <c r="R79" s="98" t="s">
-        <v>2225</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="81" spans="1:15">
       <c r="O81" s="98" t="s">
-        <v>2068</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="82" spans="1:15">
       <c r="B82" s="109" t="s">
-        <v>1961</v>
+        <v>1939</v>
       </c>
       <c r="O82" s="98" t="s">
-        <v>2069</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="83" spans="1:15">
       <c r="A83" s="98" t="s">
-        <v>1966</v>
+        <v>1944</v>
       </c>
       <c r="B83" s="98" t="s">
-        <v>2015</v>
+        <v>1991</v>
       </c>
       <c r="E83" s="98" t="s">
-        <v>2021</v>
+        <v>1997</v>
       </c>
       <c r="G83" s="98" t="s">
-        <v>2014</v>
+        <v>1990</v>
       </c>
       <c r="I83" s="98" t="s">
-        <v>2017</v>
+        <v>1993</v>
       </c>
       <c r="O83" s="98" t="s">
-        <v>2070</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="84" spans="1:15">
       <c r="O84" s="98" t="s">
-        <v>2071</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="85" spans="1:15">
       <c r="B85" s="98" t="s">
-        <v>1980</v>
+        <v>1956</v>
       </c>
       <c r="E85" s="98" t="s">
-        <v>1965</v>
+        <v>1943</v>
       </c>
       <c r="G85" s="98" t="s">
         <v>155</v>
       </c>
       <c r="I85" s="98" t="s">
-        <v>1965</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="86" spans="1:15">
       <c r="E86" s="98" t="s">
-        <v>2018</v>
+        <v>1994</v>
       </c>
       <c r="F86" s="98" t="s">
-        <v>2020</v>
+        <v>1996</v>
       </c>
       <c r="G86" s="98" t="s">
         <v>231</v>
       </c>
       <c r="I86" s="98" t="s">
-        <v>2023</v>
+        <v>1999</v>
       </c>
       <c r="J86" s="98" t="s">
-        <v>2016</v>
+        <v>1992</v>
       </c>
       <c r="O86" s="98" t="s">
-        <v>2072</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="87" spans="1:15">
       <c r="B87" s="98" t="s">
-        <v>1981</v>
+        <v>1957</v>
       </c>
       <c r="E87" s="98" t="s">
-        <v>2019</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="88" spans="1:15">
       <c r="B88" s="98" t="s">
-        <v>1982</v>
+        <v>1958</v>
       </c>
       <c r="E88" s="98" t="s">
-        <v>2022</v>
+        <v>1998</v>
       </c>
       <c r="O88" s="98" t="s">
-        <v>2073</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="89" spans="1:15">
       <c r="O89" s="98" t="s">
-        <v>2074</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="90" spans="1:15">
       <c r="B90" s="98" t="s">
-        <v>1983</v>
+        <v>1959</v>
       </c>
       <c r="O90" s="98" t="s">
-        <v>2075</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="91" spans="1:15">
       <c r="B91" s="98" t="s">
-        <v>1984</v>
+        <v>1960</v>
       </c>
       <c r="O91" s="98" t="s">
-        <v>2076</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="92" spans="1:15">
       <c r="B92" s="98" t="s">
-        <v>1985</v>
+        <v>1961</v>
       </c>
       <c r="O92" s="98" t="s">
-        <v>2077</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="93" spans="1:15">
       <c r="B93" s="98" t="s">
-        <v>1986</v>
+        <v>1962</v>
       </c>
       <c r="O93" s="98" t="s">
-        <v>2078</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="94" spans="1:15">
       <c r="B94" s="98" t="s">
-        <v>1987</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="95" spans="1:15">
       <c r="O95" s="98" t="s">
-        <v>2079</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="96" spans="1:15">
       <c r="B96" s="98" t="s">
-        <v>1988</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="97" spans="2:15">
       <c r="B97" s="98" t="s">
-        <v>1989</v>
+        <v>1965</v>
       </c>
       <c r="O97" s="98" t="s">
-        <v>2080</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="98" spans="2:15">
       <c r="B98" s="98" t="s">
-        <v>1990</v>
+        <v>1966</v>
       </c>
       <c r="O98" s="98" t="s">
-        <v>2081</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="99" spans="2:15">
       <c r="O99" s="98" t="s">
-        <v>2082</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="100" spans="2:15">
       <c r="B100" s="98" t="s">
-        <v>1991</v>
+        <v>1967</v>
       </c>
       <c r="O100" s="98" t="s">
-        <v>2083</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="101" spans="2:15">
       <c r="B101" s="98" t="s">
-        <v>1992</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="102" spans="2:15">
       <c r="O102" s="98" t="s">
-        <v>2084</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="103" spans="2:15">
       <c r="B103" s="98" t="s">
-        <v>1993</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="104" spans="2:15">
       <c r="B104" s="98" t="s">
-        <v>1994</v>
+        <v>1970</v>
       </c>
       <c r="O104" s="98" t="s">
-        <v>2085</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="105" spans="2:15">
       <c r="B105" s="98" t="s">
-        <v>1995</v>
+        <v>1971</v>
       </c>
       <c r="O105" s="98" t="s">
-        <v>2086</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="106" spans="2:15">
       <c r="O106" s="98" t="s">
-        <v>2087</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="107" spans="2:15">
       <c r="B107" s="98" t="s">
-        <v>1996</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="108" spans="2:15">
       <c r="B108" s="98" t="s">
-        <v>1997</v>
+        <v>1973</v>
       </c>
       <c r="O108" s="98" t="s">
-        <v>2088</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="109" spans="2:15">
       <c r="B109" s="98" t="s">
-        <v>1998</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="110" spans="2:15">
       <c r="B110" s="98" t="s">
-        <v>1999</v>
+        <v>1975</v>
       </c>
       <c r="O110" s="98" t="s">
-        <v>2089</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="111" spans="2:15">
       <c r="B111" s="98" t="s">
-        <v>2000</v>
+        <v>1976</v>
       </c>
       <c r="O111" s="98" t="s">
-        <v>2090</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="112" spans="2:15">
       <c r="O112" s="98" t="s">
-        <v>2091</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="113" spans="1:15">
       <c r="O113" s="98" t="s">
-        <v>2092</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="114" spans="1:15">
       <c r="O114" s="98" t="s">
-        <v>2093</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="115" spans="1:15">
       <c r="O115" s="98" t="s">
-        <v>2094</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="116" spans="1:15">
       <c r="A116" s="98" t="s">
-        <v>2001</v>
+        <v>1977</v>
       </c>
       <c r="O116" s="98" t="s">
-        <v>2095</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="117" spans="1:15">
       <c r="B117" s="98" t="s">
-        <v>2002</v>
+        <v>1978</v>
       </c>
       <c r="O117" s="98" t="s">
-        <v>2096</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="118" spans="1:15">
       <c r="B118" s="98" t="s">
-        <v>2003</v>
+        <v>1979</v>
       </c>
       <c r="O118" s="98" t="s">
-        <v>2097</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="120" spans="1:15">
       <c r="B120" s="98" t="s">
-        <v>2004</v>
+        <v>1980</v>
       </c>
       <c r="O120" s="98" t="s">
-        <v>2098</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="121" spans="1:15">
       <c r="B121" s="98" t="s">
-        <v>2005</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="122" spans="1:15">
       <c r="O122" s="98" t="s">
-        <v>2099</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="123" spans="1:15">
       <c r="B123" s="98" t="s">
-        <v>2006</v>
+        <v>1982</v>
       </c>
       <c r="O123" s="98" t="s">
-        <v>2100</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="124" spans="1:15">
       <c r="B124" s="98" t="s">
-        <v>2009</v>
+        <v>1985</v>
       </c>
       <c r="O124" s="98" t="s">
-        <v>2101</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="125" spans="1:15">
       <c r="B125" s="98" t="s">
-        <v>2010</v>
+        <v>1986</v>
       </c>
       <c r="O125" s="98" t="s">
-        <v>2102</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="126" spans="1:15">
       <c r="B126" s="98" t="s">
-        <v>2013</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="127" spans="1:15">
       <c r="B127" s="98" t="s">
-        <v>2011</v>
+        <v>1987</v>
       </c>
       <c r="O127" s="98" t="s">
-        <v>2103</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="129" spans="1:15">
       <c r="B129" s="98" t="s">
-        <v>2007</v>
+        <v>1983</v>
       </c>
       <c r="O129" s="98" t="s">
-        <v>2104</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="130" spans="1:15">
       <c r="B130" s="98" t="s">
-        <v>2012</v>
+        <v>1988</v>
       </c>
       <c r="O130" s="98" t="s">
-        <v>2105</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="131" spans="1:15">
       <c r="B131" s="98" t="s">
-        <v>2008</v>
+        <v>1984</v>
       </c>
       <c r="O131" s="98" t="s">
-        <v>2106</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="132" spans="1:15">
       <c r="O132" s="98" t="s">
-        <v>2107</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="133" spans="1:15">
       <c r="O133" s="98" t="s">
-        <v>2108</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="134" spans="1:15">
       <c r="A134" s="98" t="s">
-        <v>2024</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="135" spans="1:15">
       <c r="B135" s="98" t="s">
-        <v>2025</v>
+        <v>2001</v>
       </c>
       <c r="O135" s="98" t="s">
-        <v>2109</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="136" spans="1:15">
@@ -19011,18 +19014,18 @@
     </row>
     <row r="137" spans="1:15">
       <c r="B137" s="98" t="s">
-        <v>2026</v>
+        <v>2002</v>
       </c>
       <c r="O137" s="98" t="s">
-        <v>2110</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="138" spans="1:15">
       <c r="B138" s="98" t="s">
-        <v>2027</v>
+        <v>2003</v>
       </c>
       <c r="O138" s="98" t="s">
-        <v>2111</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="139" spans="1:15">
@@ -19030,15 +19033,15 @@
         <v>1842</v>
       </c>
       <c r="O139" s="98" t="s">
-        <v>2112</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="140" spans="1:15">
       <c r="B140" s="98" t="s">
-        <v>2028</v>
+        <v>2004</v>
       </c>
       <c r="O140" s="98" t="s">
-        <v>2113</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="141" spans="1:15">
@@ -19048,10 +19051,10 @@
     </row>
     <row r="142" spans="1:15">
       <c r="B142" s="98" t="s">
-        <v>2029</v>
+        <v>2005</v>
       </c>
       <c r="O142" s="98" t="s">
-        <v>2114</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="143" spans="1:15">
@@ -19061,574 +19064,574 @@
     </row>
     <row r="144" spans="1:15">
       <c r="B144" s="98" t="s">
-        <v>2030</v>
+        <v>2006</v>
       </c>
       <c r="O144" s="98" t="s">
-        <v>2115</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="145" spans="2:15">
       <c r="B145" s="98" t="s">
-        <v>2031</v>
+        <v>2007</v>
       </c>
       <c r="O145" s="98" t="s">
-        <v>2116</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="146" spans="2:15">
       <c r="B146" s="98" t="s">
-        <v>2032</v>
+        <v>2008</v>
       </c>
       <c r="O146" s="98" t="s">
-        <v>2117</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="147" spans="2:15">
       <c r="B147" s="98" t="s">
-        <v>2033</v>
+        <v>2009</v>
       </c>
       <c r="O147" s="98" t="s">
-        <v>2118</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="148" spans="2:15">
       <c r="B148" s="98" t="s">
-        <v>2034</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="149" spans="2:15">
       <c r="B149" s="98" t="s">
-        <v>2033</v>
+        <v>2009</v>
       </c>
       <c r="O149" s="98" t="s">
-        <v>2119</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="150" spans="2:15">
       <c r="B150" s="98" t="s">
-        <v>2035</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="151" spans="2:15">
       <c r="B151" s="98" t="s">
-        <v>2033</v>
+        <v>2009</v>
       </c>
       <c r="O151" s="98" t="s">
-        <v>2120</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="152" spans="2:15">
       <c r="B152" s="98" t="s">
-        <v>2036</v>
+        <v>2012</v>
       </c>
       <c r="O152" s="98" t="s">
-        <v>2121</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="153" spans="2:15">
       <c r="B153" s="98" t="s">
-        <v>2033</v>
+        <v>2009</v>
       </c>
       <c r="O153" s="98" t="s">
-        <v>2122</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="154" spans="2:15">
       <c r="B154" s="98" t="s">
-        <v>2037</v>
+        <v>2013</v>
       </c>
       <c r="O154" s="98" t="s">
-        <v>2123</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="156" spans="2:15">
       <c r="O156" s="98" t="s">
-        <v>2124</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="158" spans="2:15">
       <c r="O158" s="98" t="s">
-        <v>2125</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="159" spans="2:15">
       <c r="O159" s="98" t="s">
-        <v>2126</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="160" spans="2:15">
       <c r="O160" s="98" t="s">
-        <v>2127</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="161" spans="15:15">
       <c r="O161" s="98" t="s">
-        <v>2128</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="162" spans="15:15">
       <c r="O162" s="98" t="s">
-        <v>2129</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="163" spans="15:15">
       <c r="O163" s="98" t="s">
-        <v>2130</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="165" spans="15:15">
       <c r="O165" s="98" t="s">
-        <v>2131</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="167" spans="15:15">
       <c r="O167" s="98" t="s">
-        <v>2132</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="168" spans="15:15">
       <c r="O168" s="98" t="s">
-        <v>2133</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="169" spans="15:15">
       <c r="O169" s="98" t="s">
-        <v>2134</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="171" spans="15:15">
       <c r="O171" s="98" t="s">
-        <v>2135</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="173" spans="15:15">
       <c r="O173" s="98" t="s">
-        <v>2136</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="174" spans="15:15">
       <c r="O174" s="98" t="s">
-        <v>2137</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="175" spans="15:15">
       <c r="O175" s="98" t="s">
-        <v>2138</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="176" spans="15:15">
       <c r="O176" s="98" t="s">
-        <v>2139</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="177" spans="15:15">
       <c r="O177" s="98" t="s">
-        <v>2140</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="179" spans="15:15">
       <c r="O179" s="98" t="s">
-        <v>2141</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="181" spans="15:15">
       <c r="O181" s="98" t="s">
-        <v>2142</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="182" spans="15:15">
       <c r="O182" s="98" t="s">
-        <v>2143</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="183" spans="15:15">
       <c r="O183" s="98" t="s">
-        <v>2144</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="184" spans="15:15">
       <c r="O184" s="98" t="s">
-        <v>2145</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="185" spans="15:15">
       <c r="O185" s="98" t="s">
-        <v>2146</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="187" spans="15:15">
       <c r="O187" s="98" t="s">
-        <v>2147</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="189" spans="15:15">
       <c r="O189" s="98" t="s">
-        <v>2148</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="190" spans="15:15">
       <c r="O190" s="98" t="s">
-        <v>2149</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="191" spans="15:15">
       <c r="O191" s="98" t="s">
-        <v>2120</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="192" spans="15:15">
       <c r="O192" s="98" t="s">
-        <v>2150</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="193" spans="15:15">
       <c r="O193" s="98" t="s">
-        <v>2151</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="194" spans="15:15">
       <c r="O194" s="98" t="s">
-        <v>2152</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="196" spans="15:15">
       <c r="O196" s="98" t="s">
-        <v>2153</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="198" spans="15:15">
       <c r="O198" s="98" t="s">
-        <v>2150</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="199" spans="15:15">
       <c r="O199" s="98" t="s">
-        <v>2154</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="200" spans="15:15">
       <c r="O200" s="98" t="s">
-        <v>2155</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="201" spans="15:15">
       <c r="O201" s="98" t="s">
-        <v>2156</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="203" spans="15:15">
       <c r="O203" s="98" t="s">
-        <v>2157</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="205" spans="15:15">
       <c r="O205" s="98" t="s">
-        <v>2158</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="206" spans="15:15">
       <c r="O206" s="98" t="s">
-        <v>2159</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="207" spans="15:15">
       <c r="O207" s="98" t="s">
-        <v>2160</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="209" spans="15:15">
       <c r="O209" s="98" t="s">
-        <v>2161</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="211" spans="15:15">
       <c r="O211" s="98" t="s">
-        <v>2162</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="212" spans="15:15">
       <c r="O212" s="98" t="s">
-        <v>2163</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="213" spans="15:15">
       <c r="O213" s="98" t="s">
-        <v>2164</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="215" spans="15:15">
       <c r="O215" s="98" t="s">
-        <v>2165</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="217" spans="15:15">
       <c r="O217" s="98" t="s">
-        <v>2166</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="218" spans="15:15">
       <c r="O218" s="98" t="s">
-        <v>2167</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="219" spans="15:15">
       <c r="O219" s="98" t="s">
-        <v>2168</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="221" spans="15:15">
       <c r="O221" s="98" t="s">
-        <v>2169</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="223" spans="15:15">
       <c r="O223" s="98" t="s">
-        <v>2170</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="224" spans="15:15">
       <c r="O224" s="98" t="s">
-        <v>2171</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="225" spans="15:15">
       <c r="O225" s="98" t="s">
-        <v>2172</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="227" spans="15:15">
       <c r="O227" s="98" t="s">
-        <v>2173</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="229" spans="15:15">
       <c r="O229" s="98" t="s">
-        <v>2174</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="230" spans="15:15">
       <c r="O230" s="98" t="s">
-        <v>2175</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="231" spans="15:15">
       <c r="O231" s="98" t="s">
-        <v>2176</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="232" spans="15:15">
       <c r="O232" s="98" t="s">
-        <v>2177</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="233" spans="15:15">
       <c r="O233" s="98" t="s">
-        <v>2178</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="235" spans="15:15">
       <c r="O235" s="98" t="s">
-        <v>2179</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="237" spans="15:15">
       <c r="O237" s="98" t="s">
-        <v>2180</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="238" spans="15:15">
       <c r="O238" s="98" t="s">
-        <v>2181</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="239" spans="15:15">
       <c r="O239" s="98" t="s">
-        <v>2182</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="241" spans="15:15">
       <c r="O241" s="98" t="s">
-        <v>2183</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="243" spans="15:15">
       <c r="O243" s="98" t="s">
-        <v>2184</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="244" spans="15:15">
       <c r="O244" s="98" t="s">
-        <v>2185</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="245" spans="15:15">
       <c r="O245" s="98" t="s">
-        <v>2186</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="247" spans="15:15">
       <c r="O247" s="98" t="s">
-        <v>2187</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="249" spans="15:15">
       <c r="O249" s="98" t="s">
-        <v>2188</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="250" spans="15:15">
       <c r="O250" s="98" t="s">
-        <v>2189</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="251" spans="15:15">
       <c r="O251" s="98" t="s">
-        <v>2190</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="253" spans="15:15">
       <c r="O253" s="98" t="s">
-        <v>2191</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="255" spans="15:15">
       <c r="O255" s="98" t="s">
-        <v>2192</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="256" spans="15:15">
       <c r="O256" s="98" t="s">
-        <v>2193</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="257" spans="15:15">
       <c r="O257" s="98" t="s">
-        <v>2194</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="258" spans="15:15">
       <c r="O258" s="98" t="s">
-        <v>2195</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="259" spans="15:15">
       <c r="O259" s="98" t="s">
-        <v>2063</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="260" spans="15:15">
       <c r="O260" s="98" t="s">
-        <v>2196</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="262" spans="15:15">
       <c r="O262" s="98" t="s">
-        <v>2197</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="264" spans="15:15">
       <c r="O264" s="98" t="s">
-        <v>2198</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="265" spans="15:15">
       <c r="O265" s="98" t="s">
-        <v>2199</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="266" spans="15:15">
       <c r="O266" s="98" t="s">
-        <v>2200</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="267" spans="15:15">
       <c r="O267" s="98" t="s">
-        <v>2201</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="268" spans="15:15">
       <c r="O268" s="98" t="s">
-        <v>2202</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="270" spans="15:15">
       <c r="O270" s="98" t="s">
-        <v>2203</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="272" spans="15:15">
       <c r="O272" s="98" t="s">
-        <v>2204</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="273" spans="15:15">
       <c r="O273" s="98" t="s">
-        <v>2205</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="274" spans="15:15">
       <c r="O274" s="98" t="s">
-        <v>2206</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="276" spans="15:15">
       <c r="O276" s="98" t="s">
-        <v>2207</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="278" spans="15:15">
       <c r="O278" s="98" t="s">
-        <v>2208</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="279" spans="15:15">
       <c r="O279" s="98" t="s">
-        <v>2209</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="280" spans="15:15">
       <c r="O280" s="98" t="s">
-        <v>2210</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="281" spans="15:15">
       <c r="O281" s="98" t="s">
-        <v>2211</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="283" spans="15:15">
       <c r="O283" s="98" t="s">
-        <v>2212</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="285" spans="15:15">
       <c r="O285" s="98" t="s">
-        <v>2213</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="286" spans="15:15">
       <c r="O286" s="98" t="s">
-        <v>2149</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="287" spans="15:15">
       <c r="O287" s="98" t="s">
-        <v>2214</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="288" spans="15:15">
       <c r="O288" s="98" t="s">
-        <v>2215</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="289" spans="15:15">
       <c r="O289" s="98" t="s">
-        <v>2216</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="290" spans="15:15">
       <c r="O290" s="98" t="s">
-        <v>2217</v>
+        <v>2193</v>
       </c>
     </row>
   </sheetData>
@@ -19641,10 +19644,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F0B575-2DDF-49B9-8DE2-F372EEC2F3B3}">
   <dimension ref="A2:O79"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="11.875" style="1" customWidth="1"/>
-    <col min="2" max="6" width="10.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.8984375" style="1" customWidth="1"/>
+    <col min="2" max="6" width="10.8984375" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -19676,7 +19679,7 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="18.75">
+    <row r="4" spans="1:15" ht="18">
       <c r="A4" s="1" t="s">
         <v>1280</v>
       </c>
@@ -19705,7 +19708,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" ht="13.2">
       <c r="B5" s="58" t="s">
         <v>1175</v>
       </c>
@@ -19722,7 +19725,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" ht="13.2">
       <c r="B6" s="58" t="s">
         <v>1176</v>
       </c>
@@ -19745,7 +19748,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" ht="13.2">
       <c r="B7" s="58" t="s">
         <v>1189</v>
       </c>
@@ -19774,7 +19777,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" ht="13.2">
       <c r="B8" s="58" t="s">
         <v>1177</v>
       </c>
@@ -19803,7 +19806,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" ht="13.2">
       <c r="B9" s="58" t="s">
         <v>1178</v>
       </c>
@@ -19829,7 +19832,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" ht="13.2">
       <c r="B10" s="58" t="s">
         <v>1179</v>
       </c>
@@ -19855,7 +19858,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" ht="13.2">
       <c r="B11" s="58" t="s">
         <v>1180</v>
       </c>
@@ -19881,7 +19884,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" ht="13.2">
       <c r="B12" s="58" t="s">
         <v>1181</v>
       </c>
@@ -19907,7 +19910,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" ht="13.2">
       <c r="B13" s="58" t="s">
         <v>1182</v>
       </c>
@@ -19930,7 +19933,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" ht="13.2">
       <c r="B14" s="58" t="s">
         <v>1183</v>
       </c>
@@ -19953,7 +19956,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" ht="13.2">
       <c r="B15" s="58" t="s">
         <v>1184</v>
       </c>
@@ -19976,7 +19979,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" ht="13.2">
       <c r="B16" s="58" t="s">
         <v>1185</v>
       </c>
@@ -19996,7 +19999,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" ht="13.2">
       <c r="B17" s="58" t="s">
         <v>1186</v>
       </c>
@@ -20016,7 +20019,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:10" ht="13.2">
       <c r="B18" s="58" t="s">
         <v>1190</v>
       </c>
@@ -20036,7 +20039,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:10" ht="13.2">
       <c r="B19" s="58" t="s">
         <v>1187</v>
       </c>
@@ -20056,7 +20059,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:10" ht="13.2">
       <c r="B20" s="58" t="s">
         <v>1191</v>
       </c>
@@ -20601,9 +20604,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FCFD5C-696C-43AD-A2BD-D69C05CB2D44}">
   <dimension ref="B2:P57"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="16384" width="8.75" style="1"/>
+    <col min="1" max="16384" width="8.69921875" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
@@ -21079,9 +21082,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E898285-845A-4583-B20D-F3A331C07E8E}">
   <dimension ref="B2:R45"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="13" max="13" width="8.625" customWidth="1"/>
+    <col min="13" max="13" width="8.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18">
@@ -21096,7 +21099,7 @@
       <c r="O2" s="86"/>
       <c r="P2" s="86"/>
     </row>
-    <row r="3" spans="2:18" ht="19.5" thickBot="1">
+    <row r="3" spans="2:18" ht="18.600000000000001" thickBot="1">
       <c r="F3" s="89" t="s">
         <v>1582</v>
       </c>
@@ -21218,7 +21221,7 @@
       <c r="P10" s="65"/>
       <c r="R10" s="84"/>
     </row>
-    <row r="11" spans="2:18" ht="19.5" thickBot="1">
+    <row r="11" spans="2:18" ht="18.600000000000001" thickBot="1">
       <c r="F11" s="91"/>
       <c r="I11" s="75"/>
       <c r="J11" s="66"/>
@@ -21307,7 +21310,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="22" spans="4:18" ht="19.5" thickBot="1">
+    <row r="22" spans="4:18" ht="18.600000000000001" thickBot="1">
       <c r="D22" s="80"/>
       <c r="E22" s="81"/>
       <c r="F22" s="81"/>
@@ -21436,7 +21439,7 @@
       </c>
       <c r="N29" s="84"/>
     </row>
-    <row r="30" spans="4:18" ht="19.5" thickBot="1">
+    <row r="30" spans="4:18" ht="18.600000000000001" thickBot="1">
       <c r="D30" s="83"/>
       <c r="E30" s="77"/>
       <c r="F30" s="78"/>
@@ -21672,11 +21675,11 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD79B98E-03E4-44E6-9FBF-39CA1C89C95A}">
   <dimension ref="B3:L149"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="8.75" style="73"/>
-    <col min="3" max="3" width="10.625" customWidth="1"/>
-    <col min="6" max="6" width="10.875" customWidth="1"/>
+    <col min="2" max="2" width="8.69921875" style="73"/>
+    <col min="3" max="3" width="10.59765625" customWidth="1"/>
+    <col min="6" max="6" width="10.8984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:10">
@@ -22456,7 +22459,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="16384" width="9" style="5"/>
   </cols>
@@ -22470,7 +22473,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBD988A-503C-4F44-AC4A-B26683FC9B4C}">
   <dimension ref="B4:O34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="16384" width="9" style="5"/>
   </cols>
@@ -22621,14 +22624,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
   <dimension ref="B4:K166"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="2" width="20.25" style="5" customWidth="1"/>
-    <col min="3" max="3" width="24.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.19921875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="24.09765625" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" style="5" customWidth="1"/>
     <col min="5" max="8" width="9" style="5"/>
-    <col min="9" max="9" width="45.625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="45.59765625" style="5" customWidth="1"/>
     <col min="10" max="22" width="9" style="5"/>
     <col min="23" max="23" width="8" style="5" customWidth="1"/>
     <col min="24" max="16384" width="9" style="5"/>
@@ -26982,22 +26985,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EB7090A-0065-41E7-85DA-75EEB9504A67}">
   <dimension ref="C3:Q81"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="2" width="7.5" style="5" customWidth="1"/>
-    <col min="3" max="3" width="13.75" style="5" customWidth="1"/>
+    <col min="3" max="3" width="13.69921875" style="5" customWidth="1"/>
     <col min="4" max="4" width="20" style="5" customWidth="1"/>
-    <col min="5" max="5" width="30.625" style="5" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="13.375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="30.59765625" style="5" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="13.3984375" style="5" customWidth="1"/>
     <col min="7" max="7" width="11" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.75" style="5" customWidth="1"/>
-    <col min="10" max="12" width="9.875" style="18" customWidth="1"/>
-    <col min="13" max="13" width="9.25" style="18" customWidth="1"/>
-    <col min="14" max="14" width="12.625" style="18" customWidth="1"/>
-    <col min="15" max="15" width="27.125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="15.19921875" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.69921875" style="5" customWidth="1"/>
+    <col min="10" max="12" width="9.8984375" style="18" customWidth="1"/>
+    <col min="13" max="13" width="9.19921875" style="18" customWidth="1"/>
+    <col min="14" max="14" width="12.59765625" style="18" customWidth="1"/>
+    <col min="15" max="15" width="27.09765625" style="5" customWidth="1"/>
     <col min="16" max="16" width="7.5" style="5" customWidth="1"/>
-    <col min="17" max="17" width="15.125" style="5" customWidth="1"/>
+    <col min="17" max="17" width="15.09765625" style="5" customWidth="1"/>
     <col min="18" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -28661,7 +28664,7 @@
         <v>INSERT INTO m_skill VALUES ('skill037','グラビジャ',4,0,0,1,75,50,0.0,1,1200,'現HPの７５％ダメージ');</v>
       </c>
     </row>
-    <row r="41" spans="3:17" ht="40.5">
+    <row r="41" spans="3:17" ht="37.799999999999997">
       <c r="C41" s="47" t="s">
         <v>1048</v>
       </c>
@@ -30413,10 +30416,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F51B408-D4E3-46FE-97DE-15AB67B6AAB6}">
   <dimension ref="B1:Q100"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="2" width="12.75" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.69921875" style="5" customWidth="1"/>
     <col min="3" max="3" width="17.5" style="5" customWidth="1"/>
     <col min="4" max="16384" width="9" style="5"/>
   </cols>
@@ -33232,22 +33235,22 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E63A27D9-C8B6-491D-9205-8D7433312F14}">
   <dimension ref="A4:U522"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="12.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.8984375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="12.75" style="3" customWidth="1"/>
-    <col min="8" max="8" width="5.375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="5.3984375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="14.09765625" style="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="1"/>
-    <col min="12" max="12" width="17.75" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.69921875" style="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1"/>
-    <col min="14" max="14" width="5.25" style="1" customWidth="1"/>
+    <col min="14" max="14" width="5.19921875" style="1" customWidth="1"/>
     <col min="15" max="20" width="9" style="1"/>
-    <col min="21" max="21" width="8.875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="8.8984375" style="1" customWidth="1"/>
     <col min="22" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -49840,7 +49843,7 @@
         <v>INSERT INTO m_monster_skills VALUES ('myskill0505','monster084','skill051',FALSE);</v>
       </c>
     </row>
-    <row r="510" spans="1:21" ht="18.75">
+    <row r="510" spans="1:21" ht="18">
       <c r="A510"/>
       <c r="B510"/>
       <c r="C510"/>
@@ -49863,7 +49866,7 @@
       <c r="T510"/>
       <c r="U510"/>
     </row>
-    <row r="511" spans="1:21" ht="18.75">
+    <row r="511" spans="1:21" ht="18">
       <c r="A511"/>
       <c r="B511"/>
       <c r="C511"/>
@@ -49886,7 +49889,7 @@
       <c r="T511"/>
       <c r="U511"/>
     </row>
-    <row r="512" spans="1:21" ht="18.75">
+    <row r="512" spans="1:21" ht="18">
       <c r="A512"/>
       <c r="B512"/>
       <c r="C512"/>
@@ -49909,7 +49912,7 @@
       <c r="T512"/>
       <c r="U512"/>
     </row>
-    <row r="513" spans="1:21" ht="18.75">
+    <row r="513" spans="1:21" ht="18">
       <c r="A513"/>
       <c r="B513"/>
       <c r="C513"/>
@@ -49932,7 +49935,7 @@
       <c r="T513"/>
       <c r="U513"/>
     </row>
-    <row r="514" spans="1:21" ht="18.75">
+    <row r="514" spans="1:21" ht="18">
       <c r="A514"/>
       <c r="B514"/>
       <c r="C514"/>
@@ -49955,7 +49958,7 @@
       <c r="T514"/>
       <c r="U514"/>
     </row>
-    <row r="515" spans="1:21" ht="18.75">
+    <row r="515" spans="1:21" ht="18">
       <c r="A515"/>
       <c r="B515"/>
       <c r="C515"/>
@@ -49978,7 +49981,7 @@
       <c r="T515"/>
       <c r="U515"/>
     </row>
-    <row r="516" spans="1:21" ht="18.75">
+    <row r="516" spans="1:21" ht="18">
       <c r="A516"/>
       <c r="B516"/>
       <c r="C516"/>
@@ -50001,7 +50004,7 @@
       <c r="T516"/>
       <c r="U516"/>
     </row>
-    <row r="517" spans="1:21" ht="18.75">
+    <row r="517" spans="1:21" ht="18">
       <c r="A517"/>
       <c r="B517"/>
       <c r="C517"/>
@@ -50024,7 +50027,7 @@
       <c r="T517"/>
       <c r="U517"/>
     </row>
-    <row r="518" spans="1:21" ht="18.75">
+    <row r="518" spans="1:21" ht="18">
       <c r="A518"/>
       <c r="B518"/>
       <c r="C518"/>
@@ -50047,7 +50050,7 @@
       <c r="T518"/>
       <c r="U518"/>
     </row>
-    <row r="519" spans="1:21" ht="18.75">
+    <row r="519" spans="1:21" ht="18">
       <c r="A519"/>
       <c r="B519"/>
       <c r="C519"/>
@@ -50070,7 +50073,7 @@
       <c r="T519"/>
       <c r="U519"/>
     </row>
-    <row r="520" spans="1:21" ht="18.75">
+    <row r="520" spans="1:21" ht="18">
       <c r="A520"/>
       <c r="B520"/>
       <c r="C520"/>
@@ -50093,7 +50096,7 @@
       <c r="T520"/>
       <c r="U520"/>
     </row>
-    <row r="521" spans="1:21" ht="18.75">
+    <row r="521" spans="1:21" ht="18">
       <c r="A521"/>
       <c r="B521"/>
       <c r="C521"/>
@@ -50116,7 +50119,7 @@
       <c r="T521"/>
       <c r="U521"/>
     </row>
-    <row r="522" spans="1:21" ht="18.75">
+    <row r="522" spans="1:21" ht="18">
       <c r="A522"/>
       <c r="B522"/>
       <c r="C522"/>
@@ -50148,15 +50151,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A843E7EA-D614-495E-86B7-D31F628C6221}">
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="3" width="17.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="17.19921875" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.75" style="5" customWidth="1"/>
+    <col min="5" max="5" width="11.59765625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.69921875" style="5" customWidth="1"/>
     <col min="7" max="7" width="13.5" style="5" customWidth="1"/>
-    <col min="8" max="8" width="11.875" style="5" customWidth="1"/>
+    <col min="8" max="8" width="11.8984375" style="5" customWidth="1"/>
     <col min="9" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -50517,13 +50520,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE71EC6-0DD3-461C-A8FC-74E22154B7A5}">
   <dimension ref="A4:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="3.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="3.8984375" style="1" customWidth="1"/>
     <col min="2" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="4.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="95.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="4.19921875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="95.19921875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.8984375" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D50EB4-36DF-4A89-9A37-9DA17336751B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE81F9C-F14B-4541-988A-020733B9B55B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="3" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="3" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="architecture" sheetId="12" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4428" uniqueCount="2226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4485" uniqueCount="2250">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -7668,9 +7668,6 @@
     <t>案件サイトによっては</t>
   </si>
   <si>
-    <t>スクレイピング禁止</t>
-  </si>
-  <si>
     <t>再配布禁止</t>
   </si>
   <si>
@@ -8792,653 +8789,738 @@
     <t xml:space="preserve">                 COMMIT</t>
   </si>
   <si>
-    <t>分析可能なもの</t>
+    <t>求人総数の推移</t>
+  </si>
+  <si>
+    <t>日別・週別・月別</t>
+  </si>
+  <si>
+    <t>新規求人が増えてるか減ってるか</t>
+  </si>
+  <si>
+    <t>新規求人件数</t>
+  </si>
+  <si>
+    <t>今日初めて観測した求人</t>
+  </si>
+  <si>
+    <t>先週比・先月比</t>
+  </si>
+  <si>
+    <t>「求人市場が活発か」の指標</t>
+  </si>
+  <si>
+    <t>アクティブ求人件数</t>
+  </si>
+  <si>
+    <t>last_seen_at を基準に現在も掲載されていると判断した件数</t>
+  </si>
+  <si>
+    <t>期間内に消えた求人数</t>
+  </si>
+  <si>
+    <t>求人の増減</t>
+  </si>
+  <si>
+    <t>求人の平均掲載期間</t>
+  </si>
+  <si>
+    <t>初回検出日 → 最終検出日</t>
+  </si>
+  <si>
+    <t>何日くらい募集され続けるか</t>
+  </si>
+  <si>
+    <t>長期間残る求人の割合</t>
+  </si>
+  <si>
+    <t>求人の消化速度</t>
+  </si>
+  <si>
+    <t>新規掲載から消えるまでの日数</t>
+  </si>
+  <si>
+    <t>すぐ消える求人＝応募が集まりやすい／採用が決まりやすい可能性</t>
+  </si>
+  <si>
+    <t>長く残る求人＝条件が厳しい可能性</t>
+  </si>
+  <si>
+    <t>プログラミング言語ランキング</t>
+  </si>
+  <si>
+    <t>Go</t>
+  </si>
+  <si>
+    <t>Java</t>
+  </si>
+  <si>
+    <t>C#</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>TypeScript</t>
+  </si>
+  <si>
+    <t>PHP</t>
+  </si>
+  <si>
+    <t>求人数順</t>
+  </si>
+  <si>
+    <t>技術の人気推移</t>
+  </si>
+  <si>
+    <t>Go求人は3か月前より増えたか</t>
+  </si>
+  <si>
+    <t>Reactは横ばいか</t>
+  </si>
+  <si>
+    <t>AI関連技術は増えているか</t>
+  </si>
+  <si>
+    <t>技術ごとの時系列グラフ</t>
+  </si>
+  <si>
+    <t>言語 × フレームワーク</t>
+  </si>
+  <si>
+    <t>Java × Spring</t>
+  </si>
+  <si>
+    <t>C# × ASP.NET Core</t>
+  </si>
+  <si>
+    <t>TypeScript × React</t>
+  </si>
+  <si>
+    <t>Python × Django</t>
+  </si>
+  <si>
+    <t>Go × Gin</t>
+  </si>
+  <si>
+    <t>よくセットで要求される技術</t>
+  </si>
+  <si>
+    <t>スキルの共起分析</t>
+  </si>
+  <si>
+    <t>Go案件に一緒に出やすい技術</t>
+  </si>
+  <si>
+    <t>React案件で要求されやすい技術</t>
+  </si>
+  <si>
+    <t>PostgreSQLと一緒に出やすい技術</t>
+  </si>
+  <si>
+    <t>「次に何を覚えると求人の幅が広がるか」</t>
+  </si>
+  <si>
+    <t>必須スキルと歓迎スキルの比較</t>
+  </si>
+  <si>
+    <t>Goは必須が多いか、歓迎が多いか</t>
+  </si>
+  <si>
+    <t>AWSは必須か、あると有利程度か</t>
+  </si>
+  <si>
+    <t>Reactは必須なのか経験者歓迎なのか</t>
+  </si>
+  <si>
+    <t>カテゴリ別の需要</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>Framework / Library</t>
+  </si>
+  <si>
+    <t>Database</t>
+  </si>
+  <si>
+    <t>Cloud</t>
+  </si>
+  <si>
+    <t>Infrastructure</t>
+  </si>
+  <si>
+    <t>Tool</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Architecture</t>
+  </si>
+  <si>
+    <t>Methodology</t>
+  </si>
+  <si>
+    <t>給与ランキング</t>
+  </si>
+  <si>
+    <t>言語別の平均単価</t>
+  </si>
+  <si>
+    <t>フレームワーク別の平均単価</t>
+  </si>
+  <si>
+    <t>スキル別の平均単価</t>
+  </si>
+  <si>
+    <t>求人件数と単価を合わせた分析</t>
+  </si>
+  <si>
+    <t>給与レンジの分布</t>
+  </si>
+  <si>
+    <t>月40万未満</t>
+  </si>
+  <si>
+    <t>40〜60万</t>
+  </si>
+  <si>
+    <t>60〜80万</t>
+  </si>
+  <si>
+    <t>80万以上</t>
+  </si>
+  <si>
+    <t>単価の中央値</t>
+  </si>
+  <si>
+    <t>技術別の単価</t>
+  </si>
+  <si>
+    <t>Go案件の平均・中央値</t>
+  </si>
+  <si>
+    <t>Java案件の平均・中央値</t>
+  </si>
+  <si>
+    <t>C#案件の平均・中央値</t>
+  </si>
+  <si>
+    <t>React案件の平均・中央値</t>
+  </si>
+  <si>
+    <t>経験年数 × 単価</t>
+  </si>
+  <si>
+    <t>1〜2年</t>
+  </si>
+  <si>
+    <t>3〜5年</t>
+  </si>
+  <si>
+    <t>5年以上</t>
+  </si>
+  <si>
+    <t>経験年数による単価差</t>
+  </si>
+  <si>
+    <t>リモート率</t>
+  </si>
+  <si>
+    <t>フルリモート</t>
+  </si>
+  <si>
+    <t>一部リモート</t>
+  </si>
+  <si>
+    <t>常駐</t>
+  </si>
+  <si>
+    <t>技術別のリモート率</t>
+  </si>
+  <si>
+    <t>地域別求人</t>
+  </si>
+  <si>
+    <t>東京</t>
+  </si>
+  <si>
+    <t>大阪</t>
+  </si>
+  <si>
+    <t>名古屋</t>
+  </si>
+  <si>
+    <t>福岡</t>
+  </si>
+  <si>
+    <t>地方</t>
+  </si>
+  <si>
+    <t>都道府県ごとの求人密度</t>
+  </si>
+  <si>
+    <t>地域 × 単価</t>
+  </si>
+  <si>
+    <t>東京は高単価だが常駐が多い</t>
+  </si>
+  <si>
+    <t>地方は求人が少ないがフルリモート率が高い</t>
+  </si>
+  <si>
+    <t>地域ごとの比較</t>
+  </si>
+  <si>
+    <t>雇用形態の割合</t>
+  </si>
+  <si>
+    <t>正社員</t>
+  </si>
+  <si>
+    <t>業務委託</t>
+  </si>
+  <si>
+    <t>派遣</t>
+  </si>
+  <si>
+    <t>副業</t>
+  </si>
+  <si>
+    <t>アルバイト</t>
+  </si>
+  <si>
+    <t>勤務条件</t>
+  </si>
+  <si>
+    <t>週5</t>
+  </si>
+  <si>
+    <t>週4</t>
+  </si>
+  <si>
+    <t>週3</t>
+  </si>
+  <si>
+    <t>時短</t>
+  </si>
+  <si>
+    <t>副業可</t>
+  </si>
+  <si>
+    <t>案件の競争度っぽい指標</t>
+  </si>
+  <si>
+    <t>掲載期間</t>
+  </si>
+  <si>
+    <t>単価</t>
+  </si>
+  <si>
+    <t>必須スキル数</t>
+  </si>
+  <si>
+    <t>条件の良さ</t>
+  </si>
+  <si>
+    <t>※応募数が取れないなら推定になる</t>
+  </si>
+  <si>
+    <t>求人の難易度</t>
+  </si>
+  <si>
+    <t>必須経験年数</t>
+  </si>
+  <si>
+    <t>求められる技術カテゴリ数</t>
+  </si>
+  <si>
+    <t>「要求が盛られている求人」を可視化</t>
+  </si>
+  <si>
+    <t>スキル要求数ランキング</t>
+  </si>
+  <si>
+    <t>必須スキルが多い求人</t>
+  </si>
+  <si>
+    <t>「全部入り案件」</t>
+  </si>
+  <si>
+    <t>技術スタックが広すぎる求人</t>
+  </si>
+  <si>
+    <t>技術スタックの複雑度</t>
+  </si>
+  <si>
+    <t>言語1個＋FW1個</t>
+  </si>
+  <si>
+    <t>言語3個＋Cloud＋Docker＋Kubernetes＋CI/CD</t>
+  </si>
+  <si>
+    <t>求人ごとの要求範囲</t>
+  </si>
+  <si>
+    <t>求人文の長さ</t>
+  </si>
+  <si>
+    <t>説明文が長い求人</t>
+  </si>
+  <si>
+    <t>短すぎる求人</t>
+  </si>
+  <si>
+    <t>情報量と単価の関係</t>
+  </si>
+  <si>
+    <t>企業別の求人傾向</t>
+  </si>
+  <si>
+    <t>同じ企業が何件出しているか</t>
+  </si>
+  <si>
+    <t>よく募集している技術</t>
+  </si>
+  <si>
+    <t>長期間募集している案件</t>
+  </si>
+  <si>
+    <t>求人サイト比較</t>
+  </si>
+  <si>
+    <t>サイトごとの求人件数</t>
+  </si>
+  <si>
+    <t>平均単価</t>
+  </si>
+  <si>
+    <t>フルリモート率</t>
+  </si>
+  <si>
+    <t>技術の偏り</t>
+  </si>
+  <si>
+    <t>同じ求人の重複率</t>
+  </si>
+  <si>
+    <t>重複求人分析</t>
+  </si>
+  <si>
+    <t>複数サイトに載っている案件</t>
+  </si>
+  <si>
+    <t>どのサイトが一番早く掲載したか</t>
+  </si>
+  <si>
+    <t>サイトごとの掲載遅延</t>
+  </si>
+  <si>
+    <t>新技術の急上昇</t>
+  </si>
+  <si>
+    <t>前月比で急増したスキル</t>
+  </si>
+  <si>
+    <t>3か月移動平均</t>
+  </si>
+  <si>
+    <t>急上昇ランキング</t>
+  </si>
+  <si>
+    <t>技術の衰退傾向</t>
+  </si>
+  <si>
+    <t>求人数が減っている技術</t>
+  </si>
+  <si>
+    <t>長期的な推移</t>
+  </si>
+  <si>
+    <t>ただし収集サイトや収集範囲の変化には注意</t>
+  </si>
+  <si>
+    <t>AI関連求人の推移</t>
+  </si>
+  <si>
+    <t>LLM</t>
+  </si>
+  <si>
+    <t>生成AI</t>
+  </si>
+  <si>
+    <t>RAG</t>
+  </si>
+  <si>
+    <t>AIエージェント</t>
+  </si>
+  <si>
+    <t>MLOps</t>
+  </si>
+  <si>
+    <t>「自分に合う求人」分析</t>
+  </si>
+  <si>
+    <t>登録スキルとの一致率</t>
+  </si>
+  <si>
+    <t>必須スキルの充足率</t>
+  </si>
+  <si>
+    <t>希望単価</t>
+  </si>
+  <si>
+    <t>リモート条件</t>
+  </si>
+  <si>
+    <t>新着順</t>
+  </si>
+  <si>
+    <t>不足スキル分析</t>
+  </si>
+  <si>
+    <t>自分が持っていないが、求人で頻出する技術</t>
+  </si>
+  <si>
+    <t>1つ覚えたら何件応募可能になるか</t>
+  </si>
+  <si>
+    <t>学習コスパランキング</t>
+  </si>
+  <si>
+    <t>学習ロードマップ</t>
+  </si>
+  <si>
+    <t>今のスキルセット</t>
+  </si>
+  <si>
+    <t>次に追加する技術</t>
+  </si>
+  <si>
+    <t>到達可能な求人の増加数</t>
+  </si>
+  <si>
+    <t>「Go + PostgreSQLの次はDockerかAWSか」みたいな分析</t>
+  </si>
+  <si>
+    <t>求人のおすすめ順位</t>
+  </si>
+  <si>
+    <t>スキル一致度</t>
+  </si>
+  <si>
+    <t>リモート</t>
+  </si>
+  <si>
+    <t>新着度</t>
+  </si>
+  <si>
+    <t>必須条件</t>
+  </si>
+  <si>
+    <t>総合スコア</t>
+  </si>
+  <si>
+    <t>「Goの需要を見たい」</t>
+  </si>
+  <si>
+    <t>だけでも、実は定義がいくつもある。</t>
+  </si>
+  <si>
+    <t>A. 現在掲載中のGo案件数</t>
+  </si>
+  <si>
+    <t>B. 今月新しく出たGo案件数</t>
+  </si>
+  <si>
+    <t>C. Go案件の増減率</t>
+  </si>
+  <si>
+    <t>D. Go案件の平均単価</t>
+  </si>
+  <si>
+    <t>E. Go案件で一緒に要求される技術</t>
+  </si>
+  <si>
+    <t>F. Go経験者が応募可能な案件割合</t>
+  </si>
+  <si>
+    <t>- フリーランスHub（370,000件前後） — Java、C#/.NET、Go、TypeScriptなどで大量検索可能</t>
+  </si>
+  <si>
+    <t>- SES JOB LINK（44,000件前後） — SES/業務委託案件を大量に見られる</t>
+  </si>
+  <si>
+    <t>- エイジレスフリーランス（6,000〜7,000件前後） — 年齢不問を掲げるIT案件サイト</t>
+  </si>
+  <si>
+    <t>- フリジョブ（20,000件前後） — 複数の案件サイト・エージェントの公開案件を横断検索</t>
+  </si>
+  <si>
+    <t>- フリーランスフリー（1,000〜2,000件前後） — IT案件を掲載</t>
+  </si>
+  <si>
+    <t>- レバテックフリーランス（50,000件前後）</t>
+  </si>
+  <si>
+    <t>- Midworks（10,000件前後）</t>
+  </si>
+  <si>
+    <t>- TechStock（8,000件前後）</t>
+  </si>
+  <si>
+    <t>- PE-BANK（5,000件前後）</t>
+  </si>
+  <si>
+    <t>- ギークスジョブ（5,000件前後）</t>
+  </si>
+  <si>
+    <t>- テックリーチ（10,000件前後）</t>
+  </si>
+  <si>
+    <t>- エンジニアファクトリー（10,000件前後）</t>
+  </si>
+  <si>
+    <t>- フォスターフリーランス（5,000件前後）</t>
+  </si>
+  <si>
+    <t>- フリーランススタート（100,000件前後）</t>
+  </si>
+  <si>
+    <t>- テクフリ（10,000件前後）</t>
+  </si>
+  <si>
+    <t>- エンジニアスタイル東京（300,000件前後）</t>
+  </si>
+  <si>
+    <t>- ポテパンフリーランス（2,000〜3,000件前後）</t>
+  </si>
+  <si>
+    <t>- PE-BANK案件検索（5,000件前後）</t>
+  </si>
+  <si>
+    <t>TechSpace(数千件前後) — 会員登録なしで案件閲覧可能。エンド直・元請直案件も検索対象</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ENGER(数千件前後) — 公開案件多数。ただし案件詳細の閲覧には登録が必要なものあり</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Findy Freelance(数千件前後)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>doocyJob(数千件前後)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>案件ナビ(数千件前後)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>テックビズフリーランス(数千件前後)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>サイト別の掲載件数</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>分析可能なもの（全求人 or アクティブなものだけ）</t>
     <rPh sb="0" eb="2">
       <t>ブンセキ</t>
     </rPh>
     <rPh sb="2" eb="4">
       <t>カノウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>求人総数の推移</t>
-  </si>
-  <si>
-    <t>日別・週別・月別</t>
-  </si>
-  <si>
-    <t>新規求人が増えてるか減ってるか</t>
-  </si>
-  <si>
-    <t>サイト別の掲載件数</t>
-  </si>
-  <si>
-    <t>新規求人件数</t>
-  </si>
-  <si>
-    <t>今日初めて観測した求人</t>
-  </si>
-  <si>
-    <t>先週比・先月比</t>
-  </si>
-  <si>
-    <t>「求人市場が活発か」の指標</t>
-  </si>
-  <si>
-    <t>アクティブ求人件数</t>
-  </si>
-  <si>
-    <t>last_seen_at を基準に現在も掲載されていると判断した件数</t>
-  </si>
-  <si>
-    <t>期間内に消えた求人数</t>
-  </si>
-  <si>
-    <t>求人の増減</t>
-  </si>
-  <si>
-    <t>求人の平均掲載期間</t>
-  </si>
-  <si>
-    <t>初回検出日 → 最終検出日</t>
-  </si>
-  <si>
-    <t>何日くらい募集され続けるか</t>
-  </si>
-  <si>
-    <t>長期間残る求人の割合</t>
-  </si>
-  <si>
-    <t>求人の消化速度</t>
-  </si>
-  <si>
-    <t>新規掲載から消えるまでの日数</t>
-  </si>
-  <si>
-    <t>すぐ消える求人＝応募が集まりやすい／採用が決まりやすい可能性</t>
-  </si>
-  <si>
-    <t>長く残る求人＝条件が厳しい可能性</t>
-  </si>
-  <si>
-    <t>プログラミング言語ランキング</t>
-  </si>
-  <si>
-    <t>Go</t>
-  </si>
-  <si>
-    <t>Java</t>
-  </si>
-  <si>
-    <t>C#</t>
-  </si>
-  <si>
-    <t>Python</t>
-  </si>
-  <si>
-    <t>TypeScript</t>
-  </si>
-  <si>
-    <t>PHP</t>
-  </si>
-  <si>
-    <t>求人数順</t>
-  </si>
-  <si>
-    <t>技術の人気推移</t>
-  </si>
-  <si>
-    <t>Go求人は3か月前より増えたか</t>
-  </si>
-  <si>
-    <t>Reactは横ばいか</t>
-  </si>
-  <si>
-    <t>AI関連技術は増えているか</t>
-  </si>
-  <si>
-    <t>技術ごとの時系列グラフ</t>
-  </si>
-  <si>
-    <t>言語 × フレームワーク</t>
-  </si>
-  <si>
-    <t>Java × Spring</t>
-  </si>
-  <si>
-    <t>C# × ASP.NET Core</t>
-  </si>
-  <si>
-    <t>TypeScript × React</t>
-  </si>
-  <si>
-    <t>Python × Django</t>
-  </si>
-  <si>
-    <t>Go × Gin</t>
-  </si>
-  <si>
-    <t>よくセットで要求される技術</t>
-  </si>
-  <si>
-    <t>スキルの共起分析</t>
-  </si>
-  <si>
-    <t>Go案件に一緒に出やすい技術</t>
-  </si>
-  <si>
-    <t>React案件で要求されやすい技術</t>
-  </si>
-  <si>
-    <t>PostgreSQLと一緒に出やすい技術</t>
-  </si>
-  <si>
-    <t>「次に何を覚えると求人の幅が広がるか」</t>
-  </si>
-  <si>
-    <t>必須スキルと歓迎スキルの比較</t>
-  </si>
-  <si>
-    <t>Goは必須が多いか、歓迎が多いか</t>
-  </si>
-  <si>
-    <t>AWSは必須か、あると有利程度か</t>
-  </si>
-  <si>
-    <t>Reactは必須なのか経験者歓迎なのか</t>
-  </si>
-  <si>
-    <t>カテゴリ別の需要</t>
-  </si>
-  <si>
-    <t>Language</t>
-  </si>
-  <si>
-    <t>Framework / Library</t>
-  </si>
-  <si>
-    <t>Database</t>
-  </si>
-  <si>
-    <t>Cloud</t>
-  </si>
-  <si>
-    <t>Infrastructure</t>
-  </si>
-  <si>
-    <t>Tool</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>Architecture</t>
-  </si>
-  <si>
-    <t>Methodology</t>
-  </si>
-  <si>
-    <t>給与ランキング</t>
-  </si>
-  <si>
-    <t>言語別の平均単価</t>
-  </si>
-  <si>
-    <t>フレームワーク別の平均単価</t>
-  </si>
-  <si>
-    <t>スキル別の平均単価</t>
-  </si>
-  <si>
-    <t>求人件数と単価を合わせた分析</t>
-  </si>
-  <si>
-    <t>給与レンジの分布</t>
-  </si>
-  <si>
-    <t>月40万未満</t>
-  </si>
-  <si>
-    <t>40〜60万</t>
-  </si>
-  <si>
-    <t>60〜80万</t>
-  </si>
-  <si>
-    <t>80万以上</t>
-  </si>
-  <si>
-    <t>単価の中央値</t>
-  </si>
-  <si>
-    <t>技術別の単価</t>
-  </si>
-  <si>
-    <t>Go案件の平均・中央値</t>
-  </si>
-  <si>
-    <t>Java案件の平均・中央値</t>
-  </si>
-  <si>
-    <t>C#案件の平均・中央値</t>
-  </si>
-  <si>
-    <t>React案件の平均・中央値</t>
-  </si>
-  <si>
-    <t>経験年数 × 単価</t>
-  </si>
-  <si>
-    <t>1〜2年</t>
-  </si>
-  <si>
-    <t>3〜5年</t>
-  </si>
-  <si>
-    <t>5年以上</t>
-  </si>
-  <si>
-    <t>経験年数による単価差</t>
-  </si>
-  <si>
-    <t>リモート率</t>
-  </si>
-  <si>
-    <t>フルリモート</t>
-  </si>
-  <si>
-    <t>一部リモート</t>
-  </si>
-  <si>
-    <t>常駐</t>
-  </si>
-  <si>
-    <t>技術別のリモート率</t>
-  </si>
-  <si>
-    <t>地域別求人</t>
-  </si>
-  <si>
-    <t>東京</t>
-  </si>
-  <si>
-    <t>大阪</t>
-  </si>
-  <si>
-    <t>名古屋</t>
-  </si>
-  <si>
-    <t>福岡</t>
-  </si>
-  <si>
-    <t>地方</t>
-  </si>
-  <si>
-    <t>都道府県ごとの求人密度</t>
-  </si>
-  <si>
-    <t>地域 × 単価</t>
-  </si>
-  <si>
-    <t>東京は高単価だが常駐が多い</t>
-  </si>
-  <si>
-    <t>地方は求人が少ないがフルリモート率が高い</t>
-  </si>
-  <si>
-    <t>地域ごとの比較</t>
-  </si>
-  <si>
-    <t>雇用形態の割合</t>
-  </si>
-  <si>
-    <t>正社員</t>
-  </si>
-  <si>
-    <t>業務委託</t>
-  </si>
-  <si>
-    <t>派遣</t>
-  </si>
-  <si>
-    <t>副業</t>
-  </si>
-  <si>
-    <t>アルバイト</t>
-  </si>
-  <si>
-    <t>勤務条件</t>
-  </si>
-  <si>
-    <t>週5</t>
-  </si>
-  <si>
-    <t>週4</t>
-  </si>
-  <si>
-    <t>週3</t>
-  </si>
-  <si>
-    <t>時短</t>
-  </si>
-  <si>
-    <t>副業可</t>
-  </si>
-  <si>
-    <t>案件の競争度っぽい指標</t>
-  </si>
-  <si>
-    <t>掲載期間</t>
-  </si>
-  <si>
-    <t>単価</t>
-  </si>
-  <si>
-    <t>必須スキル数</t>
-  </si>
-  <si>
-    <t>条件の良さ</t>
-  </si>
-  <si>
-    <t>※応募数が取れないなら推定になる</t>
-  </si>
-  <si>
-    <t>求人の難易度</t>
-  </si>
-  <si>
-    <t>必須経験年数</t>
-  </si>
-  <si>
-    <t>求められる技術カテゴリ数</t>
-  </si>
-  <si>
-    <t>「要求が盛られている求人」を可視化</t>
-  </si>
-  <si>
-    <t>スキル要求数ランキング</t>
-  </si>
-  <si>
-    <t>必須スキルが多い求人</t>
-  </si>
-  <si>
-    <t>「全部入り案件」</t>
-  </si>
-  <si>
-    <t>技術スタックが広すぎる求人</t>
-  </si>
-  <si>
-    <t>技術スタックの複雑度</t>
-  </si>
-  <si>
-    <t>言語1個＋FW1個</t>
-  </si>
-  <si>
-    <t>言語3個＋Cloud＋Docker＋Kubernetes＋CI/CD</t>
-  </si>
-  <si>
-    <t>求人ごとの要求範囲</t>
-  </si>
-  <si>
-    <t>求人文の長さ</t>
-  </si>
-  <si>
-    <t>説明文が長い求人</t>
-  </si>
-  <si>
-    <t>短すぎる求人</t>
-  </si>
-  <si>
-    <t>情報量と単価の関係</t>
-  </si>
-  <si>
-    <t>企業別の求人傾向</t>
-  </si>
-  <si>
-    <t>同じ企業が何件出しているか</t>
-  </si>
-  <si>
-    <t>よく募集している技術</t>
-  </si>
-  <si>
-    <t>長期間募集している案件</t>
-  </si>
-  <si>
-    <t>求人サイト比較</t>
-  </si>
-  <si>
-    <t>サイトごとの求人件数</t>
-  </si>
-  <si>
-    <t>平均単価</t>
-  </si>
-  <si>
-    <t>フルリモート率</t>
-  </si>
-  <si>
-    <t>技術の偏り</t>
-  </si>
-  <si>
-    <t>同じ求人の重複率</t>
-  </si>
-  <si>
-    <t>重複求人分析</t>
-  </si>
-  <si>
-    <t>複数サイトに載っている案件</t>
-  </si>
-  <si>
-    <t>どのサイトが一番早く掲載したか</t>
-  </si>
-  <si>
-    <t>サイトごとの掲載遅延</t>
-  </si>
-  <si>
-    <t>新技術の急上昇</t>
-  </si>
-  <si>
-    <t>前月比で急増したスキル</t>
-  </si>
-  <si>
-    <t>3か月移動平均</t>
-  </si>
-  <si>
-    <t>急上昇ランキング</t>
-  </si>
-  <si>
-    <t>技術の衰退傾向</t>
-  </si>
-  <si>
-    <t>求人数が減っている技術</t>
-  </si>
-  <si>
-    <t>長期的な推移</t>
-  </si>
-  <si>
-    <t>ただし収集サイトや収集範囲の変化には注意</t>
-  </si>
-  <si>
-    <t>AI関連求人の推移</t>
-  </si>
-  <si>
-    <t>LLM</t>
-  </si>
-  <si>
-    <t>生成AI</t>
-  </si>
-  <si>
-    <t>RAG</t>
-  </si>
-  <si>
-    <t>AIエージェント</t>
-  </si>
-  <si>
-    <t>MLOps</t>
-  </si>
-  <si>
-    <t>「自分に合う求人」分析</t>
-  </si>
-  <si>
-    <t>登録スキルとの一致率</t>
-  </si>
-  <si>
-    <t>必須スキルの充足率</t>
-  </si>
-  <si>
-    <t>希望単価</t>
-  </si>
-  <si>
-    <t>リモート条件</t>
-  </si>
-  <si>
-    <t>新着順</t>
-  </si>
-  <si>
-    <t>不足スキル分析</t>
-  </si>
-  <si>
-    <t>自分が持っていないが、求人で頻出する技術</t>
-  </si>
-  <si>
-    <t>1つ覚えたら何件応募可能になるか</t>
-  </si>
-  <si>
-    <t>学習コスパランキング</t>
-  </si>
-  <si>
-    <t>学習ロードマップ</t>
-  </si>
-  <si>
-    <t>今のスキルセット</t>
-  </si>
-  <si>
-    <t>次に追加する技術</t>
-  </si>
-  <si>
-    <t>到達可能な求人の増加数</t>
-  </si>
-  <si>
-    <t>「Go + PostgreSQLの次はDockerかAWSか」みたいな分析</t>
-  </si>
-  <si>
-    <t>求人のおすすめ順位</t>
-  </si>
-  <si>
-    <t>スキル一致度</t>
-  </si>
-  <si>
-    <t>リモート</t>
-  </si>
-  <si>
-    <t>新着度</t>
-  </si>
-  <si>
-    <t>必須条件</t>
-  </si>
-  <si>
-    <t>総合スコア</t>
-  </si>
-  <si>
-    <t>「Goの需要を見たい」</t>
-  </si>
-  <si>
-    <t>だけでも、実は定義がいくつもある。</t>
-  </si>
-  <si>
-    <t>A. 現在掲載中のGo案件数</t>
-  </si>
-  <si>
-    <t>B. 今月新しく出たGo案件数</t>
-  </si>
-  <si>
-    <t>C. Go案件の増減率</t>
-  </si>
-  <si>
-    <t>D. Go案件の平均単価</t>
-  </si>
-  <si>
-    <t>E. Go案件で一緒に要求される技術</t>
-  </si>
-  <si>
-    <t>F. Go経験者が応募可能な案件割合</t>
-  </si>
-  <si>
-    <t>- フリーランスHub（370,000件前後） — Java、C#/.NET、Go、TypeScriptなどで大量検索可能</t>
-  </si>
-  <si>
-    <t>- SES JOB LINK（44,000件前後） — SES/業務委託案件を大量に見られる</t>
-  </si>
-  <si>
-    <t>- エイジレスフリーランス（6,000〜7,000件前後） — 年齢不問を掲げるIT案件サイト</t>
-  </si>
-  <si>
-    <t>- フリジョブ（20,000件前後） — 複数の案件サイト・エージェントの公開案件を横断検索</t>
-  </si>
-  <si>
-    <t>- フリーランスフリー（1,000〜2,000件前後） — IT案件を掲載</t>
-  </si>
-  <si>
-    <t>- レバテックフリーランス（50,000件前後）</t>
-  </si>
-  <si>
-    <t>- Midworks（10,000件前後）</t>
-  </si>
-  <si>
-    <t>- TechStock（8,000件前後）</t>
-  </si>
-  <si>
-    <t>- PE-BANK（5,000件前後）</t>
-  </si>
-  <si>
-    <t>- ギークスジョブ（5,000件前後）</t>
-  </si>
-  <si>
-    <t>- テックリーチ（10,000件前後）</t>
-  </si>
-  <si>
-    <t>- エンジニアファクトリー（10,000件前後）</t>
-  </si>
-  <si>
-    <t>- フォスターフリーランス（5,000件前後）</t>
-  </si>
-  <si>
-    <t>- フリーランススタート（100,000件前後）</t>
-  </si>
-  <si>
-    <t>- テクフリ（10,000件前後）</t>
-  </si>
-  <si>
-    <t>- エンジニアスタイル東京（300,000件前後）</t>
-  </si>
-  <si>
-    <t>- ポテパンフリーランス（2,000〜3,000件前後）</t>
-  </si>
-  <si>
-    <t>- PE-BANK案件検索（5,000件前後）</t>
-  </si>
-  <si>
-    <t>TechSpace(数千件前後) — 会員登録なしで案件閲覧可能。エンド直・元請直案件も検索対象</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ENGER(数千件前後) — 公開案件多数。ただし案件詳細の閲覧には登録が必要なものあり</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Findy Freelance(数千件前後)</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>doocyJob(数千件前後)</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>案件ナビ(数千件前後)</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>テックビズフリーランス(数千件前後)</t>
-    <phoneticPr fontId="2"/>
+    <rPh sb="8" eb="11">
+      <t>ゼンキュウジン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>そもそもスクレイピング禁止が多い</t>
+    <rPh sb="14" eb="15">
+      <t>オオ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>グラフライブラリ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>候補</t>
+  </si>
+  <si>
+    <t>ライブラリ</t>
+  </si>
+  <si>
+    <t>Reactとの相性</t>
+  </si>
+  <si>
+    <t>使いやすさ</t>
+  </si>
+  <si>
+    <t>向いてる用途</t>
+  </si>
+  <si>
+    <t>Recharts</t>
+  </si>
+  <si>
+    <t>◎</t>
+  </si>
+  <si>
+    <t>★★★★★</t>
+  </si>
+  <si>
+    <t>ダッシュボード、棒/折れ線/円グラフ</t>
+  </si>
+  <si>
+    <t>Nivo</t>
+  </si>
+  <si>
+    <t>★★★★☆</t>
+  </si>
+  <si>
+    <t>見栄えのいい分析ダッシュボード</t>
+  </si>
+  <si>
+    <t>Chart.js + react-chartjs-2</t>
+  </si>
+  <si>
+    <t>一般的なグラフ全般</t>
+  </si>
+  <si>
+    <t>Apache ECharts</t>
+  </si>
+  <si>
+    <t>★★★☆☆</t>
+  </si>
+  <si>
+    <t>高機能・大量データ・複雑なグラフ</t>
+  </si>
+  <si>
+    <t>Victory</t>
+  </si>
+  <si>
+    <t>Reactらしい宣言的なグラフ</t>
+  </si>
+  <si>
+    <t>Plotly</t>
+  </si>
+  <si>
+    <t>○</t>
+  </si>
+  <si>
+    <t>分析・散布図・高度な可視化</t>
   </si>
 </sst>
 </file>
@@ -9448,7 +9530,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9561,6 +9643,15 @@
     <font>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
+      <name val="BIZ UDゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="BIZ UDゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -9890,7 +9981,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -10069,6 +10160,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -17759,19 +17851,19 @@
     <row r="2" spans="1:23" ht="19.2">
       <c r="A2" s="108"/>
       <c r="B2" s="107" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="19.2">
       <c r="A3" s="107"/>
       <c r="B3" s="107" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="19.2">
       <c r="A4" s="107"/>
       <c r="B4" s="107" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="18.600000000000001" thickBot="1">
@@ -18034,19 +18126,19 @@
     </row>
     <row r="6" spans="1:15">
       <c r="D6" s="109" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="G6" s="109" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="M6" s="100"/>
       <c r="O6" s="100" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="D7" s="98" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="M7" s="100"/>
       <c r="O7" s="100"/>
@@ -18097,7 +18189,7 @@
       </c>
       <c r="M13" s="100"/>
       <c r="O13" s="98" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -18105,11 +18197,11 @@
     </row>
     <row r="15" spans="1:15">
       <c r="G15" s="98" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="M15" s="100"/>
       <c r="O15" s="98" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -18135,7 +18227,7 @@
     </row>
     <row r="20" spans="2:17">
       <c r="O20" s="100" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="22" spans="2:17">
@@ -18143,7 +18235,7 @@
         <v>1753</v>
       </c>
       <c r="Q22" s="98" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="23" spans="2:17">
@@ -18162,7 +18254,7 @@
         <v>1754</v>
       </c>
       <c r="Q25" s="102" t="s">
-        <v>1756</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="26" spans="2:17">
@@ -18170,7 +18262,7 @@
         <v>1748</v>
       </c>
       <c r="Q26" s="99" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="27" spans="2:17">
@@ -18178,7 +18270,7 @@
         <v>1749</v>
       </c>
       <c r="Q27" s="99" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="28" spans="2:17">
@@ -18194,7 +18286,7 @@
         <v>1751</v>
       </c>
       <c r="Q29" s="98" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="30" spans="2:17">
@@ -18202,7 +18294,7 @@
         <v>1752</v>
       </c>
       <c r="Q30" s="101" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="31" spans="2:17">
@@ -18212,7 +18304,7 @@
     </row>
     <row r="32" spans="2:17">
       <c r="B32" s="98" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="33" spans="2:15">
@@ -18232,23 +18324,24 @@
     </row>
     <row r="37" spans="2:15">
       <c r="B37" s="98" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="38" spans="2:15">
       <c r="B38" s="98" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="J38" s="109" t="s">
         <v>1715</v>
       </c>
       <c r="N38" s="109" t="s">
-        <v>2014</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="39" spans="2:15">
+      <c r="N39" s="110"/>
       <c r="O39" s="98" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="40" spans="2:15">
@@ -18258,14 +18351,16 @@
       <c r="J40" s="98" t="s">
         <v>1708</v>
       </c>
+      <c r="N40" s="110"/>
     </row>
     <row r="41" spans="2:15">
       <c r="B41" s="99"/>
       <c r="J41" s="98" t="s">
         <v>1709</v>
       </c>
+      <c r="N41" s="110"/>
       <c r="O41" s="98" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="42" spans="2:15">
@@ -18275,8 +18370,9 @@
       <c r="J42" s="98" t="s">
         <v>1710</v>
       </c>
+      <c r="N42" s="110"/>
       <c r="O42" s="98" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="43" spans="2:15">
@@ -18286,8 +18382,11 @@
       <c r="J43" s="98" t="s">
         <v>1711</v>
       </c>
+      <c r="N43" s="110" t="s">
+        <v>2223</v>
+      </c>
       <c r="O43" s="98" t="s">
-        <v>2018</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="44" spans="2:15">
@@ -18297,6 +18396,7 @@
       <c r="J44" s="98" t="s">
         <v>1719</v>
       </c>
+      <c r="N44" s="110"/>
     </row>
     <row r="45" spans="2:15">
       <c r="B45" s="99" t="s">
@@ -18305,8 +18405,9 @@
       <c r="J45" s="98" t="s">
         <v>1720</v>
       </c>
+      <c r="N45" s="110"/>
       <c r="O45" s="98" t="s">
-        <v>2019</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="46" spans="2:15">
@@ -18316,51 +18417,57 @@
       <c r="J46" s="98" t="s">
         <v>1712</v>
       </c>
+      <c r="N46" s="110"/>
     </row>
     <row r="47" spans="2:15">
       <c r="B47" s="98" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="J47" s="98" t="s">
         <v>1713</v>
       </c>
+      <c r="N47" s="110"/>
       <c r="O47" s="98" t="s">
-        <v>2020</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="48" spans="2:15">
       <c r="J48" s="98" t="s">
         <v>1716</v>
       </c>
+      <c r="N48" s="110"/>
       <c r="O48" s="98" t="s">
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="49" spans="2:15">
       <c r="J49" s="98" t="s">
         <v>1717</v>
       </c>
+      <c r="N49" s="110"/>
       <c r="O49" s="98" t="s">
-        <v>2022</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="50" spans="2:15">
       <c r="B50" s="109" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="J50" s="98" t="s">
         <v>1718</v>
       </c>
+      <c r="N50" s="110"/>
     </row>
     <row r="51" spans="2:15">
       <c r="B51" s="98" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="J51" s="98" t="s">
         <v>1721</v>
       </c>
+      <c r="N51" s="110"/>
       <c r="O51" s="98" t="s">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="52" spans="2:15">
@@ -18368,1270 +18475,1735 @@
       <c r="J52" s="98" t="s">
         <v>1722</v>
       </c>
+      <c r="N52" s="110"/>
     </row>
     <row r="53" spans="2:15">
       <c r="B53" s="99" t="s">
-        <v>2202</v>
+        <v>2199</v>
       </c>
       <c r="J53" s="98" t="s">
         <v>1728</v>
       </c>
+      <c r="N53" s="110"/>
       <c r="O53" s="98" t="s">
-        <v>2024</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="54" spans="2:15">
       <c r="B54" s="99" t="s">
-        <v>2203</v>
+        <v>2200</v>
       </c>
       <c r="J54" s="98" t="s">
         <v>307</v>
       </c>
+      <c r="N54" s="110"/>
       <c r="O54" s="98" t="s">
-        <v>2025</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="55" spans="2:15">
       <c r="B55" s="99" t="s">
-        <v>2204</v>
-      </c>
+        <v>2201</v>
+      </c>
+      <c r="N55" s="110"/>
       <c r="O55" s="98" t="s">
-        <v>2026</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="56" spans="2:15">
       <c r="B56" s="99" t="s">
-        <v>2205</v>
-      </c>
+        <v>2202</v>
+      </c>
+      <c r="N56" s="110"/>
     </row>
     <row r="57" spans="2:15">
       <c r="B57" s="98" t="s">
-        <v>2206</v>
-      </c>
+        <v>2203</v>
+      </c>
+      <c r="N57" s="110"/>
       <c r="O57" s="98" t="s">
-        <v>2027</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="58" spans="2:15">
       <c r="B58" s="98" t="s">
-        <v>2220</v>
-      </c>
+        <v>2217</v>
+      </c>
+      <c r="N58" s="110"/>
     </row>
     <row r="59" spans="2:15">
       <c r="B59" s="98" t="s">
-        <v>2221</v>
-      </c>
+        <v>2218</v>
+      </c>
+      <c r="N59" s="110"/>
       <c r="O59" s="98" t="s">
-        <v>2028</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="60" spans="2:15">
+      <c r="N60" s="110"/>
       <c r="O60" s="98" t="s">
-        <v>2029</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="61" spans="2:15">
       <c r="B61" s="98" t="s">
-        <v>1936</v>
-      </c>
+        <v>1935</v>
+      </c>
+      <c r="N61" s="110"/>
       <c r="O61" s="98" t="s">
-        <v>2030</v>
-      </c>
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="62" spans="2:15">
+      <c r="N62" s="110"/>
     </row>
     <row r="63" spans="2:15">
       <c r="B63" s="98" t="s">
-        <v>2207</v>
+        <v>2204</v>
       </c>
       <c r="F63" s="109" t="s">
-        <v>1955</v>
-      </c>
+        <v>1954</v>
+      </c>
+      <c r="N63" s="110"/>
       <c r="O63" s="98" t="s">
-        <v>2031</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="64" spans="2:15">
       <c r="B64" s="98" t="s">
-        <v>2208</v>
-      </c>
+        <v>2205</v>
+      </c>
+      <c r="N64" s="110"/>
     </row>
     <row r="65" spans="2:18">
       <c r="B65" s="98" t="s">
-        <v>2209</v>
+        <v>2206</v>
       </c>
       <c r="F65" s="98" t="s">
-        <v>1945</v>
-      </c>
+        <v>1944</v>
+      </c>
+      <c r="N65" s="110"/>
       <c r="O65" s="98" t="s">
-        <v>2032</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="66" spans="2:18">
       <c r="B66" s="98" t="s">
-        <v>2210</v>
+        <v>2207</v>
       </c>
       <c r="F66" s="98" t="s">
-        <v>1946</v>
-      </c>
+        <v>1945</v>
+      </c>
+      <c r="N66" s="110"/>
       <c r="O66" s="98" t="s">
-        <v>2033</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="67" spans="2:18">
       <c r="B67" s="98" t="s">
-        <v>2211</v>
+        <v>2208</v>
       </c>
       <c r="F67" s="98" t="s">
-        <v>1947</v>
-      </c>
+        <v>1946</v>
+      </c>
+      <c r="N67" s="110"/>
       <c r="O67" s="98" t="s">
-        <v>2034</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="68" spans="2:18">
       <c r="B68" s="98" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
       <c r="F68" s="98" t="s">
-        <v>1948</v>
-      </c>
+        <v>1947</v>
+      </c>
+      <c r="N68" s="110"/>
     </row>
     <row r="69" spans="2:18">
       <c r="B69" s="98" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="F69" s="98" t="s">
-        <v>1949</v>
+        <v>1948</v>
+      </c>
+      <c r="N69" s="110" t="s">
+        <v>2223</v>
       </c>
       <c r="O69" s="98" t="s">
-        <v>2035</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="70" spans="2:18">
       <c r="B70" s="98" t="s">
-        <v>2213</v>
+        <v>2210</v>
       </c>
       <c r="F70" s="98" t="s">
-        <v>1950</v>
-      </c>
+        <v>1949</v>
+      </c>
+      <c r="N70" s="110"/>
     </row>
     <row r="71" spans="2:18">
       <c r="B71" s="98" t="s">
-        <v>2214</v>
+        <v>2211</v>
       </c>
       <c r="F71" s="98" t="s">
-        <v>1951</v>
+        <v>1950</v>
+      </c>
+      <c r="N71" s="110" t="s">
+        <v>2223</v>
       </c>
       <c r="O71" s="98" t="s">
-        <v>2036</v>
+        <v>2033</v>
       </c>
       <c r="R71" s="98" t="s">
-        <v>2194</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="72" spans="2:18">
       <c r="B72" s="98" t="s">
-        <v>2215</v>
+        <v>2212</v>
       </c>
       <c r="F72" s="98" t="s">
-        <v>1952</v>
+        <v>1951</v>
+      </c>
+      <c r="N72" s="110" t="s">
+        <v>2223</v>
       </c>
       <c r="O72" s="98" t="s">
-        <v>2037</v>
+        <v>2034</v>
       </c>
       <c r="R72" s="98" t="s">
-        <v>2195</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="73" spans="2:18">
       <c r="B73" s="98" t="s">
-        <v>2216</v>
+        <v>2213</v>
       </c>
       <c r="F73" s="98" t="s">
-        <v>1953</v>
+        <v>1952</v>
+      </c>
+      <c r="N73" s="110" t="s">
+        <v>2223</v>
       </c>
       <c r="O73" s="98" t="s">
-        <v>2038</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="74" spans="2:18">
       <c r="B74" s="98" t="s">
+        <v>2220</v>
+      </c>
+      <c r="F74" s="98" t="s">
+        <v>1953</v>
+      </c>
+      <c r="N74" s="110" t="s">
         <v>2223</v>
       </c>
-      <c r="F74" s="98" t="s">
-        <v>1954</v>
-      </c>
       <c r="O74" s="98" t="s">
-        <v>2039</v>
+        <v>2036</v>
       </c>
       <c r="R74" s="98" t="s">
-        <v>2196</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="75" spans="2:18">
       <c r="B75" s="98" t="s">
-        <v>2224</v>
+        <v>2221</v>
+      </c>
+      <c r="N75" s="110" t="s">
+        <v>2223</v>
       </c>
       <c r="O75" s="98" t="s">
-        <v>2040</v>
+        <v>2037</v>
       </c>
       <c r="R75" s="98" t="s">
-        <v>2197</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="76" spans="2:18">
       <c r="B76" s="98" t="s">
-        <v>2217</v>
+        <v>2214</v>
+      </c>
+      <c r="N76" s="110" t="s">
+        <v>2223</v>
       </c>
       <c r="O76" s="98" t="s">
-        <v>2041</v>
+        <v>2038</v>
       </c>
       <c r="R76" s="98" t="s">
-        <v>2198</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="77" spans="2:18">
       <c r="B77" s="98" t="s">
-        <v>2225</v>
-      </c>
+        <v>2222</v>
+      </c>
+      <c r="N77" s="110"/>
       <c r="O77" s="98" t="s">
-        <v>2042</v>
+        <v>2039</v>
       </c>
       <c r="R77" s="98" t="s">
-        <v>2199</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="78" spans="2:18">
       <c r="B78" s="98" t="s">
-        <v>2218</v>
-      </c>
+        <v>2215</v>
+      </c>
+      <c r="N78" s="110"/>
       <c r="R78" s="98" t="s">
-        <v>2200</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="79" spans="2:18">
       <c r="B79" s="98" t="s">
-        <v>2219</v>
-      </c>
+        <v>2216</v>
+      </c>
+      <c r="N79" s="110"/>
       <c r="O79" s="98" t="s">
-        <v>2043</v>
+        <v>2040</v>
       </c>
       <c r="R79" s="98" t="s">
-        <v>2201</v>
-      </c>
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="80" spans="2:18">
+      <c r="N80" s="110"/>
     </row>
     <row r="81" spans="1:15">
+      <c r="N81" s="110"/>
       <c r="O81" s="98" t="s">
-        <v>2044</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="82" spans="1:15">
       <c r="B82" s="109" t="s">
-        <v>1939</v>
-      </c>
+        <v>1938</v>
+      </c>
+      <c r="N82" s="110"/>
       <c r="O82" s="98" t="s">
-        <v>2045</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="83" spans="1:15">
       <c r="A83" s="98" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="B83" s="98" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="E83" s="98" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="G83" s="98" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="I83" s="98" t="s">
-        <v>1993</v>
-      </c>
+        <v>1992</v>
+      </c>
+      <c r="N83" s="110"/>
       <c r="O83" s="98" t="s">
-        <v>2046</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="84" spans="1:15">
+      <c r="N84" s="110"/>
       <c r="O84" s="98" t="s">
-        <v>2047</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="85" spans="1:15">
       <c r="B85" s="98" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="E85" s="98" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="G85" s="98" t="s">
         <v>155</v>
       </c>
       <c r="I85" s="98" t="s">
-        <v>1943</v>
-      </c>
+        <v>1942</v>
+      </c>
+      <c r="N85" s="110"/>
     </row>
     <row r="86" spans="1:15">
       <c r="E86" s="98" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="F86" s="98" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="G86" s="98" t="s">
         <v>231</v>
       </c>
       <c r="I86" s="98" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="J86" s="98" t="s">
-        <v>1992</v>
-      </c>
+        <v>1991</v>
+      </c>
+      <c r="N86" s="110"/>
       <c r="O86" s="98" t="s">
-        <v>2048</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="87" spans="1:15">
       <c r="B87" s="98" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="E87" s="98" t="s">
-        <v>1995</v>
-      </c>
+        <v>1994</v>
+      </c>
+      <c r="N87" s="110"/>
     </row>
     <row r="88" spans="1:15">
       <c r="B88" s="98" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="E88" s="98" t="s">
-        <v>1998</v>
-      </c>
+        <v>1997</v>
+      </c>
+      <c r="N88" s="110"/>
       <c r="O88" s="98" t="s">
-        <v>2049</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="89" spans="1:15">
+      <c r="N89" s="110"/>
       <c r="O89" s="98" t="s">
-        <v>2050</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="90" spans="1:15">
       <c r="B90" s="98" t="s">
-        <v>1959</v>
-      </c>
+        <v>1958</v>
+      </c>
+      <c r="N90" s="110"/>
       <c r="O90" s="98" t="s">
-        <v>2051</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="91" spans="1:15">
       <c r="B91" s="98" t="s">
-        <v>1960</v>
-      </c>
+        <v>1959</v>
+      </c>
+      <c r="N91" s="110"/>
       <c r="O91" s="98" t="s">
-        <v>2052</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="92" spans="1:15">
       <c r="B92" s="98" t="s">
-        <v>1961</v>
-      </c>
+        <v>1960</v>
+      </c>
+      <c r="N92" s="110"/>
       <c r="O92" s="98" t="s">
-        <v>2053</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="93" spans="1:15">
       <c r="B93" s="98" t="s">
-        <v>1962</v>
-      </c>
+        <v>1961</v>
+      </c>
+      <c r="N93" s="110"/>
       <c r="O93" s="98" t="s">
-        <v>2054</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="94" spans="1:15">
       <c r="B94" s="98" t="s">
-        <v>1963</v>
-      </c>
+        <v>1962</v>
+      </c>
+      <c r="N94" s="110"/>
     </row>
     <row r="95" spans="1:15">
+      <c r="N95" s="110"/>
       <c r="O95" s="98" t="s">
-        <v>2055</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="96" spans="1:15">
       <c r="B96" s="98" t="s">
-        <v>1964</v>
-      </c>
+        <v>1963</v>
+      </c>
+      <c r="N96" s="110"/>
     </row>
     <row r="97" spans="2:15">
       <c r="B97" s="98" t="s">
-        <v>1965</v>
-      </c>
+        <v>1964</v>
+      </c>
+      <c r="N97" s="110"/>
       <c r="O97" s="98" t="s">
-        <v>2056</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="98" spans="2:15">
       <c r="B98" s="98" t="s">
-        <v>1966</v>
-      </c>
+        <v>1965</v>
+      </c>
+      <c r="N98" s="110"/>
       <c r="O98" s="98" t="s">
-        <v>2057</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="99" spans="2:15">
+      <c r="N99" s="110"/>
       <c r="O99" s="98" t="s">
-        <v>2058</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="100" spans="2:15">
       <c r="B100" s="98" t="s">
-        <v>1967</v>
-      </c>
+        <v>1966</v>
+      </c>
+      <c r="N100" s="110"/>
       <c r="O100" s="98" t="s">
-        <v>2059</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="101" spans="2:15">
       <c r="B101" s="98" t="s">
-        <v>1968</v>
-      </c>
+        <v>1967</v>
+      </c>
+      <c r="N101" s="110"/>
     </row>
     <row r="102" spans="2:15">
+      <c r="N102" s="110"/>
       <c r="O102" s="98" t="s">
-        <v>2060</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="103" spans="2:15">
       <c r="B103" s="98" t="s">
-        <v>1969</v>
-      </c>
+        <v>1968</v>
+      </c>
+      <c r="N103" s="110"/>
     </row>
     <row r="104" spans="2:15">
       <c r="B104" s="98" t="s">
-        <v>1970</v>
-      </c>
+        <v>1969</v>
+      </c>
+      <c r="N104" s="110"/>
       <c r="O104" s="98" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="105" spans="2:15">
       <c r="B105" s="98" t="s">
-        <v>1971</v>
-      </c>
+        <v>1970</v>
+      </c>
+      <c r="N105" s="110"/>
       <c r="O105" s="98" t="s">
-        <v>2062</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="106" spans="2:15">
+      <c r="N106" s="110"/>
       <c r="O106" s="98" t="s">
-        <v>2063</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="107" spans="2:15">
       <c r="B107" s="98" t="s">
-        <v>1972</v>
-      </c>
+        <v>1971</v>
+      </c>
+      <c r="N107" s="110"/>
     </row>
     <row r="108" spans="2:15">
       <c r="B108" s="98" t="s">
-        <v>1973</v>
-      </c>
+        <v>1972</v>
+      </c>
+      <c r="N108" s="110"/>
       <c r="O108" s="98" t="s">
-        <v>2064</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="109" spans="2:15">
       <c r="B109" s="98" t="s">
-        <v>1974</v>
-      </c>
+        <v>1973</v>
+      </c>
+      <c r="N109" s="110"/>
     </row>
     <row r="110" spans="2:15">
       <c r="B110" s="98" t="s">
-        <v>1975</v>
-      </c>
+        <v>1974</v>
+      </c>
+      <c r="N110" s="110"/>
       <c r="O110" s="98" t="s">
-        <v>2065</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="111" spans="2:15">
       <c r="B111" s="98" t="s">
-        <v>1976</v>
-      </c>
+        <v>1975</v>
+      </c>
+      <c r="N111" s="110"/>
       <c r="O111" s="98" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="112" spans="2:15">
+      <c r="N112" s="110"/>
+      <c r="O112" s="98" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15">
+      <c r="N113" s="110"/>
+      <c r="O113" s="98" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15">
+      <c r="N114" s="110"/>
+      <c r="O114" s="98" t="s">
         <v>2066</v>
       </c>
     </row>
-    <row r="112" spans="2:15">
-      <c r="O112" s="98" t="s">
+    <row r="115" spans="1:15">
+      <c r="N115" s="110"/>
+      <c r="O115" s="98" t="s">
         <v>2067</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15">
-      <c r="O113" s="98" t="s">
-        <v>2068</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15">
-      <c r="O114" s="98" t="s">
-        <v>2069</v>
-      </c>
-    </row>
-    <row r="115" spans="1:15">
-      <c r="O115" s="98" t="s">
-        <v>2070</v>
       </c>
     </row>
     <row r="116" spans="1:15">
       <c r="A116" s="98" t="s">
-        <v>1977</v>
-      </c>
+        <v>1976</v>
+      </c>
+      <c r="N116" s="110"/>
       <c r="O116" s="98" t="s">
-        <v>2071</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="117" spans="1:15">
       <c r="B117" s="98" t="s">
-        <v>1978</v>
-      </c>
+        <v>1977</v>
+      </c>
+      <c r="N117" s="110"/>
       <c r="O117" s="98" t="s">
-        <v>2072</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="118" spans="1:15">
       <c r="B118" s="98" t="s">
-        <v>1979</v>
-      </c>
+        <v>1978</v>
+      </c>
+      <c r="N118" s="110"/>
       <c r="O118" s="98" t="s">
-        <v>2073</v>
-      </c>
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15">
+      <c r="N119" s="110"/>
     </row>
     <row r="120" spans="1:15">
       <c r="B120" s="98" t="s">
-        <v>1980</v>
+        <v>1979</v>
+      </c>
+      <c r="N120" s="110" t="s">
+        <v>2223</v>
       </c>
       <c r="O120" s="98" t="s">
-        <v>2074</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="121" spans="1:15">
       <c r="B121" s="98" t="s">
-        <v>1981</v>
-      </c>
+        <v>1980</v>
+      </c>
+      <c r="N121" s="110"/>
     </row>
     <row r="122" spans="1:15">
+      <c r="N122" s="110" t="s">
+        <v>2223</v>
+      </c>
       <c r="O122" s="98" t="s">
-        <v>2075</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="123" spans="1:15">
       <c r="B123" s="98" t="s">
-        <v>1982</v>
+        <v>1981</v>
+      </c>
+      <c r="N123" s="110" t="s">
+        <v>2223</v>
       </c>
       <c r="O123" s="98" t="s">
-        <v>2076</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="124" spans="1:15">
       <c r="B124" s="98" t="s">
-        <v>1985</v>
+        <v>1984</v>
+      </c>
+      <c r="N124" s="110" t="s">
+        <v>2223</v>
       </c>
       <c r="O124" s="98" t="s">
-        <v>2077</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="125" spans="1:15">
       <c r="B125" s="98" t="s">
-        <v>1986</v>
-      </c>
+        <v>1985</v>
+      </c>
+      <c r="N125" s="110"/>
       <c r="O125" s="98" t="s">
-        <v>2078</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="126" spans="1:15">
       <c r="B126" s="98" t="s">
-        <v>1989</v>
-      </c>
+        <v>1988</v>
+      </c>
+      <c r="N126" s="110"/>
     </row>
     <row r="127" spans="1:15">
       <c r="B127" s="98" t="s">
-        <v>1987</v>
-      </c>
+        <v>1986</v>
+      </c>
+      <c r="N127" s="110"/>
       <c r="O127" s="98" t="s">
-        <v>2079</v>
-      </c>
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15">
+      <c r="N128" s="110"/>
     </row>
     <row r="129" spans="1:15">
       <c r="B129" s="98" t="s">
-        <v>1983</v>
-      </c>
+        <v>1982</v>
+      </c>
+      <c r="N129" s="110"/>
       <c r="O129" s="98" t="s">
-        <v>2080</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="130" spans="1:15">
       <c r="B130" s="98" t="s">
-        <v>1988</v>
-      </c>
+        <v>1987</v>
+      </c>
+      <c r="N130" s="110"/>
       <c r="O130" s="98" t="s">
-        <v>2081</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="131" spans="1:15">
       <c r="B131" s="98" t="s">
-        <v>1984</v>
-      </c>
+        <v>1983</v>
+      </c>
+      <c r="N131" s="110"/>
       <c r="O131" s="98" t="s">
-        <v>2082</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="132" spans="1:15">
+      <c r="N132" s="110"/>
       <c r="O132" s="98" t="s">
-        <v>2083</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="133" spans="1:15">
+      <c r="N133" s="110"/>
       <c r="O133" s="98" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="134" spans="1:15">
       <c r="A134" s="98" t="s">
-        <v>2000</v>
-      </c>
+        <v>1999</v>
+      </c>
+      <c r="N134" s="110"/>
     </row>
     <row r="135" spans="1:15">
       <c r="B135" s="98" t="s">
-        <v>2001</v>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="N135" s="110"/>
       <c r="O135" s="98" t="s">
-        <v>2085</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="136" spans="1:15">
       <c r="B136" s="98" t="s">
-        <v>1842</v>
-      </c>
+        <v>1841</v>
+      </c>
+      <c r="N136" s="110"/>
     </row>
     <row r="137" spans="1:15">
       <c r="B137" s="98" t="s">
-        <v>2002</v>
-      </c>
+        <v>2001</v>
+      </c>
+      <c r="N137" s="110"/>
       <c r="O137" s="98" t="s">
-        <v>2086</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="138" spans="1:15">
       <c r="B138" s="98" t="s">
-        <v>2003</v>
-      </c>
+        <v>2002</v>
+      </c>
+      <c r="N138" s="110"/>
       <c r="O138" s="98" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="139" spans="1:15">
       <c r="B139" s="98" t="s">
-        <v>1842</v>
-      </c>
+        <v>1841</v>
+      </c>
+      <c r="N139" s="110"/>
       <c r="O139" s="98" t="s">
-        <v>2088</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="140" spans="1:15">
       <c r="B140" s="98" t="s">
-        <v>2004</v>
-      </c>
+        <v>2003</v>
+      </c>
+      <c r="N140" s="110"/>
       <c r="O140" s="98" t="s">
-        <v>2089</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="141" spans="1:15">
       <c r="B141" s="98" t="s">
-        <v>1842</v>
-      </c>
+        <v>1841</v>
+      </c>
+      <c r="N141" s="110"/>
     </row>
     <row r="142" spans="1:15">
       <c r="B142" s="98" t="s">
-        <v>2005</v>
-      </c>
+        <v>2004</v>
+      </c>
+      <c r="N142" s="110"/>
       <c r="O142" s="98" t="s">
-        <v>2090</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="143" spans="1:15">
       <c r="B143" s="98" t="s">
-        <v>1842</v>
-      </c>
+        <v>1841</v>
+      </c>
+      <c r="N143" s="110"/>
     </row>
     <row r="144" spans="1:15">
       <c r="B144" s="98" t="s">
+        <v>2005</v>
+      </c>
+      <c r="N144" s="110"/>
+      <c r="O144" s="98" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15">
+      <c r="B145" s="98" t="s">
         <v>2006</v>
       </c>
-      <c r="O144" s="98" t="s">
+      <c r="N145" s="110"/>
+      <c r="O145" s="98" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15">
+      <c r="B146" s="98" t="s">
+        <v>2007</v>
+      </c>
+      <c r="N146" s="110"/>
+      <c r="O146" s="98" t="s">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15">
+      <c r="B147" s="98" t="s">
+        <v>2008</v>
+      </c>
+      <c r="N147" s="110"/>
+      <c r="O147" s="98" t="s">
         <v>2091</v>
       </c>
     </row>
-    <row r="145" spans="2:15">
-      <c r="B145" s="98" t="s">
-        <v>2007</v>
-      </c>
-      <c r="O145" s="98" t="s">
+    <row r="148" spans="1:15">
+      <c r="B148" s="98" t="s">
+        <v>2009</v>
+      </c>
+      <c r="N148" s="110"/>
+    </row>
+    <row r="149" spans="1:15">
+      <c r="B149" s="98" t="s">
+        <v>2008</v>
+      </c>
+      <c r="N149" s="110" t="s">
+        <v>2223</v>
+      </c>
+      <c r="O149" s="98" t="s">
         <v>2092</v>
       </c>
     </row>
-    <row r="146" spans="2:15">
-      <c r="B146" s="98" t="s">
+    <row r="150" spans="1:15">
+      <c r="B150" s="98" t="s">
+        <v>2010</v>
+      </c>
+      <c r="N150" s="110"/>
+    </row>
+    <row r="151" spans="1:15">
+      <c r="B151" s="98" t="s">
         <v>2008</v>
       </c>
-      <c r="O146" s="98" t="s">
+      <c r="N151" s="110" t="s">
+        <v>2223</v>
+      </c>
+      <c r="O151" s="98" t="s">
         <v>2093</v>
       </c>
     </row>
-    <row r="147" spans="2:15">
-      <c r="B147" s="98" t="s">
-        <v>2009</v>
-      </c>
-      <c r="O147" s="98" t="s">
+    <row r="152" spans="1:15">
+      <c r="B152" s="98" t="s">
+        <v>2011</v>
+      </c>
+      <c r="N152" s="110" t="s">
+        <v>2223</v>
+      </c>
+      <c r="O152" s="98" t="s">
         <v>2094</v>
       </c>
     </row>
-    <row r="148" spans="2:15">
-      <c r="B148" s="98" t="s">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="149" spans="2:15">
-      <c r="B149" s="98" t="s">
-        <v>2009</v>
-      </c>
-      <c r="O149" s="98" t="s">
+    <row r="153" spans="1:15">
+      <c r="B153" s="98" t="s">
+        <v>2008</v>
+      </c>
+      <c r="N153" s="110" t="s">
+        <v>2223</v>
+      </c>
+      <c r="O153" s="98" t="s">
         <v>2095</v>
       </c>
     </row>
-    <row r="150" spans="2:15">
-      <c r="B150" s="98" t="s">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="151" spans="2:15">
-      <c r="B151" s="98" t="s">
-        <v>2009</v>
-      </c>
-      <c r="O151" s="98" t="s">
+    <row r="154" spans="1:15">
+      <c r="B154" s="98" t="s">
+        <v>2012</v>
+      </c>
+      <c r="N154" s="110"/>
+      <c r="O154" s="98" t="s">
         <v>2096</v>
       </c>
     </row>
-    <row r="152" spans="2:15">
-      <c r="B152" s="98" t="s">
-        <v>2012</v>
-      </c>
-      <c r="O152" s="98" t="s">
+    <row r="155" spans="1:15">
+      <c r="N155" s="110"/>
+    </row>
+    <row r="156" spans="1:15">
+      <c r="N156" s="110" t="s">
+        <v>2223</v>
+      </c>
+      <c r="O156" s="98" t="s">
         <v>2097</v>
       </c>
     </row>
-    <row r="153" spans="2:15">
-      <c r="B153" s="98" t="s">
-        <v>2009</v>
-      </c>
-      <c r="O153" s="98" t="s">
+    <row r="157" spans="1:15">
+      <c r="A157" s="109" t="s">
+        <v>2227</v>
+      </c>
+      <c r="N157" s="110"/>
+    </row>
+    <row r="158" spans="1:15">
+      <c r="B158" s="98" t="s">
+        <v>2228</v>
+      </c>
+      <c r="N158" s="110" t="s">
+        <v>2223</v>
+      </c>
+      <c r="O158" s="98" t="s">
         <v>2098</v>
       </c>
     </row>
-    <row r="154" spans="2:15">
-      <c r="B154" s="98" t="s">
-        <v>2013</v>
-      </c>
-      <c r="O154" s="98" t="s">
+    <row r="159" spans="1:15">
+      <c r="N159" s="110" t="s">
+        <v>2223</v>
+      </c>
+      <c r="O159" s="98" t="s">
         <v>2099</v>
       </c>
     </row>
-    <row r="156" spans="2:15">
-      <c r="O156" s="98" t="s">
+    <row r="160" spans="1:15">
+      <c r="B160" s="98" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C160" s="98" t="s">
+        <v>2230</v>
+      </c>
+      <c r="D160" s="98" t="s">
+        <v>2231</v>
+      </c>
+      <c r="E160" s="98" t="s">
+        <v>2232</v>
+      </c>
+      <c r="N160" s="110" t="s">
+        <v>2223</v>
+      </c>
+      <c r="O160" s="98" t="s">
         <v>2100</v>
       </c>
     </row>
-    <row r="158" spans="2:15">
-      <c r="O158" s="98" t="s">
+    <row r="161" spans="2:15">
+      <c r="B161" s="98" t="s">
+        <v>2233</v>
+      </c>
+      <c r="C161" s="98" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D161" s="98" t="s">
+        <v>2235</v>
+      </c>
+      <c r="E161" s="98" t="s">
+        <v>2236</v>
+      </c>
+      <c r="N161" s="110" t="s">
+        <v>2223</v>
+      </c>
+      <c r="O161" s="98" t="s">
         <v>2101</v>
       </c>
     </row>
-    <row r="159" spans="2:15">
-      <c r="O159" s="98" t="s">
+    <row r="162" spans="2:15">
+      <c r="B162" s="109" t="s">
+        <v>2237</v>
+      </c>
+      <c r="C162" s="109" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D162" s="109" t="s">
+        <v>2238</v>
+      </c>
+      <c r="E162" s="109" t="s">
+        <v>2239</v>
+      </c>
+      <c r="N162" s="110" t="s">
+        <v>2223</v>
+      </c>
+      <c r="O162" s="98" t="s">
         <v>2102</v>
       </c>
     </row>
-    <row r="160" spans="2:15">
-      <c r="O160" s="98" t="s">
+    <row r="163" spans="2:15">
+      <c r="B163" s="98" t="s">
+        <v>2240</v>
+      </c>
+      <c r="C163" s="98" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D163" s="98" t="s">
+        <v>2238</v>
+      </c>
+      <c r="E163" s="98" t="s">
+        <v>2241</v>
+      </c>
+      <c r="N163" s="110" t="s">
+        <v>2223</v>
+      </c>
+      <c r="O163" s="98" t="s">
         <v>2103</v>
       </c>
     </row>
-    <row r="161" spans="15:15">
-      <c r="O161" s="98" t="s">
+    <row r="164" spans="2:15">
+      <c r="B164" s="98" t="s">
+        <v>2242</v>
+      </c>
+      <c r="C164" s="98" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D164" s="98" t="s">
+        <v>2243</v>
+      </c>
+      <c r="E164" s="98" t="s">
+        <v>2244</v>
+      </c>
+      <c r="N164" s="110"/>
+    </row>
+    <row r="165" spans="2:15">
+      <c r="B165" s="98" t="s">
+        <v>2245</v>
+      </c>
+      <c r="C165" s="98" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D165" s="98" t="s">
+        <v>2238</v>
+      </c>
+      <c r="E165" s="98" t="s">
+        <v>2246</v>
+      </c>
+      <c r="N165" s="110"/>
+      <c r="O165" s="98" t="s">
         <v>2104</v>
       </c>
     </row>
-    <row r="162" spans="15:15">
-      <c r="O162" s="98" t="s">
+    <row r="166" spans="2:15">
+      <c r="B166" s="98" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C166" s="98" t="s">
+        <v>2248</v>
+      </c>
+      <c r="D166" s="98" t="s">
+        <v>2243</v>
+      </c>
+      <c r="E166" s="98" t="s">
+        <v>2249</v>
+      </c>
+      <c r="N166" s="110"/>
+    </row>
+    <row r="167" spans="2:15">
+      <c r="N167" s="110"/>
+      <c r="O167" s="98" t="s">
         <v>2105</v>
       </c>
     </row>
-    <row r="163" spans="15:15">
-      <c r="O163" s="98" t="s">
+    <row r="168" spans="2:15">
+      <c r="N168" s="110"/>
+      <c r="O168" s="98" t="s">
         <v>2106</v>
       </c>
     </row>
-    <row r="165" spans="15:15">
-      <c r="O165" s="98" t="s">
+    <row r="169" spans="2:15">
+      <c r="N169" s="110"/>
+      <c r="O169" s="98" t="s">
         <v>2107</v>
       </c>
     </row>
-    <row r="167" spans="15:15">
-      <c r="O167" s="98" t="s">
+    <row r="170" spans="2:15">
+      <c r="N170" s="110"/>
+    </row>
+    <row r="171" spans="2:15">
+      <c r="N171" s="110"/>
+      <c r="O171" s="98" t="s">
         <v>2108</v>
       </c>
     </row>
-    <row r="168" spans="15:15">
-      <c r="O168" s="98" t="s">
+    <row r="172" spans="2:15">
+      <c r="N172" s="110"/>
+    </row>
+    <row r="173" spans="2:15">
+      <c r="N173" s="110"/>
+      <c r="O173" s="98" t="s">
         <v>2109</v>
       </c>
     </row>
-    <row r="169" spans="15:15">
-      <c r="O169" s="98" t="s">
+    <row r="174" spans="2:15">
+      <c r="N174" s="110"/>
+      <c r="O174" s="98" t="s">
         <v>2110</v>
       </c>
     </row>
-    <row r="171" spans="15:15">
-      <c r="O171" s="98" t="s">
+    <row r="175" spans="2:15">
+      <c r="N175" s="110"/>
+      <c r="O175" s="98" t="s">
         <v>2111</v>
       </c>
     </row>
-    <row r="173" spans="15:15">
-      <c r="O173" s="98" t="s">
+    <row r="176" spans="2:15">
+      <c r="N176" s="110"/>
+      <c r="O176" s="98" t="s">
         <v>2112</v>
       </c>
     </row>
-    <row r="174" spans="15:15">
-      <c r="O174" s="98" t="s">
+    <row r="177" spans="14:15">
+      <c r="N177" s="110"/>
+      <c r="O177" s="98" t="s">
         <v>2113</v>
       </c>
     </row>
-    <row r="175" spans="15:15">
-      <c r="O175" s="98" t="s">
+    <row r="178" spans="14:15">
+      <c r="N178" s="110"/>
+    </row>
+    <row r="179" spans="14:15">
+      <c r="N179" s="110"/>
+      <c r="O179" s="98" t="s">
         <v>2114</v>
       </c>
     </row>
-    <row r="176" spans="15:15">
-      <c r="O176" s="98" t="s">
+    <row r="180" spans="14:15">
+      <c r="N180" s="110"/>
+    </row>
+    <row r="181" spans="14:15">
+      <c r="N181" s="110"/>
+      <c r="O181" s="98" t="s">
         <v>2115</v>
       </c>
     </row>
-    <row r="177" spans="15:15">
-      <c r="O177" s="98" t="s">
+    <row r="182" spans="14:15">
+      <c r="N182" s="110"/>
+      <c r="O182" s="98" t="s">
         <v>2116</v>
       </c>
     </row>
-    <row r="179" spans="15:15">
-      <c r="O179" s="98" t="s">
+    <row r="183" spans="14:15">
+      <c r="N183" s="110"/>
+      <c r="O183" s="98" t="s">
         <v>2117</v>
       </c>
     </row>
-    <row r="181" spans="15:15">
-      <c r="O181" s="98" t="s">
+    <row r="184" spans="14:15">
+      <c r="N184" s="110"/>
+      <c r="O184" s="98" t="s">
         <v>2118</v>
       </c>
     </row>
-    <row r="182" spans="15:15">
-      <c r="O182" s="98" t="s">
+    <row r="185" spans="14:15">
+      <c r="N185" s="110"/>
+      <c r="O185" s="98" t="s">
         <v>2119</v>
       </c>
     </row>
-    <row r="183" spans="15:15">
-      <c r="O183" s="98" t="s">
+    <row r="186" spans="14:15">
+      <c r="N186" s="110"/>
+    </row>
+    <row r="187" spans="14:15">
+      <c r="N187" s="110"/>
+      <c r="O187" s="98" t="s">
         <v>2120</v>
       </c>
     </row>
-    <row r="184" spans="15:15">
-      <c r="O184" s="98" t="s">
+    <row r="188" spans="14:15">
+      <c r="N188" s="110"/>
+    </row>
+    <row r="189" spans="14:15">
+      <c r="N189" s="110"/>
+      <c r="O189" s="98" t="s">
         <v>2121</v>
       </c>
     </row>
-    <row r="185" spans="15:15">
-      <c r="O185" s="98" t="s">
+    <row r="190" spans="14:15">
+      <c r="N190" s="110"/>
+      <c r="O190" s="98" t="s">
         <v>2122</v>
       </c>
     </row>
-    <row r="187" spans="15:15">
-      <c r="O187" s="98" t="s">
+    <row r="191" spans="14:15">
+      <c r="N191" s="110"/>
+      <c r="O191" s="98" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="192" spans="14:15">
+      <c r="N192" s="110"/>
+      <c r="O192" s="98" t="s">
         <v>2123</v>
       </c>
     </row>
-    <row r="189" spans="15:15">
-      <c r="O189" s="98" t="s">
+    <row r="193" spans="14:15">
+      <c r="N193" s="110"/>
+      <c r="O193" s="98" t="s">
         <v>2124</v>
       </c>
     </row>
-    <row r="190" spans="15:15">
-      <c r="O190" s="98" t="s">
+    <row r="194" spans="14:15">
+      <c r="N194" s="110"/>
+      <c r="O194" s="98" t="s">
         <v>2125</v>
       </c>
     </row>
-    <row r="191" spans="15:15">
-      <c r="O191" s="98" t="s">
-        <v>2096</v>
-      </c>
-    </row>
-    <row r="192" spans="15:15">
-      <c r="O192" s="98" t="s">
+    <row r="195" spans="14:15">
+      <c r="N195" s="110"/>
+    </row>
+    <row r="196" spans="14:15">
+      <c r="N196" s="110"/>
+      <c r="O196" s="98" t="s">
         <v>2126</v>
       </c>
     </row>
-    <row r="193" spans="15:15">
-      <c r="O193" s="98" t="s">
+    <row r="197" spans="14:15">
+      <c r="N197" s="110"/>
+    </row>
+    <row r="198" spans="14:15">
+      <c r="N198" s="110"/>
+      <c r="O198" s="98" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="199" spans="14:15">
+      <c r="N199" s="110"/>
+      <c r="O199" s="98" t="s">
         <v>2127</v>
       </c>
     </row>
-    <row r="194" spans="15:15">
-      <c r="O194" s="98" t="s">
+    <row r="200" spans="14:15">
+      <c r="N200" s="110" t="s">
+        <v>2223</v>
+      </c>
+      <c r="O200" s="98" t="s">
         <v>2128</v>
       </c>
     </row>
-    <row r="196" spans="15:15">
-      <c r="O196" s="98" t="s">
+    <row r="201" spans="14:15">
+      <c r="N201" s="110"/>
+      <c r="O201" s="98" t="s">
         <v>2129</v>
       </c>
     </row>
-    <row r="198" spans="15:15">
-      <c r="O198" s="98" t="s">
-        <v>2126</v>
-      </c>
-    </row>
-    <row r="199" spans="15:15">
-      <c r="O199" s="98" t="s">
+    <row r="202" spans="14:15">
+      <c r="N202" s="110"/>
+    </row>
+    <row r="203" spans="14:15">
+      <c r="N203" s="110"/>
+      <c r="O203" s="98" t="s">
         <v>2130</v>
       </c>
     </row>
-    <row r="200" spans="15:15">
-      <c r="O200" s="98" t="s">
+    <row r="204" spans="14:15">
+      <c r="N204" s="110"/>
+    </row>
+    <row r="205" spans="14:15">
+      <c r="N205" s="110"/>
+      <c r="O205" s="98" t="s">
         <v>2131</v>
       </c>
     </row>
-    <row r="201" spans="15:15">
-      <c r="O201" s="98" t="s">
+    <row r="206" spans="14:15">
+      <c r="N206" s="110"/>
+      <c r="O206" s="98" t="s">
         <v>2132</v>
       </c>
     </row>
-    <row r="203" spans="15:15">
-      <c r="O203" s="98" t="s">
+    <row r="207" spans="14:15">
+      <c r="N207" s="110" t="s">
+        <v>2223</v>
+      </c>
+      <c r="O207" s="98" t="s">
         <v>2133</v>
       </c>
     </row>
-    <row r="205" spans="15:15">
-      <c r="O205" s="98" t="s">
+    <row r="208" spans="14:15">
+      <c r="N208" s="110"/>
+    </row>
+    <row r="209" spans="14:15">
+      <c r="N209" s="110"/>
+      <c r="O209" s="98" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="206" spans="15:15">
-      <c r="O206" s="98" t="s">
+    <row r="210" spans="14:15">
+      <c r="N210" s="110"/>
+    </row>
+    <row r="211" spans="14:15">
+      <c r="N211" s="110"/>
+      <c r="O211" s="98" t="s">
         <v>2135</v>
       </c>
     </row>
-    <row r="207" spans="15:15">
-      <c r="O207" s="98" t="s">
+    <row r="212" spans="14:15">
+      <c r="N212" s="110"/>
+      <c r="O212" s="98" t="s">
         <v>2136</v>
       </c>
     </row>
-    <row r="209" spans="15:15">
-      <c r="O209" s="98" t="s">
+    <row r="213" spans="14:15">
+      <c r="N213" s="110"/>
+      <c r="O213" s="98" t="s">
         <v>2137</v>
       </c>
     </row>
-    <row r="211" spans="15:15">
-      <c r="O211" s="98" t="s">
+    <row r="214" spans="14:15">
+      <c r="N214" s="110"/>
+    </row>
+    <row r="215" spans="14:15">
+      <c r="N215" s="110"/>
+      <c r="O215" s="98" t="s">
         <v>2138</v>
       </c>
     </row>
-    <row r="212" spans="15:15">
-      <c r="O212" s="98" t="s">
+    <row r="216" spans="14:15">
+      <c r="N216" s="110"/>
+    </row>
+    <row r="217" spans="14:15">
+      <c r="N217" s="110"/>
+      <c r="O217" s="98" t="s">
         <v>2139</v>
       </c>
     </row>
-    <row r="213" spans="15:15">
-      <c r="O213" s="98" t="s">
+    <row r="218" spans="14:15">
+      <c r="N218" s="110"/>
+      <c r="O218" s="98" t="s">
         <v>2140</v>
       </c>
     </row>
-    <row r="215" spans="15:15">
-      <c r="O215" s="98" t="s">
+    <row r="219" spans="14:15">
+      <c r="N219" s="110"/>
+      <c r="O219" s="98" t="s">
         <v>2141</v>
       </c>
     </row>
-    <row r="217" spans="15:15">
-      <c r="O217" s="98" t="s">
+    <row r="220" spans="14:15">
+      <c r="N220" s="110"/>
+    </row>
+    <row r="221" spans="14:15">
+      <c r="N221" s="110"/>
+      <c r="O221" s="98" t="s">
         <v>2142</v>
       </c>
     </row>
-    <row r="218" spans="15:15">
-      <c r="O218" s="98" t="s">
+    <row r="222" spans="14:15">
+      <c r="N222" s="110"/>
+    </row>
+    <row r="223" spans="14:15">
+      <c r="N223" s="110"/>
+      <c r="O223" s="98" t="s">
         <v>2143</v>
       </c>
     </row>
-    <row r="219" spans="15:15">
-      <c r="O219" s="98" t="s">
+    <row r="224" spans="14:15">
+      <c r="N224" s="110"/>
+      <c r="O224" s="98" t="s">
         <v>2144</v>
       </c>
     </row>
-    <row r="221" spans="15:15">
-      <c r="O221" s="98" t="s">
+    <row r="225" spans="14:15">
+      <c r="N225" s="110"/>
+      <c r="O225" s="98" t="s">
         <v>2145</v>
       </c>
     </row>
-    <row r="223" spans="15:15">
-      <c r="O223" s="98" t="s">
+    <row r="226" spans="14:15">
+      <c r="N226" s="110"/>
+    </row>
+    <row r="227" spans="14:15">
+      <c r="N227" s="110"/>
+      <c r="O227" s="98" t="s">
         <v>2146</v>
       </c>
     </row>
-    <row r="224" spans="15:15">
-      <c r="O224" s="98" t="s">
+    <row r="228" spans="14:15">
+      <c r="N228" s="110"/>
+    </row>
+    <row r="229" spans="14:15">
+      <c r="N229" s="110"/>
+      <c r="O229" s="98" t="s">
         <v>2147</v>
       </c>
     </row>
-    <row r="225" spans="15:15">
-      <c r="O225" s="98" t="s">
+    <row r="230" spans="14:15">
+      <c r="N230" s="110"/>
+      <c r="O230" s="98" t="s">
         <v>2148</v>
       </c>
     </row>
-    <row r="227" spans="15:15">
-      <c r="O227" s="98" t="s">
+    <row r="231" spans="14:15">
+      <c r="N231" s="110"/>
+      <c r="O231" s="98" t="s">
         <v>2149</v>
       </c>
     </row>
-    <row r="229" spans="15:15">
-      <c r="O229" s="98" t="s">
+    <row r="232" spans="14:15">
+      <c r="N232" s="110"/>
+      <c r="O232" s="98" t="s">
         <v>2150</v>
       </c>
     </row>
-    <row r="230" spans="15:15">
-      <c r="O230" s="98" t="s">
+    <row r="233" spans="14:15">
+      <c r="N233" s="110"/>
+      <c r="O233" s="98" t="s">
         <v>2151</v>
       </c>
     </row>
-    <row r="231" spans="15:15">
-      <c r="O231" s="98" t="s">
+    <row r="234" spans="14:15">
+      <c r="N234" s="110"/>
+    </row>
+    <row r="235" spans="14:15">
+      <c r="N235" s="110"/>
+      <c r="O235" s="98" t="s">
         <v>2152</v>
       </c>
     </row>
-    <row r="232" spans="15:15">
-      <c r="O232" s="98" t="s">
+    <row r="236" spans="14:15">
+      <c r="N236" s="110"/>
+    </row>
+    <row r="237" spans="14:15">
+      <c r="N237" s="110"/>
+      <c r="O237" s="98" t="s">
         <v>2153</v>
       </c>
     </row>
-    <row r="233" spans="15:15">
-      <c r="O233" s="98" t="s">
+    <row r="238" spans="14:15">
+      <c r="N238" s="110"/>
+      <c r="O238" s="98" t="s">
         <v>2154</v>
       </c>
     </row>
-    <row r="235" spans="15:15">
-      <c r="O235" s="98" t="s">
+    <row r="239" spans="14:15">
+      <c r="N239" s="110"/>
+      <c r="O239" s="98" t="s">
         <v>2155</v>
       </c>
     </row>
-    <row r="237" spans="15:15">
-      <c r="O237" s="98" t="s">
+    <row r="240" spans="14:15">
+      <c r="N240" s="110"/>
+    </row>
+    <row r="241" spans="14:15">
+      <c r="N241" s="110" t="s">
+        <v>2223</v>
+      </c>
+      <c r="O241" s="98" t="s">
         <v>2156</v>
       </c>
     </row>
-    <row r="238" spans="15:15">
-      <c r="O238" s="98" t="s">
+    <row r="242" spans="14:15">
+      <c r="N242" s="110"/>
+    </row>
+    <row r="243" spans="14:15">
+      <c r="N243" s="110"/>
+      <c r="O243" s="98" t="s">
         <v>2157</v>
       </c>
     </row>
-    <row r="239" spans="15:15">
-      <c r="O239" s="98" t="s">
+    <row r="244" spans="14:15">
+      <c r="N244" s="110"/>
+      <c r="O244" s="98" t="s">
         <v>2158</v>
       </c>
     </row>
-    <row r="241" spans="15:15">
-      <c r="O241" s="98" t="s">
+    <row r="245" spans="14:15">
+      <c r="N245" s="110"/>
+      <c r="O245" s="98" t="s">
         <v>2159</v>
       </c>
     </row>
-    <row r="243" spans="15:15">
-      <c r="O243" s="98" t="s">
+    <row r="246" spans="14:15">
+      <c r="N246" s="110"/>
+    </row>
+    <row r="247" spans="14:15">
+      <c r="N247" s="110" t="s">
+        <v>2223</v>
+      </c>
+      <c r="O247" s="98" t="s">
         <v>2160</v>
       </c>
     </row>
-    <row r="244" spans="15:15">
-      <c r="O244" s="98" t="s">
+    <row r="248" spans="14:15">
+      <c r="N248" s="110"/>
+    </row>
+    <row r="249" spans="14:15">
+      <c r="N249" s="110"/>
+      <c r="O249" s="98" t="s">
         <v>2161</v>
       </c>
     </row>
-    <row r="245" spans="15:15">
-      <c r="O245" s="98" t="s">
+    <row r="250" spans="14:15">
+      <c r="N250" s="110"/>
+      <c r="O250" s="98" t="s">
         <v>2162</v>
       </c>
     </row>
-    <row r="247" spans="15:15">
-      <c r="O247" s="98" t="s">
+    <row r="251" spans="14:15">
+      <c r="N251" s="110"/>
+      <c r="O251" s="98" t="s">
         <v>2163</v>
       </c>
     </row>
-    <row r="249" spans="15:15">
-      <c r="O249" s="98" t="s">
+    <row r="252" spans="14:15">
+      <c r="N252" s="110"/>
+    </row>
+    <row r="253" spans="14:15">
+      <c r="N253" s="110"/>
+      <c r="O253" s="98" t="s">
         <v>2164</v>
       </c>
     </row>
-    <row r="250" spans="15:15">
-      <c r="O250" s="98" t="s">
+    <row r="254" spans="14:15">
+      <c r="N254" s="110"/>
+    </row>
+    <row r="255" spans="14:15">
+      <c r="N255" s="110"/>
+      <c r="O255" s="98" t="s">
         <v>2165</v>
       </c>
     </row>
-    <row r="251" spans="15:15">
-      <c r="O251" s="98" t="s">
+    <row r="256" spans="14:15">
+      <c r="N256" s="110"/>
+      <c r="O256" s="98" t="s">
         <v>2166</v>
       </c>
     </row>
-    <row r="253" spans="15:15">
-      <c r="O253" s="98" t="s">
+    <row r="257" spans="14:15">
+      <c r="N257" s="110"/>
+      <c r="O257" s="98" t="s">
         <v>2167</v>
       </c>
     </row>
-    <row r="255" spans="15:15">
-      <c r="O255" s="98" t="s">
+    <row r="258" spans="14:15">
+      <c r="N258" s="110"/>
+      <c r="O258" s="98" t="s">
         <v>2168</v>
       </c>
     </row>
-    <row r="256" spans="15:15">
-      <c r="O256" s="98" t="s">
+    <row r="259" spans="14:15">
+      <c r="N259" s="110"/>
+      <c r="O259" s="98" t="s">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="260" spans="14:15">
+      <c r="N260" s="110"/>
+      <c r="O260" s="98" t="s">
         <v>2169</v>
       </c>
     </row>
-    <row r="257" spans="15:15">
-      <c r="O257" s="98" t="s">
+    <row r="261" spans="14:15">
+      <c r="N261" s="110"/>
+    </row>
+    <row r="262" spans="14:15">
+      <c r="N262" s="110"/>
+      <c r="O262" s="98" t="s">
         <v>2170</v>
       </c>
     </row>
-    <row r="258" spans="15:15">
-      <c r="O258" s="98" t="s">
+    <row r="263" spans="14:15">
+      <c r="N263" s="110"/>
+    </row>
+    <row r="264" spans="14:15">
+      <c r="N264" s="110"/>
+      <c r="O264" s="98" t="s">
         <v>2171</v>
       </c>
     </row>
-    <row r="259" spans="15:15">
-      <c r="O259" s="98" t="s">
-        <v>2039</v>
-      </c>
-    </row>
-    <row r="260" spans="15:15">
-      <c r="O260" s="98" t="s">
+    <row r="265" spans="14:15">
+      <c r="N265" s="110"/>
+      <c r="O265" s="98" t="s">
         <v>2172</v>
       </c>
     </row>
-    <row r="262" spans="15:15">
-      <c r="O262" s="98" t="s">
+    <row r="266" spans="14:15">
+      <c r="N266" s="110"/>
+      <c r="O266" s="98" t="s">
         <v>2173</v>
       </c>
     </row>
-    <row r="264" spans="15:15">
-      <c r="O264" s="98" t="s">
+    <row r="267" spans="14:15">
+      <c r="N267" s="110"/>
+      <c r="O267" s="98" t="s">
         <v>2174</v>
       </c>
     </row>
-    <row r="265" spans="15:15">
-      <c r="O265" s="98" t="s">
+    <row r="268" spans="14:15">
+      <c r="N268" s="110"/>
+      <c r="O268" s="98" t="s">
         <v>2175</v>
       </c>
     </row>
-    <row r="266" spans="15:15">
-      <c r="O266" s="98" t="s">
+    <row r="269" spans="14:15">
+      <c r="N269" s="110"/>
+    </row>
+    <row r="270" spans="14:15">
+      <c r="N270" s="110"/>
+      <c r="O270" s="98" t="s">
         <v>2176</v>
       </c>
     </row>
-    <row r="267" spans="15:15">
-      <c r="O267" s="98" t="s">
+    <row r="271" spans="14:15">
+      <c r="N271" s="110"/>
+    </row>
+    <row r="272" spans="14:15">
+      <c r="N272" s="110"/>
+      <c r="O272" s="98" t="s">
         <v>2177</v>
       </c>
     </row>
-    <row r="268" spans="15:15">
-      <c r="O268" s="98" t="s">
+    <row r="273" spans="14:15">
+      <c r="N273" s="110"/>
+      <c r="O273" s="98" t="s">
         <v>2178</v>
       </c>
     </row>
-    <row r="270" spans="15:15">
-      <c r="O270" s="98" t="s">
+    <row r="274" spans="14:15">
+      <c r="N274" s="110"/>
+      <c r="O274" s="98" t="s">
         <v>2179</v>
       </c>
     </row>
-    <row r="272" spans="15:15">
-      <c r="O272" s="98" t="s">
+    <row r="275" spans="14:15">
+      <c r="N275" s="110"/>
+    </row>
+    <row r="276" spans="14:15">
+      <c r="N276" s="110"/>
+      <c r="O276" s="98" t="s">
         <v>2180</v>
       </c>
     </row>
-    <row r="273" spans="15:15">
-      <c r="O273" s="98" t="s">
+    <row r="277" spans="14:15">
+      <c r="N277" s="110"/>
+    </row>
+    <row r="278" spans="14:15">
+      <c r="N278" s="110"/>
+      <c r="O278" s="98" t="s">
         <v>2181</v>
       </c>
     </row>
-    <row r="274" spans="15:15">
-      <c r="O274" s="98" t="s">
+    <row r="279" spans="14:15">
+      <c r="N279" s="110"/>
+      <c r="O279" s="98" t="s">
         <v>2182</v>
       </c>
     </row>
-    <row r="276" spans="15:15">
-      <c r="O276" s="98" t="s">
+    <row r="280" spans="14:15">
+      <c r="N280" s="110"/>
+      <c r="O280" s="98" t="s">
         <v>2183</v>
       </c>
     </row>
-    <row r="278" spans="15:15">
-      <c r="O278" s="98" t="s">
+    <row r="281" spans="14:15">
+      <c r="N281" s="110"/>
+      <c r="O281" s="98" t="s">
         <v>2184</v>
       </c>
     </row>
-    <row r="279" spans="15:15">
-      <c r="O279" s="98" t="s">
+    <row r="282" spans="14:15">
+      <c r="N282" s="110"/>
+    </row>
+    <row r="283" spans="14:15">
+      <c r="N283" s="110"/>
+      <c r="O283" s="98" t="s">
         <v>2185</v>
       </c>
     </row>
-    <row r="280" spans="15:15">
-      <c r="O280" s="98" t="s">
+    <row r="284" spans="14:15">
+      <c r="N284" s="110"/>
+    </row>
+    <row r="285" spans="14:15">
+      <c r="N285" s="110"/>
+      <c r="O285" s="98" t="s">
         <v>2186</v>
       </c>
     </row>
-    <row r="281" spans="15:15">
-      <c r="O281" s="98" t="s">
+    <row r="286" spans="14:15">
+      <c r="N286" s="110"/>
+      <c r="O286" s="98" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="287" spans="14:15">
+      <c r="N287" s="110"/>
+      <c r="O287" s="98" t="s">
         <v>2187</v>
       </c>
     </row>
-    <row r="283" spans="15:15">
-      <c r="O283" s="98" t="s">
+    <row r="288" spans="14:15">
+      <c r="N288" s="110"/>
+      <c r="O288" s="98" t="s">
         <v>2188</v>
       </c>
     </row>
-    <row r="285" spans="15:15">
-      <c r="O285" s="98" t="s">
+    <row r="289" spans="14:15">
+      <c r="N289" s="110"/>
+      <c r="O289" s="98" t="s">
         <v>2189</v>
       </c>
     </row>
-    <row r="286" spans="15:15">
-      <c r="O286" s="98" t="s">
-        <v>2125</v>
-      </c>
-    </row>
-    <row r="287" spans="15:15">
-      <c r="O287" s="98" t="s">
+    <row r="290" spans="14:15">
+      <c r="N290" s="110"/>
+      <c r="O290" s="98" t="s">
         <v>2190</v>
-      </c>
-    </row>
-    <row r="288" spans="15:15">
-      <c r="O288" s="98" t="s">
-        <v>2191</v>
-      </c>
-    </row>
-    <row r="289" spans="15:15">
-      <c r="O289" s="98" t="s">
-        <v>2192</v>
-      </c>
-    </row>
-    <row r="290" spans="15:15">
-      <c r="O290" s="98" t="s">
-        <v>2193</v>
       </c>
     </row>
   </sheetData>
@@ -21684,55 +22256,55 @@
   <sheetData>
     <row r="3" spans="2:10">
       <c r="B3" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="5" spans="2:10">
       <c r="C5" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="7" spans="2:10">
       <c r="C7" t="s">
+        <v>1781</v>
+      </c>
+      <c r="E7" t="s">
         <v>1782</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1783</v>
       </c>
     </row>
     <row r="8" spans="2:10">
       <c r="C8" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E8" t="s">
         <v>1784</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1785</v>
       </c>
     </row>
     <row r="9" spans="2:10">
       <c r="C9" t="s">
+        <v>1785</v>
+      </c>
+      <c r="E9" t="s">
         <v>1786</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1787</v>
       </c>
     </row>
     <row r="11" spans="2:10">
       <c r="C11" t="s">
+        <v>1787</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H11" t="s">
+        <v>1796</v>
+      </c>
+      <c r="J11" t="s">
         <v>1788</v>
-      </c>
-      <c r="E11" t="s">
-        <v>1792</v>
-      </c>
-      <c r="H11" t="s">
-        <v>1797</v>
-      </c>
-      <c r="J11" t="s">
-        <v>1789</v>
       </c>
     </row>
     <row r="12" spans="2:10">
       <c r="E12" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="J12" t="s">
         <v>1590</v>
@@ -21740,12 +22312,12 @@
     </row>
     <row r="13" spans="2:10">
       <c r="E13" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="14" spans="2:10">
       <c r="E14" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="J14" t="s">
         <v>1596</v>
@@ -21753,10 +22325,10 @@
     </row>
     <row r="15" spans="2:10">
       <c r="E15" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="J15" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="16" spans="2:10">
@@ -21766,7 +22338,7 @@
     </row>
     <row r="17" spans="2:12">
       <c r="L17" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="18" spans="2:12">
@@ -21776,7 +22348,7 @@
     </row>
     <row r="19" spans="2:12">
       <c r="J19" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="20" spans="2:12">
@@ -21791,47 +22363,47 @@
     </row>
     <row r="24" spans="2:12">
       <c r="B24" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="26" spans="2:12">
       <c r="C26" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="27" spans="2:12">
       <c r="D27" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="28" spans="2:12">
       <c r="D28" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="29" spans="2:12">
       <c r="D29" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="30" spans="2:12">
       <c r="D30" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="31" spans="2:12">
       <c r="C31" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="32" spans="2:12">
       <c r="D32" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="D33" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -21841,36 +22413,36 @@
     </row>
     <row r="37" spans="2:7">
       <c r="D37" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="39" spans="2:7">
       <c r="B39" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="40" spans="2:7">
       <c r="C40" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="D40" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="G40" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="41" spans="2:7">
       <c r="D41" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="42" spans="2:7">
       <c r="C42" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="D42" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="G42" t="s">
         <v>1617</v>
@@ -21878,187 +22450,187 @@
     </row>
     <row r="43" spans="2:7">
       <c r="D43" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="44" spans="2:7">
       <c r="C44" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="G44" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="47" spans="2:7">
       <c r="B47" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="49" spans="2:5">
       <c r="C49" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="E49" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="50" spans="2:5">
       <c r="C50" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="E50" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="51" spans="2:5">
       <c r="C51" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="E51" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="52" spans="2:5">
       <c r="C52" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="53" spans="2:5">
       <c r="C53" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="56" spans="2:5">
       <c r="B56" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="58" spans="2:5">
       <c r="C58" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="60" spans="2:5">
       <c r="B60" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="62" spans="2:5">
       <c r="D62" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="63" spans="2:5">
       <c r="D63" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="64" spans="2:5">
       <c r="D64" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="65" spans="2:5">
       <c r="D65" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="66" spans="2:5">
       <c r="D66" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="67" spans="2:5">
       <c r="D67" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="68" spans="2:5">
       <c r="D68" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="69" spans="2:5">
       <c r="D69" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="70" spans="2:5">
       <c r="D70" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="71" spans="2:5">
       <c r="D71" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="72" spans="2:5">
       <c r="D72" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="E72" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="73" spans="2:5">
       <c r="D73" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="74" spans="2:5">
       <c r="D74" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="75" spans="2:5">
       <c r="D75" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="76" spans="2:5">
       <c r="D76" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="77" spans="2:5">
       <c r="D77" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="78" spans="2:5">
       <c r="D78" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="80" spans="2:5">
       <c r="B80" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="82" spans="2:11">
       <c r="C82" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="F82" s="103" t="s">
+        <v>1830</v>
+      </c>
+      <c r="G82" s="103" t="s">
         <v>1831</v>
       </c>
-      <c r="G82" s="103" t="s">
+      <c r="H82" s="103" t="s">
         <v>1832</v>
       </c>
-      <c r="H82" s="103" t="s">
-        <v>1833</v>
-      </c>
       <c r="J82" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="83" spans="2:11">
       <c r="C83" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="F83" s="104" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="G83" s="104">
         <v>1440</v>
@@ -22067,15 +22639,15 @@
         <v>180</v>
       </c>
       <c r="J83" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="84" spans="2:11">
       <c r="C84" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="F84" s="104" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="G84" s="104">
         <v>30</v>
@@ -22084,15 +22656,15 @@
         <v>10</v>
       </c>
       <c r="J84" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="85" spans="2:11">
       <c r="C85" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="F85" s="104" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="G85" s="104">
         <v>5</v>
@@ -22103,12 +22675,12 @@
     </row>
     <row r="86" spans="2:11">
       <c r="C86" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="88" spans="2:11">
       <c r="B88" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="89" spans="2:11">
@@ -22119,141 +22691,141 @@
         <v>7</v>
       </c>
       <c r="D90" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="91" spans="2:11">
       <c r="D91" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="92" spans="2:11">
       <c r="D92" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="K92" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="93" spans="2:11">
       <c r="D93" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="94" spans="2:11">
       <c r="D94" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="K94" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="95" spans="2:11">
       <c r="D95" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="K95" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="96" spans="2:11">
       <c r="D96" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="K96" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="97" spans="3:10">
       <c r="D97" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="99" spans="3:10">
       <c r="D99" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="100" spans="3:10">
       <c r="D100" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="101" spans="3:10">
       <c r="D101" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="102" spans="3:10">
       <c r="D102" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="103" spans="3:10">
       <c r="D103" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="104" spans="3:10">
       <c r="D104" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="105" spans="3:10">
       <c r="D105" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="J105" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="106" spans="3:10">
       <c r="D106" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="J106" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="108" spans="3:10">
       <c r="D108" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="109" spans="3:10">
       <c r="D109" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="110" spans="3:10">
       <c r="D110" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="112" spans="3:10">
       <c r="C112" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="D112" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="113" spans="2:10">
       <c r="D113" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="115" spans="2:10">
       <c r="C115" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="D115" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="116" spans="2:10">
       <c r="D116" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="118" spans="2:10">
@@ -22263,191 +22835,191 @@
     </row>
     <row r="119" spans="2:10">
       <c r="B119" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="120" spans="2:10">
       <c r="D120" t="s">
+        <v>1899</v>
+      </c>
+      <c r="F120" t="s">
         <v>1900</v>
-      </c>
-      <c r="F120" t="s">
-        <v>1901</v>
       </c>
     </row>
     <row r="121" spans="2:10">
       <c r="D121" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="F121" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="122" spans="2:10">
       <c r="D122" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="F122" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="123" spans="2:10">
       <c r="D123" s="105" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="E123" s="106"/>
       <c r="F123" s="106" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="J123" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="124" spans="2:10">
       <c r="D124" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="F124" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="126" spans="2:10">
       <c r="B126" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="127" spans="2:10">
       <c r="D127" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="128" spans="2:10">
       <c r="D128" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="129" spans="4:4">
       <c r="D129" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="130" spans="4:4">
       <c r="D130" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="131" spans="4:4">
       <c r="D131" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="132" spans="4:4">
       <c r="D132" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="133" spans="4:4">
       <c r="D133" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="134" spans="4:4">
       <c r="D134" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="135" spans="4:4">
       <c r="D135" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="137" spans="4:4">
       <c r="D137" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="138" spans="4:4">
       <c r="D138" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="139" spans="4:4">
       <c r="D139" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="140" spans="4:4">
       <c r="D140" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="141" spans="4:4">
       <c r="D141" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="142" spans="4:4">
       <c r="D142" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="144" spans="4:4">
       <c r="D144" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="145" spans="4:10">
       <c r="D145" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="G145" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="J145" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="146" spans="4:10">
       <c r="D146" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="G146" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="J146" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="147" spans="4:10">
       <c r="D147" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="G147" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="J147" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="148" spans="4:10">
       <c r="D148" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="G148" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="J148" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="149" spans="4:10">
       <c r="D149" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="G149" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="J149" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
     </row>
   </sheetData>
@@ -22666,7 +23238,7 @@
     </row>
     <row r="5" spans="2:11">
       <c r="B5" s="43" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>128</v>
@@ -22691,7 +23263,7 @@
     </row>
     <row r="6" spans="2:11">
       <c r="B6" s="43" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>150</v>
@@ -22717,7 +23289,7 @@
     </row>
     <row r="7" spans="2:11">
       <c r="B7" s="43" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>34</v>
@@ -22743,7 +23315,7 @@
     </row>
     <row r="8" spans="2:11">
       <c r="B8" s="43" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>151</v>
@@ -22769,7 +23341,7 @@
     </row>
     <row r="9" spans="2:11">
       <c r="B9" s="43" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>35</v>
@@ -22795,7 +23367,7 @@
     </row>
     <row r="10" spans="2:11">
       <c r="B10" s="43" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>36</v>
@@ -22821,7 +23393,7 @@
     </row>
     <row r="11" spans="2:11">
       <c r="B11" s="43" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>37</v>
@@ -22874,7 +23446,7 @@
     </row>
     <row r="13" spans="2:11">
       <c r="B13" s="43" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>128</v>
@@ -22902,7 +23474,7 @@
     </row>
     <row r="14" spans="2:11">
       <c r="B14" s="43" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>58</v>
@@ -22931,7 +23503,7 @@
     </row>
     <row r="15" spans="2:11">
       <c r="B15" s="43" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>77</v>
@@ -22960,7 +23532,7 @@
     </row>
     <row r="16" spans="2:11">
       <c r="B16" s="43" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>59</v>
@@ -22989,7 +23561,7 @@
     </row>
     <row r="17" spans="2:11">
       <c r="B17" s="43" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>63</v>
@@ -23018,7 +23590,7 @@
     </row>
     <row r="18" spans="2:11">
       <c r="B18" s="43" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>147</v>
@@ -23047,7 +23619,7 @@
     </row>
     <row r="19" spans="2:11">
       <c r="B19" s="43" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>148</v>
@@ -23076,7 +23648,7 @@
     </row>
     <row r="20" spans="2:11">
       <c r="B20" s="43" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>1116</v>
@@ -23105,7 +23677,7 @@
     </row>
     <row r="21" spans="2:11">
       <c r="B21" s="43" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>1115</v>
@@ -23134,7 +23706,7 @@
     </row>
     <row r="22" spans="2:11">
       <c r="B22" s="43" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>1114</v>
@@ -23190,7 +23762,7 @@
     </row>
     <row r="24" spans="2:11">
       <c r="B24" s="43" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>127</v>
@@ -23215,7 +23787,7 @@
     </row>
     <row r="25" spans="2:11">
       <c r="B25" s="43" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>27</v>
@@ -23241,7 +23813,7 @@
     </row>
     <row r="26" spans="2:11">
       <c r="B26" s="43" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>32</v>
@@ -23267,7 +23839,7 @@
     </row>
     <row r="27" spans="2:11">
       <c r="B27" s="43" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>112</v>
@@ -23293,7 +23865,7 @@
     </row>
     <row r="28" spans="2:11">
       <c r="B28" s="43" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>111</v>
@@ -23319,7 +23891,7 @@
     </row>
     <row r="29" spans="2:11">
       <c r="B29" s="43" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>110</v>
@@ -23345,7 +23917,7 @@
     </row>
     <row r="30" spans="2:11">
       <c r="B30" s="43" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>73</v>
@@ -23371,7 +23943,7 @@
     </row>
     <row r="31" spans="2:11">
       <c r="B31" s="43" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>71</v>
@@ -23397,7 +23969,7 @@
     </row>
     <row r="32" spans="2:11">
       <c r="B32" s="43" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>113</v>
@@ -23450,7 +24022,7 @@
     </row>
     <row r="34" spans="2:11">
       <c r="B34" s="43" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>127</v>
@@ -23477,7 +24049,7 @@
     </row>
     <row r="35" spans="2:11">
       <c r="B35" s="43" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>90</v>
@@ -23505,7 +24077,7 @@
     </row>
     <row r="36" spans="2:11">
       <c r="B36" s="43" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="C36" s="13" t="s">
         <v>91</v>
@@ -23533,7 +24105,7 @@
     </row>
     <row r="37" spans="2:11">
       <c r="B37" s="43" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="C37" s="13" t="s">
         <v>89</v>
@@ -23561,7 +24133,7 @@
     </row>
     <row r="38" spans="2:11">
       <c r="B38" s="43" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>140</v>
@@ -23589,7 +24161,7 @@
     </row>
     <row r="39" spans="2:11">
       <c r="B39" s="43" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>145</v>
@@ -23617,7 +24189,7 @@
     </row>
     <row r="40" spans="2:11">
       <c r="B40" s="43" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>69</v>
@@ -23645,7 +24217,7 @@
     </row>
     <row r="41" spans="2:11">
       <c r="B41" s="43" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>57</v>
@@ -23673,7 +24245,7 @@
     </row>
     <row r="42" spans="2:11">
       <c r="B42" s="43" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>86</v>
@@ -23728,7 +24300,7 @@
     </row>
     <row r="44" spans="2:11">
       <c r="B44" s="43" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>117</v>
@@ -23753,7 +24325,7 @@
     </row>
     <row r="45" spans="2:11">
       <c r="B45" s="43" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>118</v>
@@ -23779,7 +24351,7 @@
     </row>
     <row r="46" spans="2:11">
       <c r="B46" s="43" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>119</v>
@@ -23832,7 +24404,7 @@
     </row>
     <row r="48" spans="2:11">
       <c r="B48" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>195</v>
@@ -23857,7 +24429,7 @@
     </row>
     <row r="49" spans="2:11">
       <c r="B49" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C49" s="9" t="s">
         <v>163</v>
@@ -23883,7 +24455,7 @@
     </row>
     <row r="50" spans="2:11">
       <c r="B50" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C50" s="9" t="s">
         <v>164</v>
@@ -23909,7 +24481,7 @@
     </row>
     <row r="51" spans="2:11">
       <c r="B51" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C51" s="9" t="s">
         <v>99</v>
@@ -23935,7 +24507,7 @@
     </row>
     <row r="52" spans="2:11">
       <c r="B52" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C52" s="9" t="s">
         <v>191</v>
@@ -23961,7 +24533,7 @@
     </row>
     <row r="53" spans="2:11">
       <c r="B53" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C53" s="9" t="s">
         <v>165</v>
@@ -23987,7 +24559,7 @@
     </row>
     <row r="54" spans="2:11">
       <c r="B54" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C54" s="9" t="s">
         <v>194</v>
@@ -24013,7 +24585,7 @@
     </row>
     <row r="55" spans="2:11">
       <c r="B55" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C55" s="9" t="s">
         <v>100</v>
@@ -24039,7 +24611,7 @@
     </row>
     <row r="56" spans="2:11">
       <c r="B56" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C56" s="9" t="s">
         <v>192</v>
@@ -24065,7 +24637,7 @@
     </row>
     <row r="57" spans="2:11">
       <c r="B57" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C57" s="9" t="s">
         <v>166</v>
@@ -24091,7 +24663,7 @@
     </row>
     <row r="58" spans="2:11">
       <c r="B58" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C58" s="9" t="s">
         <v>167</v>
@@ -24117,7 +24689,7 @@
     </row>
     <row r="59" spans="2:11">
       <c r="B59" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C59" s="9" t="s">
         <v>168</v>
@@ -24143,7 +24715,7 @@
     </row>
     <row r="60" spans="2:11">
       <c r="B60" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C60" s="9" t="s">
         <v>169</v>
@@ -24169,7 +24741,7 @@
     </row>
     <row r="61" spans="2:11">
       <c r="B61" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C61" s="9" t="s">
         <v>171</v>
@@ -24195,7 +24767,7 @@
     </row>
     <row r="62" spans="2:11">
       <c r="B62" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C62" s="9" t="s">
         <v>193</v>
@@ -24221,7 +24793,7 @@
     </row>
     <row r="63" spans="2:11">
       <c r="B63" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C63" s="9" t="s">
         <v>185</v>
@@ -24247,7 +24819,7 @@
     </row>
     <row r="64" spans="2:11">
       <c r="B64" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>267</v>
@@ -24272,7 +24844,7 @@
     </row>
     <row r="65" spans="2:11">
       <c r="B65" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>271</v>
@@ -24297,7 +24869,7 @@
     </row>
     <row r="66" spans="2:11">
       <c r="B66" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>235</v>
@@ -24322,7 +24894,7 @@
     </row>
     <row r="67" spans="2:11">
       <c r="B67" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>196</v>
@@ -24347,7 +24919,7 @@
     </row>
     <row r="68" spans="2:11">
       <c r="B68" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>239</v>
@@ -24372,7 +24944,7 @@
     </row>
     <row r="69" spans="2:11">
       <c r="B69" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>197</v>
@@ -24397,7 +24969,7 @@
     </row>
     <row r="70" spans="2:11">
       <c r="B70" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>280</v>
@@ -24422,7 +24994,7 @@
     </row>
     <row r="71" spans="2:11">
       <c r="B71" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>242</v>
@@ -24447,7 +25019,7 @@
     </row>
     <row r="72" spans="2:11">
       <c r="B72" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C72" s="8" t="s">
         <v>244</v>
@@ -24472,7 +25044,7 @@
     </row>
     <row r="73" spans="2:11">
       <c r="B73" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>246</v>
@@ -24497,7 +25069,7 @@
     </row>
     <row r="74" spans="2:11">
       <c r="B74" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C74" s="8" t="s">
         <v>248</v>
@@ -24522,7 +25094,7 @@
     </row>
     <row r="75" spans="2:11">
       <c r="B75" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>250</v>
@@ -24547,7 +25119,7 @@
     </row>
     <row r="76" spans="2:11">
       <c r="B76" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C76" s="8" t="s">
         <v>253</v>
@@ -24572,7 +25144,7 @@
     </row>
     <row r="77" spans="2:11">
       <c r="B77" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>199</v>
@@ -24597,7 +25169,7 @@
     </row>
     <row r="78" spans="2:11">
       <c r="B78" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>201</v>
@@ -24622,7 +25194,7 @@
     </row>
     <row r="79" spans="2:11">
       <c r="B79" s="43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>285</v>
@@ -24673,7 +25245,7 @@
     </row>
     <row r="81" spans="2:11">
       <c r="B81" s="43" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>336</v>
@@ -24699,7 +25271,7 @@
     </row>
     <row r="82" spans="2:11">
       <c r="B82" s="43" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>338</v>
@@ -24725,7 +25297,7 @@
     </row>
     <row r="83" spans="2:11">
       <c r="B83" s="43" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>339</v>
@@ -24751,7 +25323,7 @@
     </row>
     <row r="84" spans="2:11">
       <c r="B84" s="43" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>337</v>
@@ -24777,7 +25349,7 @@
     </row>
     <row r="85" spans="2:11">
       <c r="B85" s="43" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>340</v>
@@ -24803,7 +25375,7 @@
     </row>
     <row r="86" spans="2:11">
       <c r="B86" s="43" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>341</v>
@@ -24829,7 +25401,7 @@
     </row>
     <row r="87" spans="2:11">
       <c r="B87" s="43" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>342</v>
@@ -24881,7 +25453,7 @@
     </row>
     <row r="89" spans="2:11">
       <c r="B89" s="43" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>1110</v>
@@ -24905,7 +25477,7 @@
     </row>
     <row r="90" spans="2:11">
       <c r="B90" s="43" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>1100</v>
@@ -24929,7 +25501,7 @@
     </row>
     <row r="91" spans="2:11">
       <c r="B91" s="43" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>1111</v>
@@ -24979,7 +25551,7 @@
     </row>
     <row r="93" spans="2:11">
       <c r="B93" s="8" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>1174</v>
@@ -25005,7 +25577,7 @@
     </row>
     <row r="94" spans="2:11">
       <c r="B94" s="8" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>1281</v>
@@ -25031,7 +25603,7 @@
     </row>
     <row r="95" spans="2:11">
       <c r="B95" s="8" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>1188</v>
@@ -25057,7 +25629,7 @@
     </row>
     <row r="96" spans="2:11">
       <c r="B96" s="8" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>1540</v>
@@ -25086,7 +25658,7 @@
     </row>
     <row r="97" spans="2:11">
       <c r="B97" s="8" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>1290</v>
@@ -25112,7 +25684,7 @@
     </row>
     <row r="98" spans="2:11">
       <c r="B98" s="8" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>1538</v>
@@ -25138,7 +25710,7 @@
     </row>
     <row r="99" spans="2:11">
       <c r="B99" s="8" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>1543</v>
@@ -25164,7 +25736,7 @@
     </row>
     <row r="100" spans="2:11">
       <c r="B100" s="8" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>1544</v>
@@ -25190,7 +25762,7 @@
     </row>
     <row r="101" spans="2:11">
       <c r="B101" s="8" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>1545</v>
@@ -25216,7 +25788,7 @@
     </row>
     <row r="102" spans="2:11">
       <c r="B102" s="8" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>1546</v>
@@ -25242,7 +25814,7 @@
     </row>
     <row r="103" spans="2:11">
       <c r="B103" s="8" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>1570</v>
@@ -25268,7 +25840,7 @@
     </row>
     <row r="104" spans="2:11">
       <c r="B104" s="8" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>1547</v>
@@ -25320,7 +25892,7 @@
     </row>
     <row r="106" spans="2:11">
       <c r="B106" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>1425</v>
@@ -25348,7 +25920,7 @@
     </row>
     <row r="107" spans="2:11">
       <c r="B107" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C107" s="8" t="s">
         <v>1426</v>
@@ -25376,7 +25948,7 @@
     </row>
     <row r="108" spans="2:11">
       <c r="B108" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>1427</v>
@@ -25404,7 +25976,7 @@
     </row>
     <row r="109" spans="2:11">
       <c r="B109" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>1428</v>
@@ -25432,7 +26004,7 @@
     </row>
     <row r="110" spans="2:11">
       <c r="B110" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C110" s="8" t="s">
         <v>1429</v>
@@ -25460,7 +26032,7 @@
     </row>
     <row r="111" spans="2:11">
       <c r="B111" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C111" s="8" t="s">
         <v>1389</v>
@@ -25488,7 +26060,7 @@
     </row>
     <row r="112" spans="2:11">
       <c r="B112" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>1430</v>
@@ -25516,7 +26088,7 @@
     </row>
     <row r="113" spans="2:11">
       <c r="B113" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C113" s="8" t="s">
         <v>1390</v>
@@ -25544,7 +26116,7 @@
     </row>
     <row r="114" spans="2:11">
       <c r="B114" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C114" s="8" t="s">
         <v>1431</v>
@@ -25572,7 +26144,7 @@
     </row>
     <row r="115" spans="2:11">
       <c r="B115" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C115" s="8" t="s">
         <v>1397</v>
@@ -25600,7 +26172,7 @@
     </row>
     <row r="116" spans="2:11">
       <c r="B116" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C116" s="8" t="s">
         <v>1432</v>
@@ -25628,7 +26200,7 @@
     </row>
     <row r="117" spans="2:11">
       <c r="B117" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>1391</v>
@@ -25656,7 +26228,7 @@
     </row>
     <row r="118" spans="2:11">
       <c r="B118" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C118" s="8" t="s">
         <v>1392</v>
@@ -25684,7 +26256,7 @@
     </row>
     <row r="119" spans="2:11">
       <c r="B119" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>1393</v>
@@ -25712,7 +26284,7 @@
     </row>
     <row r="120" spans="2:11">
       <c r="B120" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C120" s="8" t="s">
         <v>1402</v>
@@ -25740,7 +26312,7 @@
     </row>
     <row r="121" spans="2:11">
       <c r="B121" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C121" s="8" t="s">
         <v>1398</v>
@@ -25768,7 +26340,7 @@
     </row>
     <row r="122" spans="2:11">
       <c r="B122" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C122" s="8" t="s">
         <v>1399</v>
@@ -25796,7 +26368,7 @@
     </row>
     <row r="123" spans="2:11">
       <c r="B123" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C123" s="8" t="s">
         <v>1433</v>
@@ -25824,7 +26396,7 @@
     </row>
     <row r="124" spans="2:11">
       <c r="B124" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C124" s="8" t="s">
         <v>1434</v>
@@ -25852,7 +26424,7 @@
     </row>
     <row r="125" spans="2:11">
       <c r="B125" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C125" s="8" t="s">
         <v>1394</v>
@@ -25880,7 +26452,7 @@
     </row>
     <row r="126" spans="2:11">
       <c r="B126" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C126" s="8" t="s">
         <v>1435</v>
@@ -25908,7 +26480,7 @@
     </row>
     <row r="127" spans="2:11">
       <c r="B127" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C127" s="8" t="s">
         <v>1400</v>
@@ -25936,7 +26508,7 @@
     </row>
     <row r="128" spans="2:11">
       <c r="B128" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C128" s="8" t="s">
         <v>1395</v>
@@ -25964,7 +26536,7 @@
     </row>
     <row r="129" spans="2:11">
       <c r="B129" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C129" s="8" t="s">
         <v>1396</v>
@@ -25992,7 +26564,7 @@
     </row>
     <row r="130" spans="2:11">
       <c r="B130" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C130" s="8" t="s">
         <v>1436</v>
@@ -26020,7 +26592,7 @@
     </row>
     <row r="131" spans="2:11">
       <c r="B131" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C131" s="8" t="s">
         <v>1401</v>
@@ -26048,7 +26620,7 @@
     </row>
     <row r="132" spans="2:11">
       <c r="B132" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C132" s="8" t="s">
         <v>1403</v>
@@ -26076,7 +26648,7 @@
     </row>
     <row r="133" spans="2:11">
       <c r="B133" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C133" s="8" t="s">
         <v>1404</v>
@@ -26104,7 +26676,7 @@
     </row>
     <row r="134" spans="2:11">
       <c r="B134" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C134" s="8" t="s">
         <v>1405</v>
@@ -26132,7 +26704,7 @@
     </row>
     <row r="135" spans="2:11">
       <c r="B135" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C135" s="8" t="s">
         <v>1406</v>
@@ -26160,7 +26732,7 @@
     </row>
     <row r="136" spans="2:11">
       <c r="B136" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C136" s="8" t="s">
         <v>1407</v>
@@ -26188,7 +26760,7 @@
     </row>
     <row r="137" spans="2:11">
       <c r="B137" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C137" s="8" t="s">
         <v>1437</v>
@@ -26216,7 +26788,7 @@
     </row>
     <row r="138" spans="2:11">
       <c r="B138" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C138" s="8" t="s">
         <v>1558</v>
@@ -26244,7 +26816,7 @@
     </row>
     <row r="139" spans="2:11">
       <c r="B139" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>1562</v>
@@ -26272,7 +26844,7 @@
     </row>
     <row r="140" spans="2:11">
       <c r="B140" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C140" s="8" t="s">
         <v>1564</v>
@@ -26300,7 +26872,7 @@
     </row>
     <row r="141" spans="2:11">
       <c r="B141" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>1566</v>
@@ -26328,7 +26900,7 @@
     </row>
     <row r="142" spans="2:11">
       <c r="B142" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>1424</v>
@@ -26380,7 +26952,7 @@
     </row>
     <row r="144" spans="2:11">
       <c r="B144" s="8" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C144" s="8" t="s">
         <v>1504</v>
@@ -26406,7 +26978,7 @@
     </row>
     <row r="145" spans="2:11">
       <c r="B145" s="8" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C145" s="8" t="s">
         <v>1518</v>
@@ -26432,7 +27004,7 @@
     </row>
     <row r="146" spans="2:11">
       <c r="B146" s="8" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C146" s="8" t="s">
         <v>1505</v>
@@ -26458,7 +27030,7 @@
     </row>
     <row r="147" spans="2:11">
       <c r="B147" s="8" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>1506</v>
@@ -26484,7 +27056,7 @@
     </row>
     <row r="148" spans="2:11">
       <c r="B148" s="8" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C148" s="8" t="s">
         <v>1507</v>
@@ -26510,7 +27082,7 @@
     </row>
     <row r="149" spans="2:11">
       <c r="B149" s="8" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C149" s="8" t="s">
         <v>1508</v>
@@ -26536,7 +27108,7 @@
     </row>
     <row r="150" spans="2:11">
       <c r="B150" s="8" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C150" s="8" t="s">
         <v>1509</v>
@@ -26562,7 +27134,7 @@
     </row>
     <row r="151" spans="2:11">
       <c r="B151" s="8" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C151" s="8" t="s">
         <v>1510</v>
@@ -26588,7 +27160,7 @@
     </row>
     <row r="152" spans="2:11">
       <c r="B152" s="8" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C152" s="8" t="s">
         <v>1511</v>
@@ -26614,7 +27186,7 @@
     </row>
     <row r="153" spans="2:11">
       <c r="B153" s="8" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C153" s="8" t="s">
         <v>1512</v>
@@ -26640,7 +27212,7 @@
     </row>
     <row r="154" spans="2:11">
       <c r="B154" s="8" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C154" s="8" t="s">
         <v>1513</v>
@@ -26666,7 +27238,7 @@
     </row>
     <row r="155" spans="2:11">
       <c r="B155" s="8" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C155" s="8" t="s">
         <v>1514</v>
@@ -26692,7 +27264,7 @@
     </row>
     <row r="156" spans="2:11">
       <c r="B156" s="8" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C156" s="8" t="s">
         <v>1519</v>
@@ -26718,7 +27290,7 @@
     </row>
     <row r="157" spans="2:11">
       <c r="B157" s="8" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C157" s="8" t="s">
         <v>1515</v>
@@ -26744,7 +27316,7 @@
     </row>
     <row r="158" spans="2:11">
       <c r="B158" s="8" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C158" s="8" t="s">
         <v>1516</v>
@@ -26770,7 +27342,7 @@
     </row>
     <row r="159" spans="2:11">
       <c r="B159" s="8" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C159" s="8" t="s">
         <v>1517</v>
@@ -26796,10 +27368,10 @@
     </row>
     <row r="160" spans="2:11">
       <c r="B160" s="6" t="s">
+        <v>1888</v>
+      </c>
+      <c r="C160" s="6" t="s">
         <v>1889</v>
-      </c>
-      <c r="C160" s="6" t="s">
-        <v>1890</v>
       </c>
       <c r="D160" s="6" t="s">
         <v>1117</v>
@@ -26822,10 +27394,10 @@
     </row>
     <row r="161" spans="2:11">
       <c r="B161" s="8" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="D161" s="8"/>
       <c r="E161" s="8">
@@ -26839,7 +27411,7 @@
         <v>125</v>
       </c>
       <c r="I161" s="8" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="K161" s="5" t="str">
         <f t="shared" si="18"/>
@@ -26848,10 +27420,10 @@
     </row>
     <row r="162" spans="2:11">
       <c r="B162" s="8" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="D162" s="8"/>
       <c r="E162" s="8">
@@ -26865,7 +27437,7 @@
         <v>125</v>
       </c>
       <c r="I162" s="8" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="K162" s="5" t="str">
         <f t="shared" si="18"/>
@@ -26874,10 +27446,10 @@
     </row>
     <row r="163" spans="2:11">
       <c r="B163" s="8" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="D163" s="8"/>
       <c r="E163" s="8">
@@ -26891,7 +27463,7 @@
         <v>125</v>
       </c>
       <c r="I163" s="8" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="K163" s="5" t="str">
         <f t="shared" si="18"/>
@@ -26900,10 +27472,10 @@
     </row>
     <row r="164" spans="2:11">
       <c r="B164" s="8" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="D164" s="8"/>
       <c r="E164" s="8">
@@ -26917,7 +27489,7 @@
         <v>125</v>
       </c>
       <c r="I164" s="8" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="K164" s="5" t="str">
         <f t="shared" si="18"/>
@@ -26926,10 +27498,10 @@
     </row>
     <row r="165" spans="2:11">
       <c r="B165" s="8" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="D165" s="8"/>
       <c r="E165" s="8">
@@ -26943,7 +27515,7 @@
         <v>125</v>
       </c>
       <c r="I165" s="8" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="K165" s="5" t="str">
         <f t="shared" si="18"/>
@@ -26952,10 +27524,10 @@
     </row>
     <row r="166" spans="2:11">
       <c r="B166" s="8" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="D166" s="8"/>
       <c r="E166" s="8">
@@ -26969,7 +27541,7 @@
         <v>125</v>
       </c>
       <c r="I166" s="8" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="K166" s="5" t="str">
         <f t="shared" si="18"/>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE81F9C-F14B-4541-988A-020733B9B55B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467D6ACF-1B96-40D3-8192-9812A5CD7B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="3" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4485" uniqueCount="2250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4556" uniqueCount="2315">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -9521,6 +9521,203 @@
   </si>
   <si>
     <t>分析・散布図・高度な可視化</t>
+  </si>
+  <si>
+    <t>① スキルの「共起ランキング」</t>
+  </si>
+  <si>
+    <t>これはかなり面白いと思う。</t>
+  </si>
+  <si>
+    <t>Java + Spring       12,342件</t>
+  </si>
+  <si>
+    <t>Java + AWS           8,123件</t>
+  </si>
+  <si>
+    <t>Python + AWS         6,842件</t>
+  </si>
+  <si>
+    <t>React + TypeScript   5,931件</t>
+  </si>
+  <si>
+    <t>C# + .NET            5,102件</t>
+  </si>
+  <si>
+    <t>単純なスキルランキングではなく、</t>
+  </si>
+  <si>
+    <t>「この技術が要求される案件では、何が一緒に要求されるのか」</t>
+  </si>
+  <si>
+    <t>を見る。</t>
+  </si>
+  <si>
+    <t>t_job_features があるからかなり簡単にできる。</t>
+  </si>
+  <si>
+    <t>①の発展。</t>
+  </si>
+  <si>
+    <t>例えば Go を選択したら、</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ├─ Docker       63%</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ├─ AWS          51%</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ├─ Kubernetes   28%</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ├─ PostgreSQL   21%</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> └─ React         8%</t>
+  </si>
+  <si>
+    <t>みたいな感じ。</t>
+  </si>
+  <si>
+    <t>**「Goエンジニアに求められている周辺技術」**というUIにすると、かなり面白い。</t>
+  </si>
+  <si>
+    <t>② 「このスキルを持っていると、何が要求されるか」</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>③ スキル × リモート率</t>
+  </si>
+  <si>
+    <t>今のSQLを組み合わせるだけでも作れる。</t>
+  </si>
+  <si>
+    <t>技術       案件数   フルリモート率</t>
+  </si>
+  <si>
+    <t>----------------------------------</t>
+  </si>
+  <si>
+    <t>Java       20,000      42%</t>
+  </si>
+  <si>
+    <t>Python     12,000      57%</t>
+  </si>
+  <si>
+    <t>Go          3,000      64%</t>
+  </si>
+  <si>
+    <t>C#          8,000      31%</t>
+  </si>
+  <si>
+    <t>これ、単価ランキングとは違う切り口になる。</t>
+  </si>
+  <si>
+    <t>東京      45%</t>
+  </si>
+  <si>
+    <t>大阪      18%</t>
+  </si>
+  <si>
+    <t>福岡       9%</t>
+  </si>
+  <si>
+    <t>愛知       7%</t>
+  </si>
+  <si>
+    <t>...</t>
+  </si>
+  <si>
+    <t>さらに、</t>
+  </si>
+  <si>
+    <t>福岡ではどんな技術が多い？</t>
+  </si>
+  <si>
+    <t>みたいな逆引きもできる。</t>
+  </si>
+  <si>
+    <t>あなたがさっき作った都道府県ソートも、ここで生きる。</t>
+  </si>
+  <si>
+    <t>④ スキル × 地域</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>⑤ 「要求スキル数 × 単価」は、今のアイデアをもう少し育てたい</t>
+  </si>
+  <si>
+    <t>これは結構面白い。</t>
+  </si>
+  <si>
+    <t>今の</t>
+  </si>
+  <si>
+    <t>max_salary / skill_count</t>
+  </si>
+  <si>
+    <t>は、分析指標としてはかなり雑だけど、アイデアとしては面白い。</t>
+  </si>
+  <si>
+    <t>高単価なのに要求スキルが少ない案件</t>
+  </si>
+  <si>
+    <t>を探す。</t>
+  </si>
+  <si>
+    <t>ただし skill_count は、</t>
+  </si>
+  <si>
+    <t>featureの抽出精度</t>
+  </si>
+  <si>
+    <t>カテゴリ数</t>
+  </si>
+  <si>
+    <t>サイトごとの記載量</t>
+  </si>
+  <si>
+    <t>にかなり影響される。</t>
+  </si>
+  <si>
+    <t>なので「お得度」と断定するより、</t>
+  </si>
+  <si>
+    <t>「報酬 / 要求スキル数」という独自指標</t>
+  </si>
+  <si>
+    <t>として扱うのがよさそう。</t>
+  </si>
+  <si>
+    <t>あと、今後の差分クロール方針と相性がいいのが「新着傾向」</t>
+  </si>
+  <si>
+    <t>ここは今すぐは無理でも、将来的にかなり強い。</t>
+  </si>
+  <si>
+    <t>created_at があなたがクロールした日で、updated_at がサイト掲載日/更新日なら、</t>
+  </si>
+  <si>
+    <t>直近1週間で追加された案件</t>
+  </si>
+  <si>
+    <t>を見られる。</t>
+  </si>
+  <si>
+    <t>今週増えた技術</t>
+  </si>
+  <si>
+    <t>今週増えた地域</t>
+  </si>
+  <si>
+    <t>今週増えた高単価案件</t>
+  </si>
+  <si>
+    <t>みたいにできる。</t>
+  </si>
+  <si>
+    <t>これは静的なランキングよりダッシュボード映えする。</t>
   </si>
 </sst>
 </file>
@@ -18105,7 +18302,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC349EE6-5475-4F9C-BD43-5DC02797CE07}">
-  <dimension ref="A2:R290"/>
+  <dimension ref="A2:R415"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="11" style="98" customWidth="1"/>
@@ -20204,6 +20401,361 @@
       <c r="N290" s="110"/>
       <c r="O290" s="98" t="s">
         <v>2190</v>
+      </c>
+    </row>
+    <row r="293" spans="14:15">
+      <c r="O293" s="98" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="295" spans="14:15">
+      <c r="O295" s="98" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="297" spans="14:15">
+      <c r="O297" s="98" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="299" spans="14:15">
+      <c r="O299" s="98" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="300" spans="14:15">
+      <c r="O300" s="98" t="s">
+        <v>2253</v>
+      </c>
+    </row>
+    <row r="301" spans="14:15">
+      <c r="O301" s="98" t="s">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="302" spans="14:15">
+      <c r="O302" s="98" t="s">
+        <v>2255</v>
+      </c>
+    </row>
+    <row r="303" spans="14:15">
+      <c r="O303" s="98" t="s">
+        <v>2256</v>
+      </c>
+    </row>
+    <row r="305" spans="15:15">
+      <c r="O305" s="98" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="307" spans="15:15">
+      <c r="O307" s="98" t="s">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="309" spans="15:15">
+      <c r="O309" s="98" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="311" spans="15:15">
+      <c r="O311" s="98" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="314" spans="15:15">
+      <c r="O314" s="98" t="s">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="316" spans="15:15">
+      <c r="O316" s="98" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="318" spans="15:15">
+      <c r="O318" s="98" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="320" spans="15:15">
+      <c r="O320" s="98" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="321" spans="15:15">
+      <c r="O321" s="98" t="s">
+        <v>2263</v>
+      </c>
+    </row>
+    <row r="322" spans="15:15">
+      <c r="O322" s="98" t="s">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="323" spans="15:15">
+      <c r="O323" s="98" t="s">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="324" spans="15:15">
+      <c r="O324" s="98" t="s">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="325" spans="15:15">
+      <c r="O325" s="98" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="327" spans="15:15">
+      <c r="O327" s="98" t="s">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="329" spans="15:15">
+      <c r="O329" s="98" t="s">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="331" spans="15:15">
+      <c r="O331" s="98" t="s">
+        <v>2271</v>
+      </c>
+    </row>
+    <row r="333" spans="15:15">
+      <c r="O333" s="98" t="s">
+        <v>2272</v>
+      </c>
+    </row>
+    <row r="335" spans="15:15">
+      <c r="O335" s="98" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="336" spans="15:15">
+      <c r="O336" s="98" t="s">
+        <v>2274</v>
+      </c>
+    </row>
+    <row r="337" spans="15:15">
+      <c r="O337" s="98" t="s">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="338" spans="15:15">
+      <c r="O338" s="98" t="s">
+        <v>2276</v>
+      </c>
+    </row>
+    <row r="339" spans="15:15">
+      <c r="O339" s="98" t="s">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="340" spans="15:15">
+      <c r="O340" s="98" t="s">
+        <v>2278</v>
+      </c>
+    </row>
+    <row r="342" spans="15:15">
+      <c r="O342" s="98" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="345" spans="15:15">
+      <c r="O345" s="98" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="347" spans="15:15">
+      <c r="O347" s="98" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="349" spans="15:15">
+      <c r="O349" s="98" t="s">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="350" spans="15:15">
+      <c r="O350" s="98" t="s">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="351" spans="15:15">
+      <c r="O351" s="98" t="s">
+        <v>2281</v>
+      </c>
+    </row>
+    <row r="352" spans="15:15">
+      <c r="O352" s="98" t="s">
+        <v>2282</v>
+      </c>
+    </row>
+    <row r="353" spans="15:15">
+      <c r="O353" s="98" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="354" spans="15:15">
+      <c r="O354" s="98" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="356" spans="15:15">
+      <c r="O356" s="98" t="s">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="358" spans="15:15">
+      <c r="O358" s="98" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="360" spans="15:15">
+      <c r="O360" s="98" t="s">
+        <v>2287</v>
+      </c>
+    </row>
+    <row r="362" spans="15:15">
+      <c r="O362" s="98" t="s">
+        <v>2288</v>
+      </c>
+    </row>
+    <row r="365" spans="15:15">
+      <c r="O365" s="98" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="367" spans="15:15">
+      <c r="O367" s="98" t="s">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="369" spans="15:15">
+      <c r="O369" s="98" t="s">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="371" spans="15:15">
+      <c r="O371" s="98" t="s">
+        <v>2293</v>
+      </c>
+    </row>
+    <row r="373" spans="15:15">
+      <c r="O373" s="98" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="375" spans="15:15">
+      <c r="O375" s="98" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="377" spans="15:15">
+      <c r="O377" s="98" t="s">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="379" spans="15:15">
+      <c r="O379" s="98" t="s">
+        <v>2296</v>
+      </c>
+    </row>
+    <row r="381" spans="15:15">
+      <c r="O381" s="98" t="s">
+        <v>2297</v>
+      </c>
+    </row>
+    <row r="383" spans="15:15">
+      <c r="O383" s="98" t="s">
+        <v>2298</v>
+      </c>
+    </row>
+    <row r="384" spans="15:15">
+      <c r="O384" s="98" t="s">
+        <v>2299</v>
+      </c>
+    </row>
+    <row r="385" spans="15:15">
+      <c r="O385" s="98" t="s">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="387" spans="15:15">
+      <c r="O387" s="98" t="s">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="389" spans="15:15">
+      <c r="O389" s="98" t="s">
+        <v>2302</v>
+      </c>
+    </row>
+    <row r="391" spans="15:15">
+      <c r="O391" s="98" t="s">
+        <v>2303</v>
+      </c>
+    </row>
+    <row r="393" spans="15:15">
+      <c r="O393" s="98" t="s">
+        <v>2304</v>
+      </c>
+    </row>
+    <row r="397" spans="15:15">
+      <c r="O397" s="98" t="s">
+        <v>2305</v>
+      </c>
+    </row>
+    <row r="399" spans="15:15">
+      <c r="O399" s="98" t="s">
+        <v>2306</v>
+      </c>
+    </row>
+    <row r="401" spans="15:15">
+      <c r="O401" s="98" t="s">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="403" spans="15:15">
+      <c r="O403" s="98" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="405" spans="15:15">
+      <c r="O405" s="98" t="s">
+        <v>2309</v>
+      </c>
+    </row>
+    <row r="407" spans="15:15">
+      <c r="O407" s="98" t="s">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="409" spans="15:15">
+      <c r="O409" s="98" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="410" spans="15:15">
+      <c r="O410" s="98" t="s">
+        <v>2311</v>
+      </c>
+    </row>
+    <row r="411" spans="15:15">
+      <c r="O411" s="98" t="s">
+        <v>2312</v>
+      </c>
+    </row>
+    <row r="413" spans="15:15">
+      <c r="O413" s="98" t="s">
+        <v>2313</v>
+      </c>
+    </row>
+    <row r="415" spans="15:15">
+      <c r="O415" s="98" t="s">
+        <v>2314</v>
       </c>
     </row>
   </sheetData>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467D6ACF-1B96-40D3-8192-9812A5CD7B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF2D6EDA-2C74-4C6D-91B2-620EC1BB6737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="3" activeTab="9" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="3" activeTab="10" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="architecture" sheetId="12" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4556" uniqueCount="2315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4640" uniqueCount="2370">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -9718,6 +9718,233 @@
   </si>
   <si>
     <t>これは静的なランキングよりダッシュボード映えする。</t>
+  </si>
+  <si>
+    <t>ブランド</t>
+  </si>
+  <si>
+    <t>グレード感</t>
+  </si>
+  <si>
+    <t>バリエーション</t>
+  </si>
+  <si>
+    <t>コメント</t>
+  </si>
+  <si>
+    <t>中～高</t>
+  </si>
+  <si>
+    <t>Soloist / Dinky / Kelly / King V / Warriorなど非常に多い</t>
+  </si>
+  <si>
+    <t>Pro-Mod系など現行モデルが豊富。Jacksonとは違う方向性</t>
+  </si>
+  <si>
+    <t>Electromatic～Professionalまで幅広い。セミアコ系も大量</t>
+  </si>
+  <si>
+    <t>PRS SE / Core</t>
+  </si>
+  <si>
+    <t>既にPRSあるけど、SE系まで拾うならかなり増える</t>
+  </si>
+  <si>
+    <t>Tokai</t>
+  </si>
+  <si>
+    <t>国産系でかなり面白い。Les Paul系、ST系、TE系など</t>
+  </si>
+  <si>
+    <t>国産。Expert / J-Standard等でモデル展開が多い</t>
+  </si>
+  <si>
+    <t>Universe～Global～Craft等、価格帯・モデル数ともに多い</t>
+  </si>
+  <si>
+    <t>Navigator</t>
+  </si>
+  <si>
+    <t>高</t>
+  </si>
+  <si>
+    <t>★★★</t>
+  </si>
+  <si>
+    <t>ESP系だけど独立ブランドとして見ると高級国産枠</t>
+  </si>
+  <si>
+    <t>日本ブランド。変形系を含め個性的</t>
+  </si>
+  <si>
+    <t>Duvell / Regius / Hydra等。ハイエンド寄り</t>
+  </si>
+  <si>
+    <t>既に入ってるけど、Modern / Classic / Alt T等かなり多い</t>
+  </si>
+  <si>
+    <t>Tom Anderson</t>
+  </si>
+  <si>
+    <t>ハイエンド。Classic / Angel / Drop Top等</t>
+  </si>
+  <si>
+    <t>既にMusicManならブランド表記統一候補</t>
+  </si>
+  <si>
+    <t>EVH</t>
+  </si>
+  <si>
+    <t>Wolfgang中心だがグレード違いが多い</t>
+  </si>
+  <si>
+    <t>Rickenbacker</t>
+  </si>
+  <si>
+    <t>モデル数自体はそこまで多くないがブランド価値は高い</t>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>国産ヴィンテージ系。モデル展開が非常に広い</t>
+  </si>
+  <si>
+    <t>Ernie Ball Music Man</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Caparison — 日本のハイエンド系。モデル数もそこそこ</t>
+  </si>
+  <si>
+    <t>Kiesel — カスタムオーダー型でバリエーションが異常に多い</t>
+  </si>
+  <si>
+    <t>Vigier — フランスのハイエンド</t>
+  </si>
+  <si>
+    <t>Knaggs — 高級系、モデル展開もそこそこ</t>
+  </si>
+  <si>
+    <t>LTD — ESPと別ブランドとして扱うなら大量追加できる</t>
+  </si>
+  <si>
+    <t>colly、価格なし、モデル少な目</t>
+    <rPh sb="6" eb="8">
+      <t>カカク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>スク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Bacchus</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>momoseと同じ構造かも。クロール実績あり</t>
+    <rPh sb="7" eb="8">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウゾウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジッセキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Killer</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>カラー取れない</t>
+    <rPh sb="3" eb="4">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FUJIGEN</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>colly</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Aristides — 超ハイエンド。モデル数は少なめ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>見送り</t>
+    <rPh sb="0" eb="2">
+      <t>ミオク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Mayones — メタル系ハイエンドとして非常に強い</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>モデル多め？カラバリをどう取るか。</t>
+    <rPh sb="3" eb="4">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Charvel</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>colly、モデル多め？カラバリとれる</t>
+    <rPh sb="9" eb="10">
+      <t>オオ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Mayones</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Greco</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Jackson</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>colly、価格なし、モデル少なめ？（カラー表記にクセあり）</t>
+    <rPh sb="6" eb="8">
+      <t>カカク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>スク</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヒョウキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Gretsch</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Suhr</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -20767,7 +20994,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F0B575-2DDF-49B9-8DE2-F372EEC2F3B3}">
-  <dimension ref="A2:O79"/>
+  <dimension ref="A2:O108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="11.8984375" style="1" customWidth="1"/>
@@ -21709,6 +21936,306 @@
     <row r="79" spans="8:8">
       <c r="H79" s="1" t="s">
         <v>1369</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11">
+      <c r="B83" s="1" t="s">
+        <v>2315</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>2316</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>2317</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>2318</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11">
+      <c r="B84" s="1" t="s">
+        <v>2366</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>2235</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>2320</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11">
+      <c r="B85" s="1" t="s">
+        <v>2362</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>2235</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>2321</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11">
+      <c r="B86" s="1" t="s">
+        <v>2368</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>2235</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11">
+      <c r="B87" s="1" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>2235</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>2324</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11">
+      <c r="B88" s="1" t="s">
+        <v>2325</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>2235</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>2326</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>2351</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11">
+      <c r="B89" s="1" t="s">
+        <v>2356</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>2238</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>2327</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11">
+      <c r="B90" s="1" t="s">
+        <v>2352</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>2235</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>2328</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>2353</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11">
+      <c r="B91" s="1" t="s">
+        <v>2329</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>2330</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>2331</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>2332</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11">
+      <c r="B92" s="1" t="s">
+        <v>2354</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>2238</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>2333</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>2355</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11">
+      <c r="B93" s="1" t="s">
+        <v>2364</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>2330</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>2238</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>2334</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11">
+      <c r="B94" s="1" t="s">
+        <v>2369</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>2330</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>2238</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11">
+      <c r="B95" s="1" t="s">
+        <v>2336</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>2330</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>2238</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11">
+      <c r="B96" s="1" t="s">
+        <v>2345</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>2238</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7">
+      <c r="B97" s="1" t="s">
+        <v>2339</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>2238</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7">
+      <c r="B98" s="1" t="s">
+        <v>2341</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>2330</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>2331</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7">
+      <c r="B99" s="1" t="s">
+        <v>2365</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>2343</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>2235</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7">
+      <c r="B101" s="1" t="s">
+        <v>2346</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7">
+      <c r="B102" s="1" t="s">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7">
+      <c r="B103" s="1" t="s">
+        <v>2358</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7">
+      <c r="B104" s="1" t="s">
+        <v>2360</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7">
+      <c r="B106" s="1" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7">
+      <c r="B107" s="1" t="s">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7">
+      <c r="B108" s="1" t="s">
+        <v>2350</v>
       </c>
     </row>
   </sheetData>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF2D6EDA-2C74-4C6D-91B2-620EC1BB6737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F434E750-A8DB-40A2-82D5-C6E4750875FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="3" activeTab="10" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="3" activeTab="3" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="architecture" sheetId="12" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4640" uniqueCount="2370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4643" uniqueCount="2371">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -9944,6 +9944,10 @@
   </si>
   <si>
     <t>Suhr</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Fernandes</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -24274,7 +24278,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
-  <dimension ref="B4:K166"/>
+  <dimension ref="B4:K167"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -26887,7 +26891,7 @@
         <v>1551</v>
       </c>
       <c r="K102" s="5" t="str">
-        <f t="shared" ref="K102:K104" si="14">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B102&amp;"'"&amp;","&amp;E102&amp;","&amp;"'"&amp;C102&amp;"'"&amp;","&amp;"'"&amp;D102&amp;"'"&amp;","&amp;"'"&amp;F102&amp;"'"&amp;","&amp;G102&amp;","&amp;H102&amp;","&amp;"'"&amp;I102&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K102:K105" si="14">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B102&amp;"'"&amp;","&amp;E102&amp;","&amp;"'"&amp;C102&amp;"'"&amp;","&amp;"'"&amp;D102&amp;"'"&amp;","&amp;"'"&amp;F102&amp;"'"&amp;","&amp;G102&amp;","&amp;H102&amp;","&amp;"'"&amp;I102&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('guitar_makers',10,'MusicMan','','',0,0.0,'https://www.music-man.com/instruments/guitars');</v>
       </c>
     </row>
@@ -26939,62 +26943,58 @@
         <v>1553</v>
       </c>
       <c r="K104" s="5" t="str">
+        <f t="shared" ref="K104" si="15">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B104&amp;"'"&amp;","&amp;E104&amp;","&amp;"'"&amp;C104&amp;"'"&amp;","&amp;"'"&amp;D104&amp;"'"&amp;","&amp;"'"&amp;F104&amp;"'"&amp;","&amp;G104&amp;","&amp;H104&amp;","&amp;"'"&amp;I104&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_makers',12,'Momose','','',0,0.0,'https://www.deviser.co.jp/momose');</v>
+      </c>
+    </row>
+    <row r="105" spans="2:11">
+      <c r="B105" s="8" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>2370</v>
+      </c>
+      <c r="D105" s="8"/>
+      <c r="E105" s="8">
+        <v>13</v>
+      </c>
+      <c r="F105" s="8"/>
+      <c r="G105" s="9">
+        <v>0</v>
+      </c>
+      <c r="H105" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I105" s="8"/>
+      <c r="K105" s="5" t="str">
         <f t="shared" si="14"/>
-        <v>INSERT INTO m_code VALUES ('guitar_makers',12,'Momose','','',0,0.0,'https://www.deviser.co.jp/momose');</v>
-      </c>
-    </row>
-    <row r="105" spans="2:11">
-      <c r="B105" s="6" t="s">
+        <v>INSERT INTO m_code VALUES ('guitar_makers',13,'Fernandes','','',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="106" spans="2:11">
+      <c r="B106" s="6" t="s">
         <v>1542</v>
       </c>
-      <c r="C105" s="6" t="s">
+      <c r="C106" s="6" t="s">
         <v>1388</v>
       </c>
-      <c r="D105" s="6" t="s">
+      <c r="D106" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E105" s="7" t="s">
+      <c r="E106" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F105" s="6" t="s">
+      <c r="F106" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G105" s="6" t="s">
+      <c r="G106" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H105" s="6" t="s">
+      <c r="H106" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I105" s="6" t="s">
+      <c r="I106" s="6" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="106" spans="2:11">
-      <c r="B106" s="8" t="s">
-        <v>1778</v>
-      </c>
-      <c r="C106" s="8" t="s">
-        <v>1425</v>
-      </c>
-      <c r="D106" s="8"/>
-      <c r="E106" s="8">
-        <v>1</v>
-      </c>
-      <c r="F106" s="8" t="s">
-        <v>1439</v>
-      </c>
-      <c r="G106" s="9">
-        <v>0</v>
-      </c>
-      <c r="H106" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I106" s="8" t="s">
-        <v>1463</v>
-      </c>
-      <c r="K106" s="5" t="str">
-        <f t="shared" ref="K106:K141" si="15">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B106&amp;"'"&amp;","&amp;E106&amp;","&amp;"'"&amp;C106&amp;"'"&amp;","&amp;"'"&amp;D106&amp;"'"&amp;","&amp;"'"&amp;F106&amp;"'"&amp;","&amp;G106&amp;","&amp;H106&amp;","&amp;"'"&amp;I106&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',1,'HardMaple','','ハードメイプル',0,0.0,'硬質でタイト、明瞭なアタック。');</v>
       </c>
     </row>
     <row r="107" spans="2:11">
@@ -27002,14 +27002,14 @@
         <v>1778</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="D107" s="8"/>
       <c r="E107" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G107" s="9">
         <v>0</v>
@@ -27018,11 +27018,11 @@
         <v>125</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="K107" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',2,'FlameMaple','','フレイムメイプル',0,0.0,'明るく抜けが良く、華やかな倍音。');</v>
+        <f t="shared" ref="K107:K142" si="16">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B107&amp;"'"&amp;","&amp;E107&amp;","&amp;"'"&amp;C107&amp;"'"&amp;","&amp;"'"&amp;D107&amp;"'"&amp;","&amp;"'"&amp;F107&amp;"'"&amp;","&amp;G107&amp;","&amp;H107&amp;","&amp;"'"&amp;I107&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',1,'HardMaple','','ハードメイプル',0,0.0,'硬質でタイト、明瞭なアタック。');</v>
       </c>
     </row>
     <row r="108" spans="2:11">
@@ -27030,14 +27030,14 @@
         <v>1778</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="D108" s="8"/>
       <c r="E108" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="G108" s="9">
         <v>0</v>
@@ -27046,11 +27046,11 @@
         <v>125</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="K108" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',3,'QuiltedMaple','','キルテッドメイプル',0,0.0,'立体的で広がりがあり、煌びやかな響き。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',2,'FlameMaple','','フレイムメイプル',0,0.0,'明るく抜けが良く、華やかな倍音。');</v>
       </c>
     </row>
     <row r="109" spans="2:11">
@@ -27058,14 +27058,14 @@
         <v>1778</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="D109" s="8"/>
       <c r="E109" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="G109" s="9">
         <v>0</v>
@@ -27074,11 +27074,11 @@
         <v>125</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="K109" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',4,'BirdseyeMaple','','バーズアイメイプル',0,0.0,'粒立ちが良く、明るくシャープ。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',3,'QuiltedMaple','','キルテッドメイプル',0,0.0,'立体的で広がりがあり、煌びやかな響き。');</v>
       </c>
     </row>
     <row r="110" spans="2:11">
@@ -27086,14 +27086,14 @@
         <v>1778</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="D110" s="8"/>
       <c r="E110" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="G110" s="9">
         <v>0</v>
@@ -27102,11 +27102,11 @@
         <v>125</v>
       </c>
       <c r="I110" s="8" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="K110" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',5,'RoastedMaple','','ローステッドメイプル',0,0.0,'引き締まったタイトな音で反応が速い。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',4,'BirdseyeMaple','','バーズアイメイプル',0,0.0,'粒立ちが良く、明るくシャープ。');</v>
       </c>
     </row>
     <row r="111" spans="2:11">
@@ -27114,14 +27114,14 @@
         <v>1778</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>1389</v>
+        <v>1429</v>
       </c>
       <c r="D111" s="8"/>
       <c r="E111" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>1438</v>
+        <v>1443</v>
       </c>
       <c r="G111" s="9">
         <v>0</v>
@@ -27130,11 +27130,11 @@
         <v>125</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>1462</v>
+        <v>1467</v>
       </c>
       <c r="K111" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',6,'Maple','','メイプル',0,0.0,'明るくハリがあり、アタックが強い。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',5,'RoastedMaple','','ローステッドメイプル',0,0.0,'引き締まったタイトな音で反応が速い。');</v>
       </c>
     </row>
     <row r="112" spans="2:11">
@@ -27142,14 +27142,14 @@
         <v>1778</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>1430</v>
+        <v>1389</v>
       </c>
       <c r="D112" s="8"/>
       <c r="E112" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>1444</v>
+        <v>1438</v>
       </c>
       <c r="G112" s="9">
         <v>0</v>
@@ -27158,11 +27158,11 @@
         <v>125</v>
       </c>
       <c r="I112" s="8" t="s">
-        <v>1469</v>
+        <v>1462</v>
       </c>
       <c r="K112" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',7,'HonduranMahogany','','ホンジュラスマホガニー',0,0.0,'深みがあり、太くリッチな中低域。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',6,'Maple','','メイプル',0,0.0,'明るくハリがあり、アタックが強い。');</v>
       </c>
     </row>
     <row r="113" spans="2:11">
@@ -27170,14 +27170,14 @@
         <v>1778</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>1390</v>
+        <v>1430</v>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>1408</v>
+        <v>1444</v>
       </c>
       <c r="G113" s="9">
         <v>0</v>
@@ -27186,11 +27186,11 @@
         <v>125</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="K113" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',8,'Mahogany','','マホガニー',0,0.0,'中低域が豊かで温かい音。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',7,'HonduranMahogany','','ホンジュラスマホガニー',0,0.0,'深みがあり、太くリッチな中低域。');</v>
       </c>
     </row>
     <row r="114" spans="2:11">
@@ -27198,14 +27198,14 @@
         <v>1778</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>1431</v>
+        <v>1390</v>
       </c>
       <c r="D114" s="8"/>
       <c r="E114" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>1445</v>
+        <v>1408</v>
       </c>
       <c r="G114" s="9">
         <v>0</v>
@@ -27214,11 +27214,11 @@
         <v>125</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="K114" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',9,'Sapele','','サペリ',0,0.0,'温かく柔らかいトーンでバランスが良い。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',8,'Mahogany','','マホガニー',0,0.0,'中低域が豊かで温かい音。');</v>
       </c>
     </row>
     <row r="115" spans="2:11">
@@ -27226,14 +27226,14 @@
         <v>1778</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>1397</v>
+        <v>1431</v>
       </c>
       <c r="D115" s="8"/>
       <c r="E115" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="G115" s="9">
         <v>0</v>
@@ -27242,11 +27242,11 @@
         <v>125</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="K115" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',10,'Korina','','コリーナ',0,0.0,'中域が豊かで太い音。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',9,'Sapele','','サペリ',0,0.0,'温かく柔らかいトーンでバランスが良い。');</v>
       </c>
     </row>
     <row r="116" spans="2:11">
@@ -27254,14 +27254,14 @@
         <v>1778</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>1432</v>
+        <v>1397</v>
       </c>
       <c r="D116" s="8"/>
       <c r="E116" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="G116" s="9">
         <v>0</v>
@@ -27270,11 +27270,11 @@
         <v>125</v>
       </c>
       <c r="I116" s="8" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="K116" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',11,'WhiteKorina','','ホワイトコリーナ',0,0.0,'明るく抜けが良く、軽快なレスポンス。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',10,'Korina','','コリーナ',0,0.0,'中域が豊かで太い音。');</v>
       </c>
     </row>
     <row r="117" spans="2:11">
@@ -27282,14 +27282,14 @@
         <v>1778</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>1391</v>
+        <v>1432</v>
       </c>
       <c r="D117" s="8"/>
       <c r="E117" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>1409</v>
+        <v>1447</v>
       </c>
       <c r="G117" s="9">
         <v>0</v>
@@ -27298,11 +27298,11 @@
         <v>125</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="K117" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',12,'Alder','','アルダー',0,0.0,'バランスが良くクセが少ない。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',11,'WhiteKorina','','ホワイトコリーナ',0,0.0,'明るく抜けが良く、軽快なレスポンス。');</v>
       </c>
     </row>
     <row r="118" spans="2:11">
@@ -27310,14 +27310,14 @@
         <v>1778</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="D118" s="8"/>
       <c r="E118" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>1448</v>
+        <v>1409</v>
       </c>
       <c r="G118" s="9">
         <v>0</v>
@@ -27326,11 +27326,11 @@
         <v>125</v>
       </c>
       <c r="I118" s="8" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="K118" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',13,'Ash','','アッシュ',0,0.0,'明るく抜ける音でアタックが強い。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',12,'Alder','','アルダー',0,0.0,'バランスが良くクセが少ない。');</v>
       </c>
     </row>
     <row r="119" spans="2:11">
@@ -27338,14 +27338,14 @@
         <v>1778</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="D119" s="8"/>
       <c r="E119" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="G119" s="9">
         <v>0</v>
@@ -27354,11 +27354,11 @@
         <v>125</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="K119" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',14,'Basswood','','バスウッド',0,0.0,'軽く柔らかく、ウォームで扱いやすい。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',13,'Ash','','アッシュ',0,0.0,'明るく抜ける音でアタックが強い。');</v>
       </c>
     </row>
     <row r="120" spans="2:11">
@@ -27366,14 +27366,14 @@
         <v>1778</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>1402</v>
+        <v>1393</v>
       </c>
       <c r="D120" s="8"/>
       <c r="E120" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="G120" s="9">
         <v>0</v>
@@ -27382,11 +27382,11 @@
         <v>125</v>
       </c>
       <c r="I120" s="8" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="K120" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',15,'Poplar','','ポプラ',0,0.0,'軽く素直でクセが少ない。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',14,'Basswood','','バスウッド',0,0.0,'軽く柔らかく、ウォームで扱いやすい。');</v>
       </c>
     </row>
     <row r="121" spans="2:11">
@@ -27394,14 +27394,14 @@
         <v>1778</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="D121" s="8"/>
       <c r="E121" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="G121" s="9">
         <v>0</v>
@@ -27410,11 +27410,11 @@
         <v>125</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="K121" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',16,'Spruce','','スプルース',0,0.0,'軽く響きが良く、明るいトーン。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',15,'Poplar','','ポプラ',0,0.0,'軽く素直でクセが少ない。');</v>
       </c>
     </row>
     <row r="122" spans="2:11">
@@ -27422,14 +27422,14 @@
         <v>1778</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="D122" s="8"/>
       <c r="E122" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="G122" s="9">
         <v>0</v>
@@ -27438,11 +27438,11 @@
         <v>125</v>
       </c>
       <c r="I122" s="8" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="K122" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',17,'Cedar','','シダー',0,0.0,'柔らかく温かい音。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',16,'Spruce','','スプルース',0,0.0,'軽く響きが良く、明るいトーン。');</v>
       </c>
     </row>
     <row r="123" spans="2:11">
@@ -27450,14 +27450,14 @@
         <v>1778</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>1433</v>
+        <v>1399</v>
       </c>
       <c r="D123" s="8"/>
       <c r="E123" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="G123" s="9">
         <v>0</v>
@@ -27466,11 +27466,11 @@
         <v>125</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="K123" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',18,'IndianRosewood','','インディアンローズウッド',0,0.0,'甘く深みがあり、豊かな中低域。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',17,'Cedar','','シダー',0,0.0,'柔らかく温かい音。');</v>
       </c>
     </row>
     <row r="124" spans="2:11">
@@ -27478,14 +27478,14 @@
         <v>1778</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="D124" s="8"/>
       <c r="E124" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F124" s="8" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="G124" s="9">
         <v>0</v>
@@ -27494,11 +27494,11 @@
         <v>125</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="K124" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',19,'BrazilianRosewood','','ブラジリアンローズウッド',0,0.0,'濃厚で深いトーン、豊かな倍音。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',18,'IndianRosewood','','インディアンローズウッド',0,0.0,'甘く深みがあり、豊かな中低域。');</v>
       </c>
     </row>
     <row r="125" spans="2:11">
@@ -27506,14 +27506,14 @@
         <v>1778</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>1394</v>
+        <v>1434</v>
       </c>
       <c r="D125" s="8"/>
       <c r="E125" s="8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="G125" s="9">
         <v>0</v>
@@ -27522,11 +27522,11 @@
         <v>125</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="K125" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',20,'Rosewood','','ローズウッド',0,0.0,'甘く丸い音で中域が豊か。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',19,'BrazilianRosewood','','ブラジリアンローズウッド',0,0.0,'濃厚で深いトーン、豊かな倍音。');</v>
       </c>
     </row>
     <row r="126" spans="2:11">
@@ -27534,14 +27534,14 @@
         <v>1778</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>1435</v>
+        <v>1394</v>
       </c>
       <c r="D126" s="8"/>
       <c r="E126" s="8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>1410</v>
+        <v>1453</v>
       </c>
       <c r="G126" s="9">
         <v>0</v>
@@ -27550,11 +27550,11 @@
         <v>125</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="K126" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',21,'PauFerro','','パーフェロー',0,0.0,'明るく硬質でタイトな音。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',20,'Rosewood','','ローズウッド',0,0.0,'甘く丸い音で中域が豊か。');</v>
       </c>
     </row>
     <row r="127" spans="2:11">
@@ -27562,14 +27562,14 @@
         <v>1778</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>1400</v>
+        <v>1435</v>
       </c>
       <c r="D127" s="8"/>
       <c r="E127" s="8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="G127" s="9">
         <v>0</v>
@@ -27578,11 +27578,11 @@
         <v>125</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="K127" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',22,'Ovangkol','','オバンコール',0,0.0,'中域が豊かで温かいトーン。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',21,'PauFerro','','パーフェロー',0,0.0,'明るく硬質でタイトな音。');</v>
       </c>
     </row>
     <row r="128" spans="2:11">
@@ -27590,14 +27590,14 @@
         <v>1778</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>1395</v>
+        <v>1400</v>
       </c>
       <c r="D128" s="8"/>
       <c r="E128" s="8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>1456</v>
+        <v>1411</v>
       </c>
       <c r="G128" s="9">
         <v>0</v>
@@ -27606,11 +27606,11 @@
         <v>125</v>
       </c>
       <c r="I128" s="8" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="K128" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',23,'Ebony','','エボニー',0,0.0,'硬くタイトで高域がクリア。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',22,'Ovangkol','','オバンコール',0,0.0,'中域が豊かで温かいトーン。');</v>
       </c>
     </row>
     <row r="129" spans="2:11">
@@ -27618,14 +27618,14 @@
         <v>1778</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="D129" s="8"/>
       <c r="E129" s="8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="G129" s="9">
         <v>0</v>
@@ -27634,11 +27634,11 @@
         <v>125</v>
       </c>
       <c r="I129" s="8" t="s">
-        <v>1416</v>
+        <v>1484</v>
       </c>
       <c r="K129" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',24,'Walnut','','ウォルナット',0,0.0,'中域が豊かで落ち着いたトーン。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',23,'Ebony','','エボニー',0,0.0,'硬くタイトで高域がクリア。');</v>
       </c>
     </row>
     <row r="130" spans="2:11">
@@ -27646,14 +27646,14 @@
         <v>1778</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>1436</v>
+        <v>1396</v>
       </c>
       <c r="D130" s="8"/>
       <c r="E130" s="8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="G130" s="9">
         <v>0</v>
@@ -27662,11 +27662,11 @@
         <v>125</v>
       </c>
       <c r="I130" s="8" t="s">
-        <v>1485</v>
+        <v>1416</v>
       </c>
       <c r="K130" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',25,'Padauk','','パドゥーク',0,0.0,'明るく抜けが良く、個性的な響き。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',24,'Walnut','','ウォルナット',0,0.0,'中域が豊かで落ち着いたトーン。');</v>
       </c>
     </row>
     <row r="131" spans="2:11">
@@ -27674,14 +27674,14 @@
         <v>1778</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>1401</v>
+        <v>1436</v>
       </c>
       <c r="D131" s="8"/>
       <c r="E131" s="8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="G131" s="9">
         <v>0</v>
@@ -27690,11 +27690,11 @@
         <v>125</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="K131" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',26,'Koa','','コア',0,0.0,'明るく華やかで軽快。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',25,'Padauk','','パドゥーク',0,0.0,'明るく抜けが良く、個性的な響き。');</v>
       </c>
     </row>
     <row r="132" spans="2:11">
@@ -27702,14 +27702,14 @@
         <v>1778</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="D132" s="8"/>
       <c r="E132" s="8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="G132" s="9">
         <v>0</v>
@@ -27718,11 +27718,11 @@
         <v>125</v>
       </c>
       <c r="I132" s="8" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="K132" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',27,'Nato','','ナトー',0,0.0,'中低域が豊かで温かい。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',26,'Koa','','コア',0,0.0,'明るく華やかで軽快。');</v>
       </c>
     </row>
     <row r="133" spans="2:11">
@@ -27730,14 +27730,14 @@
         <v>1778</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="D133" s="8"/>
       <c r="E133" s="8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F133" s="8" t="s">
-        <v>1412</v>
+        <v>1460</v>
       </c>
       <c r="G133" s="9">
         <v>0</v>
@@ -27746,11 +27746,11 @@
         <v>125</v>
       </c>
       <c r="I133" s="8" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="K133" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',28,'Agathis','','アガチス',0,0.0,'柔らかくウォームで素直。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',27,'Nato','','ナトー',0,0.0,'中低域が豊かで温かい。');</v>
       </c>
     </row>
     <row r="134" spans="2:11">
@@ -27758,14 +27758,14 @@
         <v>1778</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="D134" s="8"/>
       <c r="E134" s="8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F134" s="8" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="G134" s="9">
         <v>0</v>
@@ -27774,11 +27774,11 @@
         <v>125</v>
       </c>
       <c r="I134" s="8" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="K134" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',29,'Bubinga','','ブビンガ',0,0.0,'重く硬質でサスティンが長い。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',28,'Agathis','','アガチス',0,0.0,'柔らかくウォームで素直。');</v>
       </c>
     </row>
     <row r="135" spans="2:11">
@@ -27786,14 +27786,14 @@
         <v>1778</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="D135" s="8"/>
       <c r="E135" s="8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F135" s="8" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="G135" s="9">
         <v>0</v>
@@ -27802,11 +27802,11 @@
         <v>125</v>
       </c>
       <c r="I135" s="8" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="K135" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',30,'Wenge','','ウェンジ',0,0.0,'非常に硬くタイトで個性的。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',29,'Bubinga','','ブビンガ',0,0.0,'重く硬質でサスティンが長い。');</v>
       </c>
     </row>
     <row r="136" spans="2:11">
@@ -27814,14 +27814,14 @@
         <v>1778</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D136" s="8"/>
       <c r="E136" s="8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F136" s="8" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="G136" s="9">
         <v>0</v>
@@ -27830,11 +27830,11 @@
         <v>125</v>
       </c>
       <c r="I136" s="8" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="K136" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',31,'Purpleheart','','パープルハート',0,0.0,'硬く鮮やかでアタックが強い。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',30,'Wenge','','ウェンジ',0,0.0,'非常に硬くタイトで個性的。');</v>
       </c>
     </row>
     <row r="137" spans="2:11">
@@ -27842,14 +27842,14 @@
         <v>1778</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>1437</v>
+        <v>1407</v>
       </c>
       <c r="D137" s="8"/>
       <c r="E137" s="8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F137" s="8" t="s">
-        <v>1461</v>
+        <v>1415</v>
       </c>
       <c r="G137" s="9">
         <v>0</v>
@@ -27858,11 +27858,11 @@
         <v>125</v>
       </c>
       <c r="I137" s="8" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="K137" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',32,'Zebrawood','','ゼブラウッド',0,0.0,'明るく硬質でクセのあるトーン。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',31,'Purpleheart','','パープルハート',0,0.0,'硬く鮮やかでアタックが強い。');</v>
       </c>
     </row>
     <row r="138" spans="2:11">
@@ -27870,14 +27870,14 @@
         <v>1778</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>1558</v>
+        <v>1437</v>
       </c>
       <c r="D138" s="8"/>
       <c r="E138" s="8">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>1559</v>
+        <v>1461</v>
       </c>
       <c r="G138" s="9">
         <v>0</v>
@@ -27886,11 +27886,11 @@
         <v>125</v>
       </c>
       <c r="I138" s="8" t="s">
-        <v>1560</v>
+        <v>1492</v>
       </c>
       <c r="K138" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',33,'Okoume','','オクメ',0,0.0,'マホガニーに近く、中低域が豊かで軽量。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',32,'Zebrawood','','ゼブラウッド',0,0.0,'明るく硬質でクセのあるトーン。');</v>
       </c>
     </row>
     <row r="139" spans="2:11">
@@ -27898,14 +27898,14 @@
         <v>1778</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="G139" s="9">
         <v>0</v>
@@ -27914,11 +27914,11 @@
         <v>125</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="K139" s="5" t="str">
-        <f t="shared" ref="K139" si="16">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B139&amp;"'"&amp;","&amp;E139&amp;","&amp;"'"&amp;C139&amp;"'"&amp;","&amp;"'"&amp;D139&amp;"'"&amp;","&amp;"'"&amp;F139&amp;"'"&amp;","&amp;G139&amp;","&amp;H139&amp;","&amp;"'"&amp;I139&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',34,'Meranti','','メランティ',0,0.0,'中域寄りで温かめ、マホガニー系に近い。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',33,'Okoume','','オクメ',0,0.0,'マホガニーに近く、中低域が豊かで軽量。');</v>
       </c>
     </row>
     <row r="140" spans="2:11">
@@ -27926,14 +27926,14 @@
         <v>1778</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="D140" s="8"/>
       <c r="E140" s="8">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F140" s="8" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="G140" s="9">
         <v>0</v>
@@ -27942,11 +27942,11 @@
         <v>125</v>
       </c>
       <c r="I140" s="8" t="s">
-        <v>1569</v>
+        <v>1563</v>
       </c>
       <c r="K140" s="5" t="str">
         <f t="shared" ref="K140" si="17">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B140&amp;"'"&amp;","&amp;E140&amp;","&amp;"'"&amp;C140&amp;"'"&amp;","&amp;"'"&amp;D140&amp;"'"&amp;","&amp;"'"&amp;F140&amp;"'"&amp;","&amp;G140&amp;","&amp;H140&amp;","&amp;"'"&amp;I140&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',35,'Sakura','','サクラ',0,0.0,'中高域が明るく立ち上がりが速い、日本らしい軽快で抜けの良いサウンド。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',34,'Meranti','','メランティ',0,0.0,'中域寄りで温かめ、マホガニー系に近い。');</v>
       </c>
     </row>
     <row r="141" spans="2:11">
@@ -27954,14 +27954,14 @@
         <v>1778</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="D141" s="8"/>
       <c r="E141" s="8">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="G141" s="9">
         <v>0</v>
@@ -27970,11 +27970,11 @@
         <v>125</v>
       </c>
       <c r="I141" s="8" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="K141" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',36,'Tochi','','トチ',0,0.0,'メイプルに近いクリアさと華やかさを持ちつつ、やや柔らかく豊かな倍音.');</v>
+        <f t="shared" ref="K141" si="18">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B141&amp;"'"&amp;","&amp;E141&amp;","&amp;"'"&amp;C141&amp;"'"&amp;","&amp;"'"&amp;D141&amp;"'"&amp;","&amp;"'"&amp;F141&amp;"'"&amp;","&amp;G141&amp;","&amp;H141&amp;","&amp;"'"&amp;I141&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',35,'Sakura','','サクラ',0,0.0,'中高域が明るく立ち上がりが速い、日本らしい軽快で抜けの良いサウンド。');</v>
       </c>
     </row>
     <row r="142" spans="2:11">
@@ -27982,14 +27982,14 @@
         <v>1778</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>1424</v>
+        <v>1566</v>
       </c>
       <c r="D142" s="8"/>
       <c r="E142" s="8">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>1423</v>
+        <v>1567</v>
       </c>
       <c r="G142" s="9">
         <v>0</v>
@@ -27997,62 +27997,64 @@
       <c r="H142" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="I142" s="8"/>
+      <c r="I142" s="8" t="s">
+        <v>1568</v>
+      </c>
       <c r="K142" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B142&amp;"'"&amp;","&amp;E142&amp;","&amp;"'"&amp;C142&amp;"'"&amp;","&amp;"'"&amp;D142&amp;"'"&amp;","&amp;"'"&amp;F142&amp;"'"&amp;","&amp;G142&amp;","&amp;H142&amp;","&amp;"'"&amp;I142&amp;"'"&amp;");"</f>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',36,'Tochi','','トチ',0,0.0,'メイプルに近いクリアさと華やかさを持ちつつ、やや柔らかく豊かな倍音.');</v>
+      </c>
+    </row>
+    <row r="143" spans="2:11">
+      <c r="B143" s="8" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D143" s="8"/>
+      <c r="E143" s="8">
+        <v>99</v>
+      </c>
+      <c r="F143" s="8" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G143" s="9">
+        <v>0</v>
+      </c>
+      <c r="H143" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I143" s="8"/>
+      <c r="K143" s="5" t="str">
+        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B143&amp;"'"&amp;","&amp;E143&amp;","&amp;"'"&amp;C143&amp;"'"&amp;","&amp;"'"&amp;D143&amp;"'"&amp;","&amp;"'"&amp;F143&amp;"'"&amp;","&amp;G143&amp;","&amp;H143&amp;","&amp;"'"&amp;I143&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('guitar_woods',99,'Unknown','','？？',0,0.0,'');</v>
       </c>
     </row>
-    <row r="143" spans="2:11">
-      <c r="B143" s="6" t="s">
+    <row r="144" spans="2:11">
+      <c r="B144" s="6" t="s">
         <v>1503</v>
       </c>
-      <c r="C143" s="6" t="s">
+      <c r="C144" s="6" t="s">
         <v>1502</v>
       </c>
-      <c r="D143" s="6" t="s">
+      <c r="D144" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E143" s="7" t="s">
+      <c r="E144" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F143" s="6" t="s">
+      <c r="F144" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G143" s="6" t="s">
+      <c r="G144" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H143" s="6" t="s">
+      <c r="H144" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I143" s="6" t="s">
+      <c r="I144" s="6" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="144" spans="2:11">
-      <c r="B144" s="8" t="s">
-        <v>1779</v>
-      </c>
-      <c r="C144" s="8" t="s">
-        <v>1504</v>
-      </c>
-      <c r="D144" s="8"/>
-      <c r="E144" s="8">
-        <v>1</v>
-      </c>
-      <c r="F144" s="8" t="s">
-        <v>1520</v>
-      </c>
-      <c r="G144" s="9">
-        <v>0</v>
-      </c>
-      <c r="H144" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I144" s="8"/>
-      <c r="K144" s="5" t="str">
-        <f t="shared" ref="K144:K166" si="18">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B144&amp;"'"&amp;","&amp;E144&amp;","&amp;"'"&amp;C144&amp;"'"&amp;","&amp;"'"&amp;D144&amp;"'"&amp;","&amp;"'"&amp;F144&amp;"'"&amp;","&amp;G144&amp;","&amp;H144&amp;","&amp;"'"&amp;I144&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',1,'Red','','レッド',0,0.0,'');</v>
       </c>
     </row>
     <row r="145" spans="2:11">
@@ -28060,14 +28062,14 @@
         <v>1779</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>1518</v>
+        <v>1504</v>
       </c>
       <c r="D145" s="8"/>
       <c r="E145" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="G145" s="9">
         <v>0</v>
@@ -28077,8 +28079,8 @@
       </c>
       <c r="I145" s="8"/>
       <c r="K145" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',2,'Pink','','ピンク',0,0.0,'');</v>
+        <f t="shared" ref="K145:K167" si="19">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B145&amp;"'"&amp;","&amp;E145&amp;","&amp;"'"&amp;C145&amp;"'"&amp;","&amp;"'"&amp;D145&amp;"'"&amp;","&amp;"'"&amp;F145&amp;"'"&amp;","&amp;G145&amp;","&amp;H145&amp;","&amp;"'"&amp;I145&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',1,'Red','','レッド',0,0.0,'');</v>
       </c>
     </row>
     <row r="146" spans="2:11">
@@ -28086,14 +28088,14 @@
         <v>1779</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>1505</v>
+        <v>1518</v>
       </c>
       <c r="D146" s="8"/>
       <c r="E146" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F146" s="8" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="G146" s="9">
         <v>0</v>
@@ -28103,8 +28105,8 @@
       </c>
       <c r="I146" s="8"/>
       <c r="K146" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',3,'Orange','','オレンジ',0,0.0,'');</v>
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',2,'Pink','','ピンク',0,0.0,'');</v>
       </c>
     </row>
     <row r="147" spans="2:11">
@@ -28112,14 +28114,14 @@
         <v>1779</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="D147" s="8"/>
       <c r="E147" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F147" s="8" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="G147" s="9">
         <v>0</v>
@@ -28129,8 +28131,8 @@
       </c>
       <c r="I147" s="8"/>
       <c r="K147" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',4,'Yellow','','イエロー',0,0.0,'');</v>
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',3,'Orange','','オレンジ',0,0.0,'');</v>
       </c>
     </row>
     <row r="148" spans="2:11">
@@ -28138,14 +28140,14 @@
         <v>1779</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D148" s="8"/>
       <c r="E148" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F148" s="8" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="G148" s="9">
         <v>0</v>
@@ -28155,8 +28157,8 @@
       </c>
       <c r="I148" s="8"/>
       <c r="K148" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',5,'Green','','グリーン',0,0.0,'');</v>
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',4,'Yellow','','イエロー',0,0.0,'');</v>
       </c>
     </row>
     <row r="149" spans="2:11">
@@ -28164,14 +28166,14 @@
         <v>1779</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="D149" s="8"/>
       <c r="E149" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F149" s="8" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="G149" s="9">
         <v>0</v>
@@ -28181,8 +28183,8 @@
       </c>
       <c r="I149" s="8"/>
       <c r="K149" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',6,'SkyBlue','','スカイブルー',0,0.0,'');</v>
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',5,'Green','','グリーン',0,0.0,'');</v>
       </c>
     </row>
     <row r="150" spans="2:11">
@@ -28190,14 +28192,14 @@
         <v>1779</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="D150" s="8"/>
       <c r="E150" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="G150" s="9">
         <v>0</v>
@@ -28207,8 +28209,8 @@
       </c>
       <c r="I150" s="8"/>
       <c r="K150" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',7,'Blue','','ブルー',0,0.0,'');</v>
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',6,'SkyBlue','','スカイブルー',0,0.0,'');</v>
       </c>
     </row>
     <row r="151" spans="2:11">
@@ -28216,14 +28218,14 @@
         <v>1779</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="D151" s="8"/>
       <c r="E151" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="G151" s="9">
         <v>0</v>
@@ -28233,8 +28235,8 @@
       </c>
       <c r="I151" s="8"/>
       <c r="K151" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',8,'Purple','','パープル',0,0.0,'');</v>
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',7,'Blue','','ブルー',0,0.0,'');</v>
       </c>
     </row>
     <row r="152" spans="2:11">
@@ -28242,14 +28244,14 @@
         <v>1779</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="D152" s="8"/>
       <c r="E152" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F152" s="8" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="G152" s="9">
         <v>0</v>
@@ -28259,8 +28261,8 @@
       </c>
       <c r="I152" s="8"/>
       <c r="K152" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',9,'Gray','','グレー',0,0.0,'');</v>
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',8,'Purple','','パープル',0,0.0,'');</v>
       </c>
     </row>
     <row r="153" spans="2:11">
@@ -28268,14 +28270,14 @@
         <v>1779</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="D153" s="8"/>
       <c r="E153" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="G153" s="9">
         <v>0</v>
@@ -28285,8 +28287,8 @@
       </c>
       <c r="I153" s="8"/>
       <c r="K153" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',10,'Black','','ブラック',0,0.0,'');</v>
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',9,'Gray','','グレー',0,0.0,'');</v>
       </c>
     </row>
     <row r="154" spans="2:11">
@@ -28294,14 +28296,14 @@
         <v>1779</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="D154" s="8"/>
       <c r="E154" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="G154" s="9">
         <v>0</v>
@@ -28311,8 +28313,8 @@
       </c>
       <c r="I154" s="8"/>
       <c r="K154" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',11,'White','','ホワイト',0,0.0,'');</v>
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',10,'Black','','ブラック',0,0.0,'');</v>
       </c>
     </row>
     <row r="155" spans="2:11">
@@ -28320,14 +28322,14 @@
         <v>1779</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="D155" s="8"/>
       <c r="E155" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F155" s="8" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="G155" s="9">
         <v>0</v>
@@ -28337,8 +28339,8 @@
       </c>
       <c r="I155" s="8"/>
       <c r="K155" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',12,'Natural','','ナチュラル',0,0.0,'');</v>
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',11,'White','','ホワイト',0,0.0,'');</v>
       </c>
     </row>
     <row r="156" spans="2:11">
@@ -28346,14 +28348,14 @@
         <v>1779</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>1519</v>
+        <v>1514</v>
       </c>
       <c r="D156" s="8"/>
       <c r="E156" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F156" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="G156" s="9">
         <v>0</v>
@@ -28363,8 +28365,8 @@
       </c>
       <c r="I156" s="8"/>
       <c r="K156" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',13,'Brown','','ブラウン',0,0.0,'');</v>
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',12,'Natural','','ナチュラル',0,0.0,'');</v>
       </c>
     </row>
     <row r="157" spans="2:11">
@@ -28372,14 +28374,14 @@
         <v>1779</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="D157" s="8"/>
       <c r="E157" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F157" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="G157" s="9">
         <v>0</v>
@@ -28389,8 +28391,8 @@
       </c>
       <c r="I157" s="8"/>
       <c r="K157" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',14,'Gold','','ゴールド',0,0.0,'');</v>
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',13,'Brown','','ブラウン',0,0.0,'');</v>
       </c>
     </row>
     <row r="158" spans="2:11">
@@ -28398,14 +28400,14 @@
         <v>1779</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="D158" s="8"/>
       <c r="E158" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="G158" s="9">
         <v>0</v>
@@ -28415,8 +28417,8 @@
       </c>
       <c r="I158" s="8"/>
       <c r="K158" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',15,'Silver','','シルバー',0,0.0,'');</v>
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',14,'Gold','','ゴールド',0,0.0,'');</v>
       </c>
     </row>
     <row r="159" spans="2:11">
@@ -28424,14 +28426,14 @@
         <v>1779</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D159" s="8"/>
       <c r="E159" s="8">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G159" s="9">
         <v>0</v>
@@ -28441,60 +28443,60 @@
       </c>
       <c r="I159" s="8"/>
       <c r="K159" s="5" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',15,'Silver','','シルバー',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="160" spans="2:11">
+      <c r="B160" s="8" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C160" s="8" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D160" s="8"/>
+      <c r="E160" s="8">
+        <v>99</v>
+      </c>
+      <c r="F160" s="8" t="s">
+        <v>1535</v>
+      </c>
+      <c r="G160" s="9">
+        <v>0</v>
+      </c>
+      <c r="H160" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I160" s="8"/>
+      <c r="K160" s="5" t="str">
+        <f t="shared" si="19"/>
         <v>INSERT INTO m_code VALUES ('guitar_colors',99,'Others','','その他',0,0.0,'');</v>
       </c>
     </row>
-    <row r="160" spans="2:11">
-      <c r="B160" s="6" t="s">
+    <row r="161" spans="2:11">
+      <c r="B161" s="6" t="s">
         <v>1888</v>
       </c>
-      <c r="C160" s="6" t="s">
+      <c r="C161" s="6" t="s">
         <v>1889</v>
       </c>
-      <c r="D160" s="6" t="s">
+      <c r="D161" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E160" s="7" t="s">
+      <c r="E161" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F160" s="6" t="s">
+      <c r="F161" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G160" s="6" t="s">
+      <c r="G161" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H160" s="6" t="s">
+      <c r="H161" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I160" s="6" t="s">
+      <c r="I161" s="6" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="161" spans="2:11">
-      <c r="B161" s="8" t="s">
-        <v>1892</v>
-      </c>
-      <c r="C161" s="8" t="s">
-        <v>1890</v>
-      </c>
-      <c r="D161" s="8"/>
-      <c r="E161" s="8">
-        <v>1</v>
-      </c>
-      <c r="F161" s="8"/>
-      <c r="G161" s="9">
-        <v>0</v>
-      </c>
-      <c r="H161" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I161" s="8" t="s">
-        <v>1893</v>
-      </c>
-      <c r="K161" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',1,'SUCCESS','','',0,0.0,'処理成功');</v>
       </c>
     </row>
     <row r="162" spans="2:11">
@@ -28502,11 +28504,11 @@
         <v>1892</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="D162" s="8"/>
       <c r="E162" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F162" s="8"/>
       <c r="G162" s="9">
@@ -28516,11 +28518,11 @@
         <v>125</v>
       </c>
       <c r="I162" s="8" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="K162" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',2,'STARTED','','',0,0.0,'処理開始。いずかのステータスに遷移する。');</v>
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('batch_status',1,'SUCCESS','','',0,0.0,'処理成功');</v>
       </c>
     </row>
     <row r="163" spans="2:11">
@@ -28528,11 +28530,11 @@
         <v>1892</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>1881</v>
+        <v>1891</v>
       </c>
       <c r="D163" s="8"/>
       <c r="E163" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F163" s="8"/>
       <c r="G163" s="9">
@@ -28542,11 +28544,11 @@
         <v>125</v>
       </c>
       <c r="I163" s="8" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="K163" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',3,'NOT_STARTED','','',0,0.0,'予定時刻に開始されていない。');</v>
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('batch_status',2,'STARTED','','',0,0.0,'処理開始。いずかのステータスに遷移する。');</v>
       </c>
     </row>
     <row r="164" spans="2:11">
@@ -28554,11 +28556,11 @@
         <v>1892</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="D164" s="8"/>
       <c r="E164" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F164" s="8"/>
       <c r="G164" s="9">
@@ -28568,11 +28570,11 @@
         <v>125</v>
       </c>
       <c r="I164" s="8" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="K164" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',4,'ERROR','','',0,0.0,'例外、パニック等が発生した。');</v>
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('batch_status',3,'NOT_STARTED','','',0,0.0,'予定時刻に開始されていない。');</v>
       </c>
     </row>
     <row r="165" spans="2:11">
@@ -28580,11 +28582,11 @@
         <v>1892</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>1882</v>
+        <v>1879</v>
       </c>
       <c r="D165" s="8"/>
       <c r="E165" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F165" s="8"/>
       <c r="G165" s="9">
@@ -28594,11 +28596,11 @@
         <v>125</v>
       </c>
       <c r="I165" s="8" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="K165" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',5,'SLOW','','',0,0.0,'想定時間内に処理が終了しなかった。');</v>
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('batch_status',4,'ERROR','','',0,0.0,'例外、パニック等が発生した。');</v>
       </c>
     </row>
     <row r="166" spans="2:11">
@@ -28606,11 +28608,11 @@
         <v>1892</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="D166" s="8"/>
       <c r="E166" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F166" s="8"/>
       <c r="G166" s="9">
@@ -28620,10 +28622,36 @@
         <v>125</v>
       </c>
       <c r="I166" s="8" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K166" s="5" t="str">
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('batch_status',5,'SLOW','','',0,0.0,'想定時間内に処理が終了しなかった。');</v>
+      </c>
+    </row>
+    <row r="167" spans="2:11">
+      <c r="B167" s="8" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C167" s="8" t="s">
+        <v>1880</v>
+      </c>
+      <c r="D167" s="8"/>
+      <c r="E167" s="8">
+        <v>6</v>
+      </c>
+      <c r="F167" s="8"/>
+      <c r="G167" s="9">
+        <v>0</v>
+      </c>
+      <c r="H167" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I167" s="8" t="s">
         <v>1897</v>
       </c>
-      <c r="K166" s="5" t="str">
-        <f t="shared" si="18"/>
+      <c r="K167" s="5" t="str">
+        <f t="shared" si="19"/>
         <v>INSERT INTO m_code VALUES ('batch_status',6,'TIMEOUT','','',0,0.0,'時間内に処理が終了しなかった。');</v>
       </c>
     </row>
@@ -32181,7 +32209,7 @@
         <v>150</v>
       </c>
       <c r="L6" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;H6&amp;","&amp;VLOOKUP(I6,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;H6&amp;","&amp;VLOOKUP(I6,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster001','キラービー',1,110,12,16,0.3,1);</v>
       </c>
     </row>
@@ -32214,7 +32242,7 @@
         <v>150</v>
       </c>
       <c r="L7" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;H7&amp;","&amp;VLOOKUP(I7,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;H7&amp;","&amp;VLOOKUP(I7,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster002','アサシンバグ',1,132,15,20,0.3,1);</v>
       </c>
     </row>
@@ -32247,7 +32275,7 @@
         <v>150</v>
       </c>
       <c r="L8" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;H8&amp;","&amp;VLOOKUP(I8,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;H8&amp;","&amp;VLOOKUP(I8,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster003','ラスターバグ',1,158,19,26,0.3,1);</v>
       </c>
     </row>
@@ -32277,7 +32305,7 @@
         <v>34</v>
       </c>
       <c r="L9" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;H9&amp;","&amp;VLOOKUP(I9,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;H9&amp;","&amp;VLOOKUP(I9,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster004','カーミラ',2,100,10,13,0.13,2);</v>
       </c>
     </row>
@@ -32310,7 +32338,7 @@
         <v>34</v>
       </c>
       <c r="L10" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;H10&amp;","&amp;VLOOKUP(I10,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;H10&amp;","&amp;VLOOKUP(I10,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster005','カーミラクイーン',2,120,13,16,0.15,2);</v>
       </c>
     </row>
@@ -32340,7 +32368,7 @@
         <v>36</v>
       </c>
       <c r="L11" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;H11&amp;","&amp;VLOOKUP(I11,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;H11&amp;","&amp;VLOOKUP(I11,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster006','デーモン',3,130,15,7,0.08,5);</v>
       </c>
     </row>
@@ -32373,7 +32401,7 @@
         <v>36</v>
       </c>
       <c r="L12" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;H12&amp;","&amp;VLOOKUP(I12,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;H12&amp;","&amp;VLOOKUP(I12,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster007','グレートデーモン',3,156,19,9,0.1,5);</v>
       </c>
     </row>
@@ -32403,7 +32431,7 @@
         <v>35</v>
       </c>
       <c r="L13" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;H13&amp;","&amp;VLOOKUP(I13,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;H13&amp;","&amp;VLOOKUP(I13,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster008','ゴブリン',4,120,11,10,0.15,4);</v>
       </c>
     </row>
@@ -32436,7 +32464,7 @@
         <v>35</v>
       </c>
       <c r="L14" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;H14&amp;","&amp;VLOOKUP(I14,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;H14&amp;","&amp;VLOOKUP(I14,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster009','ゴブリンガード',4,144,14,13,0.15,4);</v>
       </c>
     </row>
@@ -32469,7 +32497,7 @@
         <v>35</v>
       </c>
       <c r="L15" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;H15&amp;","&amp;VLOOKUP(I15,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;H15&amp;","&amp;VLOOKUP(I15,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster010','ゴブリンロード',4,172,18,16,0.15,4);</v>
       </c>
     </row>
@@ -32499,7 +32527,7 @@
         <v>151</v>
       </c>
       <c r="L16" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;H16&amp;","&amp;VLOOKUP(I16,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;H16&amp;","&amp;VLOOKUP(I16,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster011','マシンゴーレム',5,140,17,5,0.02,3);</v>
       </c>
     </row>
@@ -32532,7 +32560,7 @@
         <v>151</v>
       </c>
       <c r="L17" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;H17&amp;","&amp;VLOOKUP(I17,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;H17&amp;","&amp;VLOOKUP(I17,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster012','ガーディアン',5,168,22,6,0.04,3);</v>
       </c>
     </row>
@@ -32565,7 +32593,7 @@
         <v>151</v>
       </c>
       <c r="L18" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;H18&amp;","&amp;VLOOKUP(I18,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;H18&amp;","&amp;VLOOKUP(I18,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster013','デスマシン',5,201,28,7,0.05,3);</v>
       </c>
     </row>
@@ -32595,7 +32623,7 @@
         <v>35</v>
       </c>
       <c r="L19" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;H19&amp;","&amp;VLOOKUP(I19,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;H19&amp;","&amp;VLOOKUP(I19,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster014','ハーピー',6,100,8,14,0.2,4);</v>
       </c>
     </row>
@@ -32628,7 +32656,7 @@
         <v>35</v>
       </c>
       <c r="L20" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;H20&amp;","&amp;VLOOKUP(I20,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;H20&amp;","&amp;VLOOKUP(I20,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster015','セイレーン',6,120,10,18,0.23,4);</v>
       </c>
     </row>
@@ -32658,7 +32686,7 @@
         <v>34</v>
       </c>
       <c r="L21" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;H21&amp;","&amp;VLOOKUP(I21,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;H21&amp;","&amp;VLOOKUP(I21,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster016','アーマーナイト',7,120,13,8,0.05,2);</v>
       </c>
     </row>
@@ -32691,7 +32719,7 @@
         <v>34</v>
       </c>
       <c r="L22" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;H22&amp;","&amp;VLOOKUP(I22,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;H22&amp;","&amp;VLOOKUP(I22,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster017','ダークナイト',7,144,16,10,0.05,2);</v>
       </c>
     </row>
@@ -32724,7 +32752,7 @@
         <v>34</v>
       </c>
       <c r="L23" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;H23&amp;","&amp;VLOOKUP(I23,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;H23&amp;","&amp;VLOOKUP(I23,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster018','ターミネータ',7,172,20,13,0.07,2);</v>
       </c>
     </row>
@@ -32754,7 +32782,7 @@
         <v>35</v>
       </c>
       <c r="L24" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;H24&amp;","&amp;VLOOKUP(I24,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;H24&amp;","&amp;VLOOKUP(I24,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster019','マジシャン',8,100,9,12,0.1,4);</v>
       </c>
     </row>
@@ -32787,7 +32815,7 @@
         <v>35</v>
       </c>
       <c r="L25" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;H25&amp;","&amp;VLOOKUP(I25,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;H25&amp;","&amp;VLOOKUP(I25,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster020','ウィザード',8,120,11,15,0.11,4);</v>
       </c>
     </row>
@@ -32820,7 +32848,7 @@
         <v>35</v>
       </c>
       <c r="L26" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;H26&amp;","&amp;VLOOKUP(I26,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;H26&amp;","&amp;VLOOKUP(I26,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster021','ハイウィザード',8,144,14,19,0.12,4);</v>
       </c>
     </row>
@@ -32850,7 +32878,7 @@
         <v>150</v>
       </c>
       <c r="L27" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;H27&amp;","&amp;VLOOKUP(I27,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;H27&amp;","&amp;VLOOKUP(I27,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster022','マイコニド',9,120,10,12,0.15,1);</v>
       </c>
     </row>
@@ -32883,7 +32911,7 @@
         <v>150</v>
       </c>
       <c r="L28" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;H28&amp;","&amp;VLOOKUP(I28,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;H28&amp;","&amp;VLOOKUP(I28,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster023','ダースマタンゴ',9,144,13,15,0.15,1);</v>
       </c>
     </row>
@@ -32913,7 +32941,7 @@
         <v>151</v>
       </c>
       <c r="L29" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;H29&amp;","&amp;VLOOKUP(I29,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;H29&amp;","&amp;VLOOKUP(I29,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster024','ニードルバード',10,100,13,16,0.25,3);</v>
       </c>
     </row>
@@ -32946,7 +32974,7 @@
         <v>151</v>
       </c>
       <c r="L30" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;H30&amp;","&amp;VLOOKUP(I30,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;H30&amp;","&amp;VLOOKUP(I30,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster025','コカトバード',10,120,16,20,0.27,3);</v>
       </c>
     </row>
@@ -32976,7 +33004,7 @@
         <v>151</v>
       </c>
       <c r="L31" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;H31&amp;","&amp;VLOOKUP(I31,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;H31&amp;","&amp;VLOOKUP(I31,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster026','プチドラゴン',11,130,13,8,0.08,3);</v>
       </c>
     </row>
@@ -33009,7 +33037,7 @@
         <v>36</v>
       </c>
       <c r="L32" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;H32&amp;","&amp;VLOOKUP(I32,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;H32&amp;","&amp;VLOOKUP(I32,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster027','プチドラゾンビ',11,156,16,10,0.1,5);</v>
       </c>
     </row>
@@ -33042,7 +33070,7 @@
         <v>150</v>
       </c>
       <c r="L33" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;H33&amp;","&amp;VLOOKUP(I33,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;H33&amp;","&amp;VLOOKUP(I33,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster028','フロストドラゴン',11,187,20,13,0.12,1);</v>
       </c>
     </row>
@@ -33075,7 +33103,7 @@
         <v>37</v>
       </c>
       <c r="L34" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;H34&amp;","&amp;VLOOKUP(I34,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;H34&amp;","&amp;VLOOKUP(I34,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster029','プチティアマット',11,224,26,16,0.13,6);</v>
       </c>
     </row>
@@ -33105,7 +33133,7 @@
         <v>37</v>
       </c>
       <c r="L35" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;H35&amp;","&amp;VLOOKUP(I35,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;H35&amp;","&amp;VLOOKUP(I35,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster030','ポト',12,100,10,16,0.18,6);</v>
       </c>
     </row>
@@ -33138,7 +33166,7 @@
         <v>37</v>
       </c>
       <c r="L36" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;H36&amp;","&amp;VLOOKUP(I36,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;H36&amp;","&amp;VLOOKUP(I36,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster031','マーマポト',12,120,13,20,0.2,6);</v>
       </c>
     </row>
@@ -33171,7 +33199,7 @@
         <v>37</v>
       </c>
       <c r="L37" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;H37&amp;","&amp;VLOOKUP(I37,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;H37&amp;","&amp;VLOOKUP(I37,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster032','パーパポト',12,141,16,26,0.22,6);</v>
       </c>
     </row>
@@ -33201,7 +33229,7 @@
         <v>37</v>
       </c>
       <c r="L38" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;H38&amp;","&amp;VLOOKUP(I38,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;H38&amp;","&amp;VLOOKUP(I38,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster033','プリースト',13,100,9,13,0.1,6);</v>
       </c>
     </row>
@@ -33234,7 +33262,7 @@
         <v>36</v>
       </c>
       <c r="L39" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;H39&amp;","&amp;VLOOKUP(I39,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;H39&amp;","&amp;VLOOKUP(I39,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster034','カオスソーサラー',13,120,11,16,0.11,5);</v>
       </c>
     </row>
@@ -33267,7 +33295,7 @@
         <v>36</v>
       </c>
       <c r="L40" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;H40&amp;","&amp;VLOOKUP(I40,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;H40&amp;","&amp;VLOOKUP(I40,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster035','イビルシャーマン',13,144,14,20,0.13,5);</v>
       </c>
     </row>
@@ -33298,7 +33326,7 @@
         <v>37</v>
       </c>
       <c r="L41" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;H41&amp;","&amp;VLOOKUP(I41,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;H41&amp;","&amp;VLOOKUP(I41,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster036','ラビ',14,100,11,16,0.16,6);</v>
       </c>
     </row>
@@ -33331,7 +33359,7 @@
         <v>37</v>
       </c>
       <c r="L42" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;H42&amp;","&amp;VLOOKUP(I42,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;H42&amp;","&amp;VLOOKUP(I42,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster037','ラビリオン',14,120,14,20,0.17,6);</v>
       </c>
     </row>
@@ -33364,7 +33392,7 @@
         <v>37</v>
       </c>
       <c r="L43" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;H43&amp;","&amp;VLOOKUP(I43,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;H43&amp;","&amp;VLOOKUP(I43,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster038','キングラビ',14,144,18,26,0.18,6);</v>
       </c>
     </row>
@@ -33397,7 +33425,7 @@
         <v>37</v>
       </c>
       <c r="L44" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;H44&amp;","&amp;VLOOKUP(I44,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;H44&amp;","&amp;VLOOKUP(I44,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster039','グレートラビ',14,172,23,33,0.2,6);</v>
       </c>
     </row>
@@ -33427,7 +33455,7 @@
         <v>34</v>
       </c>
       <c r="L45" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;H45&amp;","&amp;VLOOKUP(I45,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;H45&amp;","&amp;VLOOKUP(I45,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster040','スライム',15,100,10,18,0.15,2);</v>
       </c>
     </row>
@@ -33460,7 +33488,7 @@
         <v>150</v>
       </c>
       <c r="L46" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;H46&amp;","&amp;VLOOKUP(I46,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;H46&amp;","&amp;VLOOKUP(I46,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster041','ブルーババロア',15,120,13,23,0.15,1);</v>
       </c>
     </row>
@@ -33493,7 +33521,7 @@
         <v>151</v>
       </c>
       <c r="L47" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;H47&amp;","&amp;VLOOKUP(I47,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;H47&amp;","&amp;VLOOKUP(I47,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster042','レッドマシュマロ',15,141,16,29,0.15,3);</v>
       </c>
     </row>
@@ -33523,7 +33551,7 @@
         <v>36</v>
       </c>
       <c r="L48" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;H48&amp;","&amp;VLOOKUP(I48,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;H48&amp;","&amp;VLOOKUP(I48,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster043','イビルソード',16,110,15,13,0.14,5);</v>
       </c>
     </row>
@@ -33556,7 +33584,7 @@
         <v>36</v>
       </c>
       <c r="L49" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;H49&amp;","&amp;VLOOKUP(I49,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;H49&amp;","&amp;VLOOKUP(I49,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster044','イビルウェポン',16,132,19,16,0.15,5);</v>
       </c>
     </row>
@@ -33589,7 +33617,7 @@
         <v>37</v>
       </c>
       <c r="L50" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;H50&amp;","&amp;VLOOKUP(I50,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;H50&amp;","&amp;VLOOKUP(I50,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster045','エレメントソード',16,158,24,20,0.16,6);</v>
       </c>
     </row>
@@ -33619,7 +33647,7 @@
         <v>150</v>
       </c>
       <c r="L51" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;H51&amp;","&amp;VLOOKUP(I51,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;H51&amp;","&amp;VLOOKUP(I51,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster046','ケルベロス',17,110,11,19,0.18,1);</v>
       </c>
     </row>
@@ -33652,7 +33680,7 @@
         <v>150</v>
       </c>
       <c r="L52" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;H52&amp;","&amp;VLOOKUP(I52,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;H52&amp;","&amp;VLOOKUP(I52,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster047','バウンドウルフ',17,132,14,24,0.2,1);</v>
       </c>
     </row>
@@ -33685,7 +33713,7 @@
         <v>150</v>
       </c>
       <c r="L53" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;H53&amp;","&amp;VLOOKUP(I53,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;H53&amp;","&amp;VLOOKUP(I53,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster048','ジャッカル',17,158,18,31,0.21,1);</v>
       </c>
     </row>
@@ -33715,7 +33743,7 @@
         <v>151</v>
       </c>
       <c r="L54" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;H54&amp;","&amp;VLOOKUP(I54,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;H54&amp;","&amp;VLOOKUP(I54,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster049','ダックソルジャー',18,120,16,14,0.15,3);</v>
       </c>
     </row>
@@ -33745,7 +33773,7 @@
         <v>151</v>
       </c>
       <c r="L55" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;H55&amp;","&amp;VLOOKUP(I55,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;H55&amp;","&amp;VLOOKUP(I55,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster050','ダックジェネラル',18,160,24,20,0.15,3);</v>
       </c>
     </row>
@@ -33775,7 +33803,7 @@
         <v>34</v>
       </c>
       <c r="L56" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;H56&amp;","&amp;VLOOKUP(I56,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;H56&amp;","&amp;VLOOKUP(I56,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster051','モールベア',19,130,14,18,0.18,2);</v>
       </c>
     </row>
@@ -33805,7 +33833,7 @@
         <v>34</v>
       </c>
       <c r="L57" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;H57&amp;","&amp;VLOOKUP(I57,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;H57&amp;","&amp;VLOOKUP(I57,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster052','ニードリオン',19,170,18,26,0.2,2);</v>
       </c>
     </row>
@@ -33835,7 +33863,7 @@
         <v>35</v>
       </c>
       <c r="L58" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;H58&amp;","&amp;VLOOKUP(I58,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;H58&amp;","&amp;VLOOKUP(I58,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster053','ギャルビー',20,120,13,16,0.2,4);</v>
       </c>
     </row>
@@ -33868,7 +33896,7 @@
         <v>35</v>
       </c>
       <c r="L59" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;H59&amp;","&amp;VLOOKUP(I59,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;H59&amp;","&amp;VLOOKUP(I59,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster054','レディビー',20,144,16,20,0.22,4);</v>
       </c>
     </row>
@@ -33901,7 +33929,7 @@
         <v>35</v>
       </c>
       <c r="L60" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;H60&amp;","&amp;VLOOKUP(I60,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;H60&amp;","&amp;VLOOKUP(I60,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster055','クインビー',20,172,20,26,0.23,4);</v>
       </c>
     </row>
@@ -33931,7 +33959,7 @@
         <v>150</v>
       </c>
       <c r="L61" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;H61&amp;","&amp;VLOOKUP(I61,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;H61&amp;","&amp;VLOOKUP(I61,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster056','サハギン',21,130,16,16,0.15,1);</v>
       </c>
     </row>
@@ -33961,7 +33989,7 @@
         <v>150</v>
       </c>
       <c r="L62" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;H62&amp;","&amp;VLOOKUP(I62,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;H62&amp;","&amp;VLOOKUP(I62,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster057','プチポセイドン',21,150,22,19,0.15,1);</v>
       </c>
     </row>
@@ -33991,7 +34019,7 @@
         <v>298</v>
       </c>
       <c r="L63" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;H63&amp;","&amp;VLOOKUP(I63,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;H63&amp;","&amp;VLOOKUP(I63,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster058','クロウラー',22,130,15,11,0.08,2);</v>
       </c>
     </row>
@@ -34024,7 +34052,7 @@
         <v>34</v>
       </c>
       <c r="L64" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;H64&amp;","&amp;VLOOKUP(I64,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;H64&amp;","&amp;VLOOKUP(I64,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster059','メガクロウラー',22,156,19,14,0.09,2);</v>
       </c>
     </row>
@@ -34057,7 +34085,7 @@
         <v>34</v>
       </c>
       <c r="L65" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;H65&amp;","&amp;VLOOKUP(I65,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;H65&amp;","&amp;VLOOKUP(I65,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster060','ギガクロウラー',22,187,24,18,0.1,2);</v>
       </c>
     </row>
@@ -34087,7 +34115,7 @@
         <v>34</v>
       </c>
       <c r="L66" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;H66&amp;","&amp;VLOOKUP(I66,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;H66&amp;","&amp;VLOOKUP(I66,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster061','ぱっくんオタマ',23,110,12,10,0.15,2);</v>
       </c>
     </row>
@@ -34120,7 +34148,7 @@
         <v>34</v>
       </c>
       <c r="L67" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;H67&amp;","&amp;VLOOKUP(I67,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;H67&amp;","&amp;VLOOKUP(I67,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster062','ぱっくりオタマ',23,132,15,13,0.15,2);</v>
       </c>
     </row>
@@ -34153,7 +34181,7 @@
         <v>151</v>
       </c>
       <c r="L68" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;H68&amp;","&amp;VLOOKUP(I68,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;H68&amp;","&amp;VLOOKUP(I68,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster063','ぱっくんトカゲ',23,158,19,16,0.1,3);</v>
       </c>
     </row>
@@ -34186,7 +34214,7 @@
         <v>151</v>
       </c>
       <c r="L69" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;H69&amp;","&amp;VLOOKUP(I69,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;H69&amp;","&amp;VLOOKUP(I69,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster064','ぱっくんドラゴン',23,189,24,20,0.11,3);</v>
       </c>
     </row>
@@ -34216,7 +34244,7 @@
         <v>36</v>
       </c>
       <c r="L70" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;H70&amp;","&amp;VLOOKUP(I70,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;H70&amp;","&amp;VLOOKUP(I70,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster065','チビデビル',24,120,13,17,0.22,5);</v>
       </c>
     </row>
@@ -34246,7 +34274,7 @@
         <v>36</v>
       </c>
       <c r="L71" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;H71&amp;","&amp;VLOOKUP(I71,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;H71&amp;","&amp;VLOOKUP(I71,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster066','グレムリン',24,160,18,20,0.24,5);</v>
       </c>
     </row>
@@ -34276,7 +34304,7 @@
         <v>36</v>
       </c>
       <c r="L72" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;H72&amp;","&amp;VLOOKUP(I72,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;H72&amp;","&amp;VLOOKUP(I72,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster067','オーガボックス',25,140,18,17,0.15,5);</v>
       </c>
     </row>
@@ -34306,7 +34334,7 @@
         <v>36</v>
       </c>
       <c r="L73" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;H73&amp;","&amp;VLOOKUP(I73,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;H73&amp;","&amp;VLOOKUP(I73,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster068','カイザーミミック',25,170,23,20,0.15,5);</v>
       </c>
     </row>
@@ -34336,7 +34364,7 @@
         <v>151</v>
       </c>
       <c r="L74" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;H74&amp;","&amp;VLOOKUP(I74,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;H74&amp;","&amp;VLOOKUP(I74,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster069','バレッテ',26,140,15,12,0.05,3);</v>
       </c>
     </row>
@@ -34366,7 +34394,7 @@
         <v>151</v>
       </c>
       <c r="L75" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;H75&amp;","&amp;VLOOKUP(I75,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;H75&amp;","&amp;VLOOKUP(I75,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster070','ゴールドバレッテ',26,180,19,14,0.05,3);</v>
       </c>
     </row>
@@ -34396,7 +34424,7 @@
         <v>34</v>
       </c>
       <c r="L76" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;H76&amp;","&amp;VLOOKUP(I76,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;H76&amp;","&amp;VLOOKUP(I76,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster071','バシリスク',27,110,12,15,0.15,2);</v>
       </c>
     </row>
@@ -34426,7 +34454,7 @@
         <v>151</v>
       </c>
       <c r="L77" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;H77&amp;","&amp;VLOOKUP(I77,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;H77&amp;","&amp;VLOOKUP(I77,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster072','ファイアドレイク',27,150,18,22,0.18,3);</v>
       </c>
     </row>
@@ -34456,7 +34484,7 @@
         <v>36</v>
       </c>
       <c r="L78" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;H78&amp;","&amp;VLOOKUP(I78,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;H78&amp;","&amp;VLOOKUP(I78,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster073','スペクター',28,130,13,17,0.2,5);</v>
       </c>
     </row>
@@ -34486,7 +34514,7 @@
         <v>36</v>
       </c>
       <c r="L79" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;H79&amp;","&amp;VLOOKUP(I79,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;H79&amp;","&amp;VLOOKUP(I79,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster074','ゴースト',28,160,17,20,0.21,5);</v>
       </c>
     </row>
@@ -34516,7 +34544,7 @@
         <v>37</v>
       </c>
       <c r="L80" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;","&amp;VLOOKUP(I80,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;","&amp;VLOOKUP(I80,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster075','ユニコーンヘッド',29,120,15,14,0.15,6);</v>
       </c>
     </row>
@@ -34546,7 +34574,7 @@
         <v>37</v>
       </c>
       <c r="L81" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;H81&amp;","&amp;VLOOKUP(I81,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;H81&amp;","&amp;VLOOKUP(I81,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster076','ゴールドユニコ',29,170,22,25,0.15,6);</v>
       </c>
     </row>
@@ -34576,7 +34604,7 @@
         <v>36</v>
       </c>
       <c r="L82" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;H82&amp;","&amp;VLOOKUP(I82,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;H82&amp;","&amp;VLOOKUP(I82,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster077','シェイプシフター',30,130,12,14,0.14,5);</v>
       </c>
     </row>
@@ -34608,7 +34636,7 @@
         <v>36</v>
       </c>
       <c r="L83" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;H83&amp;","&amp;VLOOKUP(I83,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;H83&amp;","&amp;VLOOKUP(I83,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster078','シャドウゼロ',30,170,15,18,0.15,5);</v>
       </c>
     </row>
@@ -34640,7 +34668,7 @@
         <v>36</v>
       </c>
       <c r="L84" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;H84&amp;","&amp;VLOOKUP(I84,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;H84&amp;","&amp;VLOOKUP(I84,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster079','シャドウゼロワン',30,190,19,23,0.16,5);</v>
       </c>
     </row>
@@ -34670,7 +34698,7 @@
         <v>36</v>
       </c>
       <c r="L85" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;H85&amp;","&amp;VLOOKUP(I85,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;H85&amp;","&amp;VLOOKUP(I85,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster080','ボルダー',31,120,13,14,0.25,5);</v>
       </c>
     </row>
@@ -34703,7 +34731,7 @@
         <v>36</v>
       </c>
       <c r="L86" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;H86&amp;","&amp;VLOOKUP(I86,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;H86&amp;","&amp;VLOOKUP(I86,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster081','パワーボルダー',31,144,16,18,0.25,5);</v>
       </c>
     </row>
@@ -34736,7 +34764,7 @@
         <v>36</v>
       </c>
       <c r="L87" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;H87&amp;","&amp;VLOOKUP(I87,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;H87&amp;","&amp;VLOOKUP(I87,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster082','デスボルダー',31,172,20,23,0.25,5);</v>
       </c>
     </row>
@@ -34766,7 +34794,7 @@
         <v>151</v>
       </c>
       <c r="L88" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;H88&amp;","&amp;VLOOKUP(I88,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;H88&amp;","&amp;VLOOKUP(I88,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster083','パンプキンボム',32,130,17,12,0.18,3);</v>
       </c>
     </row>
@@ -34796,7 +34824,7 @@
         <v>151</v>
       </c>
       <c r="L89" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$48:$I$106,3,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;H89&amp;","&amp;VLOOKUP(I89,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;H89&amp;","&amp;VLOOKUP(I89,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster084','グレネードボム',32,160,24,15,0.2,3);</v>
       </c>
     </row>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F434E750-A8DB-40A2-82D5-C6E4750875FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0006DF47-37FF-4D17-B0AE-0331CC729D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="3" activeTab="3" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4643" uniqueCount="2371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4647" uniqueCount="2373">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -9948,6 +9948,14 @@
   </si>
   <si>
     <t>Fernandes</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>MAYONES</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://mayones.com/</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -24278,7 +24286,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
-  <dimension ref="B4:K167"/>
+  <dimension ref="B4:K168"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -26891,7 +26899,7 @@
         <v>1551</v>
       </c>
       <c r="K102" s="5" t="str">
-        <f t="shared" ref="K102:K105" si="14">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B102&amp;"'"&amp;","&amp;E102&amp;","&amp;"'"&amp;C102&amp;"'"&amp;","&amp;"'"&amp;D102&amp;"'"&amp;","&amp;"'"&amp;F102&amp;"'"&amp;","&amp;G102&amp;","&amp;H102&amp;","&amp;"'"&amp;I102&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K102:K106" si="14">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B102&amp;"'"&amp;","&amp;E102&amp;","&amp;"'"&amp;C102&amp;"'"&amp;","&amp;"'"&amp;D102&amp;"'"&amp;","&amp;"'"&amp;F102&amp;"'"&amp;","&amp;G102&amp;","&amp;H102&amp;","&amp;"'"&amp;I102&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('guitar_makers',10,'MusicMan','','',0,0.0,'https://www.music-man.com/instruments/guitars');</v>
       </c>
     </row>
@@ -26943,7 +26951,7 @@
         <v>1553</v>
       </c>
       <c r="K104" s="5" t="str">
-        <f t="shared" ref="K104" si="15">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B104&amp;"'"&amp;","&amp;E104&amp;","&amp;"'"&amp;C104&amp;"'"&amp;","&amp;"'"&amp;D104&amp;"'"&amp;","&amp;"'"&amp;F104&amp;"'"&amp;","&amp;G104&amp;","&amp;H104&amp;","&amp;"'"&amp;I104&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K104:K105" si="15">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B104&amp;"'"&amp;","&amp;E104&amp;","&amp;"'"&amp;C104&amp;"'"&amp;","&amp;"'"&amp;D104&amp;"'"&amp;","&amp;"'"&amp;F104&amp;"'"&amp;","&amp;G104&amp;","&amp;H104&amp;","&amp;"'"&amp;I104&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('guitar_makers',12,'Momose','','',0,0.0,'https://www.deviser.co.jp/momose');</v>
       </c>
     </row>
@@ -26967,62 +26975,60 @@
       </c>
       <c r="I105" s="8"/>
       <c r="K105" s="5" t="str">
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('guitar_makers',13,'Fernandes','','',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="106" spans="2:11">
+      <c r="B106" s="8" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>2371</v>
+      </c>
+      <c r="D106" s="8"/>
+      <c r="E106" s="8">
+        <v>14</v>
+      </c>
+      <c r="F106" s="8"/>
+      <c r="G106" s="9">
+        <v>0</v>
+      </c>
+      <c r="H106" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I106" s="8" t="s">
+        <v>2372</v>
+      </c>
+      <c r="K106" s="5" t="str">
         <f t="shared" si="14"/>
-        <v>INSERT INTO m_code VALUES ('guitar_makers',13,'Fernandes','','',0,0.0,'');</v>
-      </c>
-    </row>
-    <row r="106" spans="2:11">
-      <c r="B106" s="6" t="s">
+        <v>INSERT INTO m_code VALUES ('guitar_makers',14,'MAYONES','','',0,0.0,'https://mayones.com/');</v>
+      </c>
+    </row>
+    <row r="107" spans="2:11">
+      <c r="B107" s="6" t="s">
         <v>1542</v>
       </c>
-      <c r="C106" s="6" t="s">
+      <c r="C107" s="6" t="s">
         <v>1388</v>
       </c>
-      <c r="D106" s="6" t="s">
+      <c r="D107" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E106" s="7" t="s">
+      <c r="E107" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F106" s="6" t="s">
+      <c r="F107" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G106" s="6" t="s">
+      <c r="G107" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H106" s="6" t="s">
+      <c r="H107" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I106" s="6" t="s">
+      <c r="I107" s="6" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="107" spans="2:11">
-      <c r="B107" s="8" t="s">
-        <v>1778</v>
-      </c>
-      <c r="C107" s="8" t="s">
-        <v>1425</v>
-      </c>
-      <c r="D107" s="8"/>
-      <c r="E107" s="8">
-        <v>1</v>
-      </c>
-      <c r="F107" s="8" t="s">
-        <v>1439</v>
-      </c>
-      <c r="G107" s="9">
-        <v>0</v>
-      </c>
-      <c r="H107" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I107" s="8" t="s">
-        <v>1463</v>
-      </c>
-      <c r="K107" s="5" t="str">
-        <f t="shared" ref="K107:K142" si="16">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B107&amp;"'"&amp;","&amp;E107&amp;","&amp;"'"&amp;C107&amp;"'"&amp;","&amp;"'"&amp;D107&amp;"'"&amp;","&amp;"'"&amp;F107&amp;"'"&amp;","&amp;G107&amp;","&amp;H107&amp;","&amp;"'"&amp;I107&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',1,'HardMaple','','ハードメイプル',0,0.0,'硬質でタイト、明瞭なアタック。');</v>
       </c>
     </row>
     <row r="108" spans="2:11">
@@ -27030,14 +27036,14 @@
         <v>1778</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="D108" s="8"/>
       <c r="E108" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G108" s="9">
         <v>0</v>
@@ -27046,11 +27052,11 @@
         <v>125</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="K108" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',2,'FlameMaple','','フレイムメイプル',0,0.0,'明るく抜けが良く、華やかな倍音。');</v>
+        <f t="shared" ref="K108:K143" si="16">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B108&amp;"'"&amp;","&amp;E108&amp;","&amp;"'"&amp;C108&amp;"'"&amp;","&amp;"'"&amp;D108&amp;"'"&amp;","&amp;"'"&amp;F108&amp;"'"&amp;","&amp;G108&amp;","&amp;H108&amp;","&amp;"'"&amp;I108&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',1,'HardMaple','','ハードメイプル',0,0.0,'硬質でタイト、明瞭なアタック。');</v>
       </c>
     </row>
     <row r="109" spans="2:11">
@@ -27058,14 +27064,14 @@
         <v>1778</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="D109" s="8"/>
       <c r="E109" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="G109" s="9">
         <v>0</v>
@@ -27074,11 +27080,11 @@
         <v>125</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="K109" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',3,'QuiltedMaple','','キルテッドメイプル',0,0.0,'立体的で広がりがあり、煌びやかな響き。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',2,'FlameMaple','','フレイムメイプル',0,0.0,'明るく抜けが良く、華やかな倍音。');</v>
       </c>
     </row>
     <row r="110" spans="2:11">
@@ -27086,14 +27092,14 @@
         <v>1778</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="D110" s="8"/>
       <c r="E110" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="G110" s="9">
         <v>0</v>
@@ -27102,11 +27108,11 @@
         <v>125</v>
       </c>
       <c r="I110" s="8" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="K110" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',4,'BirdseyeMaple','','バーズアイメイプル',0,0.0,'粒立ちが良く、明るくシャープ。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',3,'QuiltedMaple','','キルテッドメイプル',0,0.0,'立体的で広がりがあり、煌びやかな響き。');</v>
       </c>
     </row>
     <row r="111" spans="2:11">
@@ -27114,14 +27120,14 @@
         <v>1778</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="D111" s="8"/>
       <c r="E111" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="G111" s="9">
         <v>0</v>
@@ -27130,11 +27136,11 @@
         <v>125</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="K111" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',5,'RoastedMaple','','ローステッドメイプル',0,0.0,'引き締まったタイトな音で反応が速い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',4,'BirdseyeMaple','','バーズアイメイプル',0,0.0,'粒立ちが良く、明るくシャープ。');</v>
       </c>
     </row>
     <row r="112" spans="2:11">
@@ -27142,14 +27148,14 @@
         <v>1778</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>1389</v>
+        <v>1429</v>
       </c>
       <c r="D112" s="8"/>
       <c r="E112" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>1438</v>
+        <v>1443</v>
       </c>
       <c r="G112" s="9">
         <v>0</v>
@@ -27158,11 +27164,11 @@
         <v>125</v>
       </c>
       <c r="I112" s="8" t="s">
-        <v>1462</v>
+        <v>1467</v>
       </c>
       <c r="K112" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',6,'Maple','','メイプル',0,0.0,'明るくハリがあり、アタックが強い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',5,'RoastedMaple','','ローステッドメイプル',0,0.0,'引き締まったタイトな音で反応が速い。');</v>
       </c>
     </row>
     <row r="113" spans="2:11">
@@ -27170,14 +27176,14 @@
         <v>1778</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>1430</v>
+        <v>1389</v>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>1444</v>
+        <v>1438</v>
       </c>
       <c r="G113" s="9">
         <v>0</v>
@@ -27186,11 +27192,11 @@
         <v>125</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>1469</v>
+        <v>1462</v>
       </c>
       <c r="K113" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',7,'HonduranMahogany','','ホンジュラスマホガニー',0,0.0,'深みがあり、太くリッチな中低域。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',6,'Maple','','メイプル',0,0.0,'明るくハリがあり、アタックが強い。');</v>
       </c>
     </row>
     <row r="114" spans="2:11">
@@ -27198,14 +27204,14 @@
         <v>1778</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>1390</v>
+        <v>1430</v>
       </c>
       <c r="D114" s="8"/>
       <c r="E114" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>1408</v>
+        <v>1444</v>
       </c>
       <c r="G114" s="9">
         <v>0</v>
@@ -27214,11 +27220,11 @@
         <v>125</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="K114" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',8,'Mahogany','','マホガニー',0,0.0,'中低域が豊かで温かい音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',7,'HonduranMahogany','','ホンジュラスマホガニー',0,0.0,'深みがあり、太くリッチな中低域。');</v>
       </c>
     </row>
     <row r="115" spans="2:11">
@@ -27226,14 +27232,14 @@
         <v>1778</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>1431</v>
+        <v>1390</v>
       </c>
       <c r="D115" s="8"/>
       <c r="E115" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>1445</v>
+        <v>1408</v>
       </c>
       <c r="G115" s="9">
         <v>0</v>
@@ -27242,11 +27248,11 @@
         <v>125</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="K115" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',9,'Sapele','','サペリ',0,0.0,'温かく柔らかいトーンでバランスが良い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',8,'Mahogany','','マホガニー',0,0.0,'中低域が豊かで温かい音。');</v>
       </c>
     </row>
     <row r="116" spans="2:11">
@@ -27254,14 +27260,14 @@
         <v>1778</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>1397</v>
+        <v>1431</v>
       </c>
       <c r="D116" s="8"/>
       <c r="E116" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="G116" s="9">
         <v>0</v>
@@ -27270,11 +27276,11 @@
         <v>125</v>
       </c>
       <c r="I116" s="8" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="K116" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',10,'Korina','','コリーナ',0,0.0,'中域が豊かで太い音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',9,'Sapele','','サペリ',0,0.0,'温かく柔らかいトーンでバランスが良い。');</v>
       </c>
     </row>
     <row r="117" spans="2:11">
@@ -27282,14 +27288,14 @@
         <v>1778</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>1432</v>
+        <v>1397</v>
       </c>
       <c r="D117" s="8"/>
       <c r="E117" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="G117" s="9">
         <v>0</v>
@@ -27298,11 +27304,11 @@
         <v>125</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="K117" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',11,'WhiteKorina','','ホワイトコリーナ',0,0.0,'明るく抜けが良く、軽快なレスポンス。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',10,'Korina','','コリーナ',0,0.0,'中域が豊かで太い音。');</v>
       </c>
     </row>
     <row r="118" spans="2:11">
@@ -27310,14 +27316,14 @@
         <v>1778</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>1391</v>
+        <v>1432</v>
       </c>
       <c r="D118" s="8"/>
       <c r="E118" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>1409</v>
+        <v>1447</v>
       </c>
       <c r="G118" s="9">
         <v>0</v>
@@ -27326,11 +27332,11 @@
         <v>125</v>
       </c>
       <c r="I118" s="8" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="K118" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',12,'Alder','','アルダー',0,0.0,'バランスが良くクセが少ない。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',11,'WhiteKorina','','ホワイトコリーナ',0,0.0,'明るく抜けが良く、軽快なレスポンス。');</v>
       </c>
     </row>
     <row r="119" spans="2:11">
@@ -27338,14 +27344,14 @@
         <v>1778</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="D119" s="8"/>
       <c r="E119" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>1448</v>
+        <v>1409</v>
       </c>
       <c r="G119" s="9">
         <v>0</v>
@@ -27354,11 +27360,11 @@
         <v>125</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="K119" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',13,'Ash','','アッシュ',0,0.0,'明るく抜ける音でアタックが強い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',12,'Alder','','アルダー',0,0.0,'バランスが良くクセが少ない。');</v>
       </c>
     </row>
     <row r="120" spans="2:11">
@@ -27366,14 +27372,14 @@
         <v>1778</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="D120" s="8"/>
       <c r="E120" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="G120" s="9">
         <v>0</v>
@@ -27382,11 +27388,11 @@
         <v>125</v>
       </c>
       <c r="I120" s="8" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="K120" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',14,'Basswood','','バスウッド',0,0.0,'軽く柔らかく、ウォームで扱いやすい。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',13,'Ash','','アッシュ',0,0.0,'明るく抜ける音でアタックが強い。');</v>
       </c>
     </row>
     <row r="121" spans="2:11">
@@ -27394,14 +27400,14 @@
         <v>1778</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>1402</v>
+        <v>1393</v>
       </c>
       <c r="D121" s="8"/>
       <c r="E121" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="G121" s="9">
         <v>0</v>
@@ -27410,11 +27416,11 @@
         <v>125</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="K121" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',15,'Poplar','','ポプラ',0,0.0,'軽く素直でクセが少ない。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',14,'Basswood','','バスウッド',0,0.0,'軽く柔らかく、ウォームで扱いやすい。');</v>
       </c>
     </row>
     <row r="122" spans="2:11">
@@ -27422,14 +27428,14 @@
         <v>1778</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="D122" s="8"/>
       <c r="E122" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="G122" s="9">
         <v>0</v>
@@ -27438,11 +27444,11 @@
         <v>125</v>
       </c>
       <c r="I122" s="8" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="K122" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',16,'Spruce','','スプルース',0,0.0,'軽く響きが良く、明るいトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',15,'Poplar','','ポプラ',0,0.0,'軽く素直でクセが少ない。');</v>
       </c>
     </row>
     <row r="123" spans="2:11">
@@ -27450,14 +27456,14 @@
         <v>1778</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="D123" s="8"/>
       <c r="E123" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="G123" s="9">
         <v>0</v>
@@ -27466,11 +27472,11 @@
         <v>125</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="K123" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',17,'Cedar','','シダー',0,0.0,'柔らかく温かい音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',16,'Spruce','','スプルース',0,0.0,'軽く響きが良く、明るいトーン。');</v>
       </c>
     </row>
     <row r="124" spans="2:11">
@@ -27478,14 +27484,14 @@
         <v>1778</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>1433</v>
+        <v>1399</v>
       </c>
       <c r="D124" s="8"/>
       <c r="E124" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F124" s="8" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="G124" s="9">
         <v>0</v>
@@ -27494,11 +27500,11 @@
         <v>125</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="K124" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',18,'IndianRosewood','','インディアンローズウッド',0,0.0,'甘く深みがあり、豊かな中低域。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',17,'Cedar','','シダー',0,0.0,'柔らかく温かい音。');</v>
       </c>
     </row>
     <row r="125" spans="2:11">
@@ -27506,14 +27512,14 @@
         <v>1778</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="D125" s="8"/>
       <c r="E125" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="G125" s="9">
         <v>0</v>
@@ -27522,11 +27528,11 @@
         <v>125</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="K125" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',19,'BrazilianRosewood','','ブラジリアンローズウッド',0,0.0,'濃厚で深いトーン、豊かな倍音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',18,'IndianRosewood','','インディアンローズウッド',0,0.0,'甘く深みがあり、豊かな中低域。');</v>
       </c>
     </row>
     <row r="126" spans="2:11">
@@ -27534,14 +27540,14 @@
         <v>1778</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>1394</v>
+        <v>1434</v>
       </c>
       <c r="D126" s="8"/>
       <c r="E126" s="8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="G126" s="9">
         <v>0</v>
@@ -27550,11 +27556,11 @@
         <v>125</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="K126" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',20,'Rosewood','','ローズウッド',0,0.0,'甘く丸い音で中域が豊か。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',19,'BrazilianRosewood','','ブラジリアンローズウッド',0,0.0,'濃厚で深いトーン、豊かな倍音。');</v>
       </c>
     </row>
     <row r="127" spans="2:11">
@@ -27562,14 +27568,14 @@
         <v>1778</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>1435</v>
+        <v>1394</v>
       </c>
       <c r="D127" s="8"/>
       <c r="E127" s="8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>1410</v>
+        <v>1453</v>
       </c>
       <c r="G127" s="9">
         <v>0</v>
@@ -27578,11 +27584,11 @@
         <v>125</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="K127" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',21,'PauFerro','','パーフェロー',0,0.0,'明るく硬質でタイトな音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',20,'Rosewood','','ローズウッド',0,0.0,'甘く丸い音で中域が豊か。');</v>
       </c>
     </row>
     <row r="128" spans="2:11">
@@ -27590,14 +27596,14 @@
         <v>1778</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>1400</v>
+        <v>1435</v>
       </c>
       <c r="D128" s="8"/>
       <c r="E128" s="8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="G128" s="9">
         <v>0</v>
@@ -27606,11 +27612,11 @@
         <v>125</v>
       </c>
       <c r="I128" s="8" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="K128" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',22,'Ovangkol','','オバンコール',0,0.0,'中域が豊かで温かいトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',21,'PauFerro','','パーフェロー',0,0.0,'明るく硬質でタイトな音。');</v>
       </c>
     </row>
     <row r="129" spans="2:11">
@@ -27618,14 +27624,14 @@
         <v>1778</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>1395</v>
+        <v>1400</v>
       </c>
       <c r="D129" s="8"/>
       <c r="E129" s="8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>1456</v>
+        <v>1411</v>
       </c>
       <c r="G129" s="9">
         <v>0</v>
@@ -27634,11 +27640,11 @@
         <v>125</v>
       </c>
       <c r="I129" s="8" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="K129" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',23,'Ebony','','エボニー',0,0.0,'硬くタイトで高域がクリア。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',22,'Ovangkol','','オバンコール',0,0.0,'中域が豊かで温かいトーン。');</v>
       </c>
     </row>
     <row r="130" spans="2:11">
@@ -27646,14 +27652,14 @@
         <v>1778</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="D130" s="8"/>
       <c r="E130" s="8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="G130" s="9">
         <v>0</v>
@@ -27662,11 +27668,11 @@
         <v>125</v>
       </c>
       <c r="I130" s="8" t="s">
-        <v>1416</v>
+        <v>1484</v>
       </c>
       <c r="K130" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',24,'Walnut','','ウォルナット',0,0.0,'中域が豊かで落ち着いたトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',23,'Ebony','','エボニー',0,0.0,'硬くタイトで高域がクリア。');</v>
       </c>
     </row>
     <row r="131" spans="2:11">
@@ -27674,14 +27680,14 @@
         <v>1778</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>1436</v>
+        <v>1396</v>
       </c>
       <c r="D131" s="8"/>
       <c r="E131" s="8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="G131" s="9">
         <v>0</v>
@@ -27690,11 +27696,11 @@
         <v>125</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>1485</v>
+        <v>1416</v>
       </c>
       <c r="K131" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',25,'Padauk','','パドゥーク',0,0.0,'明るく抜けが良く、個性的な響き。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',24,'Walnut','','ウォルナット',0,0.0,'中域が豊かで落ち着いたトーン。');</v>
       </c>
     </row>
     <row r="132" spans="2:11">
@@ -27702,14 +27708,14 @@
         <v>1778</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>1401</v>
+        <v>1436</v>
       </c>
       <c r="D132" s="8"/>
       <c r="E132" s="8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="G132" s="9">
         <v>0</v>
@@ -27718,11 +27724,11 @@
         <v>125</v>
       </c>
       <c r="I132" s="8" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="K132" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',26,'Koa','','コア',0,0.0,'明るく華やかで軽快。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',25,'Padauk','','パドゥーク',0,0.0,'明るく抜けが良く、個性的な響き。');</v>
       </c>
     </row>
     <row r="133" spans="2:11">
@@ -27730,14 +27736,14 @@
         <v>1778</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="D133" s="8"/>
       <c r="E133" s="8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F133" s="8" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="G133" s="9">
         <v>0</v>
@@ -27746,11 +27752,11 @@
         <v>125</v>
       </c>
       <c r="I133" s="8" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="K133" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',27,'Nato','','ナトー',0,0.0,'中低域が豊かで温かい。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',26,'Koa','','コア',0,0.0,'明るく華やかで軽快。');</v>
       </c>
     </row>
     <row r="134" spans="2:11">
@@ -27758,14 +27764,14 @@
         <v>1778</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="D134" s="8"/>
       <c r="E134" s="8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F134" s="8" t="s">
-        <v>1412</v>
+        <v>1460</v>
       </c>
       <c r="G134" s="9">
         <v>0</v>
@@ -27774,11 +27780,11 @@
         <v>125</v>
       </c>
       <c r="I134" s="8" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="K134" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',28,'Agathis','','アガチス',0,0.0,'柔らかくウォームで素直。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',27,'Nato','','ナトー',0,0.0,'中低域が豊かで温かい。');</v>
       </c>
     </row>
     <row r="135" spans="2:11">
@@ -27786,14 +27792,14 @@
         <v>1778</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="D135" s="8"/>
       <c r="E135" s="8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F135" s="8" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="G135" s="9">
         <v>0</v>
@@ -27802,11 +27808,11 @@
         <v>125</v>
       </c>
       <c r="I135" s="8" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="K135" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',29,'Bubinga','','ブビンガ',0,0.0,'重く硬質でサスティンが長い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',28,'Agathis','','アガチス',0,0.0,'柔らかくウォームで素直。');</v>
       </c>
     </row>
     <row r="136" spans="2:11">
@@ -27814,14 +27820,14 @@
         <v>1778</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="D136" s="8"/>
       <c r="E136" s="8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F136" s="8" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="G136" s="9">
         <v>0</v>
@@ -27830,11 +27836,11 @@
         <v>125</v>
       </c>
       <c r="I136" s="8" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="K136" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',30,'Wenge','','ウェンジ',0,0.0,'非常に硬くタイトで個性的。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',29,'Bubinga','','ブビンガ',0,0.0,'重く硬質でサスティンが長い。');</v>
       </c>
     </row>
     <row r="137" spans="2:11">
@@ -27842,14 +27848,14 @@
         <v>1778</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D137" s="8"/>
       <c r="E137" s="8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F137" s="8" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="G137" s="9">
         <v>0</v>
@@ -27858,11 +27864,11 @@
         <v>125</v>
       </c>
       <c r="I137" s="8" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="K137" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',31,'Purpleheart','','パープルハート',0,0.0,'硬く鮮やかでアタックが強い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',30,'Wenge','','ウェンジ',0,0.0,'非常に硬くタイトで個性的。');</v>
       </c>
     </row>
     <row r="138" spans="2:11">
@@ -27870,14 +27876,14 @@
         <v>1778</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>1437</v>
+        <v>1407</v>
       </c>
       <c r="D138" s="8"/>
       <c r="E138" s="8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>1461</v>
+        <v>1415</v>
       </c>
       <c r="G138" s="9">
         <v>0</v>
@@ -27886,11 +27892,11 @@
         <v>125</v>
       </c>
       <c r="I138" s="8" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="K138" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',32,'Zebrawood','','ゼブラウッド',0,0.0,'明るく硬質でクセのあるトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',31,'Purpleheart','','パープルハート',0,0.0,'硬く鮮やかでアタックが強い。');</v>
       </c>
     </row>
     <row r="139" spans="2:11">
@@ -27898,14 +27904,14 @@
         <v>1778</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>1558</v>
+        <v>1437</v>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>1559</v>
+        <v>1461</v>
       </c>
       <c r="G139" s="9">
         <v>0</v>
@@ -27914,11 +27920,11 @@
         <v>125</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>1560</v>
+        <v>1492</v>
       </c>
       <c r="K139" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',33,'Okoume','','オクメ',0,0.0,'マホガニーに近く、中低域が豊かで軽量。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',32,'Zebrawood','','ゼブラウッド',0,0.0,'明るく硬質でクセのあるトーン。');</v>
       </c>
     </row>
     <row r="140" spans="2:11">
@@ -27926,14 +27932,14 @@
         <v>1778</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="D140" s="8"/>
       <c r="E140" s="8">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F140" s="8" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="G140" s="9">
         <v>0</v>
@@ -27942,11 +27948,11 @@
         <v>125</v>
       </c>
       <c r="I140" s="8" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="K140" s="5" t="str">
-        <f t="shared" ref="K140" si="17">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B140&amp;"'"&amp;","&amp;E140&amp;","&amp;"'"&amp;C140&amp;"'"&amp;","&amp;"'"&amp;D140&amp;"'"&amp;","&amp;"'"&amp;F140&amp;"'"&amp;","&amp;G140&amp;","&amp;H140&amp;","&amp;"'"&amp;I140&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',34,'Meranti','','メランティ',0,0.0,'中域寄りで温かめ、マホガニー系に近い。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',33,'Okoume','','オクメ',0,0.0,'マホガニーに近く、中低域が豊かで軽量。');</v>
       </c>
     </row>
     <row r="141" spans="2:11">
@@ -27954,14 +27960,14 @@
         <v>1778</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="D141" s="8"/>
       <c r="E141" s="8">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="G141" s="9">
         <v>0</v>
@@ -27970,11 +27976,11 @@
         <v>125</v>
       </c>
       <c r="I141" s="8" t="s">
-        <v>1569</v>
+        <v>1563</v>
       </c>
       <c r="K141" s="5" t="str">
-        <f t="shared" ref="K141" si="18">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B141&amp;"'"&amp;","&amp;E141&amp;","&amp;"'"&amp;C141&amp;"'"&amp;","&amp;"'"&amp;D141&amp;"'"&amp;","&amp;"'"&amp;F141&amp;"'"&amp;","&amp;G141&amp;","&amp;H141&amp;","&amp;"'"&amp;I141&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',35,'Sakura','','サクラ',0,0.0,'中高域が明るく立ち上がりが速い、日本らしい軽快で抜けの良いサウンド。');</v>
+        <f t="shared" ref="K141" si="17">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B141&amp;"'"&amp;","&amp;E141&amp;","&amp;"'"&amp;C141&amp;"'"&amp;","&amp;"'"&amp;D141&amp;"'"&amp;","&amp;"'"&amp;F141&amp;"'"&amp;","&amp;G141&amp;","&amp;H141&amp;","&amp;"'"&amp;I141&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',34,'Meranti','','メランティ',0,0.0,'中域寄りで温かめ、マホガニー系に近い。');</v>
       </c>
     </row>
     <row r="142" spans="2:11">
@@ -27982,14 +27988,14 @@
         <v>1778</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="D142" s="8"/>
       <c r="E142" s="8">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="G142" s="9">
         <v>0</v>
@@ -27998,11 +28004,11 @@
         <v>125</v>
       </c>
       <c r="I142" s="8" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="K142" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',36,'Tochi','','トチ',0,0.0,'メイプルに近いクリアさと華やかさを持ちつつ、やや柔らかく豊かな倍音.');</v>
+        <f t="shared" ref="K142" si="18">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B142&amp;"'"&amp;","&amp;E142&amp;","&amp;"'"&amp;C142&amp;"'"&amp;","&amp;"'"&amp;D142&amp;"'"&amp;","&amp;"'"&amp;F142&amp;"'"&amp;","&amp;G142&amp;","&amp;H142&amp;","&amp;"'"&amp;I142&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',35,'Sakura','','サクラ',0,0.0,'中高域が明るく立ち上がりが速い、日本らしい軽快で抜けの良いサウンド。');</v>
       </c>
     </row>
     <row r="143" spans="2:11">
@@ -28010,14 +28016,14 @@
         <v>1778</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>1424</v>
+        <v>1566</v>
       </c>
       <c r="D143" s="8"/>
       <c r="E143" s="8">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="F143" s="8" t="s">
-        <v>1423</v>
+        <v>1567</v>
       </c>
       <c r="G143" s="9">
         <v>0</v>
@@ -28025,62 +28031,64 @@
       <c r="H143" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="I143" s="8"/>
+      <c r="I143" s="8" t="s">
+        <v>1568</v>
+      </c>
       <c r="K143" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B143&amp;"'"&amp;","&amp;E143&amp;","&amp;"'"&amp;C143&amp;"'"&amp;","&amp;"'"&amp;D143&amp;"'"&amp;","&amp;"'"&amp;F143&amp;"'"&amp;","&amp;G143&amp;","&amp;H143&amp;","&amp;"'"&amp;I143&amp;"'"&amp;");"</f>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',36,'Tochi','','トチ',0,0.0,'メイプルに近いクリアさと華やかさを持ちつつ、やや柔らかく豊かな倍音.');</v>
+      </c>
+    </row>
+    <row r="144" spans="2:11">
+      <c r="B144" s="8" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D144" s="8"/>
+      <c r="E144" s="8">
+        <v>99</v>
+      </c>
+      <c r="F144" s="8" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G144" s="9">
+        <v>0</v>
+      </c>
+      <c r="H144" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I144" s="8"/>
+      <c r="K144" s="5" t="str">
+        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B144&amp;"'"&amp;","&amp;E144&amp;","&amp;"'"&amp;C144&amp;"'"&amp;","&amp;"'"&amp;D144&amp;"'"&amp;","&amp;"'"&amp;F144&amp;"'"&amp;","&amp;G144&amp;","&amp;H144&amp;","&amp;"'"&amp;I144&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('guitar_woods',99,'Unknown','','？？',0,0.0,'');</v>
       </c>
     </row>
-    <row r="144" spans="2:11">
-      <c r="B144" s="6" t="s">
+    <row r="145" spans="2:11">
+      <c r="B145" s="6" t="s">
         <v>1503</v>
       </c>
-      <c r="C144" s="6" t="s">
+      <c r="C145" s="6" t="s">
         <v>1502</v>
       </c>
-      <c r="D144" s="6" t="s">
+      <c r="D145" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E144" s="7" t="s">
+      <c r="E145" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F144" s="6" t="s">
+      <c r="F145" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G144" s="6" t="s">
+      <c r="G145" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H144" s="6" t="s">
+      <c r="H145" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I144" s="6" t="s">
+      <c r="I145" s="6" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="145" spans="2:11">
-      <c r="B145" s="8" t="s">
-        <v>1779</v>
-      </c>
-      <c r="C145" s="8" t="s">
-        <v>1504</v>
-      </c>
-      <c r="D145" s="8"/>
-      <c r="E145" s="8">
-        <v>1</v>
-      </c>
-      <c r="F145" s="8" t="s">
-        <v>1520</v>
-      </c>
-      <c r="G145" s="9">
-        <v>0</v>
-      </c>
-      <c r="H145" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I145" s="8"/>
-      <c r="K145" s="5" t="str">
-        <f t="shared" ref="K145:K167" si="19">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B145&amp;"'"&amp;","&amp;E145&amp;","&amp;"'"&amp;C145&amp;"'"&amp;","&amp;"'"&amp;D145&amp;"'"&amp;","&amp;"'"&amp;F145&amp;"'"&amp;","&amp;G145&amp;","&amp;H145&amp;","&amp;"'"&amp;I145&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',1,'Red','','レッド',0,0.0,'');</v>
       </c>
     </row>
     <row r="146" spans="2:11">
@@ -28088,14 +28096,14 @@
         <v>1779</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>1518</v>
+        <v>1504</v>
       </c>
       <c r="D146" s="8"/>
       <c r="E146" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F146" s="8" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="G146" s="9">
         <v>0</v>
@@ -28105,8 +28113,8 @@
       </c>
       <c r="I146" s="8"/>
       <c r="K146" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',2,'Pink','','ピンク',0,0.0,'');</v>
+        <f t="shared" ref="K146:K168" si="19">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B146&amp;"'"&amp;","&amp;E146&amp;","&amp;"'"&amp;C146&amp;"'"&amp;","&amp;"'"&amp;D146&amp;"'"&amp;","&amp;"'"&amp;F146&amp;"'"&amp;","&amp;G146&amp;","&amp;H146&amp;","&amp;"'"&amp;I146&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',1,'Red','','レッド',0,0.0,'');</v>
       </c>
     </row>
     <row r="147" spans="2:11">
@@ -28114,14 +28122,14 @@
         <v>1779</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>1505</v>
+        <v>1518</v>
       </c>
       <c r="D147" s="8"/>
       <c r="E147" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F147" s="8" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="G147" s="9">
         <v>0</v>
@@ -28132,7 +28140,7 @@
       <c r="I147" s="8"/>
       <c r="K147" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',3,'Orange','','オレンジ',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',2,'Pink','','ピンク',0,0.0,'');</v>
       </c>
     </row>
     <row r="148" spans="2:11">
@@ -28140,14 +28148,14 @@
         <v>1779</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="D148" s="8"/>
       <c r="E148" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F148" s="8" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="G148" s="9">
         <v>0</v>
@@ -28158,7 +28166,7 @@
       <c r="I148" s="8"/>
       <c r="K148" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',4,'Yellow','','イエロー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',3,'Orange','','オレンジ',0,0.0,'');</v>
       </c>
     </row>
     <row r="149" spans="2:11">
@@ -28166,14 +28174,14 @@
         <v>1779</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D149" s="8"/>
       <c r="E149" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F149" s="8" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="G149" s="9">
         <v>0</v>
@@ -28184,7 +28192,7 @@
       <c r="I149" s="8"/>
       <c r="K149" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',5,'Green','','グリーン',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',4,'Yellow','','イエロー',0,0.0,'');</v>
       </c>
     </row>
     <row r="150" spans="2:11">
@@ -28192,14 +28200,14 @@
         <v>1779</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="D150" s="8"/>
       <c r="E150" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="G150" s="9">
         <v>0</v>
@@ -28210,7 +28218,7 @@
       <c r="I150" s="8"/>
       <c r="K150" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',6,'SkyBlue','','スカイブルー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',5,'Green','','グリーン',0,0.0,'');</v>
       </c>
     </row>
     <row r="151" spans="2:11">
@@ -28218,14 +28226,14 @@
         <v>1779</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="D151" s="8"/>
       <c r="E151" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="G151" s="9">
         <v>0</v>
@@ -28236,7 +28244,7 @@
       <c r="I151" s="8"/>
       <c r="K151" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',7,'Blue','','ブルー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',6,'SkyBlue','','スカイブルー',0,0.0,'');</v>
       </c>
     </row>
     <row r="152" spans="2:11">
@@ -28244,14 +28252,14 @@
         <v>1779</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="D152" s="8"/>
       <c r="E152" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F152" s="8" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="G152" s="9">
         <v>0</v>
@@ -28262,7 +28270,7 @@
       <c r="I152" s="8"/>
       <c r="K152" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',8,'Purple','','パープル',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',7,'Blue','','ブルー',0,0.0,'');</v>
       </c>
     </row>
     <row r="153" spans="2:11">
@@ -28270,14 +28278,14 @@
         <v>1779</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="D153" s="8"/>
       <c r="E153" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="G153" s="9">
         <v>0</v>
@@ -28288,7 +28296,7 @@
       <c r="I153" s="8"/>
       <c r="K153" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',9,'Gray','','グレー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',8,'Purple','','パープル',0,0.0,'');</v>
       </c>
     </row>
     <row r="154" spans="2:11">
@@ -28296,14 +28304,14 @@
         <v>1779</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="D154" s="8"/>
       <c r="E154" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="G154" s="9">
         <v>0</v>
@@ -28314,7 +28322,7 @@
       <c r="I154" s="8"/>
       <c r="K154" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',10,'Black','','ブラック',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',9,'Gray','','グレー',0,0.0,'');</v>
       </c>
     </row>
     <row r="155" spans="2:11">
@@ -28322,14 +28330,14 @@
         <v>1779</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="D155" s="8"/>
       <c r="E155" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F155" s="8" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="G155" s="9">
         <v>0</v>
@@ -28340,7 +28348,7 @@
       <c r="I155" s="8"/>
       <c r="K155" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',11,'White','','ホワイト',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',10,'Black','','ブラック',0,0.0,'');</v>
       </c>
     </row>
     <row r="156" spans="2:11">
@@ -28348,14 +28356,14 @@
         <v>1779</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="D156" s="8"/>
       <c r="E156" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F156" s="8" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="G156" s="9">
         <v>0</v>
@@ -28366,7 +28374,7 @@
       <c r="I156" s="8"/>
       <c r="K156" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',12,'Natural','','ナチュラル',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',11,'White','','ホワイト',0,0.0,'');</v>
       </c>
     </row>
     <row r="157" spans="2:11">
@@ -28374,14 +28382,14 @@
         <v>1779</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>1519</v>
+        <v>1514</v>
       </c>
       <c r="D157" s="8"/>
       <c r="E157" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F157" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="G157" s="9">
         <v>0</v>
@@ -28392,7 +28400,7 @@
       <c r="I157" s="8"/>
       <c r="K157" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',13,'Brown','','ブラウン',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',12,'Natural','','ナチュラル',0,0.0,'');</v>
       </c>
     </row>
     <row r="158" spans="2:11">
@@ -28400,14 +28408,14 @@
         <v>1779</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="D158" s="8"/>
       <c r="E158" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="G158" s="9">
         <v>0</v>
@@ -28418,7 +28426,7 @@
       <c r="I158" s="8"/>
       <c r="K158" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',14,'Gold','','ゴールド',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',13,'Brown','','ブラウン',0,0.0,'');</v>
       </c>
     </row>
     <row r="159" spans="2:11">
@@ -28426,14 +28434,14 @@
         <v>1779</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="D159" s="8"/>
       <c r="E159" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="G159" s="9">
         <v>0</v>
@@ -28444,7 +28452,7 @@
       <c r="I159" s="8"/>
       <c r="K159" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',15,'Silver','','シルバー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',14,'Gold','','ゴールド',0,0.0,'');</v>
       </c>
     </row>
     <row r="160" spans="2:11">
@@ -28452,14 +28460,14 @@
         <v>1779</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D160" s="8"/>
       <c r="E160" s="8">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="F160" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G160" s="9">
         <v>0</v>
@@ -28470,59 +28478,59 @@
       <c r="I160" s="8"/>
       <c r="K160" s="5" t="str">
         <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',15,'Silver','','シルバー',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="161" spans="2:11">
+      <c r="B161" s="8" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C161" s="8" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D161" s="8"/>
+      <c r="E161" s="8">
+        <v>99</v>
+      </c>
+      <c r="F161" s="8" t="s">
+        <v>1535</v>
+      </c>
+      <c r="G161" s="9">
+        <v>0</v>
+      </c>
+      <c r="H161" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I161" s="8"/>
+      <c r="K161" s="5" t="str">
+        <f t="shared" si="19"/>
         <v>INSERT INTO m_code VALUES ('guitar_colors',99,'Others','','その他',0,0.0,'');</v>
       </c>
     </row>
-    <row r="161" spans="2:11">
-      <c r="B161" s="6" t="s">
+    <row r="162" spans="2:11">
+      <c r="B162" s="6" t="s">
         <v>1888</v>
       </c>
-      <c r="C161" s="6" t="s">
+      <c r="C162" s="6" t="s">
         <v>1889</v>
       </c>
-      <c r="D161" s="6" t="s">
+      <c r="D162" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E161" s="7" t="s">
+      <c r="E162" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F161" s="6" t="s">
+      <c r="F162" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G161" s="6" t="s">
+      <c r="G162" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H161" s="6" t="s">
+      <c r="H162" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I161" s="6" t="s">
+      <c r="I162" s="6" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="162" spans="2:11">
-      <c r="B162" s="8" t="s">
-        <v>1892</v>
-      </c>
-      <c r="C162" s="8" t="s">
-        <v>1890</v>
-      </c>
-      <c r="D162" s="8"/>
-      <c r="E162" s="8">
-        <v>1</v>
-      </c>
-      <c r="F162" s="8"/>
-      <c r="G162" s="9">
-        <v>0</v>
-      </c>
-      <c r="H162" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I162" s="8" t="s">
-        <v>1893</v>
-      </c>
-      <c r="K162" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',1,'SUCCESS','','',0,0.0,'処理成功');</v>
       </c>
     </row>
     <row r="163" spans="2:11">
@@ -28530,11 +28538,11 @@
         <v>1892</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="D163" s="8"/>
       <c r="E163" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F163" s="8"/>
       <c r="G163" s="9">
@@ -28544,11 +28552,11 @@
         <v>125</v>
       </c>
       <c r="I163" s="8" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="K163" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',2,'STARTED','','',0,0.0,'処理開始。いずかのステータスに遷移する。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',1,'SUCCESS','','',0,0.0,'処理成功');</v>
       </c>
     </row>
     <row r="164" spans="2:11">
@@ -28556,11 +28564,11 @@
         <v>1892</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>1881</v>
+        <v>1891</v>
       </c>
       <c r="D164" s="8"/>
       <c r="E164" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F164" s="8"/>
       <c r="G164" s="9">
@@ -28570,11 +28578,11 @@
         <v>125</v>
       </c>
       <c r="I164" s="8" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="K164" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',3,'NOT_STARTED','','',0,0.0,'予定時刻に開始されていない。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',2,'STARTED','','',0,0.0,'処理開始。いずかのステータスに遷移する。');</v>
       </c>
     </row>
     <row r="165" spans="2:11">
@@ -28582,11 +28590,11 @@
         <v>1892</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="D165" s="8"/>
       <c r="E165" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F165" s="8"/>
       <c r="G165" s="9">
@@ -28596,11 +28604,11 @@
         <v>125</v>
       </c>
       <c r="I165" s="8" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="K165" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',4,'ERROR','','',0,0.0,'例外、パニック等が発生した。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',3,'NOT_STARTED','','',0,0.0,'予定時刻に開始されていない。');</v>
       </c>
     </row>
     <row r="166" spans="2:11">
@@ -28608,11 +28616,11 @@
         <v>1892</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>1882</v>
+        <v>1879</v>
       </c>
       <c r="D166" s="8"/>
       <c r="E166" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F166" s="8"/>
       <c r="G166" s="9">
@@ -28622,11 +28630,11 @@
         <v>125</v>
       </c>
       <c r="I166" s="8" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="K166" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',5,'SLOW','','',0,0.0,'想定時間内に処理が終了しなかった。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',4,'ERROR','','',0,0.0,'例外、パニック等が発生した。');</v>
       </c>
     </row>
     <row r="167" spans="2:11">
@@ -28634,11 +28642,11 @@
         <v>1892</v>
       </c>
       <c r="C167" s="8" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="D167" s="8"/>
       <c r="E167" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F167" s="8"/>
       <c r="G167" s="9">
@@ -28648,9 +28656,35 @@
         <v>125</v>
       </c>
       <c r="I167" s="8" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K167" s="5" t="str">
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('batch_status',5,'SLOW','','',0,0.0,'想定時間内に処理が終了しなかった。');</v>
+      </c>
+    </row>
+    <row r="168" spans="2:11">
+      <c r="B168" s="8" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C168" s="8" t="s">
+        <v>1880</v>
+      </c>
+      <c r="D168" s="8"/>
+      <c r="E168" s="8">
+        <v>6</v>
+      </c>
+      <c r="F168" s="8"/>
+      <c r="G168" s="9">
+        <v>0</v>
+      </c>
+      <c r="H168" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I168" s="8" t="s">
         <v>1897</v>
       </c>
-      <c r="K167" s="5" t="str">
+      <c r="K168" s="5" t="str">
         <f t="shared" si="19"/>
         <v>INSERT INTO m_code VALUES ('batch_status',6,'TIMEOUT','','',0,0.0,'時間内に処理が終了しなかった。');</v>
       </c>
@@ -32209,7 +32243,7 @@
         <v>150</v>
       </c>
       <c r="L6" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;H6&amp;","&amp;VLOOKUP(I6,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;H6&amp;","&amp;VLOOKUP(I6,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster001','キラービー',1,110,12,16,0.3,1);</v>
       </c>
     </row>
@@ -32242,7 +32276,7 @@
         <v>150</v>
       </c>
       <c r="L7" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;H7&amp;","&amp;VLOOKUP(I7,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;H7&amp;","&amp;VLOOKUP(I7,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster002','アサシンバグ',1,132,15,20,0.3,1);</v>
       </c>
     </row>
@@ -32275,7 +32309,7 @@
         <v>150</v>
       </c>
       <c r="L8" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;H8&amp;","&amp;VLOOKUP(I8,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;H8&amp;","&amp;VLOOKUP(I8,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster003','ラスターバグ',1,158,19,26,0.3,1);</v>
       </c>
     </row>
@@ -32305,7 +32339,7 @@
         <v>34</v>
       </c>
       <c r="L9" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;H9&amp;","&amp;VLOOKUP(I9,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;H9&amp;","&amp;VLOOKUP(I9,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster004','カーミラ',2,100,10,13,0.13,2);</v>
       </c>
     </row>
@@ -32338,7 +32372,7 @@
         <v>34</v>
       </c>
       <c r="L10" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;H10&amp;","&amp;VLOOKUP(I10,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;H10&amp;","&amp;VLOOKUP(I10,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster005','カーミラクイーン',2,120,13,16,0.15,2);</v>
       </c>
     </row>
@@ -32368,7 +32402,7 @@
         <v>36</v>
       </c>
       <c r="L11" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;H11&amp;","&amp;VLOOKUP(I11,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;H11&amp;","&amp;VLOOKUP(I11,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster006','デーモン',3,130,15,7,0.08,5);</v>
       </c>
     </row>
@@ -32401,7 +32435,7 @@
         <v>36</v>
       </c>
       <c r="L12" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;H12&amp;","&amp;VLOOKUP(I12,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;H12&amp;","&amp;VLOOKUP(I12,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster007','グレートデーモン',3,156,19,9,0.1,5);</v>
       </c>
     </row>
@@ -32431,7 +32465,7 @@
         <v>35</v>
       </c>
       <c r="L13" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;H13&amp;","&amp;VLOOKUP(I13,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;H13&amp;","&amp;VLOOKUP(I13,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster008','ゴブリン',4,120,11,10,0.15,4);</v>
       </c>
     </row>
@@ -32464,7 +32498,7 @@
         <v>35</v>
       </c>
       <c r="L14" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;H14&amp;","&amp;VLOOKUP(I14,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;H14&amp;","&amp;VLOOKUP(I14,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster009','ゴブリンガード',4,144,14,13,0.15,4);</v>
       </c>
     </row>
@@ -32497,7 +32531,7 @@
         <v>35</v>
       </c>
       <c r="L15" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;H15&amp;","&amp;VLOOKUP(I15,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;H15&amp;","&amp;VLOOKUP(I15,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster010','ゴブリンロード',4,172,18,16,0.15,4);</v>
       </c>
     </row>
@@ -32527,7 +32561,7 @@
         <v>151</v>
       </c>
       <c r="L16" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;H16&amp;","&amp;VLOOKUP(I16,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;H16&amp;","&amp;VLOOKUP(I16,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster011','マシンゴーレム',5,140,17,5,0.02,3);</v>
       </c>
     </row>
@@ -32560,7 +32594,7 @@
         <v>151</v>
       </c>
       <c r="L17" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;H17&amp;","&amp;VLOOKUP(I17,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;H17&amp;","&amp;VLOOKUP(I17,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster012','ガーディアン',5,168,22,6,0.04,3);</v>
       </c>
     </row>
@@ -32593,7 +32627,7 @@
         <v>151</v>
       </c>
       <c r="L18" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;H18&amp;","&amp;VLOOKUP(I18,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;H18&amp;","&amp;VLOOKUP(I18,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster013','デスマシン',5,201,28,7,0.05,3);</v>
       </c>
     </row>
@@ -32623,7 +32657,7 @@
         <v>35</v>
       </c>
       <c r="L19" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;H19&amp;","&amp;VLOOKUP(I19,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;H19&amp;","&amp;VLOOKUP(I19,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster014','ハーピー',6,100,8,14,0.2,4);</v>
       </c>
     </row>
@@ -32656,7 +32690,7 @@
         <v>35</v>
       </c>
       <c r="L20" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;H20&amp;","&amp;VLOOKUP(I20,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;H20&amp;","&amp;VLOOKUP(I20,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster015','セイレーン',6,120,10,18,0.23,4);</v>
       </c>
     </row>
@@ -32686,7 +32720,7 @@
         <v>34</v>
       </c>
       <c r="L21" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;H21&amp;","&amp;VLOOKUP(I21,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;H21&amp;","&amp;VLOOKUP(I21,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster016','アーマーナイト',7,120,13,8,0.05,2);</v>
       </c>
     </row>
@@ -32719,7 +32753,7 @@
         <v>34</v>
       </c>
       <c r="L22" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;H22&amp;","&amp;VLOOKUP(I22,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;H22&amp;","&amp;VLOOKUP(I22,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster017','ダークナイト',7,144,16,10,0.05,2);</v>
       </c>
     </row>
@@ -32752,7 +32786,7 @@
         <v>34</v>
       </c>
       <c r="L23" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;H23&amp;","&amp;VLOOKUP(I23,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;H23&amp;","&amp;VLOOKUP(I23,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster018','ターミネータ',7,172,20,13,0.07,2);</v>
       </c>
     </row>
@@ -32782,7 +32816,7 @@
         <v>35</v>
       </c>
       <c r="L24" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;H24&amp;","&amp;VLOOKUP(I24,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;H24&amp;","&amp;VLOOKUP(I24,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster019','マジシャン',8,100,9,12,0.1,4);</v>
       </c>
     </row>
@@ -32815,7 +32849,7 @@
         <v>35</v>
       </c>
       <c r="L25" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;H25&amp;","&amp;VLOOKUP(I25,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;H25&amp;","&amp;VLOOKUP(I25,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster020','ウィザード',8,120,11,15,0.11,4);</v>
       </c>
     </row>
@@ -32848,7 +32882,7 @@
         <v>35</v>
       </c>
       <c r="L26" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;H26&amp;","&amp;VLOOKUP(I26,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;H26&amp;","&amp;VLOOKUP(I26,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster021','ハイウィザード',8,144,14,19,0.12,4);</v>
       </c>
     </row>
@@ -32878,7 +32912,7 @@
         <v>150</v>
       </c>
       <c r="L27" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;H27&amp;","&amp;VLOOKUP(I27,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;H27&amp;","&amp;VLOOKUP(I27,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster022','マイコニド',9,120,10,12,0.15,1);</v>
       </c>
     </row>
@@ -32911,7 +32945,7 @@
         <v>150</v>
       </c>
       <c r="L28" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;H28&amp;","&amp;VLOOKUP(I28,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;H28&amp;","&amp;VLOOKUP(I28,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster023','ダースマタンゴ',9,144,13,15,0.15,1);</v>
       </c>
     </row>
@@ -32941,7 +32975,7 @@
         <v>151</v>
       </c>
       <c r="L29" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;H29&amp;","&amp;VLOOKUP(I29,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;H29&amp;","&amp;VLOOKUP(I29,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster024','ニードルバード',10,100,13,16,0.25,3);</v>
       </c>
     </row>
@@ -32974,7 +33008,7 @@
         <v>151</v>
       </c>
       <c r="L30" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;H30&amp;","&amp;VLOOKUP(I30,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;H30&amp;","&amp;VLOOKUP(I30,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster025','コカトバード',10,120,16,20,0.27,3);</v>
       </c>
     </row>
@@ -33004,7 +33038,7 @@
         <v>151</v>
       </c>
       <c r="L31" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;H31&amp;","&amp;VLOOKUP(I31,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;H31&amp;","&amp;VLOOKUP(I31,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster026','プチドラゴン',11,130,13,8,0.08,3);</v>
       </c>
     </row>
@@ -33037,7 +33071,7 @@
         <v>36</v>
       </c>
       <c r="L32" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;H32&amp;","&amp;VLOOKUP(I32,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;H32&amp;","&amp;VLOOKUP(I32,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster027','プチドラゾンビ',11,156,16,10,0.1,5);</v>
       </c>
     </row>
@@ -33070,7 +33104,7 @@
         <v>150</v>
       </c>
       <c r="L33" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;H33&amp;","&amp;VLOOKUP(I33,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;H33&amp;","&amp;VLOOKUP(I33,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster028','フロストドラゴン',11,187,20,13,0.12,1);</v>
       </c>
     </row>
@@ -33103,7 +33137,7 @@
         <v>37</v>
       </c>
       <c r="L34" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;H34&amp;","&amp;VLOOKUP(I34,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;H34&amp;","&amp;VLOOKUP(I34,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster029','プチティアマット',11,224,26,16,0.13,6);</v>
       </c>
     </row>
@@ -33133,7 +33167,7 @@
         <v>37</v>
       </c>
       <c r="L35" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;H35&amp;","&amp;VLOOKUP(I35,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;H35&amp;","&amp;VLOOKUP(I35,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster030','ポト',12,100,10,16,0.18,6);</v>
       </c>
     </row>
@@ -33166,7 +33200,7 @@
         <v>37</v>
       </c>
       <c r="L36" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;H36&amp;","&amp;VLOOKUP(I36,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;H36&amp;","&amp;VLOOKUP(I36,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster031','マーマポト',12,120,13,20,0.2,6);</v>
       </c>
     </row>
@@ -33199,7 +33233,7 @@
         <v>37</v>
       </c>
       <c r="L37" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;H37&amp;","&amp;VLOOKUP(I37,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;H37&amp;","&amp;VLOOKUP(I37,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster032','パーパポト',12,141,16,26,0.22,6);</v>
       </c>
     </row>
@@ -33229,7 +33263,7 @@
         <v>37</v>
       </c>
       <c r="L38" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;H38&amp;","&amp;VLOOKUP(I38,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;H38&amp;","&amp;VLOOKUP(I38,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster033','プリースト',13,100,9,13,0.1,6);</v>
       </c>
     </row>
@@ -33262,7 +33296,7 @@
         <v>36</v>
       </c>
       <c r="L39" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;H39&amp;","&amp;VLOOKUP(I39,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;H39&amp;","&amp;VLOOKUP(I39,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster034','カオスソーサラー',13,120,11,16,0.11,5);</v>
       </c>
     </row>
@@ -33295,7 +33329,7 @@
         <v>36</v>
       </c>
       <c r="L40" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;H40&amp;","&amp;VLOOKUP(I40,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;H40&amp;","&amp;VLOOKUP(I40,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster035','イビルシャーマン',13,144,14,20,0.13,5);</v>
       </c>
     </row>
@@ -33326,7 +33360,7 @@
         <v>37</v>
       </c>
       <c r="L41" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;H41&amp;","&amp;VLOOKUP(I41,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;H41&amp;","&amp;VLOOKUP(I41,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster036','ラビ',14,100,11,16,0.16,6);</v>
       </c>
     </row>
@@ -33359,7 +33393,7 @@
         <v>37</v>
       </c>
       <c r="L42" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;H42&amp;","&amp;VLOOKUP(I42,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;H42&amp;","&amp;VLOOKUP(I42,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster037','ラビリオン',14,120,14,20,0.17,6);</v>
       </c>
     </row>
@@ -33392,7 +33426,7 @@
         <v>37</v>
       </c>
       <c r="L43" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;H43&amp;","&amp;VLOOKUP(I43,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;H43&amp;","&amp;VLOOKUP(I43,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster038','キングラビ',14,144,18,26,0.18,6);</v>
       </c>
     </row>
@@ -33425,7 +33459,7 @@
         <v>37</v>
       </c>
       <c r="L44" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;H44&amp;","&amp;VLOOKUP(I44,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;H44&amp;","&amp;VLOOKUP(I44,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster039','グレートラビ',14,172,23,33,0.2,6);</v>
       </c>
     </row>
@@ -33455,7 +33489,7 @@
         <v>34</v>
       </c>
       <c r="L45" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;H45&amp;","&amp;VLOOKUP(I45,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;H45&amp;","&amp;VLOOKUP(I45,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster040','スライム',15,100,10,18,0.15,2);</v>
       </c>
     </row>
@@ -33488,7 +33522,7 @@
         <v>150</v>
       </c>
       <c r="L46" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;H46&amp;","&amp;VLOOKUP(I46,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;H46&amp;","&amp;VLOOKUP(I46,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster041','ブルーババロア',15,120,13,23,0.15,1);</v>
       </c>
     </row>
@@ -33521,7 +33555,7 @@
         <v>151</v>
       </c>
       <c r="L47" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;H47&amp;","&amp;VLOOKUP(I47,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;H47&amp;","&amp;VLOOKUP(I47,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster042','レッドマシュマロ',15,141,16,29,0.15,3);</v>
       </c>
     </row>
@@ -33551,7 +33585,7 @@
         <v>36</v>
       </c>
       <c r="L48" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;H48&amp;","&amp;VLOOKUP(I48,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;H48&amp;","&amp;VLOOKUP(I48,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster043','イビルソード',16,110,15,13,0.14,5);</v>
       </c>
     </row>
@@ -33584,7 +33618,7 @@
         <v>36</v>
       </c>
       <c r="L49" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;H49&amp;","&amp;VLOOKUP(I49,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;H49&amp;","&amp;VLOOKUP(I49,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster044','イビルウェポン',16,132,19,16,0.15,5);</v>
       </c>
     </row>
@@ -33617,7 +33651,7 @@
         <v>37</v>
       </c>
       <c r="L50" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;H50&amp;","&amp;VLOOKUP(I50,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;H50&amp;","&amp;VLOOKUP(I50,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster045','エレメントソード',16,158,24,20,0.16,6);</v>
       </c>
     </row>
@@ -33647,7 +33681,7 @@
         <v>150</v>
       </c>
       <c r="L51" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;H51&amp;","&amp;VLOOKUP(I51,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;H51&amp;","&amp;VLOOKUP(I51,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster046','ケルベロス',17,110,11,19,0.18,1);</v>
       </c>
     </row>
@@ -33680,7 +33714,7 @@
         <v>150</v>
       </c>
       <c r="L52" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;H52&amp;","&amp;VLOOKUP(I52,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;H52&amp;","&amp;VLOOKUP(I52,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster047','バウンドウルフ',17,132,14,24,0.2,1);</v>
       </c>
     </row>
@@ -33713,7 +33747,7 @@
         <v>150</v>
       </c>
       <c r="L53" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;H53&amp;","&amp;VLOOKUP(I53,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;H53&amp;","&amp;VLOOKUP(I53,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster048','ジャッカル',17,158,18,31,0.21,1);</v>
       </c>
     </row>
@@ -33743,7 +33777,7 @@
         <v>151</v>
       </c>
       <c r="L54" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;H54&amp;","&amp;VLOOKUP(I54,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;H54&amp;","&amp;VLOOKUP(I54,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster049','ダックソルジャー',18,120,16,14,0.15,3);</v>
       </c>
     </row>
@@ -33773,7 +33807,7 @@
         <v>151</v>
       </c>
       <c r="L55" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;H55&amp;","&amp;VLOOKUP(I55,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;H55&amp;","&amp;VLOOKUP(I55,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster050','ダックジェネラル',18,160,24,20,0.15,3);</v>
       </c>
     </row>
@@ -33803,7 +33837,7 @@
         <v>34</v>
       </c>
       <c r="L56" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;H56&amp;","&amp;VLOOKUP(I56,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;H56&amp;","&amp;VLOOKUP(I56,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster051','モールベア',19,130,14,18,0.18,2);</v>
       </c>
     </row>
@@ -33833,7 +33867,7 @@
         <v>34</v>
       </c>
       <c r="L57" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;H57&amp;","&amp;VLOOKUP(I57,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;H57&amp;","&amp;VLOOKUP(I57,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster052','ニードリオン',19,170,18,26,0.2,2);</v>
       </c>
     </row>
@@ -33863,7 +33897,7 @@
         <v>35</v>
       </c>
       <c r="L58" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;H58&amp;","&amp;VLOOKUP(I58,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;H58&amp;","&amp;VLOOKUP(I58,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster053','ギャルビー',20,120,13,16,0.2,4);</v>
       </c>
     </row>
@@ -33896,7 +33930,7 @@
         <v>35</v>
       </c>
       <c r="L59" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;H59&amp;","&amp;VLOOKUP(I59,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;H59&amp;","&amp;VLOOKUP(I59,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster054','レディビー',20,144,16,20,0.22,4);</v>
       </c>
     </row>
@@ -33929,7 +33963,7 @@
         <v>35</v>
       </c>
       <c r="L60" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;H60&amp;","&amp;VLOOKUP(I60,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;H60&amp;","&amp;VLOOKUP(I60,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster055','クインビー',20,172,20,26,0.23,4);</v>
       </c>
     </row>
@@ -33959,7 +33993,7 @@
         <v>150</v>
       </c>
       <c r="L61" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;H61&amp;","&amp;VLOOKUP(I61,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;H61&amp;","&amp;VLOOKUP(I61,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster056','サハギン',21,130,16,16,0.15,1);</v>
       </c>
     </row>
@@ -33989,7 +34023,7 @@
         <v>150</v>
       </c>
       <c r="L62" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;H62&amp;","&amp;VLOOKUP(I62,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;H62&amp;","&amp;VLOOKUP(I62,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster057','プチポセイドン',21,150,22,19,0.15,1);</v>
       </c>
     </row>
@@ -34019,7 +34053,7 @@
         <v>298</v>
       </c>
       <c r="L63" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;H63&amp;","&amp;VLOOKUP(I63,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;H63&amp;","&amp;VLOOKUP(I63,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster058','クロウラー',22,130,15,11,0.08,2);</v>
       </c>
     </row>
@@ -34052,7 +34086,7 @@
         <v>34</v>
       </c>
       <c r="L64" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;H64&amp;","&amp;VLOOKUP(I64,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;H64&amp;","&amp;VLOOKUP(I64,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster059','メガクロウラー',22,156,19,14,0.09,2);</v>
       </c>
     </row>
@@ -34085,7 +34119,7 @@
         <v>34</v>
       </c>
       <c r="L65" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;H65&amp;","&amp;VLOOKUP(I65,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;H65&amp;","&amp;VLOOKUP(I65,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster060','ギガクロウラー',22,187,24,18,0.1,2);</v>
       </c>
     </row>
@@ -34115,7 +34149,7 @@
         <v>34</v>
       </c>
       <c r="L66" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;H66&amp;","&amp;VLOOKUP(I66,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;H66&amp;","&amp;VLOOKUP(I66,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster061','ぱっくんオタマ',23,110,12,10,0.15,2);</v>
       </c>
     </row>
@@ -34148,7 +34182,7 @@
         <v>34</v>
       </c>
       <c r="L67" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;H67&amp;","&amp;VLOOKUP(I67,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;H67&amp;","&amp;VLOOKUP(I67,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster062','ぱっくりオタマ',23,132,15,13,0.15,2);</v>
       </c>
     </row>
@@ -34181,7 +34215,7 @@
         <v>151</v>
       </c>
       <c r="L68" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;H68&amp;","&amp;VLOOKUP(I68,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;H68&amp;","&amp;VLOOKUP(I68,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster063','ぱっくんトカゲ',23,158,19,16,0.1,3);</v>
       </c>
     </row>
@@ -34214,7 +34248,7 @@
         <v>151</v>
       </c>
       <c r="L69" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;H69&amp;","&amp;VLOOKUP(I69,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;H69&amp;","&amp;VLOOKUP(I69,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster064','ぱっくんドラゴン',23,189,24,20,0.11,3);</v>
       </c>
     </row>
@@ -34244,7 +34278,7 @@
         <v>36</v>
       </c>
       <c r="L70" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;H70&amp;","&amp;VLOOKUP(I70,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;H70&amp;","&amp;VLOOKUP(I70,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster065','チビデビル',24,120,13,17,0.22,5);</v>
       </c>
     </row>
@@ -34274,7 +34308,7 @@
         <v>36</v>
       </c>
       <c r="L71" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;H71&amp;","&amp;VLOOKUP(I71,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;H71&amp;","&amp;VLOOKUP(I71,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster066','グレムリン',24,160,18,20,0.24,5);</v>
       </c>
     </row>
@@ -34304,7 +34338,7 @@
         <v>36</v>
       </c>
       <c r="L72" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;H72&amp;","&amp;VLOOKUP(I72,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;H72&amp;","&amp;VLOOKUP(I72,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster067','オーガボックス',25,140,18,17,0.15,5);</v>
       </c>
     </row>
@@ -34334,7 +34368,7 @@
         <v>36</v>
       </c>
       <c r="L73" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;H73&amp;","&amp;VLOOKUP(I73,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;H73&amp;","&amp;VLOOKUP(I73,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster068','カイザーミミック',25,170,23,20,0.15,5);</v>
       </c>
     </row>
@@ -34364,7 +34398,7 @@
         <v>151</v>
       </c>
       <c r="L74" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;H74&amp;","&amp;VLOOKUP(I74,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;H74&amp;","&amp;VLOOKUP(I74,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster069','バレッテ',26,140,15,12,0.05,3);</v>
       </c>
     </row>
@@ -34394,7 +34428,7 @@
         <v>151</v>
       </c>
       <c r="L75" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;H75&amp;","&amp;VLOOKUP(I75,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;H75&amp;","&amp;VLOOKUP(I75,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster070','ゴールドバレッテ',26,180,19,14,0.05,3);</v>
       </c>
     </row>
@@ -34424,7 +34458,7 @@
         <v>34</v>
       </c>
       <c r="L76" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;H76&amp;","&amp;VLOOKUP(I76,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;H76&amp;","&amp;VLOOKUP(I76,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster071','バシリスク',27,110,12,15,0.15,2);</v>
       </c>
     </row>
@@ -34454,7 +34488,7 @@
         <v>151</v>
       </c>
       <c r="L77" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;H77&amp;","&amp;VLOOKUP(I77,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;H77&amp;","&amp;VLOOKUP(I77,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster072','ファイアドレイク',27,150,18,22,0.18,3);</v>
       </c>
     </row>
@@ -34484,7 +34518,7 @@
         <v>36</v>
       </c>
       <c r="L78" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;H78&amp;","&amp;VLOOKUP(I78,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;H78&amp;","&amp;VLOOKUP(I78,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster073','スペクター',28,130,13,17,0.2,5);</v>
       </c>
     </row>
@@ -34514,7 +34548,7 @@
         <v>36</v>
       </c>
       <c r="L79" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;H79&amp;","&amp;VLOOKUP(I79,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;H79&amp;","&amp;VLOOKUP(I79,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster074','ゴースト',28,160,17,20,0.21,5);</v>
       </c>
     </row>
@@ -34544,7 +34578,7 @@
         <v>37</v>
       </c>
       <c r="L80" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;","&amp;VLOOKUP(I80,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;","&amp;VLOOKUP(I80,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster075','ユニコーンヘッド',29,120,15,14,0.15,6);</v>
       </c>
     </row>
@@ -34574,7 +34608,7 @@
         <v>37</v>
       </c>
       <c r="L81" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;H81&amp;","&amp;VLOOKUP(I81,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;H81&amp;","&amp;VLOOKUP(I81,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster076','ゴールドユニコ',29,170,22,25,0.15,6);</v>
       </c>
     </row>
@@ -34604,7 +34638,7 @@
         <v>36</v>
       </c>
       <c r="L82" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;H82&amp;","&amp;VLOOKUP(I82,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;H82&amp;","&amp;VLOOKUP(I82,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster077','シェイプシフター',30,130,12,14,0.14,5);</v>
       </c>
     </row>
@@ -34636,7 +34670,7 @@
         <v>36</v>
       </c>
       <c r="L83" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;H83&amp;","&amp;VLOOKUP(I83,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;H83&amp;","&amp;VLOOKUP(I83,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster078','シャドウゼロ',30,170,15,18,0.15,5);</v>
       </c>
     </row>
@@ -34668,7 +34702,7 @@
         <v>36</v>
       </c>
       <c r="L84" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;H84&amp;","&amp;VLOOKUP(I84,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;H84&amp;","&amp;VLOOKUP(I84,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster079','シャドウゼロワン',30,190,19,23,0.16,5);</v>
       </c>
     </row>
@@ -34698,7 +34732,7 @@
         <v>36</v>
       </c>
       <c r="L85" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;H85&amp;","&amp;VLOOKUP(I85,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;H85&amp;","&amp;VLOOKUP(I85,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster080','ボルダー',31,120,13,14,0.25,5);</v>
       </c>
     </row>
@@ -34731,7 +34765,7 @@
         <v>36</v>
       </c>
       <c r="L86" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;H86&amp;","&amp;VLOOKUP(I86,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;H86&amp;","&amp;VLOOKUP(I86,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster081','パワーボルダー',31,144,16,18,0.25,5);</v>
       </c>
     </row>
@@ -34764,7 +34798,7 @@
         <v>36</v>
       </c>
       <c r="L87" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;H87&amp;","&amp;VLOOKUP(I87,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;H87&amp;","&amp;VLOOKUP(I87,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster082','デスボルダー',31,172,20,23,0.25,5);</v>
       </c>
     </row>
@@ -34794,7 +34828,7 @@
         <v>151</v>
       </c>
       <c r="L88" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;H88&amp;","&amp;VLOOKUP(I88,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;H88&amp;","&amp;VLOOKUP(I88,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster083','パンプキンボム',32,130,17,12,0.18,3);</v>
       </c>
     </row>
@@ -34824,7 +34858,7 @@
         <v>151</v>
       </c>
       <c r="L89" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$48:$I$107,3,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;H89&amp;","&amp;VLOOKUP(I89,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;H89&amp;","&amp;VLOOKUP(I89,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster084','グレネードボム',32,160,24,15,0.2,3);</v>
       </c>
     </row>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0006DF47-37FF-4D17-B0AE-0331CC729D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F99F8E-AACC-4702-AD4F-1D854082BE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="3" activeTab="3" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="3" activeTab="10" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="architecture" sheetId="12" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4647" uniqueCount="2373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4824" uniqueCount="2442">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -9783,9 +9783,6 @@
     <t>既に入ってるけど、Modern / Classic / Alt T等かなり多い</t>
   </si>
   <si>
-    <t>Tom Anderson</t>
-  </si>
-  <si>
     <t>ハイエンド。Classic / Angel / Drop Top等</t>
   </si>
   <si>
@@ -9815,15 +9812,6 @@
   </si>
   <si>
     <t>Caparison — 日本のハイエンド系。モデル数もそこそこ</t>
-  </si>
-  <si>
-    <t>Kiesel — カスタムオーダー型でバリエーションが異常に多い</t>
-  </si>
-  <si>
-    <t>Vigier — フランスのハイエンド</t>
-  </si>
-  <si>
-    <t>Knaggs — 高級系、モデル展開もそこそこ</t>
   </si>
   <si>
     <t>LTD — ESPと別ブランドとして扱うなら大量追加できる</t>
@@ -9863,13 +9851,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>カラー取れない</t>
-    <rPh sb="3" eb="4">
-      <t>ト</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>FUJIGEN</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -9943,19 +9924,260 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>Fernandes</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>MAYONES</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://mayones.com/</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クロールなし</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Kiesel — カスタムオーダー型でバリエーションが異常に多い</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Gretsch</t>
+  </si>
+  <si>
+    <t>Tom Anderson</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Rickenbacker</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Body colorの1行目を取ればOK?</t>
+    <rPh sb="12" eb="14">
+      <t>ギョウメ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Knaggs — 高級系、モデル展開もそこそこ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Vigier — フランスのハイエンド</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>Suhr</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Fernandes</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>MAYONES</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://mayones.com/</t>
+  </si>
+  <si>
+    <t>Tokai</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>知名度</t>
+  </si>
+  <si>
+    <t>モデル規模</t>
+  </si>
+  <si>
+    <t>個性</t>
+  </si>
+  <si>
+    <t>優先度</t>
+  </si>
+  <si>
+    <t>一言</t>
+  </si>
+  <si>
+    <t>Fender</t>
+  </si>
+  <si>
+    <t>特大</t>
+  </si>
+  <si>
+    <t>🔥🔥🔥</t>
+  </si>
+  <si>
+    <t>Strat / Tele / Jaguar / Jazzmaster</t>
+  </si>
+  <si>
+    <t>Gibson</t>
+  </si>
+  <si>
+    <t>大</t>
+  </si>
+  <si>
+    <t>Les Paul / SG / ES</t>
+  </si>
+  <si>
+    <t>Ibanez</t>
+  </si>
+  <si>
+    <t>RG / AZ / JEM / Iceman</t>
+  </si>
+  <si>
+    <t>PRS</t>
+  </si>
+  <si>
+    <t>中〜大</t>
+  </si>
+  <si>
+    <t>Custom 24の存在感</t>
+  </si>
+  <si>
+    <t>ESP</t>
+  </si>
+  <si>
+    <t>日本メタル系の王道</t>
+  </si>
+  <si>
+    <t>Jackson</t>
+  </si>
+  <si>
+    <t>Soloist / Dinky / Kelly / King V</t>
+  </si>
+  <si>
+    <t>Schecter</t>
+  </si>
+  <si>
+    <t>現代メタル系の物量が凄い</t>
+  </si>
+  <si>
+    <t>🔥🔥</t>
+  </si>
+  <si>
+    <t>Hollowbodyの代表格</t>
+  </si>
+  <si>
+    <t>小〜中</t>
+  </si>
+  <si>
+    <t>360 / 4003など唯一無二</t>
+  </si>
+  <si>
+    <t>Music Man</t>
+  </si>
+  <si>
+    <t>John Petrucci / StingRay等</t>
+  </si>
+  <si>
+    <t>Charvel</t>
+  </si>
+  <si>
+    <t>Super Strat系の名門</t>
+  </si>
+  <si>
+    <t>ハイエンド・Super Strat</t>
+  </si>
+  <si>
+    <t>Taylor</t>
+  </si>
+  <si>
+    <t>アコギも入れるなら必須級</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>アコギ界の超大物</t>
+  </si>
+  <si>
+    <t>Takamine</t>
+  </si>
+  <si>
+    <t>日本勢の代表格</t>
+  </si>
+  <si>
+    <t>PACIFICA / SG / Revstar / LL等</t>
+  </si>
+  <si>
+    <t>Greco</t>
+  </si>
+  <si>
+    <t>日本ヴィンテージ勢として面白い</t>
+  </si>
+  <si>
+    <t>Love Rock / AST等</t>
+  </si>
+  <si>
+    <t>B.C. Rich</t>
+  </si>
+  <si>
+    <t>変形ギター枠の超重要ブランド</t>
+  </si>
+  <si>
+    <t>Dean</t>
+  </si>
+  <si>
+    <t>ML / V / Zなど</t>
+  </si>
+  <si>
+    <t>Kramer</t>
+  </si>
+  <si>
+    <t>🔥</t>
+  </si>
+  <si>
+    <t>Van Halen、80年代HR/HM</t>
+  </si>
+  <si>
+    <t>Guild</t>
+  </si>
+  <si>
+    <t>アコギ＋セミアコ</t>
+  </si>
+  <si>
+    <t>D'Angelico</t>
+  </si>
+  <si>
+    <t>セミアコ・ジャズ系</t>
+  </si>
+  <si>
+    <t>G&amp;L</t>
+  </si>
+  <si>
+    <t>Leo Fender最後のブランド</t>
+  </si>
+  <si>
+    <t>Frankenstein / Wolfgang</t>
+  </si>
+  <si>
+    <t>Kiesel</t>
+  </si>
+  <si>
+    <t>カスタム仕様が鬼</t>
+  </si>
+  <si>
+    <t>Reverend</t>
+  </si>
+  <si>
+    <t>個性的な現代ギター</t>
+  </si>
+  <si>
+    <t>Godin</t>
+  </si>
+  <si>
+    <t>カナダ勢、モデルが多彩</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>有名どころ</t>
+    <rPh sb="0" eb="2">
+      <t>ユウメイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Yamaha</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -10417,7 +10639,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -10597,6 +10819,15 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -21006,7 +21237,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F0B575-2DDF-49B9-8DE2-F372EEC2F3B3}">
-  <dimension ref="A2:O108"/>
+  <dimension ref="A2:O139"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="11.8984375" style="1" customWidth="1"/>
@@ -21966,7 +22197,7 @@
     </row>
     <row r="84" spans="2:11">
       <c r="B84" s="1" t="s">
-        <v>2366</v>
+        <v>2361</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>2319</v>
@@ -21978,12 +22209,12 @@
         <v>2320</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>2363</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="85" spans="2:11">
       <c r="B85" s="1" t="s">
-        <v>2362</v>
+        <v>2357</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>2319</v>
@@ -21995,12 +22226,12 @@
         <v>2321</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>2363</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="86" spans="2:11">
       <c r="B86" s="1" t="s">
-        <v>2368</v>
+        <v>2363</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>2319</v>
@@ -22028,7 +22259,7 @@
     </row>
     <row r="88" spans="2:11">
       <c r="B88" s="1" t="s">
-        <v>2325</v>
+        <v>2376</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>2319</v>
@@ -22040,12 +22271,12 @@
         <v>2326</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>2351</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="89" spans="2:11">
       <c r="B89" s="1" t="s">
-        <v>2356</v>
+        <v>2351</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>2319</v>
@@ -22057,12 +22288,12 @@
         <v>2327</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>2357</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="90" spans="2:11">
       <c r="B90" s="1" t="s">
-        <v>2352</v>
+        <v>2348</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>2319</v>
@@ -22074,7 +22305,7 @@
         <v>2328</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>2353</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="91" spans="2:11">
@@ -22093,7 +22324,7 @@
     </row>
     <row r="92" spans="2:11">
       <c r="B92" s="1" t="s">
-        <v>2354</v>
+        <v>2350</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>2319</v>
@@ -22105,12 +22336,12 @@
         <v>2333</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>2355</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="93" spans="2:11">
       <c r="B93" s="1" t="s">
-        <v>2364</v>
+        <v>2359</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>2330</v>
@@ -22124,7 +22355,7 @@
     </row>
     <row r="94" spans="2:11">
       <c r="B94" s="1" t="s">
-        <v>2369</v>
+        <v>1545</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>2330</v>
@@ -22138,7 +22369,7 @@
     </row>
     <row r="95" spans="2:11">
       <c r="B95" s="1" t="s">
-        <v>2336</v>
+        <v>2370</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>2330</v>
@@ -22147,12 +22378,12 @@
         <v>2238</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="96" spans="2:11">
       <c r="B96" s="1" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>2319</v>
@@ -22161,12 +22392,12 @@
         <v>2238</v>
       </c>
       <c r="E96" s="1" t="s">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="B97" s="1" t="s">
         <v>2338</v>
-      </c>
-    </row>
-    <row r="97" spans="2:7">
-      <c r="B97" s="1" t="s">
-        <v>2339</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>2319</v>
@@ -22175,12 +22406,12 @@
         <v>2238</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>2340</v>
-      </c>
-    </row>
-    <row r="98" spans="2:7">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
       <c r="B98" s="1" t="s">
-        <v>2341</v>
+        <v>2371</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>2330</v>
@@ -22189,65 +22420,653 @@
         <v>2331</v>
       </c>
       <c r="E98" s="1" t="s">
+        <v>2341</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="B99" s="1" t="s">
+        <v>2360</v>
+      </c>
+      <c r="C99" s="1" t="s">
         <v>2342</v>
-      </c>
-    </row>
-    <row r="99" spans="2:7">
-      <c r="B99" s="1" t="s">
-        <v>2365</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>2343</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>2235</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>2344</v>
-      </c>
-    </row>
-    <row r="101" spans="2:7">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
       <c r="B101" s="1" t="s">
+        <v>2345</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="B102" s="1" t="s">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="B103" s="1" t="s">
+        <v>2353</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="B104" s="1" t="s">
+        <v>2355</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="B106" s="1" t="s">
+        <v>2374</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="B107" s="1" t="s">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="B108" s="1" t="s">
         <v>2346</v>
       </c>
-      <c r="G101" s="1" t="s">
-        <v>2367</v>
-      </c>
-    </row>
-    <row r="102" spans="2:7">
-      <c r="B102" s="1" t="s">
-        <v>2347</v>
-      </c>
-    </row>
-    <row r="103" spans="2:7">
-      <c r="B103" s="1" t="s">
-        <v>2358</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>2359</v>
-      </c>
-    </row>
-    <row r="104" spans="2:7">
-      <c r="B104" s="1" t="s">
-        <v>2360</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>2361</v>
-      </c>
-    </row>
-    <row r="106" spans="2:7">
-      <c r="B106" s="1" t="s">
-        <v>2348</v>
-      </c>
-    </row>
-    <row r="107" spans="2:7">
-      <c r="B107" s="1" t="s">
-        <v>2349</v>
-      </c>
-    </row>
-    <row r="108" spans="2:7">
-      <c r="B108" s="1" t="s">
-        <v>2350</v>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" s="1" t="s">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="18">
+      <c r="B111" s="103" t="s">
+        <v>2315</v>
+      </c>
+      <c r="C111" s="103" t="s">
+        <v>2377</v>
+      </c>
+      <c r="D111" s="103" t="s">
+        <v>2378</v>
+      </c>
+      <c r="E111" s="103" t="s">
+        <v>2379</v>
+      </c>
+      <c r="F111" s="103" t="s">
+        <v>2380</v>
+      </c>
+      <c r="G111" s="103" t="s">
+        <v>2381</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="18">
+      <c r="A112" s="1" t="s">
+        <v>2439</v>
+      </c>
+      <c r="B112" s="111" t="s">
+        <v>2382</v>
+      </c>
+      <c r="C112" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="D112" s="104" t="s">
+        <v>2383</v>
+      </c>
+      <c r="E112" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="F112" s="104" t="s">
+        <v>2384</v>
+      </c>
+      <c r="G112" s="112" t="s">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="113" spans="2:7" ht="18">
+      <c r="B113" s="111" t="s">
+        <v>2386</v>
+      </c>
+      <c r="C113" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="D113" s="104" t="s">
+        <v>2387</v>
+      </c>
+      <c r="E113" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F113" s="104" t="s">
+        <v>2384</v>
+      </c>
+      <c r="G113" s="112" t="s">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="114" spans="2:7" ht="18">
+      <c r="B114" s="111" t="s">
+        <v>2389</v>
+      </c>
+      <c r="C114" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="D114" s="104" t="s">
+        <v>2383</v>
+      </c>
+      <c r="E114" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F114" s="104" t="s">
+        <v>2384</v>
+      </c>
+      <c r="G114" s="112" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="115" spans="2:7" ht="18">
+      <c r="B115" s="111" t="s">
+        <v>2391</v>
+      </c>
+      <c r="C115" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="D115" s="104" t="s">
+        <v>2392</v>
+      </c>
+      <c r="E115" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F115" s="104" t="s">
+        <v>2384</v>
+      </c>
+      <c r="G115" s="112" t="s">
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="116" spans="2:7" ht="18">
+      <c r="B116" s="111" t="s">
+        <v>2394</v>
+      </c>
+      <c r="C116" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="D116" s="104" t="s">
+        <v>2387</v>
+      </c>
+      <c r="E116" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F116" s="104" t="s">
+        <v>2384</v>
+      </c>
+      <c r="G116" s="112" t="s">
+        <v>2395</v>
+      </c>
+    </row>
+    <row r="117" spans="2:7" ht="18">
+      <c r="B117" s="111" t="s">
+        <v>2396</v>
+      </c>
+      <c r="C117" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="D117" s="104" t="s">
+        <v>2387</v>
+      </c>
+      <c r="E117" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F117" s="104" t="s">
+        <v>2384</v>
+      </c>
+      <c r="G117" s="112" t="s">
+        <v>2397</v>
+      </c>
+    </row>
+    <row r="118" spans="2:7" ht="18">
+      <c r="B118" s="111" t="s">
+        <v>2398</v>
+      </c>
+      <c r="C118" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="D118" s="104" t="s">
+        <v>2383</v>
+      </c>
+      <c r="E118" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="F118" s="104" t="s">
+        <v>2384</v>
+      </c>
+      <c r="G118" s="112" t="s">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="119" spans="2:7" ht="18">
+      <c r="B119" s="111" t="s">
+        <v>2369</v>
+      </c>
+      <c r="C119" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="D119" s="104" t="s">
+        <v>2387</v>
+      </c>
+      <c r="E119" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F119" s="104" t="s">
+        <v>2400</v>
+      </c>
+      <c r="G119" s="112" t="s">
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="120" spans="2:7" ht="36">
+      <c r="B120" s="111" t="s">
+        <v>2340</v>
+      </c>
+      <c r="C120" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="D120" s="104" t="s">
+        <v>2402</v>
+      </c>
+      <c r="E120" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F120" s="104" t="s">
+        <v>2400</v>
+      </c>
+      <c r="G120" s="112" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="121" spans="2:7" ht="18">
+      <c r="B121" s="111" t="s">
+        <v>2404</v>
+      </c>
+      <c r="C121" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D121" s="104" t="s">
+        <v>2342</v>
+      </c>
+      <c r="E121" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F121" s="104" t="s">
+        <v>2400</v>
+      </c>
+      <c r="G121" s="112" t="s">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="122" spans="2:7" ht="18">
+      <c r="B122" s="111" t="s">
+        <v>2406</v>
+      </c>
+      <c r="C122" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D122" s="104" t="s">
+        <v>2392</v>
+      </c>
+      <c r="E122" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F122" s="104" t="s">
+        <v>2400</v>
+      </c>
+      <c r="G122" s="112" t="s">
+        <v>2407</v>
+      </c>
+    </row>
+    <row r="123" spans="2:7" ht="18">
+      <c r="B123" s="111" t="s">
+        <v>2375</v>
+      </c>
+      <c r="C123" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D123" s="104" t="s">
+        <v>2342</v>
+      </c>
+      <c r="E123" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F123" s="104" t="s">
+        <v>2400</v>
+      </c>
+      <c r="G123" s="112" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="124" spans="2:7" ht="18">
+      <c r="B124" s="111" t="s">
+        <v>2409</v>
+      </c>
+      <c r="C124" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="D124" s="104" t="s">
+        <v>2387</v>
+      </c>
+      <c r="E124" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="F124" s="104" t="s">
+        <v>2400</v>
+      </c>
+      <c r="G124" s="112" t="s">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="125" spans="2:7" ht="18">
+      <c r="B125" s="111" t="s">
+        <v>2411</v>
+      </c>
+      <c r="C125" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="D125" s="104" t="s">
+        <v>2387</v>
+      </c>
+      <c r="E125" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F125" s="104" t="s">
+        <v>2400</v>
+      </c>
+      <c r="G125" s="112" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="126" spans="2:7" ht="18">
+      <c r="B126" s="111" t="s">
+        <v>2413</v>
+      </c>
+      <c r="C126" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D126" s="104" t="s">
+        <v>2387</v>
+      </c>
+      <c r="E126" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="F126" s="104" t="s">
+        <v>2400</v>
+      </c>
+      <c r="G126" s="112" t="s">
+        <v>2414</v>
+      </c>
+    </row>
+    <row r="127" spans="2:7" ht="18">
+      <c r="B127" s="111" t="s">
+        <v>2441</v>
+      </c>
+      <c r="C127" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="D127" s="104" t="s">
+        <v>2383</v>
+      </c>
+      <c r="E127" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="F127" s="104" t="s">
+        <v>2384</v>
+      </c>
+      <c r="G127" s="112" t="s">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="128" spans="2:7" ht="18">
+      <c r="B128" s="111" t="s">
+        <v>2416</v>
+      </c>
+      <c r="C128" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D128" s="104" t="s">
+        <v>2387</v>
+      </c>
+      <c r="E128" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="F128" s="104" t="s">
+        <v>2400</v>
+      </c>
+      <c r="G128" s="112" t="s">
+        <v>2417</v>
+      </c>
+    </row>
+    <row r="129" spans="2:7" ht="18">
+      <c r="B129" s="111" t="s">
+        <v>2325</v>
+      </c>
+      <c r="C129" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D129" s="104" t="s">
+        <v>2392</v>
+      </c>
+      <c r="E129" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="F129" s="104" t="s">
+        <v>2400</v>
+      </c>
+      <c r="G129" s="112" t="s">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="130" spans="2:7" ht="18">
+      <c r="B130" s="111" t="s">
+        <v>2419</v>
+      </c>
+      <c r="C130" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D130" s="104" t="s">
+        <v>2342</v>
+      </c>
+      <c r="E130" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F130" s="104" t="s">
+        <v>2400</v>
+      </c>
+      <c r="G130" s="113" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="131" spans="2:7" ht="18">
+      <c r="B131" s="111" t="s">
+        <v>2421</v>
+      </c>
+      <c r="C131" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D131" s="104" t="s">
+        <v>2392</v>
+      </c>
+      <c r="E131" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F131" s="104" t="s">
+        <v>2400</v>
+      </c>
+      <c r="G131" s="112" t="s">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="132" spans="2:7" ht="18">
+      <c r="B132" s="111" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C132" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D132" s="104" t="s">
+        <v>2342</v>
+      </c>
+      <c r="E132" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F132" s="104" t="s">
+        <v>2424</v>
+      </c>
+      <c r="G132" s="112" t="s">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="133" spans="2:7" ht="18">
+      <c r="B133" s="111" t="s">
+        <v>2426</v>
+      </c>
+      <c r="C133" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D133" s="104" t="s">
+        <v>2392</v>
+      </c>
+      <c r="E133" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="F133" s="104" t="s">
+        <v>2424</v>
+      </c>
+      <c r="G133" s="112" t="s">
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="134" spans="2:7" ht="18">
+      <c r="B134" s="111" t="s">
+        <v>2428</v>
+      </c>
+      <c r="C134" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D134" s="104" t="s">
+        <v>2342</v>
+      </c>
+      <c r="E134" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F134" s="104" t="s">
+        <v>2424</v>
+      </c>
+      <c r="G134" s="112" t="s">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="135" spans="2:7" ht="18">
+      <c r="B135" s="111" t="s">
+        <v>2430</v>
+      </c>
+      <c r="C135" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D135" s="104" t="s">
+        <v>2342</v>
+      </c>
+      <c r="E135" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="F135" s="104" t="s">
+        <v>2424</v>
+      </c>
+      <c r="G135" s="112" t="s">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="136" spans="2:7" ht="18">
+      <c r="B136" s="111" t="s">
+        <v>2338</v>
+      </c>
+      <c r="C136" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D136" s="104" t="s">
+        <v>2402</v>
+      </c>
+      <c r="E136" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F136" s="104" t="s">
+        <v>2424</v>
+      </c>
+      <c r="G136" s="112" t="s">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="137" spans="2:7" ht="18">
+      <c r="B137" s="111" t="s">
+        <v>2433</v>
+      </c>
+      <c r="C137" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D137" s="104" t="s">
+        <v>2383</v>
+      </c>
+      <c r="E137" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F137" s="104" t="s">
+        <v>2400</v>
+      </c>
+      <c r="G137" s="112" t="s">
+        <v>2434</v>
+      </c>
+    </row>
+    <row r="138" spans="2:7" ht="18">
+      <c r="B138" s="111" t="s">
+        <v>2435</v>
+      </c>
+      <c r="C138" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D138" s="104" t="s">
+        <v>2342</v>
+      </c>
+      <c r="E138" s="104" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F138" s="104" t="s">
+        <v>2424</v>
+      </c>
+      <c r="G138" s="112" t="s">
+        <v>2436</v>
+      </c>
+    </row>
+    <row r="139" spans="2:7" ht="18">
+      <c r="B139" s="111" t="s">
+        <v>2437</v>
+      </c>
+      <c r="C139" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D139" s="104" t="s">
+        <v>2387</v>
+      </c>
+      <c r="E139" s="104" t="s">
+        <v>2238</v>
+      </c>
+      <c r="F139" s="104" t="s">
+        <v>2424</v>
+      </c>
+      <c r="G139" s="112" t="s">
+        <v>2438</v>
       </c>
     </row>
   </sheetData>
@@ -26960,7 +27779,7 @@
         <v>1777</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>2370</v>
+        <v>2364</v>
       </c>
       <c r="D105" s="8"/>
       <c r="E105" s="8">
@@ -26973,10 +27792,12 @@
       <c r="H105" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="I105" s="8"/>
+      <c r="I105" s="8" t="s">
+        <v>2367</v>
+      </c>
       <c r="K105" s="5" t="str">
         <f t="shared" si="15"/>
-        <v>INSERT INTO m_code VALUES ('guitar_makers',13,'Fernandes','','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_makers',13,'Fernandes','','',0,0.0,'クロールなし');</v>
       </c>
     </row>
     <row r="106" spans="2:11">
@@ -26984,7 +27805,7 @@
         <v>1777</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>2371</v>
+        <v>2365</v>
       </c>
       <c r="D106" s="8"/>
       <c r="E106" s="8">
@@ -26998,7 +27819,7 @@
         <v>125</v>
       </c>
       <c r="I106" s="8" t="s">
-        <v>2372</v>
+        <v>2366</v>
       </c>
       <c r="K106" s="5" t="str">
         <f t="shared" si="14"/>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F99F8E-AACC-4702-AD4F-1D854082BE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D6382FA-AA00-4891-BD5A-5D233F4A8E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="3" activeTab="10" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="3" activeTab="3" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="architecture" sheetId="12" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4824" uniqueCount="2442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4828" uniqueCount="2444">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -10178,6 +10178,14 @@
   </si>
   <si>
     <t>Yamaha</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.jacksonguitars.jp/</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Jackson</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -25105,7 +25113,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
-  <dimension ref="B4:K168"/>
+  <dimension ref="B4:K169"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -27718,7 +27726,7 @@
         <v>1551</v>
       </c>
       <c r="K102" s="5" t="str">
-        <f t="shared" ref="K102:K106" si="14">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B102&amp;"'"&amp;","&amp;E102&amp;","&amp;"'"&amp;C102&amp;"'"&amp;","&amp;"'"&amp;D102&amp;"'"&amp;","&amp;"'"&amp;F102&amp;"'"&amp;","&amp;G102&amp;","&amp;H102&amp;","&amp;"'"&amp;I102&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K102:K107" si="14">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B102&amp;"'"&amp;","&amp;E102&amp;","&amp;"'"&amp;C102&amp;"'"&amp;","&amp;"'"&amp;D102&amp;"'"&amp;","&amp;"'"&amp;F102&amp;"'"&amp;","&amp;G102&amp;","&amp;H102&amp;","&amp;"'"&amp;I102&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('guitar_makers',10,'MusicMan','','',0,0.0,'https://www.music-man.com/instruments/guitars');</v>
       </c>
     </row>
@@ -27770,7 +27778,7 @@
         <v>1553</v>
       </c>
       <c r="K104" s="5" t="str">
-        <f t="shared" ref="K104:K105" si="15">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B104&amp;"'"&amp;","&amp;E104&amp;","&amp;"'"&amp;C104&amp;"'"&amp;","&amp;"'"&amp;D104&amp;"'"&amp;","&amp;"'"&amp;F104&amp;"'"&amp;","&amp;G104&amp;","&amp;H104&amp;","&amp;"'"&amp;I104&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K104:K106" si="15">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B104&amp;"'"&amp;","&amp;E104&amp;","&amp;"'"&amp;C104&amp;"'"&amp;","&amp;"'"&amp;D104&amp;"'"&amp;","&amp;"'"&amp;F104&amp;"'"&amp;","&amp;G104&amp;","&amp;H104&amp;","&amp;"'"&amp;I104&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('guitar_makers',12,'Momose','','',0,0.0,'https://www.deviser.co.jp/momose');</v>
       </c>
     </row>
@@ -27822,62 +27830,60 @@
         <v>2366</v>
       </c>
       <c r="K106" s="5" t="str">
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('guitar_makers',14,'MAYONES','','',0,0.0,'https://mayones.com/');</v>
+      </c>
+    </row>
+    <row r="107" spans="2:11">
+      <c r="B107" s="8" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>2443</v>
+      </c>
+      <c r="D107" s="8"/>
+      <c r="E107" s="8">
+        <v>15</v>
+      </c>
+      <c r="F107" s="8"/>
+      <c r="G107" s="9">
+        <v>0</v>
+      </c>
+      <c r="H107" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I107" s="8" t="s">
+        <v>2442</v>
+      </c>
+      <c r="K107" s="5" t="str">
         <f t="shared" si="14"/>
-        <v>INSERT INTO m_code VALUES ('guitar_makers',14,'MAYONES','','',0,0.0,'https://mayones.com/');</v>
-      </c>
-    </row>
-    <row r="107" spans="2:11">
-      <c r="B107" s="6" t="s">
+        <v>INSERT INTO m_code VALUES ('guitar_makers',15,'Jackson','','',0,0.0,'https://www.jacksonguitars.jp/');</v>
+      </c>
+    </row>
+    <row r="108" spans="2:11">
+      <c r="B108" s="6" t="s">
         <v>1542</v>
       </c>
-      <c r="C107" s="6" t="s">
+      <c r="C108" s="6" t="s">
         <v>1388</v>
       </c>
-      <c r="D107" s="6" t="s">
+      <c r="D108" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E107" s="7" t="s">
+      <c r="E108" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F107" s="6" t="s">
+      <c r="F108" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G107" s="6" t="s">
+      <c r="G108" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H107" s="6" t="s">
+      <c r="H108" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I107" s="6" t="s">
+      <c r="I108" s="6" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="108" spans="2:11">
-      <c r="B108" s="8" t="s">
-        <v>1778</v>
-      </c>
-      <c r="C108" s="8" t="s">
-        <v>1425</v>
-      </c>
-      <c r="D108" s="8"/>
-      <c r="E108" s="8">
-        <v>1</v>
-      </c>
-      <c r="F108" s="8" t="s">
-        <v>1439</v>
-      </c>
-      <c r="G108" s="9">
-        <v>0</v>
-      </c>
-      <c r="H108" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I108" s="8" t="s">
-        <v>1463</v>
-      </c>
-      <c r="K108" s="5" t="str">
-        <f t="shared" ref="K108:K143" si="16">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B108&amp;"'"&amp;","&amp;E108&amp;","&amp;"'"&amp;C108&amp;"'"&amp;","&amp;"'"&amp;D108&amp;"'"&amp;","&amp;"'"&amp;F108&amp;"'"&amp;","&amp;G108&amp;","&amp;H108&amp;","&amp;"'"&amp;I108&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',1,'HardMaple','','ハードメイプル',0,0.0,'硬質でタイト、明瞭なアタック。');</v>
       </c>
     </row>
     <row r="109" spans="2:11">
@@ -27885,14 +27891,14 @@
         <v>1778</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="D109" s="8"/>
       <c r="E109" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G109" s="9">
         <v>0</v>
@@ -27901,11 +27907,11 @@
         <v>125</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="K109" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',2,'FlameMaple','','フレイムメイプル',0,0.0,'明るく抜けが良く、華やかな倍音。');</v>
+        <f t="shared" ref="K109:K144" si="16">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B109&amp;"'"&amp;","&amp;E109&amp;","&amp;"'"&amp;C109&amp;"'"&amp;","&amp;"'"&amp;D109&amp;"'"&amp;","&amp;"'"&amp;F109&amp;"'"&amp;","&amp;G109&amp;","&amp;H109&amp;","&amp;"'"&amp;I109&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',1,'HardMaple','','ハードメイプル',0,0.0,'硬質でタイト、明瞭なアタック。');</v>
       </c>
     </row>
     <row r="110" spans="2:11">
@@ -27913,14 +27919,14 @@
         <v>1778</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="D110" s="8"/>
       <c r="E110" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="G110" s="9">
         <v>0</v>
@@ -27929,11 +27935,11 @@
         <v>125</v>
       </c>
       <c r="I110" s="8" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="K110" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',3,'QuiltedMaple','','キルテッドメイプル',0,0.0,'立体的で広がりがあり、煌びやかな響き。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',2,'FlameMaple','','フレイムメイプル',0,0.0,'明るく抜けが良く、華やかな倍音。');</v>
       </c>
     </row>
     <row r="111" spans="2:11">
@@ -27941,14 +27947,14 @@
         <v>1778</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="D111" s="8"/>
       <c r="E111" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="G111" s="9">
         <v>0</v>
@@ -27957,11 +27963,11 @@
         <v>125</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="K111" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',4,'BirdseyeMaple','','バーズアイメイプル',0,0.0,'粒立ちが良く、明るくシャープ。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',3,'QuiltedMaple','','キルテッドメイプル',0,0.0,'立体的で広がりがあり、煌びやかな響き。');</v>
       </c>
     </row>
     <row r="112" spans="2:11">
@@ -27969,14 +27975,14 @@
         <v>1778</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="D112" s="8"/>
       <c r="E112" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="G112" s="9">
         <v>0</v>
@@ -27985,11 +27991,11 @@
         <v>125</v>
       </c>
       <c r="I112" s="8" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="K112" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',5,'RoastedMaple','','ローステッドメイプル',0,0.0,'引き締まったタイトな音で反応が速い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',4,'BirdseyeMaple','','バーズアイメイプル',0,0.0,'粒立ちが良く、明るくシャープ。');</v>
       </c>
     </row>
     <row r="113" spans="2:11">
@@ -27997,14 +28003,14 @@
         <v>1778</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>1389</v>
+        <v>1429</v>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>1438</v>
+        <v>1443</v>
       </c>
       <c r="G113" s="9">
         <v>0</v>
@@ -28013,11 +28019,11 @@
         <v>125</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>1462</v>
+        <v>1467</v>
       </c>
       <c r="K113" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',6,'Maple','','メイプル',0,0.0,'明るくハリがあり、アタックが強い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',5,'RoastedMaple','','ローステッドメイプル',0,0.0,'引き締まったタイトな音で反応が速い。');</v>
       </c>
     </row>
     <row r="114" spans="2:11">
@@ -28025,14 +28031,14 @@
         <v>1778</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>1430</v>
+        <v>1389</v>
       </c>
       <c r="D114" s="8"/>
       <c r="E114" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>1444</v>
+        <v>1438</v>
       </c>
       <c r="G114" s="9">
         <v>0</v>
@@ -28041,11 +28047,11 @@
         <v>125</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>1469</v>
+        <v>1462</v>
       </c>
       <c r="K114" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',7,'HonduranMahogany','','ホンジュラスマホガニー',0,0.0,'深みがあり、太くリッチな中低域。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',6,'Maple','','メイプル',0,0.0,'明るくハリがあり、アタックが強い。');</v>
       </c>
     </row>
     <row r="115" spans="2:11">
@@ -28053,14 +28059,14 @@
         <v>1778</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>1390</v>
+        <v>1430</v>
       </c>
       <c r="D115" s="8"/>
       <c r="E115" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>1408</v>
+        <v>1444</v>
       </c>
       <c r="G115" s="9">
         <v>0</v>
@@ -28069,11 +28075,11 @@
         <v>125</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="K115" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',8,'Mahogany','','マホガニー',0,0.0,'中低域が豊かで温かい音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',7,'HonduranMahogany','','ホンジュラスマホガニー',0,0.0,'深みがあり、太くリッチな中低域。');</v>
       </c>
     </row>
     <row r="116" spans="2:11">
@@ -28081,14 +28087,14 @@
         <v>1778</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>1431</v>
+        <v>1390</v>
       </c>
       <c r="D116" s="8"/>
       <c r="E116" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>1445</v>
+        <v>1408</v>
       </c>
       <c r="G116" s="9">
         <v>0</v>
@@ -28097,11 +28103,11 @@
         <v>125</v>
       </c>
       <c r="I116" s="8" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="K116" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',9,'Sapele','','サペリ',0,0.0,'温かく柔らかいトーンでバランスが良い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',8,'Mahogany','','マホガニー',0,0.0,'中低域が豊かで温かい音。');</v>
       </c>
     </row>
     <row r="117" spans="2:11">
@@ -28109,14 +28115,14 @@
         <v>1778</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>1397</v>
+        <v>1431</v>
       </c>
       <c r="D117" s="8"/>
       <c r="E117" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="G117" s="9">
         <v>0</v>
@@ -28125,11 +28131,11 @@
         <v>125</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="K117" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',10,'Korina','','コリーナ',0,0.0,'中域が豊かで太い音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',9,'Sapele','','サペリ',0,0.0,'温かく柔らかいトーンでバランスが良い。');</v>
       </c>
     </row>
     <row r="118" spans="2:11">
@@ -28137,14 +28143,14 @@
         <v>1778</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>1432</v>
+        <v>1397</v>
       </c>
       <c r="D118" s="8"/>
       <c r="E118" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="G118" s="9">
         <v>0</v>
@@ -28153,11 +28159,11 @@
         <v>125</v>
       </c>
       <c r="I118" s="8" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="K118" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',11,'WhiteKorina','','ホワイトコリーナ',0,0.0,'明るく抜けが良く、軽快なレスポンス。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',10,'Korina','','コリーナ',0,0.0,'中域が豊かで太い音。');</v>
       </c>
     </row>
     <row r="119" spans="2:11">
@@ -28165,14 +28171,14 @@
         <v>1778</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>1391</v>
+        <v>1432</v>
       </c>
       <c r="D119" s="8"/>
       <c r="E119" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>1409</v>
+        <v>1447</v>
       </c>
       <c r="G119" s="9">
         <v>0</v>
@@ -28181,11 +28187,11 @@
         <v>125</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="K119" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',12,'Alder','','アルダー',0,0.0,'バランスが良くクセが少ない。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',11,'WhiteKorina','','ホワイトコリーナ',0,0.0,'明るく抜けが良く、軽快なレスポンス。');</v>
       </c>
     </row>
     <row r="120" spans="2:11">
@@ -28193,14 +28199,14 @@
         <v>1778</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="D120" s="8"/>
       <c r="E120" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>1448</v>
+        <v>1409</v>
       </c>
       <c r="G120" s="9">
         <v>0</v>
@@ -28209,11 +28215,11 @@
         <v>125</v>
       </c>
       <c r="I120" s="8" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="K120" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',13,'Ash','','アッシュ',0,0.0,'明るく抜ける音でアタックが強い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',12,'Alder','','アルダー',0,0.0,'バランスが良くクセが少ない。');</v>
       </c>
     </row>
     <row r="121" spans="2:11">
@@ -28221,14 +28227,14 @@
         <v>1778</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="D121" s="8"/>
       <c r="E121" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="G121" s="9">
         <v>0</v>
@@ -28237,11 +28243,11 @@
         <v>125</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="K121" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',14,'Basswood','','バスウッド',0,0.0,'軽く柔らかく、ウォームで扱いやすい。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',13,'Ash','','アッシュ',0,0.0,'明るく抜ける音でアタックが強い。');</v>
       </c>
     </row>
     <row r="122" spans="2:11">
@@ -28249,14 +28255,14 @@
         <v>1778</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>1402</v>
+        <v>1393</v>
       </c>
       <c r="D122" s="8"/>
       <c r="E122" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="G122" s="9">
         <v>0</v>
@@ -28265,11 +28271,11 @@
         <v>125</v>
       </c>
       <c r="I122" s="8" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="K122" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',15,'Poplar','','ポプラ',0,0.0,'軽く素直でクセが少ない。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',14,'Basswood','','バスウッド',0,0.0,'軽く柔らかく、ウォームで扱いやすい。');</v>
       </c>
     </row>
     <row r="123" spans="2:11">
@@ -28277,14 +28283,14 @@
         <v>1778</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="D123" s="8"/>
       <c r="E123" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="G123" s="9">
         <v>0</v>
@@ -28293,11 +28299,11 @@
         <v>125</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="K123" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',16,'Spruce','','スプルース',0,0.0,'軽く響きが良く、明るいトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',15,'Poplar','','ポプラ',0,0.0,'軽く素直でクセが少ない。');</v>
       </c>
     </row>
     <row r="124" spans="2:11">
@@ -28305,14 +28311,14 @@
         <v>1778</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="D124" s="8"/>
       <c r="E124" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F124" s="8" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="G124" s="9">
         <v>0</v>
@@ -28321,11 +28327,11 @@
         <v>125</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="K124" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',17,'Cedar','','シダー',0,0.0,'柔らかく温かい音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',16,'Spruce','','スプルース',0,0.0,'軽く響きが良く、明るいトーン。');</v>
       </c>
     </row>
     <row r="125" spans="2:11">
@@ -28333,14 +28339,14 @@
         <v>1778</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>1433</v>
+        <v>1399</v>
       </c>
       <c r="D125" s="8"/>
       <c r="E125" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="G125" s="9">
         <v>0</v>
@@ -28349,11 +28355,11 @@
         <v>125</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="K125" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',18,'IndianRosewood','','インディアンローズウッド',0,0.0,'甘く深みがあり、豊かな中低域。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',17,'Cedar','','シダー',0,0.0,'柔らかく温かい音。');</v>
       </c>
     </row>
     <row r="126" spans="2:11">
@@ -28361,14 +28367,14 @@
         <v>1778</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="D126" s="8"/>
       <c r="E126" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="G126" s="9">
         <v>0</v>
@@ -28377,11 +28383,11 @@
         <v>125</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="K126" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',19,'BrazilianRosewood','','ブラジリアンローズウッド',0,0.0,'濃厚で深いトーン、豊かな倍音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',18,'IndianRosewood','','インディアンローズウッド',0,0.0,'甘く深みがあり、豊かな中低域。');</v>
       </c>
     </row>
     <row r="127" spans="2:11">
@@ -28389,14 +28395,14 @@
         <v>1778</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>1394</v>
+        <v>1434</v>
       </c>
       <c r="D127" s="8"/>
       <c r="E127" s="8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="G127" s="9">
         <v>0</v>
@@ -28405,11 +28411,11 @@
         <v>125</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="K127" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',20,'Rosewood','','ローズウッド',0,0.0,'甘く丸い音で中域が豊か。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',19,'BrazilianRosewood','','ブラジリアンローズウッド',0,0.0,'濃厚で深いトーン、豊かな倍音。');</v>
       </c>
     </row>
     <row r="128" spans="2:11">
@@ -28417,14 +28423,14 @@
         <v>1778</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>1435</v>
+        <v>1394</v>
       </c>
       <c r="D128" s="8"/>
       <c r="E128" s="8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>1410</v>
+        <v>1453</v>
       </c>
       <c r="G128" s="9">
         <v>0</v>
@@ -28433,11 +28439,11 @@
         <v>125</v>
       </c>
       <c r="I128" s="8" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="K128" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',21,'PauFerro','','パーフェロー',0,0.0,'明るく硬質でタイトな音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',20,'Rosewood','','ローズウッド',0,0.0,'甘く丸い音で中域が豊か。');</v>
       </c>
     </row>
     <row r="129" spans="2:11">
@@ -28445,14 +28451,14 @@
         <v>1778</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>1400</v>
+        <v>1435</v>
       </c>
       <c r="D129" s="8"/>
       <c r="E129" s="8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="G129" s="9">
         <v>0</v>
@@ -28461,11 +28467,11 @@
         <v>125</v>
       </c>
       <c r="I129" s="8" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="K129" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',22,'Ovangkol','','オバンコール',0,0.0,'中域が豊かで温かいトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',21,'PauFerro','','パーフェロー',0,0.0,'明るく硬質でタイトな音。');</v>
       </c>
     </row>
     <row r="130" spans="2:11">
@@ -28473,14 +28479,14 @@
         <v>1778</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>1395</v>
+        <v>1400</v>
       </c>
       <c r="D130" s="8"/>
       <c r="E130" s="8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>1456</v>
+        <v>1411</v>
       </c>
       <c r="G130" s="9">
         <v>0</v>
@@ -28489,11 +28495,11 @@
         <v>125</v>
       </c>
       <c r="I130" s="8" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="K130" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',23,'Ebony','','エボニー',0,0.0,'硬くタイトで高域がクリア。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',22,'Ovangkol','','オバンコール',0,0.0,'中域が豊かで温かいトーン。');</v>
       </c>
     </row>
     <row r="131" spans="2:11">
@@ -28501,14 +28507,14 @@
         <v>1778</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="D131" s="8"/>
       <c r="E131" s="8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="G131" s="9">
         <v>0</v>
@@ -28517,11 +28523,11 @@
         <v>125</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>1416</v>
+        <v>1484</v>
       </c>
       <c r="K131" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',24,'Walnut','','ウォルナット',0,0.0,'中域が豊かで落ち着いたトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',23,'Ebony','','エボニー',0,0.0,'硬くタイトで高域がクリア。');</v>
       </c>
     </row>
     <row r="132" spans="2:11">
@@ -28529,14 +28535,14 @@
         <v>1778</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>1436</v>
+        <v>1396</v>
       </c>
       <c r="D132" s="8"/>
       <c r="E132" s="8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="G132" s="9">
         <v>0</v>
@@ -28545,11 +28551,11 @@
         <v>125</v>
       </c>
       <c r="I132" s="8" t="s">
-        <v>1485</v>
+        <v>1416</v>
       </c>
       <c r="K132" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',25,'Padauk','','パドゥーク',0,0.0,'明るく抜けが良く、個性的な響き。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',24,'Walnut','','ウォルナット',0,0.0,'中域が豊かで落ち着いたトーン。');</v>
       </c>
     </row>
     <row r="133" spans="2:11">
@@ -28557,14 +28563,14 @@
         <v>1778</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>1401</v>
+        <v>1436</v>
       </c>
       <c r="D133" s="8"/>
       <c r="E133" s="8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F133" s="8" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="G133" s="9">
         <v>0</v>
@@ -28573,11 +28579,11 @@
         <v>125</v>
       </c>
       <c r="I133" s="8" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="K133" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',26,'Koa','','コア',0,0.0,'明るく華やかで軽快。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',25,'Padauk','','パドゥーク',0,0.0,'明るく抜けが良く、個性的な響き。');</v>
       </c>
     </row>
     <row r="134" spans="2:11">
@@ -28585,14 +28591,14 @@
         <v>1778</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="D134" s="8"/>
       <c r="E134" s="8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F134" s="8" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="G134" s="9">
         <v>0</v>
@@ -28601,11 +28607,11 @@
         <v>125</v>
       </c>
       <c r="I134" s="8" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="K134" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',27,'Nato','','ナトー',0,0.0,'中低域が豊かで温かい。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',26,'Koa','','コア',0,0.0,'明るく華やかで軽快。');</v>
       </c>
     </row>
     <row r="135" spans="2:11">
@@ -28613,14 +28619,14 @@
         <v>1778</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="D135" s="8"/>
       <c r="E135" s="8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F135" s="8" t="s">
-        <v>1412</v>
+        <v>1460</v>
       </c>
       <c r="G135" s="9">
         <v>0</v>
@@ -28629,11 +28635,11 @@
         <v>125</v>
       </c>
       <c r="I135" s="8" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="K135" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',28,'Agathis','','アガチス',0,0.0,'柔らかくウォームで素直。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',27,'Nato','','ナトー',0,0.0,'中低域が豊かで温かい。');</v>
       </c>
     </row>
     <row r="136" spans="2:11">
@@ -28641,14 +28647,14 @@
         <v>1778</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="D136" s="8"/>
       <c r="E136" s="8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F136" s="8" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="G136" s="9">
         <v>0</v>
@@ -28657,11 +28663,11 @@
         <v>125</v>
       </c>
       <c r="I136" s="8" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="K136" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',29,'Bubinga','','ブビンガ',0,0.0,'重く硬質でサスティンが長い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',28,'Agathis','','アガチス',0,0.0,'柔らかくウォームで素直。');</v>
       </c>
     </row>
     <row r="137" spans="2:11">
@@ -28669,14 +28675,14 @@
         <v>1778</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="D137" s="8"/>
       <c r="E137" s="8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F137" s="8" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="G137" s="9">
         <v>0</v>
@@ -28685,11 +28691,11 @@
         <v>125</v>
       </c>
       <c r="I137" s="8" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="K137" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',30,'Wenge','','ウェンジ',0,0.0,'非常に硬くタイトで個性的。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',29,'Bubinga','','ブビンガ',0,0.0,'重く硬質でサスティンが長い。');</v>
       </c>
     </row>
     <row r="138" spans="2:11">
@@ -28697,14 +28703,14 @@
         <v>1778</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D138" s="8"/>
       <c r="E138" s="8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="G138" s="9">
         <v>0</v>
@@ -28713,11 +28719,11 @@
         <v>125</v>
       </c>
       <c r="I138" s="8" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="K138" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',31,'Purpleheart','','パープルハート',0,0.0,'硬く鮮やかでアタックが強い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',30,'Wenge','','ウェンジ',0,0.0,'非常に硬くタイトで個性的。');</v>
       </c>
     </row>
     <row r="139" spans="2:11">
@@ -28725,14 +28731,14 @@
         <v>1778</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>1437</v>
+        <v>1407</v>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>1461</v>
+        <v>1415</v>
       </c>
       <c r="G139" s="9">
         <v>0</v>
@@ -28741,11 +28747,11 @@
         <v>125</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="K139" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',32,'Zebrawood','','ゼブラウッド',0,0.0,'明るく硬質でクセのあるトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',31,'Purpleheart','','パープルハート',0,0.0,'硬く鮮やかでアタックが強い。');</v>
       </c>
     </row>
     <row r="140" spans="2:11">
@@ -28753,14 +28759,14 @@
         <v>1778</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>1558</v>
+        <v>1437</v>
       </c>
       <c r="D140" s="8"/>
       <c r="E140" s="8">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F140" s="8" t="s">
-        <v>1559</v>
+        <v>1461</v>
       </c>
       <c r="G140" s="9">
         <v>0</v>
@@ -28769,11 +28775,11 @@
         <v>125</v>
       </c>
       <c r="I140" s="8" t="s">
-        <v>1560</v>
+        <v>1492</v>
       </c>
       <c r="K140" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',33,'Okoume','','オクメ',0,0.0,'マホガニーに近く、中低域が豊かで軽量。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',32,'Zebrawood','','ゼブラウッド',0,0.0,'明るく硬質でクセのあるトーン。');</v>
       </c>
     </row>
     <row r="141" spans="2:11">
@@ -28781,14 +28787,14 @@
         <v>1778</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="D141" s="8"/>
       <c r="E141" s="8">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="G141" s="9">
         <v>0</v>
@@ -28797,11 +28803,11 @@
         <v>125</v>
       </c>
       <c r="I141" s="8" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="K141" s="5" t="str">
-        <f t="shared" ref="K141" si="17">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B141&amp;"'"&amp;","&amp;E141&amp;","&amp;"'"&amp;C141&amp;"'"&amp;","&amp;"'"&amp;D141&amp;"'"&amp;","&amp;"'"&amp;F141&amp;"'"&amp;","&amp;G141&amp;","&amp;H141&amp;","&amp;"'"&amp;I141&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',34,'Meranti','','メランティ',0,0.0,'中域寄りで温かめ、マホガニー系に近い。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',33,'Okoume','','オクメ',0,0.0,'マホガニーに近く、中低域が豊かで軽量。');</v>
       </c>
     </row>
     <row r="142" spans="2:11">
@@ -28809,14 +28815,14 @@
         <v>1778</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="D142" s="8"/>
       <c r="E142" s="8">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="G142" s="9">
         <v>0</v>
@@ -28825,11 +28831,11 @@
         <v>125</v>
       </c>
       <c r="I142" s="8" t="s">
-        <v>1569</v>
+        <v>1563</v>
       </c>
       <c r="K142" s="5" t="str">
-        <f t="shared" ref="K142" si="18">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B142&amp;"'"&amp;","&amp;E142&amp;","&amp;"'"&amp;C142&amp;"'"&amp;","&amp;"'"&amp;D142&amp;"'"&amp;","&amp;"'"&amp;F142&amp;"'"&amp;","&amp;G142&amp;","&amp;H142&amp;","&amp;"'"&amp;I142&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',35,'Sakura','','サクラ',0,0.0,'中高域が明るく立ち上がりが速い、日本らしい軽快で抜けの良いサウンド。');</v>
+        <f t="shared" ref="K142" si="17">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B142&amp;"'"&amp;","&amp;E142&amp;","&amp;"'"&amp;C142&amp;"'"&amp;","&amp;"'"&amp;D142&amp;"'"&amp;","&amp;"'"&amp;F142&amp;"'"&amp;","&amp;G142&amp;","&amp;H142&amp;","&amp;"'"&amp;I142&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',34,'Meranti','','メランティ',0,0.0,'中域寄りで温かめ、マホガニー系に近い。');</v>
       </c>
     </row>
     <row r="143" spans="2:11">
@@ -28837,14 +28843,14 @@
         <v>1778</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="D143" s="8"/>
       <c r="E143" s="8">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F143" s="8" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="G143" s="9">
         <v>0</v>
@@ -28853,11 +28859,11 @@
         <v>125</v>
       </c>
       <c r="I143" s="8" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="K143" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',36,'Tochi','','トチ',0,0.0,'メイプルに近いクリアさと華やかさを持ちつつ、やや柔らかく豊かな倍音.');</v>
+        <f t="shared" ref="K143" si="18">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B143&amp;"'"&amp;","&amp;E143&amp;","&amp;"'"&amp;C143&amp;"'"&amp;","&amp;"'"&amp;D143&amp;"'"&amp;","&amp;"'"&amp;F143&amp;"'"&amp;","&amp;G143&amp;","&amp;H143&amp;","&amp;"'"&amp;I143&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',35,'Sakura','','サクラ',0,0.0,'中高域が明るく立ち上がりが速い、日本らしい軽快で抜けの良いサウンド。');</v>
       </c>
     </row>
     <row r="144" spans="2:11">
@@ -28865,14 +28871,14 @@
         <v>1778</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>1424</v>
+        <v>1566</v>
       </c>
       <c r="D144" s="8"/>
       <c r="E144" s="8">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="F144" s="8" t="s">
-        <v>1423</v>
+        <v>1567</v>
       </c>
       <c r="G144" s="9">
         <v>0</v>
@@ -28880,62 +28886,64 @@
       <c r="H144" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="I144" s="8"/>
+      <c r="I144" s="8" t="s">
+        <v>1568</v>
+      </c>
       <c r="K144" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B144&amp;"'"&amp;","&amp;E144&amp;","&amp;"'"&amp;C144&amp;"'"&amp;","&amp;"'"&amp;D144&amp;"'"&amp;","&amp;"'"&amp;F144&amp;"'"&amp;","&amp;G144&amp;","&amp;H144&amp;","&amp;"'"&amp;I144&amp;"'"&amp;");"</f>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',36,'Tochi','','トチ',0,0.0,'メイプルに近いクリアさと華やかさを持ちつつ、やや柔らかく豊かな倍音.');</v>
+      </c>
+    </row>
+    <row r="145" spans="2:11">
+      <c r="B145" s="8" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D145" s="8"/>
+      <c r="E145" s="8">
+        <v>99</v>
+      </c>
+      <c r="F145" s="8" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G145" s="9">
+        <v>0</v>
+      </c>
+      <c r="H145" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I145" s="8"/>
+      <c r="K145" s="5" t="str">
+        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B145&amp;"'"&amp;","&amp;E145&amp;","&amp;"'"&amp;C145&amp;"'"&amp;","&amp;"'"&amp;D145&amp;"'"&amp;","&amp;"'"&amp;F145&amp;"'"&amp;","&amp;G145&amp;","&amp;H145&amp;","&amp;"'"&amp;I145&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('guitar_woods',99,'Unknown','','？？',0,0.0,'');</v>
       </c>
     </row>
-    <row r="145" spans="2:11">
-      <c r="B145" s="6" t="s">
+    <row r="146" spans="2:11">
+      <c r="B146" s="6" t="s">
         <v>1503</v>
       </c>
-      <c r="C145" s="6" t="s">
+      <c r="C146" s="6" t="s">
         <v>1502</v>
       </c>
-      <c r="D145" s="6" t="s">
+      <c r="D146" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E145" s="7" t="s">
+      <c r="E146" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F145" s="6" t="s">
+      <c r="F146" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G145" s="6" t="s">
+      <c r="G146" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H145" s="6" t="s">
+      <c r="H146" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I145" s="6" t="s">
+      <c r="I146" s="6" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="146" spans="2:11">
-      <c r="B146" s="8" t="s">
-        <v>1779</v>
-      </c>
-      <c r="C146" s="8" t="s">
-        <v>1504</v>
-      </c>
-      <c r="D146" s="8"/>
-      <c r="E146" s="8">
-        <v>1</v>
-      </c>
-      <c r="F146" s="8" t="s">
-        <v>1520</v>
-      </c>
-      <c r="G146" s="9">
-        <v>0</v>
-      </c>
-      <c r="H146" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I146" s="8"/>
-      <c r="K146" s="5" t="str">
-        <f t="shared" ref="K146:K168" si="19">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B146&amp;"'"&amp;","&amp;E146&amp;","&amp;"'"&amp;C146&amp;"'"&amp;","&amp;"'"&amp;D146&amp;"'"&amp;","&amp;"'"&amp;F146&amp;"'"&amp;","&amp;G146&amp;","&amp;H146&amp;","&amp;"'"&amp;I146&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',1,'Red','','レッド',0,0.0,'');</v>
       </c>
     </row>
     <row r="147" spans="2:11">
@@ -28943,14 +28951,14 @@
         <v>1779</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>1518</v>
+        <v>1504</v>
       </c>
       <c r="D147" s="8"/>
       <c r="E147" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F147" s="8" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="G147" s="9">
         <v>0</v>
@@ -28960,8 +28968,8 @@
       </c>
       <c r="I147" s="8"/>
       <c r="K147" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',2,'Pink','','ピンク',0,0.0,'');</v>
+        <f t="shared" ref="K147:K169" si="19">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B147&amp;"'"&amp;","&amp;E147&amp;","&amp;"'"&amp;C147&amp;"'"&amp;","&amp;"'"&amp;D147&amp;"'"&amp;","&amp;"'"&amp;F147&amp;"'"&amp;","&amp;G147&amp;","&amp;H147&amp;","&amp;"'"&amp;I147&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',1,'Red','','レッド',0,0.0,'');</v>
       </c>
     </row>
     <row r="148" spans="2:11">
@@ -28969,14 +28977,14 @@
         <v>1779</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>1505</v>
+        <v>1518</v>
       </c>
       <c r="D148" s="8"/>
       <c r="E148" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F148" s="8" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="G148" s="9">
         <v>0</v>
@@ -28987,7 +28995,7 @@
       <c r="I148" s="8"/>
       <c r="K148" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',3,'Orange','','オレンジ',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',2,'Pink','','ピンク',0,0.0,'');</v>
       </c>
     </row>
     <row r="149" spans="2:11">
@@ -28995,14 +29003,14 @@
         <v>1779</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="D149" s="8"/>
       <c r="E149" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F149" s="8" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="G149" s="9">
         <v>0</v>
@@ -29013,7 +29021,7 @@
       <c r="I149" s="8"/>
       <c r="K149" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',4,'Yellow','','イエロー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',3,'Orange','','オレンジ',0,0.0,'');</v>
       </c>
     </row>
     <row r="150" spans="2:11">
@@ -29021,14 +29029,14 @@
         <v>1779</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D150" s="8"/>
       <c r="E150" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="G150" s="9">
         <v>0</v>
@@ -29039,7 +29047,7 @@
       <c r="I150" s="8"/>
       <c r="K150" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',5,'Green','','グリーン',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',4,'Yellow','','イエロー',0,0.0,'');</v>
       </c>
     </row>
     <row r="151" spans="2:11">
@@ -29047,14 +29055,14 @@
         <v>1779</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="D151" s="8"/>
       <c r="E151" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="G151" s="9">
         <v>0</v>
@@ -29065,7 +29073,7 @@
       <c r="I151" s="8"/>
       <c r="K151" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',6,'SkyBlue','','スカイブルー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',5,'Green','','グリーン',0,0.0,'');</v>
       </c>
     </row>
     <row r="152" spans="2:11">
@@ -29073,14 +29081,14 @@
         <v>1779</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="D152" s="8"/>
       <c r="E152" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F152" s="8" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="G152" s="9">
         <v>0</v>
@@ -29091,7 +29099,7 @@
       <c r="I152" s="8"/>
       <c r="K152" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',7,'Blue','','ブルー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',6,'SkyBlue','','スカイブルー',0,0.0,'');</v>
       </c>
     </row>
     <row r="153" spans="2:11">
@@ -29099,14 +29107,14 @@
         <v>1779</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="D153" s="8"/>
       <c r="E153" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="G153" s="9">
         <v>0</v>
@@ -29117,7 +29125,7 @@
       <c r="I153" s="8"/>
       <c r="K153" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',8,'Purple','','パープル',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',7,'Blue','','ブルー',0,0.0,'');</v>
       </c>
     </row>
     <row r="154" spans="2:11">
@@ -29125,14 +29133,14 @@
         <v>1779</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="D154" s="8"/>
       <c r="E154" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="G154" s="9">
         <v>0</v>
@@ -29143,7 +29151,7 @@
       <c r="I154" s="8"/>
       <c r="K154" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',9,'Gray','','グレー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',8,'Purple','','パープル',0,0.0,'');</v>
       </c>
     </row>
     <row r="155" spans="2:11">
@@ -29151,14 +29159,14 @@
         <v>1779</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="D155" s="8"/>
       <c r="E155" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F155" s="8" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="G155" s="9">
         <v>0</v>
@@ -29169,7 +29177,7 @@
       <c r="I155" s="8"/>
       <c r="K155" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',10,'Black','','ブラック',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',9,'Gray','','グレー',0,0.0,'');</v>
       </c>
     </row>
     <row r="156" spans="2:11">
@@ -29177,14 +29185,14 @@
         <v>1779</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="D156" s="8"/>
       <c r="E156" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F156" s="8" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="G156" s="9">
         <v>0</v>
@@ -29195,7 +29203,7 @@
       <c r="I156" s="8"/>
       <c r="K156" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',11,'White','','ホワイト',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',10,'Black','','ブラック',0,0.0,'');</v>
       </c>
     </row>
     <row r="157" spans="2:11">
@@ -29203,14 +29211,14 @@
         <v>1779</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="D157" s="8"/>
       <c r="E157" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F157" s="8" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="G157" s="9">
         <v>0</v>
@@ -29221,7 +29229,7 @@
       <c r="I157" s="8"/>
       <c r="K157" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',12,'Natural','','ナチュラル',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',11,'White','','ホワイト',0,0.0,'');</v>
       </c>
     </row>
     <row r="158" spans="2:11">
@@ -29229,14 +29237,14 @@
         <v>1779</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>1519</v>
+        <v>1514</v>
       </c>
       <c r="D158" s="8"/>
       <c r="E158" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="G158" s="9">
         <v>0</v>
@@ -29247,7 +29255,7 @@
       <c r="I158" s="8"/>
       <c r="K158" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',13,'Brown','','ブラウン',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',12,'Natural','','ナチュラル',0,0.0,'');</v>
       </c>
     </row>
     <row r="159" spans="2:11">
@@ -29255,14 +29263,14 @@
         <v>1779</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="D159" s="8"/>
       <c r="E159" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="G159" s="9">
         <v>0</v>
@@ -29273,7 +29281,7 @@
       <c r="I159" s="8"/>
       <c r="K159" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',14,'Gold','','ゴールド',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',13,'Brown','','ブラウン',0,0.0,'');</v>
       </c>
     </row>
     <row r="160" spans="2:11">
@@ -29281,14 +29289,14 @@
         <v>1779</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="D160" s="8"/>
       <c r="E160" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F160" s="8" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="G160" s="9">
         <v>0</v>
@@ -29299,7 +29307,7 @@
       <c r="I160" s="8"/>
       <c r="K160" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',15,'Silver','','シルバー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',14,'Gold','','ゴールド',0,0.0,'');</v>
       </c>
     </row>
     <row r="161" spans="2:11">
@@ -29307,14 +29315,14 @@
         <v>1779</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D161" s="8"/>
       <c r="E161" s="8">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="F161" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G161" s="9">
         <v>0</v>
@@ -29325,59 +29333,59 @@
       <c r="I161" s="8"/>
       <c r="K161" s="5" t="str">
         <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',15,'Silver','','シルバー',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="162" spans="2:11">
+      <c r="B162" s="8" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C162" s="8" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D162" s="8"/>
+      <c r="E162" s="8">
+        <v>99</v>
+      </c>
+      <c r="F162" s="8" t="s">
+        <v>1535</v>
+      </c>
+      <c r="G162" s="9">
+        <v>0</v>
+      </c>
+      <c r="H162" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I162" s="8"/>
+      <c r="K162" s="5" t="str">
+        <f t="shared" si="19"/>
         <v>INSERT INTO m_code VALUES ('guitar_colors',99,'Others','','その他',0,0.0,'');</v>
       </c>
     </row>
-    <row r="162" spans="2:11">
-      <c r="B162" s="6" t="s">
+    <row r="163" spans="2:11">
+      <c r="B163" s="6" t="s">
         <v>1888</v>
       </c>
-      <c r="C162" s="6" t="s">
+      <c r="C163" s="6" t="s">
         <v>1889</v>
       </c>
-      <c r="D162" s="6" t="s">
+      <c r="D163" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E162" s="7" t="s">
+      <c r="E163" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F162" s="6" t="s">
+      <c r="F163" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G162" s="6" t="s">
+      <c r="G163" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H162" s="6" t="s">
+      <c r="H163" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I162" s="6" t="s">
+      <c r="I163" s="6" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="163" spans="2:11">
-      <c r="B163" s="8" t="s">
-        <v>1892</v>
-      </c>
-      <c r="C163" s="8" t="s">
-        <v>1890</v>
-      </c>
-      <c r="D163" s="8"/>
-      <c r="E163" s="8">
-        <v>1</v>
-      </c>
-      <c r="F163" s="8"/>
-      <c r="G163" s="9">
-        <v>0</v>
-      </c>
-      <c r="H163" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I163" s="8" t="s">
-        <v>1893</v>
-      </c>
-      <c r="K163" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',1,'SUCCESS','','',0,0.0,'処理成功');</v>
       </c>
     </row>
     <row r="164" spans="2:11">
@@ -29385,11 +29393,11 @@
         <v>1892</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="D164" s="8"/>
       <c r="E164" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F164" s="8"/>
       <c r="G164" s="9">
@@ -29399,11 +29407,11 @@
         <v>125</v>
       </c>
       <c r="I164" s="8" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="K164" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',2,'STARTED','','',0,0.0,'処理開始。いずかのステータスに遷移する。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',1,'SUCCESS','','',0,0.0,'処理成功');</v>
       </c>
     </row>
     <row r="165" spans="2:11">
@@ -29411,11 +29419,11 @@
         <v>1892</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>1881</v>
+        <v>1891</v>
       </c>
       <c r="D165" s="8"/>
       <c r="E165" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F165" s="8"/>
       <c r="G165" s="9">
@@ -29425,11 +29433,11 @@
         <v>125</v>
       </c>
       <c r="I165" s="8" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="K165" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',3,'NOT_STARTED','','',0,0.0,'予定時刻に開始されていない。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',2,'STARTED','','',0,0.0,'処理開始。いずかのステータスに遷移する。');</v>
       </c>
     </row>
     <row r="166" spans="2:11">
@@ -29437,11 +29445,11 @@
         <v>1892</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="D166" s="8"/>
       <c r="E166" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F166" s="8"/>
       <c r="G166" s="9">
@@ -29451,11 +29459,11 @@
         <v>125</v>
       </c>
       <c r="I166" s="8" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="K166" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',4,'ERROR','','',0,0.0,'例外、パニック等が発生した。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',3,'NOT_STARTED','','',0,0.0,'予定時刻に開始されていない。');</v>
       </c>
     </row>
     <row r="167" spans="2:11">
@@ -29463,11 +29471,11 @@
         <v>1892</v>
       </c>
       <c r="C167" s="8" t="s">
-        <v>1882</v>
+        <v>1879</v>
       </c>
       <c r="D167" s="8"/>
       <c r="E167" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F167" s="8"/>
       <c r="G167" s="9">
@@ -29477,11 +29485,11 @@
         <v>125</v>
       </c>
       <c r="I167" s="8" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="K167" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',5,'SLOW','','',0,0.0,'想定時間内に処理が終了しなかった。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',4,'ERROR','','',0,0.0,'例外、パニック等が発生した。');</v>
       </c>
     </row>
     <row r="168" spans="2:11">
@@ -29489,11 +29497,11 @@
         <v>1892</v>
       </c>
       <c r="C168" s="8" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="D168" s="8"/>
       <c r="E168" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F168" s="8"/>
       <c r="G168" s="9">
@@ -29503,9 +29511,35 @@
         <v>125</v>
       </c>
       <c r="I168" s="8" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K168" s="5" t="str">
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('batch_status',5,'SLOW','','',0,0.0,'想定時間内に処理が終了しなかった。');</v>
+      </c>
+    </row>
+    <row r="169" spans="2:11">
+      <c r="B169" s="8" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C169" s="8" t="s">
+        <v>1880</v>
+      </c>
+      <c r="D169" s="8"/>
+      <c r="E169" s="8">
+        <v>6</v>
+      </c>
+      <c r="F169" s="8"/>
+      <c r="G169" s="9">
+        <v>0</v>
+      </c>
+      <c r="H169" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I169" s="8" t="s">
         <v>1897</v>
       </c>
-      <c r="K168" s="5" t="str">
+      <c r="K169" s="5" t="str">
         <f t="shared" si="19"/>
         <v>INSERT INTO m_code VALUES ('batch_status',6,'TIMEOUT','','',0,0.0,'時間内に処理が終了しなかった。');</v>
       </c>
@@ -33064,7 +33098,7 @@
         <v>150</v>
       </c>
       <c r="L6" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;H6&amp;","&amp;VLOOKUP(I6,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;H6&amp;","&amp;VLOOKUP(I6,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster001','キラービー',1,110,12,16,0.3,1);</v>
       </c>
     </row>
@@ -33097,7 +33131,7 @@
         <v>150</v>
       </c>
       <c r="L7" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;H7&amp;","&amp;VLOOKUP(I7,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;H7&amp;","&amp;VLOOKUP(I7,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster002','アサシンバグ',1,132,15,20,0.3,1);</v>
       </c>
     </row>
@@ -33130,7 +33164,7 @@
         <v>150</v>
       </c>
       <c r="L8" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;H8&amp;","&amp;VLOOKUP(I8,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;H8&amp;","&amp;VLOOKUP(I8,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster003','ラスターバグ',1,158,19,26,0.3,1);</v>
       </c>
     </row>
@@ -33160,7 +33194,7 @@
         <v>34</v>
       </c>
       <c r="L9" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;H9&amp;","&amp;VLOOKUP(I9,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;H9&amp;","&amp;VLOOKUP(I9,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster004','カーミラ',2,100,10,13,0.13,2);</v>
       </c>
     </row>
@@ -33193,7 +33227,7 @@
         <v>34</v>
       </c>
       <c r="L10" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;H10&amp;","&amp;VLOOKUP(I10,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;H10&amp;","&amp;VLOOKUP(I10,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster005','カーミラクイーン',2,120,13,16,0.15,2);</v>
       </c>
     </row>
@@ -33223,7 +33257,7 @@
         <v>36</v>
       </c>
       <c r="L11" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;H11&amp;","&amp;VLOOKUP(I11,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;H11&amp;","&amp;VLOOKUP(I11,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster006','デーモン',3,130,15,7,0.08,5);</v>
       </c>
     </row>
@@ -33256,7 +33290,7 @@
         <v>36</v>
       </c>
       <c r="L12" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;H12&amp;","&amp;VLOOKUP(I12,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;H12&amp;","&amp;VLOOKUP(I12,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster007','グレートデーモン',3,156,19,9,0.1,5);</v>
       </c>
     </row>
@@ -33286,7 +33320,7 @@
         <v>35</v>
       </c>
       <c r="L13" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;H13&amp;","&amp;VLOOKUP(I13,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;H13&amp;","&amp;VLOOKUP(I13,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster008','ゴブリン',4,120,11,10,0.15,4);</v>
       </c>
     </row>
@@ -33319,7 +33353,7 @@
         <v>35</v>
       </c>
       <c r="L14" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;H14&amp;","&amp;VLOOKUP(I14,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;H14&amp;","&amp;VLOOKUP(I14,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster009','ゴブリンガード',4,144,14,13,0.15,4);</v>
       </c>
     </row>
@@ -33352,7 +33386,7 @@
         <v>35</v>
       </c>
       <c r="L15" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;H15&amp;","&amp;VLOOKUP(I15,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;H15&amp;","&amp;VLOOKUP(I15,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster010','ゴブリンロード',4,172,18,16,0.15,4);</v>
       </c>
     </row>
@@ -33382,7 +33416,7 @@
         <v>151</v>
       </c>
       <c r="L16" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;H16&amp;","&amp;VLOOKUP(I16,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;H16&amp;","&amp;VLOOKUP(I16,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster011','マシンゴーレム',5,140,17,5,0.02,3);</v>
       </c>
     </row>
@@ -33415,7 +33449,7 @@
         <v>151</v>
       </c>
       <c r="L17" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;H17&amp;","&amp;VLOOKUP(I17,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;H17&amp;","&amp;VLOOKUP(I17,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster012','ガーディアン',5,168,22,6,0.04,3);</v>
       </c>
     </row>
@@ -33448,7 +33482,7 @@
         <v>151</v>
       </c>
       <c r="L18" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;H18&amp;","&amp;VLOOKUP(I18,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;H18&amp;","&amp;VLOOKUP(I18,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster013','デスマシン',5,201,28,7,0.05,3);</v>
       </c>
     </row>
@@ -33478,7 +33512,7 @@
         <v>35</v>
       </c>
       <c r="L19" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;H19&amp;","&amp;VLOOKUP(I19,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;H19&amp;","&amp;VLOOKUP(I19,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster014','ハーピー',6,100,8,14,0.2,4);</v>
       </c>
     </row>
@@ -33511,7 +33545,7 @@
         <v>35</v>
       </c>
       <c r="L20" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;H20&amp;","&amp;VLOOKUP(I20,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;H20&amp;","&amp;VLOOKUP(I20,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster015','セイレーン',6,120,10,18,0.23,4);</v>
       </c>
     </row>
@@ -33541,7 +33575,7 @@
         <v>34</v>
       </c>
       <c r="L21" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;H21&amp;","&amp;VLOOKUP(I21,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;H21&amp;","&amp;VLOOKUP(I21,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster016','アーマーナイト',7,120,13,8,0.05,2);</v>
       </c>
     </row>
@@ -33574,7 +33608,7 @@
         <v>34</v>
       </c>
       <c r="L22" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;H22&amp;","&amp;VLOOKUP(I22,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;H22&amp;","&amp;VLOOKUP(I22,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster017','ダークナイト',7,144,16,10,0.05,2);</v>
       </c>
     </row>
@@ -33607,7 +33641,7 @@
         <v>34</v>
       </c>
       <c r="L23" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;H23&amp;","&amp;VLOOKUP(I23,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;H23&amp;","&amp;VLOOKUP(I23,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster018','ターミネータ',7,172,20,13,0.07,2);</v>
       </c>
     </row>
@@ -33637,7 +33671,7 @@
         <v>35</v>
       </c>
       <c r="L24" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;H24&amp;","&amp;VLOOKUP(I24,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;H24&amp;","&amp;VLOOKUP(I24,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster019','マジシャン',8,100,9,12,0.1,4);</v>
       </c>
     </row>
@@ -33670,7 +33704,7 @@
         <v>35</v>
       </c>
       <c r="L25" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;H25&amp;","&amp;VLOOKUP(I25,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;H25&amp;","&amp;VLOOKUP(I25,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster020','ウィザード',8,120,11,15,0.11,4);</v>
       </c>
     </row>
@@ -33703,7 +33737,7 @@
         <v>35</v>
       </c>
       <c r="L26" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;H26&amp;","&amp;VLOOKUP(I26,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;H26&amp;","&amp;VLOOKUP(I26,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster021','ハイウィザード',8,144,14,19,0.12,4);</v>
       </c>
     </row>
@@ -33733,7 +33767,7 @@
         <v>150</v>
       </c>
       <c r="L27" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;H27&amp;","&amp;VLOOKUP(I27,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;H27&amp;","&amp;VLOOKUP(I27,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster022','マイコニド',9,120,10,12,0.15,1);</v>
       </c>
     </row>
@@ -33766,7 +33800,7 @@
         <v>150</v>
       </c>
       <c r="L28" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;H28&amp;","&amp;VLOOKUP(I28,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;H28&amp;","&amp;VLOOKUP(I28,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster023','ダースマタンゴ',9,144,13,15,0.15,1);</v>
       </c>
     </row>
@@ -33796,7 +33830,7 @@
         <v>151</v>
       </c>
       <c r="L29" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;H29&amp;","&amp;VLOOKUP(I29,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;H29&amp;","&amp;VLOOKUP(I29,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster024','ニードルバード',10,100,13,16,0.25,3);</v>
       </c>
     </row>
@@ -33829,7 +33863,7 @@
         <v>151</v>
       </c>
       <c r="L30" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;H30&amp;","&amp;VLOOKUP(I30,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;H30&amp;","&amp;VLOOKUP(I30,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster025','コカトバード',10,120,16,20,0.27,3);</v>
       </c>
     </row>
@@ -33859,7 +33893,7 @@
         <v>151</v>
       </c>
       <c r="L31" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;H31&amp;","&amp;VLOOKUP(I31,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;H31&amp;","&amp;VLOOKUP(I31,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster026','プチドラゴン',11,130,13,8,0.08,3);</v>
       </c>
     </row>
@@ -33892,7 +33926,7 @@
         <v>36</v>
       </c>
       <c r="L32" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;H32&amp;","&amp;VLOOKUP(I32,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;H32&amp;","&amp;VLOOKUP(I32,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster027','プチドラゾンビ',11,156,16,10,0.1,5);</v>
       </c>
     </row>
@@ -33925,7 +33959,7 @@
         <v>150</v>
       </c>
       <c r="L33" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;H33&amp;","&amp;VLOOKUP(I33,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;H33&amp;","&amp;VLOOKUP(I33,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster028','フロストドラゴン',11,187,20,13,0.12,1);</v>
       </c>
     </row>
@@ -33958,7 +33992,7 @@
         <v>37</v>
       </c>
       <c r="L34" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;H34&amp;","&amp;VLOOKUP(I34,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;H34&amp;","&amp;VLOOKUP(I34,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster029','プチティアマット',11,224,26,16,0.13,6);</v>
       </c>
     </row>
@@ -33988,7 +34022,7 @@
         <v>37</v>
       </c>
       <c r="L35" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;H35&amp;","&amp;VLOOKUP(I35,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;H35&amp;","&amp;VLOOKUP(I35,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster030','ポト',12,100,10,16,0.18,6);</v>
       </c>
     </row>
@@ -34021,7 +34055,7 @@
         <v>37</v>
       </c>
       <c r="L36" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;H36&amp;","&amp;VLOOKUP(I36,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;H36&amp;","&amp;VLOOKUP(I36,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster031','マーマポト',12,120,13,20,0.2,6);</v>
       </c>
     </row>
@@ -34054,7 +34088,7 @@
         <v>37</v>
       </c>
       <c r="L37" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;H37&amp;","&amp;VLOOKUP(I37,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;H37&amp;","&amp;VLOOKUP(I37,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster032','パーパポト',12,141,16,26,0.22,6);</v>
       </c>
     </row>
@@ -34084,7 +34118,7 @@
         <v>37</v>
       </c>
       <c r="L38" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;H38&amp;","&amp;VLOOKUP(I38,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;H38&amp;","&amp;VLOOKUP(I38,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster033','プリースト',13,100,9,13,0.1,6);</v>
       </c>
     </row>
@@ -34117,7 +34151,7 @@
         <v>36</v>
       </c>
       <c r="L39" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;H39&amp;","&amp;VLOOKUP(I39,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;H39&amp;","&amp;VLOOKUP(I39,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster034','カオスソーサラー',13,120,11,16,0.11,5);</v>
       </c>
     </row>
@@ -34150,7 +34184,7 @@
         <v>36</v>
       </c>
       <c r="L40" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;H40&amp;","&amp;VLOOKUP(I40,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;H40&amp;","&amp;VLOOKUP(I40,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster035','イビルシャーマン',13,144,14,20,0.13,5);</v>
       </c>
     </row>
@@ -34181,7 +34215,7 @@
         <v>37</v>
       </c>
       <c r="L41" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;H41&amp;","&amp;VLOOKUP(I41,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;H41&amp;","&amp;VLOOKUP(I41,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster036','ラビ',14,100,11,16,0.16,6);</v>
       </c>
     </row>
@@ -34214,7 +34248,7 @@
         <v>37</v>
       </c>
       <c r="L42" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;H42&amp;","&amp;VLOOKUP(I42,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;H42&amp;","&amp;VLOOKUP(I42,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster037','ラビリオン',14,120,14,20,0.17,6);</v>
       </c>
     </row>
@@ -34247,7 +34281,7 @@
         <v>37</v>
       </c>
       <c r="L43" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;H43&amp;","&amp;VLOOKUP(I43,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;H43&amp;","&amp;VLOOKUP(I43,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster038','キングラビ',14,144,18,26,0.18,6);</v>
       </c>
     </row>
@@ -34280,7 +34314,7 @@
         <v>37</v>
       </c>
       <c r="L44" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;H44&amp;","&amp;VLOOKUP(I44,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;H44&amp;","&amp;VLOOKUP(I44,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster039','グレートラビ',14,172,23,33,0.2,6);</v>
       </c>
     </row>
@@ -34310,7 +34344,7 @@
         <v>34</v>
       </c>
       <c r="L45" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;H45&amp;","&amp;VLOOKUP(I45,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;H45&amp;","&amp;VLOOKUP(I45,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster040','スライム',15,100,10,18,0.15,2);</v>
       </c>
     </row>
@@ -34343,7 +34377,7 @@
         <v>150</v>
       </c>
       <c r="L46" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;H46&amp;","&amp;VLOOKUP(I46,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;H46&amp;","&amp;VLOOKUP(I46,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster041','ブルーババロア',15,120,13,23,0.15,1);</v>
       </c>
     </row>
@@ -34376,7 +34410,7 @@
         <v>151</v>
       </c>
       <c r="L47" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;H47&amp;","&amp;VLOOKUP(I47,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;H47&amp;","&amp;VLOOKUP(I47,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster042','レッドマシュマロ',15,141,16,29,0.15,3);</v>
       </c>
     </row>
@@ -34406,7 +34440,7 @@
         <v>36</v>
       </c>
       <c r="L48" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;H48&amp;","&amp;VLOOKUP(I48,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;H48&amp;","&amp;VLOOKUP(I48,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster043','イビルソード',16,110,15,13,0.14,5);</v>
       </c>
     </row>
@@ -34439,7 +34473,7 @@
         <v>36</v>
       </c>
       <c r="L49" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;H49&amp;","&amp;VLOOKUP(I49,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;H49&amp;","&amp;VLOOKUP(I49,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster044','イビルウェポン',16,132,19,16,0.15,5);</v>
       </c>
     </row>
@@ -34472,7 +34506,7 @@
         <v>37</v>
       </c>
       <c r="L50" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;H50&amp;","&amp;VLOOKUP(I50,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;H50&amp;","&amp;VLOOKUP(I50,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster045','エレメントソード',16,158,24,20,0.16,6);</v>
       </c>
     </row>
@@ -34502,7 +34536,7 @@
         <v>150</v>
       </c>
       <c r="L51" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;H51&amp;","&amp;VLOOKUP(I51,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;H51&amp;","&amp;VLOOKUP(I51,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster046','ケルベロス',17,110,11,19,0.18,1);</v>
       </c>
     </row>
@@ -34535,7 +34569,7 @@
         <v>150</v>
       </c>
       <c r="L52" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;H52&amp;","&amp;VLOOKUP(I52,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;H52&amp;","&amp;VLOOKUP(I52,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster047','バウンドウルフ',17,132,14,24,0.2,1);</v>
       </c>
     </row>
@@ -34568,7 +34602,7 @@
         <v>150</v>
       </c>
       <c r="L53" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;H53&amp;","&amp;VLOOKUP(I53,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;H53&amp;","&amp;VLOOKUP(I53,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster048','ジャッカル',17,158,18,31,0.21,1);</v>
       </c>
     </row>
@@ -34598,7 +34632,7 @@
         <v>151</v>
       </c>
       <c r="L54" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;H54&amp;","&amp;VLOOKUP(I54,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;H54&amp;","&amp;VLOOKUP(I54,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster049','ダックソルジャー',18,120,16,14,0.15,3);</v>
       </c>
     </row>
@@ -34628,7 +34662,7 @@
         <v>151</v>
       </c>
       <c r="L55" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;H55&amp;","&amp;VLOOKUP(I55,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;H55&amp;","&amp;VLOOKUP(I55,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster050','ダックジェネラル',18,160,24,20,0.15,3);</v>
       </c>
     </row>
@@ -34658,7 +34692,7 @@
         <v>34</v>
       </c>
       <c r="L56" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;H56&amp;","&amp;VLOOKUP(I56,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;H56&amp;","&amp;VLOOKUP(I56,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster051','モールベア',19,130,14,18,0.18,2);</v>
       </c>
     </row>
@@ -34688,7 +34722,7 @@
         <v>34</v>
       </c>
       <c r="L57" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;H57&amp;","&amp;VLOOKUP(I57,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;H57&amp;","&amp;VLOOKUP(I57,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster052','ニードリオン',19,170,18,26,0.2,2);</v>
       </c>
     </row>
@@ -34718,7 +34752,7 @@
         <v>35</v>
       </c>
       <c r="L58" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;H58&amp;","&amp;VLOOKUP(I58,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;H58&amp;","&amp;VLOOKUP(I58,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster053','ギャルビー',20,120,13,16,0.2,4);</v>
       </c>
     </row>
@@ -34751,7 +34785,7 @@
         <v>35</v>
       </c>
       <c r="L59" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;H59&amp;","&amp;VLOOKUP(I59,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;H59&amp;","&amp;VLOOKUP(I59,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster054','レディビー',20,144,16,20,0.22,4);</v>
       </c>
     </row>
@@ -34784,7 +34818,7 @@
         <v>35</v>
       </c>
       <c r="L60" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;H60&amp;","&amp;VLOOKUP(I60,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;H60&amp;","&amp;VLOOKUP(I60,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster055','クインビー',20,172,20,26,0.23,4);</v>
       </c>
     </row>
@@ -34814,7 +34848,7 @@
         <v>150</v>
       </c>
       <c r="L61" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;H61&amp;","&amp;VLOOKUP(I61,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;H61&amp;","&amp;VLOOKUP(I61,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster056','サハギン',21,130,16,16,0.15,1);</v>
       </c>
     </row>
@@ -34844,7 +34878,7 @@
         <v>150</v>
       </c>
       <c r="L62" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;H62&amp;","&amp;VLOOKUP(I62,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;H62&amp;","&amp;VLOOKUP(I62,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster057','プチポセイドン',21,150,22,19,0.15,1);</v>
       </c>
     </row>
@@ -34874,7 +34908,7 @@
         <v>298</v>
       </c>
       <c r="L63" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;H63&amp;","&amp;VLOOKUP(I63,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;H63&amp;","&amp;VLOOKUP(I63,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster058','クロウラー',22,130,15,11,0.08,2);</v>
       </c>
     </row>
@@ -34907,7 +34941,7 @@
         <v>34</v>
       </c>
       <c r="L64" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;H64&amp;","&amp;VLOOKUP(I64,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;H64&amp;","&amp;VLOOKUP(I64,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster059','メガクロウラー',22,156,19,14,0.09,2);</v>
       </c>
     </row>
@@ -34940,7 +34974,7 @@
         <v>34</v>
       </c>
       <c r="L65" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;H65&amp;","&amp;VLOOKUP(I65,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;H65&amp;","&amp;VLOOKUP(I65,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster060','ギガクロウラー',22,187,24,18,0.1,2);</v>
       </c>
     </row>
@@ -34970,7 +35004,7 @@
         <v>34</v>
       </c>
       <c r="L66" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;H66&amp;","&amp;VLOOKUP(I66,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;H66&amp;","&amp;VLOOKUP(I66,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster061','ぱっくんオタマ',23,110,12,10,0.15,2);</v>
       </c>
     </row>
@@ -35003,7 +35037,7 @@
         <v>34</v>
       </c>
       <c r="L67" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;H67&amp;","&amp;VLOOKUP(I67,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;H67&amp;","&amp;VLOOKUP(I67,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster062','ぱっくりオタマ',23,132,15,13,0.15,2);</v>
       </c>
     </row>
@@ -35036,7 +35070,7 @@
         <v>151</v>
       </c>
       <c r="L68" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;H68&amp;","&amp;VLOOKUP(I68,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;H68&amp;","&amp;VLOOKUP(I68,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster063','ぱっくんトカゲ',23,158,19,16,0.1,3);</v>
       </c>
     </row>
@@ -35069,7 +35103,7 @@
         <v>151</v>
       </c>
       <c r="L69" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;H69&amp;","&amp;VLOOKUP(I69,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;H69&amp;","&amp;VLOOKUP(I69,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster064','ぱっくんドラゴン',23,189,24,20,0.11,3);</v>
       </c>
     </row>
@@ -35099,7 +35133,7 @@
         <v>36</v>
       </c>
       <c r="L70" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;H70&amp;","&amp;VLOOKUP(I70,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;H70&amp;","&amp;VLOOKUP(I70,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster065','チビデビル',24,120,13,17,0.22,5);</v>
       </c>
     </row>
@@ -35129,7 +35163,7 @@
         <v>36</v>
       </c>
       <c r="L71" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;H71&amp;","&amp;VLOOKUP(I71,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;H71&amp;","&amp;VLOOKUP(I71,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster066','グレムリン',24,160,18,20,0.24,5);</v>
       </c>
     </row>
@@ -35159,7 +35193,7 @@
         <v>36</v>
       </c>
       <c r="L72" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;H72&amp;","&amp;VLOOKUP(I72,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;H72&amp;","&amp;VLOOKUP(I72,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster067','オーガボックス',25,140,18,17,0.15,5);</v>
       </c>
     </row>
@@ -35189,7 +35223,7 @@
         <v>36</v>
       </c>
       <c r="L73" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;H73&amp;","&amp;VLOOKUP(I73,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;H73&amp;","&amp;VLOOKUP(I73,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster068','カイザーミミック',25,170,23,20,0.15,5);</v>
       </c>
     </row>
@@ -35219,7 +35253,7 @@
         <v>151</v>
       </c>
       <c r="L74" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;H74&amp;","&amp;VLOOKUP(I74,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;H74&amp;","&amp;VLOOKUP(I74,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster069','バレッテ',26,140,15,12,0.05,3);</v>
       </c>
     </row>
@@ -35249,7 +35283,7 @@
         <v>151</v>
       </c>
       <c r="L75" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;H75&amp;","&amp;VLOOKUP(I75,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;H75&amp;","&amp;VLOOKUP(I75,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster070','ゴールドバレッテ',26,180,19,14,0.05,3);</v>
       </c>
     </row>
@@ -35279,7 +35313,7 @@
         <v>34</v>
       </c>
       <c r="L76" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;H76&amp;","&amp;VLOOKUP(I76,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;H76&amp;","&amp;VLOOKUP(I76,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster071','バシリスク',27,110,12,15,0.15,2);</v>
       </c>
     </row>
@@ -35309,7 +35343,7 @@
         <v>151</v>
       </c>
       <c r="L77" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;H77&amp;","&amp;VLOOKUP(I77,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;H77&amp;","&amp;VLOOKUP(I77,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster072','ファイアドレイク',27,150,18,22,0.18,3);</v>
       </c>
     </row>
@@ -35339,7 +35373,7 @@
         <v>36</v>
       </c>
       <c r="L78" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;H78&amp;","&amp;VLOOKUP(I78,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;H78&amp;","&amp;VLOOKUP(I78,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster073','スペクター',28,130,13,17,0.2,5);</v>
       </c>
     </row>
@@ -35369,7 +35403,7 @@
         <v>36</v>
       </c>
       <c r="L79" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;H79&amp;","&amp;VLOOKUP(I79,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;H79&amp;","&amp;VLOOKUP(I79,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster074','ゴースト',28,160,17,20,0.21,5);</v>
       </c>
     </row>
@@ -35399,7 +35433,7 @@
         <v>37</v>
       </c>
       <c r="L80" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;","&amp;VLOOKUP(I80,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;","&amp;VLOOKUP(I80,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster075','ユニコーンヘッド',29,120,15,14,0.15,6);</v>
       </c>
     </row>
@@ -35429,7 +35463,7 @@
         <v>37</v>
       </c>
       <c r="L81" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;H81&amp;","&amp;VLOOKUP(I81,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;H81&amp;","&amp;VLOOKUP(I81,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster076','ゴールドユニコ',29,170,22,25,0.15,6);</v>
       </c>
     </row>
@@ -35459,7 +35493,7 @@
         <v>36</v>
       </c>
       <c r="L82" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;H82&amp;","&amp;VLOOKUP(I82,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;H82&amp;","&amp;VLOOKUP(I82,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster077','シェイプシフター',30,130,12,14,0.14,5);</v>
       </c>
     </row>
@@ -35491,7 +35525,7 @@
         <v>36</v>
       </c>
       <c r="L83" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;H83&amp;","&amp;VLOOKUP(I83,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;H83&amp;","&amp;VLOOKUP(I83,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster078','シャドウゼロ',30,170,15,18,0.15,5);</v>
       </c>
     </row>
@@ -35523,7 +35557,7 @@
         <v>36</v>
       </c>
       <c r="L84" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;H84&amp;","&amp;VLOOKUP(I84,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;H84&amp;","&amp;VLOOKUP(I84,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster079','シャドウゼロワン',30,190,19,23,0.16,5);</v>
       </c>
     </row>
@@ -35553,7 +35587,7 @@
         <v>36</v>
       </c>
       <c r="L85" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;H85&amp;","&amp;VLOOKUP(I85,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;H85&amp;","&amp;VLOOKUP(I85,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster080','ボルダー',31,120,13,14,0.25,5);</v>
       </c>
     </row>
@@ -35586,7 +35620,7 @@
         <v>36</v>
       </c>
       <c r="L86" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;H86&amp;","&amp;VLOOKUP(I86,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;H86&amp;","&amp;VLOOKUP(I86,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster081','パワーボルダー',31,144,16,18,0.25,5);</v>
       </c>
     </row>
@@ -35619,7 +35653,7 @@
         <v>36</v>
       </c>
       <c r="L87" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;H87&amp;","&amp;VLOOKUP(I87,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;H87&amp;","&amp;VLOOKUP(I87,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster082','デスボルダー',31,172,20,23,0.25,5);</v>
       </c>
     </row>
@@ -35649,7 +35683,7 @@
         <v>151</v>
       </c>
       <c r="L88" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;H88&amp;","&amp;VLOOKUP(I88,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;H88&amp;","&amp;VLOOKUP(I88,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster083','パンプキンボム',32,130,17,12,0.18,3);</v>
       </c>
     </row>
@@ -35679,7 +35713,7 @@
         <v>151</v>
       </c>
       <c r="L89" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$48:$I$108,3,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;H89&amp;","&amp;VLOOKUP(I89,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;H89&amp;","&amp;VLOOKUP(I89,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster084','グレネードボム',32,160,24,15,0.2,3);</v>
       </c>
     </row>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D6382FA-AA00-4891-BD5A-5D233F4A8E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6C84CA-CB96-40F3-B470-8164FE068E5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="3" activeTab="3" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4828" uniqueCount="2444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4832" uniqueCount="2445">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -10185,7 +10185,11 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Jackson</t>
+    <t>CHARVEL</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.charvel.jp/</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -25113,7 +25117,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
-  <dimension ref="B4:K169"/>
+  <dimension ref="B4:K170"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -27726,7 +27730,7 @@
         <v>1551</v>
       </c>
       <c r="K102" s="5" t="str">
-        <f t="shared" ref="K102:K107" si="14">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B102&amp;"'"&amp;","&amp;E102&amp;","&amp;"'"&amp;C102&amp;"'"&amp;","&amp;"'"&amp;D102&amp;"'"&amp;","&amp;"'"&amp;F102&amp;"'"&amp;","&amp;G102&amp;","&amp;H102&amp;","&amp;"'"&amp;I102&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K102:K108" si="14">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B102&amp;"'"&amp;","&amp;E102&amp;","&amp;"'"&amp;C102&amp;"'"&amp;","&amp;"'"&amp;D102&amp;"'"&amp;","&amp;"'"&amp;F102&amp;"'"&amp;","&amp;G102&amp;","&amp;H102&amp;","&amp;"'"&amp;I102&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('guitar_makers',10,'MusicMan','','',0,0.0,'https://www.music-man.com/instruments/guitars');</v>
       </c>
     </row>
@@ -27778,7 +27782,7 @@
         <v>1553</v>
       </c>
       <c r="K104" s="5" t="str">
-        <f t="shared" ref="K104:K106" si="15">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B104&amp;"'"&amp;","&amp;E104&amp;","&amp;"'"&amp;C104&amp;"'"&amp;","&amp;"'"&amp;D104&amp;"'"&amp;","&amp;"'"&amp;F104&amp;"'"&amp;","&amp;G104&amp;","&amp;H104&amp;","&amp;"'"&amp;I104&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K104:K107" si="15">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B104&amp;"'"&amp;","&amp;E104&amp;","&amp;"'"&amp;C104&amp;"'"&amp;","&amp;"'"&amp;D104&amp;"'"&amp;","&amp;"'"&amp;F104&amp;"'"&amp;","&amp;G104&amp;","&amp;H104&amp;","&amp;"'"&amp;I104&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('guitar_makers',12,'Momose','','',0,0.0,'https://www.deviser.co.jp/momose');</v>
       </c>
     </row>
@@ -27839,7 +27843,7 @@
         <v>1777</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>2443</v>
+        <v>2361</v>
       </c>
       <c r="D107" s="8"/>
       <c r="E107" s="8">
@@ -27856,62 +27860,60 @@
         <v>2442</v>
       </c>
       <c r="K107" s="5" t="str">
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('guitar_makers',15,'Jackson','','',0,0.0,'https://www.jacksonguitars.jp/');</v>
+      </c>
+    </row>
+    <row r="108" spans="2:11">
+      <c r="B108" s="8" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>2443</v>
+      </c>
+      <c r="D108" s="8"/>
+      <c r="E108" s="8">
+        <v>16</v>
+      </c>
+      <c r="F108" s="8"/>
+      <c r="G108" s="9">
+        <v>0</v>
+      </c>
+      <c r="H108" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I108" s="8" t="s">
+        <v>2444</v>
+      </c>
+      <c r="K108" s="5" t="str">
         <f t="shared" si="14"/>
-        <v>INSERT INTO m_code VALUES ('guitar_makers',15,'Jackson','','',0,0.0,'https://www.jacksonguitars.jp/');</v>
-      </c>
-    </row>
-    <row r="108" spans="2:11">
-      <c r="B108" s="6" t="s">
+        <v>INSERT INTO m_code VALUES ('guitar_makers',16,'CHARVEL','','',0,0.0,'https://www.charvel.jp/');</v>
+      </c>
+    </row>
+    <row r="109" spans="2:11">
+      <c r="B109" s="6" t="s">
         <v>1542</v>
       </c>
-      <c r="C108" s="6" t="s">
+      <c r="C109" s="6" t="s">
         <v>1388</v>
       </c>
-      <c r="D108" s="6" t="s">
+      <c r="D109" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E108" s="7" t="s">
+      <c r="E109" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F108" s="6" t="s">
+      <c r="F109" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G108" s="6" t="s">
+      <c r="G109" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H108" s="6" t="s">
+      <c r="H109" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I108" s="6" t="s">
+      <c r="I109" s="6" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="109" spans="2:11">
-      <c r="B109" s="8" t="s">
-        <v>1778</v>
-      </c>
-      <c r="C109" s="8" t="s">
-        <v>1425</v>
-      </c>
-      <c r="D109" s="8"/>
-      <c r="E109" s="8">
-        <v>1</v>
-      </c>
-      <c r="F109" s="8" t="s">
-        <v>1439</v>
-      </c>
-      <c r="G109" s="9">
-        <v>0</v>
-      </c>
-      <c r="H109" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I109" s="8" t="s">
-        <v>1463</v>
-      </c>
-      <c r="K109" s="5" t="str">
-        <f t="shared" ref="K109:K144" si="16">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B109&amp;"'"&amp;","&amp;E109&amp;","&amp;"'"&amp;C109&amp;"'"&amp;","&amp;"'"&amp;D109&amp;"'"&amp;","&amp;"'"&amp;F109&amp;"'"&amp;","&amp;G109&amp;","&amp;H109&amp;","&amp;"'"&amp;I109&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',1,'HardMaple','','ハードメイプル',0,0.0,'硬質でタイト、明瞭なアタック。');</v>
       </c>
     </row>
     <row r="110" spans="2:11">
@@ -27919,14 +27921,14 @@
         <v>1778</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="D110" s="8"/>
       <c r="E110" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G110" s="9">
         <v>0</v>
@@ -27935,11 +27937,11 @@
         <v>125</v>
       </c>
       <c r="I110" s="8" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="K110" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',2,'FlameMaple','','フレイムメイプル',0,0.0,'明るく抜けが良く、華やかな倍音。');</v>
+        <f t="shared" ref="K110:K145" si="16">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B110&amp;"'"&amp;","&amp;E110&amp;","&amp;"'"&amp;C110&amp;"'"&amp;","&amp;"'"&amp;D110&amp;"'"&amp;","&amp;"'"&amp;F110&amp;"'"&amp;","&amp;G110&amp;","&amp;H110&amp;","&amp;"'"&amp;I110&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',1,'HardMaple','','ハードメイプル',0,0.0,'硬質でタイト、明瞭なアタック。');</v>
       </c>
     </row>
     <row r="111" spans="2:11">
@@ -27947,14 +27949,14 @@
         <v>1778</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="D111" s="8"/>
       <c r="E111" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="G111" s="9">
         <v>0</v>
@@ -27963,11 +27965,11 @@
         <v>125</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="K111" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',3,'QuiltedMaple','','キルテッドメイプル',0,0.0,'立体的で広がりがあり、煌びやかな響き。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',2,'FlameMaple','','フレイムメイプル',0,0.0,'明るく抜けが良く、華やかな倍音。');</v>
       </c>
     </row>
     <row r="112" spans="2:11">
@@ -27975,14 +27977,14 @@
         <v>1778</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="D112" s="8"/>
       <c r="E112" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="G112" s="9">
         <v>0</v>
@@ -27991,11 +27993,11 @@
         <v>125</v>
       </c>
       <c r="I112" s="8" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="K112" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',4,'BirdseyeMaple','','バーズアイメイプル',0,0.0,'粒立ちが良く、明るくシャープ。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',3,'QuiltedMaple','','キルテッドメイプル',0,0.0,'立体的で広がりがあり、煌びやかな響き。');</v>
       </c>
     </row>
     <row r="113" spans="2:11">
@@ -28003,14 +28005,14 @@
         <v>1778</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="G113" s="9">
         <v>0</v>
@@ -28019,11 +28021,11 @@
         <v>125</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="K113" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',5,'RoastedMaple','','ローステッドメイプル',0,0.0,'引き締まったタイトな音で反応が速い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',4,'BirdseyeMaple','','バーズアイメイプル',0,0.0,'粒立ちが良く、明るくシャープ。');</v>
       </c>
     </row>
     <row r="114" spans="2:11">
@@ -28031,14 +28033,14 @@
         <v>1778</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>1389</v>
+        <v>1429</v>
       </c>
       <c r="D114" s="8"/>
       <c r="E114" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>1438</v>
+        <v>1443</v>
       </c>
       <c r="G114" s="9">
         <v>0</v>
@@ -28047,11 +28049,11 @@
         <v>125</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>1462</v>
+        <v>1467</v>
       </c>
       <c r="K114" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',6,'Maple','','メイプル',0,0.0,'明るくハリがあり、アタックが強い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',5,'RoastedMaple','','ローステッドメイプル',0,0.0,'引き締まったタイトな音で反応が速い。');</v>
       </c>
     </row>
     <row r="115" spans="2:11">
@@ -28059,14 +28061,14 @@
         <v>1778</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>1430</v>
+        <v>1389</v>
       </c>
       <c r="D115" s="8"/>
       <c r="E115" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>1444</v>
+        <v>1438</v>
       </c>
       <c r="G115" s="9">
         <v>0</v>
@@ -28075,11 +28077,11 @@
         <v>125</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>1469</v>
+        <v>1462</v>
       </c>
       <c r="K115" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',7,'HonduranMahogany','','ホンジュラスマホガニー',0,0.0,'深みがあり、太くリッチな中低域。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',6,'Maple','','メイプル',0,0.0,'明るくハリがあり、アタックが強い。');</v>
       </c>
     </row>
     <row r="116" spans="2:11">
@@ -28087,14 +28089,14 @@
         <v>1778</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>1390</v>
+        <v>1430</v>
       </c>
       <c r="D116" s="8"/>
       <c r="E116" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>1408</v>
+        <v>1444</v>
       </c>
       <c r="G116" s="9">
         <v>0</v>
@@ -28103,11 +28105,11 @@
         <v>125</v>
       </c>
       <c r="I116" s="8" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="K116" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',8,'Mahogany','','マホガニー',0,0.0,'中低域が豊かで温かい音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',7,'HonduranMahogany','','ホンジュラスマホガニー',0,0.0,'深みがあり、太くリッチな中低域。');</v>
       </c>
     </row>
     <row r="117" spans="2:11">
@@ -28115,14 +28117,14 @@
         <v>1778</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>1431</v>
+        <v>1390</v>
       </c>
       <c r="D117" s="8"/>
       <c r="E117" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>1445</v>
+        <v>1408</v>
       </c>
       <c r="G117" s="9">
         <v>0</v>
@@ -28131,11 +28133,11 @@
         <v>125</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="K117" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',9,'Sapele','','サペリ',0,0.0,'温かく柔らかいトーンでバランスが良い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',8,'Mahogany','','マホガニー',0,0.0,'中低域が豊かで温かい音。');</v>
       </c>
     </row>
     <row r="118" spans="2:11">
@@ -28143,14 +28145,14 @@
         <v>1778</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>1397</v>
+        <v>1431</v>
       </c>
       <c r="D118" s="8"/>
       <c r="E118" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="G118" s="9">
         <v>0</v>
@@ -28159,11 +28161,11 @@
         <v>125</v>
       </c>
       <c r="I118" s="8" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="K118" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',10,'Korina','','コリーナ',0,0.0,'中域が豊かで太い音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',9,'Sapele','','サペリ',0,0.0,'温かく柔らかいトーンでバランスが良い。');</v>
       </c>
     </row>
     <row r="119" spans="2:11">
@@ -28171,14 +28173,14 @@
         <v>1778</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>1432</v>
+        <v>1397</v>
       </c>
       <c r="D119" s="8"/>
       <c r="E119" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="G119" s="9">
         <v>0</v>
@@ -28187,11 +28189,11 @@
         <v>125</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="K119" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',11,'WhiteKorina','','ホワイトコリーナ',0,0.0,'明るく抜けが良く、軽快なレスポンス。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',10,'Korina','','コリーナ',0,0.0,'中域が豊かで太い音。');</v>
       </c>
     </row>
     <row r="120" spans="2:11">
@@ -28199,14 +28201,14 @@
         <v>1778</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>1391</v>
+        <v>1432</v>
       </c>
       <c r="D120" s="8"/>
       <c r="E120" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>1409</v>
+        <v>1447</v>
       </c>
       <c r="G120" s="9">
         <v>0</v>
@@ -28215,11 +28217,11 @@
         <v>125</v>
       </c>
       <c r="I120" s="8" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="K120" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',12,'Alder','','アルダー',0,0.0,'バランスが良くクセが少ない。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',11,'WhiteKorina','','ホワイトコリーナ',0,0.0,'明るく抜けが良く、軽快なレスポンス。');</v>
       </c>
     </row>
     <row r="121" spans="2:11">
@@ -28227,14 +28229,14 @@
         <v>1778</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="D121" s="8"/>
       <c r="E121" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>1448</v>
+        <v>1409</v>
       </c>
       <c r="G121" s="9">
         <v>0</v>
@@ -28243,11 +28245,11 @@
         <v>125</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="K121" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',13,'Ash','','アッシュ',0,0.0,'明るく抜ける音でアタックが強い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',12,'Alder','','アルダー',0,0.0,'バランスが良くクセが少ない。');</v>
       </c>
     </row>
     <row r="122" spans="2:11">
@@ -28255,14 +28257,14 @@
         <v>1778</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="D122" s="8"/>
       <c r="E122" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="G122" s="9">
         <v>0</v>
@@ -28271,11 +28273,11 @@
         <v>125</v>
       </c>
       <c r="I122" s="8" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="K122" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',14,'Basswood','','バスウッド',0,0.0,'軽く柔らかく、ウォームで扱いやすい。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',13,'Ash','','アッシュ',0,0.0,'明るく抜ける音でアタックが強い。');</v>
       </c>
     </row>
     <row r="123" spans="2:11">
@@ -28283,14 +28285,14 @@
         <v>1778</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>1402</v>
+        <v>1393</v>
       </c>
       <c r="D123" s="8"/>
       <c r="E123" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="G123" s="9">
         <v>0</v>
@@ -28299,11 +28301,11 @@
         <v>125</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="K123" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',15,'Poplar','','ポプラ',0,0.0,'軽く素直でクセが少ない。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',14,'Basswood','','バスウッド',0,0.0,'軽く柔らかく、ウォームで扱いやすい。');</v>
       </c>
     </row>
     <row r="124" spans="2:11">
@@ -28311,14 +28313,14 @@
         <v>1778</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="D124" s="8"/>
       <c r="E124" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F124" s="8" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="G124" s="9">
         <v>0</v>
@@ -28327,11 +28329,11 @@
         <v>125</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="K124" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',16,'Spruce','','スプルース',0,0.0,'軽く響きが良く、明るいトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',15,'Poplar','','ポプラ',0,0.0,'軽く素直でクセが少ない。');</v>
       </c>
     </row>
     <row r="125" spans="2:11">
@@ -28339,14 +28341,14 @@
         <v>1778</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="D125" s="8"/>
       <c r="E125" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="G125" s="9">
         <v>0</v>
@@ -28355,11 +28357,11 @@
         <v>125</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="K125" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',17,'Cedar','','シダー',0,0.0,'柔らかく温かい音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',16,'Spruce','','スプルース',0,0.0,'軽く響きが良く、明るいトーン。');</v>
       </c>
     </row>
     <row r="126" spans="2:11">
@@ -28367,14 +28369,14 @@
         <v>1778</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>1433</v>
+        <v>1399</v>
       </c>
       <c r="D126" s="8"/>
       <c r="E126" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="G126" s="9">
         <v>0</v>
@@ -28383,11 +28385,11 @@
         <v>125</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="K126" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',18,'IndianRosewood','','インディアンローズウッド',0,0.0,'甘く深みがあり、豊かな中低域。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',17,'Cedar','','シダー',0,0.0,'柔らかく温かい音。');</v>
       </c>
     </row>
     <row r="127" spans="2:11">
@@ -28395,14 +28397,14 @@
         <v>1778</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="D127" s="8"/>
       <c r="E127" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="G127" s="9">
         <v>0</v>
@@ -28411,11 +28413,11 @@
         <v>125</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="K127" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',19,'BrazilianRosewood','','ブラジリアンローズウッド',0,0.0,'濃厚で深いトーン、豊かな倍音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',18,'IndianRosewood','','インディアンローズウッド',0,0.0,'甘く深みがあり、豊かな中低域。');</v>
       </c>
     </row>
     <row r="128" spans="2:11">
@@ -28423,14 +28425,14 @@
         <v>1778</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>1394</v>
+        <v>1434</v>
       </c>
       <c r="D128" s="8"/>
       <c r="E128" s="8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="G128" s="9">
         <v>0</v>
@@ -28439,11 +28441,11 @@
         <v>125</v>
       </c>
       <c r="I128" s="8" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="K128" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',20,'Rosewood','','ローズウッド',0,0.0,'甘く丸い音で中域が豊か。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',19,'BrazilianRosewood','','ブラジリアンローズウッド',0,0.0,'濃厚で深いトーン、豊かな倍音。');</v>
       </c>
     </row>
     <row r="129" spans="2:11">
@@ -28451,14 +28453,14 @@
         <v>1778</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>1435</v>
+        <v>1394</v>
       </c>
       <c r="D129" s="8"/>
       <c r="E129" s="8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>1410</v>
+        <v>1453</v>
       </c>
       <c r="G129" s="9">
         <v>0</v>
@@ -28467,11 +28469,11 @@
         <v>125</v>
       </c>
       <c r="I129" s="8" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="K129" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',21,'PauFerro','','パーフェロー',0,0.0,'明るく硬質でタイトな音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',20,'Rosewood','','ローズウッド',0,0.0,'甘く丸い音で中域が豊か。');</v>
       </c>
     </row>
     <row r="130" spans="2:11">
@@ -28479,14 +28481,14 @@
         <v>1778</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>1400</v>
+        <v>1435</v>
       </c>
       <c r="D130" s="8"/>
       <c r="E130" s="8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="G130" s="9">
         <v>0</v>
@@ -28495,11 +28497,11 @@
         <v>125</v>
       </c>
       <c r="I130" s="8" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="K130" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',22,'Ovangkol','','オバンコール',0,0.0,'中域が豊かで温かいトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',21,'PauFerro','','パーフェロー',0,0.0,'明るく硬質でタイトな音。');</v>
       </c>
     </row>
     <row r="131" spans="2:11">
@@ -28507,14 +28509,14 @@
         <v>1778</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>1395</v>
+        <v>1400</v>
       </c>
       <c r="D131" s="8"/>
       <c r="E131" s="8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>1456</v>
+        <v>1411</v>
       </c>
       <c r="G131" s="9">
         <v>0</v>
@@ -28523,11 +28525,11 @@
         <v>125</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="K131" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',23,'Ebony','','エボニー',0,0.0,'硬くタイトで高域がクリア。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',22,'Ovangkol','','オバンコール',0,0.0,'中域が豊かで温かいトーン。');</v>
       </c>
     </row>
     <row r="132" spans="2:11">
@@ -28535,14 +28537,14 @@
         <v>1778</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="D132" s="8"/>
       <c r="E132" s="8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="G132" s="9">
         <v>0</v>
@@ -28551,11 +28553,11 @@
         <v>125</v>
       </c>
       <c r="I132" s="8" t="s">
-        <v>1416</v>
+        <v>1484</v>
       </c>
       <c r="K132" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',24,'Walnut','','ウォルナット',0,0.0,'中域が豊かで落ち着いたトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',23,'Ebony','','エボニー',0,0.0,'硬くタイトで高域がクリア。');</v>
       </c>
     </row>
     <row r="133" spans="2:11">
@@ -28563,14 +28565,14 @@
         <v>1778</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>1436</v>
+        <v>1396</v>
       </c>
       <c r="D133" s="8"/>
       <c r="E133" s="8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F133" s="8" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="G133" s="9">
         <v>0</v>
@@ -28579,11 +28581,11 @@
         <v>125</v>
       </c>
       <c r="I133" s="8" t="s">
-        <v>1485</v>
+        <v>1416</v>
       </c>
       <c r="K133" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',25,'Padauk','','パドゥーク',0,0.0,'明るく抜けが良く、個性的な響き。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',24,'Walnut','','ウォルナット',0,0.0,'中域が豊かで落ち着いたトーン。');</v>
       </c>
     </row>
     <row r="134" spans="2:11">
@@ -28591,14 +28593,14 @@
         <v>1778</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>1401</v>
+        <v>1436</v>
       </c>
       <c r="D134" s="8"/>
       <c r="E134" s="8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F134" s="8" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="G134" s="9">
         <v>0</v>
@@ -28607,11 +28609,11 @@
         <v>125</v>
       </c>
       <c r="I134" s="8" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="K134" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',26,'Koa','','コア',0,0.0,'明るく華やかで軽快。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',25,'Padauk','','パドゥーク',0,0.0,'明るく抜けが良く、個性的な響き。');</v>
       </c>
     </row>
     <row r="135" spans="2:11">
@@ -28619,14 +28621,14 @@
         <v>1778</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="D135" s="8"/>
       <c r="E135" s="8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F135" s="8" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="G135" s="9">
         <v>0</v>
@@ -28635,11 +28637,11 @@
         <v>125</v>
       </c>
       <c r="I135" s="8" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="K135" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',27,'Nato','','ナトー',0,0.0,'中低域が豊かで温かい。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',26,'Koa','','コア',0,0.0,'明るく華やかで軽快。');</v>
       </c>
     </row>
     <row r="136" spans="2:11">
@@ -28647,14 +28649,14 @@
         <v>1778</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="D136" s="8"/>
       <c r="E136" s="8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F136" s="8" t="s">
-        <v>1412</v>
+        <v>1460</v>
       </c>
       <c r="G136" s="9">
         <v>0</v>
@@ -28663,11 +28665,11 @@
         <v>125</v>
       </c>
       <c r="I136" s="8" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="K136" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',28,'Agathis','','アガチス',0,0.0,'柔らかくウォームで素直。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',27,'Nato','','ナトー',0,0.0,'中低域が豊かで温かい。');</v>
       </c>
     </row>
     <row r="137" spans="2:11">
@@ -28675,14 +28677,14 @@
         <v>1778</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="D137" s="8"/>
       <c r="E137" s="8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F137" s="8" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="G137" s="9">
         <v>0</v>
@@ -28691,11 +28693,11 @@
         <v>125</v>
       </c>
       <c r="I137" s="8" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="K137" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',29,'Bubinga','','ブビンガ',0,0.0,'重く硬質でサスティンが長い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',28,'Agathis','','アガチス',0,0.0,'柔らかくウォームで素直。');</v>
       </c>
     </row>
     <row r="138" spans="2:11">
@@ -28703,14 +28705,14 @@
         <v>1778</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="D138" s="8"/>
       <c r="E138" s="8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="G138" s="9">
         <v>0</v>
@@ -28719,11 +28721,11 @@
         <v>125</v>
       </c>
       <c r="I138" s="8" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="K138" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',30,'Wenge','','ウェンジ',0,0.0,'非常に硬くタイトで個性的。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',29,'Bubinga','','ブビンガ',0,0.0,'重く硬質でサスティンが長い。');</v>
       </c>
     </row>
     <row r="139" spans="2:11">
@@ -28731,14 +28733,14 @@
         <v>1778</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="G139" s="9">
         <v>0</v>
@@ -28747,11 +28749,11 @@
         <v>125</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="K139" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',31,'Purpleheart','','パープルハート',0,0.0,'硬く鮮やかでアタックが強い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',30,'Wenge','','ウェンジ',0,0.0,'非常に硬くタイトで個性的。');</v>
       </c>
     </row>
     <row r="140" spans="2:11">
@@ -28759,14 +28761,14 @@
         <v>1778</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>1437</v>
+        <v>1407</v>
       </c>
       <c r="D140" s="8"/>
       <c r="E140" s="8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F140" s="8" t="s">
-        <v>1461</v>
+        <v>1415</v>
       </c>
       <c r="G140" s="9">
         <v>0</v>
@@ -28775,11 +28777,11 @@
         <v>125</v>
       </c>
       <c r="I140" s="8" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="K140" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',32,'Zebrawood','','ゼブラウッド',0,0.0,'明るく硬質でクセのあるトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',31,'Purpleheart','','パープルハート',0,0.0,'硬く鮮やかでアタックが強い。');</v>
       </c>
     </row>
     <row r="141" spans="2:11">
@@ -28787,14 +28789,14 @@
         <v>1778</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>1558</v>
+        <v>1437</v>
       </c>
       <c r="D141" s="8"/>
       <c r="E141" s="8">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>1559</v>
+        <v>1461</v>
       </c>
       <c r="G141" s="9">
         <v>0</v>
@@ -28803,11 +28805,11 @@
         <v>125</v>
       </c>
       <c r="I141" s="8" t="s">
-        <v>1560</v>
+        <v>1492</v>
       </c>
       <c r="K141" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',33,'Okoume','','オクメ',0,0.0,'マホガニーに近く、中低域が豊かで軽量。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',32,'Zebrawood','','ゼブラウッド',0,0.0,'明るく硬質でクセのあるトーン。');</v>
       </c>
     </row>
     <row r="142" spans="2:11">
@@ -28815,14 +28817,14 @@
         <v>1778</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="D142" s="8"/>
       <c r="E142" s="8">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="G142" s="9">
         <v>0</v>
@@ -28831,11 +28833,11 @@
         <v>125</v>
       </c>
       <c r="I142" s="8" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="K142" s="5" t="str">
-        <f t="shared" ref="K142" si="17">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B142&amp;"'"&amp;","&amp;E142&amp;","&amp;"'"&amp;C142&amp;"'"&amp;","&amp;"'"&amp;D142&amp;"'"&amp;","&amp;"'"&amp;F142&amp;"'"&amp;","&amp;G142&amp;","&amp;H142&amp;","&amp;"'"&amp;I142&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',34,'Meranti','','メランティ',0,0.0,'中域寄りで温かめ、マホガニー系に近い。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',33,'Okoume','','オクメ',0,0.0,'マホガニーに近く、中低域が豊かで軽量。');</v>
       </c>
     </row>
     <row r="143" spans="2:11">
@@ -28843,14 +28845,14 @@
         <v>1778</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="D143" s="8"/>
       <c r="E143" s="8">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F143" s="8" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="G143" s="9">
         <v>0</v>
@@ -28859,11 +28861,11 @@
         <v>125</v>
       </c>
       <c r="I143" s="8" t="s">
-        <v>1569</v>
+        <v>1563</v>
       </c>
       <c r="K143" s="5" t="str">
-        <f t="shared" ref="K143" si="18">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B143&amp;"'"&amp;","&amp;E143&amp;","&amp;"'"&amp;C143&amp;"'"&amp;","&amp;"'"&amp;D143&amp;"'"&amp;","&amp;"'"&amp;F143&amp;"'"&amp;","&amp;G143&amp;","&amp;H143&amp;","&amp;"'"&amp;I143&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',35,'Sakura','','サクラ',0,0.0,'中高域が明るく立ち上がりが速い、日本らしい軽快で抜けの良いサウンド。');</v>
+        <f t="shared" ref="K143" si="17">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B143&amp;"'"&amp;","&amp;E143&amp;","&amp;"'"&amp;C143&amp;"'"&amp;","&amp;"'"&amp;D143&amp;"'"&amp;","&amp;"'"&amp;F143&amp;"'"&amp;","&amp;G143&amp;","&amp;H143&amp;","&amp;"'"&amp;I143&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',34,'Meranti','','メランティ',0,0.0,'中域寄りで温かめ、マホガニー系に近い。');</v>
       </c>
     </row>
     <row r="144" spans="2:11">
@@ -28871,14 +28873,14 @@
         <v>1778</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="D144" s="8"/>
       <c r="E144" s="8">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F144" s="8" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="G144" s="9">
         <v>0</v>
@@ -28887,11 +28889,11 @@
         <v>125</v>
       </c>
       <c r="I144" s="8" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="K144" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',36,'Tochi','','トチ',0,0.0,'メイプルに近いクリアさと華やかさを持ちつつ、やや柔らかく豊かな倍音.');</v>
+        <f t="shared" ref="K144" si="18">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B144&amp;"'"&amp;","&amp;E144&amp;","&amp;"'"&amp;C144&amp;"'"&amp;","&amp;"'"&amp;D144&amp;"'"&amp;","&amp;"'"&amp;F144&amp;"'"&amp;","&amp;G144&amp;","&amp;H144&amp;","&amp;"'"&amp;I144&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',35,'Sakura','','サクラ',0,0.0,'中高域が明るく立ち上がりが速い、日本らしい軽快で抜けの良いサウンド。');</v>
       </c>
     </row>
     <row r="145" spans="2:11">
@@ -28899,14 +28901,14 @@
         <v>1778</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>1424</v>
+        <v>1566</v>
       </c>
       <c r="D145" s="8"/>
       <c r="E145" s="8">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>1423</v>
+        <v>1567</v>
       </c>
       <c r="G145" s="9">
         <v>0</v>
@@ -28914,62 +28916,64 @@
       <c r="H145" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="I145" s="8"/>
+      <c r="I145" s="8" t="s">
+        <v>1568</v>
+      </c>
       <c r="K145" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B145&amp;"'"&amp;","&amp;E145&amp;","&amp;"'"&amp;C145&amp;"'"&amp;","&amp;"'"&amp;D145&amp;"'"&amp;","&amp;"'"&amp;F145&amp;"'"&amp;","&amp;G145&amp;","&amp;H145&amp;","&amp;"'"&amp;I145&amp;"'"&amp;");"</f>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',36,'Tochi','','トチ',0,0.0,'メイプルに近いクリアさと華やかさを持ちつつ、やや柔らかく豊かな倍音.');</v>
+      </c>
+    </row>
+    <row r="146" spans="2:11">
+      <c r="B146" s="8" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D146" s="8"/>
+      <c r="E146" s="8">
+        <v>99</v>
+      </c>
+      <c r="F146" s="8" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G146" s="9">
+        <v>0</v>
+      </c>
+      <c r="H146" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I146" s="8"/>
+      <c r="K146" s="5" t="str">
+        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B146&amp;"'"&amp;","&amp;E146&amp;","&amp;"'"&amp;C146&amp;"'"&amp;","&amp;"'"&amp;D146&amp;"'"&amp;","&amp;"'"&amp;F146&amp;"'"&amp;","&amp;G146&amp;","&amp;H146&amp;","&amp;"'"&amp;I146&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('guitar_woods',99,'Unknown','','？？',0,0.0,'');</v>
       </c>
     </row>
-    <row r="146" spans="2:11">
-      <c r="B146" s="6" t="s">
+    <row r="147" spans="2:11">
+      <c r="B147" s="6" t="s">
         <v>1503</v>
       </c>
-      <c r="C146" s="6" t="s">
+      <c r="C147" s="6" t="s">
         <v>1502</v>
       </c>
-      <c r="D146" s="6" t="s">
+      <c r="D147" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E146" s="7" t="s">
+      <c r="E147" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F146" s="6" t="s">
+      <c r="F147" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G146" s="6" t="s">
+      <c r="G147" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H146" s="6" t="s">
+      <c r="H147" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I146" s="6" t="s">
+      <c r="I147" s="6" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="147" spans="2:11">
-      <c r="B147" s="8" t="s">
-        <v>1779</v>
-      </c>
-      <c r="C147" s="8" t="s">
-        <v>1504</v>
-      </c>
-      <c r="D147" s="8"/>
-      <c r="E147" s="8">
-        <v>1</v>
-      </c>
-      <c r="F147" s="8" t="s">
-        <v>1520</v>
-      </c>
-      <c r="G147" s="9">
-        <v>0</v>
-      </c>
-      <c r="H147" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I147" s="8"/>
-      <c r="K147" s="5" t="str">
-        <f t="shared" ref="K147:K169" si="19">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B147&amp;"'"&amp;","&amp;E147&amp;","&amp;"'"&amp;C147&amp;"'"&amp;","&amp;"'"&amp;D147&amp;"'"&amp;","&amp;"'"&amp;F147&amp;"'"&amp;","&amp;G147&amp;","&amp;H147&amp;","&amp;"'"&amp;I147&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',1,'Red','','レッド',0,0.0,'');</v>
       </c>
     </row>
     <row r="148" spans="2:11">
@@ -28977,14 +28981,14 @@
         <v>1779</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>1518</v>
+        <v>1504</v>
       </c>
       <c r="D148" s="8"/>
       <c r="E148" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F148" s="8" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="G148" s="9">
         <v>0</v>
@@ -28994,8 +28998,8 @@
       </c>
       <c r="I148" s="8"/>
       <c r="K148" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',2,'Pink','','ピンク',0,0.0,'');</v>
+        <f t="shared" ref="K148:K170" si="19">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B148&amp;"'"&amp;","&amp;E148&amp;","&amp;"'"&amp;C148&amp;"'"&amp;","&amp;"'"&amp;D148&amp;"'"&amp;","&amp;"'"&amp;F148&amp;"'"&amp;","&amp;G148&amp;","&amp;H148&amp;","&amp;"'"&amp;I148&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',1,'Red','','レッド',0,0.0,'');</v>
       </c>
     </row>
     <row r="149" spans="2:11">
@@ -29003,14 +29007,14 @@
         <v>1779</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>1505</v>
+        <v>1518</v>
       </c>
       <c r="D149" s="8"/>
       <c r="E149" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F149" s="8" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="G149" s="9">
         <v>0</v>
@@ -29021,7 +29025,7 @@
       <c r="I149" s="8"/>
       <c r="K149" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',3,'Orange','','オレンジ',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',2,'Pink','','ピンク',0,0.0,'');</v>
       </c>
     </row>
     <row r="150" spans="2:11">
@@ -29029,14 +29033,14 @@
         <v>1779</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="D150" s="8"/>
       <c r="E150" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="G150" s="9">
         <v>0</v>
@@ -29047,7 +29051,7 @@
       <c r="I150" s="8"/>
       <c r="K150" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',4,'Yellow','','イエロー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',3,'Orange','','オレンジ',0,0.0,'');</v>
       </c>
     </row>
     <row r="151" spans="2:11">
@@ -29055,14 +29059,14 @@
         <v>1779</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D151" s="8"/>
       <c r="E151" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="G151" s="9">
         <v>0</v>
@@ -29073,7 +29077,7 @@
       <c r="I151" s="8"/>
       <c r="K151" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',5,'Green','','グリーン',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',4,'Yellow','','イエロー',0,0.0,'');</v>
       </c>
     </row>
     <row r="152" spans="2:11">
@@ -29081,14 +29085,14 @@
         <v>1779</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="D152" s="8"/>
       <c r="E152" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F152" s="8" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="G152" s="9">
         <v>0</v>
@@ -29099,7 +29103,7 @@
       <c r="I152" s="8"/>
       <c r="K152" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',6,'SkyBlue','','スカイブルー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',5,'Green','','グリーン',0,0.0,'');</v>
       </c>
     </row>
     <row r="153" spans="2:11">
@@ -29107,14 +29111,14 @@
         <v>1779</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="D153" s="8"/>
       <c r="E153" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="G153" s="9">
         <v>0</v>
@@ -29125,7 +29129,7 @@
       <c r="I153" s="8"/>
       <c r="K153" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',7,'Blue','','ブルー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',6,'SkyBlue','','スカイブルー',0,0.0,'');</v>
       </c>
     </row>
     <row r="154" spans="2:11">
@@ -29133,14 +29137,14 @@
         <v>1779</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="D154" s="8"/>
       <c r="E154" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="G154" s="9">
         <v>0</v>
@@ -29151,7 +29155,7 @@
       <c r="I154" s="8"/>
       <c r="K154" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',8,'Purple','','パープル',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',7,'Blue','','ブルー',0,0.0,'');</v>
       </c>
     </row>
     <row r="155" spans="2:11">
@@ -29159,14 +29163,14 @@
         <v>1779</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="D155" s="8"/>
       <c r="E155" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F155" s="8" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="G155" s="9">
         <v>0</v>
@@ -29177,7 +29181,7 @@
       <c r="I155" s="8"/>
       <c r="K155" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',9,'Gray','','グレー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',8,'Purple','','パープル',0,0.0,'');</v>
       </c>
     </row>
     <row r="156" spans="2:11">
@@ -29185,14 +29189,14 @@
         <v>1779</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="D156" s="8"/>
       <c r="E156" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F156" s="8" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="G156" s="9">
         <v>0</v>
@@ -29203,7 +29207,7 @@
       <c r="I156" s="8"/>
       <c r="K156" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',10,'Black','','ブラック',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',9,'Gray','','グレー',0,0.0,'');</v>
       </c>
     </row>
     <row r="157" spans="2:11">
@@ -29211,14 +29215,14 @@
         <v>1779</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="D157" s="8"/>
       <c r="E157" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F157" s="8" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="G157" s="9">
         <v>0</v>
@@ -29229,7 +29233,7 @@
       <c r="I157" s="8"/>
       <c r="K157" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',11,'White','','ホワイト',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',10,'Black','','ブラック',0,0.0,'');</v>
       </c>
     </row>
     <row r="158" spans="2:11">
@@ -29237,14 +29241,14 @@
         <v>1779</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="D158" s="8"/>
       <c r="E158" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="G158" s="9">
         <v>0</v>
@@ -29255,7 +29259,7 @@
       <c r="I158" s="8"/>
       <c r="K158" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',12,'Natural','','ナチュラル',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',11,'White','','ホワイト',0,0.0,'');</v>
       </c>
     </row>
     <row r="159" spans="2:11">
@@ -29263,14 +29267,14 @@
         <v>1779</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>1519</v>
+        <v>1514</v>
       </c>
       <c r="D159" s="8"/>
       <c r="E159" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="G159" s="9">
         <v>0</v>
@@ -29281,7 +29285,7 @@
       <c r="I159" s="8"/>
       <c r="K159" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',13,'Brown','','ブラウン',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',12,'Natural','','ナチュラル',0,0.0,'');</v>
       </c>
     </row>
     <row r="160" spans="2:11">
@@ -29289,14 +29293,14 @@
         <v>1779</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="D160" s="8"/>
       <c r="E160" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F160" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="G160" s="9">
         <v>0</v>
@@ -29307,7 +29311,7 @@
       <c r="I160" s="8"/>
       <c r="K160" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',14,'Gold','','ゴールド',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',13,'Brown','','ブラウン',0,0.0,'');</v>
       </c>
     </row>
     <row r="161" spans="2:11">
@@ -29315,14 +29319,14 @@
         <v>1779</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="D161" s="8"/>
       <c r="E161" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F161" s="8" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="G161" s="9">
         <v>0</v>
@@ -29333,7 +29337,7 @@
       <c r="I161" s="8"/>
       <c r="K161" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',15,'Silver','','シルバー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',14,'Gold','','ゴールド',0,0.0,'');</v>
       </c>
     </row>
     <row r="162" spans="2:11">
@@ -29341,14 +29345,14 @@
         <v>1779</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D162" s="8"/>
       <c r="E162" s="8">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G162" s="9">
         <v>0</v>
@@ -29359,59 +29363,59 @@
       <c r="I162" s="8"/>
       <c r="K162" s="5" t="str">
         <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',15,'Silver','','シルバー',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="163" spans="2:11">
+      <c r="B163" s="8" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C163" s="8" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D163" s="8"/>
+      <c r="E163" s="8">
+        <v>99</v>
+      </c>
+      <c r="F163" s="8" t="s">
+        <v>1535</v>
+      </c>
+      <c r="G163" s="9">
+        <v>0</v>
+      </c>
+      <c r="H163" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I163" s="8"/>
+      <c r="K163" s="5" t="str">
+        <f t="shared" si="19"/>
         <v>INSERT INTO m_code VALUES ('guitar_colors',99,'Others','','その他',0,0.0,'');</v>
       </c>
     </row>
-    <row r="163" spans="2:11">
-      <c r="B163" s="6" t="s">
+    <row r="164" spans="2:11">
+      <c r="B164" s="6" t="s">
         <v>1888</v>
       </c>
-      <c r="C163" s="6" t="s">
+      <c r="C164" s="6" t="s">
         <v>1889</v>
       </c>
-      <c r="D163" s="6" t="s">
+      <c r="D164" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E163" s="7" t="s">
+      <c r="E164" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F163" s="6" t="s">
+      <c r="F164" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G163" s="6" t="s">
+      <c r="G164" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H163" s="6" t="s">
+      <c r="H164" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I163" s="6" t="s">
+      <c r="I164" s="6" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="164" spans="2:11">
-      <c r="B164" s="8" t="s">
-        <v>1892</v>
-      </c>
-      <c r="C164" s="8" t="s">
-        <v>1890</v>
-      </c>
-      <c r="D164" s="8"/>
-      <c r="E164" s="8">
-        <v>1</v>
-      </c>
-      <c r="F164" s="8"/>
-      <c r="G164" s="9">
-        <v>0</v>
-      </c>
-      <c r="H164" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I164" s="8" t="s">
-        <v>1893</v>
-      </c>
-      <c r="K164" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',1,'SUCCESS','','',0,0.0,'処理成功');</v>
       </c>
     </row>
     <row r="165" spans="2:11">
@@ -29419,11 +29423,11 @@
         <v>1892</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="D165" s="8"/>
       <c r="E165" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F165" s="8"/>
       <c r="G165" s="9">
@@ -29433,11 +29437,11 @@
         <v>125</v>
       </c>
       <c r="I165" s="8" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="K165" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',2,'STARTED','','',0,0.0,'処理開始。いずかのステータスに遷移する。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',1,'SUCCESS','','',0,0.0,'処理成功');</v>
       </c>
     </row>
     <row r="166" spans="2:11">
@@ -29445,11 +29449,11 @@
         <v>1892</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>1881</v>
+        <v>1891</v>
       </c>
       <c r="D166" s="8"/>
       <c r="E166" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F166" s="8"/>
       <c r="G166" s="9">
@@ -29459,11 +29463,11 @@
         <v>125</v>
       </c>
       <c r="I166" s="8" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="K166" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',3,'NOT_STARTED','','',0,0.0,'予定時刻に開始されていない。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',2,'STARTED','','',0,0.0,'処理開始。いずかのステータスに遷移する。');</v>
       </c>
     </row>
     <row r="167" spans="2:11">
@@ -29471,11 +29475,11 @@
         <v>1892</v>
       </c>
       <c r="C167" s="8" t="s">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="D167" s="8"/>
       <c r="E167" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F167" s="8"/>
       <c r="G167" s="9">
@@ -29485,11 +29489,11 @@
         <v>125</v>
       </c>
       <c r="I167" s="8" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="K167" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',4,'ERROR','','',0,0.0,'例外、パニック等が発生した。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',3,'NOT_STARTED','','',0,0.0,'予定時刻に開始されていない。');</v>
       </c>
     </row>
     <row r="168" spans="2:11">
@@ -29497,11 +29501,11 @@
         <v>1892</v>
       </c>
       <c r="C168" s="8" t="s">
-        <v>1882</v>
+        <v>1879</v>
       </c>
       <c r="D168" s="8"/>
       <c r="E168" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F168" s="8"/>
       <c r="G168" s="9">
@@ -29511,11 +29515,11 @@
         <v>125</v>
       </c>
       <c r="I168" s="8" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="K168" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',5,'SLOW','','',0,0.0,'想定時間内に処理が終了しなかった。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',4,'ERROR','','',0,0.0,'例外、パニック等が発生した。');</v>
       </c>
     </row>
     <row r="169" spans="2:11">
@@ -29523,11 +29527,11 @@
         <v>1892</v>
       </c>
       <c r="C169" s="8" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="D169" s="8"/>
       <c r="E169" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F169" s="8"/>
       <c r="G169" s="9">
@@ -29537,9 +29541,35 @@
         <v>125</v>
       </c>
       <c r="I169" s="8" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K169" s="5" t="str">
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('batch_status',5,'SLOW','','',0,0.0,'想定時間内に処理が終了しなかった。');</v>
+      </c>
+    </row>
+    <row r="170" spans="2:11">
+      <c r="B170" s="8" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C170" s="8" t="s">
+        <v>1880</v>
+      </c>
+      <c r="D170" s="8"/>
+      <c r="E170" s="8">
+        <v>6</v>
+      </c>
+      <c r="F170" s="8"/>
+      <c r="G170" s="9">
+        <v>0</v>
+      </c>
+      <c r="H170" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I170" s="8" t="s">
         <v>1897</v>
       </c>
-      <c r="K169" s="5" t="str">
+      <c r="K170" s="5" t="str">
         <f t="shared" si="19"/>
         <v>INSERT INTO m_code VALUES ('batch_status',6,'TIMEOUT','','',0,0.0,'時間内に処理が終了しなかった。');</v>
       </c>
@@ -33098,7 +33128,7 @@
         <v>150</v>
       </c>
       <c r="L6" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;H6&amp;","&amp;VLOOKUP(I6,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;H6&amp;","&amp;VLOOKUP(I6,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster001','キラービー',1,110,12,16,0.3,1);</v>
       </c>
     </row>
@@ -33131,7 +33161,7 @@
         <v>150</v>
       </c>
       <c r="L7" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;H7&amp;","&amp;VLOOKUP(I7,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;H7&amp;","&amp;VLOOKUP(I7,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster002','アサシンバグ',1,132,15,20,0.3,1);</v>
       </c>
     </row>
@@ -33164,7 +33194,7 @@
         <v>150</v>
       </c>
       <c r="L8" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;H8&amp;","&amp;VLOOKUP(I8,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;H8&amp;","&amp;VLOOKUP(I8,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster003','ラスターバグ',1,158,19,26,0.3,1);</v>
       </c>
     </row>
@@ -33194,7 +33224,7 @@
         <v>34</v>
       </c>
       <c r="L9" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;H9&amp;","&amp;VLOOKUP(I9,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;H9&amp;","&amp;VLOOKUP(I9,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster004','カーミラ',2,100,10,13,0.13,2);</v>
       </c>
     </row>
@@ -33227,7 +33257,7 @@
         <v>34</v>
       </c>
       <c r="L10" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;H10&amp;","&amp;VLOOKUP(I10,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;H10&amp;","&amp;VLOOKUP(I10,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster005','カーミラクイーン',2,120,13,16,0.15,2);</v>
       </c>
     </row>
@@ -33257,7 +33287,7 @@
         <v>36</v>
       </c>
       <c r="L11" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;H11&amp;","&amp;VLOOKUP(I11,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;H11&amp;","&amp;VLOOKUP(I11,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster006','デーモン',3,130,15,7,0.08,5);</v>
       </c>
     </row>
@@ -33290,7 +33320,7 @@
         <v>36</v>
       </c>
       <c r="L12" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;H12&amp;","&amp;VLOOKUP(I12,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;H12&amp;","&amp;VLOOKUP(I12,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster007','グレートデーモン',3,156,19,9,0.1,5);</v>
       </c>
     </row>
@@ -33320,7 +33350,7 @@
         <v>35</v>
       </c>
       <c r="L13" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;H13&amp;","&amp;VLOOKUP(I13,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;H13&amp;","&amp;VLOOKUP(I13,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster008','ゴブリン',4,120,11,10,0.15,4);</v>
       </c>
     </row>
@@ -33353,7 +33383,7 @@
         <v>35</v>
       </c>
       <c r="L14" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;H14&amp;","&amp;VLOOKUP(I14,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;H14&amp;","&amp;VLOOKUP(I14,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster009','ゴブリンガード',4,144,14,13,0.15,4);</v>
       </c>
     </row>
@@ -33386,7 +33416,7 @@
         <v>35</v>
       </c>
       <c r="L15" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;H15&amp;","&amp;VLOOKUP(I15,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;H15&amp;","&amp;VLOOKUP(I15,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster010','ゴブリンロード',4,172,18,16,0.15,4);</v>
       </c>
     </row>
@@ -33416,7 +33446,7 @@
         <v>151</v>
       </c>
       <c r="L16" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;H16&amp;","&amp;VLOOKUP(I16,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;H16&amp;","&amp;VLOOKUP(I16,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster011','マシンゴーレム',5,140,17,5,0.02,3);</v>
       </c>
     </row>
@@ -33449,7 +33479,7 @@
         <v>151</v>
       </c>
       <c r="L17" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;H17&amp;","&amp;VLOOKUP(I17,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;H17&amp;","&amp;VLOOKUP(I17,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster012','ガーディアン',5,168,22,6,0.04,3);</v>
       </c>
     </row>
@@ -33482,7 +33512,7 @@
         <v>151</v>
       </c>
       <c r="L18" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;H18&amp;","&amp;VLOOKUP(I18,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;H18&amp;","&amp;VLOOKUP(I18,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster013','デスマシン',5,201,28,7,0.05,3);</v>
       </c>
     </row>
@@ -33512,7 +33542,7 @@
         <v>35</v>
       </c>
       <c r="L19" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;H19&amp;","&amp;VLOOKUP(I19,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;H19&amp;","&amp;VLOOKUP(I19,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster014','ハーピー',6,100,8,14,0.2,4);</v>
       </c>
     </row>
@@ -33545,7 +33575,7 @@
         <v>35</v>
       </c>
       <c r="L20" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;H20&amp;","&amp;VLOOKUP(I20,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;H20&amp;","&amp;VLOOKUP(I20,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster015','セイレーン',6,120,10,18,0.23,4);</v>
       </c>
     </row>
@@ -33575,7 +33605,7 @@
         <v>34</v>
       </c>
       <c r="L21" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;H21&amp;","&amp;VLOOKUP(I21,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;H21&amp;","&amp;VLOOKUP(I21,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster016','アーマーナイト',7,120,13,8,0.05,2);</v>
       </c>
     </row>
@@ -33608,7 +33638,7 @@
         <v>34</v>
       </c>
       <c r="L22" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;H22&amp;","&amp;VLOOKUP(I22,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;H22&amp;","&amp;VLOOKUP(I22,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster017','ダークナイト',7,144,16,10,0.05,2);</v>
       </c>
     </row>
@@ -33641,7 +33671,7 @@
         <v>34</v>
       </c>
       <c r="L23" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;H23&amp;","&amp;VLOOKUP(I23,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;H23&amp;","&amp;VLOOKUP(I23,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster018','ターミネータ',7,172,20,13,0.07,2);</v>
       </c>
     </row>
@@ -33671,7 +33701,7 @@
         <v>35</v>
       </c>
       <c r="L24" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;H24&amp;","&amp;VLOOKUP(I24,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;H24&amp;","&amp;VLOOKUP(I24,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster019','マジシャン',8,100,9,12,0.1,4);</v>
       </c>
     </row>
@@ -33704,7 +33734,7 @@
         <v>35</v>
       </c>
       <c r="L25" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;H25&amp;","&amp;VLOOKUP(I25,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;H25&amp;","&amp;VLOOKUP(I25,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster020','ウィザード',8,120,11,15,0.11,4);</v>
       </c>
     </row>
@@ -33737,7 +33767,7 @@
         <v>35</v>
       </c>
       <c r="L26" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;H26&amp;","&amp;VLOOKUP(I26,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;H26&amp;","&amp;VLOOKUP(I26,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster021','ハイウィザード',8,144,14,19,0.12,4);</v>
       </c>
     </row>
@@ -33767,7 +33797,7 @@
         <v>150</v>
       </c>
       <c r="L27" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;H27&amp;","&amp;VLOOKUP(I27,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;H27&amp;","&amp;VLOOKUP(I27,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster022','マイコニド',9,120,10,12,0.15,1);</v>
       </c>
     </row>
@@ -33800,7 +33830,7 @@
         <v>150</v>
       </c>
       <c r="L28" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;H28&amp;","&amp;VLOOKUP(I28,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;H28&amp;","&amp;VLOOKUP(I28,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster023','ダースマタンゴ',9,144,13,15,0.15,1);</v>
       </c>
     </row>
@@ -33830,7 +33860,7 @@
         <v>151</v>
       </c>
       <c r="L29" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;H29&amp;","&amp;VLOOKUP(I29,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;H29&amp;","&amp;VLOOKUP(I29,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster024','ニードルバード',10,100,13,16,0.25,3);</v>
       </c>
     </row>
@@ -33863,7 +33893,7 @@
         <v>151</v>
       </c>
       <c r="L30" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;H30&amp;","&amp;VLOOKUP(I30,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;H30&amp;","&amp;VLOOKUP(I30,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster025','コカトバード',10,120,16,20,0.27,3);</v>
       </c>
     </row>
@@ -33893,7 +33923,7 @@
         <v>151</v>
       </c>
       <c r="L31" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;H31&amp;","&amp;VLOOKUP(I31,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;H31&amp;","&amp;VLOOKUP(I31,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster026','プチドラゴン',11,130,13,8,0.08,3);</v>
       </c>
     </row>
@@ -33926,7 +33956,7 @@
         <v>36</v>
       </c>
       <c r="L32" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;H32&amp;","&amp;VLOOKUP(I32,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;H32&amp;","&amp;VLOOKUP(I32,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster027','プチドラゾンビ',11,156,16,10,0.1,5);</v>
       </c>
     </row>
@@ -33959,7 +33989,7 @@
         <v>150</v>
       </c>
       <c r="L33" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;H33&amp;","&amp;VLOOKUP(I33,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;H33&amp;","&amp;VLOOKUP(I33,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster028','フロストドラゴン',11,187,20,13,0.12,1);</v>
       </c>
     </row>
@@ -33992,7 +34022,7 @@
         <v>37</v>
       </c>
       <c r="L34" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;H34&amp;","&amp;VLOOKUP(I34,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;H34&amp;","&amp;VLOOKUP(I34,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster029','プチティアマット',11,224,26,16,0.13,6);</v>
       </c>
     </row>
@@ -34022,7 +34052,7 @@
         <v>37</v>
       </c>
       <c r="L35" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;H35&amp;","&amp;VLOOKUP(I35,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;H35&amp;","&amp;VLOOKUP(I35,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster030','ポト',12,100,10,16,0.18,6);</v>
       </c>
     </row>
@@ -34055,7 +34085,7 @@
         <v>37</v>
       </c>
       <c r="L36" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;H36&amp;","&amp;VLOOKUP(I36,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;H36&amp;","&amp;VLOOKUP(I36,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster031','マーマポト',12,120,13,20,0.2,6);</v>
       </c>
     </row>
@@ -34088,7 +34118,7 @@
         <v>37</v>
       </c>
       <c r="L37" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;H37&amp;","&amp;VLOOKUP(I37,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;H37&amp;","&amp;VLOOKUP(I37,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster032','パーパポト',12,141,16,26,0.22,6);</v>
       </c>
     </row>
@@ -34118,7 +34148,7 @@
         <v>37</v>
       </c>
       <c r="L38" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;H38&amp;","&amp;VLOOKUP(I38,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;H38&amp;","&amp;VLOOKUP(I38,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster033','プリースト',13,100,9,13,0.1,6);</v>
       </c>
     </row>
@@ -34151,7 +34181,7 @@
         <v>36</v>
       </c>
       <c r="L39" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;H39&amp;","&amp;VLOOKUP(I39,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;H39&amp;","&amp;VLOOKUP(I39,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster034','カオスソーサラー',13,120,11,16,0.11,5);</v>
       </c>
     </row>
@@ -34184,7 +34214,7 @@
         <v>36</v>
       </c>
       <c r="L40" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;H40&amp;","&amp;VLOOKUP(I40,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;H40&amp;","&amp;VLOOKUP(I40,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster035','イビルシャーマン',13,144,14,20,0.13,5);</v>
       </c>
     </row>
@@ -34215,7 +34245,7 @@
         <v>37</v>
       </c>
       <c r="L41" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;H41&amp;","&amp;VLOOKUP(I41,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;H41&amp;","&amp;VLOOKUP(I41,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster036','ラビ',14,100,11,16,0.16,6);</v>
       </c>
     </row>
@@ -34248,7 +34278,7 @@
         <v>37</v>
       </c>
       <c r="L42" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;H42&amp;","&amp;VLOOKUP(I42,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;H42&amp;","&amp;VLOOKUP(I42,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster037','ラビリオン',14,120,14,20,0.17,6);</v>
       </c>
     </row>
@@ -34281,7 +34311,7 @@
         <v>37</v>
       </c>
       <c r="L43" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;H43&amp;","&amp;VLOOKUP(I43,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;H43&amp;","&amp;VLOOKUP(I43,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster038','キングラビ',14,144,18,26,0.18,6);</v>
       </c>
     </row>
@@ -34314,7 +34344,7 @@
         <v>37</v>
       </c>
       <c r="L44" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;H44&amp;","&amp;VLOOKUP(I44,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;H44&amp;","&amp;VLOOKUP(I44,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster039','グレートラビ',14,172,23,33,0.2,6);</v>
       </c>
     </row>
@@ -34344,7 +34374,7 @@
         <v>34</v>
       </c>
       <c r="L45" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;H45&amp;","&amp;VLOOKUP(I45,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;H45&amp;","&amp;VLOOKUP(I45,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster040','スライム',15,100,10,18,0.15,2);</v>
       </c>
     </row>
@@ -34377,7 +34407,7 @@
         <v>150</v>
       </c>
       <c r="L46" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;H46&amp;","&amp;VLOOKUP(I46,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;H46&amp;","&amp;VLOOKUP(I46,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster041','ブルーババロア',15,120,13,23,0.15,1);</v>
       </c>
     </row>
@@ -34410,7 +34440,7 @@
         <v>151</v>
       </c>
       <c r="L47" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;H47&amp;","&amp;VLOOKUP(I47,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;H47&amp;","&amp;VLOOKUP(I47,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster042','レッドマシュマロ',15,141,16,29,0.15,3);</v>
       </c>
     </row>
@@ -34440,7 +34470,7 @@
         <v>36</v>
       </c>
       <c r="L48" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;H48&amp;","&amp;VLOOKUP(I48,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;H48&amp;","&amp;VLOOKUP(I48,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster043','イビルソード',16,110,15,13,0.14,5);</v>
       </c>
     </row>
@@ -34473,7 +34503,7 @@
         <v>36</v>
       </c>
       <c r="L49" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;H49&amp;","&amp;VLOOKUP(I49,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;H49&amp;","&amp;VLOOKUP(I49,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster044','イビルウェポン',16,132,19,16,0.15,5);</v>
       </c>
     </row>
@@ -34506,7 +34536,7 @@
         <v>37</v>
       </c>
       <c r="L50" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;H50&amp;","&amp;VLOOKUP(I50,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;H50&amp;","&amp;VLOOKUP(I50,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster045','エレメントソード',16,158,24,20,0.16,6);</v>
       </c>
     </row>
@@ -34536,7 +34566,7 @@
         <v>150</v>
       </c>
       <c r="L51" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;H51&amp;","&amp;VLOOKUP(I51,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;H51&amp;","&amp;VLOOKUP(I51,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster046','ケルベロス',17,110,11,19,0.18,1);</v>
       </c>
     </row>
@@ -34569,7 +34599,7 @@
         <v>150</v>
       </c>
       <c r="L52" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;H52&amp;","&amp;VLOOKUP(I52,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;H52&amp;","&amp;VLOOKUP(I52,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster047','バウンドウルフ',17,132,14,24,0.2,1);</v>
       </c>
     </row>
@@ -34602,7 +34632,7 @@
         <v>150</v>
       </c>
       <c r="L53" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;H53&amp;","&amp;VLOOKUP(I53,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;H53&amp;","&amp;VLOOKUP(I53,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster048','ジャッカル',17,158,18,31,0.21,1);</v>
       </c>
     </row>
@@ -34632,7 +34662,7 @@
         <v>151</v>
       </c>
       <c r="L54" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;H54&amp;","&amp;VLOOKUP(I54,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;H54&amp;","&amp;VLOOKUP(I54,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster049','ダックソルジャー',18,120,16,14,0.15,3);</v>
       </c>
     </row>
@@ -34662,7 +34692,7 @@
         <v>151</v>
       </c>
       <c r="L55" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;H55&amp;","&amp;VLOOKUP(I55,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;H55&amp;","&amp;VLOOKUP(I55,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster050','ダックジェネラル',18,160,24,20,0.15,3);</v>
       </c>
     </row>
@@ -34692,7 +34722,7 @@
         <v>34</v>
       </c>
       <c r="L56" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;H56&amp;","&amp;VLOOKUP(I56,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;H56&amp;","&amp;VLOOKUP(I56,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster051','モールベア',19,130,14,18,0.18,2);</v>
       </c>
     </row>
@@ -34722,7 +34752,7 @@
         <v>34</v>
       </c>
       <c r="L57" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;H57&amp;","&amp;VLOOKUP(I57,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;H57&amp;","&amp;VLOOKUP(I57,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster052','ニードリオン',19,170,18,26,0.2,2);</v>
       </c>
     </row>
@@ -34752,7 +34782,7 @@
         <v>35</v>
       </c>
       <c r="L58" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;H58&amp;","&amp;VLOOKUP(I58,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;H58&amp;","&amp;VLOOKUP(I58,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster053','ギャルビー',20,120,13,16,0.2,4);</v>
       </c>
     </row>
@@ -34785,7 +34815,7 @@
         <v>35</v>
       </c>
       <c r="L59" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;H59&amp;","&amp;VLOOKUP(I59,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;H59&amp;","&amp;VLOOKUP(I59,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster054','レディビー',20,144,16,20,0.22,4);</v>
       </c>
     </row>
@@ -34818,7 +34848,7 @@
         <v>35</v>
       </c>
       <c r="L60" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;H60&amp;","&amp;VLOOKUP(I60,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;H60&amp;","&amp;VLOOKUP(I60,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster055','クインビー',20,172,20,26,0.23,4);</v>
       </c>
     </row>
@@ -34848,7 +34878,7 @@
         <v>150</v>
       </c>
       <c r="L61" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;H61&amp;","&amp;VLOOKUP(I61,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;H61&amp;","&amp;VLOOKUP(I61,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster056','サハギン',21,130,16,16,0.15,1);</v>
       </c>
     </row>
@@ -34878,7 +34908,7 @@
         <v>150</v>
       </c>
       <c r="L62" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;H62&amp;","&amp;VLOOKUP(I62,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;H62&amp;","&amp;VLOOKUP(I62,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster057','プチポセイドン',21,150,22,19,0.15,1);</v>
       </c>
     </row>
@@ -34908,7 +34938,7 @@
         <v>298</v>
       </c>
       <c r="L63" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;H63&amp;","&amp;VLOOKUP(I63,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;H63&amp;","&amp;VLOOKUP(I63,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster058','クロウラー',22,130,15,11,0.08,2);</v>
       </c>
     </row>
@@ -34941,7 +34971,7 @@
         <v>34</v>
       </c>
       <c r="L64" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;H64&amp;","&amp;VLOOKUP(I64,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;H64&amp;","&amp;VLOOKUP(I64,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster059','メガクロウラー',22,156,19,14,0.09,2);</v>
       </c>
     </row>
@@ -34974,7 +35004,7 @@
         <v>34</v>
       </c>
       <c r="L65" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;H65&amp;","&amp;VLOOKUP(I65,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;H65&amp;","&amp;VLOOKUP(I65,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster060','ギガクロウラー',22,187,24,18,0.1,2);</v>
       </c>
     </row>
@@ -35004,7 +35034,7 @@
         <v>34</v>
       </c>
       <c r="L66" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;H66&amp;","&amp;VLOOKUP(I66,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;H66&amp;","&amp;VLOOKUP(I66,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster061','ぱっくんオタマ',23,110,12,10,0.15,2);</v>
       </c>
     </row>
@@ -35037,7 +35067,7 @@
         <v>34</v>
       </c>
       <c r="L67" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;H67&amp;","&amp;VLOOKUP(I67,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;H67&amp;","&amp;VLOOKUP(I67,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster062','ぱっくりオタマ',23,132,15,13,0.15,2);</v>
       </c>
     </row>
@@ -35070,7 +35100,7 @@
         <v>151</v>
       </c>
       <c r="L68" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;H68&amp;","&amp;VLOOKUP(I68,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;H68&amp;","&amp;VLOOKUP(I68,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster063','ぱっくんトカゲ',23,158,19,16,0.1,3);</v>
       </c>
     </row>
@@ -35103,7 +35133,7 @@
         <v>151</v>
       </c>
       <c r="L69" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;H69&amp;","&amp;VLOOKUP(I69,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;H69&amp;","&amp;VLOOKUP(I69,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster064','ぱっくんドラゴン',23,189,24,20,0.11,3);</v>
       </c>
     </row>
@@ -35133,7 +35163,7 @@
         <v>36</v>
       </c>
       <c r="L70" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;H70&amp;","&amp;VLOOKUP(I70,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;H70&amp;","&amp;VLOOKUP(I70,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster065','チビデビル',24,120,13,17,0.22,5);</v>
       </c>
     </row>
@@ -35163,7 +35193,7 @@
         <v>36</v>
       </c>
       <c r="L71" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;H71&amp;","&amp;VLOOKUP(I71,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;H71&amp;","&amp;VLOOKUP(I71,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster066','グレムリン',24,160,18,20,0.24,5);</v>
       </c>
     </row>
@@ -35193,7 +35223,7 @@
         <v>36</v>
       </c>
       <c r="L72" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;H72&amp;","&amp;VLOOKUP(I72,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;H72&amp;","&amp;VLOOKUP(I72,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster067','オーガボックス',25,140,18,17,0.15,5);</v>
       </c>
     </row>
@@ -35223,7 +35253,7 @@
         <v>36</v>
       </c>
       <c r="L73" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;H73&amp;","&amp;VLOOKUP(I73,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;H73&amp;","&amp;VLOOKUP(I73,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster068','カイザーミミック',25,170,23,20,0.15,5);</v>
       </c>
     </row>
@@ -35253,7 +35283,7 @@
         <v>151</v>
       </c>
       <c r="L74" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;H74&amp;","&amp;VLOOKUP(I74,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;H74&amp;","&amp;VLOOKUP(I74,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster069','バレッテ',26,140,15,12,0.05,3);</v>
       </c>
     </row>
@@ -35283,7 +35313,7 @@
         <v>151</v>
       </c>
       <c r="L75" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;H75&amp;","&amp;VLOOKUP(I75,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;H75&amp;","&amp;VLOOKUP(I75,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster070','ゴールドバレッテ',26,180,19,14,0.05,3);</v>
       </c>
     </row>
@@ -35313,7 +35343,7 @@
         <v>34</v>
       </c>
       <c r="L76" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;H76&amp;","&amp;VLOOKUP(I76,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;H76&amp;","&amp;VLOOKUP(I76,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster071','バシリスク',27,110,12,15,0.15,2);</v>
       </c>
     </row>
@@ -35343,7 +35373,7 @@
         <v>151</v>
       </c>
       <c r="L77" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;H77&amp;","&amp;VLOOKUP(I77,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;H77&amp;","&amp;VLOOKUP(I77,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster072','ファイアドレイク',27,150,18,22,0.18,3);</v>
       </c>
     </row>
@@ -35373,7 +35403,7 @@
         <v>36</v>
       </c>
       <c r="L78" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;H78&amp;","&amp;VLOOKUP(I78,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;H78&amp;","&amp;VLOOKUP(I78,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster073','スペクター',28,130,13,17,0.2,5);</v>
       </c>
     </row>
@@ -35403,7 +35433,7 @@
         <v>36</v>
       </c>
       <c r="L79" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;H79&amp;","&amp;VLOOKUP(I79,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;H79&amp;","&amp;VLOOKUP(I79,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster074','ゴースト',28,160,17,20,0.21,5);</v>
       </c>
     </row>
@@ -35433,7 +35463,7 @@
         <v>37</v>
       </c>
       <c r="L80" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;","&amp;VLOOKUP(I80,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;","&amp;VLOOKUP(I80,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster075','ユニコーンヘッド',29,120,15,14,0.15,6);</v>
       </c>
     </row>
@@ -35463,7 +35493,7 @@
         <v>37</v>
       </c>
       <c r="L81" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;H81&amp;","&amp;VLOOKUP(I81,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;H81&amp;","&amp;VLOOKUP(I81,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster076','ゴールドユニコ',29,170,22,25,0.15,6);</v>
       </c>
     </row>
@@ -35493,7 +35523,7 @@
         <v>36</v>
       </c>
       <c r="L82" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;H82&amp;","&amp;VLOOKUP(I82,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;H82&amp;","&amp;VLOOKUP(I82,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster077','シェイプシフター',30,130,12,14,0.14,5);</v>
       </c>
     </row>
@@ -35525,7 +35555,7 @@
         <v>36</v>
       </c>
       <c r="L83" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;H83&amp;","&amp;VLOOKUP(I83,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;H83&amp;","&amp;VLOOKUP(I83,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster078','シャドウゼロ',30,170,15,18,0.15,5);</v>
       </c>
     </row>
@@ -35557,7 +35587,7 @@
         <v>36</v>
       </c>
       <c r="L84" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;H84&amp;","&amp;VLOOKUP(I84,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;H84&amp;","&amp;VLOOKUP(I84,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster079','シャドウゼロワン',30,190,19,23,0.16,5);</v>
       </c>
     </row>
@@ -35587,7 +35617,7 @@
         <v>36</v>
       </c>
       <c r="L85" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;H85&amp;","&amp;VLOOKUP(I85,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;H85&amp;","&amp;VLOOKUP(I85,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster080','ボルダー',31,120,13,14,0.25,5);</v>
       </c>
     </row>
@@ -35620,7 +35650,7 @@
         <v>36</v>
       </c>
       <c r="L86" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;H86&amp;","&amp;VLOOKUP(I86,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;H86&amp;","&amp;VLOOKUP(I86,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster081','パワーボルダー',31,144,16,18,0.25,5);</v>
       </c>
     </row>
@@ -35653,7 +35683,7 @@
         <v>36</v>
       </c>
       <c r="L87" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;H87&amp;","&amp;VLOOKUP(I87,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;H87&amp;","&amp;VLOOKUP(I87,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster082','デスボルダー',31,172,20,23,0.25,5);</v>
       </c>
     </row>
@@ -35683,7 +35713,7 @@
         <v>151</v>
       </c>
       <c r="L88" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;H88&amp;","&amp;VLOOKUP(I88,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;H88&amp;","&amp;VLOOKUP(I88,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster083','パンプキンボム',32,130,17,12,0.18,3);</v>
       </c>
     </row>
@@ -35713,7 +35743,7 @@
         <v>151</v>
       </c>
       <c r="L89" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$48:$I$109,3,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;H89&amp;","&amp;VLOOKUP(I89,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;H89&amp;","&amp;VLOOKUP(I89,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster084','グレネードボム',32,160,24,15,0.2,3);</v>
       </c>
     </row>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6C84CA-CB96-40F3-B470-8164FE068E5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF1C6517-DF0B-40AD-8980-161C8A86A038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="3" activeTab="3" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4832" uniqueCount="2445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4836" uniqueCount="2447">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -10190,6 +10190,14 @@
   </si>
   <si>
     <t>https://www.charvel.jp/</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>KIESEL</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.kieselguitars.com/</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -25117,7 +25125,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
-  <dimension ref="B4:K170"/>
+  <dimension ref="B4:K171"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -27730,7 +27738,7 @@
         <v>1551</v>
       </c>
       <c r="K102" s="5" t="str">
-        <f t="shared" ref="K102:K108" si="14">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B102&amp;"'"&amp;","&amp;E102&amp;","&amp;"'"&amp;C102&amp;"'"&amp;","&amp;"'"&amp;D102&amp;"'"&amp;","&amp;"'"&amp;F102&amp;"'"&amp;","&amp;G102&amp;","&amp;H102&amp;","&amp;"'"&amp;I102&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K102:K109" si="14">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B102&amp;"'"&amp;","&amp;E102&amp;","&amp;"'"&amp;C102&amp;"'"&amp;","&amp;"'"&amp;D102&amp;"'"&amp;","&amp;"'"&amp;F102&amp;"'"&amp;","&amp;G102&amp;","&amp;H102&amp;","&amp;"'"&amp;I102&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('guitar_makers',10,'MusicMan','','',0,0.0,'https://www.music-man.com/instruments/guitars');</v>
       </c>
     </row>
@@ -27782,7 +27790,7 @@
         <v>1553</v>
       </c>
       <c r="K104" s="5" t="str">
-        <f t="shared" ref="K104:K107" si="15">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B104&amp;"'"&amp;","&amp;E104&amp;","&amp;"'"&amp;C104&amp;"'"&amp;","&amp;"'"&amp;D104&amp;"'"&amp;","&amp;"'"&amp;F104&amp;"'"&amp;","&amp;G104&amp;","&amp;H104&amp;","&amp;"'"&amp;I104&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K104:K108" si="15">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B104&amp;"'"&amp;","&amp;E104&amp;","&amp;"'"&amp;C104&amp;"'"&amp;","&amp;"'"&amp;D104&amp;"'"&amp;","&amp;"'"&amp;F104&amp;"'"&amp;","&amp;G104&amp;","&amp;H104&amp;","&amp;"'"&amp;I104&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('guitar_makers',12,'Momose','','',0,0.0,'https://www.deviser.co.jp/momose');</v>
       </c>
     </row>
@@ -27886,62 +27894,60 @@
         <v>2444</v>
       </c>
       <c r="K108" s="5" t="str">
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('guitar_makers',16,'CHARVEL','','',0,0.0,'https://www.charvel.jp/');</v>
+      </c>
+    </row>
+    <row r="109" spans="2:11">
+      <c r="B109" s="8" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>2445</v>
+      </c>
+      <c r="D109" s="8"/>
+      <c r="E109" s="8">
+        <v>17</v>
+      </c>
+      <c r="F109" s="8"/>
+      <c r="G109" s="9">
+        <v>0</v>
+      </c>
+      <c r="H109" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I109" s="8" t="s">
+        <v>2446</v>
+      </c>
+      <c r="K109" s="5" t="str">
         <f t="shared" si="14"/>
-        <v>INSERT INTO m_code VALUES ('guitar_makers',16,'CHARVEL','','',0,0.0,'https://www.charvel.jp/');</v>
-      </c>
-    </row>
-    <row r="109" spans="2:11">
-      <c r="B109" s="6" t="s">
+        <v>INSERT INTO m_code VALUES ('guitar_makers',17,'KIESEL','','',0,0.0,'https://www.kieselguitars.com/');</v>
+      </c>
+    </row>
+    <row r="110" spans="2:11">
+      <c r="B110" s="6" t="s">
         <v>1542</v>
       </c>
-      <c r="C109" s="6" t="s">
+      <c r="C110" s="6" t="s">
         <v>1388</v>
       </c>
-      <c r="D109" s="6" t="s">
+      <c r="D110" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E109" s="7" t="s">
+      <c r="E110" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F109" s="6" t="s">
+      <c r="F110" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G109" s="6" t="s">
+      <c r="G110" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H109" s="6" t="s">
+      <c r="H110" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I109" s="6" t="s">
+      <c r="I110" s="6" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="110" spans="2:11">
-      <c r="B110" s="8" t="s">
-        <v>1778</v>
-      </c>
-      <c r="C110" s="8" t="s">
-        <v>1425</v>
-      </c>
-      <c r="D110" s="8"/>
-      <c r="E110" s="8">
-        <v>1</v>
-      </c>
-      <c r="F110" s="8" t="s">
-        <v>1439</v>
-      </c>
-      <c r="G110" s="9">
-        <v>0</v>
-      </c>
-      <c r="H110" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I110" s="8" t="s">
-        <v>1463</v>
-      </c>
-      <c r="K110" s="5" t="str">
-        <f t="shared" ref="K110:K145" si="16">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B110&amp;"'"&amp;","&amp;E110&amp;","&amp;"'"&amp;C110&amp;"'"&amp;","&amp;"'"&amp;D110&amp;"'"&amp;","&amp;"'"&amp;F110&amp;"'"&amp;","&amp;G110&amp;","&amp;H110&amp;","&amp;"'"&amp;I110&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',1,'HardMaple','','ハードメイプル',0,0.0,'硬質でタイト、明瞭なアタック。');</v>
       </c>
     </row>
     <row r="111" spans="2:11">
@@ -27949,14 +27955,14 @@
         <v>1778</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="D111" s="8"/>
       <c r="E111" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G111" s="9">
         <v>0</v>
@@ -27965,11 +27971,11 @@
         <v>125</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="K111" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',2,'FlameMaple','','フレイムメイプル',0,0.0,'明るく抜けが良く、華やかな倍音。');</v>
+        <f t="shared" ref="K111:K146" si="16">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B111&amp;"'"&amp;","&amp;E111&amp;","&amp;"'"&amp;C111&amp;"'"&amp;","&amp;"'"&amp;D111&amp;"'"&amp;","&amp;"'"&amp;F111&amp;"'"&amp;","&amp;G111&amp;","&amp;H111&amp;","&amp;"'"&amp;I111&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',1,'HardMaple','','ハードメイプル',0,0.0,'硬質でタイト、明瞭なアタック。');</v>
       </c>
     </row>
     <row r="112" spans="2:11">
@@ -27977,14 +27983,14 @@
         <v>1778</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="D112" s="8"/>
       <c r="E112" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="G112" s="9">
         <v>0</v>
@@ -27993,11 +27999,11 @@
         <v>125</v>
       </c>
       <c r="I112" s="8" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="K112" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',3,'QuiltedMaple','','キルテッドメイプル',0,0.0,'立体的で広がりがあり、煌びやかな響き。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',2,'FlameMaple','','フレイムメイプル',0,0.0,'明るく抜けが良く、華やかな倍音。');</v>
       </c>
     </row>
     <row r="113" spans="2:11">
@@ -28005,14 +28011,14 @@
         <v>1778</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="G113" s="9">
         <v>0</v>
@@ -28021,11 +28027,11 @@
         <v>125</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="K113" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',4,'BirdseyeMaple','','バーズアイメイプル',0,0.0,'粒立ちが良く、明るくシャープ。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',3,'QuiltedMaple','','キルテッドメイプル',0,0.0,'立体的で広がりがあり、煌びやかな響き。');</v>
       </c>
     </row>
     <row r="114" spans="2:11">
@@ -28033,14 +28039,14 @@
         <v>1778</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="D114" s="8"/>
       <c r="E114" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="G114" s="9">
         <v>0</v>
@@ -28049,11 +28055,11 @@
         <v>125</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="K114" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',5,'RoastedMaple','','ローステッドメイプル',0,0.0,'引き締まったタイトな音で反応が速い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',4,'BirdseyeMaple','','バーズアイメイプル',0,0.0,'粒立ちが良く、明るくシャープ。');</v>
       </c>
     </row>
     <row r="115" spans="2:11">
@@ -28061,14 +28067,14 @@
         <v>1778</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>1389</v>
+        <v>1429</v>
       </c>
       <c r="D115" s="8"/>
       <c r="E115" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>1438</v>
+        <v>1443</v>
       </c>
       <c r="G115" s="9">
         <v>0</v>
@@ -28077,11 +28083,11 @@
         <v>125</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>1462</v>
+        <v>1467</v>
       </c>
       <c r="K115" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',6,'Maple','','メイプル',0,0.0,'明るくハリがあり、アタックが強い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',5,'RoastedMaple','','ローステッドメイプル',0,0.0,'引き締まったタイトな音で反応が速い。');</v>
       </c>
     </row>
     <row r="116" spans="2:11">
@@ -28089,14 +28095,14 @@
         <v>1778</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>1430</v>
+        <v>1389</v>
       </c>
       <c r="D116" s="8"/>
       <c r="E116" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>1444</v>
+        <v>1438</v>
       </c>
       <c r="G116" s="9">
         <v>0</v>
@@ -28105,11 +28111,11 @@
         <v>125</v>
       </c>
       <c r="I116" s="8" t="s">
-        <v>1469</v>
+        <v>1462</v>
       </c>
       <c r="K116" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',7,'HonduranMahogany','','ホンジュラスマホガニー',0,0.0,'深みがあり、太くリッチな中低域。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',6,'Maple','','メイプル',0,0.0,'明るくハリがあり、アタックが強い。');</v>
       </c>
     </row>
     <row r="117" spans="2:11">
@@ -28117,14 +28123,14 @@
         <v>1778</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>1390</v>
+        <v>1430</v>
       </c>
       <c r="D117" s="8"/>
       <c r="E117" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>1408</v>
+        <v>1444</v>
       </c>
       <c r="G117" s="9">
         <v>0</v>
@@ -28133,11 +28139,11 @@
         <v>125</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="K117" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',8,'Mahogany','','マホガニー',0,0.0,'中低域が豊かで温かい音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',7,'HonduranMahogany','','ホンジュラスマホガニー',0,0.0,'深みがあり、太くリッチな中低域。');</v>
       </c>
     </row>
     <row r="118" spans="2:11">
@@ -28145,14 +28151,14 @@
         <v>1778</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>1431</v>
+        <v>1390</v>
       </c>
       <c r="D118" s="8"/>
       <c r="E118" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>1445</v>
+        <v>1408</v>
       </c>
       <c r="G118" s="9">
         <v>0</v>
@@ -28161,11 +28167,11 @@
         <v>125</v>
       </c>
       <c r="I118" s="8" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="K118" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',9,'Sapele','','サペリ',0,0.0,'温かく柔らかいトーンでバランスが良い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',8,'Mahogany','','マホガニー',0,0.0,'中低域が豊かで温かい音。');</v>
       </c>
     </row>
     <row r="119" spans="2:11">
@@ -28173,14 +28179,14 @@
         <v>1778</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>1397</v>
+        <v>1431</v>
       </c>
       <c r="D119" s="8"/>
       <c r="E119" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="G119" s="9">
         <v>0</v>
@@ -28189,11 +28195,11 @@
         <v>125</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="K119" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',10,'Korina','','コリーナ',0,0.0,'中域が豊かで太い音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',9,'Sapele','','サペリ',0,0.0,'温かく柔らかいトーンでバランスが良い。');</v>
       </c>
     </row>
     <row r="120" spans="2:11">
@@ -28201,14 +28207,14 @@
         <v>1778</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>1432</v>
+        <v>1397</v>
       </c>
       <c r="D120" s="8"/>
       <c r="E120" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="G120" s="9">
         <v>0</v>
@@ -28217,11 +28223,11 @@
         <v>125</v>
       </c>
       <c r="I120" s="8" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="K120" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',11,'WhiteKorina','','ホワイトコリーナ',0,0.0,'明るく抜けが良く、軽快なレスポンス。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',10,'Korina','','コリーナ',0,0.0,'中域が豊かで太い音。');</v>
       </c>
     </row>
     <row r="121" spans="2:11">
@@ -28229,14 +28235,14 @@
         <v>1778</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>1391</v>
+        <v>1432</v>
       </c>
       <c r="D121" s="8"/>
       <c r="E121" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>1409</v>
+        <v>1447</v>
       </c>
       <c r="G121" s="9">
         <v>0</v>
@@ -28245,11 +28251,11 @@
         <v>125</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="K121" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',12,'Alder','','アルダー',0,0.0,'バランスが良くクセが少ない。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',11,'WhiteKorina','','ホワイトコリーナ',0,0.0,'明るく抜けが良く、軽快なレスポンス。');</v>
       </c>
     </row>
     <row r="122" spans="2:11">
@@ -28257,14 +28263,14 @@
         <v>1778</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="D122" s="8"/>
       <c r="E122" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>1448</v>
+        <v>1409</v>
       </c>
       <c r="G122" s="9">
         <v>0</v>
@@ -28273,11 +28279,11 @@
         <v>125</v>
       </c>
       <c r="I122" s="8" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="K122" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',13,'Ash','','アッシュ',0,0.0,'明るく抜ける音でアタックが強い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',12,'Alder','','アルダー',0,0.0,'バランスが良くクセが少ない。');</v>
       </c>
     </row>
     <row r="123" spans="2:11">
@@ -28285,14 +28291,14 @@
         <v>1778</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="D123" s="8"/>
       <c r="E123" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="G123" s="9">
         <v>0</v>
@@ -28301,11 +28307,11 @@
         <v>125</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="K123" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',14,'Basswood','','バスウッド',0,0.0,'軽く柔らかく、ウォームで扱いやすい。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',13,'Ash','','アッシュ',0,0.0,'明るく抜ける音でアタックが強い。');</v>
       </c>
     </row>
     <row r="124" spans="2:11">
@@ -28313,14 +28319,14 @@
         <v>1778</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>1402</v>
+        <v>1393</v>
       </c>
       <c r="D124" s="8"/>
       <c r="E124" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F124" s="8" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="G124" s="9">
         <v>0</v>
@@ -28329,11 +28335,11 @@
         <v>125</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="K124" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',15,'Poplar','','ポプラ',0,0.0,'軽く素直でクセが少ない。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',14,'Basswood','','バスウッド',0,0.0,'軽く柔らかく、ウォームで扱いやすい。');</v>
       </c>
     </row>
     <row r="125" spans="2:11">
@@ -28341,14 +28347,14 @@
         <v>1778</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="D125" s="8"/>
       <c r="E125" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="G125" s="9">
         <v>0</v>
@@ -28357,11 +28363,11 @@
         <v>125</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="K125" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',16,'Spruce','','スプルース',0,0.0,'軽く響きが良く、明るいトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',15,'Poplar','','ポプラ',0,0.0,'軽く素直でクセが少ない。');</v>
       </c>
     </row>
     <row r="126" spans="2:11">
@@ -28369,14 +28375,14 @@
         <v>1778</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="D126" s="8"/>
       <c r="E126" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="G126" s="9">
         <v>0</v>
@@ -28385,11 +28391,11 @@
         <v>125</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="K126" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',17,'Cedar','','シダー',0,0.0,'柔らかく温かい音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',16,'Spruce','','スプルース',0,0.0,'軽く響きが良く、明るいトーン。');</v>
       </c>
     </row>
     <row r="127" spans="2:11">
@@ -28397,14 +28403,14 @@
         <v>1778</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>1433</v>
+        <v>1399</v>
       </c>
       <c r="D127" s="8"/>
       <c r="E127" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="G127" s="9">
         <v>0</v>
@@ -28413,11 +28419,11 @@
         <v>125</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="K127" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',18,'IndianRosewood','','インディアンローズウッド',0,0.0,'甘く深みがあり、豊かな中低域。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',17,'Cedar','','シダー',0,0.0,'柔らかく温かい音。');</v>
       </c>
     </row>
     <row r="128" spans="2:11">
@@ -28425,14 +28431,14 @@
         <v>1778</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="D128" s="8"/>
       <c r="E128" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="G128" s="9">
         <v>0</v>
@@ -28441,11 +28447,11 @@
         <v>125</v>
       </c>
       <c r="I128" s="8" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="K128" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',19,'BrazilianRosewood','','ブラジリアンローズウッド',0,0.0,'濃厚で深いトーン、豊かな倍音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',18,'IndianRosewood','','インディアンローズウッド',0,0.0,'甘く深みがあり、豊かな中低域。');</v>
       </c>
     </row>
     <row r="129" spans="2:11">
@@ -28453,14 +28459,14 @@
         <v>1778</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>1394</v>
+        <v>1434</v>
       </c>
       <c r="D129" s="8"/>
       <c r="E129" s="8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="G129" s="9">
         <v>0</v>
@@ -28469,11 +28475,11 @@
         <v>125</v>
       </c>
       <c r="I129" s="8" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="K129" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',20,'Rosewood','','ローズウッド',0,0.0,'甘く丸い音で中域が豊か。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',19,'BrazilianRosewood','','ブラジリアンローズウッド',0,0.0,'濃厚で深いトーン、豊かな倍音。');</v>
       </c>
     </row>
     <row r="130" spans="2:11">
@@ -28481,14 +28487,14 @@
         <v>1778</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>1435</v>
+        <v>1394</v>
       </c>
       <c r="D130" s="8"/>
       <c r="E130" s="8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>1410</v>
+        <v>1453</v>
       </c>
       <c r="G130" s="9">
         <v>0</v>
@@ -28497,11 +28503,11 @@
         <v>125</v>
       </c>
       <c r="I130" s="8" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="K130" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',21,'PauFerro','','パーフェロー',0,0.0,'明るく硬質でタイトな音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',20,'Rosewood','','ローズウッド',0,0.0,'甘く丸い音で中域が豊か。');</v>
       </c>
     </row>
     <row r="131" spans="2:11">
@@ -28509,14 +28515,14 @@
         <v>1778</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>1400</v>
+        <v>1435</v>
       </c>
       <c r="D131" s="8"/>
       <c r="E131" s="8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="G131" s="9">
         <v>0</v>
@@ -28525,11 +28531,11 @@
         <v>125</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="K131" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',22,'Ovangkol','','オバンコール',0,0.0,'中域が豊かで温かいトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',21,'PauFerro','','パーフェロー',0,0.0,'明るく硬質でタイトな音。');</v>
       </c>
     </row>
     <row r="132" spans="2:11">
@@ -28537,14 +28543,14 @@
         <v>1778</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>1395</v>
+        <v>1400</v>
       </c>
       <c r="D132" s="8"/>
       <c r="E132" s="8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>1456</v>
+        <v>1411</v>
       </c>
       <c r="G132" s="9">
         <v>0</v>
@@ -28553,11 +28559,11 @@
         <v>125</v>
       </c>
       <c r="I132" s="8" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="K132" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',23,'Ebony','','エボニー',0,0.0,'硬くタイトで高域がクリア。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',22,'Ovangkol','','オバンコール',0,0.0,'中域が豊かで温かいトーン。');</v>
       </c>
     </row>
     <row r="133" spans="2:11">
@@ -28565,14 +28571,14 @@
         <v>1778</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="D133" s="8"/>
       <c r="E133" s="8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F133" s="8" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="G133" s="9">
         <v>0</v>
@@ -28581,11 +28587,11 @@
         <v>125</v>
       </c>
       <c r="I133" s="8" t="s">
-        <v>1416</v>
+        <v>1484</v>
       </c>
       <c r="K133" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',24,'Walnut','','ウォルナット',0,0.0,'中域が豊かで落ち着いたトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',23,'Ebony','','エボニー',0,0.0,'硬くタイトで高域がクリア。');</v>
       </c>
     </row>
     <row r="134" spans="2:11">
@@ -28593,14 +28599,14 @@
         <v>1778</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>1436</v>
+        <v>1396</v>
       </c>
       <c r="D134" s="8"/>
       <c r="E134" s="8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F134" s="8" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="G134" s="9">
         <v>0</v>
@@ -28609,11 +28615,11 @@
         <v>125</v>
       </c>
       <c r="I134" s="8" t="s">
-        <v>1485</v>
+        <v>1416</v>
       </c>
       <c r="K134" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',25,'Padauk','','パドゥーク',0,0.0,'明るく抜けが良く、個性的な響き。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',24,'Walnut','','ウォルナット',0,0.0,'中域が豊かで落ち着いたトーン。');</v>
       </c>
     </row>
     <row r="135" spans="2:11">
@@ -28621,14 +28627,14 @@
         <v>1778</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>1401</v>
+        <v>1436</v>
       </c>
       <c r="D135" s="8"/>
       <c r="E135" s="8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F135" s="8" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="G135" s="9">
         <v>0</v>
@@ -28637,11 +28643,11 @@
         <v>125</v>
       </c>
       <c r="I135" s="8" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="K135" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',26,'Koa','','コア',0,0.0,'明るく華やかで軽快。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',25,'Padauk','','パドゥーク',0,0.0,'明るく抜けが良く、個性的な響き。');</v>
       </c>
     </row>
     <row r="136" spans="2:11">
@@ -28649,14 +28655,14 @@
         <v>1778</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="D136" s="8"/>
       <c r="E136" s="8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F136" s="8" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="G136" s="9">
         <v>0</v>
@@ -28665,11 +28671,11 @@
         <v>125</v>
       </c>
       <c r="I136" s="8" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="K136" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',27,'Nato','','ナトー',0,0.0,'中低域が豊かで温かい。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',26,'Koa','','コア',0,0.0,'明るく華やかで軽快。');</v>
       </c>
     </row>
     <row r="137" spans="2:11">
@@ -28677,14 +28683,14 @@
         <v>1778</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="D137" s="8"/>
       <c r="E137" s="8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F137" s="8" t="s">
-        <v>1412</v>
+        <v>1460</v>
       </c>
       <c r="G137" s="9">
         <v>0</v>
@@ -28693,11 +28699,11 @@
         <v>125</v>
       </c>
       <c r="I137" s="8" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="K137" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',28,'Agathis','','アガチス',0,0.0,'柔らかくウォームで素直。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',27,'Nato','','ナトー',0,0.0,'中低域が豊かで温かい。');</v>
       </c>
     </row>
     <row r="138" spans="2:11">
@@ -28705,14 +28711,14 @@
         <v>1778</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="D138" s="8"/>
       <c r="E138" s="8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="G138" s="9">
         <v>0</v>
@@ -28721,11 +28727,11 @@
         <v>125</v>
       </c>
       <c r="I138" s="8" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="K138" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',29,'Bubinga','','ブビンガ',0,0.0,'重く硬質でサスティンが長い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',28,'Agathis','','アガチス',0,0.0,'柔らかくウォームで素直。');</v>
       </c>
     </row>
     <row r="139" spans="2:11">
@@ -28733,14 +28739,14 @@
         <v>1778</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="G139" s="9">
         <v>0</v>
@@ -28749,11 +28755,11 @@
         <v>125</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="K139" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',30,'Wenge','','ウェンジ',0,0.0,'非常に硬くタイトで個性的。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',29,'Bubinga','','ブビンガ',0,0.0,'重く硬質でサスティンが長い。');</v>
       </c>
     </row>
     <row r="140" spans="2:11">
@@ -28761,14 +28767,14 @@
         <v>1778</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D140" s="8"/>
       <c r="E140" s="8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F140" s="8" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="G140" s="9">
         <v>0</v>
@@ -28777,11 +28783,11 @@
         <v>125</v>
       </c>
       <c r="I140" s="8" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="K140" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',31,'Purpleheart','','パープルハート',0,0.0,'硬く鮮やかでアタックが強い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',30,'Wenge','','ウェンジ',0,0.0,'非常に硬くタイトで個性的。');</v>
       </c>
     </row>
     <row r="141" spans="2:11">
@@ -28789,14 +28795,14 @@
         <v>1778</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>1437</v>
+        <v>1407</v>
       </c>
       <c r="D141" s="8"/>
       <c r="E141" s="8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>1461</v>
+        <v>1415</v>
       </c>
       <c r="G141" s="9">
         <v>0</v>
@@ -28805,11 +28811,11 @@
         <v>125</v>
       </c>
       <c r="I141" s="8" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="K141" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',32,'Zebrawood','','ゼブラウッド',0,0.0,'明るく硬質でクセのあるトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',31,'Purpleheart','','パープルハート',0,0.0,'硬く鮮やかでアタックが強い。');</v>
       </c>
     </row>
     <row r="142" spans="2:11">
@@ -28817,14 +28823,14 @@
         <v>1778</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>1558</v>
+        <v>1437</v>
       </c>
       <c r="D142" s="8"/>
       <c r="E142" s="8">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>1559</v>
+        <v>1461</v>
       </c>
       <c r="G142" s="9">
         <v>0</v>
@@ -28833,11 +28839,11 @@
         <v>125</v>
       </c>
       <c r="I142" s="8" t="s">
-        <v>1560</v>
+        <v>1492</v>
       </c>
       <c r="K142" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',33,'Okoume','','オクメ',0,0.0,'マホガニーに近く、中低域が豊かで軽量。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',32,'Zebrawood','','ゼブラウッド',0,0.0,'明るく硬質でクセのあるトーン。');</v>
       </c>
     </row>
     <row r="143" spans="2:11">
@@ -28845,14 +28851,14 @@
         <v>1778</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="D143" s="8"/>
       <c r="E143" s="8">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F143" s="8" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="G143" s="9">
         <v>0</v>
@@ -28861,11 +28867,11 @@
         <v>125</v>
       </c>
       <c r="I143" s="8" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="K143" s="5" t="str">
-        <f t="shared" ref="K143" si="17">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B143&amp;"'"&amp;","&amp;E143&amp;","&amp;"'"&amp;C143&amp;"'"&amp;","&amp;"'"&amp;D143&amp;"'"&amp;","&amp;"'"&amp;F143&amp;"'"&amp;","&amp;G143&amp;","&amp;H143&amp;","&amp;"'"&amp;I143&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',34,'Meranti','','メランティ',0,0.0,'中域寄りで温かめ、マホガニー系に近い。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',33,'Okoume','','オクメ',0,0.0,'マホガニーに近く、中低域が豊かで軽量。');</v>
       </c>
     </row>
     <row r="144" spans="2:11">
@@ -28873,14 +28879,14 @@
         <v>1778</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="D144" s="8"/>
       <c r="E144" s="8">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F144" s="8" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="G144" s="9">
         <v>0</v>
@@ -28889,11 +28895,11 @@
         <v>125</v>
       </c>
       <c r="I144" s="8" t="s">
-        <v>1569</v>
+        <v>1563</v>
       </c>
       <c r="K144" s="5" t="str">
-        <f t="shared" ref="K144" si="18">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B144&amp;"'"&amp;","&amp;E144&amp;","&amp;"'"&amp;C144&amp;"'"&amp;","&amp;"'"&amp;D144&amp;"'"&amp;","&amp;"'"&amp;F144&amp;"'"&amp;","&amp;G144&amp;","&amp;H144&amp;","&amp;"'"&amp;I144&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',35,'Sakura','','サクラ',0,0.0,'中高域が明るく立ち上がりが速い、日本らしい軽快で抜けの良いサウンド。');</v>
+        <f t="shared" ref="K144" si="17">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B144&amp;"'"&amp;","&amp;E144&amp;","&amp;"'"&amp;C144&amp;"'"&amp;","&amp;"'"&amp;D144&amp;"'"&amp;","&amp;"'"&amp;F144&amp;"'"&amp;","&amp;G144&amp;","&amp;H144&amp;","&amp;"'"&amp;I144&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',34,'Meranti','','メランティ',0,0.0,'中域寄りで温かめ、マホガニー系に近い。');</v>
       </c>
     </row>
     <row r="145" spans="2:11">
@@ -28901,14 +28907,14 @@
         <v>1778</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="D145" s="8"/>
       <c r="E145" s="8">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="G145" s="9">
         <v>0</v>
@@ -28917,11 +28923,11 @@
         <v>125</v>
       </c>
       <c r="I145" s="8" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="K145" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',36,'Tochi','','トチ',0,0.0,'メイプルに近いクリアさと華やかさを持ちつつ、やや柔らかく豊かな倍音.');</v>
+        <f t="shared" ref="K145" si="18">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B145&amp;"'"&amp;","&amp;E145&amp;","&amp;"'"&amp;C145&amp;"'"&amp;","&amp;"'"&amp;D145&amp;"'"&amp;","&amp;"'"&amp;F145&amp;"'"&amp;","&amp;G145&amp;","&amp;H145&amp;","&amp;"'"&amp;I145&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',35,'Sakura','','サクラ',0,0.0,'中高域が明るく立ち上がりが速い、日本らしい軽快で抜けの良いサウンド。');</v>
       </c>
     </row>
     <row r="146" spans="2:11">
@@ -28929,14 +28935,14 @@
         <v>1778</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>1424</v>
+        <v>1566</v>
       </c>
       <c r="D146" s="8"/>
       <c r="E146" s="8">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="F146" s="8" t="s">
-        <v>1423</v>
+        <v>1567</v>
       </c>
       <c r="G146" s="9">
         <v>0</v>
@@ -28944,62 +28950,64 @@
       <c r="H146" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="I146" s="8"/>
+      <c r="I146" s="8" t="s">
+        <v>1568</v>
+      </c>
       <c r="K146" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B146&amp;"'"&amp;","&amp;E146&amp;","&amp;"'"&amp;C146&amp;"'"&amp;","&amp;"'"&amp;D146&amp;"'"&amp;","&amp;"'"&amp;F146&amp;"'"&amp;","&amp;G146&amp;","&amp;H146&amp;","&amp;"'"&amp;I146&amp;"'"&amp;");"</f>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',36,'Tochi','','トチ',0,0.0,'メイプルに近いクリアさと華やかさを持ちつつ、やや柔らかく豊かな倍音.');</v>
+      </c>
+    </row>
+    <row r="147" spans="2:11">
+      <c r="B147" s="8" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C147" s="8" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D147" s="8"/>
+      <c r="E147" s="8">
+        <v>99</v>
+      </c>
+      <c r="F147" s="8" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G147" s="9">
+        <v>0</v>
+      </c>
+      <c r="H147" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I147" s="8"/>
+      <c r="K147" s="5" t="str">
+        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B147&amp;"'"&amp;","&amp;E147&amp;","&amp;"'"&amp;C147&amp;"'"&amp;","&amp;"'"&amp;D147&amp;"'"&amp;","&amp;"'"&amp;F147&amp;"'"&amp;","&amp;G147&amp;","&amp;H147&amp;","&amp;"'"&amp;I147&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('guitar_woods',99,'Unknown','','？？',0,0.0,'');</v>
       </c>
     </row>
-    <row r="147" spans="2:11">
-      <c r="B147" s="6" t="s">
+    <row r="148" spans="2:11">
+      <c r="B148" s="6" t="s">
         <v>1503</v>
       </c>
-      <c r="C147" s="6" t="s">
+      <c r="C148" s="6" t="s">
         <v>1502</v>
       </c>
-      <c r="D147" s="6" t="s">
+      <c r="D148" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E147" s="7" t="s">
+      <c r="E148" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F147" s="6" t="s">
+      <c r="F148" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G147" s="6" t="s">
+      <c r="G148" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H147" s="6" t="s">
+      <c r="H148" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I147" s="6" t="s">
+      <c r="I148" s="6" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="148" spans="2:11">
-      <c r="B148" s="8" t="s">
-        <v>1779</v>
-      </c>
-      <c r="C148" s="8" t="s">
-        <v>1504</v>
-      </c>
-      <c r="D148" s="8"/>
-      <c r="E148" s="8">
-        <v>1</v>
-      </c>
-      <c r="F148" s="8" t="s">
-        <v>1520</v>
-      </c>
-      <c r="G148" s="9">
-        <v>0</v>
-      </c>
-      <c r="H148" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I148" s="8"/>
-      <c r="K148" s="5" t="str">
-        <f t="shared" ref="K148:K170" si="19">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B148&amp;"'"&amp;","&amp;E148&amp;","&amp;"'"&amp;C148&amp;"'"&amp;","&amp;"'"&amp;D148&amp;"'"&amp;","&amp;"'"&amp;F148&amp;"'"&amp;","&amp;G148&amp;","&amp;H148&amp;","&amp;"'"&amp;I148&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',1,'Red','','レッド',0,0.0,'');</v>
       </c>
     </row>
     <row r="149" spans="2:11">
@@ -29007,14 +29015,14 @@
         <v>1779</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>1518</v>
+        <v>1504</v>
       </c>
       <c r="D149" s="8"/>
       <c r="E149" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F149" s="8" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="G149" s="9">
         <v>0</v>
@@ -29024,8 +29032,8 @@
       </c>
       <c r="I149" s="8"/>
       <c r="K149" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',2,'Pink','','ピンク',0,0.0,'');</v>
+        <f t="shared" ref="K149:K171" si="19">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B149&amp;"'"&amp;","&amp;E149&amp;","&amp;"'"&amp;C149&amp;"'"&amp;","&amp;"'"&amp;D149&amp;"'"&amp;","&amp;"'"&amp;F149&amp;"'"&amp;","&amp;G149&amp;","&amp;H149&amp;","&amp;"'"&amp;I149&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',1,'Red','','レッド',0,0.0,'');</v>
       </c>
     </row>
     <row r="150" spans="2:11">
@@ -29033,14 +29041,14 @@
         <v>1779</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>1505</v>
+        <v>1518</v>
       </c>
       <c r="D150" s="8"/>
       <c r="E150" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="G150" s="9">
         <v>0</v>
@@ -29051,7 +29059,7 @@
       <c r="I150" s="8"/>
       <c r="K150" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',3,'Orange','','オレンジ',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',2,'Pink','','ピンク',0,0.0,'');</v>
       </c>
     </row>
     <row r="151" spans="2:11">
@@ -29059,14 +29067,14 @@
         <v>1779</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="D151" s="8"/>
       <c r="E151" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="G151" s="9">
         <v>0</v>
@@ -29077,7 +29085,7 @@
       <c r="I151" s="8"/>
       <c r="K151" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',4,'Yellow','','イエロー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',3,'Orange','','オレンジ',0,0.0,'');</v>
       </c>
     </row>
     <row r="152" spans="2:11">
@@ -29085,14 +29093,14 @@
         <v>1779</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D152" s="8"/>
       <c r="E152" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F152" s="8" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="G152" s="9">
         <v>0</v>
@@ -29103,7 +29111,7 @@
       <c r="I152" s="8"/>
       <c r="K152" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',5,'Green','','グリーン',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',4,'Yellow','','イエロー',0,0.0,'');</v>
       </c>
     </row>
     <row r="153" spans="2:11">
@@ -29111,14 +29119,14 @@
         <v>1779</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="D153" s="8"/>
       <c r="E153" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="G153" s="9">
         <v>0</v>
@@ -29129,7 +29137,7 @@
       <c r="I153" s="8"/>
       <c r="K153" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',6,'SkyBlue','','スカイブルー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',5,'Green','','グリーン',0,0.0,'');</v>
       </c>
     </row>
     <row r="154" spans="2:11">
@@ -29137,14 +29145,14 @@
         <v>1779</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="D154" s="8"/>
       <c r="E154" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="G154" s="9">
         <v>0</v>
@@ -29155,7 +29163,7 @@
       <c r="I154" s="8"/>
       <c r="K154" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',7,'Blue','','ブルー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',6,'SkyBlue','','スカイブルー',0,0.0,'');</v>
       </c>
     </row>
     <row r="155" spans="2:11">
@@ -29163,14 +29171,14 @@
         <v>1779</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="D155" s="8"/>
       <c r="E155" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F155" s="8" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="G155" s="9">
         <v>0</v>
@@ -29181,7 +29189,7 @@
       <c r="I155" s="8"/>
       <c r="K155" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',8,'Purple','','パープル',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',7,'Blue','','ブルー',0,0.0,'');</v>
       </c>
     </row>
     <row r="156" spans="2:11">
@@ -29189,14 +29197,14 @@
         <v>1779</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="D156" s="8"/>
       <c r="E156" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F156" s="8" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="G156" s="9">
         <v>0</v>
@@ -29207,7 +29215,7 @@
       <c r="I156" s="8"/>
       <c r="K156" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',9,'Gray','','グレー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',8,'Purple','','パープル',0,0.0,'');</v>
       </c>
     </row>
     <row r="157" spans="2:11">
@@ -29215,14 +29223,14 @@
         <v>1779</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="D157" s="8"/>
       <c r="E157" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F157" s="8" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="G157" s="9">
         <v>0</v>
@@ -29233,7 +29241,7 @@
       <c r="I157" s="8"/>
       <c r="K157" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',10,'Black','','ブラック',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',9,'Gray','','グレー',0,0.0,'');</v>
       </c>
     </row>
     <row r="158" spans="2:11">
@@ -29241,14 +29249,14 @@
         <v>1779</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="D158" s="8"/>
       <c r="E158" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="G158" s="9">
         <v>0</v>
@@ -29259,7 +29267,7 @@
       <c r="I158" s="8"/>
       <c r="K158" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',11,'White','','ホワイト',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',10,'Black','','ブラック',0,0.0,'');</v>
       </c>
     </row>
     <row r="159" spans="2:11">
@@ -29267,14 +29275,14 @@
         <v>1779</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="D159" s="8"/>
       <c r="E159" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="G159" s="9">
         <v>0</v>
@@ -29285,7 +29293,7 @@
       <c r="I159" s="8"/>
       <c r="K159" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',12,'Natural','','ナチュラル',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',11,'White','','ホワイト',0,0.0,'');</v>
       </c>
     </row>
     <row r="160" spans="2:11">
@@ -29293,14 +29301,14 @@
         <v>1779</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>1519</v>
+        <v>1514</v>
       </c>
       <c r="D160" s="8"/>
       <c r="E160" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F160" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="G160" s="9">
         <v>0</v>
@@ -29311,7 +29319,7 @@
       <c r="I160" s="8"/>
       <c r="K160" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',13,'Brown','','ブラウン',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',12,'Natural','','ナチュラル',0,0.0,'');</v>
       </c>
     </row>
     <row r="161" spans="2:11">
@@ -29319,14 +29327,14 @@
         <v>1779</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="D161" s="8"/>
       <c r="E161" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F161" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="G161" s="9">
         <v>0</v>
@@ -29337,7 +29345,7 @@
       <c r="I161" s="8"/>
       <c r="K161" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',14,'Gold','','ゴールド',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',13,'Brown','','ブラウン',0,0.0,'');</v>
       </c>
     </row>
     <row r="162" spans="2:11">
@@ -29345,14 +29353,14 @@
         <v>1779</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="D162" s="8"/>
       <c r="E162" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="G162" s="9">
         <v>0</v>
@@ -29363,7 +29371,7 @@
       <c r="I162" s="8"/>
       <c r="K162" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',15,'Silver','','シルバー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',14,'Gold','','ゴールド',0,0.0,'');</v>
       </c>
     </row>
     <row r="163" spans="2:11">
@@ -29371,14 +29379,14 @@
         <v>1779</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D163" s="8"/>
       <c r="E163" s="8">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="F163" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G163" s="9">
         <v>0</v>
@@ -29389,59 +29397,59 @@
       <c r="I163" s="8"/>
       <c r="K163" s="5" t="str">
         <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',15,'Silver','','シルバー',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="164" spans="2:11">
+      <c r="B164" s="8" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C164" s="8" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D164" s="8"/>
+      <c r="E164" s="8">
+        <v>99</v>
+      </c>
+      <c r="F164" s="8" t="s">
+        <v>1535</v>
+      </c>
+      <c r="G164" s="9">
+        <v>0</v>
+      </c>
+      <c r="H164" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I164" s="8"/>
+      <c r="K164" s="5" t="str">
+        <f t="shared" si="19"/>
         <v>INSERT INTO m_code VALUES ('guitar_colors',99,'Others','','その他',0,0.0,'');</v>
       </c>
     </row>
-    <row r="164" spans="2:11">
-      <c r="B164" s="6" t="s">
+    <row r="165" spans="2:11">
+      <c r="B165" s="6" t="s">
         <v>1888</v>
       </c>
-      <c r="C164" s="6" t="s">
+      <c r="C165" s="6" t="s">
         <v>1889</v>
       </c>
-      <c r="D164" s="6" t="s">
+      <c r="D165" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E164" s="7" t="s">
+      <c r="E165" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F164" s="6" t="s">
+      <c r="F165" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G164" s="6" t="s">
+      <c r="G165" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H164" s="6" t="s">
+      <c r="H165" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I164" s="6" t="s">
+      <c r="I165" s="6" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="165" spans="2:11">
-      <c r="B165" s="8" t="s">
-        <v>1892</v>
-      </c>
-      <c r="C165" s="8" t="s">
-        <v>1890</v>
-      </c>
-      <c r="D165" s="8"/>
-      <c r="E165" s="8">
-        <v>1</v>
-      </c>
-      <c r="F165" s="8"/>
-      <c r="G165" s="9">
-        <v>0</v>
-      </c>
-      <c r="H165" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I165" s="8" t="s">
-        <v>1893</v>
-      </c>
-      <c r="K165" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',1,'SUCCESS','','',0,0.0,'処理成功');</v>
       </c>
     </row>
     <row r="166" spans="2:11">
@@ -29449,11 +29457,11 @@
         <v>1892</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="D166" s="8"/>
       <c r="E166" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F166" s="8"/>
       <c r="G166" s="9">
@@ -29463,11 +29471,11 @@
         <v>125</v>
       </c>
       <c r="I166" s="8" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="K166" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',2,'STARTED','','',0,0.0,'処理開始。いずかのステータスに遷移する。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',1,'SUCCESS','','',0,0.0,'処理成功');</v>
       </c>
     </row>
     <row r="167" spans="2:11">
@@ -29475,11 +29483,11 @@
         <v>1892</v>
       </c>
       <c r="C167" s="8" t="s">
-        <v>1881</v>
+        <v>1891</v>
       </c>
       <c r="D167" s="8"/>
       <c r="E167" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F167" s="8"/>
       <c r="G167" s="9">
@@ -29489,11 +29497,11 @@
         <v>125</v>
       </c>
       <c r="I167" s="8" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="K167" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',3,'NOT_STARTED','','',0,0.0,'予定時刻に開始されていない。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',2,'STARTED','','',0,0.0,'処理開始。いずかのステータスに遷移する。');</v>
       </c>
     </row>
     <row r="168" spans="2:11">
@@ -29501,11 +29509,11 @@
         <v>1892</v>
       </c>
       <c r="C168" s="8" t="s">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="D168" s="8"/>
       <c r="E168" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F168" s="8"/>
       <c r="G168" s="9">
@@ -29515,11 +29523,11 @@
         <v>125</v>
       </c>
       <c r="I168" s="8" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="K168" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',4,'ERROR','','',0,0.0,'例外、パニック等が発生した。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',3,'NOT_STARTED','','',0,0.0,'予定時刻に開始されていない。');</v>
       </c>
     </row>
     <row r="169" spans="2:11">
@@ -29527,11 +29535,11 @@
         <v>1892</v>
       </c>
       <c r="C169" s="8" t="s">
-        <v>1882</v>
+        <v>1879</v>
       </c>
       <c r="D169" s="8"/>
       <c r="E169" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F169" s="8"/>
       <c r="G169" s="9">
@@ -29541,11 +29549,11 @@
         <v>125</v>
       </c>
       <c r="I169" s="8" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="K169" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',5,'SLOW','','',0,0.0,'想定時間内に処理が終了しなかった。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',4,'ERROR','','',0,0.0,'例外、パニック等が発生した。');</v>
       </c>
     </row>
     <row r="170" spans="2:11">
@@ -29553,11 +29561,11 @@
         <v>1892</v>
       </c>
       <c r="C170" s="8" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="D170" s="8"/>
       <c r="E170" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F170" s="8"/>
       <c r="G170" s="9">
@@ -29567,9 +29575,35 @@
         <v>125</v>
       </c>
       <c r="I170" s="8" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K170" s="5" t="str">
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('batch_status',5,'SLOW','','',0,0.0,'想定時間内に処理が終了しなかった。');</v>
+      </c>
+    </row>
+    <row r="171" spans="2:11">
+      <c r="B171" s="8" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C171" s="8" t="s">
+        <v>1880</v>
+      </c>
+      <c r="D171" s="8"/>
+      <c r="E171" s="8">
+        <v>6</v>
+      </c>
+      <c r="F171" s="8"/>
+      <c r="G171" s="9">
+        <v>0</v>
+      </c>
+      <c r="H171" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I171" s="8" t="s">
         <v>1897</v>
       </c>
-      <c r="K170" s="5" t="str">
+      <c r="K171" s="5" t="str">
         <f t="shared" si="19"/>
         <v>INSERT INTO m_code VALUES ('batch_status',6,'TIMEOUT','','',0,0.0,'時間内に処理が終了しなかった。');</v>
       </c>
@@ -33128,7 +33162,7 @@
         <v>150</v>
       </c>
       <c r="L6" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;H6&amp;","&amp;VLOOKUP(I6,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;H6&amp;","&amp;VLOOKUP(I6,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster001','キラービー',1,110,12,16,0.3,1);</v>
       </c>
     </row>
@@ -33161,7 +33195,7 @@
         <v>150</v>
       </c>
       <c r="L7" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;H7&amp;","&amp;VLOOKUP(I7,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;H7&amp;","&amp;VLOOKUP(I7,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster002','アサシンバグ',1,132,15,20,0.3,1);</v>
       </c>
     </row>
@@ -33194,7 +33228,7 @@
         <v>150</v>
       </c>
       <c r="L8" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;H8&amp;","&amp;VLOOKUP(I8,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;H8&amp;","&amp;VLOOKUP(I8,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster003','ラスターバグ',1,158,19,26,0.3,1);</v>
       </c>
     </row>
@@ -33224,7 +33258,7 @@
         <v>34</v>
       </c>
       <c r="L9" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;H9&amp;","&amp;VLOOKUP(I9,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;H9&amp;","&amp;VLOOKUP(I9,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster004','カーミラ',2,100,10,13,0.13,2);</v>
       </c>
     </row>
@@ -33257,7 +33291,7 @@
         <v>34</v>
       </c>
       <c r="L10" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;H10&amp;","&amp;VLOOKUP(I10,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;H10&amp;","&amp;VLOOKUP(I10,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster005','カーミラクイーン',2,120,13,16,0.15,2);</v>
       </c>
     </row>
@@ -33287,7 +33321,7 @@
         <v>36</v>
       </c>
       <c r="L11" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;H11&amp;","&amp;VLOOKUP(I11,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;H11&amp;","&amp;VLOOKUP(I11,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster006','デーモン',3,130,15,7,0.08,5);</v>
       </c>
     </row>
@@ -33320,7 +33354,7 @@
         <v>36</v>
       </c>
       <c r="L12" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;H12&amp;","&amp;VLOOKUP(I12,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;H12&amp;","&amp;VLOOKUP(I12,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster007','グレートデーモン',3,156,19,9,0.1,5);</v>
       </c>
     </row>
@@ -33350,7 +33384,7 @@
         <v>35</v>
       </c>
       <c r="L13" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;H13&amp;","&amp;VLOOKUP(I13,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;H13&amp;","&amp;VLOOKUP(I13,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster008','ゴブリン',4,120,11,10,0.15,4);</v>
       </c>
     </row>
@@ -33383,7 +33417,7 @@
         <v>35</v>
       </c>
       <c r="L14" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;H14&amp;","&amp;VLOOKUP(I14,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;H14&amp;","&amp;VLOOKUP(I14,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster009','ゴブリンガード',4,144,14,13,0.15,4);</v>
       </c>
     </row>
@@ -33416,7 +33450,7 @@
         <v>35</v>
       </c>
       <c r="L15" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;H15&amp;","&amp;VLOOKUP(I15,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;H15&amp;","&amp;VLOOKUP(I15,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster010','ゴブリンロード',4,172,18,16,0.15,4);</v>
       </c>
     </row>
@@ -33446,7 +33480,7 @@
         <v>151</v>
       </c>
       <c r="L16" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;H16&amp;","&amp;VLOOKUP(I16,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;H16&amp;","&amp;VLOOKUP(I16,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster011','マシンゴーレム',5,140,17,5,0.02,3);</v>
       </c>
     </row>
@@ -33479,7 +33513,7 @@
         <v>151</v>
       </c>
       <c r="L17" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;H17&amp;","&amp;VLOOKUP(I17,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;H17&amp;","&amp;VLOOKUP(I17,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster012','ガーディアン',5,168,22,6,0.04,3);</v>
       </c>
     </row>
@@ -33512,7 +33546,7 @@
         <v>151</v>
       </c>
       <c r="L18" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;H18&amp;","&amp;VLOOKUP(I18,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;H18&amp;","&amp;VLOOKUP(I18,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster013','デスマシン',5,201,28,7,0.05,3);</v>
       </c>
     </row>
@@ -33542,7 +33576,7 @@
         <v>35</v>
       </c>
       <c r="L19" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;H19&amp;","&amp;VLOOKUP(I19,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;H19&amp;","&amp;VLOOKUP(I19,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster014','ハーピー',6,100,8,14,0.2,4);</v>
       </c>
     </row>
@@ -33575,7 +33609,7 @@
         <v>35</v>
       </c>
       <c r="L20" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;H20&amp;","&amp;VLOOKUP(I20,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;H20&amp;","&amp;VLOOKUP(I20,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster015','セイレーン',6,120,10,18,0.23,4);</v>
       </c>
     </row>
@@ -33605,7 +33639,7 @@
         <v>34</v>
       </c>
       <c r="L21" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;H21&amp;","&amp;VLOOKUP(I21,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;H21&amp;","&amp;VLOOKUP(I21,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster016','アーマーナイト',7,120,13,8,0.05,2);</v>
       </c>
     </row>
@@ -33638,7 +33672,7 @@
         <v>34</v>
       </c>
       <c r="L22" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;H22&amp;","&amp;VLOOKUP(I22,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;H22&amp;","&amp;VLOOKUP(I22,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster017','ダークナイト',7,144,16,10,0.05,2);</v>
       </c>
     </row>
@@ -33671,7 +33705,7 @@
         <v>34</v>
       </c>
       <c r="L23" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;H23&amp;","&amp;VLOOKUP(I23,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;H23&amp;","&amp;VLOOKUP(I23,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster018','ターミネータ',7,172,20,13,0.07,2);</v>
       </c>
     </row>
@@ -33701,7 +33735,7 @@
         <v>35</v>
       </c>
       <c r="L24" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;H24&amp;","&amp;VLOOKUP(I24,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;H24&amp;","&amp;VLOOKUP(I24,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster019','マジシャン',8,100,9,12,0.1,4);</v>
       </c>
     </row>
@@ -33734,7 +33768,7 @@
         <v>35</v>
       </c>
       <c r="L25" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;H25&amp;","&amp;VLOOKUP(I25,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;H25&amp;","&amp;VLOOKUP(I25,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster020','ウィザード',8,120,11,15,0.11,4);</v>
       </c>
     </row>
@@ -33767,7 +33801,7 @@
         <v>35</v>
       </c>
       <c r="L26" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;H26&amp;","&amp;VLOOKUP(I26,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;H26&amp;","&amp;VLOOKUP(I26,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster021','ハイウィザード',8,144,14,19,0.12,4);</v>
       </c>
     </row>
@@ -33797,7 +33831,7 @@
         <v>150</v>
       </c>
       <c r="L27" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;H27&amp;","&amp;VLOOKUP(I27,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;H27&amp;","&amp;VLOOKUP(I27,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster022','マイコニド',9,120,10,12,0.15,1);</v>
       </c>
     </row>
@@ -33830,7 +33864,7 @@
         <v>150</v>
       </c>
       <c r="L28" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;H28&amp;","&amp;VLOOKUP(I28,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;H28&amp;","&amp;VLOOKUP(I28,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster023','ダースマタンゴ',9,144,13,15,0.15,1);</v>
       </c>
     </row>
@@ -33860,7 +33894,7 @@
         <v>151</v>
       </c>
       <c r="L29" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;H29&amp;","&amp;VLOOKUP(I29,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;H29&amp;","&amp;VLOOKUP(I29,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster024','ニードルバード',10,100,13,16,0.25,3);</v>
       </c>
     </row>
@@ -33893,7 +33927,7 @@
         <v>151</v>
       </c>
       <c r="L30" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;H30&amp;","&amp;VLOOKUP(I30,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;H30&amp;","&amp;VLOOKUP(I30,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster025','コカトバード',10,120,16,20,0.27,3);</v>
       </c>
     </row>
@@ -33923,7 +33957,7 @@
         <v>151</v>
       </c>
       <c r="L31" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;H31&amp;","&amp;VLOOKUP(I31,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;H31&amp;","&amp;VLOOKUP(I31,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster026','プチドラゴン',11,130,13,8,0.08,3);</v>
       </c>
     </row>
@@ -33956,7 +33990,7 @@
         <v>36</v>
       </c>
       <c r="L32" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;H32&amp;","&amp;VLOOKUP(I32,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;H32&amp;","&amp;VLOOKUP(I32,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster027','プチドラゾンビ',11,156,16,10,0.1,5);</v>
       </c>
     </row>
@@ -33989,7 +34023,7 @@
         <v>150</v>
       </c>
       <c r="L33" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;H33&amp;","&amp;VLOOKUP(I33,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;H33&amp;","&amp;VLOOKUP(I33,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster028','フロストドラゴン',11,187,20,13,0.12,1);</v>
       </c>
     </row>
@@ -34022,7 +34056,7 @@
         <v>37</v>
       </c>
       <c r="L34" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;H34&amp;","&amp;VLOOKUP(I34,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;H34&amp;","&amp;VLOOKUP(I34,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster029','プチティアマット',11,224,26,16,0.13,6);</v>
       </c>
     </row>
@@ -34052,7 +34086,7 @@
         <v>37</v>
       </c>
       <c r="L35" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;H35&amp;","&amp;VLOOKUP(I35,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;H35&amp;","&amp;VLOOKUP(I35,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster030','ポト',12,100,10,16,0.18,6);</v>
       </c>
     </row>
@@ -34085,7 +34119,7 @@
         <v>37</v>
       </c>
       <c r="L36" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;H36&amp;","&amp;VLOOKUP(I36,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;H36&amp;","&amp;VLOOKUP(I36,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster031','マーマポト',12,120,13,20,0.2,6);</v>
       </c>
     </row>
@@ -34118,7 +34152,7 @@
         <v>37</v>
       </c>
       <c r="L37" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;H37&amp;","&amp;VLOOKUP(I37,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;H37&amp;","&amp;VLOOKUP(I37,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster032','パーパポト',12,141,16,26,0.22,6);</v>
       </c>
     </row>
@@ -34148,7 +34182,7 @@
         <v>37</v>
       </c>
       <c r="L38" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;H38&amp;","&amp;VLOOKUP(I38,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;H38&amp;","&amp;VLOOKUP(I38,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster033','プリースト',13,100,9,13,0.1,6);</v>
       </c>
     </row>
@@ -34181,7 +34215,7 @@
         <v>36</v>
       </c>
       <c r="L39" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;H39&amp;","&amp;VLOOKUP(I39,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;H39&amp;","&amp;VLOOKUP(I39,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster034','カオスソーサラー',13,120,11,16,0.11,5);</v>
       </c>
     </row>
@@ -34214,7 +34248,7 @@
         <v>36</v>
       </c>
       <c r="L40" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;H40&amp;","&amp;VLOOKUP(I40,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;H40&amp;","&amp;VLOOKUP(I40,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster035','イビルシャーマン',13,144,14,20,0.13,5);</v>
       </c>
     </row>
@@ -34245,7 +34279,7 @@
         <v>37</v>
       </c>
       <c r="L41" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;H41&amp;","&amp;VLOOKUP(I41,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;H41&amp;","&amp;VLOOKUP(I41,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster036','ラビ',14,100,11,16,0.16,6);</v>
       </c>
     </row>
@@ -34278,7 +34312,7 @@
         <v>37</v>
       </c>
       <c r="L42" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;H42&amp;","&amp;VLOOKUP(I42,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;H42&amp;","&amp;VLOOKUP(I42,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster037','ラビリオン',14,120,14,20,0.17,6);</v>
       </c>
     </row>
@@ -34311,7 +34345,7 @@
         <v>37</v>
       </c>
       <c r="L43" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;H43&amp;","&amp;VLOOKUP(I43,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;H43&amp;","&amp;VLOOKUP(I43,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster038','キングラビ',14,144,18,26,0.18,6);</v>
       </c>
     </row>
@@ -34344,7 +34378,7 @@
         <v>37</v>
       </c>
       <c r="L44" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;H44&amp;","&amp;VLOOKUP(I44,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;H44&amp;","&amp;VLOOKUP(I44,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster039','グレートラビ',14,172,23,33,0.2,6);</v>
       </c>
     </row>
@@ -34374,7 +34408,7 @@
         <v>34</v>
       </c>
       <c r="L45" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;H45&amp;","&amp;VLOOKUP(I45,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;H45&amp;","&amp;VLOOKUP(I45,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster040','スライム',15,100,10,18,0.15,2);</v>
       </c>
     </row>
@@ -34407,7 +34441,7 @@
         <v>150</v>
       </c>
       <c r="L46" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;H46&amp;","&amp;VLOOKUP(I46,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;H46&amp;","&amp;VLOOKUP(I46,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster041','ブルーババロア',15,120,13,23,0.15,1);</v>
       </c>
     </row>
@@ -34440,7 +34474,7 @@
         <v>151</v>
       </c>
       <c r="L47" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;H47&amp;","&amp;VLOOKUP(I47,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;H47&amp;","&amp;VLOOKUP(I47,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster042','レッドマシュマロ',15,141,16,29,0.15,3);</v>
       </c>
     </row>
@@ -34470,7 +34504,7 @@
         <v>36</v>
       </c>
       <c r="L48" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;H48&amp;","&amp;VLOOKUP(I48,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;H48&amp;","&amp;VLOOKUP(I48,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster043','イビルソード',16,110,15,13,0.14,5);</v>
       </c>
     </row>
@@ -34503,7 +34537,7 @@
         <v>36</v>
       </c>
       <c r="L49" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;H49&amp;","&amp;VLOOKUP(I49,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;H49&amp;","&amp;VLOOKUP(I49,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster044','イビルウェポン',16,132,19,16,0.15,5);</v>
       </c>
     </row>
@@ -34536,7 +34570,7 @@
         <v>37</v>
       </c>
       <c r="L50" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;H50&amp;","&amp;VLOOKUP(I50,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;H50&amp;","&amp;VLOOKUP(I50,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster045','エレメントソード',16,158,24,20,0.16,6);</v>
       </c>
     </row>
@@ -34566,7 +34600,7 @@
         <v>150</v>
       </c>
       <c r="L51" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;H51&amp;","&amp;VLOOKUP(I51,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;H51&amp;","&amp;VLOOKUP(I51,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster046','ケルベロス',17,110,11,19,0.18,1);</v>
       </c>
     </row>
@@ -34599,7 +34633,7 @@
         <v>150</v>
       </c>
       <c r="L52" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;H52&amp;","&amp;VLOOKUP(I52,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;H52&amp;","&amp;VLOOKUP(I52,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster047','バウンドウルフ',17,132,14,24,0.2,1);</v>
       </c>
     </row>
@@ -34632,7 +34666,7 @@
         <v>150</v>
       </c>
       <c r="L53" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;H53&amp;","&amp;VLOOKUP(I53,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;H53&amp;","&amp;VLOOKUP(I53,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster048','ジャッカル',17,158,18,31,0.21,1);</v>
       </c>
     </row>
@@ -34662,7 +34696,7 @@
         <v>151</v>
       </c>
       <c r="L54" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;H54&amp;","&amp;VLOOKUP(I54,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;H54&amp;","&amp;VLOOKUP(I54,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster049','ダックソルジャー',18,120,16,14,0.15,3);</v>
       </c>
     </row>
@@ -34692,7 +34726,7 @@
         <v>151</v>
       </c>
       <c r="L55" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;H55&amp;","&amp;VLOOKUP(I55,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;H55&amp;","&amp;VLOOKUP(I55,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster050','ダックジェネラル',18,160,24,20,0.15,3);</v>
       </c>
     </row>
@@ -34722,7 +34756,7 @@
         <v>34</v>
       </c>
       <c r="L56" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;H56&amp;","&amp;VLOOKUP(I56,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;H56&amp;","&amp;VLOOKUP(I56,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster051','モールベア',19,130,14,18,0.18,2);</v>
       </c>
     </row>
@@ -34752,7 +34786,7 @@
         <v>34</v>
       </c>
       <c r="L57" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;H57&amp;","&amp;VLOOKUP(I57,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;H57&amp;","&amp;VLOOKUP(I57,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster052','ニードリオン',19,170,18,26,0.2,2);</v>
       </c>
     </row>
@@ -34782,7 +34816,7 @@
         <v>35</v>
       </c>
       <c r="L58" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;H58&amp;","&amp;VLOOKUP(I58,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;H58&amp;","&amp;VLOOKUP(I58,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster053','ギャルビー',20,120,13,16,0.2,4);</v>
       </c>
     </row>
@@ -34815,7 +34849,7 @@
         <v>35</v>
       </c>
       <c r="L59" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;H59&amp;","&amp;VLOOKUP(I59,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;H59&amp;","&amp;VLOOKUP(I59,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster054','レディビー',20,144,16,20,0.22,4);</v>
       </c>
     </row>
@@ -34848,7 +34882,7 @@
         <v>35</v>
       </c>
       <c r="L60" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;H60&amp;","&amp;VLOOKUP(I60,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;H60&amp;","&amp;VLOOKUP(I60,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster055','クインビー',20,172,20,26,0.23,4);</v>
       </c>
     </row>
@@ -34878,7 +34912,7 @@
         <v>150</v>
       </c>
       <c r="L61" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;H61&amp;","&amp;VLOOKUP(I61,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;H61&amp;","&amp;VLOOKUP(I61,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster056','サハギン',21,130,16,16,0.15,1);</v>
       </c>
     </row>
@@ -34908,7 +34942,7 @@
         <v>150</v>
       </c>
       <c r="L62" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;H62&amp;","&amp;VLOOKUP(I62,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;H62&amp;","&amp;VLOOKUP(I62,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster057','プチポセイドン',21,150,22,19,0.15,1);</v>
       </c>
     </row>
@@ -34938,7 +34972,7 @@
         <v>298</v>
       </c>
       <c r="L63" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;H63&amp;","&amp;VLOOKUP(I63,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;H63&amp;","&amp;VLOOKUP(I63,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster058','クロウラー',22,130,15,11,0.08,2);</v>
       </c>
     </row>
@@ -34971,7 +35005,7 @@
         <v>34</v>
       </c>
       <c r="L64" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;H64&amp;","&amp;VLOOKUP(I64,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;H64&amp;","&amp;VLOOKUP(I64,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster059','メガクロウラー',22,156,19,14,0.09,2);</v>
       </c>
     </row>
@@ -35004,7 +35038,7 @@
         <v>34</v>
       </c>
       <c r="L65" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;H65&amp;","&amp;VLOOKUP(I65,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;H65&amp;","&amp;VLOOKUP(I65,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster060','ギガクロウラー',22,187,24,18,0.1,2);</v>
       </c>
     </row>
@@ -35034,7 +35068,7 @@
         <v>34</v>
       </c>
       <c r="L66" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;H66&amp;","&amp;VLOOKUP(I66,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;H66&amp;","&amp;VLOOKUP(I66,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster061','ぱっくんオタマ',23,110,12,10,0.15,2);</v>
       </c>
     </row>
@@ -35067,7 +35101,7 @@
         <v>34</v>
       </c>
       <c r="L67" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;H67&amp;","&amp;VLOOKUP(I67,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;H67&amp;","&amp;VLOOKUP(I67,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster062','ぱっくりオタマ',23,132,15,13,0.15,2);</v>
       </c>
     </row>
@@ -35100,7 +35134,7 @@
         <v>151</v>
       </c>
       <c r="L68" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;H68&amp;","&amp;VLOOKUP(I68,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;H68&amp;","&amp;VLOOKUP(I68,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster063','ぱっくんトカゲ',23,158,19,16,0.1,3);</v>
       </c>
     </row>
@@ -35133,7 +35167,7 @@
         <v>151</v>
       </c>
       <c r="L69" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;H69&amp;","&amp;VLOOKUP(I69,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;H69&amp;","&amp;VLOOKUP(I69,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster064','ぱっくんドラゴン',23,189,24,20,0.11,3);</v>
       </c>
     </row>
@@ -35163,7 +35197,7 @@
         <v>36</v>
       </c>
       <c r="L70" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;H70&amp;","&amp;VLOOKUP(I70,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;H70&amp;","&amp;VLOOKUP(I70,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster065','チビデビル',24,120,13,17,0.22,5);</v>
       </c>
     </row>
@@ -35193,7 +35227,7 @@
         <v>36</v>
       </c>
       <c r="L71" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;H71&amp;","&amp;VLOOKUP(I71,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;H71&amp;","&amp;VLOOKUP(I71,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster066','グレムリン',24,160,18,20,0.24,5);</v>
       </c>
     </row>
@@ -35223,7 +35257,7 @@
         <v>36</v>
       </c>
       <c r="L72" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;H72&amp;","&amp;VLOOKUP(I72,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;H72&amp;","&amp;VLOOKUP(I72,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster067','オーガボックス',25,140,18,17,0.15,5);</v>
       </c>
     </row>
@@ -35253,7 +35287,7 @@
         <v>36</v>
       </c>
       <c r="L73" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;H73&amp;","&amp;VLOOKUP(I73,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;H73&amp;","&amp;VLOOKUP(I73,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster068','カイザーミミック',25,170,23,20,0.15,5);</v>
       </c>
     </row>
@@ -35283,7 +35317,7 @@
         <v>151</v>
       </c>
       <c r="L74" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;H74&amp;","&amp;VLOOKUP(I74,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;H74&amp;","&amp;VLOOKUP(I74,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster069','バレッテ',26,140,15,12,0.05,3);</v>
       </c>
     </row>
@@ -35313,7 +35347,7 @@
         <v>151</v>
       </c>
       <c r="L75" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;H75&amp;","&amp;VLOOKUP(I75,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;H75&amp;","&amp;VLOOKUP(I75,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster070','ゴールドバレッテ',26,180,19,14,0.05,3);</v>
       </c>
     </row>
@@ -35343,7 +35377,7 @@
         <v>34</v>
       </c>
       <c r="L76" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;H76&amp;","&amp;VLOOKUP(I76,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;H76&amp;","&amp;VLOOKUP(I76,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster071','バシリスク',27,110,12,15,0.15,2);</v>
       </c>
     </row>
@@ -35373,7 +35407,7 @@
         <v>151</v>
       </c>
       <c r="L77" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;H77&amp;","&amp;VLOOKUP(I77,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;H77&amp;","&amp;VLOOKUP(I77,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster072','ファイアドレイク',27,150,18,22,0.18,3);</v>
       </c>
     </row>
@@ -35403,7 +35437,7 @@
         <v>36</v>
       </c>
       <c r="L78" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;H78&amp;","&amp;VLOOKUP(I78,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;H78&amp;","&amp;VLOOKUP(I78,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster073','スペクター',28,130,13,17,0.2,5);</v>
       </c>
     </row>
@@ -35433,7 +35467,7 @@
         <v>36</v>
       </c>
       <c r="L79" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;H79&amp;","&amp;VLOOKUP(I79,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;H79&amp;","&amp;VLOOKUP(I79,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster074','ゴースト',28,160,17,20,0.21,5);</v>
       </c>
     </row>
@@ -35463,7 +35497,7 @@
         <v>37</v>
       </c>
       <c r="L80" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;","&amp;VLOOKUP(I80,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;","&amp;VLOOKUP(I80,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster075','ユニコーンヘッド',29,120,15,14,0.15,6);</v>
       </c>
     </row>
@@ -35493,7 +35527,7 @@
         <v>37</v>
       </c>
       <c r="L81" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;H81&amp;","&amp;VLOOKUP(I81,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;H81&amp;","&amp;VLOOKUP(I81,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster076','ゴールドユニコ',29,170,22,25,0.15,6);</v>
       </c>
     </row>
@@ -35523,7 +35557,7 @@
         <v>36</v>
       </c>
       <c r="L82" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;H82&amp;","&amp;VLOOKUP(I82,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;H82&amp;","&amp;VLOOKUP(I82,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster077','シェイプシフター',30,130,12,14,0.14,5);</v>
       </c>
     </row>
@@ -35555,7 +35589,7 @@
         <v>36</v>
       </c>
       <c r="L83" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;H83&amp;","&amp;VLOOKUP(I83,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;H83&amp;","&amp;VLOOKUP(I83,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster078','シャドウゼロ',30,170,15,18,0.15,5);</v>
       </c>
     </row>
@@ -35587,7 +35621,7 @@
         <v>36</v>
       </c>
       <c r="L84" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;H84&amp;","&amp;VLOOKUP(I84,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;H84&amp;","&amp;VLOOKUP(I84,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster079','シャドウゼロワン',30,190,19,23,0.16,5);</v>
       </c>
     </row>
@@ -35617,7 +35651,7 @@
         <v>36</v>
       </c>
       <c r="L85" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;H85&amp;","&amp;VLOOKUP(I85,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;H85&amp;","&amp;VLOOKUP(I85,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster080','ボルダー',31,120,13,14,0.25,5);</v>
       </c>
     </row>
@@ -35650,7 +35684,7 @@
         <v>36</v>
       </c>
       <c r="L86" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;H86&amp;","&amp;VLOOKUP(I86,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;H86&amp;","&amp;VLOOKUP(I86,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster081','パワーボルダー',31,144,16,18,0.25,5);</v>
       </c>
     </row>
@@ -35683,7 +35717,7 @@
         <v>36</v>
       </c>
       <c r="L87" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;H87&amp;","&amp;VLOOKUP(I87,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;H87&amp;","&amp;VLOOKUP(I87,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster082','デスボルダー',31,172,20,23,0.25,5);</v>
       </c>
     </row>
@@ -35713,7 +35747,7 @@
         <v>151</v>
       </c>
       <c r="L88" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;H88&amp;","&amp;VLOOKUP(I88,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;H88&amp;","&amp;VLOOKUP(I88,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster083','パンプキンボム',32,130,17,12,0.18,3);</v>
       </c>
     </row>
@@ -35743,7 +35777,7 @@
         <v>151</v>
       </c>
       <c r="L89" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$48:$I$110,3,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;H89&amp;","&amp;VLOOKUP(I89,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;H89&amp;","&amp;VLOOKUP(I89,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster084','グレネードボム',32,160,24,15,0.2,3);</v>
       </c>
     </row>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF1C6517-DF0B-40AD-8980-161C8A86A038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5326624E-C915-4BF6-B08E-FC6E9D0C42A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="3" activeTab="3" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4836" uniqueCount="2447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4840" uniqueCount="2449">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -10198,6 +10198,14 @@
   </si>
   <si>
     <t>https://www.kieselguitars.com/</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FUJIGEN</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://fujigen.shop/</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -25125,7 +25133,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
-  <dimension ref="B4:K171"/>
+  <dimension ref="B4:K172"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -27738,7 +27746,7 @@
         <v>1551</v>
       </c>
       <c r="K102" s="5" t="str">
-        <f t="shared" ref="K102:K109" si="14">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B102&amp;"'"&amp;","&amp;E102&amp;","&amp;"'"&amp;C102&amp;"'"&amp;","&amp;"'"&amp;D102&amp;"'"&amp;","&amp;"'"&amp;F102&amp;"'"&amp;","&amp;G102&amp;","&amp;H102&amp;","&amp;"'"&amp;I102&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K102:K110" si="14">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B102&amp;"'"&amp;","&amp;E102&amp;","&amp;"'"&amp;C102&amp;"'"&amp;","&amp;"'"&amp;D102&amp;"'"&amp;","&amp;"'"&amp;F102&amp;"'"&amp;","&amp;G102&amp;","&amp;H102&amp;","&amp;"'"&amp;I102&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('guitar_makers',10,'MusicMan','','',0,0.0,'https://www.music-man.com/instruments/guitars');</v>
       </c>
     </row>
@@ -27790,7 +27798,7 @@
         <v>1553</v>
       </c>
       <c r="K104" s="5" t="str">
-        <f t="shared" ref="K104:K108" si="15">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B104&amp;"'"&amp;","&amp;E104&amp;","&amp;"'"&amp;C104&amp;"'"&amp;","&amp;"'"&amp;D104&amp;"'"&amp;","&amp;"'"&amp;F104&amp;"'"&amp;","&amp;G104&amp;","&amp;H104&amp;","&amp;"'"&amp;I104&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K104:K109" si="15">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B104&amp;"'"&amp;","&amp;E104&amp;","&amp;"'"&amp;C104&amp;"'"&amp;","&amp;"'"&amp;D104&amp;"'"&amp;","&amp;"'"&amp;F104&amp;"'"&amp;","&amp;G104&amp;","&amp;H104&amp;","&amp;"'"&amp;I104&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('guitar_makers',12,'Momose','','',0,0.0,'https://www.deviser.co.jp/momose');</v>
       </c>
     </row>
@@ -27920,62 +27928,60 @@
         <v>2446</v>
       </c>
       <c r="K109" s="5" t="str">
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('guitar_makers',17,'KIESEL','','',0,0.0,'https://www.kieselguitars.com/');</v>
+      </c>
+    </row>
+    <row r="110" spans="2:11">
+      <c r="B110" s="8" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>2447</v>
+      </c>
+      <c r="D110" s="8"/>
+      <c r="E110" s="8">
+        <v>18</v>
+      </c>
+      <c r="F110" s="8"/>
+      <c r="G110" s="9">
+        <v>0</v>
+      </c>
+      <c r="H110" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I110" s="8" t="s">
+        <v>2448</v>
+      </c>
+      <c r="K110" s="5" t="str">
         <f t="shared" si="14"/>
-        <v>INSERT INTO m_code VALUES ('guitar_makers',17,'KIESEL','','',0,0.0,'https://www.kieselguitars.com/');</v>
-      </c>
-    </row>
-    <row r="110" spans="2:11">
-      <c r="B110" s="6" t="s">
+        <v>INSERT INTO m_code VALUES ('guitar_makers',18,'FUJIGEN','','',0,0.0,'https://fujigen.shop/');</v>
+      </c>
+    </row>
+    <row r="111" spans="2:11">
+      <c r="B111" s="6" t="s">
         <v>1542</v>
       </c>
-      <c r="C110" s="6" t="s">
+      <c r="C111" s="6" t="s">
         <v>1388</v>
       </c>
-      <c r="D110" s="6" t="s">
+      <c r="D111" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E110" s="7" t="s">
+      <c r="E111" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F110" s="6" t="s">
+      <c r="F111" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G110" s="6" t="s">
+      <c r="G111" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H110" s="6" t="s">
+      <c r="H111" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I110" s="6" t="s">
+      <c r="I111" s="6" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="111" spans="2:11">
-      <c r="B111" s="8" t="s">
-        <v>1778</v>
-      </c>
-      <c r="C111" s="8" t="s">
-        <v>1425</v>
-      </c>
-      <c r="D111" s="8"/>
-      <c r="E111" s="8">
-        <v>1</v>
-      </c>
-      <c r="F111" s="8" t="s">
-        <v>1439</v>
-      </c>
-      <c r="G111" s="9">
-        <v>0</v>
-      </c>
-      <c r="H111" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I111" s="8" t="s">
-        <v>1463</v>
-      </c>
-      <c r="K111" s="5" t="str">
-        <f t="shared" ref="K111:K146" si="16">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B111&amp;"'"&amp;","&amp;E111&amp;","&amp;"'"&amp;C111&amp;"'"&amp;","&amp;"'"&amp;D111&amp;"'"&amp;","&amp;"'"&amp;F111&amp;"'"&amp;","&amp;G111&amp;","&amp;H111&amp;","&amp;"'"&amp;I111&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',1,'HardMaple','','ハードメイプル',0,0.0,'硬質でタイト、明瞭なアタック。');</v>
       </c>
     </row>
     <row r="112" spans="2:11">
@@ -27983,14 +27989,14 @@
         <v>1778</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="D112" s="8"/>
       <c r="E112" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G112" s="9">
         <v>0</v>
@@ -27999,11 +28005,11 @@
         <v>125</v>
       </c>
       <c r="I112" s="8" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="K112" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',2,'FlameMaple','','フレイムメイプル',0,0.0,'明るく抜けが良く、華やかな倍音。');</v>
+        <f t="shared" ref="K112:K147" si="16">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B112&amp;"'"&amp;","&amp;E112&amp;","&amp;"'"&amp;C112&amp;"'"&amp;","&amp;"'"&amp;D112&amp;"'"&amp;","&amp;"'"&amp;F112&amp;"'"&amp;","&amp;G112&amp;","&amp;H112&amp;","&amp;"'"&amp;I112&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',1,'HardMaple','','ハードメイプル',0,0.0,'硬質でタイト、明瞭なアタック。');</v>
       </c>
     </row>
     <row r="113" spans="2:11">
@@ -28011,14 +28017,14 @@
         <v>1778</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="G113" s="9">
         <v>0</v>
@@ -28027,11 +28033,11 @@
         <v>125</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="K113" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',3,'QuiltedMaple','','キルテッドメイプル',0,0.0,'立体的で広がりがあり、煌びやかな響き。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',2,'FlameMaple','','フレイムメイプル',0,0.0,'明るく抜けが良く、華やかな倍音。');</v>
       </c>
     </row>
     <row r="114" spans="2:11">
@@ -28039,14 +28045,14 @@
         <v>1778</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="D114" s="8"/>
       <c r="E114" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="G114" s="9">
         <v>0</v>
@@ -28055,11 +28061,11 @@
         <v>125</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="K114" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',4,'BirdseyeMaple','','バーズアイメイプル',0,0.0,'粒立ちが良く、明るくシャープ。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',3,'QuiltedMaple','','キルテッドメイプル',0,0.0,'立体的で広がりがあり、煌びやかな響き。');</v>
       </c>
     </row>
     <row r="115" spans="2:11">
@@ -28067,14 +28073,14 @@
         <v>1778</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="D115" s="8"/>
       <c r="E115" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="G115" s="9">
         <v>0</v>
@@ -28083,11 +28089,11 @@
         <v>125</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="K115" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',5,'RoastedMaple','','ローステッドメイプル',0,0.0,'引き締まったタイトな音で反応が速い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',4,'BirdseyeMaple','','バーズアイメイプル',0,0.0,'粒立ちが良く、明るくシャープ。');</v>
       </c>
     </row>
     <row r="116" spans="2:11">
@@ -28095,14 +28101,14 @@
         <v>1778</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>1389</v>
+        <v>1429</v>
       </c>
       <c r="D116" s="8"/>
       <c r="E116" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>1438</v>
+        <v>1443</v>
       </c>
       <c r="G116" s="9">
         <v>0</v>
@@ -28111,11 +28117,11 @@
         <v>125</v>
       </c>
       <c r="I116" s="8" t="s">
-        <v>1462</v>
+        <v>1467</v>
       </c>
       <c r="K116" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',6,'Maple','','メイプル',0,0.0,'明るくハリがあり、アタックが強い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',5,'RoastedMaple','','ローステッドメイプル',0,0.0,'引き締まったタイトな音で反応が速い。');</v>
       </c>
     </row>
     <row r="117" spans="2:11">
@@ -28123,14 +28129,14 @@
         <v>1778</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>1430</v>
+        <v>1389</v>
       </c>
       <c r="D117" s="8"/>
       <c r="E117" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>1444</v>
+        <v>1438</v>
       </c>
       <c r="G117" s="9">
         <v>0</v>
@@ -28139,11 +28145,11 @@
         <v>125</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>1469</v>
+        <v>1462</v>
       </c>
       <c r="K117" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',7,'HonduranMahogany','','ホンジュラスマホガニー',0,0.0,'深みがあり、太くリッチな中低域。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',6,'Maple','','メイプル',0,0.0,'明るくハリがあり、アタックが強い。');</v>
       </c>
     </row>
     <row r="118" spans="2:11">
@@ -28151,14 +28157,14 @@
         <v>1778</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>1390</v>
+        <v>1430</v>
       </c>
       <c r="D118" s="8"/>
       <c r="E118" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>1408</v>
+        <v>1444</v>
       </c>
       <c r="G118" s="9">
         <v>0</v>
@@ -28167,11 +28173,11 @@
         <v>125</v>
       </c>
       <c r="I118" s="8" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="K118" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',8,'Mahogany','','マホガニー',0,0.0,'中低域が豊かで温かい音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',7,'HonduranMahogany','','ホンジュラスマホガニー',0,0.0,'深みがあり、太くリッチな中低域。');</v>
       </c>
     </row>
     <row r="119" spans="2:11">
@@ -28179,14 +28185,14 @@
         <v>1778</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>1431</v>
+        <v>1390</v>
       </c>
       <c r="D119" s="8"/>
       <c r="E119" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>1445</v>
+        <v>1408</v>
       </c>
       <c r="G119" s="9">
         <v>0</v>
@@ -28195,11 +28201,11 @@
         <v>125</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="K119" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',9,'Sapele','','サペリ',0,0.0,'温かく柔らかいトーンでバランスが良い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',8,'Mahogany','','マホガニー',0,0.0,'中低域が豊かで温かい音。');</v>
       </c>
     </row>
     <row r="120" spans="2:11">
@@ -28207,14 +28213,14 @@
         <v>1778</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>1397</v>
+        <v>1431</v>
       </c>
       <c r="D120" s="8"/>
       <c r="E120" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="G120" s="9">
         <v>0</v>
@@ -28223,11 +28229,11 @@
         <v>125</v>
       </c>
       <c r="I120" s="8" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="K120" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',10,'Korina','','コリーナ',0,0.0,'中域が豊かで太い音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',9,'Sapele','','サペリ',0,0.0,'温かく柔らかいトーンでバランスが良い。');</v>
       </c>
     </row>
     <row r="121" spans="2:11">
@@ -28235,14 +28241,14 @@
         <v>1778</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>1432</v>
+        <v>1397</v>
       </c>
       <c r="D121" s="8"/>
       <c r="E121" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="G121" s="9">
         <v>0</v>
@@ -28251,11 +28257,11 @@
         <v>125</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="K121" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',11,'WhiteKorina','','ホワイトコリーナ',0,0.0,'明るく抜けが良く、軽快なレスポンス。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',10,'Korina','','コリーナ',0,0.0,'中域が豊かで太い音。');</v>
       </c>
     </row>
     <row r="122" spans="2:11">
@@ -28263,14 +28269,14 @@
         <v>1778</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>1391</v>
+        <v>1432</v>
       </c>
       <c r="D122" s="8"/>
       <c r="E122" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>1409</v>
+        <v>1447</v>
       </c>
       <c r="G122" s="9">
         <v>0</v>
@@ -28279,11 +28285,11 @@
         <v>125</v>
       </c>
       <c r="I122" s="8" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="K122" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',12,'Alder','','アルダー',0,0.0,'バランスが良くクセが少ない。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',11,'WhiteKorina','','ホワイトコリーナ',0,0.0,'明るく抜けが良く、軽快なレスポンス。');</v>
       </c>
     </row>
     <row r="123" spans="2:11">
@@ -28291,14 +28297,14 @@
         <v>1778</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="D123" s="8"/>
       <c r="E123" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>1448</v>
+        <v>1409</v>
       </c>
       <c r="G123" s="9">
         <v>0</v>
@@ -28307,11 +28313,11 @@
         <v>125</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="K123" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',13,'Ash','','アッシュ',0,0.0,'明るく抜ける音でアタックが強い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',12,'Alder','','アルダー',0,0.0,'バランスが良くクセが少ない。');</v>
       </c>
     </row>
     <row r="124" spans="2:11">
@@ -28319,14 +28325,14 @@
         <v>1778</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="D124" s="8"/>
       <c r="E124" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F124" s="8" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="G124" s="9">
         <v>0</v>
@@ -28335,11 +28341,11 @@
         <v>125</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="K124" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',14,'Basswood','','バスウッド',0,0.0,'軽く柔らかく、ウォームで扱いやすい。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',13,'Ash','','アッシュ',0,0.0,'明るく抜ける音でアタックが強い。');</v>
       </c>
     </row>
     <row r="125" spans="2:11">
@@ -28347,14 +28353,14 @@
         <v>1778</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>1402</v>
+        <v>1393</v>
       </c>
       <c r="D125" s="8"/>
       <c r="E125" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="G125" s="9">
         <v>0</v>
@@ -28363,11 +28369,11 @@
         <v>125</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="K125" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',15,'Poplar','','ポプラ',0,0.0,'軽く素直でクセが少ない。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',14,'Basswood','','バスウッド',0,0.0,'軽く柔らかく、ウォームで扱いやすい。');</v>
       </c>
     </row>
     <row r="126" spans="2:11">
@@ -28375,14 +28381,14 @@
         <v>1778</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="D126" s="8"/>
       <c r="E126" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="G126" s="9">
         <v>0</v>
@@ -28391,11 +28397,11 @@
         <v>125</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="K126" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',16,'Spruce','','スプルース',0,0.0,'軽く響きが良く、明るいトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',15,'Poplar','','ポプラ',0,0.0,'軽く素直でクセが少ない。');</v>
       </c>
     </row>
     <row r="127" spans="2:11">
@@ -28403,14 +28409,14 @@
         <v>1778</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="D127" s="8"/>
       <c r="E127" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="G127" s="9">
         <v>0</v>
@@ -28419,11 +28425,11 @@
         <v>125</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="K127" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',17,'Cedar','','シダー',0,0.0,'柔らかく温かい音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',16,'Spruce','','スプルース',0,0.0,'軽く響きが良く、明るいトーン。');</v>
       </c>
     </row>
     <row r="128" spans="2:11">
@@ -28431,14 +28437,14 @@
         <v>1778</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>1433</v>
+        <v>1399</v>
       </c>
       <c r="D128" s="8"/>
       <c r="E128" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="G128" s="9">
         <v>0</v>
@@ -28447,11 +28453,11 @@
         <v>125</v>
       </c>
       <c r="I128" s="8" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="K128" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',18,'IndianRosewood','','インディアンローズウッド',0,0.0,'甘く深みがあり、豊かな中低域。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',17,'Cedar','','シダー',0,0.0,'柔らかく温かい音。');</v>
       </c>
     </row>
     <row r="129" spans="2:11">
@@ -28459,14 +28465,14 @@
         <v>1778</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="D129" s="8"/>
       <c r="E129" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="G129" s="9">
         <v>0</v>
@@ -28475,11 +28481,11 @@
         <v>125</v>
       </c>
       <c r="I129" s="8" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="K129" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',19,'BrazilianRosewood','','ブラジリアンローズウッド',0,0.0,'濃厚で深いトーン、豊かな倍音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',18,'IndianRosewood','','インディアンローズウッド',0,0.0,'甘く深みがあり、豊かな中低域。');</v>
       </c>
     </row>
     <row r="130" spans="2:11">
@@ -28487,14 +28493,14 @@
         <v>1778</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>1394</v>
+        <v>1434</v>
       </c>
       <c r="D130" s="8"/>
       <c r="E130" s="8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="G130" s="9">
         <v>0</v>
@@ -28503,11 +28509,11 @@
         <v>125</v>
       </c>
       <c r="I130" s="8" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="K130" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',20,'Rosewood','','ローズウッド',0,0.0,'甘く丸い音で中域が豊か。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',19,'BrazilianRosewood','','ブラジリアンローズウッド',0,0.0,'濃厚で深いトーン、豊かな倍音。');</v>
       </c>
     </row>
     <row r="131" spans="2:11">
@@ -28515,14 +28521,14 @@
         <v>1778</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>1435</v>
+        <v>1394</v>
       </c>
       <c r="D131" s="8"/>
       <c r="E131" s="8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>1410</v>
+        <v>1453</v>
       </c>
       <c r="G131" s="9">
         <v>0</v>
@@ -28531,11 +28537,11 @@
         <v>125</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="K131" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',21,'PauFerro','','パーフェロー',0,0.0,'明るく硬質でタイトな音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',20,'Rosewood','','ローズウッド',0,0.0,'甘く丸い音で中域が豊か。');</v>
       </c>
     </row>
     <row r="132" spans="2:11">
@@ -28543,14 +28549,14 @@
         <v>1778</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>1400</v>
+        <v>1435</v>
       </c>
       <c r="D132" s="8"/>
       <c r="E132" s="8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="G132" s="9">
         <v>0</v>
@@ -28559,11 +28565,11 @@
         <v>125</v>
       </c>
       <c r="I132" s="8" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="K132" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',22,'Ovangkol','','オバンコール',0,0.0,'中域が豊かで温かいトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',21,'PauFerro','','パーフェロー',0,0.0,'明るく硬質でタイトな音。');</v>
       </c>
     </row>
     <row r="133" spans="2:11">
@@ -28571,14 +28577,14 @@
         <v>1778</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>1395</v>
+        <v>1400</v>
       </c>
       <c r="D133" s="8"/>
       <c r="E133" s="8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F133" s="8" t="s">
-        <v>1456</v>
+        <v>1411</v>
       </c>
       <c r="G133" s="9">
         <v>0</v>
@@ -28587,11 +28593,11 @@
         <v>125</v>
       </c>
       <c r="I133" s="8" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="K133" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',23,'Ebony','','エボニー',0,0.0,'硬くタイトで高域がクリア。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',22,'Ovangkol','','オバンコール',0,0.0,'中域が豊かで温かいトーン。');</v>
       </c>
     </row>
     <row r="134" spans="2:11">
@@ -28599,14 +28605,14 @@
         <v>1778</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="D134" s="8"/>
       <c r="E134" s="8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F134" s="8" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="G134" s="9">
         <v>0</v>
@@ -28615,11 +28621,11 @@
         <v>125</v>
       </c>
       <c r="I134" s="8" t="s">
-        <v>1416</v>
+        <v>1484</v>
       </c>
       <c r="K134" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',24,'Walnut','','ウォルナット',0,0.0,'中域が豊かで落ち着いたトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',23,'Ebony','','エボニー',0,0.0,'硬くタイトで高域がクリア。');</v>
       </c>
     </row>
     <row r="135" spans="2:11">
@@ -28627,14 +28633,14 @@
         <v>1778</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>1436</v>
+        <v>1396</v>
       </c>
       <c r="D135" s="8"/>
       <c r="E135" s="8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F135" s="8" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="G135" s="9">
         <v>0</v>
@@ -28643,11 +28649,11 @@
         <v>125</v>
       </c>
       <c r="I135" s="8" t="s">
-        <v>1485</v>
+        <v>1416</v>
       </c>
       <c r="K135" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',25,'Padauk','','パドゥーク',0,0.0,'明るく抜けが良く、個性的な響き。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',24,'Walnut','','ウォルナット',0,0.0,'中域が豊かで落ち着いたトーン。');</v>
       </c>
     </row>
     <row r="136" spans="2:11">
@@ -28655,14 +28661,14 @@
         <v>1778</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>1401</v>
+        <v>1436</v>
       </c>
       <c r="D136" s="8"/>
       <c r="E136" s="8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F136" s="8" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="G136" s="9">
         <v>0</v>
@@ -28671,11 +28677,11 @@
         <v>125</v>
       </c>
       <c r="I136" s="8" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="K136" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',26,'Koa','','コア',0,0.0,'明るく華やかで軽快。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',25,'Padauk','','パドゥーク',0,0.0,'明るく抜けが良く、個性的な響き。');</v>
       </c>
     </row>
     <row r="137" spans="2:11">
@@ -28683,14 +28689,14 @@
         <v>1778</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="D137" s="8"/>
       <c r="E137" s="8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F137" s="8" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="G137" s="9">
         <v>0</v>
@@ -28699,11 +28705,11 @@
         <v>125</v>
       </c>
       <c r="I137" s="8" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="K137" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',27,'Nato','','ナトー',0,0.0,'中低域が豊かで温かい。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',26,'Koa','','コア',0,0.0,'明るく華やかで軽快。');</v>
       </c>
     </row>
     <row r="138" spans="2:11">
@@ -28711,14 +28717,14 @@
         <v>1778</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="D138" s="8"/>
       <c r="E138" s="8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>1412</v>
+        <v>1460</v>
       </c>
       <c r="G138" s="9">
         <v>0</v>
@@ -28727,11 +28733,11 @@
         <v>125</v>
       </c>
       <c r="I138" s="8" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="K138" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',28,'Agathis','','アガチス',0,0.0,'柔らかくウォームで素直。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',27,'Nato','','ナトー',0,0.0,'中低域が豊かで温かい。');</v>
       </c>
     </row>
     <row r="139" spans="2:11">
@@ -28739,14 +28745,14 @@
         <v>1778</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="G139" s="9">
         <v>0</v>
@@ -28755,11 +28761,11 @@
         <v>125</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="K139" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',29,'Bubinga','','ブビンガ',0,0.0,'重く硬質でサスティンが長い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',28,'Agathis','','アガチス',0,0.0,'柔らかくウォームで素直。');</v>
       </c>
     </row>
     <row r="140" spans="2:11">
@@ -28767,14 +28773,14 @@
         <v>1778</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="D140" s="8"/>
       <c r="E140" s="8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F140" s="8" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="G140" s="9">
         <v>0</v>
@@ -28783,11 +28789,11 @@
         <v>125</v>
       </c>
       <c r="I140" s="8" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="K140" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',30,'Wenge','','ウェンジ',0,0.0,'非常に硬くタイトで個性的。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',29,'Bubinga','','ブビンガ',0,0.0,'重く硬質でサスティンが長い。');</v>
       </c>
     </row>
     <row r="141" spans="2:11">
@@ -28795,14 +28801,14 @@
         <v>1778</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D141" s="8"/>
       <c r="E141" s="8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="G141" s="9">
         <v>0</v>
@@ -28811,11 +28817,11 @@
         <v>125</v>
       </c>
       <c r="I141" s="8" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="K141" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',31,'Purpleheart','','パープルハート',0,0.0,'硬く鮮やかでアタックが強い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',30,'Wenge','','ウェンジ',0,0.0,'非常に硬くタイトで個性的。');</v>
       </c>
     </row>
     <row r="142" spans="2:11">
@@ -28823,14 +28829,14 @@
         <v>1778</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>1437</v>
+        <v>1407</v>
       </c>
       <c r="D142" s="8"/>
       <c r="E142" s="8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>1461</v>
+        <v>1415</v>
       </c>
       <c r="G142" s="9">
         <v>0</v>
@@ -28839,11 +28845,11 @@
         <v>125</v>
       </c>
       <c r="I142" s="8" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="K142" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',32,'Zebrawood','','ゼブラウッド',0,0.0,'明るく硬質でクセのあるトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',31,'Purpleheart','','パープルハート',0,0.0,'硬く鮮やかでアタックが強い。');</v>
       </c>
     </row>
     <row r="143" spans="2:11">
@@ -28851,14 +28857,14 @@
         <v>1778</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>1558</v>
+        <v>1437</v>
       </c>
       <c r="D143" s="8"/>
       <c r="E143" s="8">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F143" s="8" t="s">
-        <v>1559</v>
+        <v>1461</v>
       </c>
       <c r="G143" s="9">
         <v>0</v>
@@ -28867,11 +28873,11 @@
         <v>125</v>
       </c>
       <c r="I143" s="8" t="s">
-        <v>1560</v>
+        <v>1492</v>
       </c>
       <c r="K143" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',33,'Okoume','','オクメ',0,0.0,'マホガニーに近く、中低域が豊かで軽量。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',32,'Zebrawood','','ゼブラウッド',0,0.0,'明るく硬質でクセのあるトーン。');</v>
       </c>
     </row>
     <row r="144" spans="2:11">
@@ -28879,14 +28885,14 @@
         <v>1778</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="D144" s="8"/>
       <c r="E144" s="8">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F144" s="8" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="G144" s="9">
         <v>0</v>
@@ -28895,11 +28901,11 @@
         <v>125</v>
       </c>
       <c r="I144" s="8" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="K144" s="5" t="str">
-        <f t="shared" ref="K144" si="17">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B144&amp;"'"&amp;","&amp;E144&amp;","&amp;"'"&amp;C144&amp;"'"&amp;","&amp;"'"&amp;D144&amp;"'"&amp;","&amp;"'"&amp;F144&amp;"'"&amp;","&amp;G144&amp;","&amp;H144&amp;","&amp;"'"&amp;I144&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',34,'Meranti','','メランティ',0,0.0,'中域寄りで温かめ、マホガニー系に近い。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',33,'Okoume','','オクメ',0,0.0,'マホガニーに近く、中低域が豊かで軽量。');</v>
       </c>
     </row>
     <row r="145" spans="2:11">
@@ -28907,14 +28913,14 @@
         <v>1778</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="D145" s="8"/>
       <c r="E145" s="8">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="G145" s="9">
         <v>0</v>
@@ -28923,11 +28929,11 @@
         <v>125</v>
       </c>
       <c r="I145" s="8" t="s">
-        <v>1569</v>
+        <v>1563</v>
       </c>
       <c r="K145" s="5" t="str">
-        <f t="shared" ref="K145" si="18">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B145&amp;"'"&amp;","&amp;E145&amp;","&amp;"'"&amp;C145&amp;"'"&amp;","&amp;"'"&amp;D145&amp;"'"&amp;","&amp;"'"&amp;F145&amp;"'"&amp;","&amp;G145&amp;","&amp;H145&amp;","&amp;"'"&amp;I145&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',35,'Sakura','','サクラ',0,0.0,'中高域が明るく立ち上がりが速い、日本らしい軽快で抜けの良いサウンド。');</v>
+        <f t="shared" ref="K145" si="17">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B145&amp;"'"&amp;","&amp;E145&amp;","&amp;"'"&amp;C145&amp;"'"&amp;","&amp;"'"&amp;D145&amp;"'"&amp;","&amp;"'"&amp;F145&amp;"'"&amp;","&amp;G145&amp;","&amp;H145&amp;","&amp;"'"&amp;I145&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',34,'Meranti','','メランティ',0,0.0,'中域寄りで温かめ、マホガニー系に近い。');</v>
       </c>
     </row>
     <row r="146" spans="2:11">
@@ -28935,14 +28941,14 @@
         <v>1778</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="D146" s="8"/>
       <c r="E146" s="8">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F146" s="8" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="G146" s="9">
         <v>0</v>
@@ -28951,11 +28957,11 @@
         <v>125</v>
       </c>
       <c r="I146" s="8" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="K146" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',36,'Tochi','','トチ',0,0.0,'メイプルに近いクリアさと華やかさを持ちつつ、やや柔らかく豊かな倍音.');</v>
+        <f t="shared" ref="K146" si="18">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B146&amp;"'"&amp;","&amp;E146&amp;","&amp;"'"&amp;C146&amp;"'"&amp;","&amp;"'"&amp;D146&amp;"'"&amp;","&amp;"'"&amp;F146&amp;"'"&amp;","&amp;G146&amp;","&amp;H146&amp;","&amp;"'"&amp;I146&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',35,'Sakura','','サクラ',0,0.0,'中高域が明るく立ち上がりが速い、日本らしい軽快で抜けの良いサウンド。');</v>
       </c>
     </row>
     <row r="147" spans="2:11">
@@ -28963,14 +28969,14 @@
         <v>1778</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>1424</v>
+        <v>1566</v>
       </c>
       <c r="D147" s="8"/>
       <c r="E147" s="8">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="F147" s="8" t="s">
-        <v>1423</v>
+        <v>1567</v>
       </c>
       <c r="G147" s="9">
         <v>0</v>
@@ -28978,62 +28984,64 @@
       <c r="H147" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="I147" s="8"/>
+      <c r="I147" s="8" t="s">
+        <v>1568</v>
+      </c>
       <c r="K147" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B147&amp;"'"&amp;","&amp;E147&amp;","&amp;"'"&amp;C147&amp;"'"&amp;","&amp;"'"&amp;D147&amp;"'"&amp;","&amp;"'"&amp;F147&amp;"'"&amp;","&amp;G147&amp;","&amp;H147&amp;","&amp;"'"&amp;I147&amp;"'"&amp;");"</f>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',36,'Tochi','','トチ',0,0.0,'メイプルに近いクリアさと華やかさを持ちつつ、やや柔らかく豊かな倍音.');</v>
+      </c>
+    </row>
+    <row r="148" spans="2:11">
+      <c r="B148" s="8" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C148" s="8" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D148" s="8"/>
+      <c r="E148" s="8">
+        <v>99</v>
+      </c>
+      <c r="F148" s="8" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G148" s="9">
+        <v>0</v>
+      </c>
+      <c r="H148" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I148" s="8"/>
+      <c r="K148" s="5" t="str">
+        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B148&amp;"'"&amp;","&amp;E148&amp;","&amp;"'"&amp;C148&amp;"'"&amp;","&amp;"'"&amp;D148&amp;"'"&amp;","&amp;"'"&amp;F148&amp;"'"&amp;","&amp;G148&amp;","&amp;H148&amp;","&amp;"'"&amp;I148&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('guitar_woods',99,'Unknown','','？？',0,0.0,'');</v>
       </c>
     </row>
-    <row r="148" spans="2:11">
-      <c r="B148" s="6" t="s">
+    <row r="149" spans="2:11">
+      <c r="B149" s="6" t="s">
         <v>1503</v>
       </c>
-      <c r="C148" s="6" t="s">
+      <c r="C149" s="6" t="s">
         <v>1502</v>
       </c>
-      <c r="D148" s="6" t="s">
+      <c r="D149" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E148" s="7" t="s">
+      <c r="E149" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F148" s="6" t="s">
+      <c r="F149" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G148" s="6" t="s">
+      <c r="G149" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H148" s="6" t="s">
+      <c r="H149" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I148" s="6" t="s">
+      <c r="I149" s="6" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="149" spans="2:11">
-      <c r="B149" s="8" t="s">
-        <v>1779</v>
-      </c>
-      <c r="C149" s="8" t="s">
-        <v>1504</v>
-      </c>
-      <c r="D149" s="8"/>
-      <c r="E149" s="8">
-        <v>1</v>
-      </c>
-      <c r="F149" s="8" t="s">
-        <v>1520</v>
-      </c>
-      <c r="G149" s="9">
-        <v>0</v>
-      </c>
-      <c r="H149" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I149" s="8"/>
-      <c r="K149" s="5" t="str">
-        <f t="shared" ref="K149:K171" si="19">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B149&amp;"'"&amp;","&amp;E149&amp;","&amp;"'"&amp;C149&amp;"'"&amp;","&amp;"'"&amp;D149&amp;"'"&amp;","&amp;"'"&amp;F149&amp;"'"&amp;","&amp;G149&amp;","&amp;H149&amp;","&amp;"'"&amp;I149&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',1,'Red','','レッド',0,0.0,'');</v>
       </c>
     </row>
     <row r="150" spans="2:11">
@@ -29041,14 +29049,14 @@
         <v>1779</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>1518</v>
+        <v>1504</v>
       </c>
       <c r="D150" s="8"/>
       <c r="E150" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="G150" s="9">
         <v>0</v>
@@ -29058,8 +29066,8 @@
       </c>
       <c r="I150" s="8"/>
       <c r="K150" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',2,'Pink','','ピンク',0,0.0,'');</v>
+        <f t="shared" ref="K150:K172" si="19">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B150&amp;"'"&amp;","&amp;E150&amp;","&amp;"'"&amp;C150&amp;"'"&amp;","&amp;"'"&amp;D150&amp;"'"&amp;","&amp;"'"&amp;F150&amp;"'"&amp;","&amp;G150&amp;","&amp;H150&amp;","&amp;"'"&amp;I150&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',1,'Red','','レッド',0,0.0,'');</v>
       </c>
     </row>
     <row r="151" spans="2:11">
@@ -29067,14 +29075,14 @@
         <v>1779</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>1505</v>
+        <v>1518</v>
       </c>
       <c r="D151" s="8"/>
       <c r="E151" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="G151" s="9">
         <v>0</v>
@@ -29085,7 +29093,7 @@
       <c r="I151" s="8"/>
       <c r="K151" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',3,'Orange','','オレンジ',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',2,'Pink','','ピンク',0,0.0,'');</v>
       </c>
     </row>
     <row r="152" spans="2:11">
@@ -29093,14 +29101,14 @@
         <v>1779</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="D152" s="8"/>
       <c r="E152" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F152" s="8" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="G152" s="9">
         <v>0</v>
@@ -29111,7 +29119,7 @@
       <c r="I152" s="8"/>
       <c r="K152" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',4,'Yellow','','イエロー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',3,'Orange','','オレンジ',0,0.0,'');</v>
       </c>
     </row>
     <row r="153" spans="2:11">
@@ -29119,14 +29127,14 @@
         <v>1779</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D153" s="8"/>
       <c r="E153" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="G153" s="9">
         <v>0</v>
@@ -29137,7 +29145,7 @@
       <c r="I153" s="8"/>
       <c r="K153" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',5,'Green','','グリーン',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',4,'Yellow','','イエロー',0,0.0,'');</v>
       </c>
     </row>
     <row r="154" spans="2:11">
@@ -29145,14 +29153,14 @@
         <v>1779</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="D154" s="8"/>
       <c r="E154" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="G154" s="9">
         <v>0</v>
@@ -29163,7 +29171,7 @@
       <c r="I154" s="8"/>
       <c r="K154" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',6,'SkyBlue','','スカイブルー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',5,'Green','','グリーン',0,0.0,'');</v>
       </c>
     </row>
     <row r="155" spans="2:11">
@@ -29171,14 +29179,14 @@
         <v>1779</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="D155" s="8"/>
       <c r="E155" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F155" s="8" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="G155" s="9">
         <v>0</v>
@@ -29189,7 +29197,7 @@
       <c r="I155" s="8"/>
       <c r="K155" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',7,'Blue','','ブルー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',6,'SkyBlue','','スカイブルー',0,0.0,'');</v>
       </c>
     </row>
     <row r="156" spans="2:11">
@@ -29197,14 +29205,14 @@
         <v>1779</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="D156" s="8"/>
       <c r="E156" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F156" s="8" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="G156" s="9">
         <v>0</v>
@@ -29215,7 +29223,7 @@
       <c r="I156" s="8"/>
       <c r="K156" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',8,'Purple','','パープル',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',7,'Blue','','ブルー',0,0.0,'');</v>
       </c>
     </row>
     <row r="157" spans="2:11">
@@ -29223,14 +29231,14 @@
         <v>1779</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="D157" s="8"/>
       <c r="E157" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F157" s="8" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="G157" s="9">
         <v>0</v>
@@ -29241,7 +29249,7 @@
       <c r="I157" s="8"/>
       <c r="K157" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',9,'Gray','','グレー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',8,'Purple','','パープル',0,0.0,'');</v>
       </c>
     </row>
     <row r="158" spans="2:11">
@@ -29249,14 +29257,14 @@
         <v>1779</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="D158" s="8"/>
       <c r="E158" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="G158" s="9">
         <v>0</v>
@@ -29267,7 +29275,7 @@
       <c r="I158" s="8"/>
       <c r="K158" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',10,'Black','','ブラック',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',9,'Gray','','グレー',0,0.0,'');</v>
       </c>
     </row>
     <row r="159" spans="2:11">
@@ -29275,14 +29283,14 @@
         <v>1779</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="D159" s="8"/>
       <c r="E159" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="G159" s="9">
         <v>0</v>
@@ -29293,7 +29301,7 @@
       <c r="I159" s="8"/>
       <c r="K159" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',11,'White','','ホワイト',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',10,'Black','','ブラック',0,0.0,'');</v>
       </c>
     </row>
     <row r="160" spans="2:11">
@@ -29301,14 +29309,14 @@
         <v>1779</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="D160" s="8"/>
       <c r="E160" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F160" s="8" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="G160" s="9">
         <v>0</v>
@@ -29319,7 +29327,7 @@
       <c r="I160" s="8"/>
       <c r="K160" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',12,'Natural','','ナチュラル',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',11,'White','','ホワイト',0,0.0,'');</v>
       </c>
     </row>
     <row r="161" spans="2:11">
@@ -29327,14 +29335,14 @@
         <v>1779</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>1519</v>
+        <v>1514</v>
       </c>
       <c r="D161" s="8"/>
       <c r="E161" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F161" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="G161" s="9">
         <v>0</v>
@@ -29345,7 +29353,7 @@
       <c r="I161" s="8"/>
       <c r="K161" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',13,'Brown','','ブラウン',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',12,'Natural','','ナチュラル',0,0.0,'');</v>
       </c>
     </row>
     <row r="162" spans="2:11">
@@ -29353,14 +29361,14 @@
         <v>1779</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="D162" s="8"/>
       <c r="E162" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="G162" s="9">
         <v>0</v>
@@ -29371,7 +29379,7 @@
       <c r="I162" s="8"/>
       <c r="K162" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',14,'Gold','','ゴールド',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',13,'Brown','','ブラウン',0,0.0,'');</v>
       </c>
     </row>
     <row r="163" spans="2:11">
@@ -29379,14 +29387,14 @@
         <v>1779</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="D163" s="8"/>
       <c r="E163" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F163" s="8" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="G163" s="9">
         <v>0</v>
@@ -29397,7 +29405,7 @@
       <c r="I163" s="8"/>
       <c r="K163" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',15,'Silver','','シルバー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',14,'Gold','','ゴールド',0,0.0,'');</v>
       </c>
     </row>
     <row r="164" spans="2:11">
@@ -29405,14 +29413,14 @@
         <v>1779</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D164" s="8"/>
       <c r="E164" s="8">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="F164" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G164" s="9">
         <v>0</v>
@@ -29423,59 +29431,59 @@
       <c r="I164" s="8"/>
       <c r="K164" s="5" t="str">
         <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',15,'Silver','','シルバー',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="165" spans="2:11">
+      <c r="B165" s="8" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C165" s="8" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D165" s="8"/>
+      <c r="E165" s="8">
+        <v>99</v>
+      </c>
+      <c r="F165" s="8" t="s">
+        <v>1535</v>
+      </c>
+      <c r="G165" s="9">
+        <v>0</v>
+      </c>
+      <c r="H165" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I165" s="8"/>
+      <c r="K165" s="5" t="str">
+        <f t="shared" si="19"/>
         <v>INSERT INTO m_code VALUES ('guitar_colors',99,'Others','','その他',0,0.0,'');</v>
       </c>
     </row>
-    <row r="165" spans="2:11">
-      <c r="B165" s="6" t="s">
+    <row r="166" spans="2:11">
+      <c r="B166" s="6" t="s">
         <v>1888</v>
       </c>
-      <c r="C165" s="6" t="s">
+      <c r="C166" s="6" t="s">
         <v>1889</v>
       </c>
-      <c r="D165" s="6" t="s">
+      <c r="D166" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E165" s="7" t="s">
+      <c r="E166" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F165" s="6" t="s">
+      <c r="F166" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G165" s="6" t="s">
+      <c r="G166" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H165" s="6" t="s">
+      <c r="H166" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I165" s="6" t="s">
+      <c r="I166" s="6" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="166" spans="2:11">
-      <c r="B166" s="8" t="s">
-        <v>1892</v>
-      </c>
-      <c r="C166" s="8" t="s">
-        <v>1890</v>
-      </c>
-      <c r="D166" s="8"/>
-      <c r="E166" s="8">
-        <v>1</v>
-      </c>
-      <c r="F166" s="8"/>
-      <c r="G166" s="9">
-        <v>0</v>
-      </c>
-      <c r="H166" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I166" s="8" t="s">
-        <v>1893</v>
-      </c>
-      <c r="K166" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',1,'SUCCESS','','',0,0.0,'処理成功');</v>
       </c>
     </row>
     <row r="167" spans="2:11">
@@ -29483,11 +29491,11 @@
         <v>1892</v>
       </c>
       <c r="C167" s="8" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="D167" s="8"/>
       <c r="E167" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F167" s="8"/>
       <c r="G167" s="9">
@@ -29497,11 +29505,11 @@
         <v>125</v>
       </c>
       <c r="I167" s="8" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="K167" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',2,'STARTED','','',0,0.0,'処理開始。いずかのステータスに遷移する。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',1,'SUCCESS','','',0,0.0,'処理成功');</v>
       </c>
     </row>
     <row r="168" spans="2:11">
@@ -29509,11 +29517,11 @@
         <v>1892</v>
       </c>
       <c r="C168" s="8" t="s">
-        <v>1881</v>
+        <v>1891</v>
       </c>
       <c r="D168" s="8"/>
       <c r="E168" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F168" s="8"/>
       <c r="G168" s="9">
@@ -29523,11 +29531,11 @@
         <v>125</v>
       </c>
       <c r="I168" s="8" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="K168" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',3,'NOT_STARTED','','',0,0.0,'予定時刻に開始されていない。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',2,'STARTED','','',0,0.0,'処理開始。いずかのステータスに遷移する。');</v>
       </c>
     </row>
     <row r="169" spans="2:11">
@@ -29535,11 +29543,11 @@
         <v>1892</v>
       </c>
       <c r="C169" s="8" t="s">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="D169" s="8"/>
       <c r="E169" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F169" s="8"/>
       <c r="G169" s="9">
@@ -29549,11 +29557,11 @@
         <v>125</v>
       </c>
       <c r="I169" s="8" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="K169" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',4,'ERROR','','',0,0.0,'例外、パニック等が発生した。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',3,'NOT_STARTED','','',0,0.0,'予定時刻に開始されていない。');</v>
       </c>
     </row>
     <row r="170" spans="2:11">
@@ -29561,11 +29569,11 @@
         <v>1892</v>
       </c>
       <c r="C170" s="8" t="s">
-        <v>1882</v>
+        <v>1879</v>
       </c>
       <c r="D170" s="8"/>
       <c r="E170" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F170" s="8"/>
       <c r="G170" s="9">
@@ -29575,11 +29583,11 @@
         <v>125</v>
       </c>
       <c r="I170" s="8" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="K170" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',5,'SLOW','','',0,0.0,'想定時間内に処理が終了しなかった。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',4,'ERROR','','',0,0.0,'例外、パニック等が発生した。');</v>
       </c>
     </row>
     <row r="171" spans="2:11">
@@ -29587,11 +29595,11 @@
         <v>1892</v>
       </c>
       <c r="C171" s="8" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="D171" s="8"/>
       <c r="E171" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F171" s="8"/>
       <c r="G171" s="9">
@@ -29601,9 +29609,35 @@
         <v>125</v>
       </c>
       <c r="I171" s="8" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K171" s="5" t="str">
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('batch_status',5,'SLOW','','',0,0.0,'想定時間内に処理が終了しなかった。');</v>
+      </c>
+    </row>
+    <row r="172" spans="2:11">
+      <c r="B172" s="8" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C172" s="8" t="s">
+        <v>1880</v>
+      </c>
+      <c r="D172" s="8"/>
+      <c r="E172" s="8">
+        <v>6</v>
+      </c>
+      <c r="F172" s="8"/>
+      <c r="G172" s="9">
+        <v>0</v>
+      </c>
+      <c r="H172" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I172" s="8" t="s">
         <v>1897</v>
       </c>
-      <c r="K171" s="5" t="str">
+      <c r="K172" s="5" t="str">
         <f t="shared" si="19"/>
         <v>INSERT INTO m_code VALUES ('batch_status',6,'TIMEOUT','','',0,0.0,'時間内に処理が終了しなかった。');</v>
       </c>
@@ -33162,7 +33196,7 @@
         <v>150</v>
       </c>
       <c r="L6" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;H6&amp;","&amp;VLOOKUP(I6,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;H6&amp;","&amp;VLOOKUP(I6,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster001','キラービー',1,110,12,16,0.3,1);</v>
       </c>
     </row>
@@ -33195,7 +33229,7 @@
         <v>150</v>
       </c>
       <c r="L7" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;H7&amp;","&amp;VLOOKUP(I7,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;H7&amp;","&amp;VLOOKUP(I7,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster002','アサシンバグ',1,132,15,20,0.3,1);</v>
       </c>
     </row>
@@ -33228,7 +33262,7 @@
         <v>150</v>
       </c>
       <c r="L8" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;H8&amp;","&amp;VLOOKUP(I8,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;H8&amp;","&amp;VLOOKUP(I8,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster003','ラスターバグ',1,158,19,26,0.3,1);</v>
       </c>
     </row>
@@ -33258,7 +33292,7 @@
         <v>34</v>
       </c>
       <c r="L9" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;H9&amp;","&amp;VLOOKUP(I9,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;H9&amp;","&amp;VLOOKUP(I9,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster004','カーミラ',2,100,10,13,0.13,2);</v>
       </c>
     </row>
@@ -33291,7 +33325,7 @@
         <v>34</v>
       </c>
       <c r="L10" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;H10&amp;","&amp;VLOOKUP(I10,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;H10&amp;","&amp;VLOOKUP(I10,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster005','カーミラクイーン',2,120,13,16,0.15,2);</v>
       </c>
     </row>
@@ -33321,7 +33355,7 @@
         <v>36</v>
       </c>
       <c r="L11" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;H11&amp;","&amp;VLOOKUP(I11,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;H11&amp;","&amp;VLOOKUP(I11,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster006','デーモン',3,130,15,7,0.08,5);</v>
       </c>
     </row>
@@ -33354,7 +33388,7 @@
         <v>36</v>
       </c>
       <c r="L12" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;H12&amp;","&amp;VLOOKUP(I12,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;H12&amp;","&amp;VLOOKUP(I12,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster007','グレートデーモン',3,156,19,9,0.1,5);</v>
       </c>
     </row>
@@ -33384,7 +33418,7 @@
         <v>35</v>
       </c>
       <c r="L13" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;H13&amp;","&amp;VLOOKUP(I13,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;H13&amp;","&amp;VLOOKUP(I13,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster008','ゴブリン',4,120,11,10,0.15,4);</v>
       </c>
     </row>
@@ -33417,7 +33451,7 @@
         <v>35</v>
       </c>
       <c r="L14" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;H14&amp;","&amp;VLOOKUP(I14,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;H14&amp;","&amp;VLOOKUP(I14,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster009','ゴブリンガード',4,144,14,13,0.15,4);</v>
       </c>
     </row>
@@ -33450,7 +33484,7 @@
         <v>35</v>
       </c>
       <c r="L15" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;H15&amp;","&amp;VLOOKUP(I15,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;H15&amp;","&amp;VLOOKUP(I15,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster010','ゴブリンロード',4,172,18,16,0.15,4);</v>
       </c>
     </row>
@@ -33480,7 +33514,7 @@
         <v>151</v>
       </c>
       <c r="L16" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;H16&amp;","&amp;VLOOKUP(I16,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;H16&amp;","&amp;VLOOKUP(I16,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster011','マシンゴーレム',5,140,17,5,0.02,3);</v>
       </c>
     </row>
@@ -33513,7 +33547,7 @@
         <v>151</v>
       </c>
       <c r="L17" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;H17&amp;","&amp;VLOOKUP(I17,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;H17&amp;","&amp;VLOOKUP(I17,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster012','ガーディアン',5,168,22,6,0.04,3);</v>
       </c>
     </row>
@@ -33546,7 +33580,7 @@
         <v>151</v>
       </c>
       <c r="L18" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;H18&amp;","&amp;VLOOKUP(I18,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;H18&amp;","&amp;VLOOKUP(I18,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster013','デスマシン',5,201,28,7,0.05,3);</v>
       </c>
     </row>
@@ -33576,7 +33610,7 @@
         <v>35</v>
       </c>
       <c r="L19" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;H19&amp;","&amp;VLOOKUP(I19,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;H19&amp;","&amp;VLOOKUP(I19,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster014','ハーピー',6,100,8,14,0.2,4);</v>
       </c>
     </row>
@@ -33609,7 +33643,7 @@
         <v>35</v>
       </c>
       <c r="L20" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;H20&amp;","&amp;VLOOKUP(I20,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;H20&amp;","&amp;VLOOKUP(I20,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster015','セイレーン',6,120,10,18,0.23,4);</v>
       </c>
     </row>
@@ -33639,7 +33673,7 @@
         <v>34</v>
       </c>
       <c r="L21" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;H21&amp;","&amp;VLOOKUP(I21,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;H21&amp;","&amp;VLOOKUP(I21,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster016','アーマーナイト',7,120,13,8,0.05,2);</v>
       </c>
     </row>
@@ -33672,7 +33706,7 @@
         <v>34</v>
       </c>
       <c r="L22" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;H22&amp;","&amp;VLOOKUP(I22,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;H22&amp;","&amp;VLOOKUP(I22,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster017','ダークナイト',7,144,16,10,0.05,2);</v>
       </c>
     </row>
@@ -33705,7 +33739,7 @@
         <v>34</v>
       </c>
       <c r="L23" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;H23&amp;","&amp;VLOOKUP(I23,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;H23&amp;","&amp;VLOOKUP(I23,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster018','ターミネータ',7,172,20,13,0.07,2);</v>
       </c>
     </row>
@@ -33735,7 +33769,7 @@
         <v>35</v>
       </c>
       <c r="L24" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;H24&amp;","&amp;VLOOKUP(I24,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;H24&amp;","&amp;VLOOKUP(I24,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster019','マジシャン',8,100,9,12,0.1,4);</v>
       </c>
     </row>
@@ -33768,7 +33802,7 @@
         <v>35</v>
       </c>
       <c r="L25" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;H25&amp;","&amp;VLOOKUP(I25,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;H25&amp;","&amp;VLOOKUP(I25,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster020','ウィザード',8,120,11,15,0.11,4);</v>
       </c>
     </row>
@@ -33801,7 +33835,7 @@
         <v>35</v>
       </c>
       <c r="L26" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;H26&amp;","&amp;VLOOKUP(I26,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;H26&amp;","&amp;VLOOKUP(I26,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster021','ハイウィザード',8,144,14,19,0.12,4);</v>
       </c>
     </row>
@@ -33831,7 +33865,7 @@
         <v>150</v>
       </c>
       <c r="L27" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;H27&amp;","&amp;VLOOKUP(I27,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;H27&amp;","&amp;VLOOKUP(I27,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster022','マイコニド',9,120,10,12,0.15,1);</v>
       </c>
     </row>
@@ -33864,7 +33898,7 @@
         <v>150</v>
       </c>
       <c r="L28" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;H28&amp;","&amp;VLOOKUP(I28,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;H28&amp;","&amp;VLOOKUP(I28,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster023','ダースマタンゴ',9,144,13,15,0.15,1);</v>
       </c>
     </row>
@@ -33894,7 +33928,7 @@
         <v>151</v>
       </c>
       <c r="L29" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;H29&amp;","&amp;VLOOKUP(I29,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;H29&amp;","&amp;VLOOKUP(I29,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster024','ニードルバード',10,100,13,16,0.25,3);</v>
       </c>
     </row>
@@ -33927,7 +33961,7 @@
         <v>151</v>
       </c>
       <c r="L30" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;H30&amp;","&amp;VLOOKUP(I30,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;H30&amp;","&amp;VLOOKUP(I30,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster025','コカトバード',10,120,16,20,0.27,3);</v>
       </c>
     </row>
@@ -33957,7 +33991,7 @@
         <v>151</v>
       </c>
       <c r="L31" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;H31&amp;","&amp;VLOOKUP(I31,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;H31&amp;","&amp;VLOOKUP(I31,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster026','プチドラゴン',11,130,13,8,0.08,3);</v>
       </c>
     </row>
@@ -33990,7 +34024,7 @@
         <v>36</v>
       </c>
       <c r="L32" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;H32&amp;","&amp;VLOOKUP(I32,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;H32&amp;","&amp;VLOOKUP(I32,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster027','プチドラゾンビ',11,156,16,10,0.1,5);</v>
       </c>
     </row>
@@ -34023,7 +34057,7 @@
         <v>150</v>
       </c>
       <c r="L33" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;H33&amp;","&amp;VLOOKUP(I33,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;H33&amp;","&amp;VLOOKUP(I33,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster028','フロストドラゴン',11,187,20,13,0.12,1);</v>
       </c>
     </row>
@@ -34056,7 +34090,7 @@
         <v>37</v>
       </c>
       <c r="L34" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;H34&amp;","&amp;VLOOKUP(I34,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;H34&amp;","&amp;VLOOKUP(I34,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster029','プチティアマット',11,224,26,16,0.13,6);</v>
       </c>
     </row>
@@ -34086,7 +34120,7 @@
         <v>37</v>
       </c>
       <c r="L35" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;H35&amp;","&amp;VLOOKUP(I35,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;H35&amp;","&amp;VLOOKUP(I35,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster030','ポト',12,100,10,16,0.18,6);</v>
       </c>
     </row>
@@ -34119,7 +34153,7 @@
         <v>37</v>
       </c>
       <c r="L36" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;H36&amp;","&amp;VLOOKUP(I36,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;H36&amp;","&amp;VLOOKUP(I36,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster031','マーマポト',12,120,13,20,0.2,6);</v>
       </c>
     </row>
@@ -34152,7 +34186,7 @@
         <v>37</v>
       </c>
       <c r="L37" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;H37&amp;","&amp;VLOOKUP(I37,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;H37&amp;","&amp;VLOOKUP(I37,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster032','パーパポト',12,141,16,26,0.22,6);</v>
       </c>
     </row>
@@ -34182,7 +34216,7 @@
         <v>37</v>
       </c>
       <c r="L38" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;H38&amp;","&amp;VLOOKUP(I38,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;H38&amp;","&amp;VLOOKUP(I38,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster033','プリースト',13,100,9,13,0.1,6);</v>
       </c>
     </row>
@@ -34215,7 +34249,7 @@
         <v>36</v>
       </c>
       <c r="L39" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;H39&amp;","&amp;VLOOKUP(I39,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;H39&amp;","&amp;VLOOKUP(I39,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster034','カオスソーサラー',13,120,11,16,0.11,5);</v>
       </c>
     </row>
@@ -34248,7 +34282,7 @@
         <v>36</v>
       </c>
       <c r="L40" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;H40&amp;","&amp;VLOOKUP(I40,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;H40&amp;","&amp;VLOOKUP(I40,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster035','イビルシャーマン',13,144,14,20,0.13,5);</v>
       </c>
     </row>
@@ -34279,7 +34313,7 @@
         <v>37</v>
       </c>
       <c r="L41" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;H41&amp;","&amp;VLOOKUP(I41,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;H41&amp;","&amp;VLOOKUP(I41,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster036','ラビ',14,100,11,16,0.16,6);</v>
       </c>
     </row>
@@ -34312,7 +34346,7 @@
         <v>37</v>
       </c>
       <c r="L42" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;H42&amp;","&amp;VLOOKUP(I42,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;H42&amp;","&amp;VLOOKUP(I42,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster037','ラビリオン',14,120,14,20,0.17,6);</v>
       </c>
     </row>
@@ -34345,7 +34379,7 @@
         <v>37</v>
       </c>
       <c r="L43" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;H43&amp;","&amp;VLOOKUP(I43,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;H43&amp;","&amp;VLOOKUP(I43,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster038','キングラビ',14,144,18,26,0.18,6);</v>
       </c>
     </row>
@@ -34378,7 +34412,7 @@
         <v>37</v>
       </c>
       <c r="L44" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;H44&amp;","&amp;VLOOKUP(I44,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;H44&amp;","&amp;VLOOKUP(I44,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster039','グレートラビ',14,172,23,33,0.2,6);</v>
       </c>
     </row>
@@ -34408,7 +34442,7 @@
         <v>34</v>
       </c>
       <c r="L45" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;H45&amp;","&amp;VLOOKUP(I45,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;H45&amp;","&amp;VLOOKUP(I45,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster040','スライム',15,100,10,18,0.15,2);</v>
       </c>
     </row>
@@ -34441,7 +34475,7 @@
         <v>150</v>
       </c>
       <c r="L46" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;H46&amp;","&amp;VLOOKUP(I46,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;H46&amp;","&amp;VLOOKUP(I46,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster041','ブルーババロア',15,120,13,23,0.15,1);</v>
       </c>
     </row>
@@ -34474,7 +34508,7 @@
         <v>151</v>
       </c>
       <c r="L47" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;H47&amp;","&amp;VLOOKUP(I47,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;H47&amp;","&amp;VLOOKUP(I47,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster042','レッドマシュマロ',15,141,16,29,0.15,3);</v>
       </c>
     </row>
@@ -34504,7 +34538,7 @@
         <v>36</v>
       </c>
       <c r="L48" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;H48&amp;","&amp;VLOOKUP(I48,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;H48&amp;","&amp;VLOOKUP(I48,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster043','イビルソード',16,110,15,13,0.14,5);</v>
       </c>
     </row>
@@ -34537,7 +34571,7 @@
         <v>36</v>
       </c>
       <c r="L49" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;H49&amp;","&amp;VLOOKUP(I49,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;H49&amp;","&amp;VLOOKUP(I49,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster044','イビルウェポン',16,132,19,16,0.15,5);</v>
       </c>
     </row>
@@ -34570,7 +34604,7 @@
         <v>37</v>
       </c>
       <c r="L50" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;H50&amp;","&amp;VLOOKUP(I50,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;H50&amp;","&amp;VLOOKUP(I50,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster045','エレメントソード',16,158,24,20,0.16,6);</v>
       </c>
     </row>
@@ -34600,7 +34634,7 @@
         <v>150</v>
       </c>
       <c r="L51" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;H51&amp;","&amp;VLOOKUP(I51,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;H51&amp;","&amp;VLOOKUP(I51,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster046','ケルベロス',17,110,11,19,0.18,1);</v>
       </c>
     </row>
@@ -34633,7 +34667,7 @@
         <v>150</v>
       </c>
       <c r="L52" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;H52&amp;","&amp;VLOOKUP(I52,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;H52&amp;","&amp;VLOOKUP(I52,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster047','バウンドウルフ',17,132,14,24,0.2,1);</v>
       </c>
     </row>
@@ -34666,7 +34700,7 @@
         <v>150</v>
       </c>
       <c r="L53" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;H53&amp;","&amp;VLOOKUP(I53,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;H53&amp;","&amp;VLOOKUP(I53,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster048','ジャッカル',17,158,18,31,0.21,1);</v>
       </c>
     </row>
@@ -34696,7 +34730,7 @@
         <v>151</v>
       </c>
       <c r="L54" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;H54&amp;","&amp;VLOOKUP(I54,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;H54&amp;","&amp;VLOOKUP(I54,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster049','ダックソルジャー',18,120,16,14,0.15,3);</v>
       </c>
     </row>
@@ -34726,7 +34760,7 @@
         <v>151</v>
       </c>
       <c r="L55" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;H55&amp;","&amp;VLOOKUP(I55,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;H55&amp;","&amp;VLOOKUP(I55,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster050','ダックジェネラル',18,160,24,20,0.15,3);</v>
       </c>
     </row>
@@ -34756,7 +34790,7 @@
         <v>34</v>
       </c>
       <c r="L56" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;H56&amp;","&amp;VLOOKUP(I56,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;H56&amp;","&amp;VLOOKUP(I56,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster051','モールベア',19,130,14,18,0.18,2);</v>
       </c>
     </row>
@@ -34786,7 +34820,7 @@
         <v>34</v>
       </c>
       <c r="L57" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;H57&amp;","&amp;VLOOKUP(I57,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;H57&amp;","&amp;VLOOKUP(I57,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster052','ニードリオン',19,170,18,26,0.2,2);</v>
       </c>
     </row>
@@ -34816,7 +34850,7 @@
         <v>35</v>
       </c>
       <c r="L58" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;H58&amp;","&amp;VLOOKUP(I58,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;H58&amp;","&amp;VLOOKUP(I58,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster053','ギャルビー',20,120,13,16,0.2,4);</v>
       </c>
     </row>
@@ -34849,7 +34883,7 @@
         <v>35</v>
       </c>
       <c r="L59" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;H59&amp;","&amp;VLOOKUP(I59,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;H59&amp;","&amp;VLOOKUP(I59,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster054','レディビー',20,144,16,20,0.22,4);</v>
       </c>
     </row>
@@ -34882,7 +34916,7 @@
         <v>35</v>
       </c>
       <c r="L60" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;H60&amp;","&amp;VLOOKUP(I60,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;H60&amp;","&amp;VLOOKUP(I60,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster055','クインビー',20,172,20,26,0.23,4);</v>
       </c>
     </row>
@@ -34912,7 +34946,7 @@
         <v>150</v>
       </c>
       <c r="L61" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;H61&amp;","&amp;VLOOKUP(I61,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;H61&amp;","&amp;VLOOKUP(I61,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster056','サハギン',21,130,16,16,0.15,1);</v>
       </c>
     </row>
@@ -34942,7 +34976,7 @@
         <v>150</v>
       </c>
       <c r="L62" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;H62&amp;","&amp;VLOOKUP(I62,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;H62&amp;","&amp;VLOOKUP(I62,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster057','プチポセイドン',21,150,22,19,0.15,1);</v>
       </c>
     </row>
@@ -34972,7 +35006,7 @@
         <v>298</v>
       </c>
       <c r="L63" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;H63&amp;","&amp;VLOOKUP(I63,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;H63&amp;","&amp;VLOOKUP(I63,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster058','クロウラー',22,130,15,11,0.08,2);</v>
       </c>
     </row>
@@ -35005,7 +35039,7 @@
         <v>34</v>
       </c>
       <c r="L64" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;H64&amp;","&amp;VLOOKUP(I64,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;H64&amp;","&amp;VLOOKUP(I64,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster059','メガクロウラー',22,156,19,14,0.09,2);</v>
       </c>
     </row>
@@ -35038,7 +35072,7 @@
         <v>34</v>
       </c>
       <c r="L65" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;H65&amp;","&amp;VLOOKUP(I65,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;H65&amp;","&amp;VLOOKUP(I65,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster060','ギガクロウラー',22,187,24,18,0.1,2);</v>
       </c>
     </row>
@@ -35068,7 +35102,7 @@
         <v>34</v>
       </c>
       <c r="L66" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;H66&amp;","&amp;VLOOKUP(I66,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;H66&amp;","&amp;VLOOKUP(I66,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster061','ぱっくんオタマ',23,110,12,10,0.15,2);</v>
       </c>
     </row>
@@ -35101,7 +35135,7 @@
         <v>34</v>
       </c>
       <c r="L67" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;H67&amp;","&amp;VLOOKUP(I67,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;H67&amp;","&amp;VLOOKUP(I67,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster062','ぱっくりオタマ',23,132,15,13,0.15,2);</v>
       </c>
     </row>
@@ -35134,7 +35168,7 @@
         <v>151</v>
       </c>
       <c r="L68" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;H68&amp;","&amp;VLOOKUP(I68,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;H68&amp;","&amp;VLOOKUP(I68,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster063','ぱっくんトカゲ',23,158,19,16,0.1,3);</v>
       </c>
     </row>
@@ -35167,7 +35201,7 @@
         <v>151</v>
       </c>
       <c r="L69" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;H69&amp;","&amp;VLOOKUP(I69,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;H69&amp;","&amp;VLOOKUP(I69,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster064','ぱっくんドラゴン',23,189,24,20,0.11,3);</v>
       </c>
     </row>
@@ -35197,7 +35231,7 @@
         <v>36</v>
       </c>
       <c r="L70" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;H70&amp;","&amp;VLOOKUP(I70,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;H70&amp;","&amp;VLOOKUP(I70,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster065','チビデビル',24,120,13,17,0.22,5);</v>
       </c>
     </row>
@@ -35227,7 +35261,7 @@
         <v>36</v>
       </c>
       <c r="L71" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;H71&amp;","&amp;VLOOKUP(I71,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;H71&amp;","&amp;VLOOKUP(I71,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster066','グレムリン',24,160,18,20,0.24,5);</v>
       </c>
     </row>
@@ -35257,7 +35291,7 @@
         <v>36</v>
       </c>
       <c r="L72" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;H72&amp;","&amp;VLOOKUP(I72,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;H72&amp;","&amp;VLOOKUP(I72,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster067','オーガボックス',25,140,18,17,0.15,5);</v>
       </c>
     </row>
@@ -35287,7 +35321,7 @@
         <v>36</v>
       </c>
       <c r="L73" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;H73&amp;","&amp;VLOOKUP(I73,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;H73&amp;","&amp;VLOOKUP(I73,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster068','カイザーミミック',25,170,23,20,0.15,5);</v>
       </c>
     </row>
@@ -35317,7 +35351,7 @@
         <v>151</v>
       </c>
       <c r="L74" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;H74&amp;","&amp;VLOOKUP(I74,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;H74&amp;","&amp;VLOOKUP(I74,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster069','バレッテ',26,140,15,12,0.05,3);</v>
       </c>
     </row>
@@ -35347,7 +35381,7 @@
         <v>151</v>
       </c>
       <c r="L75" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;H75&amp;","&amp;VLOOKUP(I75,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;H75&amp;","&amp;VLOOKUP(I75,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster070','ゴールドバレッテ',26,180,19,14,0.05,3);</v>
       </c>
     </row>
@@ -35377,7 +35411,7 @@
         <v>34</v>
       </c>
       <c r="L76" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;H76&amp;","&amp;VLOOKUP(I76,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;H76&amp;","&amp;VLOOKUP(I76,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster071','バシリスク',27,110,12,15,0.15,2);</v>
       </c>
     </row>
@@ -35407,7 +35441,7 @@
         <v>151</v>
       </c>
       <c r="L77" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;H77&amp;","&amp;VLOOKUP(I77,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;H77&amp;","&amp;VLOOKUP(I77,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster072','ファイアドレイク',27,150,18,22,0.18,3);</v>
       </c>
     </row>
@@ -35437,7 +35471,7 @@
         <v>36</v>
       </c>
       <c r="L78" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;H78&amp;","&amp;VLOOKUP(I78,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;H78&amp;","&amp;VLOOKUP(I78,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster073','スペクター',28,130,13,17,0.2,5);</v>
       </c>
     </row>
@@ -35467,7 +35501,7 @@
         <v>36</v>
       </c>
       <c r="L79" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;H79&amp;","&amp;VLOOKUP(I79,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;H79&amp;","&amp;VLOOKUP(I79,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster074','ゴースト',28,160,17,20,0.21,5);</v>
       </c>
     </row>
@@ -35497,7 +35531,7 @@
         <v>37</v>
       </c>
       <c r="L80" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;","&amp;VLOOKUP(I80,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;","&amp;VLOOKUP(I80,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster075','ユニコーンヘッド',29,120,15,14,0.15,6);</v>
       </c>
     </row>
@@ -35527,7 +35561,7 @@
         <v>37</v>
       </c>
       <c r="L81" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;H81&amp;","&amp;VLOOKUP(I81,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;H81&amp;","&amp;VLOOKUP(I81,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster076','ゴールドユニコ',29,170,22,25,0.15,6);</v>
       </c>
     </row>
@@ -35557,7 +35591,7 @@
         <v>36</v>
       </c>
       <c r="L82" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;H82&amp;","&amp;VLOOKUP(I82,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;H82&amp;","&amp;VLOOKUP(I82,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster077','シェイプシフター',30,130,12,14,0.14,5);</v>
       </c>
     </row>
@@ -35589,7 +35623,7 @@
         <v>36</v>
       </c>
       <c r="L83" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;H83&amp;","&amp;VLOOKUP(I83,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;H83&amp;","&amp;VLOOKUP(I83,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster078','シャドウゼロ',30,170,15,18,0.15,5);</v>
       </c>
     </row>
@@ -35621,7 +35655,7 @@
         <v>36</v>
       </c>
       <c r="L84" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;H84&amp;","&amp;VLOOKUP(I84,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;H84&amp;","&amp;VLOOKUP(I84,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster079','シャドウゼロワン',30,190,19,23,0.16,5);</v>
       </c>
     </row>
@@ -35651,7 +35685,7 @@
         <v>36</v>
       </c>
       <c r="L85" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;H85&amp;","&amp;VLOOKUP(I85,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;H85&amp;","&amp;VLOOKUP(I85,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster080','ボルダー',31,120,13,14,0.25,5);</v>
       </c>
     </row>
@@ -35684,7 +35718,7 @@
         <v>36</v>
       </c>
       <c r="L86" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;H86&amp;","&amp;VLOOKUP(I86,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;H86&amp;","&amp;VLOOKUP(I86,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster081','パワーボルダー',31,144,16,18,0.25,5);</v>
       </c>
     </row>
@@ -35717,7 +35751,7 @@
         <v>36</v>
       </c>
       <c r="L87" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;H87&amp;","&amp;VLOOKUP(I87,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;H87&amp;","&amp;VLOOKUP(I87,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster082','デスボルダー',31,172,20,23,0.25,5);</v>
       </c>
     </row>
@@ -35747,7 +35781,7 @@
         <v>151</v>
       </c>
       <c r="L88" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;H88&amp;","&amp;VLOOKUP(I88,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;H88&amp;","&amp;VLOOKUP(I88,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster083','パンプキンボム',32,130,17,12,0.18,3);</v>
       </c>
     </row>
@@ -35777,7 +35811,7 @@
         <v>151</v>
       </c>
       <c r="L89" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$48:$I$111,3,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;H89&amp;","&amp;VLOOKUP(I89,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;H89&amp;","&amp;VLOOKUP(I89,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster084','グレネードボム',32,160,24,15,0.2,3);</v>
       </c>
     </row>

--- a/_docs/設計メモ.xlsx
+++ b/_docs/設計メモ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository\portfolio\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5326624E-C915-4BF6-B08E-FC6E9D0C42A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC1C587-B01B-4E0F-A04D-492197035FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="778" firstSheet="3" activeTab="3" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4840" uniqueCount="2449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4844" uniqueCount="2450">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -10201,11 +10201,15 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>FUJIGEN</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>https://fujigen.shop/</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GRETSCH</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.gretschguitars.jp/</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -25133,7 +25137,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
-  <dimension ref="B4:K172"/>
+  <dimension ref="B4:K173"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -27746,7 +27750,7 @@
         <v>1551</v>
       </c>
       <c r="K102" s="5" t="str">
-        <f t="shared" ref="K102:K110" si="14">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B102&amp;"'"&amp;","&amp;E102&amp;","&amp;"'"&amp;C102&amp;"'"&amp;","&amp;"'"&amp;D102&amp;"'"&amp;","&amp;"'"&amp;F102&amp;"'"&amp;","&amp;G102&amp;","&amp;H102&amp;","&amp;"'"&amp;I102&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K102:K111" si="14">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B102&amp;"'"&amp;","&amp;E102&amp;","&amp;"'"&amp;C102&amp;"'"&amp;","&amp;"'"&amp;D102&amp;"'"&amp;","&amp;"'"&amp;F102&amp;"'"&amp;","&amp;G102&amp;","&amp;H102&amp;","&amp;"'"&amp;I102&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('guitar_makers',10,'MusicMan','','',0,0.0,'https://www.music-man.com/instruments/guitars');</v>
       </c>
     </row>
@@ -27798,7 +27802,7 @@
         <v>1553</v>
       </c>
       <c r="K104" s="5" t="str">
-        <f t="shared" ref="K104:K109" si="15">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B104&amp;"'"&amp;","&amp;E104&amp;","&amp;"'"&amp;C104&amp;"'"&amp;","&amp;"'"&amp;D104&amp;"'"&amp;","&amp;"'"&amp;F104&amp;"'"&amp;","&amp;G104&amp;","&amp;H104&amp;","&amp;"'"&amp;I104&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K104:K110" si="15">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B104&amp;"'"&amp;","&amp;E104&amp;","&amp;"'"&amp;C104&amp;"'"&amp;","&amp;"'"&amp;D104&amp;"'"&amp;","&amp;"'"&amp;F104&amp;"'"&amp;","&amp;G104&amp;","&amp;H104&amp;","&amp;"'"&amp;I104&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('guitar_makers',12,'Momose','','',0,0.0,'https://www.deviser.co.jp/momose');</v>
       </c>
     </row>
@@ -27937,7 +27941,7 @@
         <v>1777</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>2447</v>
+        <v>2351</v>
       </c>
       <c r="D110" s="8"/>
       <c r="E110" s="8">
@@ -27951,65 +27955,63 @@
         <v>125</v>
       </c>
       <c r="I110" s="8" t="s">
+        <v>2447</v>
+      </c>
+      <c r="K110" s="5" t="str">
+        <f t="shared" si="15"/>
+        <v>INSERT INTO m_code VALUES ('guitar_makers',18,'FUJIGEN','','',0,0.0,'https://fujigen.shop/');</v>
+      </c>
+    </row>
+    <row r="111" spans="2:11">
+      <c r="B111" s="8" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C111" s="8" t="s">
         <v>2448</v>
       </c>
-      <c r="K110" s="5" t="str">
+      <c r="D111" s="8"/>
+      <c r="E111" s="8">
+        <v>19</v>
+      </c>
+      <c r="F111" s="8"/>
+      <c r="G111" s="9">
+        <v>0</v>
+      </c>
+      <c r="H111" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I111" s="8" t="s">
+        <v>2449</v>
+      </c>
+      <c r="K111" s="5" t="str">
         <f t="shared" si="14"/>
-        <v>INSERT INTO m_code VALUES ('guitar_makers',18,'FUJIGEN','','',0,0.0,'https://fujigen.shop/');</v>
-      </c>
-    </row>
-    <row r="111" spans="2:11">
-      <c r="B111" s="6" t="s">
+        <v>INSERT INTO m_code VALUES ('guitar_makers',19,'GRETSCH','','',0,0.0,'https://www.gretschguitars.jp/');</v>
+      </c>
+    </row>
+    <row r="112" spans="2:11">
+      <c r="B112" s="6" t="s">
         <v>1542</v>
       </c>
-      <c r="C111" s="6" t="s">
+      <c r="C112" s="6" t="s">
         <v>1388</v>
       </c>
-      <c r="D111" s="6" t="s">
+      <c r="D112" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E111" s="7" t="s">
+      <c r="E112" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F111" s="6" t="s">
+      <c r="F112" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G111" s="6" t="s">
+      <c r="G112" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H111" s="6" t="s">
+      <c r="H112" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I111" s="6" t="s">
+      <c r="I112" s="6" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="112" spans="2:11">
-      <c r="B112" s="8" t="s">
-        <v>1778</v>
-      </c>
-      <c r="C112" s="8" t="s">
-        <v>1425</v>
-      </c>
-      <c r="D112" s="8"/>
-      <c r="E112" s="8">
-        <v>1</v>
-      </c>
-      <c r="F112" s="8" t="s">
-        <v>1439</v>
-      </c>
-      <c r="G112" s="9">
-        <v>0</v>
-      </c>
-      <c r="H112" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I112" s="8" t="s">
-        <v>1463</v>
-      </c>
-      <c r="K112" s="5" t="str">
-        <f t="shared" ref="K112:K147" si="16">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B112&amp;"'"&amp;","&amp;E112&amp;","&amp;"'"&amp;C112&amp;"'"&amp;","&amp;"'"&amp;D112&amp;"'"&amp;","&amp;"'"&amp;F112&amp;"'"&amp;","&amp;G112&amp;","&amp;H112&amp;","&amp;"'"&amp;I112&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',1,'HardMaple','','ハードメイプル',0,0.0,'硬質でタイト、明瞭なアタック。');</v>
       </c>
     </row>
     <row r="113" spans="2:11">
@@ -28017,14 +28019,14 @@
         <v>1778</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G113" s="9">
         <v>0</v>
@@ -28033,11 +28035,11 @@
         <v>125</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="K113" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',2,'FlameMaple','','フレイムメイプル',0,0.0,'明るく抜けが良く、華やかな倍音。');</v>
+        <f t="shared" ref="K113:K148" si="16">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B113&amp;"'"&amp;","&amp;E113&amp;","&amp;"'"&amp;C113&amp;"'"&amp;","&amp;"'"&amp;D113&amp;"'"&amp;","&amp;"'"&amp;F113&amp;"'"&amp;","&amp;G113&amp;","&amp;H113&amp;","&amp;"'"&amp;I113&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',1,'HardMaple','','ハードメイプル',0,0.0,'硬質でタイト、明瞭なアタック。');</v>
       </c>
     </row>
     <row r="114" spans="2:11">
@@ -28045,14 +28047,14 @@
         <v>1778</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="D114" s="8"/>
       <c r="E114" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="G114" s="9">
         <v>0</v>
@@ -28061,11 +28063,11 @@
         <v>125</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="K114" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',3,'QuiltedMaple','','キルテッドメイプル',0,0.0,'立体的で広がりがあり、煌びやかな響き。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',2,'FlameMaple','','フレイムメイプル',0,0.0,'明るく抜けが良く、華やかな倍音。');</v>
       </c>
     </row>
     <row r="115" spans="2:11">
@@ -28073,14 +28075,14 @@
         <v>1778</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="D115" s="8"/>
       <c r="E115" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="G115" s="9">
         <v>0</v>
@@ -28089,11 +28091,11 @@
         <v>125</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="K115" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',4,'BirdseyeMaple','','バーズアイメイプル',0,0.0,'粒立ちが良く、明るくシャープ。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',3,'QuiltedMaple','','キルテッドメイプル',0,0.0,'立体的で広がりがあり、煌びやかな響き。');</v>
       </c>
     </row>
     <row r="116" spans="2:11">
@@ -28101,14 +28103,14 @@
         <v>1778</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="D116" s="8"/>
       <c r="E116" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="G116" s="9">
         <v>0</v>
@@ -28117,11 +28119,11 @@
         <v>125</v>
       </c>
       <c r="I116" s="8" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="K116" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',5,'RoastedMaple','','ローステッドメイプル',0,0.0,'引き締まったタイトな音で反応が速い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',4,'BirdseyeMaple','','バーズアイメイプル',0,0.0,'粒立ちが良く、明るくシャープ。');</v>
       </c>
     </row>
     <row r="117" spans="2:11">
@@ -28129,14 +28131,14 @@
         <v>1778</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>1389</v>
+        <v>1429</v>
       </c>
       <c r="D117" s="8"/>
       <c r="E117" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>1438</v>
+        <v>1443</v>
       </c>
       <c r="G117" s="9">
         <v>0</v>
@@ -28145,11 +28147,11 @@
         <v>125</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>1462</v>
+        <v>1467</v>
       </c>
       <c r="K117" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',6,'Maple','','メイプル',0,0.0,'明るくハリがあり、アタックが強い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',5,'RoastedMaple','','ローステッドメイプル',0,0.0,'引き締まったタイトな音で反応が速い。');</v>
       </c>
     </row>
     <row r="118" spans="2:11">
@@ -28157,14 +28159,14 @@
         <v>1778</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>1430</v>
+        <v>1389</v>
       </c>
       <c r="D118" s="8"/>
       <c r="E118" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>1444</v>
+        <v>1438</v>
       </c>
       <c r="G118" s="9">
         <v>0</v>
@@ -28173,11 +28175,11 @@
         <v>125</v>
       </c>
       <c r="I118" s="8" t="s">
-        <v>1469</v>
+        <v>1462</v>
       </c>
       <c r="K118" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',7,'HonduranMahogany','','ホンジュラスマホガニー',0,0.0,'深みがあり、太くリッチな中低域。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',6,'Maple','','メイプル',0,0.0,'明るくハリがあり、アタックが強い。');</v>
       </c>
     </row>
     <row r="119" spans="2:11">
@@ -28185,14 +28187,14 @@
         <v>1778</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>1390</v>
+        <v>1430</v>
       </c>
       <c r="D119" s="8"/>
       <c r="E119" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>1408</v>
+        <v>1444</v>
       </c>
       <c r="G119" s="9">
         <v>0</v>
@@ -28201,11 +28203,11 @@
         <v>125</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="K119" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',8,'Mahogany','','マホガニー',0,0.0,'中低域が豊かで温かい音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',7,'HonduranMahogany','','ホンジュラスマホガニー',0,0.0,'深みがあり、太くリッチな中低域。');</v>
       </c>
     </row>
     <row r="120" spans="2:11">
@@ -28213,14 +28215,14 @@
         <v>1778</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>1431</v>
+        <v>1390</v>
       </c>
       <c r="D120" s="8"/>
       <c r="E120" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>1445</v>
+        <v>1408</v>
       </c>
       <c r="G120" s="9">
         <v>0</v>
@@ -28229,11 +28231,11 @@
         <v>125</v>
       </c>
       <c r="I120" s="8" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="K120" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',9,'Sapele','','サペリ',0,0.0,'温かく柔らかいトーンでバランスが良い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',8,'Mahogany','','マホガニー',0,0.0,'中低域が豊かで温かい音。');</v>
       </c>
     </row>
     <row r="121" spans="2:11">
@@ -28241,14 +28243,14 @@
         <v>1778</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>1397</v>
+        <v>1431</v>
       </c>
       <c r="D121" s="8"/>
       <c r="E121" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="G121" s="9">
         <v>0</v>
@@ -28257,11 +28259,11 @@
         <v>125</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="K121" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',10,'Korina','','コリーナ',0,0.0,'中域が豊かで太い音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',9,'Sapele','','サペリ',0,0.0,'温かく柔らかいトーンでバランスが良い。');</v>
       </c>
     </row>
     <row r="122" spans="2:11">
@@ -28269,14 +28271,14 @@
         <v>1778</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>1432</v>
+        <v>1397</v>
       </c>
       <c r="D122" s="8"/>
       <c r="E122" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="G122" s="9">
         <v>0</v>
@@ -28285,11 +28287,11 @@
         <v>125</v>
       </c>
       <c r="I122" s="8" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="K122" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',11,'WhiteKorina','','ホワイトコリーナ',0,0.0,'明るく抜けが良く、軽快なレスポンス。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',10,'Korina','','コリーナ',0,0.0,'中域が豊かで太い音。');</v>
       </c>
     </row>
     <row r="123" spans="2:11">
@@ -28297,14 +28299,14 @@
         <v>1778</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>1391</v>
+        <v>1432</v>
       </c>
       <c r="D123" s="8"/>
       <c r="E123" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>1409</v>
+        <v>1447</v>
       </c>
       <c r="G123" s="9">
         <v>0</v>
@@ -28313,11 +28315,11 @@
         <v>125</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="K123" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',12,'Alder','','アルダー',0,0.0,'バランスが良くクセが少ない。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',11,'WhiteKorina','','ホワイトコリーナ',0,0.0,'明るく抜けが良く、軽快なレスポンス。');</v>
       </c>
     </row>
     <row r="124" spans="2:11">
@@ -28325,14 +28327,14 @@
         <v>1778</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="D124" s="8"/>
       <c r="E124" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F124" s="8" t="s">
-        <v>1448</v>
+        <v>1409</v>
       </c>
       <c r="G124" s="9">
         <v>0</v>
@@ -28341,11 +28343,11 @@
         <v>125</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="K124" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',13,'Ash','','アッシュ',0,0.0,'明るく抜ける音でアタックが強い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',12,'Alder','','アルダー',0,0.0,'バランスが良くクセが少ない。');</v>
       </c>
     </row>
     <row r="125" spans="2:11">
@@ -28353,14 +28355,14 @@
         <v>1778</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="D125" s="8"/>
       <c r="E125" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="G125" s="9">
         <v>0</v>
@@ -28369,11 +28371,11 @@
         <v>125</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="K125" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',14,'Basswood','','バスウッド',0,0.0,'軽く柔らかく、ウォームで扱いやすい。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',13,'Ash','','アッシュ',0,0.0,'明るく抜ける音でアタックが強い。');</v>
       </c>
     </row>
     <row r="126" spans="2:11">
@@ -28381,14 +28383,14 @@
         <v>1778</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>1402</v>
+        <v>1393</v>
       </c>
       <c r="D126" s="8"/>
       <c r="E126" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="G126" s="9">
         <v>0</v>
@@ -28397,11 +28399,11 @@
         <v>125</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="K126" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',15,'Poplar','','ポプラ',0,0.0,'軽く素直でクセが少ない。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',14,'Basswood','','バスウッド',0,0.0,'軽く柔らかく、ウォームで扱いやすい。');</v>
       </c>
     </row>
     <row r="127" spans="2:11">
@@ -28409,14 +28411,14 @@
         <v>1778</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="D127" s="8"/>
       <c r="E127" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="G127" s="9">
         <v>0</v>
@@ -28425,11 +28427,11 @@
         <v>125</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="K127" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',16,'Spruce','','スプルース',0,0.0,'軽く響きが良く、明るいトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',15,'Poplar','','ポプラ',0,0.0,'軽く素直でクセが少ない。');</v>
       </c>
     </row>
     <row r="128" spans="2:11">
@@ -28437,14 +28439,14 @@
         <v>1778</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="D128" s="8"/>
       <c r="E128" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="G128" s="9">
         <v>0</v>
@@ -28453,11 +28455,11 @@
         <v>125</v>
       </c>
       <c r="I128" s="8" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="K128" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',17,'Cedar','','シダー',0,0.0,'柔らかく温かい音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',16,'Spruce','','スプルース',0,0.0,'軽く響きが良く、明るいトーン。');</v>
       </c>
     </row>
     <row r="129" spans="2:11">
@@ -28465,14 +28467,14 @@
         <v>1778</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>1433</v>
+        <v>1399</v>
       </c>
       <c r="D129" s="8"/>
       <c r="E129" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="G129" s="9">
         <v>0</v>
@@ -28481,11 +28483,11 @@
         <v>125</v>
       </c>
       <c r="I129" s="8" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="K129" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',18,'IndianRosewood','','インディアンローズウッド',0,0.0,'甘く深みがあり、豊かな中低域。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',17,'Cedar','','シダー',0,0.0,'柔らかく温かい音。');</v>
       </c>
     </row>
     <row r="130" spans="2:11">
@@ -28493,14 +28495,14 @@
         <v>1778</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="D130" s="8"/>
       <c r="E130" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="G130" s="9">
         <v>0</v>
@@ -28509,11 +28511,11 @@
         <v>125</v>
       </c>
       <c r="I130" s="8" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="K130" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',19,'BrazilianRosewood','','ブラジリアンローズウッド',0,0.0,'濃厚で深いトーン、豊かな倍音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',18,'IndianRosewood','','インディアンローズウッド',0,0.0,'甘く深みがあり、豊かな中低域。');</v>
       </c>
     </row>
     <row r="131" spans="2:11">
@@ -28521,14 +28523,14 @@
         <v>1778</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>1394</v>
+        <v>1434</v>
       </c>
       <c r="D131" s="8"/>
       <c r="E131" s="8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="G131" s="9">
         <v>0</v>
@@ -28537,11 +28539,11 @@
         <v>125</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="K131" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',20,'Rosewood','','ローズウッド',0,0.0,'甘く丸い音で中域が豊か。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',19,'BrazilianRosewood','','ブラジリアンローズウッド',0,0.0,'濃厚で深いトーン、豊かな倍音。');</v>
       </c>
     </row>
     <row r="132" spans="2:11">
@@ -28549,14 +28551,14 @@
         <v>1778</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>1435</v>
+        <v>1394</v>
       </c>
       <c r="D132" s="8"/>
       <c r="E132" s="8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>1410</v>
+        <v>1453</v>
       </c>
       <c r="G132" s="9">
         <v>0</v>
@@ -28565,11 +28567,11 @@
         <v>125</v>
       </c>
       <c r="I132" s="8" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="K132" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',21,'PauFerro','','パーフェロー',0,0.0,'明るく硬質でタイトな音。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',20,'Rosewood','','ローズウッド',0,0.0,'甘く丸い音で中域が豊か。');</v>
       </c>
     </row>
     <row r="133" spans="2:11">
@@ -28577,14 +28579,14 @@
         <v>1778</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>1400</v>
+        <v>1435</v>
       </c>
       <c r="D133" s="8"/>
       <c r="E133" s="8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F133" s="8" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="G133" s="9">
         <v>0</v>
@@ -28593,11 +28595,11 @@
         <v>125</v>
       </c>
       <c r="I133" s="8" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="K133" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',22,'Ovangkol','','オバンコール',0,0.0,'中域が豊かで温かいトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',21,'PauFerro','','パーフェロー',0,0.0,'明るく硬質でタイトな音。');</v>
       </c>
     </row>
     <row r="134" spans="2:11">
@@ -28605,14 +28607,14 @@
         <v>1778</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>1395</v>
+        <v>1400</v>
       </c>
       <c r="D134" s="8"/>
       <c r="E134" s="8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F134" s="8" t="s">
-        <v>1456</v>
+        <v>1411</v>
       </c>
       <c r="G134" s="9">
         <v>0</v>
@@ -28621,11 +28623,11 @@
         <v>125</v>
       </c>
       <c r="I134" s="8" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="K134" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',23,'Ebony','','エボニー',0,0.0,'硬くタイトで高域がクリア。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',22,'Ovangkol','','オバンコール',0,0.0,'中域が豊かで温かいトーン。');</v>
       </c>
     </row>
     <row r="135" spans="2:11">
@@ -28633,14 +28635,14 @@
         <v>1778</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="D135" s="8"/>
       <c r="E135" s="8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F135" s="8" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="G135" s="9">
         <v>0</v>
@@ -28649,11 +28651,11 @@
         <v>125</v>
       </c>
       <c r="I135" s="8" t="s">
-        <v>1416</v>
+        <v>1484</v>
       </c>
       <c r="K135" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',24,'Walnut','','ウォルナット',0,0.0,'中域が豊かで落ち着いたトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',23,'Ebony','','エボニー',0,0.0,'硬くタイトで高域がクリア。');</v>
       </c>
     </row>
     <row r="136" spans="2:11">
@@ -28661,14 +28663,14 @@
         <v>1778</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>1436</v>
+        <v>1396</v>
       </c>
       <c r="D136" s="8"/>
       <c r="E136" s="8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F136" s="8" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="G136" s="9">
         <v>0</v>
@@ -28677,11 +28679,11 @@
         <v>125</v>
       </c>
       <c r="I136" s="8" t="s">
-        <v>1485</v>
+        <v>1416</v>
       </c>
       <c r="K136" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',25,'Padauk','','パドゥーク',0,0.0,'明るく抜けが良く、個性的な響き。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',24,'Walnut','','ウォルナット',0,0.0,'中域が豊かで落ち着いたトーン。');</v>
       </c>
     </row>
     <row r="137" spans="2:11">
@@ -28689,14 +28691,14 @@
         <v>1778</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>1401</v>
+        <v>1436</v>
       </c>
       <c r="D137" s="8"/>
       <c r="E137" s="8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F137" s="8" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="G137" s="9">
         <v>0</v>
@@ -28705,11 +28707,11 @@
         <v>125</v>
       </c>
       <c r="I137" s="8" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="K137" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',26,'Koa','','コア',0,0.0,'明るく華やかで軽快。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',25,'Padauk','','パドゥーク',0,0.0,'明るく抜けが良く、個性的な響き。');</v>
       </c>
     </row>
     <row r="138" spans="2:11">
@@ -28717,14 +28719,14 @@
         <v>1778</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="D138" s="8"/>
       <c r="E138" s="8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="G138" s="9">
         <v>0</v>
@@ -28733,11 +28735,11 @@
         <v>125</v>
       </c>
       <c r="I138" s="8" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="K138" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',27,'Nato','','ナトー',0,0.0,'中低域が豊かで温かい。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',26,'Koa','','コア',0,0.0,'明るく華やかで軽快。');</v>
       </c>
     </row>
     <row r="139" spans="2:11">
@@ -28745,14 +28747,14 @@
         <v>1778</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>1412</v>
+        <v>1460</v>
       </c>
       <c r="G139" s="9">
         <v>0</v>
@@ -28761,11 +28763,11 @@
         <v>125</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="K139" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',28,'Agathis','','アガチス',0,0.0,'柔らかくウォームで素直。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',27,'Nato','','ナトー',0,0.0,'中低域が豊かで温かい。');</v>
       </c>
     </row>
     <row r="140" spans="2:11">
@@ -28773,14 +28775,14 @@
         <v>1778</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="D140" s="8"/>
       <c r="E140" s="8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F140" s="8" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="G140" s="9">
         <v>0</v>
@@ -28789,11 +28791,11 @@
         <v>125</v>
       </c>
       <c r="I140" s="8" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="K140" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',29,'Bubinga','','ブビンガ',0,0.0,'重く硬質でサスティンが長い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',28,'Agathis','','アガチス',0,0.0,'柔らかくウォームで素直。');</v>
       </c>
     </row>
     <row r="141" spans="2:11">
@@ -28801,14 +28803,14 @@
         <v>1778</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="D141" s="8"/>
       <c r="E141" s="8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="G141" s="9">
         <v>0</v>
@@ -28817,11 +28819,11 @@
         <v>125</v>
       </c>
       <c r="I141" s="8" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="K141" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',30,'Wenge','','ウェンジ',0,0.0,'非常に硬くタイトで個性的。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',29,'Bubinga','','ブビンガ',0,0.0,'重く硬質でサスティンが長い。');</v>
       </c>
     </row>
     <row r="142" spans="2:11">
@@ -28829,14 +28831,14 @@
         <v>1778</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D142" s="8"/>
       <c r="E142" s="8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="G142" s="9">
         <v>0</v>
@@ -28845,11 +28847,11 @@
         <v>125</v>
       </c>
       <c r="I142" s="8" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="K142" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',31,'Purpleheart','','パープルハート',0,0.0,'硬く鮮やかでアタックが強い。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',30,'Wenge','','ウェンジ',0,0.0,'非常に硬くタイトで個性的。');</v>
       </c>
     </row>
     <row r="143" spans="2:11">
@@ -28857,14 +28859,14 @@
         <v>1778</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>1437</v>
+        <v>1407</v>
       </c>
       <c r="D143" s="8"/>
       <c r="E143" s="8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F143" s="8" t="s">
-        <v>1461</v>
+        <v>1415</v>
       </c>
       <c r="G143" s="9">
         <v>0</v>
@@ -28873,11 +28875,11 @@
         <v>125</v>
       </c>
       <c r="I143" s="8" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="K143" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',32,'Zebrawood','','ゼブラウッド',0,0.0,'明るく硬質でクセのあるトーン。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',31,'Purpleheart','','パープルハート',0,0.0,'硬く鮮やかでアタックが強い。');</v>
       </c>
     </row>
     <row r="144" spans="2:11">
@@ -28885,14 +28887,14 @@
         <v>1778</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>1558</v>
+        <v>1437</v>
       </c>
       <c r="D144" s="8"/>
       <c r="E144" s="8">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F144" s="8" t="s">
-        <v>1559</v>
+        <v>1461</v>
       </c>
       <c r="G144" s="9">
         <v>0</v>
@@ -28901,11 +28903,11 @@
         <v>125</v>
       </c>
       <c r="I144" s="8" t="s">
-        <v>1560</v>
+        <v>1492</v>
       </c>
       <c r="K144" s="5" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',33,'Okoume','','オクメ',0,0.0,'マホガニーに近く、中低域が豊かで軽量。');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',32,'Zebrawood','','ゼブラウッド',0,0.0,'明るく硬質でクセのあるトーン。');</v>
       </c>
     </row>
     <row r="145" spans="2:11">
@@ -28913,14 +28915,14 @@
         <v>1778</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="D145" s="8"/>
       <c r="E145" s="8">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="G145" s="9">
         <v>0</v>
@@ -28929,11 +28931,11 @@
         <v>125</v>
       </c>
       <c r="I145" s="8" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="K145" s="5" t="str">
-        <f t="shared" ref="K145" si="17">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B145&amp;"'"&amp;","&amp;E145&amp;","&amp;"'"&amp;C145&amp;"'"&amp;","&amp;"'"&amp;D145&amp;"'"&amp;","&amp;"'"&amp;F145&amp;"'"&amp;","&amp;G145&amp;","&amp;H145&amp;","&amp;"'"&amp;I145&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',34,'Meranti','','メランティ',0,0.0,'中域寄りで温かめ、マホガニー系に近い。');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',33,'Okoume','','オクメ',0,0.0,'マホガニーに近く、中低域が豊かで軽量。');</v>
       </c>
     </row>
     <row r="146" spans="2:11">
@@ -28941,14 +28943,14 @@
         <v>1778</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="D146" s="8"/>
       <c r="E146" s="8">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F146" s="8" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="G146" s="9">
         <v>0</v>
@@ -28957,11 +28959,11 @@
         <v>125</v>
       </c>
       <c r="I146" s="8" t="s">
-        <v>1569</v>
+        <v>1563</v>
       </c>
       <c r="K146" s="5" t="str">
-        <f t="shared" ref="K146" si="18">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B146&amp;"'"&amp;","&amp;E146&amp;","&amp;"'"&amp;C146&amp;"'"&amp;","&amp;"'"&amp;D146&amp;"'"&amp;","&amp;"'"&amp;F146&amp;"'"&amp;","&amp;G146&amp;","&amp;H146&amp;","&amp;"'"&amp;I146&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',35,'Sakura','','サクラ',0,0.0,'中高域が明るく立ち上がりが速い、日本らしい軽快で抜けの良いサウンド。');</v>
+        <f t="shared" ref="K146" si="17">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B146&amp;"'"&amp;","&amp;E146&amp;","&amp;"'"&amp;C146&amp;"'"&amp;","&amp;"'"&amp;D146&amp;"'"&amp;","&amp;"'"&amp;F146&amp;"'"&amp;","&amp;G146&amp;","&amp;H146&amp;","&amp;"'"&amp;I146&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',34,'Meranti','','メランティ',0,0.0,'中域寄りで温かめ、マホガニー系に近い。');</v>
       </c>
     </row>
     <row r="147" spans="2:11">
@@ -28969,14 +28971,14 @@
         <v>1778</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="D147" s="8"/>
       <c r="E147" s="8">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F147" s="8" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="G147" s="9">
         <v>0</v>
@@ -28985,11 +28987,11 @@
         <v>125</v>
       </c>
       <c r="I147" s="8" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="K147" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO m_code VALUES ('guitar_woods',36,'Tochi','','トチ',0,0.0,'メイプルに近いクリアさと華やかさを持ちつつ、やや柔らかく豊かな倍音.');</v>
+        <f t="shared" ref="K147" si="18">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B147&amp;"'"&amp;","&amp;E147&amp;","&amp;"'"&amp;C147&amp;"'"&amp;","&amp;"'"&amp;D147&amp;"'"&amp;","&amp;"'"&amp;F147&amp;"'"&amp;","&amp;G147&amp;","&amp;H147&amp;","&amp;"'"&amp;I147&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',35,'Sakura','','サクラ',0,0.0,'中高域が明るく立ち上がりが速い、日本らしい軽快で抜けの良いサウンド。');</v>
       </c>
     </row>
     <row r="148" spans="2:11">
@@ -28997,14 +28999,14 @@
         <v>1778</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>1424</v>
+        <v>1566</v>
       </c>
       <c r="D148" s="8"/>
       <c r="E148" s="8">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="F148" s="8" t="s">
-        <v>1423</v>
+        <v>1567</v>
       </c>
       <c r="G148" s="9">
         <v>0</v>
@@ -29012,62 +29014,64 @@
       <c r="H148" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="I148" s="8"/>
+      <c r="I148" s="8" t="s">
+        <v>1568</v>
+      </c>
       <c r="K148" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B148&amp;"'"&amp;","&amp;E148&amp;","&amp;"'"&amp;C148&amp;"'"&amp;","&amp;"'"&amp;D148&amp;"'"&amp;","&amp;"'"&amp;F148&amp;"'"&amp;","&amp;G148&amp;","&amp;H148&amp;","&amp;"'"&amp;I148&amp;"'"&amp;");"</f>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO m_code VALUES ('guitar_woods',36,'Tochi','','トチ',0,0.0,'メイプルに近いクリアさと華やかさを持ちつつ、やや柔らかく豊かな倍音.');</v>
+      </c>
+    </row>
+    <row r="149" spans="2:11">
+      <c r="B149" s="8" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C149" s="8" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D149" s="8"/>
+      <c r="E149" s="8">
+        <v>99</v>
+      </c>
+      <c r="F149" s="8" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G149" s="9">
+        <v>0</v>
+      </c>
+      <c r="H149" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I149" s="8"/>
+      <c r="K149" s="5" t="str">
+        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B149&amp;"'"&amp;","&amp;E149&amp;","&amp;"'"&amp;C149&amp;"'"&amp;","&amp;"'"&amp;D149&amp;"'"&amp;","&amp;"'"&amp;F149&amp;"'"&amp;","&amp;G149&amp;","&amp;H149&amp;","&amp;"'"&amp;I149&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('guitar_woods',99,'Unknown','','？？',0,0.0,'');</v>
       </c>
     </row>
-    <row r="149" spans="2:11">
-      <c r="B149" s="6" t="s">
+    <row r="150" spans="2:11">
+      <c r="B150" s="6" t="s">
         <v>1503</v>
       </c>
-      <c r="C149" s="6" t="s">
+      <c r="C150" s="6" t="s">
         <v>1502</v>
       </c>
-      <c r="D149" s="6" t="s">
+      <c r="D150" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E149" s="7" t="s">
+      <c r="E150" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F149" s="6" t="s">
+      <c r="F150" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G149" s="6" t="s">
+      <c r="G150" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H149" s="6" t="s">
+      <c r="H150" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I149" s="6" t="s">
+      <c r="I150" s="6" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="150" spans="2:11">
-      <c r="B150" s="8" t="s">
-        <v>1779</v>
-      </c>
-      <c r="C150" s="8" t="s">
-        <v>1504</v>
-      </c>
-      <c r="D150" s="8"/>
-      <c r="E150" s="8">
-        <v>1</v>
-      </c>
-      <c r="F150" s="8" t="s">
-        <v>1520</v>
-      </c>
-      <c r="G150" s="9">
-        <v>0</v>
-      </c>
-      <c r="H150" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I150" s="8"/>
-      <c r="K150" s="5" t="str">
-        <f t="shared" ref="K150:K172" si="19">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B150&amp;"'"&amp;","&amp;E150&amp;","&amp;"'"&amp;C150&amp;"'"&amp;","&amp;"'"&amp;D150&amp;"'"&amp;","&amp;"'"&amp;F150&amp;"'"&amp;","&amp;G150&amp;","&amp;H150&amp;","&amp;"'"&amp;I150&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',1,'Red','','レッド',0,0.0,'');</v>
       </c>
     </row>
     <row r="151" spans="2:11">
@@ -29075,14 +29079,14 @@
         <v>1779</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>1518</v>
+        <v>1504</v>
       </c>
       <c r="D151" s="8"/>
       <c r="E151" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="G151" s="9">
         <v>0</v>
@@ -29092,8 +29096,8 @@
       </c>
       <c r="I151" s="8"/>
       <c r="K151" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',2,'Pink','','ピンク',0,0.0,'');</v>
+        <f t="shared" ref="K151:K173" si="19">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B151&amp;"'"&amp;","&amp;E151&amp;","&amp;"'"&amp;C151&amp;"'"&amp;","&amp;"'"&amp;D151&amp;"'"&amp;","&amp;"'"&amp;F151&amp;"'"&amp;","&amp;G151&amp;","&amp;H151&amp;","&amp;"'"&amp;I151&amp;"'"&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',1,'Red','','レッド',0,0.0,'');</v>
       </c>
     </row>
     <row r="152" spans="2:11">
@@ -29101,14 +29105,14 @@
         <v>1779</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>1505</v>
+        <v>1518</v>
       </c>
       <c r="D152" s="8"/>
       <c r="E152" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F152" s="8" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="G152" s="9">
         <v>0</v>
@@ -29119,7 +29123,7 @@
       <c r="I152" s="8"/>
       <c r="K152" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',3,'Orange','','オレンジ',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',2,'Pink','','ピンク',0,0.0,'');</v>
       </c>
     </row>
     <row r="153" spans="2:11">
@@ -29127,14 +29131,14 @@
         <v>1779</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="D153" s="8"/>
       <c r="E153" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="G153" s="9">
         <v>0</v>
@@ -29145,7 +29149,7 @@
       <c r="I153" s="8"/>
       <c r="K153" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',4,'Yellow','','イエロー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',3,'Orange','','オレンジ',0,0.0,'');</v>
       </c>
     </row>
     <row r="154" spans="2:11">
@@ -29153,14 +29157,14 @@
         <v>1779</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D154" s="8"/>
       <c r="E154" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="G154" s="9">
         <v>0</v>
@@ -29171,7 +29175,7 @@
       <c r="I154" s="8"/>
       <c r="K154" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',5,'Green','','グリーン',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',4,'Yellow','','イエロー',0,0.0,'');</v>
       </c>
     </row>
     <row r="155" spans="2:11">
@@ -29179,14 +29183,14 @@
         <v>1779</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="D155" s="8"/>
       <c r="E155" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F155" s="8" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="G155" s="9">
         <v>0</v>
@@ -29197,7 +29201,7 @@
       <c r="I155" s="8"/>
       <c r="K155" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',6,'SkyBlue','','スカイブルー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',5,'Green','','グリーン',0,0.0,'');</v>
       </c>
     </row>
     <row r="156" spans="2:11">
@@ -29205,14 +29209,14 @@
         <v>1779</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="D156" s="8"/>
       <c r="E156" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F156" s="8" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="G156" s="9">
         <v>0</v>
@@ -29223,7 +29227,7 @@
       <c r="I156" s="8"/>
       <c r="K156" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',7,'Blue','','ブルー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',6,'SkyBlue','','スカイブルー',0,0.0,'');</v>
       </c>
     </row>
     <row r="157" spans="2:11">
@@ -29231,14 +29235,14 @@
         <v>1779</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="D157" s="8"/>
       <c r="E157" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F157" s="8" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="G157" s="9">
         <v>0</v>
@@ -29249,7 +29253,7 @@
       <c r="I157" s="8"/>
       <c r="K157" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',8,'Purple','','パープル',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',7,'Blue','','ブルー',0,0.0,'');</v>
       </c>
     </row>
     <row r="158" spans="2:11">
@@ -29257,14 +29261,14 @@
         <v>1779</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="D158" s="8"/>
       <c r="E158" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="G158" s="9">
         <v>0</v>
@@ -29275,7 +29279,7 @@
       <c r="I158" s="8"/>
       <c r="K158" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',9,'Gray','','グレー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',8,'Purple','','パープル',0,0.0,'');</v>
       </c>
     </row>
     <row r="159" spans="2:11">
@@ -29283,14 +29287,14 @@
         <v>1779</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="D159" s="8"/>
       <c r="E159" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="G159" s="9">
         <v>0</v>
@@ -29301,7 +29305,7 @@
       <c r="I159" s="8"/>
       <c r="K159" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',10,'Black','','ブラック',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',9,'Gray','','グレー',0,0.0,'');</v>
       </c>
     </row>
     <row r="160" spans="2:11">
@@ -29309,14 +29313,14 @@
         <v>1779</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="D160" s="8"/>
       <c r="E160" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F160" s="8" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="G160" s="9">
         <v>0</v>
@@ -29327,7 +29331,7 @@
       <c r="I160" s="8"/>
       <c r="K160" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',11,'White','','ホワイト',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',10,'Black','','ブラック',0,0.0,'');</v>
       </c>
     </row>
     <row r="161" spans="2:11">
@@ -29335,14 +29339,14 @@
         <v>1779</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="D161" s="8"/>
       <c r="E161" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F161" s="8" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="G161" s="9">
         <v>0</v>
@@ -29353,7 +29357,7 @@
       <c r="I161" s="8"/>
       <c r="K161" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',12,'Natural','','ナチュラル',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',11,'White','','ホワイト',0,0.0,'');</v>
       </c>
     </row>
     <row r="162" spans="2:11">
@@ -29361,14 +29365,14 @@
         <v>1779</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>1519</v>
+        <v>1514</v>
       </c>
       <c r="D162" s="8"/>
       <c r="E162" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="G162" s="9">
         <v>0</v>
@@ -29379,7 +29383,7 @@
       <c r="I162" s="8"/>
       <c r="K162" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',13,'Brown','','ブラウン',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',12,'Natural','','ナチュラル',0,0.0,'');</v>
       </c>
     </row>
     <row r="163" spans="2:11">
@@ -29387,14 +29391,14 @@
         <v>1779</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="D163" s="8"/>
       <c r="E163" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F163" s="8" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="G163" s="9">
         <v>0</v>
@@ -29405,7 +29409,7 @@
       <c r="I163" s="8"/>
       <c r="K163" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',14,'Gold','','ゴールド',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',13,'Brown','','ブラウン',0,0.0,'');</v>
       </c>
     </row>
     <row r="164" spans="2:11">
@@ -29413,14 +29417,14 @@
         <v>1779</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="D164" s="8"/>
       <c r="E164" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F164" s="8" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="G164" s="9">
         <v>0</v>
@@ -29431,7 +29435,7 @@
       <c r="I164" s="8"/>
       <c r="K164" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('guitar_colors',15,'Silver','','シルバー',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',14,'Gold','','ゴールド',0,0.0,'');</v>
       </c>
     </row>
     <row r="165" spans="2:11">
@@ -29439,14 +29443,14 @@
         <v>1779</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D165" s="8"/>
       <c r="E165" s="8">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="F165" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G165" s="9">
         <v>0</v>
@@ -29457,59 +29461,59 @@
       <c r="I165" s="8"/>
       <c r="K165" s="5" t="str">
         <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('guitar_colors',15,'Silver','','シルバー',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="166" spans="2:11">
+      <c r="B166" s="8" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C166" s="8" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D166" s="8"/>
+      <c r="E166" s="8">
+        <v>99</v>
+      </c>
+      <c r="F166" s="8" t="s">
+        <v>1535</v>
+      </c>
+      <c r="G166" s="9">
+        <v>0</v>
+      </c>
+      <c r="H166" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I166" s="8"/>
+      <c r="K166" s="5" t="str">
+        <f t="shared" si="19"/>
         <v>INSERT INTO m_code VALUES ('guitar_colors',99,'Others','','その他',0,0.0,'');</v>
       </c>
     </row>
-    <row r="166" spans="2:11">
-      <c r="B166" s="6" t="s">
+    <row r="167" spans="2:11">
+      <c r="B167" s="6" t="s">
         <v>1888</v>
       </c>
-      <c r="C166" s="6" t="s">
+      <c r="C167" s="6" t="s">
         <v>1889</v>
       </c>
-      <c r="D166" s="6" t="s">
+      <c r="D167" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E166" s="7" t="s">
+      <c r="E167" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F166" s="6" t="s">
+      <c r="F167" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G166" s="6" t="s">
+      <c r="G167" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H166" s="6" t="s">
+      <c r="H167" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I166" s="6" t="s">
+      <c r="I167" s="6" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="167" spans="2:11">
-      <c r="B167" s="8" t="s">
-        <v>1892</v>
-      </c>
-      <c r="C167" s="8" t="s">
-        <v>1890</v>
-      </c>
-      <c r="D167" s="8"/>
-      <c r="E167" s="8">
-        <v>1</v>
-      </c>
-      <c r="F167" s="8"/>
-      <c r="G167" s="9">
-        <v>0</v>
-      </c>
-      <c r="H167" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I167" s="8" t="s">
-        <v>1893</v>
-      </c>
-      <c r="K167" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',1,'SUCCESS','','',0,0.0,'処理成功');</v>
       </c>
     </row>
     <row r="168" spans="2:11">
@@ -29517,11 +29521,11 @@
         <v>1892</v>
       </c>
       <c r="C168" s="8" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="D168" s="8"/>
       <c r="E168" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F168" s="8"/>
       <c r="G168" s="9">
@@ -29531,11 +29535,11 @@
         <v>125</v>
       </c>
       <c r="I168" s="8" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="K168" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',2,'STARTED','','',0,0.0,'処理開始。いずかのステータスに遷移する。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',1,'SUCCESS','','',0,0.0,'処理成功');</v>
       </c>
     </row>
     <row r="169" spans="2:11">
@@ -29543,11 +29547,11 @@
         <v>1892</v>
       </c>
       <c r="C169" s="8" t="s">
-        <v>1881</v>
+        <v>1891</v>
       </c>
       <c r="D169" s="8"/>
       <c r="E169" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F169" s="8"/>
       <c r="G169" s="9">
@@ -29557,11 +29561,11 @@
         <v>125</v>
       </c>
       <c r="I169" s="8" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="K169" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',3,'NOT_STARTED','','',0,0.0,'予定時刻に開始されていない。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',2,'STARTED','','',0,0.0,'処理開始。いずかのステータスに遷移する。');</v>
       </c>
     </row>
     <row r="170" spans="2:11">
@@ -29569,11 +29573,11 @@
         <v>1892</v>
       </c>
       <c r="C170" s="8" t="s">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="D170" s="8"/>
       <c r="E170" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F170" s="8"/>
       <c r="G170" s="9">
@@ -29583,11 +29587,11 @@
         <v>125</v>
       </c>
       <c r="I170" s="8" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="K170" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',4,'ERROR','','',0,0.0,'例外、パニック等が発生した。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',3,'NOT_STARTED','','',0,0.0,'予定時刻に開始されていない。');</v>
       </c>
     </row>
     <row r="171" spans="2:11">
@@ -29595,11 +29599,11 @@
         <v>1892</v>
       </c>
       <c r="C171" s="8" t="s">
-        <v>1882</v>
+        <v>1879</v>
       </c>
       <c r="D171" s="8"/>
       <c r="E171" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F171" s="8"/>
       <c r="G171" s="9">
@@ -29609,11 +29613,11 @@
         <v>125</v>
       </c>
       <c r="I171" s="8" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="K171" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>INSERT INTO m_code VALUES ('batch_status',5,'SLOW','','',0,0.0,'想定時間内に処理が終了しなかった。');</v>
+        <v>INSERT INTO m_code VALUES ('batch_status',4,'ERROR','','',0,0.0,'例外、パニック等が発生した。');</v>
       </c>
     </row>
     <row r="172" spans="2:11">
@@ -29621,11 +29625,11 @@
         <v>1892</v>
       </c>
       <c r="C172" s="8" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="D172" s="8"/>
       <c r="E172" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F172" s="8"/>
       <c r="G172" s="9">
@@ -29635,9 +29639,35 @@
         <v>125</v>
       </c>
       <c r="I172" s="8" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K172" s="5" t="str">
+        <f t="shared" si="19"/>
+        <v>INSERT INTO m_code VALUES ('batch_status',5,'SLOW','','',0,0.0,'想定時間内に処理が終了しなかった。');</v>
+      </c>
+    </row>
+    <row r="173" spans="2:11">
+      <c r="B173" s="8" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C173" s="8" t="s">
+        <v>1880</v>
+      </c>
+      <c r="D173" s="8"/>
+      <c r="E173" s="8">
+        <v>6</v>
+      </c>
+      <c r="F173" s="8"/>
+      <c r="G173" s="9">
+        <v>0</v>
+      </c>
+      <c r="H173" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I173" s="8" t="s">
         <v>1897</v>
       </c>
-      <c r="K172" s="5" t="str">
+      <c r="K173" s="5" t="str">
         <f t="shared" si="19"/>
         <v>INSERT INTO m_code VALUES ('batch_status',6,'TIMEOUT','','',0,0.0,'時間内に処理が終了しなかった。');</v>
       </c>
@@ -33196,7 +33226,7 @@
         <v>150</v>
       </c>
       <c r="L6" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;H6&amp;","&amp;VLOOKUP(I6,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;H6&amp;","&amp;VLOOKUP(I6,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster001','キラービー',1,110,12,16,0.3,1);</v>
       </c>
     </row>
@@ -33229,7 +33259,7 @@
         <v>150</v>
       </c>
       <c r="L7" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;H7&amp;","&amp;VLOOKUP(I7,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;H7&amp;","&amp;VLOOKUP(I7,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster002','アサシンバグ',1,132,15,20,0.3,1);</v>
       </c>
     </row>
@@ -33262,7 +33292,7 @@
         <v>150</v>
       </c>
       <c r="L8" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;H8&amp;","&amp;VLOOKUP(I8,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;H8&amp;","&amp;VLOOKUP(I8,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster003','ラスターバグ',1,158,19,26,0.3,1);</v>
       </c>
     </row>
@@ -33292,7 +33322,7 @@
         <v>34</v>
       </c>
       <c r="L9" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;H9&amp;","&amp;VLOOKUP(I9,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;H9&amp;","&amp;VLOOKUP(I9,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster004','カーミラ',2,100,10,13,0.13,2);</v>
       </c>
     </row>
@@ -33325,7 +33355,7 @@
         <v>34</v>
       </c>
       <c r="L10" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;H10&amp;","&amp;VLOOKUP(I10,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;H10&amp;","&amp;VLOOKUP(I10,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster005','カーミラクイーン',2,120,13,16,0.15,2);</v>
       </c>
     </row>
@@ -33355,7 +33385,7 @@
         <v>36</v>
       </c>
       <c r="L11" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;H11&amp;","&amp;VLOOKUP(I11,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;H11&amp;","&amp;VLOOKUP(I11,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster006','デーモン',3,130,15,7,0.08,5);</v>
       </c>
     </row>
@@ -33388,7 +33418,7 @@
         <v>36</v>
       </c>
       <c r="L12" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;H12&amp;","&amp;VLOOKUP(I12,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;H12&amp;","&amp;VLOOKUP(I12,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster007','グレートデーモン',3,156,19,9,0.1,5);</v>
       </c>
     </row>
@@ -33418,7 +33448,7 @@
         <v>35</v>
       </c>
       <c r="L13" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;H13&amp;","&amp;VLOOKUP(I13,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;H13&amp;","&amp;VLOOKUP(I13,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster008','ゴブリン',4,120,11,10,0.15,4);</v>
       </c>
     </row>
@@ -33451,7 +33481,7 @@
         <v>35</v>
       </c>
       <c r="L14" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;H14&amp;","&amp;VLOOKUP(I14,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;H14&amp;","&amp;VLOOKUP(I14,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster009','ゴブリンガード',4,144,14,13,0.15,4);</v>
       </c>
     </row>
@@ -33484,7 +33514,7 @@
         <v>35</v>
       </c>
       <c r="L15" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;H15&amp;","&amp;VLOOKUP(I15,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;H15&amp;","&amp;VLOOKUP(I15,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster010','ゴブリンロード',4,172,18,16,0.15,4);</v>
       </c>
     </row>
@@ -33514,7 +33544,7 @@
         <v>151</v>
       </c>
       <c r="L16" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;H16&amp;","&amp;VLOOKUP(I16,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;H16&amp;","&amp;VLOOKUP(I16,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster011','マシンゴーレム',5,140,17,5,0.02,3);</v>
       </c>
     </row>
@@ -33547,7 +33577,7 @@
         <v>151</v>
       </c>
       <c r="L17" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;H17&amp;","&amp;VLOOKUP(I17,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;H17&amp;","&amp;VLOOKUP(I17,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster012','ガーディアン',5,168,22,6,0.04,3);</v>
       </c>
     </row>
@@ -33580,7 +33610,7 @@
         <v>151</v>
       </c>
       <c r="L18" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;H18&amp;","&amp;VLOOKUP(I18,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;H18&amp;","&amp;VLOOKUP(I18,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster013','デスマシン',5,201,28,7,0.05,3);</v>
       </c>
     </row>
@@ -33610,7 +33640,7 @@
         <v>35</v>
       </c>
       <c r="L19" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;H19&amp;","&amp;VLOOKUP(I19,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;H19&amp;","&amp;VLOOKUP(I19,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster014','ハーピー',6,100,8,14,0.2,4);</v>
       </c>
     </row>
@@ -33643,7 +33673,7 @@
         <v>35</v>
       </c>
       <c r="L20" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;H20&amp;","&amp;VLOOKUP(I20,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;H20&amp;","&amp;VLOOKUP(I20,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster015','セイレーン',6,120,10,18,0.23,4);</v>
       </c>
     </row>
@@ -33673,7 +33703,7 @@
         <v>34</v>
       </c>
       <c r="L21" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;H21&amp;","&amp;VLOOKUP(I21,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;H21&amp;","&amp;VLOOKUP(I21,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster016','アーマーナイト',7,120,13,8,0.05,2);</v>
       </c>
     </row>
@@ -33706,7 +33736,7 @@
         <v>34</v>
       </c>
       <c r="L22" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;H22&amp;","&amp;VLOOKUP(I22,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;H22&amp;","&amp;VLOOKUP(I22,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster017','ダークナイト',7,144,16,10,0.05,2);</v>
       </c>
     </row>
@@ -33739,7 +33769,7 @@
         <v>34</v>
       </c>
       <c r="L23" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;H23&amp;","&amp;VLOOKUP(I23,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;H23&amp;","&amp;VLOOKUP(I23,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster018','ターミネータ',7,172,20,13,0.07,2);</v>
       </c>
     </row>
@@ -33769,7 +33799,7 @@
         <v>35</v>
       </c>
       <c r="L24" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;H24&amp;","&amp;VLOOKUP(I24,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;H24&amp;","&amp;VLOOKUP(I24,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster019','マジシャン',8,100,9,12,0.1,4);</v>
       </c>
     </row>
@@ -33802,7 +33832,7 @@
         <v>35</v>
       </c>
       <c r="L25" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;H25&amp;","&amp;VLOOKUP(I25,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;H25&amp;","&amp;VLOOKUP(I25,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster020','ウィザード',8,120,11,15,0.11,4);</v>
       </c>
     </row>
@@ -33835,7 +33865,7 @@
         <v>35</v>
       </c>
       <c r="L26" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;H26&amp;","&amp;VLOOKUP(I26,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;H26&amp;","&amp;VLOOKUP(I26,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster021','ハイウィザード',8,144,14,19,0.12,4);</v>
       </c>
     </row>
@@ -33865,7 +33895,7 @@
         <v>150</v>
       </c>
       <c r="L27" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;H27&amp;","&amp;VLOOKUP(I27,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;H27&amp;","&amp;VLOOKUP(I27,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster022','マイコニド',9,120,10,12,0.15,1);</v>
       </c>
     </row>
@@ -33898,7 +33928,7 @@
         <v>150</v>
       </c>
       <c r="L28" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;H28&amp;","&amp;VLOOKUP(I28,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;H28&amp;","&amp;VLOOKUP(I28,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster023','ダースマタンゴ',9,144,13,15,0.15,1);</v>
       </c>
     </row>
@@ -33928,7 +33958,7 @@
         <v>151</v>
       </c>
       <c r="L29" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;H29&amp;","&amp;VLOOKUP(I29,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;H29&amp;","&amp;VLOOKUP(I29,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster024','ニードルバード',10,100,13,16,0.25,3);</v>
       </c>
     </row>
@@ -33961,7 +33991,7 @@
         <v>151</v>
       </c>
       <c r="L30" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;H30&amp;","&amp;VLOOKUP(I30,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;H30&amp;","&amp;VLOOKUP(I30,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster025','コカトバード',10,120,16,20,0.27,3);</v>
       </c>
     </row>
@@ -33991,7 +34021,7 @@
         <v>151</v>
       </c>
       <c r="L31" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;H31&amp;","&amp;VLOOKUP(I31,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;H31&amp;","&amp;VLOOKUP(I31,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster026','プチドラゴン',11,130,13,8,0.08,3);</v>
       </c>
     </row>
@@ -34024,7 +34054,7 @@
         <v>36</v>
       </c>
       <c r="L32" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;H32&amp;","&amp;VLOOKUP(I32,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;H32&amp;","&amp;VLOOKUP(I32,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster027','プチドラゾンビ',11,156,16,10,0.1,5);</v>
       </c>
     </row>
@@ -34057,7 +34087,7 @@
         <v>150</v>
       </c>
       <c r="L33" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;H33&amp;","&amp;VLOOKUP(I33,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;H33&amp;","&amp;VLOOKUP(I33,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster028','フロストドラゴン',11,187,20,13,0.12,1);</v>
       </c>
     </row>
@@ -34090,7 +34120,7 @@
         <v>37</v>
       </c>
       <c r="L34" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;H34&amp;","&amp;VLOOKUP(I34,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;H34&amp;","&amp;VLOOKUP(I34,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster029','プチティアマット',11,224,26,16,0.13,6);</v>
       </c>
     </row>
@@ -34120,7 +34150,7 @@
         <v>37</v>
       </c>
       <c r="L35" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;H35&amp;","&amp;VLOOKUP(I35,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;H35&amp;","&amp;VLOOKUP(I35,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster030','ポト',12,100,10,16,0.18,6);</v>
       </c>
     </row>
@@ -34153,7 +34183,7 @@
         <v>37</v>
       </c>
       <c r="L36" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;H36&amp;","&amp;VLOOKUP(I36,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;H36&amp;","&amp;VLOOKUP(I36,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster031','マーマポト',12,120,13,20,0.2,6);</v>
       </c>
     </row>
@@ -34186,7 +34216,7 @@
         <v>37</v>
       </c>
       <c r="L37" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;H37&amp;","&amp;VLOOKUP(I37,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;H37&amp;","&amp;VLOOKUP(I37,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster032','パーパポト',12,141,16,26,0.22,6);</v>
       </c>
     </row>
@@ -34216,7 +34246,7 @@
         <v>37</v>
       </c>
       <c r="L38" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;H38&amp;","&amp;VLOOKUP(I38,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;H38&amp;","&amp;VLOOKUP(I38,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster033','プリースト',13,100,9,13,0.1,6);</v>
       </c>
     </row>
@@ -34249,7 +34279,7 @@
         <v>36</v>
       </c>
       <c r="L39" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;H39&amp;","&amp;VLOOKUP(I39,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;H39&amp;","&amp;VLOOKUP(I39,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster034','カオスソーサラー',13,120,11,16,0.11,5);</v>
       </c>
     </row>
@@ -34282,7 +34312,7 @@
         <v>36</v>
       </c>
       <c r="L40" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;H40&amp;","&amp;VLOOKUP(I40,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;H40&amp;","&amp;VLOOKUP(I40,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster035','イビルシャーマン',13,144,14,20,0.13,5);</v>
       </c>
     </row>
@@ -34313,7 +34343,7 @@
         <v>37</v>
       </c>
       <c r="L41" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;H41&amp;","&amp;VLOOKUP(I41,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;H41&amp;","&amp;VLOOKUP(I41,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster036','ラビ',14,100,11,16,0.16,6);</v>
       </c>
     </row>
@@ -34346,7 +34376,7 @@
         <v>37</v>
       </c>
       <c r="L42" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;H42&amp;","&amp;VLOOKUP(I42,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;H42&amp;","&amp;VLOOKUP(I42,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster037','ラビリオン',14,120,14,20,0.17,6);</v>
       </c>
     </row>
@@ -34379,7 +34409,7 @@
         <v>37</v>
       </c>
       <c r="L43" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;H43&amp;","&amp;VLOOKUP(I43,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;H43&amp;","&amp;VLOOKUP(I43,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster038','キングラビ',14,144,18,26,0.18,6);</v>
       </c>
     </row>
@@ -34412,7 +34442,7 @@
         <v>37</v>
       </c>
       <c r="L44" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;H44&amp;","&amp;VLOOKUP(I44,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;H44&amp;","&amp;VLOOKUP(I44,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster039','グレートラビ',14,172,23,33,0.2,6);</v>
       </c>
     </row>
@@ -34442,7 +34472,7 @@
         <v>34</v>
       </c>
       <c r="L45" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;H45&amp;","&amp;VLOOKUP(I45,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;H45&amp;","&amp;VLOOKUP(I45,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster040','スライム',15,100,10,18,0.15,2);</v>
       </c>
     </row>
@@ -34475,7 +34505,7 @@
         <v>150</v>
       </c>
       <c r="L46" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;H46&amp;","&amp;VLOOKUP(I46,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;H46&amp;","&amp;VLOOKUP(I46,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster041','ブルーババロア',15,120,13,23,0.15,1);</v>
       </c>
     </row>
@@ -34508,7 +34538,7 @@
         <v>151</v>
       </c>
       <c r="L47" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;H47&amp;","&amp;VLOOKUP(I47,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;H47&amp;","&amp;VLOOKUP(I47,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster042','レッドマシュマロ',15,141,16,29,0.15,3);</v>
       </c>
     </row>
@@ -34538,7 +34568,7 @@
         <v>36</v>
       </c>
       <c r="L48" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;H48&amp;","&amp;VLOOKUP(I48,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;H48&amp;","&amp;VLOOKUP(I48,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster043','イビルソード',16,110,15,13,0.14,5);</v>
       </c>
     </row>
@@ -34571,7 +34601,7 @@
         <v>36</v>
       </c>
       <c r="L49" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;H49&amp;","&amp;VLOOKUP(I49,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;H49&amp;","&amp;VLOOKUP(I49,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster044','イビルウェポン',16,132,19,16,0.15,5);</v>
       </c>
     </row>
@@ -34604,7 +34634,7 @@
         <v>37</v>
       </c>
       <c r="L50" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;H50&amp;","&amp;VLOOKUP(I50,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;H50&amp;","&amp;VLOOKUP(I50,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster045','エレメントソード',16,158,24,20,0.16,6);</v>
       </c>
     </row>
@@ -34634,7 +34664,7 @@
         <v>150</v>
       </c>
       <c r="L51" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;H51&amp;","&amp;VLOOKUP(I51,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;H51&amp;","&amp;VLOOKUP(I51,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster046','ケルベロス',17,110,11,19,0.18,1);</v>
       </c>
     </row>
@@ -34667,7 +34697,7 @@
         <v>150</v>
       </c>
       <c r="L52" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;H52&amp;","&amp;VLOOKUP(I52,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;H52&amp;","&amp;VLOOKUP(I52,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster047','バウンドウルフ',17,132,14,24,0.2,1);</v>
       </c>
     </row>
@@ -34700,7 +34730,7 @@
         <v>150</v>
       </c>
       <c r="L53" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;H53&amp;","&amp;VLOOKUP(I53,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;H53&amp;","&amp;VLOOKUP(I53,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster048','ジャッカル',17,158,18,31,0.21,1);</v>
       </c>
     </row>
@@ -34730,7 +34760,7 @@
         <v>151</v>
       </c>
       <c r="L54" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;H54&amp;","&amp;VLOOKUP(I54,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;H54&amp;","&amp;VLOOKUP(I54,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster049','ダックソルジャー',18,120,16,14,0.15,3);</v>
       </c>
     </row>
@@ -34760,7 +34790,7 @@
         <v>151</v>
       </c>
       <c r="L55" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;H55&amp;","&amp;VLOOKUP(I55,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;H55&amp;","&amp;VLOOKUP(I55,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster050','ダックジェネラル',18,160,24,20,0.15,3);</v>
       </c>
     </row>
@@ -34790,7 +34820,7 @@
         <v>34</v>
       </c>
       <c r="L56" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;H56&amp;","&amp;VLOOKUP(I56,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;H56&amp;","&amp;VLOOKUP(I56,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster051','モールベア',19,130,14,18,0.18,2);</v>
       </c>
     </row>
@@ -34820,7 +34850,7 @@
         <v>34</v>
       </c>
       <c r="L57" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;H57&amp;","&amp;VLOOKUP(I57,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;H57&amp;","&amp;VLOOKUP(I57,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster052','ニードリオン',19,170,18,26,0.2,2);</v>
       </c>
     </row>
@@ -34850,7 +34880,7 @@
         <v>35</v>
       </c>
       <c r="L58" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;H58&amp;","&amp;VLOOKUP(I58,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;H58&amp;","&amp;VLOOKUP(I58,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster053','ギャルビー',20,120,13,16,0.2,4);</v>
       </c>
     </row>
@@ -34883,7 +34913,7 @@
         <v>35</v>
       </c>
       <c r="L59" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;H59&amp;","&amp;VLOOKUP(I59,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;H59&amp;","&amp;VLOOKUP(I59,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster054','レディビー',20,144,16,20,0.22,4);</v>
       </c>
     </row>
@@ -34916,7 +34946,7 @@
         <v>35</v>
       </c>
       <c r="L60" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;H60&amp;","&amp;VLOOKUP(I60,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;H60&amp;","&amp;VLOOKUP(I60,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster055','クインビー',20,172,20,26,0.23,4);</v>
       </c>
     </row>
@@ -34946,7 +34976,7 @@
         <v>150</v>
       </c>
       <c r="L61" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;H61&amp;","&amp;VLOOKUP(I61,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;H61&amp;","&amp;VLOOKUP(I61,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster056','サハギン',21,130,16,16,0.15,1);</v>
       </c>
     </row>
@@ -34976,7 +35006,7 @@
         <v>150</v>
       </c>
       <c r="L62" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;H62&amp;","&amp;VLOOKUP(I62,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;H62&amp;","&amp;VLOOKUP(I62,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster057','プチポセイドン',21,150,22,19,0.15,1);</v>
       </c>
     </row>
@@ -35006,7 +35036,7 @@
         <v>298</v>
       </c>
       <c r="L63" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;H63&amp;","&amp;VLOOKUP(I63,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;H63&amp;","&amp;VLOOKUP(I63,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster058','クロウラー',22,130,15,11,0.08,2);</v>
       </c>
     </row>
@@ -35039,7 +35069,7 @@
         <v>34</v>
       </c>
       <c r="L64" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;H64&amp;","&amp;VLOOKUP(I64,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;H64&amp;","&amp;VLOOKUP(I64,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster059','メガクロウラー',22,156,19,14,0.09,2);</v>
       </c>
     </row>
@@ -35072,7 +35102,7 @@
         <v>34</v>
       </c>
       <c r="L65" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;H65&amp;","&amp;VLOOKUP(I65,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;H65&amp;","&amp;VLOOKUP(I65,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster060','ギガクロウラー',22,187,24,18,0.1,2);</v>
       </c>
     </row>
@@ -35102,7 +35132,7 @@
         <v>34</v>
       </c>
       <c r="L66" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;H66&amp;","&amp;VLOOKUP(I66,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;H66&amp;","&amp;VLOOKUP(I66,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster061','ぱっくんオタマ',23,110,12,10,0.15,2);</v>
       </c>
     </row>
@@ -35135,7 +35165,7 @@
         <v>34</v>
       </c>
       <c r="L67" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;H67&amp;","&amp;VLOOKUP(I67,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;H67&amp;","&amp;VLOOKUP(I67,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster062','ぱっくりオタマ',23,132,15,13,0.15,2);</v>
       </c>
     </row>
@@ -35168,7 +35198,7 @@
         <v>151</v>
       </c>
       <c r="L68" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;H68&amp;","&amp;VLOOKUP(I68,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;H68&amp;","&amp;VLOOKUP(I68,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster063','ぱっくんトカゲ',23,158,19,16,0.1,3);</v>
       </c>
     </row>
@@ -35201,7 +35231,7 @@
         <v>151</v>
       </c>
       <c r="L69" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;H69&amp;","&amp;VLOOKUP(I69,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;H69&amp;","&amp;VLOOKUP(I69,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster064','ぱっくんドラゴン',23,189,24,20,0.11,3);</v>
       </c>
     </row>
@@ -35231,7 +35261,7 @@
         <v>36</v>
       </c>
       <c r="L70" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;H70&amp;","&amp;VLOOKUP(I70,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;H70&amp;","&amp;VLOOKUP(I70,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster065','チビデビル',24,120,13,17,0.22,5);</v>
       </c>
     </row>
@@ -35261,7 +35291,7 @@
         <v>36</v>
       </c>
       <c r="L71" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;H71&amp;","&amp;VLOOKUP(I71,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;H71&amp;","&amp;VLOOKUP(I71,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster066','グレムリン',24,160,18,20,0.24,5);</v>
       </c>
     </row>
@@ -35291,7 +35321,7 @@
         <v>36</v>
       </c>
       <c r="L72" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;H72&amp;","&amp;VLOOKUP(I72,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;H72&amp;","&amp;VLOOKUP(I72,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster067','オーガボックス',25,140,18,17,0.15,5);</v>
       </c>
     </row>
@@ -35321,7 +35351,7 @@
         <v>36</v>
       </c>
       <c r="L73" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;H73&amp;","&amp;VLOOKUP(I73,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;H73&amp;","&amp;VLOOKUP(I73,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster068','カイザーミミック',25,170,23,20,0.15,5);</v>
       </c>
     </row>
@@ -35351,7 +35381,7 @@
         <v>151</v>
       </c>
       <c r="L74" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;H74&amp;","&amp;VLOOKUP(I74,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;H74&amp;","&amp;VLOOKUP(I74,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster069','バレッテ',26,140,15,12,0.05,3);</v>
       </c>
     </row>
@@ -35381,7 +35411,7 @@
         <v>151</v>
       </c>
       <c r="L75" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;H75&amp;","&amp;VLOOKUP(I75,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;H75&amp;","&amp;VLOOKUP(I75,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster070','ゴールドバレッテ',26,180,19,14,0.05,3);</v>
       </c>
     </row>
@@ -35411,7 +35441,7 @@
         <v>34</v>
       </c>
       <c r="L76" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;H76&amp;","&amp;VLOOKUP(I76,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;H76&amp;","&amp;VLOOKUP(I76,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster071','バシリスク',27,110,12,15,0.15,2);</v>
       </c>
     </row>
@@ -35441,7 +35471,7 @@
         <v>151</v>
       </c>
       <c r="L77" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;H77&amp;","&amp;VLOOKUP(I77,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;H77&amp;","&amp;VLOOKUP(I77,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster072','ファイアドレイク',27,150,18,22,0.18,3);</v>
       </c>
     </row>
@@ -35471,7 +35501,7 @@
         <v>36</v>
       </c>
       <c r="L78" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;H78&amp;","&amp;VLOOKUP(I78,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;H78&amp;","&amp;VLOOKUP(I78,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster073','スペクター',28,130,13,17,0.2,5);</v>
       </c>
     </row>
@@ -35501,7 +35531,7 @@
         <v>36</v>
       </c>
       <c r="L79" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;H79&amp;","&amp;VLOOKUP(I79,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;H79&amp;","&amp;VLOOKUP(I79,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster074','ゴースト',28,160,17,20,0.21,5);</v>
       </c>
     </row>
@@ -35531,7 +35561,7 @@
         <v>37</v>
       </c>
       <c r="L80" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;","&amp;VLOOKUP(I80,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;","&amp;VLOOKUP(I80,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster075','ユニコーンヘッド',29,120,15,14,0.15,6);</v>
       </c>
     </row>
@@ -35561,7 +35591,7 @@
         <v>37</v>
       </c>
       <c r="L81" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;H81&amp;","&amp;VLOOKUP(I81,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;H81&amp;","&amp;VLOOKUP(I81,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster076','ゴールドユニコ',29,170,22,25,0.15,6);</v>
       </c>
     </row>
@@ -35591,7 +35621,7 @@
         <v>36</v>
       </c>
       <c r="L82" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;H82&amp;","&amp;VLOOKUP(I82,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;H82&amp;","&amp;VLOOKUP(I82,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster077','シェイプシフター',30,130,12,14,0.14,5);</v>
       </c>
     </row>
@@ -35623,7 +35653,7 @@
         <v>36</v>
       </c>
       <c r="L83" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;H83&amp;","&amp;VLOOKUP(I83,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;H83&amp;","&amp;VLOOKUP(I83,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster078','シャドウゼロ',30,170,15,18,0.15,5);</v>
       </c>
     </row>
@@ -35655,7 +35685,7 @@
         <v>36</v>
       </c>
       <c r="L84" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;H84&amp;","&amp;VLOOKUP(I84,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;H84&amp;","&amp;VLOOKUP(I84,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster079','シャドウゼロワン',30,190,19,23,0.16,5);</v>
       </c>
     </row>
@@ -35685,7 +35715,7 @@
         <v>36</v>
       </c>
       <c r="L85" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;H85&amp;","&amp;VLOOKUP(I85,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;H85&amp;","&amp;VLOOKUP(I85,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster080','ボルダー',31,120,13,14,0.25,5);</v>
       </c>
     </row>
@@ -35718,7 +35748,7 @@
         <v>36</v>
       </c>
       <c r="L86" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;H86&amp;","&amp;VLOOKUP(I86,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;H86&amp;","&amp;VLOOKUP(I86,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster081','パワーボルダー',31,144,16,18,0.25,5);</v>
       </c>
     </row>
@@ -35751,7 +35781,7 @@
         <v>36</v>
       </c>
       <c r="L87" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;H87&amp;","&amp;VLOOKUP(I87,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;H87&amp;","&amp;VLOOKUP(I87,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster082','デスボルダー',31,172,20,23,0.25,5);</v>
       </c>
     </row>
@@ -35781,7 +35811,7 @@
         <v>151</v>
       </c>
       <c r="L88" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;H88&amp;","&amp;VLOOKUP(I88,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;H88&amp;","&amp;VLOOKUP(I88,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster083','パンプキンボム',32,130,17,12,0.18,3);</v>
       </c>
     </row>
@@ -35811,7 +35841,7 @@
         <v>151</v>
       </c>
       <c r="L89" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$48:$I$112,3,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;H89&amp;","&amp;VLOOKUP(I89,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$48:$I$113,3,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;H89&amp;","&amp;VLOOKUP(I89,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster084','グレネードボム',32,160,24,15,0.2,3);</v>
       </c>
     </row>
